--- a/Database/Akrual.xlsx
+++ b/Database/Akrual.xlsx
@@ -601,7 +601,7 @@
       <c r="A3" s="4" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Periode Juli 2025</t>
+            <t xml:space="preserve">Periode Agustus 2025</t>
           </r>
         </is>
       </c>
@@ -979,22 +979,22 @@
       <c r="U9" s="10" t="inlineStr"/>
       <c r="V9" s="10" t="inlineStr"/>
       <c r="W9" s="11" t="n">
-        <v>5.4924374881E10</v>
+        <v>6.1530207365E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>6.595922484E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>6.1520297365E10</v>
+        <v>6.1530207365E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.7236762548405614</v>
+        <v>0.7237928282641735</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>2.3490502635E10</v>
+        <v>2.3480592635E10</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1042,10 +1042,10 @@
       <c r="U10" s="14" t="inlineStr"/>
       <c r="V10" s="14" t="inlineStr"/>
       <c r="W10" s="14" t="n">
-        <v>3.52885832E9</v>
+        <v>4.03336804E9</v>
       </c>
       <c r="X10" s="14" t="n">
-        <v>5.0450972E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y10" s="14" t="inlineStr"/>
       <c r="Z10" s="14" t="n">
@@ -1105,10 +1105,10 @@
       <c r="U11" s="14" t="inlineStr"/>
       <c r="V11" s="14" t="inlineStr"/>
       <c r="W11" s="14" t="n">
-        <v>3.52885832E9</v>
+        <v>4.03336804E9</v>
       </c>
       <c r="X11" s="14" t="n">
-        <v>5.0450972E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y11" s="14" t="inlineStr"/>
       <c r="Z11" s="14" t="n">
@@ -1168,10 +1168,10 @@
       <c r="U12" s="17" t="inlineStr"/>
       <c r="V12" s="17" t="inlineStr"/>
       <c r="W12" s="17" t="n">
-        <v>3.52885832E9</v>
+        <v>4.03336804E9</v>
       </c>
       <c r="X12" s="17" t="n">
-        <v>5.0450972E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y12" s="17" t="inlineStr"/>
       <c r="Z12" s="17" t="n">
@@ -1231,10 +1231,10 @@
       <c r="U13" s="21" t="inlineStr"/>
       <c r="V13" s="21" t="inlineStr"/>
       <c r="W13" s="22" t="n">
-        <v>3.52885832E9</v>
+        <v>4.03336804E9</v>
       </c>
       <c r="X13" s="22" t="n">
-        <v>5.0450972E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y13" s="22" t="inlineStr"/>
       <c r="Z13" s="21" t="n">
@@ -1294,10 +1294,10 @@
       <c r="U14" s="25" t="inlineStr"/>
       <c r="V14" s="25" t="inlineStr"/>
       <c r="W14" s="25" t="n">
-        <v>3.52885832E9</v>
+        <v>4.03336804E9</v>
       </c>
       <c r="X14" s="25" t="n">
-        <v>5.0450972E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y14" s="25" t="inlineStr"/>
       <c r="Z14" s="25" t="n">
@@ -1357,10 +1357,10 @@
       <c r="U15" s="14" t="inlineStr"/>
       <c r="V15" s="14" t="inlineStr"/>
       <c r="W15" s="14" t="n">
-        <v>3.52885832E9</v>
+        <v>4.03336804E9</v>
       </c>
       <c r="X15" s="14" t="n">
-        <v>5.0450972E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y15" s="14" t="inlineStr"/>
       <c r="Z15" s="14" t="n">
@@ -1420,10 +1420,10 @@
       <c r="U16" s="14" t="inlineStr"/>
       <c r="V16" s="14" t="inlineStr"/>
       <c r="W16" s="14" t="n">
-        <v>3.52885832E9</v>
+        <v>4.03336804E9</v>
       </c>
       <c r="X16" s="14" t="n">
-        <v>5.0450972E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y16" s="14" t="inlineStr"/>
       <c r="Z16" s="14" t="n">
@@ -1477,10 +1477,10 @@
       <c r="U17" s="14" t="inlineStr"/>
       <c r="V17" s="14" t="inlineStr"/>
       <c r="W17" s="14" t="n">
-        <v>3.024E8</v>
+        <v>3.456E8</v>
       </c>
       <c r="X17" s="14" t="n">
-        <v>4.32E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y17" s="14" t="inlineStr"/>
       <c r="Z17" s="14" t="n">
@@ -1534,10 +1534,10 @@
       <c r="U18" s="14" t="inlineStr"/>
       <c r="V18" s="14" t="inlineStr"/>
       <c r="W18" s="14" t="n">
-        <v>3.1122E9</v>
+        <v>3.5568E9</v>
       </c>
       <c r="X18" s="14" t="n">
-        <v>4.446E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y18" s="14" t="inlineStr"/>
       <c r="Z18" s="14" t="n">
@@ -1591,10 +1591,10 @@
       <c r="U19" s="14" t="inlineStr"/>
       <c r="V19" s="14" t="inlineStr"/>
       <c r="W19" s="14" t="n">
-        <v>9.8E7</v>
+        <v>1.12E8</v>
       </c>
       <c r="X19" s="14" t="n">
-        <v>1.4E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y19" s="14" t="inlineStr"/>
       <c r="Z19" s="14" t="n">
@@ -1648,10 +1648,10 @@
       <c r="U20" s="14" t="inlineStr"/>
       <c r="V20" s="14" t="inlineStr"/>
       <c r="W20" s="14" t="n">
-        <v>1.625832E7</v>
+        <v>1.896804E7</v>
       </c>
       <c r="X20" s="14" t="n">
-        <v>2709720.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y20" s="14" t="inlineStr"/>
       <c r="Z20" s="14" t="n">
@@ -1711,23 +1711,23 @@
       <c r="U21" s="14" t="inlineStr"/>
       <c r="V21" s="14" t="inlineStr"/>
       <c r="W21" s="14" t="n">
-        <v>5.1395516561E10</v>
+        <v>5.7496839325E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>6.091412764E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>5.7486929325E10</v>
+        <v>5.7496839325E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.7189023584783437</v>
+        <v>0.7190262879081493</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>2.2477934675E10</v>
+        <v>2.2468024675E10</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1774,23 +1774,23 @@
       <c r="U22" s="14" t="inlineStr"/>
       <c r="V22" s="14" t="inlineStr"/>
       <c r="W22" s="14" t="n">
-        <v>5.1395516561E10</v>
+        <v>5.7496839325E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>6.091412764E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>5.7486929325E10</v>
+        <v>5.7496839325E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.7189023584783437</v>
+        <v>0.7190262879081493</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>2.2477934675E10</v>
+        <v>2.2468024675E10</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1837,23 +1837,23 @@
       <c r="U23" s="17" t="inlineStr"/>
       <c r="V23" s="17" t="inlineStr"/>
       <c r="W23" s="17" t="n">
-        <v>5.1394916561E10</v>
+        <v>5.7496239325E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>6.091412764E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>5.7486329325E10</v>
+        <v>5.7496239325E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.718900249303864</v>
+        <v>0.7190241796635557</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>2.2477934675E10</v>
+        <v>2.2468024675E10</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -2561,10 +2561,10 @@
       <c r="U35" s="21" t="inlineStr"/>
       <c r="V35" s="21" t="inlineStr"/>
       <c r="W35" s="22" t="n">
-        <v>3949100.0</v>
+        <v>9686100.0</v>
       </c>
       <c r="X35" s="22" t="n">
-        <v>5737000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y35" s="22" t="inlineStr"/>
       <c r="Z35" s="21" t="n">
@@ -2624,10 +2624,10 @@
       <c r="U36" s="25" t="inlineStr"/>
       <c r="V36" s="25" t="inlineStr"/>
       <c r="W36" s="25" t="n">
-        <v>3949100.0</v>
+        <v>9686100.0</v>
       </c>
       <c r="X36" s="25" t="n">
-        <v>5737000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y36" s="25" t="inlineStr"/>
       <c r="Z36" s="25" t="n">
@@ -2687,10 +2687,10 @@
       <c r="U37" s="14" t="inlineStr"/>
       <c r="V37" s="14" t="inlineStr"/>
       <c r="W37" s="14" t="n">
-        <v>600000.0</v>
+        <v>2400000.0</v>
       </c>
       <c r="X37" s="14" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y37" s="14" t="inlineStr"/>
       <c r="Z37" s="14" t="n">
@@ -2750,10 +2750,10 @@
       <c r="U38" s="14" t="inlineStr"/>
       <c r="V38" s="14" t="inlineStr"/>
       <c r="W38" s="14" t="n">
-        <v>0.0</v>
+        <v>1800000.0</v>
       </c>
       <c r="X38" s="14" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y38" s="14" t="inlineStr"/>
       <c r="Z38" s="14" t="n">
@@ -2807,10 +2807,10 @@
       <c r="U39" s="14" t="inlineStr"/>
       <c r="V39" s="14" t="inlineStr"/>
       <c r="W39" s="14" t="n">
-        <v>0.0</v>
+        <v>1800000.0</v>
       </c>
       <c r="X39" s="14" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y39" s="14" t="inlineStr"/>
       <c r="Z39" s="14" t="n">
@@ -2990,10 +2990,10 @@
       <c r="U42" s="14" t="inlineStr"/>
       <c r="V42" s="14" t="inlineStr"/>
       <c r="W42" s="14" t="n">
-        <v>3349100.0</v>
+        <v>7286100.0</v>
       </c>
       <c r="X42" s="14" t="n">
-        <v>3937000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y42" s="14" t="inlineStr"/>
       <c r="Z42" s="14" t="n">
@@ -3053,10 +3053,10 @@
       <c r="U43" s="14" t="inlineStr"/>
       <c r="V43" s="14" t="inlineStr"/>
       <c r="W43" s="14" t="n">
-        <v>3349100.0</v>
+        <v>7286100.0</v>
       </c>
       <c r="X43" s="14" t="n">
-        <v>3937000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y43" s="14" t="inlineStr"/>
       <c r="Z43" s="14" t="n">
@@ -3110,10 +3110,10 @@
       <c r="U44" s="14" t="inlineStr"/>
       <c r="V44" s="14" t="inlineStr"/>
       <c r="W44" s="14" t="n">
-        <v>2600000.0</v>
+        <v>6537000.0</v>
       </c>
       <c r="X44" s="14" t="n">
-        <v>3937000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y44" s="14" t="inlineStr"/>
       <c r="Z44" s="14" t="n">
@@ -3230,23 +3230,23 @@
       <c r="U46" s="21" t="inlineStr"/>
       <c r="V46" s="21" t="inlineStr"/>
       <c r="W46" s="22" t="n">
-        <v>5.1389917461E10</v>
+        <v>5.7485503225E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>6.085675764E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>5.7475593225E10</v>
+        <v>5.7485503225E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.7189325852583954</v>
+        <v>0.7190565443429414</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>2.2470140775E10</v>
+        <v>2.2460230775E10</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -3293,10 +3293,10 @@
       <c r="U47" s="25" t="inlineStr"/>
       <c r="V47" s="25" t="inlineStr"/>
       <c r="W47" s="25" t="n">
-        <v>4.7473912316E10</v>
+        <v>5.3329786245E10</v>
       </c>
       <c r="X47" s="25" t="n">
-        <v>5.855873929E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y47" s="25" t="inlineStr"/>
       <c r="Z47" s="25" t="n">
@@ -3356,10 +3356,10 @@
       <c r="U48" s="14" t="inlineStr"/>
       <c r="V48" s="14" t="inlineStr"/>
       <c r="W48" s="14" t="n">
-        <v>3.772450364E9</v>
+        <v>4.187549504E9</v>
       </c>
       <c r="X48" s="14" t="n">
-        <v>4.1509914E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y48" s="14" t="inlineStr"/>
       <c r="Z48" s="14" t="n">
@@ -3419,10 +3419,10 @@
       <c r="U49" s="14" t="inlineStr"/>
       <c r="V49" s="14" t="inlineStr"/>
       <c r="W49" s="14" t="n">
-        <v>1.4858101E9</v>
+        <v>1.6503171E9</v>
       </c>
       <c r="X49" s="14" t="n">
-        <v>1.64507E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y49" s="14" t="inlineStr"/>
       <c r="Z49" s="14" t="n">
@@ -3476,10 +3476,10 @@
       <c r="U50" s="14" t="inlineStr"/>
       <c r="V50" s="14" t="inlineStr"/>
       <c r="W50" s="14" t="n">
-        <v>1.1556297E9</v>
+        <v>1.3201367E9</v>
       </c>
       <c r="X50" s="14" t="n">
-        <v>1.64507E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y50" s="14" t="inlineStr"/>
       <c r="Z50" s="14" t="n">
@@ -3653,10 +3653,10 @@
       <c r="U53" s="14" t="inlineStr"/>
       <c r="V53" s="14" t="inlineStr"/>
       <c r="W53" s="14" t="n">
-        <v>17822.0</v>
+        <v>19549.0</v>
       </c>
       <c r="X53" s="14" t="n">
-        <v>1727.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y53" s="14" t="inlineStr"/>
       <c r="Z53" s="14" t="n">
@@ -3710,10 +3710,10 @@
       <c r="U54" s="14" t="inlineStr"/>
       <c r="V54" s="14" t="inlineStr"/>
       <c r="W54" s="14" t="n">
-        <v>13240.0</v>
+        <v>14967.0</v>
       </c>
       <c r="X54" s="14" t="n">
-        <v>1727.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y54" s="14" t="inlineStr"/>
       <c r="Z54" s="14" t="n">
@@ -3887,10 +3887,10 @@
       <c r="U57" s="14" t="inlineStr"/>
       <c r="V57" s="14" t="inlineStr"/>
       <c r="W57" s="14" t="n">
-        <v>1.1333796E8</v>
+        <v>1.2585432E8</v>
       </c>
       <c r="X57" s="14" t="n">
-        <v>1.251636E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y57" s="14" t="inlineStr"/>
       <c r="Z57" s="14" t="n">
@@ -3944,10 +3944,10 @@
       <c r="U58" s="14" t="inlineStr"/>
       <c r="V58" s="14" t="inlineStr"/>
       <c r="W58" s="14" t="n">
-        <v>8.813964E7</v>
+        <v>1.00656E8</v>
       </c>
       <c r="X58" s="14" t="n">
-        <v>1.251636E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y58" s="14" t="inlineStr"/>
       <c r="Z58" s="14" t="n">
@@ -4164,10 +4164,10 @@
       <c r="U62" s="14" t="inlineStr"/>
       <c r="V62" s="14" t="inlineStr"/>
       <c r="W62" s="14" t="n">
-        <v>3.4441812E7</v>
+        <v>3.8237084E7</v>
       </c>
       <c r="X62" s="14" t="n">
-        <v>3795272.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y62" s="14" t="inlineStr"/>
       <c r="Z62" s="14" t="n">
@@ -4221,10 +4221,10 @@
       <c r="U63" s="14" t="inlineStr"/>
       <c r="V63" s="14" t="inlineStr"/>
       <c r="W63" s="14" t="n">
-        <v>2.6765754E7</v>
+        <v>3.0561026E7</v>
       </c>
       <c r="X63" s="14" t="n">
-        <v>3795272.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y63" s="14" t="inlineStr"/>
       <c r="Z63" s="14" t="n">
@@ -4398,10 +4398,10 @@
       <c r="U66" s="14" t="inlineStr"/>
       <c r="V66" s="14" t="inlineStr"/>
       <c r="W66" s="14" t="n">
-        <v>1.62E7</v>
+        <v>1.8E7</v>
       </c>
       <c r="X66" s="14" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y66" s="14" t="inlineStr"/>
       <c r="Z66" s="14" t="n">
@@ -4455,10 +4455,10 @@
       <c r="U67" s="14" t="inlineStr"/>
       <c r="V67" s="14" t="inlineStr"/>
       <c r="W67" s="14" t="n">
-        <v>1.26E7</v>
+        <v>1.44E7</v>
       </c>
       <c r="X67" s="14" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y67" s="14" t="inlineStr"/>
       <c r="Z67" s="14" t="n">
@@ -4632,10 +4632,10 @@
       <c r="U70" s="14" t="inlineStr"/>
       <c r="V70" s="14" t="inlineStr"/>
       <c r="W70" s="14" t="n">
-        <v>1.06486E8</v>
+        <v>1.1796E8</v>
       </c>
       <c r="X70" s="14" t="n">
-        <v>1.1474E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y70" s="14" t="inlineStr"/>
       <c r="Z70" s="14" t="n">
@@ -4689,10 +4689,10 @@
       <c r="U71" s="14" t="inlineStr"/>
       <c r="V71" s="14" t="inlineStr"/>
       <c r="W71" s="14" t="n">
-        <v>8.2458E7</v>
+        <v>9.3932E7</v>
       </c>
       <c r="X71" s="14" t="n">
-        <v>1.1474E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y71" s="14" t="inlineStr"/>
       <c r="Z71" s="14" t="n">
@@ -4866,10 +4866,10 @@
       <c r="U74" s="14" t="inlineStr"/>
       <c r="V74" s="14" t="inlineStr"/>
       <c r="W74" s="14" t="n">
-        <v>1.9186331E7</v>
+        <v>1.9384414E7</v>
       </c>
       <c r="X74" s="14" t="n">
-        <v>198083.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y74" s="14" t="inlineStr"/>
       <c r="Z74" s="14" t="n">
@@ -4923,10 +4923,10 @@
       <c r="U75" s="14" t="inlineStr"/>
       <c r="V75" s="14" t="inlineStr"/>
       <c r="W75" s="14" t="n">
-        <v>1655315.0</v>
+        <v>1853398.0</v>
       </c>
       <c r="X75" s="14" t="n">
-        <v>198083.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y75" s="14" t="inlineStr"/>
       <c r="Z75" s="14" t="n">
@@ -5100,10 +5100,10 @@
       <c r="U78" s="14" t="inlineStr"/>
       <c r="V78" s="14" t="inlineStr"/>
       <c r="W78" s="14" t="n">
-        <v>7.864812E7</v>
+        <v>8.72661E7</v>
       </c>
       <c r="X78" s="14" t="n">
-        <v>8617980.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y78" s="14" t="inlineStr"/>
       <c r="Z78" s="14" t="n">
@@ -5157,10 +5157,10 @@
       <c r="U79" s="14" t="inlineStr"/>
       <c r="V79" s="14" t="inlineStr"/>
       <c r="W79" s="14" t="n">
-        <v>6.112248E7</v>
+        <v>6.974046E7</v>
       </c>
       <c r="X79" s="14" t="n">
-        <v>8617980.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y79" s="14" t="inlineStr"/>
       <c r="Z79" s="14" t="n">
@@ -5334,10 +5334,10 @@
       <c r="U82" s="14" t="inlineStr"/>
       <c r="V82" s="14" t="inlineStr"/>
       <c r="W82" s="14" t="n">
-        <v>1.28383E8</v>
+        <v>1.54008E8</v>
       </c>
       <c r="X82" s="14" t="n">
-        <v>2.5625E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y82" s="14" t="inlineStr"/>
       <c r="Z82" s="14" t="n">
@@ -5391,10 +5391,10 @@
       <c r="U83" s="14" t="inlineStr"/>
       <c r="V83" s="14" t="inlineStr"/>
       <c r="W83" s="14" t="n">
-        <v>8260000.0</v>
+        <v>9450000.0</v>
       </c>
       <c r="X83" s="14" t="n">
-        <v>1190000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y83" s="14" t="inlineStr"/>
       <c r="Z83" s="14" t="n">
@@ -5448,10 +5448,10 @@
       <c r="U84" s="14" t="inlineStr"/>
       <c r="V84" s="14" t="inlineStr"/>
       <c r="W84" s="14" t="n">
-        <v>1.05117E8</v>
+        <v>1.25985E8</v>
       </c>
       <c r="X84" s="14" t="n">
-        <v>2.0868E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y84" s="14" t="inlineStr"/>
       <c r="Z84" s="14" t="n">
@@ -5505,10 +5505,10 @@
       <c r="U85" s="14" t="inlineStr"/>
       <c r="V85" s="14" t="inlineStr"/>
       <c r="W85" s="14" t="n">
-        <v>1.5006E7</v>
+        <v>1.8573E7</v>
       </c>
       <c r="X85" s="14" t="n">
-        <v>3567000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y85" s="14" t="inlineStr"/>
       <c r="Z85" s="14" t="n">
@@ -5568,10 +5568,10 @@
       <c r="U86" s="14" t="inlineStr"/>
       <c r="V86" s="14" t="inlineStr"/>
       <c r="W86" s="14" t="n">
-        <v>3.637E7</v>
+        <v>4.044E7</v>
       </c>
       <c r="X86" s="14" t="n">
-        <v>4070000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y86" s="14" t="inlineStr"/>
       <c r="Z86" s="14" t="n">
@@ -5625,10 +5625,10 @@
       <c r="U87" s="14" t="inlineStr"/>
       <c r="V87" s="14" t="inlineStr"/>
       <c r="W87" s="14" t="n">
-        <v>2.844E7</v>
+        <v>3.251E7</v>
       </c>
       <c r="X87" s="14" t="n">
-        <v>4070000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y87" s="14" t="inlineStr"/>
       <c r="Z87" s="14" t="n">
@@ -5845,10 +5845,10 @@
       <c r="U91" s="14" t="inlineStr"/>
       <c r="V91" s="14" t="inlineStr"/>
       <c r="W91" s="14" t="n">
-        <v>1.753569219E9</v>
+        <v>1.936062937E9</v>
       </c>
       <c r="X91" s="14" t="n">
-        <v>1.82493718E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y91" s="14" t="inlineStr"/>
       <c r="Z91" s="14" t="n">
@@ -5902,10 +5902,10 @@
       <c r="U92" s="14" t="inlineStr"/>
       <c r="V92" s="14" t="inlineStr"/>
       <c r="W92" s="14" t="n">
-        <v>1.310954427E9</v>
+        <v>1.493448145E9</v>
       </c>
       <c r="X92" s="14" t="n">
-        <v>1.82493718E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y92" s="14" t="inlineStr"/>
       <c r="Z92" s="14" t="n">
@@ -7943,10 +7943,10 @@
       <c r="U127" s="14" t="inlineStr"/>
       <c r="V127" s="14" t="inlineStr"/>
       <c r="W127" s="14" t="n">
-        <v>3.169917513E10</v>
+        <v>3.5544999187E10</v>
       </c>
       <c r="X127" s="14" t="n">
-        <v>3.845824057E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y127" s="14" t="inlineStr"/>
       <c r="Z127" s="14" t="n">
@@ -8006,10 +8006,10 @@
       <c r="U128" s="14" t="inlineStr"/>
       <c r="V128" s="14" t="inlineStr"/>
       <c r="W128" s="14" t="n">
-        <v>1.11880769E10</v>
+        <v>1.23832303E10</v>
       </c>
       <c r="X128" s="14" t="n">
-        <v>1.1951534E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y128" s="14" t="inlineStr"/>
       <c r="Z128" s="14" t="n">
@@ -8063,10 +8063,10 @@
       <c r="U129" s="14" t="inlineStr"/>
       <c r="V129" s="14" t="inlineStr"/>
       <c r="W129" s="14" t="n">
-        <v>8.6973235E9</v>
+        <v>9.8924769E9</v>
       </c>
       <c r="X129" s="14" t="n">
-        <v>1.1951534E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y129" s="14" t="inlineStr"/>
       <c r="Z129" s="14" t="n">
@@ -8240,10 +8240,10 @@
       <c r="U132" s="14" t="inlineStr"/>
       <c r="V132" s="14" t="inlineStr"/>
       <c r="W132" s="14" t="n">
-        <v>152199.0</v>
+        <v>168114.0</v>
       </c>
       <c r="X132" s="14" t="n">
-        <v>15915.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y132" s="14" t="inlineStr"/>
       <c r="Z132" s="14" t="n">
@@ -8297,10 +8297,10 @@
       <c r="U133" s="14" t="inlineStr"/>
       <c r="V133" s="14" t="inlineStr"/>
       <c r="W133" s="14" t="n">
-        <v>118425.0</v>
+        <v>134340.0</v>
       </c>
       <c r="X133" s="14" t="n">
-        <v>15915.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y133" s="14" t="inlineStr"/>
       <c r="Z133" s="14" t="n">
@@ -8474,10 +8474,10 @@
       <c r="U136" s="14" t="inlineStr"/>
       <c r="V136" s="14" t="inlineStr"/>
       <c r="W136" s="14" t="n">
-        <v>8.786895E8</v>
+        <v>9.7329066E8</v>
       </c>
       <c r="X136" s="14" t="n">
-        <v>9.460116E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y136" s="14" t="inlineStr"/>
       <c r="Z136" s="14" t="n">
@@ -8531,10 +8531,10 @@
       <c r="U137" s="14" t="inlineStr"/>
       <c r="V137" s="14" t="inlineStr"/>
       <c r="W137" s="14" t="n">
-        <v>6.8370444E8</v>
+        <v>7.783056E8</v>
       </c>
       <c r="X137" s="14" t="n">
-        <v>9.460116E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y137" s="14" t="inlineStr"/>
       <c r="Z137" s="14" t="n">
@@ -8708,10 +8708,10 @@
       <c r="U140" s="14" t="inlineStr"/>
       <c r="V140" s="14" t="inlineStr"/>
       <c r="W140" s="14" t="n">
-        <v>2.7256082E8</v>
+        <v>3.02306822E8</v>
       </c>
       <c r="X140" s="14" t="n">
-        <v>2.9746002E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y140" s="14" t="inlineStr"/>
       <c r="Z140" s="14" t="n">
@@ -8765,10 +8765,10 @@
       <c r="U141" s="14" t="inlineStr"/>
       <c r="V141" s="14" t="inlineStr"/>
       <c r="W141" s="14" t="n">
-        <v>2.12169964E8</v>
+        <v>2.41915966E8</v>
       </c>
       <c r="X141" s="14" t="n">
-        <v>2.9746002E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y141" s="14" t="inlineStr"/>
       <c r="Z141" s="14" t="n">
@@ -8942,10 +8942,10 @@
       <c r="U144" s="14" t="inlineStr"/>
       <c r="V144" s="14" t="inlineStr"/>
       <c r="W144" s="14" t="n">
-        <v>2.41703E9</v>
+        <v>2.67431E9</v>
       </c>
       <c r="X144" s="14" t="n">
-        <v>2.5728E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y144" s="14" t="inlineStr"/>
       <c r="Z144" s="14" t="n">
@@ -9042,10 +9042,10 @@
       <c r="U146" s="14" t="inlineStr"/>
       <c r="V146" s="14" t="inlineStr"/>
       <c r="W146" s="14" t="n">
-        <v>1.87877E9</v>
+        <v>2.13605E9</v>
       </c>
       <c r="X146" s="14" t="n">
-        <v>2.5728E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y146" s="14" t="inlineStr"/>
       <c r="Z146" s="14" t="n">
@@ -9219,10 +9219,10 @@
       <c r="U149" s="14" t="inlineStr"/>
       <c r="V149" s="14" t="inlineStr"/>
       <c r="W149" s="14" t="n">
-        <v>2.14257962E8</v>
+        <v>2.17635496E8</v>
       </c>
       <c r="X149" s="14" t="n">
-        <v>3377534.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y149" s="14" t="inlineStr"/>
       <c r="Z149" s="14" t="n">
@@ -9276,10 +9276,10 @@
       <c r="U150" s="14" t="inlineStr"/>
       <c r="V150" s="14" t="inlineStr"/>
       <c r="W150" s="14" t="n">
-        <v>2.8801831E7</v>
+        <v>3.2179365E7</v>
       </c>
       <c r="X150" s="14" t="n">
-        <v>3377534.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y150" s="14" t="inlineStr"/>
       <c r="Z150" s="14" t="n">
@@ -9453,10 +9453,10 @@
       <c r="U153" s="14" t="inlineStr"/>
       <c r="V153" s="14" t="inlineStr"/>
       <c r="W153" s="14" t="n">
-        <v>6.133974E8</v>
+        <v>6.7995138E8</v>
       </c>
       <c r="X153" s="14" t="n">
-        <v>6.655398E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y153" s="14" t="inlineStr"/>
       <c r="Z153" s="14" t="n">
@@ -9510,10 +9510,10 @@
       <c r="U154" s="14" t="inlineStr"/>
       <c r="V154" s="14" t="inlineStr"/>
       <c r="W154" s="14" t="n">
-        <v>4.7666844E8</v>
+        <v>5.4322242E8</v>
       </c>
       <c r="X154" s="14" t="n">
-        <v>6.655398E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y154" s="14" t="inlineStr"/>
       <c r="Z154" s="14" t="n">
@@ -9687,10 +9687,10 @@
       <c r="U157" s="14" t="inlineStr"/>
       <c r="V157" s="14" t="inlineStr"/>
       <c r="W157" s="14" t="n">
-        <v>1.046634E9</v>
+        <v>1.249247E9</v>
       </c>
       <c r="X157" s="14" t="n">
-        <v>2.02613E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y157" s="14" t="inlineStr"/>
       <c r="Z157" s="14" t="n">
@@ -9744,10 +9744,10 @@
       <c r="U158" s="14" t="inlineStr"/>
       <c r="V158" s="14" t="inlineStr"/>
       <c r="W158" s="14" t="n">
-        <v>9.1E7</v>
+        <v>1.09165E8</v>
       </c>
       <c r="X158" s="14" t="n">
-        <v>1.8165E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y158" s="14" t="inlineStr"/>
       <c r="Z158" s="14" t="n">
@@ -9801,10 +9801,10 @@
       <c r="U159" s="14" t="inlineStr"/>
       <c r="V159" s="14" t="inlineStr"/>
       <c r="W159" s="14" t="n">
-        <v>7.40999E8</v>
+        <v>8.87112E8</v>
       </c>
       <c r="X159" s="14" t="n">
-        <v>1.46113E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y159" s="14" t="inlineStr"/>
       <c r="Z159" s="14" t="n">
@@ -9858,10 +9858,10 @@
       <c r="U160" s="14" t="inlineStr"/>
       <c r="V160" s="14" t="inlineStr"/>
       <c r="W160" s="14" t="n">
-        <v>2.14635E8</v>
+        <v>2.5297E8</v>
       </c>
       <c r="X160" s="14" t="n">
-        <v>3.8335E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y160" s="14" t="inlineStr"/>
       <c r="Z160" s="14" t="n">
@@ -9921,10 +9921,10 @@
       <c r="U161" s="14" t="inlineStr"/>
       <c r="V161" s="14" t="inlineStr"/>
       <c r="W161" s="14" t="n">
-        <v>2035000.0</v>
+        <v>2220000.0</v>
       </c>
       <c r="X161" s="14" t="n">
-        <v>185000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y161" s="14" t="inlineStr"/>
       <c r="Z161" s="14" t="n">
@@ -9978,10 +9978,10 @@
       <c r="U162" s="14" t="inlineStr"/>
       <c r="V162" s="14" t="inlineStr"/>
       <c r="W162" s="14" t="n">
-        <v>1480000.0</v>
+        <v>1665000.0</v>
       </c>
       <c r="X162" s="14" t="n">
-        <v>185000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y162" s="14" t="inlineStr"/>
       <c r="Z162" s="14" t="n">
@@ -10155,10 +10155,10 @@
       <c r="U165" s="14" t="inlineStr"/>
       <c r="V165" s="14" t="inlineStr"/>
       <c r="W165" s="14" t="n">
-        <v>1.5066341349E10</v>
+        <v>1.7062639415E10</v>
       </c>
       <c r="X165" s="14" t="n">
-        <v>1.996298066E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y165" s="14" t="inlineStr"/>
       <c r="Z165" s="14" t="n">
@@ -10212,10 +10212,10 @@
       <c r="U166" s="14" t="inlineStr"/>
       <c r="V166" s="14" t="inlineStr"/>
       <c r="W166" s="14" t="n">
-        <v>1.0293742797E10</v>
+        <v>1.2285354215E10</v>
       </c>
       <c r="X166" s="14" t="n">
-        <v>1.991611418E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y166" s="14" t="inlineStr"/>
       <c r="Z166" s="14" t="n">
@@ -10269,10 +10269,10 @@
       <c r="U167" s="14" t="inlineStr"/>
       <c r="V167" s="14" t="inlineStr"/>
       <c r="W167" s="14" t="n">
-        <v>2.362459773E9</v>
+        <v>2.367146421E9</v>
       </c>
       <c r="X167" s="14" t="n">
-        <v>4686648.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y167" s="14" t="inlineStr"/>
       <c r="Z167" s="14" t="n">
@@ -10389,10 +10389,10 @@
       <c r="U169" s="14" t="inlineStr"/>
       <c r="V169" s="14" t="inlineStr"/>
       <c r="W169" s="14" t="n">
-        <v>1.2002286822E10</v>
+        <v>1.3597237554E10</v>
       </c>
       <c r="X169" s="14" t="n">
-        <v>1.594950732E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y169" s="14" t="inlineStr"/>
       <c r="Z169" s="14" t="n">
@@ -10452,10 +10452,10 @@
       <c r="U170" s="14" t="inlineStr"/>
       <c r="V170" s="14" t="inlineStr"/>
       <c r="W170" s="14" t="n">
-        <v>4.762388866E9</v>
+        <v>5.311759666E9</v>
       </c>
       <c r="X170" s="14" t="n">
-        <v>5.493708E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y170" s="14" t="inlineStr"/>
       <c r="Z170" s="14" t="n">
@@ -10509,10 +10509,10 @@
       <c r="U171" s="14" t="inlineStr"/>
       <c r="V171" s="14" t="inlineStr"/>
       <c r="W171" s="14" t="n">
-        <v>3.6732752E9</v>
+        <v>4.222646E9</v>
       </c>
       <c r="X171" s="14" t="n">
-        <v>5.493708E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y171" s="14" t="inlineStr"/>
       <c r="Z171" s="14" t="n">
@@ -10729,10 +10729,10 @@
       <c r="U175" s="14" t="inlineStr"/>
       <c r="V175" s="14" t="inlineStr"/>
       <c r="W175" s="14" t="n">
-        <v>91671.0</v>
+        <v>101733.0</v>
       </c>
       <c r="X175" s="14" t="n">
-        <v>10062.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y175" s="14" t="inlineStr"/>
       <c r="Z175" s="14" t="n">
@@ -10786,10 +10786,10 @@
       <c r="U176" s="14" t="inlineStr"/>
       <c r="V176" s="14" t="inlineStr"/>
       <c r="W176" s="14" t="n">
-        <v>78551.0</v>
+        <v>88613.0</v>
       </c>
       <c r="X176" s="14" t="n">
-        <v>10062.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y176" s="14" t="inlineStr"/>
       <c r="Z176" s="14" t="n">
@@ -10963,10 +10963,10 @@
       <c r="U179" s="14" t="inlineStr"/>
       <c r="V179" s="14" t="inlineStr"/>
       <c r="W179" s="14" t="n">
-        <v>3.2254353E8</v>
+        <v>3.5985017E8</v>
       </c>
       <c r="X179" s="14" t="n">
-        <v>3.730664E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y179" s="14" t="inlineStr"/>
       <c r="Z179" s="14" t="n">
@@ -11020,10 +11020,10 @@
       <c r="U180" s="14" t="inlineStr"/>
       <c r="V180" s="14" t="inlineStr"/>
       <c r="W180" s="14" t="n">
-        <v>2.4881876E8</v>
+        <v>2.861254E8</v>
       </c>
       <c r="X180" s="14" t="n">
-        <v>3.730664E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y180" s="14" t="inlineStr"/>
       <c r="Z180" s="14" t="n">
@@ -11197,10 +11197,10 @@
       <c r="U183" s="14" t="inlineStr"/>
       <c r="V183" s="14" t="inlineStr"/>
       <c r="W183" s="14" t="n">
-        <v>9.6747576E7</v>
+        <v>1.07733296E8</v>
       </c>
       <c r="X183" s="14" t="n">
-        <v>1.098572E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y183" s="14" t="inlineStr"/>
       <c r="Z183" s="14" t="n">
@@ -11254,10 +11254,10 @@
       <c r="U184" s="14" t="inlineStr"/>
       <c r="V184" s="14" t="inlineStr"/>
       <c r="W184" s="14" t="n">
-        <v>7.4864992E7</v>
+        <v>8.5850712E7</v>
       </c>
       <c r="X184" s="14" t="n">
-        <v>1.098572E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y184" s="14" t="inlineStr"/>
       <c r="Z184" s="14" t="n">
@@ -11431,10 +11431,10 @@
       <c r="U187" s="14" t="inlineStr"/>
       <c r="V187" s="14" t="inlineStr"/>
       <c r="W187" s="14" t="n">
-        <v>7.7817E8</v>
+        <v>8.6691E8</v>
       </c>
       <c r="X187" s="14" t="n">
-        <v>8.874E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y187" s="14" t="inlineStr"/>
       <c r="Z187" s="14" t="n">
@@ -11488,10 +11488,10 @@
       <c r="U188" s="14" t="inlineStr"/>
       <c r="V188" s="14" t="inlineStr"/>
       <c r="W188" s="14" t="n">
-        <v>6.0036E8</v>
+        <v>6.891E8</v>
       </c>
       <c r="X188" s="14" t="n">
-        <v>8.874E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y188" s="14" t="inlineStr"/>
       <c r="Z188" s="14" t="n">
@@ -11665,10 +11665,10 @@
       <c r="U191" s="14" t="inlineStr"/>
       <c r="V191" s="14" t="inlineStr"/>
       <c r="W191" s="14" t="n">
-        <v>2.9241989E8</v>
+        <v>3.2558825E8</v>
       </c>
       <c r="X191" s="14" t="n">
-        <v>3.316836E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y191" s="14" t="inlineStr"/>
       <c r="Z191" s="14" t="n">
@@ -11722,10 +11722,10 @@
       <c r="U192" s="14" t="inlineStr"/>
       <c r="V192" s="14" t="inlineStr"/>
       <c r="W192" s="14" t="n">
-        <v>2.2587798E8</v>
+        <v>2.5904634E8</v>
       </c>
       <c r="X192" s="14" t="n">
-        <v>3.316836E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y192" s="14" t="inlineStr"/>
       <c r="Z192" s="14" t="n">
@@ -11899,10 +11899,10 @@
       <c r="U195" s="14" t="inlineStr"/>
       <c r="V195" s="14" t="inlineStr"/>
       <c r="W195" s="14" t="n">
-        <v>5.34431E8</v>
+        <v>6.44264E8</v>
       </c>
       <c r="X195" s="14" t="n">
-        <v>1.09833E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y195" s="14" t="inlineStr"/>
       <c r="Z195" s="14" t="n">
@@ -11956,10 +11956,10 @@
       <c r="U196" s="14" t="inlineStr"/>
       <c r="V196" s="14" t="inlineStr"/>
       <c r="W196" s="14" t="n">
-        <v>5.11E7</v>
+        <v>6.181E7</v>
       </c>
       <c r="X196" s="14" t="n">
-        <v>1.071E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y196" s="14" t="inlineStr"/>
       <c r="Z196" s="14" t="n">
@@ -12013,10 +12013,10 @@
       <c r="U197" s="14" t="inlineStr"/>
       <c r="V197" s="14" t="inlineStr"/>
       <c r="W197" s="14" t="n">
-        <v>4.83331E8</v>
+        <v>5.82454E8</v>
       </c>
       <c r="X197" s="14" t="n">
-        <v>9.9123E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y197" s="14" t="inlineStr"/>
       <c r="Z197" s="14" t="n">
@@ -12076,10 +12076,10 @@
       <c r="U198" s="14" t="inlineStr"/>
       <c r="V198" s="14" t="inlineStr"/>
       <c r="W198" s="14" t="n">
-        <v>5.215494289E9</v>
+        <v>5.981030439E9</v>
       </c>
       <c r="X198" s="14" t="n">
-        <v>7.6553615E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y198" s="14" t="inlineStr"/>
       <c r="Z198" s="14" t="n">
@@ -12133,10 +12133,10 @@
       <c r="U199" s="14" t="inlineStr"/>
       <c r="V199" s="14" t="inlineStr"/>
       <c r="W199" s="14" t="n">
-        <v>3.641050913E9</v>
+        <v>4.406587063E9</v>
       </c>
       <c r="X199" s="14" t="n">
-        <v>7.6553615E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y199" s="14" t="inlineStr"/>
       <c r="Z199" s="14" t="n">
@@ -12353,23 +12353,23 @@
       <c r="U203" s="25" t="inlineStr"/>
       <c r="V203" s="25" t="inlineStr"/>
       <c r="W203" s="25" t="n">
-        <v>3.916005145E9</v>
+        <v>4.15571698E9</v>
       </c>
       <c r="X203" s="25" t="n">
-        <v>2.29801835E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y203" s="25" t="inlineStr"/>
       <c r="Z203" s="25" t="n">
-        <v>4.14580698E9</v>
+        <v>4.15571698E9</v>
       </c>
       <c r="AA203" s="25" t="inlineStr"/>
       <c r="AB203" s="25" t="inlineStr"/>
       <c r="AC203" s="26" t="n">
-        <v>0.7330226853324455</v>
+        <v>0.7347748785355271</v>
       </c>
       <c r="AD203" s="26" t="inlineStr"/>
       <c r="AE203" s="25" t="n">
-        <v>1.50996202E9</v>
+        <v>1.50005202E9</v>
       </c>
       <c r="AF203" s="25" t="inlineStr"/>
       <c r="AG203" s="25" t="inlineStr"/>
@@ -12416,10 +12416,10 @@
       <c r="U204" s="14" t="inlineStr"/>
       <c r="V204" s="14" t="inlineStr"/>
       <c r="W204" s="14" t="n">
-        <v>3.114927616E9</v>
+        <v>3.258757999E9</v>
       </c>
       <c r="X204" s="14" t="n">
-        <v>1.43830383E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y204" s="14" t="inlineStr"/>
       <c r="Z204" s="14" t="n">
@@ -12479,10 +12479,10 @@
       <c r="U205" s="14" t="inlineStr"/>
       <c r="V205" s="14" t="inlineStr"/>
       <c r="W205" s="14" t="n">
-        <v>4.77118356E8</v>
+        <v>5.46628803E8</v>
       </c>
       <c r="X205" s="14" t="n">
-        <v>6.9510447E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y205" s="14" t="inlineStr"/>
       <c r="Z205" s="14" t="n">
@@ -12536,10 +12536,10 @@
       <c r="U206" s="14" t="inlineStr"/>
       <c r="V206" s="14" t="inlineStr"/>
       <c r="W206" s="14" t="n">
-        <v>4.48E8</v>
+        <v>5.115E8</v>
       </c>
       <c r="X206" s="14" t="n">
-        <v>6.35E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y206" s="14" t="inlineStr"/>
       <c r="Z206" s="14" t="n">
@@ -12593,10 +12593,10 @@
       <c r="U207" s="14" t="inlineStr"/>
       <c r="V207" s="14" t="inlineStr"/>
       <c r="W207" s="14" t="n">
-        <v>2076300.0</v>
+        <v>2419200.0</v>
       </c>
       <c r="X207" s="14" t="n">
-        <v>342900.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y207" s="14" t="inlineStr"/>
       <c r="Z207" s="14" t="n">
@@ -12650,10 +12650,10 @@
       <c r="U208" s="14" t="inlineStr"/>
       <c r="V208" s="14" t="inlineStr"/>
       <c r="W208" s="14" t="n">
-        <v>2.7042056E7</v>
+        <v>3.2709603E7</v>
       </c>
       <c r="X208" s="14" t="n">
-        <v>5667547.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y208" s="14" t="inlineStr"/>
       <c r="Z208" s="14" t="n">
@@ -12713,10 +12713,10 @@
       <c r="U209" s="14" t="inlineStr"/>
       <c r="V209" s="14" t="inlineStr"/>
       <c r="W209" s="14" t="n">
-        <v>4157000.0</v>
+        <v>5144000.0</v>
       </c>
       <c r="X209" s="14" t="n">
-        <v>987000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y209" s="14" t="inlineStr"/>
       <c r="Z209" s="14" t="n">
@@ -12770,10 +12770,10 @@
       <c r="U210" s="14" t="inlineStr"/>
       <c r="V210" s="14" t="inlineStr"/>
       <c r="W210" s="14" t="n">
-        <v>2137000.0</v>
+        <v>2720000.0</v>
       </c>
       <c r="X210" s="14" t="n">
-        <v>583000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y210" s="14" t="inlineStr"/>
       <c r="Z210" s="14" t="n">
@@ -12827,10 +12827,10 @@
       <c r="U211" s="14" t="inlineStr"/>
       <c r="V211" s="14" t="inlineStr"/>
       <c r="W211" s="14" t="n">
-        <v>2020000.0</v>
+        <v>2424000.0</v>
       </c>
       <c r="X211" s="14" t="n">
-        <v>404000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y211" s="14" t="inlineStr"/>
       <c r="Z211" s="14" t="n">
@@ -12890,10 +12890,10 @@
       <c r="U212" s="14" t="inlineStr"/>
       <c r="V212" s="14" t="inlineStr"/>
       <c r="W212" s="14" t="n">
-        <v>8622580.0</v>
+        <v>1.280558E7</v>
       </c>
       <c r="X212" s="14" t="n">
-        <v>4183000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y212" s="14" t="inlineStr"/>
       <c r="Z212" s="14" t="n">
@@ -12947,10 +12947,10 @@
       <c r="U213" s="14" t="inlineStr"/>
       <c r="V213" s="14" t="inlineStr"/>
       <c r="W213" s="14" t="n">
-        <v>8622580.0</v>
+        <v>1.280558E7</v>
       </c>
       <c r="X213" s="14" t="n">
-        <v>4183000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y213" s="14" t="inlineStr"/>
       <c r="Z213" s="14" t="n">
@@ -13130,10 +13130,10 @@
       <c r="U216" s="14" t="inlineStr"/>
       <c r="V216" s="14" t="inlineStr"/>
       <c r="W216" s="14" t="n">
-        <v>2.62303968E9</v>
+        <v>2.692189616E9</v>
       </c>
       <c r="X216" s="14" t="n">
-        <v>6.9149936E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y216" s="14" t="inlineStr"/>
       <c r="Z216" s="14" t="n">
@@ -13187,10 +13187,10 @@
       <c r="U217" s="14" t="inlineStr"/>
       <c r="V217" s="14" t="inlineStr"/>
       <c r="W217" s="14" t="n">
-        <v>2.4455968E8</v>
+        <v>2.85881376E8</v>
       </c>
       <c r="X217" s="14" t="n">
-        <v>4.1321696E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y217" s="14" t="inlineStr"/>
       <c r="Z217" s="14" t="n">
@@ -13244,10 +13244,10 @@
       <c r="U218" s="14" t="inlineStr"/>
       <c r="V218" s="14" t="inlineStr"/>
       <c r="W218" s="14" t="n">
-        <v>5.597624E7</v>
+        <v>6.5444768E7</v>
       </c>
       <c r="X218" s="14" t="n">
-        <v>9468528.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y218" s="14" t="inlineStr"/>
       <c r="Z218" s="14" t="n">
@@ -13301,10 +13301,10 @@
       <c r="U219" s="14" t="inlineStr"/>
       <c r="V219" s="14" t="inlineStr"/>
       <c r="W219" s="14" t="n">
-        <v>8.129932E7</v>
+        <v>9.5029104E7</v>
       </c>
       <c r="X219" s="14" t="n">
-        <v>1.3729784E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y219" s="14" t="inlineStr"/>
       <c r="Z219" s="14" t="n">
@@ -13358,10 +13358,10 @@
       <c r="U220" s="14" t="inlineStr"/>
       <c r="V220" s="14" t="inlineStr"/>
       <c r="W220" s="14" t="n">
-        <v>2.736644E7</v>
+        <v>3.1996368E7</v>
       </c>
       <c r="X220" s="14" t="n">
-        <v>4629928.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y220" s="14" t="inlineStr"/>
       <c r="Z220" s="14" t="n">
@@ -13478,10 +13478,10 @@
       <c r="U222" s="14" t="inlineStr"/>
       <c r="V222" s="14" t="inlineStr"/>
       <c r="W222" s="14" t="n">
-        <v>3.80681131E8</v>
+        <v>4.32620013E8</v>
       </c>
       <c r="X222" s="14" t="n">
-        <v>5.1938882E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y222" s="14" t="inlineStr"/>
       <c r="Z222" s="14" t="n">
@@ -13541,10 +13541,10 @@
       <c r="U223" s="14" t="inlineStr"/>
       <c r="V223" s="14" t="inlineStr"/>
       <c r="W223" s="14" t="n">
-        <v>2.73406741E8</v>
+        <v>3.10883859E8</v>
       </c>
       <c r="X223" s="14" t="n">
-        <v>3.7477118E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y223" s="14" t="inlineStr"/>
       <c r="Z223" s="14" t="n">
@@ -13598,10 +13598,10 @@
       <c r="U224" s="14" t="inlineStr"/>
       <c r="V224" s="14" t="inlineStr"/>
       <c r="W224" s="14" t="n">
-        <v>2.73406741E8</v>
+        <v>3.10883859E8</v>
       </c>
       <c r="X224" s="14" t="n">
-        <v>3.7477118E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y224" s="14" t="inlineStr"/>
       <c r="Z224" s="14" t="n">
@@ -13661,10 +13661,10 @@
       <c r="U225" s="14" t="inlineStr"/>
       <c r="V225" s="14" t="inlineStr"/>
       <c r="W225" s="14" t="n">
-        <v>4161834.0</v>
+        <v>4425348.0</v>
       </c>
       <c r="X225" s="14" t="n">
-        <v>263514.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y225" s="14" t="inlineStr"/>
       <c r="Z225" s="14" t="n">
@@ -13718,10 +13718,10 @@
       <c r="U226" s="14" t="inlineStr"/>
       <c r="V226" s="14" t="inlineStr"/>
       <c r="W226" s="14" t="n">
-        <v>4161834.0</v>
+        <v>4425348.0</v>
       </c>
       <c r="X226" s="14" t="n">
-        <v>263514.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y226" s="14" t="inlineStr"/>
       <c r="Z226" s="14" t="n">
@@ -13781,10 +13781,10 @@
       <c r="U227" s="14" t="inlineStr"/>
       <c r="V227" s="14" t="inlineStr"/>
       <c r="W227" s="14" t="n">
-        <v>2.13328E7</v>
+        <v>2.48451E7</v>
       </c>
       <c r="X227" s="14" t="n">
-        <v>3512300.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y227" s="14" t="inlineStr"/>
       <c r="Z227" s="14" t="n">
@@ -13881,10 +13881,10 @@
       <c r="U229" s="14" t="inlineStr"/>
       <c r="V229" s="14" t="inlineStr"/>
       <c r="W229" s="14" t="n">
-        <v>2.13328E7</v>
+        <v>2.48451E7</v>
       </c>
       <c r="X229" s="14" t="n">
-        <v>3512300.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y229" s="14" t="inlineStr"/>
       <c r="Z229" s="14" t="n">
@@ -13944,10 +13944,10 @@
       <c r="U230" s="14" t="inlineStr"/>
       <c r="V230" s="14" t="inlineStr"/>
       <c r="W230" s="14" t="n">
-        <v>8.1779756E7</v>
+        <v>9.2465706E7</v>
       </c>
       <c r="X230" s="14" t="n">
-        <v>1.068595E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y230" s="14" t="inlineStr"/>
       <c r="Z230" s="14" t="n">
@@ -14001,10 +14001,10 @@
       <c r="U231" s="14" t="inlineStr"/>
       <c r="V231" s="14" t="inlineStr"/>
       <c r="W231" s="14" t="n">
-        <v>5.607995E7</v>
+        <v>6.58569E7</v>
       </c>
       <c r="X231" s="14" t="n">
-        <v>9776950.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y231" s="14" t="inlineStr"/>
       <c r="Z231" s="14" t="n">
@@ -14058,10 +14058,10 @@
       <c r="U232" s="14" t="inlineStr"/>
       <c r="V232" s="14" t="inlineStr"/>
       <c r="W232" s="14" t="n">
-        <v>2.5699806E7</v>
+        <v>2.6608806E7</v>
       </c>
       <c r="X232" s="14" t="n">
-        <v>909000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y232" s="14" t="inlineStr"/>
       <c r="Z232" s="14" t="n">
@@ -14121,10 +14121,10 @@
       <c r="U233" s="14" t="inlineStr"/>
       <c r="V233" s="14" t="inlineStr"/>
       <c r="W233" s="14" t="n">
-        <v>3.51036398E8</v>
+        <v>3.84588968E8</v>
       </c>
       <c r="X233" s="14" t="n">
-        <v>3.355257E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y233" s="14" t="inlineStr"/>
       <c r="Z233" s="14" t="n">
@@ -14481,10 +14481,10 @@
       <c r="U239" s="14" t="inlineStr"/>
       <c r="V239" s="14" t="inlineStr"/>
       <c r="W239" s="14" t="n">
-        <v>9.0095326E7</v>
+        <v>1.10331326E8</v>
       </c>
       <c r="X239" s="14" t="n">
-        <v>2.0236E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y239" s="14" t="inlineStr"/>
       <c r="Z239" s="14" t="n">
@@ -14538,10 +14538,10 @@
       <c r="U240" s="14" t="inlineStr"/>
       <c r="V240" s="14" t="inlineStr"/>
       <c r="W240" s="14" t="n">
-        <v>1.5716622E7</v>
+        <v>1.6931622E7</v>
       </c>
       <c r="X240" s="14" t="n">
-        <v>1215000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y240" s="14" t="inlineStr"/>
       <c r="Z240" s="14" t="n">
@@ -14595,10 +14595,10 @@
       <c r="U241" s="14" t="inlineStr"/>
       <c r="V241" s="14" t="inlineStr"/>
       <c r="W241" s="14" t="n">
-        <v>1.0101299E7</v>
+        <v>1.1156299E7</v>
       </c>
       <c r="X241" s="14" t="n">
-        <v>1055000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y241" s="14" t="inlineStr"/>
       <c r="Z241" s="14" t="n">
@@ -14652,10 +14652,10 @@
       <c r="U242" s="14" t="inlineStr"/>
       <c r="V242" s="14" t="inlineStr"/>
       <c r="W242" s="14" t="n">
-        <v>1.155E7</v>
+        <v>2.5327E7</v>
       </c>
       <c r="X242" s="14" t="n">
-        <v>1.3777E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y242" s="14" t="inlineStr"/>
       <c r="Z242" s="14" t="n">
@@ -15108,10 +15108,10 @@
       <c r="U250" s="14" t="inlineStr"/>
       <c r="V250" s="14" t="inlineStr"/>
       <c r="W250" s="14" t="n">
-        <v>1.1095E7</v>
+        <v>1.5284E7</v>
       </c>
       <c r="X250" s="14" t="n">
-        <v>4189000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y250" s="14" t="inlineStr"/>
       <c r="Z250" s="14" t="n">
@@ -15285,10 +15285,10 @@
       <c r="U253" s="14" t="inlineStr"/>
       <c r="V253" s="14" t="inlineStr"/>
       <c r="W253" s="14" t="n">
-        <v>8.3881357E7</v>
+        <v>8.8386927E7</v>
       </c>
       <c r="X253" s="14" t="n">
-        <v>4505570.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y253" s="14" t="inlineStr"/>
       <c r="Z253" s="14" t="n">
@@ -15556,10 +15556,10 @@
       <c r="U258" s="14" t="inlineStr"/>
       <c r="V258" s="14" t="inlineStr"/>
       <c r="W258" s="14" t="n">
-        <v>6.3191077E7</v>
+        <v>6.6116077E7</v>
       </c>
       <c r="X258" s="14" t="n">
-        <v>2925000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y258" s="14" t="inlineStr"/>
       <c r="Z258" s="14" t="n">
@@ -15613,10 +15613,10 @@
       <c r="U259" s="14" t="inlineStr"/>
       <c r="V259" s="14" t="inlineStr"/>
       <c r="W259" s="14" t="n">
-        <v>2027000.0</v>
+        <v>2177000.0</v>
       </c>
       <c r="X259" s="14" t="n">
-        <v>150000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y259" s="14" t="inlineStr"/>
       <c r="Z259" s="14" t="n">
@@ -15670,10 +15670,10 @@
       <c r="U260" s="14" t="inlineStr"/>
       <c r="V260" s="14" t="inlineStr"/>
       <c r="W260" s="14" t="n">
-        <v>4686025.0</v>
+        <v>4737535.0</v>
       </c>
       <c r="X260" s="14" t="n">
-        <v>51510.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y260" s="14" t="inlineStr"/>
       <c r="Z260" s="14" t="n">
@@ -15841,10 +15841,10 @@
       <c r="U263" s="14" t="inlineStr"/>
       <c r="V263" s="14" t="inlineStr"/>
       <c r="W263" s="14" t="n">
-        <v>2597953.0</v>
+        <v>3707013.0</v>
       </c>
       <c r="X263" s="14" t="n">
-        <v>1109060.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y263" s="14" t="inlineStr"/>
       <c r="Z263" s="14" t="n">
@@ -16012,10 +16012,10 @@
       <c r="U266" s="14" t="inlineStr"/>
       <c r="V266" s="14" t="inlineStr"/>
       <c r="W266" s="14" t="n">
-        <v>0.0</v>
+        <v>270000.0</v>
       </c>
       <c r="X266" s="14" t="n">
-        <v>270000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y266" s="14" t="inlineStr"/>
       <c r="Z266" s="14" t="n">
@@ -16075,10 +16075,10 @@
       <c r="U267" s="14" t="inlineStr"/>
       <c r="V267" s="14" t="inlineStr"/>
       <c r="W267" s="14" t="n">
-        <v>5.2605E7</v>
+        <v>6.1416E7</v>
       </c>
       <c r="X267" s="14" t="n">
-        <v>8811000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y267" s="14" t="inlineStr"/>
       <c r="Z267" s="14" t="n">
@@ -16246,10 +16246,10 @@
       <c r="U270" s="14" t="inlineStr"/>
       <c r="V270" s="14" t="inlineStr"/>
       <c r="W270" s="14" t="n">
-        <v>1965000.0</v>
+        <v>1.0776E7</v>
       </c>
       <c r="X270" s="14" t="n">
-        <v>8811000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y270" s="14" t="inlineStr"/>
       <c r="Z270" s="14" t="n">
@@ -16309,23 +16309,23 @@
       <c r="U271" s="14" t="inlineStr"/>
       <c r="V271" s="14" t="inlineStr"/>
       <c r="W271" s="14" t="n">
-        <v>6.936E7</v>
+        <v>7.975E7</v>
       </c>
       <c r="X271" s="14" t="n">
-        <v>480000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y271" s="14" t="inlineStr"/>
       <c r="Z271" s="14" t="n">
-        <v>6.984E7</v>
+        <v>7.975E7</v>
       </c>
       <c r="AA271" s="14" t="inlineStr"/>
       <c r="AB271" s="14" t="inlineStr"/>
       <c r="AC271" s="15" t="n">
-        <v>0.5283704039945529</v>
+        <v>0.6033439249508247</v>
       </c>
       <c r="AD271" s="15" t="inlineStr"/>
       <c r="AE271" s="14" t="n">
-        <v>6.234E7</v>
+        <v>5.243E7</v>
       </c>
       <c r="AF271" s="14" t="inlineStr"/>
       <c r="AG271" s="14" t="inlineStr"/>
@@ -16372,23 +16372,23 @@
       <c r="U272" s="14" t="inlineStr"/>
       <c r="V272" s="14" t="inlineStr"/>
       <c r="W272" s="14" t="n">
-        <v>6.186E7</v>
+        <v>7.225E7</v>
       </c>
       <c r="X272" s="14" t="n">
-        <v>480000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y272" s="14" t="inlineStr"/>
       <c r="Z272" s="14" t="n">
-        <v>6.234E7</v>
+        <v>7.225E7</v>
       </c>
       <c r="AA272" s="14" t="inlineStr"/>
       <c r="AB272" s="14" t="inlineStr"/>
       <c r="AC272" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5794834777029195</v>
       </c>
       <c r="AD272" s="15" t="inlineStr"/>
       <c r="AE272" s="14" t="n">
-        <v>6.234E7</v>
+        <v>5.243E7</v>
       </c>
       <c r="AF272" s="14" t="inlineStr"/>
       <c r="AG272" s="14" t="inlineStr"/>
@@ -16429,23 +16429,23 @@
       <c r="U273" s="14" t="inlineStr"/>
       <c r="V273" s="14" t="inlineStr"/>
       <c r="W273" s="14" t="n">
-        <v>1.53E7</v>
+        <v>1.785E7</v>
       </c>
       <c r="X273" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y273" s="14" t="inlineStr"/>
       <c r="Z273" s="14" t="n">
-        <v>1.53E7</v>
+        <v>1.785E7</v>
       </c>
       <c r="AA273" s="14" t="inlineStr"/>
       <c r="AB273" s="14" t="inlineStr"/>
       <c r="AC273" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AD273" s="15" t="inlineStr"/>
       <c r="AE273" s="14" t="n">
-        <v>1.53E7</v>
+        <v>1.275E7</v>
       </c>
       <c r="AF273" s="14" t="inlineStr"/>
       <c r="AG273" s="14" t="inlineStr"/>
@@ -16486,23 +16486,23 @@
       <c r="U274" s="14" t="inlineStr"/>
       <c r="V274" s="14" t="inlineStr"/>
       <c r="W274" s="14" t="n">
-        <v>1.488E7</v>
+        <v>1.736E7</v>
       </c>
       <c r="X274" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y274" s="14" t="inlineStr"/>
       <c r="Z274" s="14" t="n">
-        <v>1.488E7</v>
+        <v>1.736E7</v>
       </c>
       <c r="AA274" s="14" t="inlineStr"/>
       <c r="AB274" s="14" t="inlineStr"/>
       <c r="AC274" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AD274" s="15" t="inlineStr"/>
       <c r="AE274" s="14" t="n">
-        <v>1.488E7</v>
+        <v>1.24E7</v>
       </c>
       <c r="AF274" s="14" t="inlineStr"/>
       <c r="AG274" s="14" t="inlineStr"/>
@@ -16543,23 +16543,23 @@
       <c r="U275" s="14" t="inlineStr"/>
       <c r="V275" s="14" t="inlineStr"/>
       <c r="W275" s="14" t="n">
-        <v>7380000.0</v>
+        <v>8610000.0</v>
       </c>
       <c r="X275" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y275" s="14" t="inlineStr"/>
       <c r="Z275" s="14" t="n">
-        <v>7380000.0</v>
+        <v>8610000.0</v>
       </c>
       <c r="AA275" s="14" t="inlineStr"/>
       <c r="AB275" s="14" t="inlineStr"/>
       <c r="AC275" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AD275" s="15" t="inlineStr"/>
       <c r="AE275" s="14" t="n">
-        <v>7380000.0</v>
+        <v>6150000.0</v>
       </c>
       <c r="AF275" s="14" t="inlineStr"/>
       <c r="AG275" s="14" t="inlineStr"/>
@@ -16600,23 +16600,23 @@
       <c r="U276" s="14" t="inlineStr"/>
       <c r="V276" s="14" t="inlineStr"/>
       <c r="W276" s="14" t="n">
-        <v>6420000.0</v>
+        <v>7490000.0</v>
       </c>
       <c r="X276" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y276" s="14" t="inlineStr"/>
       <c r="Z276" s="14" t="n">
-        <v>6420000.0</v>
+        <v>7490000.0</v>
       </c>
       <c r="AA276" s="14" t="inlineStr"/>
       <c r="AB276" s="14" t="inlineStr"/>
       <c r="AC276" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AD276" s="15" t="inlineStr"/>
       <c r="AE276" s="14" t="n">
-        <v>6420000.0</v>
+        <v>5350000.0</v>
       </c>
       <c r="AF276" s="14" t="inlineStr"/>
       <c r="AG276" s="14" t="inlineStr"/>
@@ -16657,23 +16657,23 @@
       <c r="U277" s="14" t="inlineStr"/>
       <c r="V277" s="14" t="inlineStr"/>
       <c r="W277" s="14" t="n">
-        <v>1.44E7</v>
+        <v>1.68E7</v>
       </c>
       <c r="X277" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y277" s="14" t="inlineStr"/>
       <c r="Z277" s="14" t="n">
-        <v>1.44E7</v>
+        <v>1.68E7</v>
       </c>
       <c r="AA277" s="14" t="inlineStr"/>
       <c r="AB277" s="14" t="inlineStr"/>
       <c r="AC277" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="AD277" s="15" t="inlineStr"/>
       <c r="AE277" s="14" t="n">
-        <v>1.44E7</v>
+        <v>1.2E7</v>
       </c>
       <c r="AF277" s="14" t="inlineStr"/>
       <c r="AG277" s="14" t="inlineStr"/>
@@ -16714,10 +16714,10 @@
       <c r="U278" s="14" t="inlineStr"/>
       <c r="V278" s="14" t="inlineStr"/>
       <c r="W278" s="14" t="n">
-        <v>1500000.0</v>
+        <v>1800000.0</v>
       </c>
       <c r="X278" s="14" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y278" s="14" t="inlineStr"/>
       <c r="Z278" s="14" t="n">
@@ -16771,23 +16771,23 @@
       <c r="U279" s="14" t="inlineStr"/>
       <c r="V279" s="14" t="inlineStr"/>
       <c r="W279" s="14" t="n">
-        <v>1980000.0</v>
+        <v>2340000.0</v>
       </c>
       <c r="X279" s="14" t="n">
-        <v>180000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y279" s="14" t="inlineStr"/>
       <c r="Z279" s="14" t="n">
-        <v>2160000.0</v>
+        <v>2340000.0</v>
       </c>
       <c r="AA279" s="14" t="inlineStr"/>
       <c r="AB279" s="14" t="inlineStr"/>
       <c r="AC279" s="15" t="n">
-        <v>0.5</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="AD279" s="15" t="inlineStr"/>
       <c r="AE279" s="14" t="n">
-        <v>2160000.0</v>
+        <v>1980000.0</v>
       </c>
       <c r="AF279" s="14" t="inlineStr"/>
       <c r="AG279" s="14" t="inlineStr"/>

--- a/Database/Akrual.xlsx
+++ b/Database/Akrual.xlsx
@@ -982,19 +982,19 @@
         <v>6.1530207365E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>0.0</v>
+        <v>647800.0</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>6.1530207365E10</v>
+        <v>6.1530855165E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.7237928282641735</v>
+        <v>0.7238004484724294</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>2.3480592635E10</v>
+        <v>2.3479944835E10</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1714,20 +1714,20 @@
         <v>5.7496839325E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>0.0</v>
+        <v>647800.0</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>5.7496839325E10</v>
+        <v>5.7497487125E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.7190262879081493</v>
+        <v>0.7190343889661339</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>2.2468024675E10</v>
+        <v>2.2467376875E10</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1777,20 +1777,20 @@
         <v>5.7496839325E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>0.0</v>
+        <v>647800.0</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>5.7496839325E10</v>
+        <v>5.7497487125E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.7190262879081493</v>
+        <v>0.7190343889661339</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>2.2468024675E10</v>
+        <v>2.2467376875E10</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1840,20 +1840,20 @@
         <v>5.7496239325E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>0.0</v>
+        <v>647800.0</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>5.7496239325E10</v>
+        <v>5.7496887125E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.7190241796635557</v>
+        <v>0.7190322807823255</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>2.2468024675E10</v>
+        <v>2.2467376875E10</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -3233,20 +3233,20 @@
         <v>5.7485503225E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>0.0</v>
+        <v>647800.0</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>5.7485503225E10</v>
+        <v>5.7486151025E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.7190565443429414</v>
+        <v>0.7190646473394064</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>2.2460230775E10</v>
+        <v>2.2459582975E10</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -12356,20 +12356,20 @@
         <v>4.15571698E9</v>
       </c>
       <c r="X203" s="25" t="n">
-        <v>0.0</v>
+        <v>647800.0</v>
       </c>
       <c r="Y203" s="25" t="inlineStr"/>
       <c r="Z203" s="25" t="n">
-        <v>4.15571698E9</v>
+        <v>4.15636478E9</v>
       </c>
       <c r="AA203" s="25" t="inlineStr"/>
       <c r="AB203" s="25" t="inlineStr"/>
       <c r="AC203" s="26" t="n">
-        <v>0.7347748785355271</v>
+        <v>0.7348894164524753</v>
       </c>
       <c r="AD203" s="26" t="inlineStr"/>
       <c r="AE203" s="25" t="n">
-        <v>1.50005202E9</v>
+        <v>1.49940422E9</v>
       </c>
       <c r="AF203" s="25" t="inlineStr"/>
       <c r="AG203" s="25" t="inlineStr"/>
@@ -13481,20 +13481,20 @@
         <v>4.32620013E8</v>
       </c>
       <c r="X222" s="14" t="n">
-        <v>0.0</v>
+        <v>647800.0</v>
       </c>
       <c r="Y222" s="14" t="inlineStr"/>
       <c r="Z222" s="14" t="n">
-        <v>4.32620013E8</v>
+        <v>4.33267813E8</v>
       </c>
       <c r="AA222" s="14" t="inlineStr"/>
       <c r="AB222" s="14" t="inlineStr"/>
       <c r="AC222" s="15" t="n">
-        <v>0.4647829963472282</v>
+        <v>0.4654789568113451</v>
       </c>
       <c r="AD222" s="15" t="inlineStr"/>
       <c r="AE222" s="14" t="n">
-        <v>4.98179987E8</v>
+        <v>4.97532187E8</v>
       </c>
       <c r="AF222" s="14" t="inlineStr"/>
       <c r="AG222" s="14" t="inlineStr"/>
@@ -13784,20 +13784,20 @@
         <v>2.48451E7</v>
       </c>
       <c r="X227" s="14" t="n">
-        <v>0.0</v>
+        <v>647800.0</v>
       </c>
       <c r="Y227" s="14" t="inlineStr"/>
       <c r="Z227" s="14" t="n">
-        <v>2.48451E7</v>
+        <v>2.54929E7</v>
       </c>
       <c r="AA227" s="14" t="inlineStr"/>
       <c r="AB227" s="14" t="inlineStr"/>
       <c r="AC227" s="15" t="n">
-        <v>0.6274015151515151</v>
+        <v>0.6437601010101011</v>
       </c>
       <c r="AD227" s="15" t="inlineStr"/>
       <c r="AE227" s="14" t="n">
-        <v>1.47549E7</v>
+        <v>1.41071E7</v>
       </c>
       <c r="AF227" s="14" t="inlineStr"/>
       <c r="AG227" s="14" t="inlineStr"/>
@@ -13884,20 +13884,20 @@
         <v>2.48451E7</v>
       </c>
       <c r="X229" s="14" t="n">
-        <v>0.0</v>
+        <v>647800.0</v>
       </c>
       <c r="Y229" s="14" t="inlineStr"/>
       <c r="Z229" s="14" t="n">
-        <v>2.48451E7</v>
+        <v>2.54929E7</v>
       </c>
       <c r="AA229" s="14" t="inlineStr"/>
       <c r="AB229" s="14" t="inlineStr"/>
       <c r="AC229" s="15" t="n">
-        <v>0.6274015151515151</v>
+        <v>0.6437601010101011</v>
       </c>
       <c r="AD229" s="15" t="inlineStr"/>
       <c r="AE229" s="14" t="n">
-        <v>1.47549E7</v>
+        <v>1.41071E7</v>
       </c>
       <c r="AF229" s="14" t="inlineStr"/>
       <c r="AG229" s="14" t="inlineStr"/>

--- a/Database/Akrual.xlsx
+++ b/Database/Akrual.xlsx
@@ -982,19 +982,19 @@
         <v>6.1530207365E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>647800.0</v>
+        <v>2.980475502E9</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>6.1530855165E10</v>
+        <v>6.4510682867E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.7238004484724294</v>
+        <v>0.7588527912571109</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>2.3479944835E10</v>
+        <v>2.0500117133E10</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1714,20 +1714,20 @@
         <v>5.7496839325E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>647800.0</v>
+        <v>2.980475502E9</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>5.7497487125E10</v>
+        <v>6.0477314827E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.7190343889661339</v>
+        <v>0.7562986016833594</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>2.2467376875E10</v>
+        <v>1.9487549173E10</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1777,20 +1777,20 @@
         <v>5.7496839325E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>647800.0</v>
+        <v>2.980475502E9</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>5.7497487125E10</v>
+        <v>6.0477314827E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.7190343889661339</v>
+        <v>0.7562986016833594</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>2.2467376875E10</v>
+        <v>1.9487549173E10</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1840,20 +1840,20 @@
         <v>5.7496239325E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>647800.0</v>
+        <v>2.980475502E9</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>5.7496887125E10</v>
+        <v>6.0476714827E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.7190322807823255</v>
+        <v>0.7562967731060465</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>2.2467376875E10</v>
+        <v>1.9487549173E10</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -3233,20 +3233,20 @@
         <v>5.7485503225E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>647800.0</v>
+        <v>2.980475502E9</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>5.7486151025E10</v>
+        <v>6.0465978727E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.7190646473394064</v>
+        <v>0.7563377769100225</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>2.2459582975E10</v>
+        <v>1.9479755273E10</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -3296,20 +3296,20 @@
         <v>5.3329786245E10</v>
       </c>
       <c r="X47" s="25" t="n">
-        <v>0.0</v>
+        <v>2.81070658E9</v>
       </c>
       <c r="Y47" s="25" t="inlineStr"/>
       <c r="Z47" s="25" t="n">
-        <v>5.3329786245E10</v>
+        <v>5.6140492825E10</v>
       </c>
       <c r="AA47" s="25" t="inlineStr"/>
       <c r="AB47" s="25" t="inlineStr"/>
       <c r="AC47" s="26" t="n">
-        <v>0.7178598919113772</v>
+        <v>0.755694161721573</v>
       </c>
       <c r="AD47" s="26" t="inlineStr"/>
       <c r="AE47" s="25" t="n">
-        <v>2.0960178755E10</v>
+        <v>1.8149472175E10</v>
       </c>
       <c r="AF47" s="25" t="inlineStr"/>
       <c r="AG47" s="25" t="inlineStr"/>
@@ -3359,20 +3359,20 @@
         <v>4.187549504E9</v>
       </c>
       <c r="X48" s="14" t="n">
-        <v>0.0</v>
+        <v>5.4407639E7</v>
       </c>
       <c r="Y48" s="14" t="inlineStr"/>
       <c r="Z48" s="14" t="n">
-        <v>4.187549504E9</v>
+        <v>4.241957143E9</v>
       </c>
       <c r="AA48" s="14" t="inlineStr"/>
       <c r="AB48" s="14" t="inlineStr"/>
       <c r="AC48" s="15" t="n">
-        <v>0.6536032120530656</v>
+        <v>0.662095292582897</v>
       </c>
       <c r="AD48" s="15" t="inlineStr"/>
       <c r="AE48" s="14" t="n">
-        <v>2.219318496E9</v>
+        <v>2.164910857E9</v>
       </c>
       <c r="AF48" s="14" t="inlineStr"/>
       <c r="AG48" s="14" t="inlineStr"/>
@@ -3422,20 +3422,20 @@
         <v>1.6503171E9</v>
       </c>
       <c r="X49" s="14" t="n">
-        <v>0.0</v>
+        <v>1.62007E7</v>
       </c>
       <c r="Y49" s="14" t="inlineStr"/>
       <c r="Z49" s="14" t="n">
-        <v>1.6503171E9</v>
+        <v>1.6665178E9</v>
       </c>
       <c r="AA49" s="14" t="inlineStr"/>
       <c r="AB49" s="14" t="inlineStr"/>
       <c r="AC49" s="15" t="n">
-        <v>0.5888925167213339</v>
+        <v>0.5946735093533847</v>
       </c>
       <c r="AD49" s="15" t="inlineStr"/>
       <c r="AE49" s="14" t="n">
-        <v>1.1520909E9</v>
+        <v>1.1358902E9</v>
       </c>
       <c r="AF49" s="14" t="inlineStr"/>
       <c r="AG49" s="14" t="inlineStr"/>
@@ -3479,20 +3479,20 @@
         <v>1.3201367E9</v>
       </c>
       <c r="X50" s="14" t="n">
-        <v>0.0</v>
+        <v>1.62007E7</v>
       </c>
       <c r="Y50" s="14" t="inlineStr"/>
       <c r="Z50" s="14" t="n">
-        <v>1.3201367E9</v>
+        <v>1.3363374E9</v>
       </c>
       <c r="AA50" s="14" t="inlineStr"/>
       <c r="AB50" s="14" t="inlineStr"/>
       <c r="AC50" s="15" t="n">
-        <v>0.5369028387831463</v>
+        <v>0.5434917032698877</v>
       </c>
       <c r="AD50" s="15" t="inlineStr"/>
       <c r="AE50" s="14" t="n">
-        <v>1.1386633E9</v>
+        <v>1.1224626E9</v>
       </c>
       <c r="AF50" s="14" t="inlineStr"/>
       <c r="AG50" s="14" t="inlineStr"/>
@@ -3656,20 +3656,20 @@
         <v>19549.0</v>
       </c>
       <c r="X53" s="14" t="n">
-        <v>0.0</v>
+        <v>121.0</v>
       </c>
       <c r="Y53" s="14" t="inlineStr"/>
       <c r="Z53" s="14" t="n">
-        <v>19549.0</v>
+        <v>19670.0</v>
       </c>
       <c r="AA53" s="14" t="inlineStr"/>
       <c r="AB53" s="14" t="inlineStr"/>
       <c r="AC53" s="15" t="n">
-        <v>0.6516333333333333</v>
+        <v>0.6556666666666666</v>
       </c>
       <c r="AD53" s="15" t="inlineStr"/>
       <c r="AE53" s="14" t="n">
-        <v>10451.0</v>
+        <v>10330.0</v>
       </c>
       <c r="AF53" s="14" t="inlineStr"/>
       <c r="AG53" s="14" t="inlineStr"/>
@@ -3713,20 +3713,20 @@
         <v>14967.0</v>
       </c>
       <c r="X54" s="14" t="n">
-        <v>0.0</v>
+        <v>121.0</v>
       </c>
       <c r="Y54" s="14" t="inlineStr"/>
       <c r="Z54" s="14" t="n">
-        <v>14967.0</v>
+        <v>15088.0</v>
       </c>
       <c r="AA54" s="14" t="inlineStr"/>
       <c r="AB54" s="14" t="inlineStr"/>
       <c r="AC54" s="15" t="n">
-        <v>0.623625</v>
+        <v>0.6286666666666667</v>
       </c>
       <c r="AD54" s="15" t="inlineStr"/>
       <c r="AE54" s="14" t="n">
-        <v>9033.0</v>
+        <v>8912.0</v>
       </c>
       <c r="AF54" s="14" t="inlineStr"/>
       <c r="AG54" s="14" t="inlineStr"/>
@@ -3890,20 +3890,20 @@
         <v>1.2585432E8</v>
       </c>
       <c r="X57" s="14" t="n">
-        <v>0.0</v>
+        <v>1620070.0</v>
       </c>
       <c r="Y57" s="14" t="inlineStr"/>
       <c r="Z57" s="14" t="n">
-        <v>1.2585432E8</v>
+        <v>1.2747439E8</v>
       </c>
       <c r="AA57" s="14" t="inlineStr"/>
       <c r="AB57" s="14" t="inlineStr"/>
       <c r="AC57" s="15" t="n">
-        <v>0.6915072527472528</v>
+        <v>0.7004087362637362</v>
       </c>
       <c r="AD57" s="15" t="inlineStr"/>
       <c r="AE57" s="14" t="n">
-        <v>5.614568E7</v>
+        <v>5.452561E7</v>
       </c>
       <c r="AF57" s="14" t="inlineStr"/>
       <c r="AG57" s="14" t="inlineStr"/>
@@ -3947,20 +3947,20 @@
         <v>1.00656E8</v>
       </c>
       <c r="X58" s="14" t="n">
-        <v>0.0</v>
+        <v>1620070.0</v>
       </c>
       <c r="Y58" s="14" t="inlineStr"/>
       <c r="Z58" s="14" t="n">
-        <v>1.00656E8</v>
+        <v>1.0227607E8</v>
       </c>
       <c r="AA58" s="14" t="inlineStr"/>
       <c r="AB58" s="14" t="inlineStr"/>
       <c r="AC58" s="15" t="n">
-        <v>0.6452307692307693</v>
+        <v>0.6556158333333333</v>
       </c>
       <c r="AD58" s="15" t="inlineStr"/>
       <c r="AE58" s="14" t="n">
-        <v>5.5344E7</v>
+        <v>5.372393E7</v>
       </c>
       <c r="AF58" s="14" t="inlineStr"/>
       <c r="AG58" s="14" t="inlineStr"/>
@@ -4167,20 +4167,20 @@
         <v>3.8237084E7</v>
       </c>
       <c r="X62" s="14" t="n">
-        <v>0.0</v>
+        <v>648028.0</v>
       </c>
       <c r="Y62" s="14" t="inlineStr"/>
       <c r="Z62" s="14" t="n">
-        <v>3.8237084E7</v>
+        <v>3.8885112E7</v>
       </c>
       <c r="AA62" s="14" t="inlineStr"/>
       <c r="AB62" s="14" t="inlineStr"/>
       <c r="AC62" s="15" t="n">
-        <v>0.6828050714285714</v>
+        <v>0.694377</v>
       </c>
       <c r="AD62" s="15" t="inlineStr"/>
       <c r="AE62" s="14" t="n">
-        <v>1.7762916E7</v>
+        <v>1.7114888E7</v>
       </c>
       <c r="AF62" s="14" t="inlineStr"/>
       <c r="AG62" s="14" t="inlineStr"/>
@@ -4224,20 +4224,20 @@
         <v>3.0561026E7</v>
       </c>
       <c r="X63" s="14" t="n">
-        <v>0.0</v>
+        <v>648028.0</v>
       </c>
       <c r="Y63" s="14" t="inlineStr"/>
       <c r="Z63" s="14" t="n">
-        <v>3.0561026E7</v>
+        <v>3.1209054E7</v>
       </c>
       <c r="AA63" s="14" t="inlineStr"/>
       <c r="AB63" s="14" t="inlineStr"/>
       <c r="AC63" s="15" t="n">
-        <v>0.6366880416666667</v>
+        <v>0.650188625</v>
       </c>
       <c r="AD63" s="15" t="inlineStr"/>
       <c r="AE63" s="14" t="n">
-        <v>1.7438974E7</v>
+        <v>1.6790946E7</v>
       </c>
       <c r="AF63" s="14" t="inlineStr"/>
       <c r="AG63" s="14" t="inlineStr"/>
@@ -4401,20 +4401,20 @@
         <v>1.8E7</v>
       </c>
       <c r="X66" s="14" t="n">
-        <v>0.0</v>
+        <v>540000.0</v>
       </c>
       <c r="Y66" s="14" t="inlineStr"/>
       <c r="Z66" s="14" t="n">
-        <v>1.8E7</v>
+        <v>1.854E7</v>
       </c>
       <c r="AA66" s="14" t="inlineStr"/>
       <c r="AB66" s="14" t="inlineStr"/>
       <c r="AC66" s="15" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7357142857142858</v>
       </c>
       <c r="AD66" s="15" t="inlineStr"/>
       <c r="AE66" s="14" t="n">
-        <v>7200000.0</v>
+        <v>6660000.0</v>
       </c>
       <c r="AF66" s="14" t="inlineStr"/>
       <c r="AG66" s="14" t="inlineStr"/>
@@ -4458,20 +4458,20 @@
         <v>1.44E7</v>
       </c>
       <c r="X67" s="14" t="n">
-        <v>0.0</v>
+        <v>540000.0</v>
       </c>
       <c r="Y67" s="14" t="inlineStr"/>
       <c r="Z67" s="14" t="n">
-        <v>1.44E7</v>
+        <v>1.494E7</v>
       </c>
       <c r="AA67" s="14" t="inlineStr"/>
       <c r="AB67" s="14" t="inlineStr"/>
       <c r="AC67" s="15" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6916666666666667</v>
       </c>
       <c r="AD67" s="15" t="inlineStr"/>
       <c r="AE67" s="14" t="n">
-        <v>7200000.0</v>
+        <v>6660000.0</v>
       </c>
       <c r="AF67" s="14" t="inlineStr"/>
       <c r="AG67" s="14" t="inlineStr"/>
@@ -4635,20 +4635,20 @@
         <v>1.1796E8</v>
       </c>
       <c r="X70" s="14" t="n">
-        <v>0.0</v>
+        <v>1100000.0</v>
       </c>
       <c r="Y70" s="14" t="inlineStr"/>
       <c r="Z70" s="14" t="n">
-        <v>1.1796E8</v>
+        <v>1.1906E8</v>
       </c>
       <c r="AA70" s="14" t="inlineStr"/>
       <c r="AB70" s="14" t="inlineStr"/>
       <c r="AC70" s="15" t="n">
-        <v>0.8134387024701063</v>
+        <v>0.8210241769760162</v>
       </c>
       <c r="AD70" s="15" t="inlineStr"/>
       <c r="AE70" s="14" t="n">
-        <v>2.7054E7</v>
+        <v>2.5954E7</v>
       </c>
       <c r="AF70" s="14" t="inlineStr"/>
       <c r="AG70" s="14" t="inlineStr"/>
@@ -4692,20 +4692,20 @@
         <v>9.3932E7</v>
       </c>
       <c r="X71" s="14" t="n">
-        <v>0.0</v>
+        <v>1100000.0</v>
       </c>
       <c r="Y71" s="14" t="inlineStr"/>
       <c r="Z71" s="14" t="n">
-        <v>9.3932E7</v>
+        <v>9.5032E7</v>
       </c>
       <c r="AA71" s="14" t="inlineStr"/>
       <c r="AB71" s="14" t="inlineStr"/>
       <c r="AC71" s="15" t="n">
-        <v>0.7827666666666667</v>
+        <v>0.7919333333333334</v>
       </c>
       <c r="AD71" s="15" t="inlineStr"/>
       <c r="AE71" s="14" t="n">
-        <v>2.6068E7</v>
+        <v>2.4968E7</v>
       </c>
       <c r="AF71" s="14" t="inlineStr"/>
       <c r="AG71" s="14" t="inlineStr"/>
@@ -5103,20 +5103,20 @@
         <v>8.72661E7</v>
       </c>
       <c r="X78" s="14" t="n">
-        <v>0.0</v>
+        <v>1158720.0</v>
       </c>
       <c r="Y78" s="14" t="inlineStr"/>
       <c r="Z78" s="14" t="n">
-        <v>8.72661E7</v>
+        <v>8.842482E7</v>
       </c>
       <c r="AA78" s="14" t="inlineStr"/>
       <c r="AB78" s="14" t="inlineStr"/>
       <c r="AC78" s="15" t="n">
-        <v>0.6925880952380953</v>
+        <v>0.7017842857142857</v>
       </c>
       <c r="AD78" s="15" t="inlineStr"/>
       <c r="AE78" s="14" t="n">
-        <v>3.87339E7</v>
+        <v>3.757518E7</v>
       </c>
       <c r="AF78" s="14" t="inlineStr"/>
       <c r="AG78" s="14" t="inlineStr"/>
@@ -5160,20 +5160,20 @@
         <v>6.974046E7</v>
       </c>
       <c r="X79" s="14" t="n">
-        <v>0.0</v>
+        <v>1158720.0</v>
       </c>
       <c r="Y79" s="14" t="inlineStr"/>
       <c r="Z79" s="14" t="n">
-        <v>6.974046E7</v>
+        <v>7.089918E7</v>
       </c>
       <c r="AA79" s="14" t="inlineStr"/>
       <c r="AB79" s="14" t="inlineStr"/>
       <c r="AC79" s="15" t="n">
-        <v>0.645745</v>
+        <v>0.6564738888888889</v>
       </c>
       <c r="AD79" s="15" t="inlineStr"/>
       <c r="AE79" s="14" t="n">
-        <v>3.825954E7</v>
+        <v>3.710082E7</v>
       </c>
       <c r="AF79" s="14" t="inlineStr"/>
       <c r="AG79" s="14" t="inlineStr"/>
@@ -5337,20 +5337,20 @@
         <v>1.54008E8</v>
       </c>
       <c r="X82" s="14" t="n">
-        <v>0.0</v>
+        <v>3.2765E7</v>
       </c>
       <c r="Y82" s="14" t="inlineStr"/>
       <c r="Z82" s="14" t="n">
-        <v>1.54008E8</v>
+        <v>1.86773E8</v>
       </c>
       <c r="AA82" s="14" t="inlineStr"/>
       <c r="AB82" s="14" t="inlineStr"/>
       <c r="AC82" s="15" t="n">
-        <v>0.4913852515506547</v>
+        <v>0.5959268193072466</v>
       </c>
       <c r="AD82" s="15" t="inlineStr"/>
       <c r="AE82" s="14" t="n">
-        <v>1.59408E8</v>
+        <v>1.26643E8</v>
       </c>
       <c r="AF82" s="14" t="inlineStr"/>
       <c r="AG82" s="14" t="inlineStr"/>
@@ -5394,20 +5394,20 @@
         <v>9450000.0</v>
       </c>
       <c r="X83" s="14" t="n">
-        <v>0.0</v>
+        <v>1610000.0</v>
       </c>
       <c r="Y83" s="14" t="inlineStr"/>
       <c r="Z83" s="14" t="n">
-        <v>9450000.0</v>
+        <v>1.106E7</v>
       </c>
       <c r="AA83" s="14" t="inlineStr"/>
       <c r="AB83" s="14" t="inlineStr"/>
       <c r="AC83" s="15" t="n">
-        <v>0.3125</v>
+        <v>0.36574074074074076</v>
       </c>
       <c r="AD83" s="15" t="inlineStr"/>
       <c r="AE83" s="14" t="n">
-        <v>2.079E7</v>
+        <v>1.918E7</v>
       </c>
       <c r="AF83" s="14" t="inlineStr"/>
       <c r="AG83" s="14" t="inlineStr"/>
@@ -5451,20 +5451,20 @@
         <v>1.25985E8</v>
       </c>
       <c r="X84" s="14" t="n">
-        <v>0.0</v>
+        <v>2.6973E7</v>
       </c>
       <c r="Y84" s="14" t="inlineStr"/>
       <c r="Z84" s="14" t="n">
-        <v>1.25985E8</v>
+        <v>1.52958E8</v>
       </c>
       <c r="AA84" s="14" t="inlineStr"/>
       <c r="AB84" s="14" t="inlineStr"/>
       <c r="AC84" s="15" t="n">
-        <v>0.5085125448028673</v>
+        <v>0.6173835125448028</v>
       </c>
       <c r="AD84" s="15" t="inlineStr"/>
       <c r="AE84" s="14" t="n">
-        <v>1.21767E8</v>
+        <v>9.4794E7</v>
       </c>
       <c r="AF84" s="14" t="inlineStr"/>
       <c r="AG84" s="14" t="inlineStr"/>
@@ -5508,20 +5508,20 @@
         <v>1.8573E7</v>
       </c>
       <c r="X85" s="14" t="n">
-        <v>0.0</v>
+        <v>4182000.0</v>
       </c>
       <c r="Y85" s="14" t="inlineStr"/>
       <c r="Z85" s="14" t="n">
-        <v>1.8573E7</v>
+        <v>2.2755E7</v>
       </c>
       <c r="AA85" s="14" t="inlineStr"/>
       <c r="AB85" s="14" t="inlineStr"/>
       <c r="AC85" s="15" t="n">
-        <v>0.5243055555555556</v>
+        <v>0.6423611111111112</v>
       </c>
       <c r="AD85" s="15" t="inlineStr"/>
       <c r="AE85" s="14" t="n">
-        <v>1.6851E7</v>
+        <v>1.2669E7</v>
       </c>
       <c r="AF85" s="14" t="inlineStr"/>
       <c r="AG85" s="14" t="inlineStr"/>
@@ -5571,20 +5571,20 @@
         <v>4.044E7</v>
       </c>
       <c r="X86" s="14" t="n">
-        <v>0.0</v>
+        <v>375000.0</v>
       </c>
       <c r="Y86" s="14" t="inlineStr"/>
       <c r="Z86" s="14" t="n">
-        <v>4.044E7</v>
+        <v>4.0815E7</v>
       </c>
       <c r="AA86" s="14" t="inlineStr"/>
       <c r="AB86" s="14" t="inlineStr"/>
       <c r="AC86" s="15" t="n">
-        <v>0.6419047619047619</v>
+        <v>0.6478571428571429</v>
       </c>
       <c r="AD86" s="15" t="inlineStr"/>
       <c r="AE86" s="14" t="n">
-        <v>2.256E7</v>
+        <v>2.2185E7</v>
       </c>
       <c r="AF86" s="14" t="inlineStr"/>
       <c r="AG86" s="14" t="inlineStr"/>
@@ -5628,20 +5628,20 @@
         <v>3.251E7</v>
       </c>
       <c r="X87" s="14" t="n">
-        <v>0.0</v>
+        <v>375000.0</v>
       </c>
       <c r="Y87" s="14" t="inlineStr"/>
       <c r="Z87" s="14" t="n">
-        <v>3.251E7</v>
+        <v>3.2885E7</v>
       </c>
       <c r="AA87" s="14" t="inlineStr"/>
       <c r="AB87" s="14" t="inlineStr"/>
       <c r="AC87" s="15" t="n">
-        <v>0.602037037037037</v>
+        <v>0.6089814814814815</v>
       </c>
       <c r="AD87" s="15" t="inlineStr"/>
       <c r="AE87" s="14" t="n">
-        <v>2.149E7</v>
+        <v>2.1115E7</v>
       </c>
       <c r="AF87" s="14" t="inlineStr"/>
       <c r="AG87" s="14" t="inlineStr"/>
@@ -7946,20 +7946,20 @@
         <v>3.5544999187E10</v>
       </c>
       <c r="X127" s="14" t="n">
-        <v>0.0</v>
+        <v>1.897709787E9</v>
       </c>
       <c r="Y127" s="14" t="inlineStr"/>
       <c r="Z127" s="14" t="n">
-        <v>3.5544999187E10</v>
+        <v>3.7442708974E10</v>
       </c>
       <c r="AA127" s="14" t="inlineStr"/>
       <c r="AB127" s="14" t="inlineStr"/>
       <c r="AC127" s="15" t="n">
-        <v>0.672068230837679</v>
+        <v>0.7079492404976508</v>
       </c>
       <c r="AD127" s="15" t="inlineStr"/>
       <c r="AE127" s="14" t="n">
-        <v>1.7343974813E10</v>
+        <v>1.5446265026E10</v>
       </c>
       <c r="AF127" s="14" t="inlineStr"/>
       <c r="AG127" s="14" t="inlineStr"/>
@@ -8009,20 +8009,20 @@
         <v>1.23832303E10</v>
       </c>
       <c r="X128" s="14" t="n">
-        <v>0.0</v>
+        <v>1.190934E9</v>
       </c>
       <c r="Y128" s="14" t="inlineStr"/>
       <c r="Z128" s="14" t="n">
-        <v>1.23832303E10</v>
+        <v>1.35741643E10</v>
       </c>
       <c r="AA128" s="14" t="inlineStr"/>
       <c r="AB128" s="14" t="inlineStr"/>
       <c r="AC128" s="15" t="n">
-        <v>0.9416393177101017</v>
+        <v>1.0321997168975223</v>
       </c>
       <c r="AD128" s="15" t="inlineStr"/>
       <c r="AE128" s="14" t="n">
-        <v>7.674847E8</v>
+        <v>-4.234493E8</v>
       </c>
       <c r="AF128" s="14" t="inlineStr"/>
       <c r="AG128" s="14" t="inlineStr"/>
@@ -8066,20 +8066,20 @@
         <v>9.8924769E9</v>
       </c>
       <c r="X129" s="14" t="n">
-        <v>0.0</v>
+        <v>1.190934E9</v>
       </c>
       <c r="Y129" s="14" t="inlineStr"/>
       <c r="Z129" s="14" t="n">
-        <v>9.8924769E9</v>
+        <v>1.10834109E10</v>
       </c>
       <c r="AA129" s="14" t="inlineStr"/>
       <c r="AB129" s="14" t="inlineStr"/>
       <c r="AC129" s="15" t="n">
-        <v>0.933490665920816</v>
+        <v>1.0458715978113662</v>
       </c>
       <c r="AD129" s="15" t="inlineStr"/>
       <c r="AE129" s="14" t="n">
-        <v>7.048191E8</v>
+        <v>-4.861149E8</v>
       </c>
       <c r="AF129" s="14" t="inlineStr"/>
       <c r="AG129" s="14" t="inlineStr"/>
@@ -8243,20 +8243,20 @@
         <v>168114.0</v>
       </c>
       <c r="X132" s="14" t="n">
-        <v>0.0</v>
+        <v>15731.0</v>
       </c>
       <c r="Y132" s="14" t="inlineStr"/>
       <c r="Z132" s="14" t="n">
-        <v>168114.0</v>
+        <v>183845.0</v>
       </c>
       <c r="AA132" s="14" t="inlineStr"/>
       <c r="AB132" s="14" t="inlineStr"/>
       <c r="AC132" s="15" t="n">
-        <v>0.7063613445378151</v>
+        <v>0.7724579831932773</v>
       </c>
       <c r="AD132" s="15" t="inlineStr"/>
       <c r="AE132" s="14" t="n">
-        <v>69886.0</v>
+        <v>54155.0</v>
       </c>
       <c r="AF132" s="14" t="inlineStr"/>
       <c r="AG132" s="14" t="inlineStr"/>
@@ -8300,20 +8300,20 @@
         <v>134340.0</v>
       </c>
       <c r="X133" s="14" t="n">
-        <v>0.0</v>
+        <v>15731.0</v>
       </c>
       <c r="Y133" s="14" t="inlineStr"/>
       <c r="Z133" s="14" t="n">
-        <v>134340.0</v>
+        <v>150071.0</v>
       </c>
       <c r="AA133" s="14" t="inlineStr"/>
       <c r="AB133" s="14" t="inlineStr"/>
       <c r="AC133" s="15" t="n">
-        <v>0.6585294117647059</v>
+        <v>0.7356421568627451</v>
       </c>
       <c r="AD133" s="15" t="inlineStr"/>
       <c r="AE133" s="14" t="n">
-        <v>69660.0</v>
+        <v>53929.0</v>
       </c>
       <c r="AF133" s="14" t="inlineStr"/>
       <c r="AG133" s="14" t="inlineStr"/>
@@ -8477,20 +8477,20 @@
         <v>9.7329066E8</v>
       </c>
       <c r="X136" s="14" t="n">
-        <v>0.0</v>
+        <v>9.414094E7</v>
       </c>
       <c r="Y136" s="14" t="inlineStr"/>
       <c r="Z136" s="14" t="n">
-        <v>9.7329066E8</v>
+        <v>1.0674316E9</v>
       </c>
       <c r="AA136" s="14" t="inlineStr"/>
       <c r="AB136" s="14" t="inlineStr"/>
       <c r="AC136" s="15" t="n">
-        <v>0.7096282745798549</v>
+        <v>0.7782666326419015</v>
       </c>
       <c r="AD136" s="15" t="inlineStr"/>
       <c r="AE136" s="14" t="n">
-        <v>3.9825934E8</v>
+        <v>3.041184E8</v>
       </c>
       <c r="AF136" s="14" t="inlineStr"/>
       <c r="AG136" s="14" t="inlineStr"/>
@@ -8534,20 +8534,20 @@
         <v>7.783056E8</v>
       </c>
       <c r="X137" s="14" t="n">
-        <v>0.0</v>
+        <v>9.414094E7</v>
       </c>
       <c r="Y137" s="14" t="inlineStr"/>
       <c r="Z137" s="14" t="n">
-        <v>7.783056E8</v>
+        <v>8.7244654E8</v>
       </c>
       <c r="AA137" s="14" t="inlineStr"/>
       <c r="AB137" s="14" t="inlineStr"/>
       <c r="AC137" s="15" t="n">
-        <v>0.6618244897959183</v>
+        <v>0.7418763095238096</v>
       </c>
       <c r="AD137" s="15" t="inlineStr"/>
       <c r="AE137" s="14" t="n">
-        <v>3.976944E8</v>
+        <v>3.0355346E8</v>
       </c>
       <c r="AF137" s="14" t="inlineStr"/>
       <c r="AG137" s="14" t="inlineStr"/>
@@ -8711,20 +8711,20 @@
         <v>3.02306822E8</v>
       </c>
       <c r="X140" s="14" t="n">
-        <v>0.0</v>
+        <v>2.9613198E7</v>
       </c>
       <c r="Y140" s="14" t="inlineStr"/>
       <c r="Z140" s="14" t="n">
-        <v>3.02306822E8</v>
+        <v>3.3192002E8</v>
       </c>
       <c r="AA140" s="14" t="inlineStr"/>
       <c r="AB140" s="14" t="inlineStr"/>
       <c r="AC140" s="15" t="n">
-        <v>0.6977540397500791</v>
+        <v>0.7661042291295929</v>
       </c>
       <c r="AD140" s="15" t="inlineStr"/>
       <c r="AE140" s="14" t="n">
-        <v>1.30950178E8</v>
+        <v>1.0133698E8</v>
       </c>
       <c r="AF140" s="14" t="inlineStr"/>
       <c r="AG140" s="14" t="inlineStr"/>
@@ -8768,20 +8768,20 @@
         <v>2.41915966E8</v>
       </c>
       <c r="X141" s="14" t="n">
-        <v>0.0</v>
+        <v>2.9613198E7</v>
       </c>
       <c r="Y141" s="14" t="inlineStr"/>
       <c r="Z141" s="14" t="n">
-        <v>2.41915966E8</v>
+        <v>2.71529164E8</v>
       </c>
       <c r="AA141" s="14" t="inlineStr"/>
       <c r="AB141" s="14" t="inlineStr"/>
       <c r="AC141" s="15" t="n">
-        <v>0.6503117365591398</v>
+        <v>0.7299171075268818</v>
       </c>
       <c r="AD141" s="15" t="inlineStr"/>
       <c r="AE141" s="14" t="n">
-        <v>1.30084034E8</v>
+        <v>1.00470836E8</v>
       </c>
       <c r="AF141" s="14" t="inlineStr"/>
       <c r="AG141" s="14" t="inlineStr"/>
@@ -8945,20 +8945,20 @@
         <v>2.67431E9</v>
       </c>
       <c r="X144" s="14" t="n">
-        <v>0.0</v>
+        <v>2.5602E8</v>
       </c>
       <c r="Y144" s="14" t="inlineStr"/>
       <c r="Z144" s="14" t="n">
-        <v>2.67431E9</v>
+        <v>2.93033E9</v>
       </c>
       <c r="AA144" s="14" t="inlineStr"/>
       <c r="AB144" s="14" t="inlineStr"/>
       <c r="AC144" s="15" t="n">
-        <v>0.694625974025974</v>
+        <v>0.7611246753246753</v>
       </c>
       <c r="AD144" s="15" t="inlineStr"/>
       <c r="AE144" s="14" t="n">
-        <v>1.17569E9</v>
+        <v>9.1967E8</v>
       </c>
       <c r="AF144" s="14" t="inlineStr"/>
       <c r="AG144" s="14" t="inlineStr"/>
@@ -9045,20 +9045,20 @@
         <v>2.13605E9</v>
       </c>
       <c r="X146" s="14" t="n">
-        <v>0.0</v>
+        <v>2.5602E8</v>
       </c>
       <c r="Y146" s="14" t="inlineStr"/>
       <c r="Z146" s="14" t="n">
-        <v>2.13605E9</v>
+        <v>2.39207E9</v>
       </c>
       <c r="AA146" s="14" t="inlineStr"/>
       <c r="AB146" s="14" t="inlineStr"/>
       <c r="AC146" s="15" t="n">
-        <v>0.6472878787878787</v>
+        <v>0.7248696969696969</v>
       </c>
       <c r="AD146" s="15" t="inlineStr"/>
       <c r="AE146" s="14" t="n">
-        <v>1.16395E9</v>
+        <v>9.0793E8</v>
       </c>
       <c r="AF146" s="14" t="inlineStr"/>
       <c r="AG146" s="14" t="inlineStr"/>
@@ -9222,20 +9222,20 @@
         <v>2.17635496E8</v>
       </c>
       <c r="X149" s="14" t="n">
-        <v>0.0</v>
+        <v>3343198.0</v>
       </c>
       <c r="Y149" s="14" t="inlineStr"/>
       <c r="Z149" s="14" t="n">
-        <v>2.17635496E8</v>
+        <v>2.20978694E8</v>
       </c>
       <c r="AA149" s="14" t="inlineStr"/>
       <c r="AB149" s="14" t="inlineStr"/>
       <c r="AC149" s="15" t="n">
-        <v>0.885669214178163</v>
+        <v>0.8992743824522851</v>
       </c>
       <c r="AD149" s="15" t="inlineStr"/>
       <c r="AE149" s="14" t="n">
-        <v>2.8094504E7</v>
+        <v>2.4751306E7</v>
       </c>
       <c r="AF149" s="14" t="inlineStr"/>
       <c r="AG149" s="14" t="inlineStr"/>
@@ -9279,20 +9279,20 @@
         <v>3.2179365E7</v>
       </c>
       <c r="X150" s="14" t="n">
-        <v>0.0</v>
+        <v>3343198.0</v>
       </c>
       <c r="Y150" s="14" t="inlineStr"/>
       <c r="Z150" s="14" t="n">
-        <v>3.2179365E7</v>
+        <v>3.5522563E7</v>
       </c>
       <c r="AA150" s="14" t="inlineStr"/>
       <c r="AB150" s="14" t="inlineStr"/>
       <c r="AC150" s="15" t="n">
-        <v>0.53632275</v>
+        <v>0.5920427166666666</v>
       </c>
       <c r="AD150" s="15" t="inlineStr"/>
       <c r="AE150" s="14" t="n">
-        <v>2.7820635E7</v>
+        <v>2.4477437E7</v>
       </c>
       <c r="AF150" s="14" t="inlineStr"/>
       <c r="AG150" s="14" t="inlineStr"/>
@@ -9456,20 +9456,20 @@
         <v>6.7995138E8</v>
       </c>
       <c r="X153" s="14" t="n">
-        <v>0.0</v>
+        <v>6.633672E7</v>
       </c>
       <c r="Y153" s="14" t="inlineStr"/>
       <c r="Z153" s="14" t="n">
-        <v>6.7995138E8</v>
+        <v>7.462881E8</v>
       </c>
       <c r="AA153" s="14" t="inlineStr"/>
       <c r="AB153" s="14" t="inlineStr"/>
       <c r="AC153" s="15" t="n">
-        <v>0.6938279387755102</v>
+        <v>0.7615184693877551</v>
       </c>
       <c r="AD153" s="15" t="inlineStr"/>
       <c r="AE153" s="14" t="n">
-        <v>3.0004862E8</v>
+        <v>2.337119E8</v>
       </c>
       <c r="AF153" s="14" t="inlineStr"/>
       <c r="AG153" s="14" t="inlineStr"/>
@@ -9513,20 +9513,20 @@
         <v>5.4322242E8</v>
       </c>
       <c r="X154" s="14" t="n">
-        <v>0.0</v>
+        <v>6.633672E7</v>
       </c>
       <c r="Y154" s="14" t="inlineStr"/>
       <c r="Z154" s="14" t="n">
-        <v>5.4322242E8</v>
+        <v>6.0955914E8</v>
       </c>
       <c r="AA154" s="14" t="inlineStr"/>
       <c r="AB154" s="14" t="inlineStr"/>
       <c r="AC154" s="15" t="n">
-        <v>0.6466933571428571</v>
+        <v>0.7256656428571429</v>
       </c>
       <c r="AD154" s="15" t="inlineStr"/>
       <c r="AE154" s="14" t="n">
-        <v>2.9677758E8</v>
+        <v>2.3044086E8</v>
       </c>
       <c r="AF154" s="14" t="inlineStr"/>
       <c r="AG154" s="14" t="inlineStr"/>
@@ -9690,20 +9690,20 @@
         <v>1.249247E9</v>
       </c>
       <c r="X157" s="14" t="n">
-        <v>0.0</v>
+        <v>2.57121E8</v>
       </c>
       <c r="Y157" s="14" t="inlineStr"/>
       <c r="Z157" s="14" t="n">
-        <v>1.249247E9</v>
+        <v>1.506368E9</v>
       </c>
       <c r="AA157" s="14" t="inlineStr"/>
       <c r="AB157" s="14" t="inlineStr"/>
       <c r="AC157" s="15" t="n">
-        <v>0.47821654753811194</v>
+        <v>0.5766434534418658</v>
       </c>
       <c r="AD157" s="15" t="inlineStr"/>
       <c r="AE157" s="14" t="n">
-        <v>1.363057E9</v>
+        <v>1.105936E9</v>
       </c>
       <c r="AF157" s="14" t="inlineStr"/>
       <c r="AG157" s="14" t="inlineStr"/>
@@ -9747,20 +9747,20 @@
         <v>1.09165E8</v>
       </c>
       <c r="X158" s="14" t="n">
-        <v>0.0</v>
+        <v>2.3555E7</v>
       </c>
       <c r="Y158" s="14" t="inlineStr"/>
       <c r="Z158" s="14" t="n">
-        <v>1.09165E8</v>
+        <v>1.3272E8</v>
       </c>
       <c r="AA158" s="14" t="inlineStr"/>
       <c r="AB158" s="14" t="inlineStr"/>
       <c r="AC158" s="15" t="n">
-        <v>0.4247004357298475</v>
+        <v>0.5163398692810458</v>
       </c>
       <c r="AD158" s="15" t="inlineStr"/>
       <c r="AE158" s="14" t="n">
-        <v>1.47875E8</v>
+        <v>1.2432E8</v>
       </c>
       <c r="AF158" s="14" t="inlineStr"/>
       <c r="AG158" s="14" t="inlineStr"/>
@@ -9804,20 +9804,20 @@
         <v>8.87112E8</v>
       </c>
       <c r="X159" s="14" t="n">
-        <v>0.0</v>
+        <v>1.84038E8</v>
       </c>
       <c r="Y159" s="14" t="inlineStr"/>
       <c r="Z159" s="14" t="n">
-        <v>8.87112E8</v>
+        <v>1.07115E9</v>
       </c>
       <c r="AA159" s="14" t="inlineStr"/>
       <c r="AB159" s="14" t="inlineStr"/>
       <c r="AC159" s="15" t="n">
-        <v>0.4911504424778761</v>
+        <v>0.5930432645034415</v>
       </c>
       <c r="AD159" s="15" t="inlineStr"/>
       <c r="AE159" s="14" t="n">
-        <v>9.1908E8</v>
+        <v>7.35042E8</v>
       </c>
       <c r="AF159" s="14" t="inlineStr"/>
       <c r="AG159" s="14" t="inlineStr"/>
@@ -9861,20 +9861,20 @@
         <v>2.5297E8</v>
       </c>
       <c r="X160" s="14" t="n">
-        <v>0.0</v>
+        <v>4.9528E7</v>
       </c>
       <c r="Y160" s="14" t="inlineStr"/>
       <c r="Z160" s="14" t="n">
-        <v>2.5297E8</v>
+        <v>3.02498E8</v>
       </c>
       <c r="AA160" s="14" t="inlineStr"/>
       <c r="AB160" s="14" t="inlineStr"/>
       <c r="AC160" s="15" t="n">
-        <v>0.46072281959378736</v>
+        <v>0.5509259259259259</v>
       </c>
       <c r="AD160" s="15" t="inlineStr"/>
       <c r="AE160" s="14" t="n">
-        <v>2.96102E8</v>
+        <v>2.46574E8</v>
       </c>
       <c r="AF160" s="14" t="inlineStr"/>
       <c r="AG160" s="14" t="inlineStr"/>
@@ -9924,20 +9924,20 @@
         <v>2220000.0</v>
       </c>
       <c r="X161" s="14" t="n">
-        <v>0.0</v>
+        <v>185000.0</v>
       </c>
       <c r="Y161" s="14" t="inlineStr"/>
       <c r="Z161" s="14" t="n">
-        <v>2220000.0</v>
+        <v>2405000.0</v>
       </c>
       <c r="AA161" s="14" t="inlineStr"/>
       <c r="AB161" s="14" t="inlineStr"/>
       <c r="AC161" s="15" t="n">
-        <v>0.42857142857142855</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="AD161" s="15" t="inlineStr"/>
       <c r="AE161" s="14" t="n">
-        <v>2960000.0</v>
+        <v>2775000.0</v>
       </c>
       <c r="AF161" s="14" t="inlineStr"/>
       <c r="AG161" s="14" t="inlineStr"/>
@@ -9981,20 +9981,20 @@
         <v>1665000.0</v>
       </c>
       <c r="X162" s="14" t="n">
-        <v>0.0</v>
+        <v>185000.0</v>
       </c>
       <c r="Y162" s="14" t="inlineStr"/>
       <c r="Z162" s="14" t="n">
-        <v>1665000.0</v>
+        <v>1850000.0</v>
       </c>
       <c r="AA162" s="14" t="inlineStr"/>
       <c r="AB162" s="14" t="inlineStr"/>
       <c r="AC162" s="15" t="n">
-        <v>0.375</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AD162" s="15" t="inlineStr"/>
       <c r="AE162" s="14" t="n">
-        <v>2775000.0</v>
+        <v>2590000.0</v>
       </c>
       <c r="AF162" s="14" t="inlineStr"/>
       <c r="AG162" s="14" t="inlineStr"/>
@@ -10392,20 +10392,20 @@
         <v>1.3597237554E10</v>
       </c>
       <c r="X169" s="14" t="n">
-        <v>0.0</v>
+        <v>8.58589154E8</v>
       </c>
       <c r="Y169" s="14" t="inlineStr"/>
       <c r="Z169" s="14" t="n">
-        <v>1.3597237554E10</v>
+        <v>1.4455826708E10</v>
       </c>
       <c r="AA169" s="14" t="inlineStr"/>
       <c r="AB169" s="14" t="inlineStr"/>
       <c r="AC169" s="15" t="n">
-        <v>0.9068459674637595</v>
+        <v>0.9641081950979286</v>
       </c>
       <c r="AD169" s="15" t="inlineStr"/>
       <c r="AE169" s="14" t="n">
-        <v>1.396750446E9</v>
+        <v>5.38161292E8</v>
       </c>
       <c r="AF169" s="14" t="inlineStr"/>
       <c r="AG169" s="14" t="inlineStr"/>
@@ -10455,20 +10455,20 @@
         <v>5.311759666E9</v>
       </c>
       <c r="X170" s="14" t="n">
-        <v>0.0</v>
+        <v>5.493708E8</v>
       </c>
       <c r="Y170" s="14" t="inlineStr"/>
       <c r="Z170" s="14" t="n">
-        <v>5.311759666E9</v>
+        <v>5.861130466E9</v>
       </c>
       <c r="AA170" s="14" t="inlineStr"/>
       <c r="AB170" s="14" t="inlineStr"/>
       <c r="AC170" s="15" t="n">
-        <v>1.1913573489125906</v>
+        <v>1.3145739439794482</v>
       </c>
       <c r="AD170" s="15" t="inlineStr"/>
       <c r="AE170" s="14" t="n">
-        <v>-8.53181666E8</v>
+        <v>-1.402552466E9</v>
       </c>
       <c r="AF170" s="14" t="inlineStr"/>
       <c r="AG170" s="14" t="inlineStr"/>
@@ -10512,20 +10512,20 @@
         <v>4.222646E9</v>
       </c>
       <c r="X171" s="14" t="n">
-        <v>0.0</v>
+        <v>5.493708E8</v>
       </c>
       <c r="Y171" s="14" t="inlineStr"/>
       <c r="Z171" s="14" t="n">
-        <v>4.222646E9</v>
+        <v>4.7720168E9</v>
       </c>
       <c r="AA171" s="14" t="inlineStr"/>
       <c r="AB171" s="14" t="inlineStr"/>
       <c r="AC171" s="15" t="n">
-        <v>1.2542045959477153</v>
+        <v>1.4173779669192512</v>
       </c>
       <c r="AD171" s="15" t="inlineStr"/>
       <c r="AE171" s="14" t="n">
-        <v>-8.55854E8</v>
+        <v>-1.4052248E9</v>
       </c>
       <c r="AF171" s="14" t="inlineStr"/>
       <c r="AG171" s="14" t="inlineStr"/>
@@ -10732,20 +10732,20 @@
         <v>101733.0</v>
       </c>
       <c r="X175" s="14" t="n">
-        <v>0.0</v>
+        <v>10038.0</v>
       </c>
       <c r="Y175" s="14" t="inlineStr"/>
       <c r="Z175" s="14" t="n">
-        <v>101733.0</v>
+        <v>111771.0</v>
       </c>
       <c r="AA175" s="14" t="inlineStr"/>
       <c r="AB175" s="14" t="inlineStr"/>
       <c r="AC175" s="15" t="n">
-        <v>0.643879746835443</v>
+        <v>0.7074113924050633</v>
       </c>
       <c r="AD175" s="15" t="inlineStr"/>
       <c r="AE175" s="14" t="n">
-        <v>56267.0</v>
+        <v>46229.0</v>
       </c>
       <c r="AF175" s="14" t="inlineStr"/>
       <c r="AG175" s="14" t="inlineStr"/>
@@ -10789,20 +10789,20 @@
         <v>88613.0</v>
       </c>
       <c r="X176" s="14" t="n">
-        <v>0.0</v>
+        <v>10038.0</v>
       </c>
       <c r="Y176" s="14" t="inlineStr"/>
       <c r="Z176" s="14" t="n">
-        <v>88613.0</v>
+        <v>98651.0</v>
       </c>
       <c r="AA176" s="14" t="inlineStr"/>
       <c r="AB176" s="14" t="inlineStr"/>
       <c r="AC176" s="15" t="n">
-        <v>0.6153680555555555</v>
+        <v>0.6850763888888889</v>
       </c>
       <c r="AD176" s="15" t="inlineStr"/>
       <c r="AE176" s="14" t="n">
-        <v>55387.0</v>
+        <v>45349.0</v>
       </c>
       <c r="AF176" s="14" t="inlineStr"/>
       <c r="AG176" s="14" t="inlineStr"/>
@@ -10966,20 +10966,20 @@
         <v>3.5985017E8</v>
       </c>
       <c r="X179" s="14" t="n">
-        <v>0.0</v>
+        <v>3.730664E7</v>
       </c>
       <c r="Y179" s="14" t="inlineStr"/>
       <c r="Z179" s="14" t="n">
-        <v>3.5985017E8</v>
+        <v>3.9715681E8</v>
       </c>
       <c r="AA179" s="14" t="inlineStr"/>
       <c r="AB179" s="14" t="inlineStr"/>
       <c r="AC179" s="15" t="n">
-        <v>0.9966326654960589</v>
+        <v>1.0999562683830657</v>
       </c>
       <c r="AD179" s="15" t="inlineStr"/>
       <c r="AE179" s="14" t="n">
-        <v>1215830.0</v>
+        <v>-3.609081E7</v>
       </c>
       <c r="AF179" s="14" t="inlineStr"/>
       <c r="AG179" s="14" t="inlineStr"/>
@@ -11023,20 +11023,20 @@
         <v>2.861254E8</v>
       </c>
       <c r="X180" s="14" t="n">
-        <v>0.0</v>
+        <v>3.730664E7</v>
       </c>
       <c r="Y180" s="14" t="inlineStr"/>
       <c r="Z180" s="14" t="n">
-        <v>2.861254E8</v>
+        <v>3.2343204E8</v>
       </c>
       <c r="AA180" s="14" t="inlineStr"/>
       <c r="AB180" s="14" t="inlineStr"/>
       <c r="AC180" s="15" t="n">
-        <v>0.9934909722222223</v>
+        <v>1.1230279166666666</v>
       </c>
       <c r="AD180" s="15" t="inlineStr"/>
       <c r="AE180" s="14" t="n">
-        <v>1874600.0</v>
+        <v>-3.543204E7</v>
       </c>
       <c r="AF180" s="14" t="inlineStr"/>
       <c r="AG180" s="14" t="inlineStr"/>
@@ -11200,20 +11200,20 @@
         <v>1.07733296E8</v>
       </c>
       <c r="X183" s="14" t="n">
-        <v>0.0</v>
+        <v>1.1042896E7</v>
       </c>
       <c r="Y183" s="14" t="inlineStr"/>
       <c r="Z183" s="14" t="n">
-        <v>1.07733296E8</v>
+        <v>1.18776192E8</v>
       </c>
       <c r="AA183" s="14" t="inlineStr"/>
       <c r="AB183" s="14" t="inlineStr"/>
       <c r="AC183" s="15" t="n">
-        <v>0.9613207695327837</v>
+        <v>1.0598582289324339</v>
       </c>
       <c r="AD183" s="15" t="inlineStr"/>
       <c r="AE183" s="14" t="n">
-        <v>4334704.0</v>
+        <v>-6708192.0</v>
       </c>
       <c r="AF183" s="14" t="inlineStr"/>
       <c r="AG183" s="14" t="inlineStr"/>
@@ -11257,20 +11257,20 @@
         <v>8.5850712E7</v>
       </c>
       <c r="X184" s="14" t="n">
-        <v>0.0</v>
+        <v>1.1042896E7</v>
       </c>
       <c r="Y184" s="14" t="inlineStr"/>
       <c r="Z184" s="14" t="n">
-        <v>8.5850712E7</v>
+        <v>9.6893608E7</v>
       </c>
       <c r="AA184" s="14" t="inlineStr"/>
       <c r="AB184" s="14" t="inlineStr"/>
       <c r="AC184" s="15" t="n">
-        <v>0.9538968</v>
+        <v>1.0765956444444444</v>
       </c>
       <c r="AD184" s="15" t="inlineStr"/>
       <c r="AE184" s="14" t="n">
-        <v>4149288.0</v>
+        <v>-6893608.0</v>
       </c>
       <c r="AF184" s="14" t="inlineStr"/>
       <c r="AG184" s="14" t="inlineStr"/>
@@ -11434,20 +11434,20 @@
         <v>8.6691E8</v>
       </c>
       <c r="X187" s="14" t="n">
-        <v>0.0</v>
+        <v>8.874E7</v>
       </c>
       <c r="Y187" s="14" t="inlineStr"/>
       <c r="Z187" s="14" t="n">
-        <v>8.6691E8</v>
+        <v>9.5565E8</v>
       </c>
       <c r="AA187" s="14" t="inlineStr"/>
       <c r="AB187" s="14" t="inlineStr"/>
       <c r="AC187" s="15" t="n">
-        <v>0.9652281381521812</v>
+        <v>1.064032333489211</v>
       </c>
       <c r="AD187" s="15" t="inlineStr"/>
       <c r="AE187" s="14" t="n">
-        <v>3.123E7</v>
+        <v>-5.751E7</v>
       </c>
       <c r="AF187" s="14" t="inlineStr"/>
       <c r="AG187" s="14" t="inlineStr"/>
@@ -11491,20 +11491,20 @@
         <v>6.891E8</v>
       </c>
       <c r="X188" s="14" t="n">
-        <v>0.0</v>
+        <v>8.874E7</v>
       </c>
       <c r="Y188" s="14" t="inlineStr"/>
       <c r="Z188" s="14" t="n">
-        <v>6.891E8</v>
+        <v>7.7784E8</v>
       </c>
       <c r="AA188" s="14" t="inlineStr"/>
       <c r="AB188" s="14" t="inlineStr"/>
       <c r="AC188" s="15" t="n">
-        <v>0.9570833333333333</v>
+        <v>1.0803333333333334</v>
       </c>
       <c r="AD188" s="15" t="inlineStr"/>
       <c r="AE188" s="14" t="n">
-        <v>3.09E7</v>
+        <v>-5.784E7</v>
       </c>
       <c r="AF188" s="14" t="inlineStr"/>
       <c r="AG188" s="14" t="inlineStr"/>
@@ -11668,20 +11668,20 @@
         <v>3.2558825E8</v>
       </c>
       <c r="X191" s="14" t="n">
-        <v>0.0</v>
+        <v>3.324078E7</v>
       </c>
       <c r="Y191" s="14" t="inlineStr"/>
       <c r="Z191" s="14" t="n">
-        <v>3.2558825E8</v>
+        <v>3.5882903E8</v>
       </c>
       <c r="AA191" s="14" t="inlineStr"/>
       <c r="AB191" s="14" t="inlineStr"/>
       <c r="AC191" s="15" t="n">
-        <v>0.9843997544958699</v>
+        <v>1.0849015867064955</v>
       </c>
       <c r="AD191" s="15" t="inlineStr"/>
       <c r="AE191" s="14" t="n">
-        <v>5159750.0</v>
+        <v>-2.808103E7</v>
       </c>
       <c r="AF191" s="14" t="inlineStr"/>
       <c r="AG191" s="14" t="inlineStr"/>
@@ -11725,20 +11725,20 @@
         <v>2.5904634E8</v>
       </c>
       <c r="X192" s="14" t="n">
-        <v>0.0</v>
+        <v>3.324078E7</v>
       </c>
       <c r="Y192" s="14" t="inlineStr"/>
       <c r="Z192" s="14" t="n">
-        <v>2.5904634E8</v>
+        <v>2.9228712E8</v>
       </c>
       <c r="AA192" s="14" t="inlineStr"/>
       <c r="AB192" s="14" t="inlineStr"/>
       <c r="AC192" s="15" t="n">
-        <v>0.9812361363636364</v>
+        <v>1.1071481818181819</v>
       </c>
       <c r="AD192" s="15" t="inlineStr"/>
       <c r="AE192" s="14" t="n">
-        <v>4953660.0</v>
+        <v>-2.828712E7</v>
       </c>
       <c r="AF192" s="14" t="inlineStr"/>
       <c r="AG192" s="14" t="inlineStr"/>
@@ -11902,20 +11902,20 @@
         <v>6.44264E8</v>
       </c>
       <c r="X195" s="14" t="n">
-        <v>0.0</v>
+        <v>1.38878E8</v>
       </c>
       <c r="Y195" s="14" t="inlineStr"/>
       <c r="Z195" s="14" t="n">
-        <v>6.44264E8</v>
+        <v>7.83142E8</v>
       </c>
       <c r="AA195" s="14" t="inlineStr"/>
       <c r="AB195" s="14" t="inlineStr"/>
       <c r="AC195" s="15" t="n">
-        <v>0.6347678726255221</v>
+        <v>0.7715988807440687</v>
       </c>
       <c r="AD195" s="15" t="inlineStr"/>
       <c r="AE195" s="14" t="n">
-        <v>3.70696E8</v>
+        <v>2.31818E8</v>
       </c>
       <c r="AF195" s="14" t="inlineStr"/>
       <c r="AG195" s="14" t="inlineStr"/>
@@ -11959,20 +11959,20 @@
         <v>6.181E7</v>
       </c>
       <c r="X196" s="14" t="n">
-        <v>0.0</v>
+        <v>1.33E7</v>
       </c>
       <c r="Y196" s="14" t="inlineStr"/>
       <c r="Z196" s="14" t="n">
-        <v>6.181E7</v>
+        <v>7.511E7</v>
       </c>
       <c r="AA196" s="14" t="inlineStr"/>
       <c r="AB196" s="14" t="inlineStr"/>
       <c r="AC196" s="15" t="n">
-        <v>0.566025641025641</v>
+        <v>0.6878205128205128</v>
       </c>
       <c r="AD196" s="15" t="inlineStr"/>
       <c r="AE196" s="14" t="n">
-        <v>4.739E7</v>
+        <v>3.409E7</v>
       </c>
       <c r="AF196" s="14" t="inlineStr"/>
       <c r="AG196" s="14" t="inlineStr"/>
@@ -12016,20 +12016,20 @@
         <v>5.82454E8</v>
       </c>
       <c r="X197" s="14" t="n">
-        <v>0.0</v>
+        <v>1.25578E8</v>
       </c>
       <c r="Y197" s="14" t="inlineStr"/>
       <c r="Z197" s="14" t="n">
-        <v>5.82454E8</v>
+        <v>7.08032E8</v>
       </c>
       <c r="AA197" s="14" t="inlineStr"/>
       <c r="AB197" s="14" t="inlineStr"/>
       <c r="AC197" s="15" t="n">
-        <v>0.6430555555555556</v>
+        <v>0.7816993464052288</v>
       </c>
       <c r="AD197" s="15" t="inlineStr"/>
       <c r="AE197" s="14" t="n">
-        <v>3.23306E8</v>
+        <v>1.97728E8</v>
       </c>
       <c r="AF197" s="14" t="inlineStr"/>
       <c r="AG197" s="14" t="inlineStr"/>
@@ -12356,20 +12356,20 @@
         <v>4.15571698E9</v>
       </c>
       <c r="X203" s="25" t="n">
-        <v>647800.0</v>
+        <v>1.69768922E8</v>
       </c>
       <c r="Y203" s="25" t="inlineStr"/>
       <c r="Z203" s="25" t="n">
-        <v>4.15636478E9</v>
+        <v>4.325485902E9</v>
       </c>
       <c r="AA203" s="25" t="inlineStr"/>
       <c r="AB203" s="25" t="inlineStr"/>
       <c r="AC203" s="26" t="n">
-        <v>0.7348894164524753</v>
+        <v>0.7647918261866777</v>
       </c>
       <c r="AD203" s="26" t="inlineStr"/>
       <c r="AE203" s="25" t="n">
-        <v>1.49940422E9</v>
+        <v>1.330283098E9</v>
       </c>
       <c r="AF203" s="25" t="inlineStr"/>
       <c r="AG203" s="25" t="inlineStr"/>
@@ -12419,20 +12419,20 @@
         <v>3.258757999E9</v>
       </c>
       <c r="X204" s="14" t="n">
-        <v>0.0</v>
+        <v>7.5668436E7</v>
       </c>
       <c r="Y204" s="14" t="inlineStr"/>
       <c r="Z204" s="14" t="n">
-        <v>3.258757999E9</v>
+        <v>3.334426435E9</v>
       </c>
       <c r="AA204" s="14" t="inlineStr"/>
       <c r="AB204" s="14" t="inlineStr"/>
       <c r="AC204" s="15" t="n">
-        <v>0.8388798587982353</v>
+        <v>0.8583586684940281</v>
       </c>
       <c r="AD204" s="15" t="inlineStr"/>
       <c r="AE204" s="14" t="n">
-        <v>6.25896001E8</v>
+        <v>5.50227565E8</v>
       </c>
       <c r="AF204" s="14" t="inlineStr"/>
       <c r="AG204" s="14" t="inlineStr"/>
@@ -12482,20 +12482,20 @@
         <v>5.46628803E8</v>
       </c>
       <c r="X205" s="14" t="n">
-        <v>0.0</v>
+        <v>2017000.0</v>
       </c>
       <c r="Y205" s="14" t="inlineStr"/>
       <c r="Z205" s="14" t="n">
-        <v>5.46628803E8</v>
+        <v>5.48645803E8</v>
       </c>
       <c r="AA205" s="14" t="inlineStr"/>
       <c r="AB205" s="14" t="inlineStr"/>
       <c r="AC205" s="15" t="n">
-        <v>0.7439991221109624</v>
+        <v>0.7467443968221777</v>
       </c>
       <c r="AD205" s="15" t="inlineStr"/>
       <c r="AE205" s="14" t="n">
-        <v>1.88088197E8</v>
+        <v>1.86071197E8</v>
       </c>
       <c r="AF205" s="14" t="inlineStr"/>
       <c r="AG205" s="14" t="inlineStr"/>
@@ -12653,20 +12653,20 @@
         <v>3.2709603E7</v>
       </c>
       <c r="X208" s="14" t="n">
-        <v>0.0</v>
+        <v>2017000.0</v>
       </c>
       <c r="Y208" s="14" t="inlineStr"/>
       <c r="Z208" s="14" t="n">
-        <v>3.2709603E7</v>
+        <v>3.4726603E7</v>
       </c>
       <c r="AA208" s="14" t="inlineStr"/>
       <c r="AB208" s="14" t="inlineStr"/>
       <c r="AC208" s="15" t="n">
-        <v>0.6339070348837209</v>
+        <v>0.6729961821705427</v>
       </c>
       <c r="AD208" s="15" t="inlineStr"/>
       <c r="AE208" s="14" t="n">
-        <v>1.8890397E7</v>
+        <v>1.6873397E7</v>
       </c>
       <c r="AF208" s="14" t="inlineStr"/>
       <c r="AG208" s="14" t="inlineStr"/>
@@ -12716,20 +12716,20 @@
         <v>5144000.0</v>
       </c>
       <c r="X209" s="14" t="n">
-        <v>0.0</v>
+        <v>222500.0</v>
       </c>
       <c r="Y209" s="14" t="inlineStr"/>
       <c r="Z209" s="14" t="n">
-        <v>5144000.0</v>
+        <v>5366500.0</v>
       </c>
       <c r="AA209" s="14" t="inlineStr"/>
       <c r="AB209" s="14" t="inlineStr"/>
       <c r="AC209" s="15" t="n">
-        <v>0.3956923076923077</v>
+        <v>0.4128076923076923</v>
       </c>
       <c r="AD209" s="15" t="inlineStr"/>
       <c r="AE209" s="14" t="n">
-        <v>7856000.0</v>
+        <v>7633500.0</v>
       </c>
       <c r="AF209" s="14" t="inlineStr"/>
       <c r="AG209" s="14" t="inlineStr"/>
@@ -12773,20 +12773,20 @@
         <v>2720000.0</v>
       </c>
       <c r="X210" s="14" t="n">
-        <v>0.0</v>
+        <v>222500.0</v>
       </c>
       <c r="Y210" s="14" t="inlineStr"/>
       <c r="Z210" s="14" t="n">
-        <v>2720000.0</v>
+        <v>2942500.0</v>
       </c>
       <c r="AA210" s="14" t="inlineStr"/>
       <c r="AB210" s="14" t="inlineStr"/>
       <c r="AC210" s="15" t="n">
-        <v>0.4689655172413793</v>
+        <v>0.5073275862068966</v>
       </c>
       <c r="AD210" s="15" t="inlineStr"/>
       <c r="AE210" s="14" t="n">
-        <v>3080000.0</v>
+        <v>2857500.0</v>
       </c>
       <c r="AF210" s="14" t="inlineStr"/>
       <c r="AG210" s="14" t="inlineStr"/>
@@ -12893,20 +12893,20 @@
         <v>1.280558E7</v>
       </c>
       <c r="X212" s="14" t="n">
-        <v>0.0</v>
+        <v>4279000.0</v>
       </c>
       <c r="Y212" s="14" t="inlineStr"/>
       <c r="Z212" s="14" t="n">
-        <v>1.280558E7</v>
+        <v>1.708458E7</v>
       </c>
       <c r="AA212" s="14" t="inlineStr"/>
       <c r="AB212" s="14" t="inlineStr"/>
       <c r="AC212" s="15" t="n">
-        <v>0.73178924509972</v>
+        <v>0.9763175038573633</v>
       </c>
       <c r="AD212" s="15" t="inlineStr"/>
       <c r="AE212" s="14" t="n">
-        <v>4693420.0</v>
+        <v>414420.0</v>
       </c>
       <c r="AF212" s="14" t="inlineStr"/>
       <c r="AG212" s="14" t="inlineStr"/>
@@ -12950,20 +12950,20 @@
         <v>1.280558E7</v>
       </c>
       <c r="X213" s="14" t="n">
-        <v>0.0</v>
+        <v>4279000.0</v>
       </c>
       <c r="Y213" s="14" t="inlineStr"/>
       <c r="Z213" s="14" t="n">
-        <v>1.280558E7</v>
+        <v>1.708458E7</v>
       </c>
       <c r="AA213" s="14" t="inlineStr"/>
       <c r="AB213" s="14" t="inlineStr"/>
       <c r="AC213" s="15" t="n">
-        <v>0.73178924509972</v>
+        <v>0.9763175038573633</v>
       </c>
       <c r="AD213" s="15" t="inlineStr"/>
       <c r="AE213" s="14" t="n">
-        <v>4693420.0</v>
+        <v>414420.0</v>
       </c>
       <c r="AF213" s="14" t="inlineStr"/>
       <c r="AG213" s="14" t="inlineStr"/>
@@ -13133,20 +13133,20 @@
         <v>2.692189616E9</v>
       </c>
       <c r="X216" s="14" t="n">
-        <v>0.0</v>
+        <v>6.9149936E7</v>
       </c>
       <c r="Y216" s="14" t="inlineStr"/>
       <c r="Z216" s="14" t="n">
-        <v>2.692189616E9</v>
+        <v>2.761339552E9</v>
       </c>
       <c r="AA216" s="14" t="inlineStr"/>
       <c r="AB216" s="14" t="inlineStr"/>
       <c r="AC216" s="15" t="n">
-        <v>0.8638675359496965</v>
+        <v>0.8860563091580836</v>
       </c>
       <c r="AD216" s="15" t="inlineStr"/>
       <c r="AE216" s="14" t="n">
-        <v>4.24248384E8</v>
+        <v>3.55098448E8</v>
       </c>
       <c r="AF216" s="14" t="inlineStr"/>
       <c r="AG216" s="14" t="inlineStr"/>
@@ -13190,20 +13190,20 @@
         <v>2.85881376E8</v>
       </c>
       <c r="X217" s="14" t="n">
-        <v>0.0</v>
+        <v>4.1321696E7</v>
       </c>
       <c r="Y217" s="14" t="inlineStr"/>
       <c r="Z217" s="14" t="n">
-        <v>2.85881376E8</v>
+        <v>3.27203072E8</v>
       </c>
       <c r="AA217" s="14" t="inlineStr"/>
       <c r="AB217" s="14" t="inlineStr"/>
       <c r="AC217" s="15" t="n">
-        <v>0.5294099555555556</v>
+        <v>0.6059316148148148</v>
       </c>
       <c r="AD217" s="15" t="inlineStr"/>
       <c r="AE217" s="14" t="n">
-        <v>2.54118624E8</v>
+        <v>2.12796928E8</v>
       </c>
       <c r="AF217" s="14" t="inlineStr"/>
       <c r="AG217" s="14" t="inlineStr"/>
@@ -13247,20 +13247,20 @@
         <v>6.5444768E7</v>
       </c>
       <c r="X218" s="14" t="n">
-        <v>0.0</v>
+        <v>9468528.0</v>
       </c>
       <c r="Y218" s="14" t="inlineStr"/>
       <c r="Z218" s="14" t="n">
-        <v>6.5444768E7</v>
+        <v>7.4913296E7</v>
       </c>
       <c r="AA218" s="14" t="inlineStr"/>
       <c r="AB218" s="14" t="inlineStr"/>
       <c r="AC218" s="15" t="n">
-        <v>0.5338072430668842</v>
+        <v>0.6110383034257749</v>
       </c>
       <c r="AD218" s="15" t="inlineStr"/>
       <c r="AE218" s="14" t="n">
-        <v>5.7155232E7</v>
+        <v>4.7686704E7</v>
       </c>
       <c r="AF218" s="14" t="inlineStr"/>
       <c r="AG218" s="14" t="inlineStr"/>
@@ -13304,20 +13304,20 @@
         <v>9.5029104E7</v>
       </c>
       <c r="X219" s="14" t="n">
-        <v>0.0</v>
+        <v>1.3729784E7</v>
       </c>
       <c r="Y219" s="14" t="inlineStr"/>
       <c r="Z219" s="14" t="n">
-        <v>9.5029104E7</v>
+        <v>1.08758888E8</v>
       </c>
       <c r="AA219" s="14" t="inlineStr"/>
       <c r="AB219" s="14" t="inlineStr"/>
       <c r="AC219" s="15" t="n">
-        <v>0.5279394666666667</v>
+        <v>0.6042160444444444</v>
       </c>
       <c r="AD219" s="15" t="inlineStr"/>
       <c r="AE219" s="14" t="n">
-        <v>8.4970896E7</v>
+        <v>7.1241112E7</v>
       </c>
       <c r="AF219" s="14" t="inlineStr"/>
       <c r="AG219" s="14" t="inlineStr"/>
@@ -13361,20 +13361,20 @@
         <v>3.1996368E7</v>
       </c>
       <c r="X220" s="14" t="n">
-        <v>0.0</v>
+        <v>4629928.0</v>
       </c>
       <c r="Y220" s="14" t="inlineStr"/>
       <c r="Z220" s="14" t="n">
-        <v>3.1996368E7</v>
+        <v>3.6626296E7</v>
       </c>
       <c r="AA220" s="14" t="inlineStr"/>
       <c r="AB220" s="14" t="inlineStr"/>
       <c r="AC220" s="15" t="n">
-        <v>0.5332728</v>
+        <v>0.6104382666666667</v>
       </c>
       <c r="AD220" s="15" t="inlineStr"/>
       <c r="AE220" s="14" t="n">
-        <v>2.8003632E7</v>
+        <v>2.3373704E7</v>
       </c>
       <c r="AF220" s="14" t="inlineStr"/>
       <c r="AG220" s="14" t="inlineStr"/>
@@ -13481,20 +13481,20 @@
         <v>4.32620013E8</v>
       </c>
       <c r="X222" s="14" t="n">
-        <v>647800.0</v>
+        <v>5.1920911E7</v>
       </c>
       <c r="Y222" s="14" t="inlineStr"/>
       <c r="Z222" s="14" t="n">
-        <v>4.33267813E8</v>
+        <v>4.84540924E8</v>
       </c>
       <c r="AA222" s="14" t="inlineStr"/>
       <c r="AB222" s="14" t="inlineStr"/>
       <c r="AC222" s="15" t="n">
-        <v>0.4654789568113451</v>
+        <v>0.5205639492909325</v>
       </c>
       <c r="AD222" s="15" t="inlineStr"/>
       <c r="AE222" s="14" t="n">
-        <v>4.97532187E8</v>
+        <v>4.46259076E8</v>
       </c>
       <c r="AF222" s="14" t="inlineStr"/>
       <c r="AG222" s="14" t="inlineStr"/>
@@ -13544,20 +13544,20 @@
         <v>3.10883859E8</v>
       </c>
       <c r="X223" s="14" t="n">
-        <v>0.0</v>
+        <v>4.1758847E7</v>
       </c>
       <c r="Y223" s="14" t="inlineStr"/>
       <c r="Z223" s="14" t="n">
-        <v>3.10883859E8</v>
+        <v>3.52642706E8</v>
       </c>
       <c r="AA223" s="14" t="inlineStr"/>
       <c r="AB223" s="14" t="inlineStr"/>
       <c r="AC223" s="15" t="n">
-        <v>0.42470472540983606</v>
+        <v>0.4817523306010929</v>
       </c>
       <c r="AD223" s="15" t="inlineStr"/>
       <c r="AE223" s="14" t="n">
-        <v>4.21116141E8</v>
+        <v>3.79357294E8</v>
       </c>
       <c r="AF223" s="14" t="inlineStr"/>
       <c r="AG223" s="14" t="inlineStr"/>
@@ -13601,20 +13601,20 @@
         <v>3.10883859E8</v>
       </c>
       <c r="X224" s="14" t="n">
-        <v>0.0</v>
+        <v>4.1758847E7</v>
       </c>
       <c r="Y224" s="14" t="inlineStr"/>
       <c r="Z224" s="14" t="n">
-        <v>3.10883859E8</v>
+        <v>3.52642706E8</v>
       </c>
       <c r="AA224" s="14" t="inlineStr"/>
       <c r="AB224" s="14" t="inlineStr"/>
       <c r="AC224" s="15" t="n">
-        <v>0.42470472540983606</v>
+        <v>0.4817523306010929</v>
       </c>
       <c r="AD224" s="15" t="inlineStr"/>
       <c r="AE224" s="14" t="n">
-        <v>4.21116141E8</v>
+        <v>3.79357294E8</v>
       </c>
       <c r="AF224" s="14" t="inlineStr"/>
       <c r="AG224" s="14" t="inlineStr"/>
@@ -13664,20 +13664,20 @@
         <v>4425348.0</v>
       </c>
       <c r="X225" s="14" t="n">
-        <v>0.0</v>
+        <v>263514.0</v>
       </c>
       <c r="Y225" s="14" t="inlineStr"/>
       <c r="Z225" s="14" t="n">
-        <v>4425348.0</v>
+        <v>4688862.0</v>
       </c>
       <c r="AA225" s="14" t="inlineStr"/>
       <c r="AB225" s="14" t="inlineStr"/>
       <c r="AC225" s="15" t="n">
-        <v>0.9219475</v>
+        <v>0.97684625</v>
       </c>
       <c r="AD225" s="15" t="inlineStr"/>
       <c r="AE225" s="14" t="n">
-        <v>374652.0</v>
+        <v>111138.0</v>
       </c>
       <c r="AF225" s="14" t="inlineStr"/>
       <c r="AG225" s="14" t="inlineStr"/>
@@ -13721,20 +13721,20 @@
         <v>4425348.0</v>
       </c>
       <c r="X226" s="14" t="n">
-        <v>0.0</v>
+        <v>263514.0</v>
       </c>
       <c r="Y226" s="14" t="inlineStr"/>
       <c r="Z226" s="14" t="n">
-        <v>4425348.0</v>
+        <v>4688862.0</v>
       </c>
       <c r="AA226" s="14" t="inlineStr"/>
       <c r="AB226" s="14" t="inlineStr"/>
       <c r="AC226" s="15" t="n">
-        <v>0.9219475</v>
+        <v>0.97684625</v>
       </c>
       <c r="AD226" s="15" t="inlineStr"/>
       <c r="AE226" s="14" t="n">
-        <v>374652.0</v>
+        <v>111138.0</v>
       </c>
       <c r="AF226" s="14" t="inlineStr"/>
       <c r="AG226" s="14" t="inlineStr"/>
@@ -13947,20 +13947,20 @@
         <v>9.2465706E7</v>
       </c>
       <c r="X230" s="14" t="n">
-        <v>0.0</v>
+        <v>9250750.0</v>
       </c>
       <c r="Y230" s="14" t="inlineStr"/>
       <c r="Z230" s="14" t="n">
-        <v>9.2465706E7</v>
+        <v>1.01716456E8</v>
       </c>
       <c r="AA230" s="14" t="inlineStr"/>
       <c r="AB230" s="14" t="inlineStr"/>
       <c r="AC230" s="15" t="n">
-        <v>0.5988711528497409</v>
+        <v>0.6587853367875648</v>
       </c>
       <c r="AD230" s="15" t="inlineStr"/>
       <c r="AE230" s="14" t="n">
-        <v>6.1934294E7</v>
+        <v>5.2683544E7</v>
       </c>
       <c r="AF230" s="14" t="inlineStr"/>
       <c r="AG230" s="14" t="inlineStr"/>
@@ -14004,20 +14004,20 @@
         <v>6.58569E7</v>
       </c>
       <c r="X231" s="14" t="n">
-        <v>0.0</v>
+        <v>9250750.0</v>
       </c>
       <c r="Y231" s="14" t="inlineStr"/>
       <c r="Z231" s="14" t="n">
-        <v>6.58569E7</v>
+        <v>7.510765E7</v>
       </c>
       <c r="AA231" s="14" t="inlineStr"/>
       <c r="AB231" s="14" t="inlineStr"/>
       <c r="AC231" s="15" t="n">
-        <v>0.5189669030732861</v>
+        <v>0.5918648542159181</v>
       </c>
       <c r="AD231" s="15" t="inlineStr"/>
       <c r="AE231" s="14" t="n">
-        <v>6.10431E7</v>
+        <v>5.179235E7</v>
       </c>
       <c r="AF231" s="14" t="inlineStr"/>
       <c r="AG231" s="14" t="inlineStr"/>
@@ -14124,20 +14124,20 @@
         <v>3.84588968E8</v>
       </c>
       <c r="X233" s="14" t="n">
-        <v>0.0</v>
+        <v>4.2179575E7</v>
       </c>
       <c r="Y233" s="14" t="inlineStr"/>
       <c r="Z233" s="14" t="n">
-        <v>3.84588968E8</v>
+        <v>4.26768543E8</v>
       </c>
       <c r="AA233" s="14" t="inlineStr"/>
       <c r="AB233" s="14" t="inlineStr"/>
       <c r="AC233" s="15" t="n">
-        <v>0.543101199630014</v>
+        <v>0.6026655129318562</v>
       </c>
       <c r="AD233" s="15" t="inlineStr"/>
       <c r="AE233" s="14" t="n">
-        <v>3.23546032E8</v>
+        <v>2.81366457E8</v>
       </c>
       <c r="AF233" s="14" t="inlineStr"/>
       <c r="AG233" s="14" t="inlineStr"/>
@@ -14187,20 +14187,20 @@
         <v>9.9195E7</v>
       </c>
       <c r="X234" s="14" t="n">
-        <v>0.0</v>
+        <v>3.474E7</v>
       </c>
       <c r="Y234" s="14" t="inlineStr"/>
       <c r="Z234" s="14" t="n">
-        <v>9.9195E7</v>
+        <v>1.33935E8</v>
       </c>
       <c r="AA234" s="14" t="inlineStr"/>
       <c r="AB234" s="14" t="inlineStr"/>
       <c r="AC234" s="15" t="n">
-        <v>0.495975</v>
+        <v>0.669675</v>
       </c>
       <c r="AD234" s="15" t="inlineStr"/>
       <c r="AE234" s="14" t="n">
-        <v>1.00805E8</v>
+        <v>6.6065E7</v>
       </c>
       <c r="AF234" s="14" t="inlineStr"/>
       <c r="AG234" s="14" t="inlineStr"/>
@@ -14244,20 +14244,20 @@
         <v>8.8315E7</v>
       </c>
       <c r="X235" s="14" t="n">
-        <v>0.0</v>
+        <v>2.5625E7</v>
       </c>
       <c r="Y235" s="14" t="inlineStr"/>
       <c r="Z235" s="14" t="n">
-        <v>8.8315E7</v>
+        <v>1.1394E8</v>
       </c>
       <c r="AA235" s="14" t="inlineStr"/>
       <c r="AB235" s="14" t="inlineStr"/>
       <c r="AC235" s="15" t="n">
-        <v>0.4906388888888889</v>
+        <v>0.633</v>
       </c>
       <c r="AD235" s="15" t="inlineStr"/>
       <c r="AE235" s="14" t="n">
-        <v>9.1685E7</v>
+        <v>6.606E7</v>
       </c>
       <c r="AF235" s="14" t="inlineStr"/>
       <c r="AG235" s="14" t="inlineStr"/>
@@ -14301,20 +14301,20 @@
         <v>1.088E7</v>
       </c>
       <c r="X236" s="14" t="n">
-        <v>0.0</v>
+        <v>9115000.0</v>
       </c>
       <c r="Y236" s="14" t="inlineStr"/>
       <c r="Z236" s="14" t="n">
-        <v>1.088E7</v>
+        <v>1.9995E7</v>
       </c>
       <c r="AA236" s="14" t="inlineStr"/>
       <c r="AB236" s="14" t="inlineStr"/>
       <c r="AC236" s="15" t="n">
-        <v>0.544</v>
+        <v>0.99975</v>
       </c>
       <c r="AD236" s="15" t="inlineStr"/>
       <c r="AE236" s="14" t="n">
-        <v>9120000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="AF236" s="14" t="inlineStr"/>
       <c r="AG236" s="14" t="inlineStr"/>
@@ -14484,20 +14484,20 @@
         <v>1.10331326E8</v>
       </c>
       <c r="X239" s="14" t="n">
-        <v>0.0</v>
+        <v>750000.0</v>
       </c>
       <c r="Y239" s="14" t="inlineStr"/>
       <c r="Z239" s="14" t="n">
-        <v>1.10331326E8</v>
+        <v>1.11081326E8</v>
       </c>
       <c r="AA239" s="14" t="inlineStr"/>
       <c r="AB239" s="14" t="inlineStr"/>
       <c r="AC239" s="15" t="n">
-        <v>0.5574682363640957</v>
+        <v>0.5612577419599323</v>
       </c>
       <c r="AD239" s="15" t="inlineStr"/>
       <c r="AE239" s="14" t="n">
-        <v>8.7583674E7</v>
+        <v>8.6833674E7</v>
       </c>
       <c r="AF239" s="14" t="inlineStr"/>
       <c r="AG239" s="14" t="inlineStr"/>
@@ -14598,20 +14598,20 @@
         <v>1.1156299E7</v>
       </c>
       <c r="X241" s="14" t="n">
-        <v>0.0</v>
+        <v>750000.0</v>
       </c>
       <c r="Y241" s="14" t="inlineStr"/>
       <c r="Z241" s="14" t="n">
-        <v>1.1156299E7</v>
+        <v>1.1906299E7</v>
       </c>
       <c r="AA241" s="14" t="inlineStr"/>
       <c r="AB241" s="14" t="inlineStr"/>
       <c r="AC241" s="15" t="n">
-        <v>0.7083364444444444</v>
+        <v>0.7559554920634921</v>
       </c>
       <c r="AD241" s="15" t="inlineStr"/>
       <c r="AE241" s="14" t="n">
-        <v>4593701.0</v>
+        <v>3843701.0</v>
       </c>
       <c r="AF241" s="14" t="inlineStr"/>
       <c r="AG241" s="14" t="inlineStr"/>
@@ -15288,20 +15288,20 @@
         <v>8.8386927E7</v>
       </c>
       <c r="X253" s="14" t="n">
-        <v>0.0</v>
+        <v>6689575.0</v>
       </c>
       <c r="Y253" s="14" t="inlineStr"/>
       <c r="Z253" s="14" t="n">
-        <v>8.8386927E7</v>
+        <v>9.5076502E7</v>
       </c>
       <c r="AA253" s="14" t="inlineStr"/>
       <c r="AB253" s="14" t="inlineStr"/>
       <c r="AC253" s="15" t="n">
-        <v>0.43356679584028257</v>
+        <v>0.4663813499460414</v>
       </c>
       <c r="AD253" s="15" t="inlineStr"/>
       <c r="AE253" s="14" t="n">
-        <v>1.15473073E8</v>
+        <v>1.08783498E8</v>
       </c>
       <c r="AF253" s="14" t="inlineStr"/>
       <c r="AG253" s="14" t="inlineStr"/>
@@ -15345,20 +15345,20 @@
         <v>4080000.0</v>
       </c>
       <c r="X254" s="14" t="n">
-        <v>0.0</v>
+        <v>4845000.0</v>
       </c>
       <c r="Y254" s="14" t="inlineStr"/>
       <c r="Z254" s="14" t="n">
-        <v>4080000.0</v>
+        <v>8925000.0</v>
       </c>
       <c r="AA254" s="14" t="inlineStr"/>
       <c r="AB254" s="14" t="inlineStr"/>
       <c r="AC254" s="15" t="n">
-        <v>0.3813084112149533</v>
+        <v>0.8341121495327103</v>
       </c>
       <c r="AD254" s="15" t="inlineStr"/>
       <c r="AE254" s="14" t="n">
-        <v>6620000.0</v>
+        <v>1775000.0</v>
       </c>
       <c r="AF254" s="14" t="inlineStr"/>
       <c r="AG254" s="14" t="inlineStr"/>
@@ -15559,20 +15559,20 @@
         <v>6.6116077E7</v>
       </c>
       <c r="X258" s="14" t="n">
-        <v>0.0</v>
+        <v>1225000.0</v>
       </c>
       <c r="Y258" s="14" t="inlineStr"/>
       <c r="Z258" s="14" t="n">
-        <v>6.6116077E7</v>
+        <v>6.7341077E7</v>
       </c>
       <c r="AA258" s="14" t="inlineStr"/>
       <c r="AB258" s="14" t="inlineStr"/>
       <c r="AC258" s="15" t="n">
-        <v>0.530626621187801</v>
+        <v>0.5404580818619583</v>
       </c>
       <c r="AD258" s="15" t="inlineStr"/>
       <c r="AE258" s="14" t="n">
-        <v>5.8483923E7</v>
+        <v>5.7258923E7</v>
       </c>
       <c r="AF258" s="14" t="inlineStr"/>
       <c r="AG258" s="14" t="inlineStr"/>
@@ -15616,20 +15616,20 @@
         <v>2177000.0</v>
       </c>
       <c r="X259" s="14" t="n">
-        <v>0.0</v>
+        <v>233875.0</v>
       </c>
       <c r="Y259" s="14" t="inlineStr"/>
       <c r="Z259" s="14" t="n">
-        <v>2177000.0</v>
+        <v>2410875.0</v>
       </c>
       <c r="AA259" s="14" t="inlineStr"/>
       <c r="AB259" s="14" t="inlineStr"/>
       <c r="AC259" s="15" t="n">
-        <v>0.7256666666666667</v>
+        <v>0.803625</v>
       </c>
       <c r="AD259" s="15" t="inlineStr"/>
       <c r="AE259" s="14" t="n">
-        <v>823000.0</v>
+        <v>589125.0</v>
       </c>
       <c r="AF259" s="14" t="inlineStr"/>
       <c r="AG259" s="14" t="inlineStr"/>
@@ -15844,20 +15844,20 @@
         <v>3707013.0</v>
       </c>
       <c r="X263" s="14" t="n">
-        <v>0.0</v>
+        <v>385700.0</v>
       </c>
       <c r="Y263" s="14" t="inlineStr"/>
       <c r="Z263" s="14" t="n">
-        <v>3707013.0</v>
+        <v>4092713.0</v>
       </c>
       <c r="AA263" s="14" t="inlineStr"/>
       <c r="AB263" s="14" t="inlineStr"/>
       <c r="AC263" s="15" t="n">
-        <v>0.3707013</v>
+        <v>0.4092713</v>
       </c>
       <c r="AD263" s="15" t="inlineStr"/>
       <c r="AE263" s="14" t="n">
-        <v>6292987.0</v>
+        <v>5907287.0</v>
       </c>
       <c r="AF263" s="14" t="inlineStr"/>
       <c r="AG263" s="14" t="inlineStr"/>

--- a/Database/Akrual.xlsx
+++ b/Database/Akrual.xlsx
@@ -982,19 +982,19 @@
         <v>6.1530207365E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>2.980475502E9</v>
+        <v>5.974419026E9</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>6.4510682867E10</v>
+        <v>6.7504626391E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.7588527912571109</v>
+        <v>0.7940711814381232</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>2.0500117133E10</v>
+        <v>1.7506173609E10</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1714,20 +1714,20 @@
         <v>5.7496839325E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>2.980475502E9</v>
+        <v>5.974419026E9</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>6.0477314827E10</v>
+        <v>6.3471258351E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.7562986016833594</v>
+        <v>0.7937393397054987</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>1.9487549173E10</v>
+        <v>1.6493605649E10</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1777,20 +1777,20 @@
         <v>5.7496839325E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>2.980475502E9</v>
+        <v>5.974419026E9</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>6.0477314827E10</v>
+        <v>6.3471258351E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.7562986016833594</v>
+        <v>0.7937393397054987</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>1.9487549173E10</v>
+        <v>1.6493605649E10</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1840,20 +1840,20 @@
         <v>5.7496239325E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>2.980475502E9</v>
+        <v>5.974419026E9</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>6.0476714827E10</v>
+        <v>6.3470658351E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.7562967731060465</v>
+        <v>0.7937377920592128</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>1.9487549173E10</v>
+        <v>1.6493605649E10</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -3233,20 +3233,20 @@
         <v>5.7485503225E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>2.980475502E9</v>
+        <v>5.974419026E9</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>6.0465978727E10</v>
+        <v>6.3459922251E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.7563377769100225</v>
+        <v>0.7937874740258186</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>1.9479755273E10</v>
+        <v>1.6485811749E10</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -3296,20 +3296,20 @@
         <v>5.3329786245E10</v>
       </c>
       <c r="X47" s="25" t="n">
-        <v>2.81070658E9</v>
+        <v>5.735081504E9</v>
       </c>
       <c r="Y47" s="25" t="inlineStr"/>
       <c r="Z47" s="25" t="n">
-        <v>5.6140492825E10</v>
+        <v>5.9064867749E10</v>
       </c>
       <c r="AA47" s="25" t="inlineStr"/>
       <c r="AB47" s="25" t="inlineStr"/>
       <c r="AC47" s="26" t="n">
-        <v>0.755694161721573</v>
+        <v>0.7950584947644006</v>
       </c>
       <c r="AD47" s="26" t="inlineStr"/>
       <c r="AE47" s="25" t="n">
-        <v>1.8149472175E10</v>
+        <v>1.5225097251E10</v>
       </c>
       <c r="AF47" s="25" t="inlineStr"/>
       <c r="AG47" s="25" t="inlineStr"/>
@@ -3359,20 +3359,20 @@
         <v>4.187549504E9</v>
       </c>
       <c r="X48" s="14" t="n">
-        <v>5.4407639E7</v>
+        <v>2.39585159E8</v>
       </c>
       <c r="Y48" s="14" t="inlineStr"/>
       <c r="Z48" s="14" t="n">
-        <v>4.241957143E9</v>
+        <v>4.427134663E9</v>
       </c>
       <c r="AA48" s="14" t="inlineStr"/>
       <c r="AB48" s="14" t="inlineStr"/>
       <c r="AC48" s="15" t="n">
-        <v>0.662095292582897</v>
+        <v>0.6909982635821434</v>
       </c>
       <c r="AD48" s="15" t="inlineStr"/>
       <c r="AE48" s="14" t="n">
-        <v>2.164910857E9</v>
+        <v>1.979733337E9</v>
       </c>
       <c r="AF48" s="14" t="inlineStr"/>
       <c r="AG48" s="14" t="inlineStr"/>
@@ -3422,20 +3422,20 @@
         <v>1.6503171E9</v>
       </c>
       <c r="X49" s="14" t="n">
-        <v>1.62007E7</v>
+        <v>1.646816E8</v>
       </c>
       <c r="Y49" s="14" t="inlineStr"/>
       <c r="Z49" s="14" t="n">
-        <v>1.6665178E9</v>
+        <v>1.8149987E9</v>
       </c>
       <c r="AA49" s="14" t="inlineStr"/>
       <c r="AB49" s="14" t="inlineStr"/>
       <c r="AC49" s="15" t="n">
-        <v>0.5946735093533847</v>
+        <v>0.6476568365491392</v>
       </c>
       <c r="AD49" s="15" t="inlineStr"/>
       <c r="AE49" s="14" t="n">
-        <v>1.1358902E9</v>
+        <v>9.874093E8</v>
       </c>
       <c r="AF49" s="14" t="inlineStr"/>
       <c r="AG49" s="14" t="inlineStr"/>
@@ -3479,20 +3479,20 @@
         <v>1.3201367E9</v>
       </c>
       <c r="X50" s="14" t="n">
-        <v>1.62007E7</v>
+        <v>1.646816E8</v>
       </c>
       <c r="Y50" s="14" t="inlineStr"/>
       <c r="Z50" s="14" t="n">
-        <v>1.3363374E9</v>
+        <v>1.4848183E9</v>
       </c>
       <c r="AA50" s="14" t="inlineStr"/>
       <c r="AB50" s="14" t="inlineStr"/>
       <c r="AC50" s="15" t="n">
-        <v>0.5434917032698877</v>
+        <v>0.6038792500406702</v>
       </c>
       <c r="AD50" s="15" t="inlineStr"/>
       <c r="AE50" s="14" t="n">
-        <v>1.1224626E9</v>
+        <v>9.739817E8</v>
       </c>
       <c r="AF50" s="14" t="inlineStr"/>
       <c r="AG50" s="14" t="inlineStr"/>
@@ -3656,20 +3656,20 @@
         <v>19549.0</v>
       </c>
       <c r="X53" s="14" t="n">
-        <v>121.0</v>
+        <v>1825.0</v>
       </c>
       <c r="Y53" s="14" t="inlineStr"/>
       <c r="Z53" s="14" t="n">
-        <v>19670.0</v>
+        <v>21374.0</v>
       </c>
       <c r="AA53" s="14" t="inlineStr"/>
       <c r="AB53" s="14" t="inlineStr"/>
       <c r="AC53" s="15" t="n">
-        <v>0.6556666666666666</v>
+        <v>0.7124666666666667</v>
       </c>
       <c r="AD53" s="15" t="inlineStr"/>
       <c r="AE53" s="14" t="n">
-        <v>10330.0</v>
+        <v>8626.0</v>
       </c>
       <c r="AF53" s="14" t="inlineStr"/>
       <c r="AG53" s="14" t="inlineStr"/>
@@ -3713,20 +3713,20 @@
         <v>14967.0</v>
       </c>
       <c r="X54" s="14" t="n">
-        <v>121.0</v>
+        <v>1825.0</v>
       </c>
       <c r="Y54" s="14" t="inlineStr"/>
       <c r="Z54" s="14" t="n">
-        <v>15088.0</v>
+        <v>16792.0</v>
       </c>
       <c r="AA54" s="14" t="inlineStr"/>
       <c r="AB54" s="14" t="inlineStr"/>
       <c r="AC54" s="15" t="n">
-        <v>0.6286666666666667</v>
+        <v>0.6996666666666667</v>
       </c>
       <c r="AD54" s="15" t="inlineStr"/>
       <c r="AE54" s="14" t="n">
-        <v>8912.0</v>
+        <v>7208.0</v>
       </c>
       <c r="AF54" s="14" t="inlineStr"/>
       <c r="AG54" s="14" t="inlineStr"/>
@@ -3890,20 +3890,20 @@
         <v>1.2585432E8</v>
       </c>
       <c r="X57" s="14" t="n">
-        <v>1620070.0</v>
+        <v>1.253382E7</v>
       </c>
       <c r="Y57" s="14" t="inlineStr"/>
       <c r="Z57" s="14" t="n">
-        <v>1.2747439E8</v>
+        <v>1.3838814E8</v>
       </c>
       <c r="AA57" s="14" t="inlineStr"/>
       <c r="AB57" s="14" t="inlineStr"/>
       <c r="AC57" s="15" t="n">
-        <v>0.7004087362637362</v>
+        <v>0.7603743956043956</v>
       </c>
       <c r="AD57" s="15" t="inlineStr"/>
       <c r="AE57" s="14" t="n">
-        <v>5.452561E7</v>
+        <v>4.361186E7</v>
       </c>
       <c r="AF57" s="14" t="inlineStr"/>
       <c r="AG57" s="14" t="inlineStr"/>
@@ -3947,20 +3947,20 @@
         <v>1.00656E8</v>
       </c>
       <c r="X58" s="14" t="n">
-        <v>1620070.0</v>
+        <v>1.253382E7</v>
       </c>
       <c r="Y58" s="14" t="inlineStr"/>
       <c r="Z58" s="14" t="n">
-        <v>1.0227607E8</v>
+        <v>1.1318982E8</v>
       </c>
       <c r="AA58" s="14" t="inlineStr"/>
       <c r="AB58" s="14" t="inlineStr"/>
       <c r="AC58" s="15" t="n">
-        <v>0.6556158333333333</v>
+        <v>0.7255757692307693</v>
       </c>
       <c r="AD58" s="15" t="inlineStr"/>
       <c r="AE58" s="14" t="n">
-        <v>5.372393E7</v>
+        <v>4.281018E7</v>
       </c>
       <c r="AF58" s="14" t="inlineStr"/>
       <c r="AG58" s="14" t="inlineStr"/>
@@ -4167,20 +4167,20 @@
         <v>3.8237084E7</v>
       </c>
       <c r="X62" s="14" t="n">
-        <v>648028.0</v>
+        <v>3798764.0</v>
       </c>
       <c r="Y62" s="14" t="inlineStr"/>
       <c r="Z62" s="14" t="n">
-        <v>3.8885112E7</v>
+        <v>4.2035848E7</v>
       </c>
       <c r="AA62" s="14" t="inlineStr"/>
       <c r="AB62" s="14" t="inlineStr"/>
       <c r="AC62" s="15" t="n">
-        <v>0.694377</v>
+        <v>0.7506401428571429</v>
       </c>
       <c r="AD62" s="15" t="inlineStr"/>
       <c r="AE62" s="14" t="n">
-        <v>1.7114888E7</v>
+        <v>1.3964152E7</v>
       </c>
       <c r="AF62" s="14" t="inlineStr"/>
       <c r="AG62" s="14" t="inlineStr"/>
@@ -4224,20 +4224,20 @@
         <v>3.0561026E7</v>
       </c>
       <c r="X63" s="14" t="n">
-        <v>648028.0</v>
+        <v>3798764.0</v>
       </c>
       <c r="Y63" s="14" t="inlineStr"/>
       <c r="Z63" s="14" t="n">
-        <v>3.1209054E7</v>
+        <v>3.435979E7</v>
       </c>
       <c r="AA63" s="14" t="inlineStr"/>
       <c r="AB63" s="14" t="inlineStr"/>
       <c r="AC63" s="15" t="n">
-        <v>0.650188625</v>
+        <v>0.7158289583333334</v>
       </c>
       <c r="AD63" s="15" t="inlineStr"/>
       <c r="AE63" s="14" t="n">
-        <v>1.6790946E7</v>
+        <v>1.364021E7</v>
       </c>
       <c r="AF63" s="14" t="inlineStr"/>
       <c r="AG63" s="14" t="inlineStr"/>
@@ -4401,20 +4401,20 @@
         <v>1.8E7</v>
       </c>
       <c r="X66" s="14" t="n">
-        <v>540000.0</v>
+        <v>1800000.0</v>
       </c>
       <c r="Y66" s="14" t="inlineStr"/>
       <c r="Z66" s="14" t="n">
-        <v>1.854E7</v>
+        <v>1.98E7</v>
       </c>
       <c r="AA66" s="14" t="inlineStr"/>
       <c r="AB66" s="14" t="inlineStr"/>
       <c r="AC66" s="15" t="n">
-        <v>0.7357142857142858</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="AD66" s="15" t="inlineStr"/>
       <c r="AE66" s="14" t="n">
-        <v>6660000.0</v>
+        <v>5400000.0</v>
       </c>
       <c r="AF66" s="14" t="inlineStr"/>
       <c r="AG66" s="14" t="inlineStr"/>
@@ -4458,20 +4458,20 @@
         <v>1.44E7</v>
       </c>
       <c r="X67" s="14" t="n">
-        <v>540000.0</v>
+        <v>1800000.0</v>
       </c>
       <c r="Y67" s="14" t="inlineStr"/>
       <c r="Z67" s="14" t="n">
-        <v>1.494E7</v>
+        <v>1.62E7</v>
       </c>
       <c r="AA67" s="14" t="inlineStr"/>
       <c r="AB67" s="14" t="inlineStr"/>
       <c r="AC67" s="15" t="n">
-        <v>0.6916666666666667</v>
+        <v>0.75</v>
       </c>
       <c r="AD67" s="15" t="inlineStr"/>
       <c r="AE67" s="14" t="n">
-        <v>6660000.0</v>
+        <v>5400000.0</v>
       </c>
       <c r="AF67" s="14" t="inlineStr"/>
       <c r="AG67" s="14" t="inlineStr"/>
@@ -4635,20 +4635,20 @@
         <v>1.1796E8</v>
       </c>
       <c r="X70" s="14" t="n">
-        <v>1100000.0</v>
+        <v>1.0934E7</v>
       </c>
       <c r="Y70" s="14" t="inlineStr"/>
       <c r="Z70" s="14" t="n">
-        <v>1.1906E8</v>
+        <v>1.28894E8</v>
       </c>
       <c r="AA70" s="14" t="inlineStr"/>
       <c r="AB70" s="14" t="inlineStr"/>
       <c r="AC70" s="15" t="n">
-        <v>0.8210241769760162</v>
+        <v>0.8888383190588495</v>
       </c>
       <c r="AD70" s="15" t="inlineStr"/>
       <c r="AE70" s="14" t="n">
-        <v>2.5954E7</v>
+        <v>1.612E7</v>
       </c>
       <c r="AF70" s="14" t="inlineStr"/>
       <c r="AG70" s="14" t="inlineStr"/>
@@ -4692,20 +4692,20 @@
         <v>9.3932E7</v>
       </c>
       <c r="X71" s="14" t="n">
-        <v>1100000.0</v>
+        <v>1.0934E7</v>
       </c>
       <c r="Y71" s="14" t="inlineStr"/>
       <c r="Z71" s="14" t="n">
-        <v>9.5032E7</v>
+        <v>1.04866E8</v>
       </c>
       <c r="AA71" s="14" t="inlineStr"/>
       <c r="AB71" s="14" t="inlineStr"/>
       <c r="AC71" s="15" t="n">
-        <v>0.7919333333333334</v>
+        <v>0.8738833333333333</v>
       </c>
       <c r="AD71" s="15" t="inlineStr"/>
       <c r="AE71" s="14" t="n">
-        <v>2.4968E7</v>
+        <v>1.5134E7</v>
       </c>
       <c r="AF71" s="14" t="inlineStr"/>
       <c r="AG71" s="14" t="inlineStr"/>
@@ -4869,20 +4869,20 @@
         <v>1.9384414E7</v>
       </c>
       <c r="X74" s="14" t="n">
-        <v>0.0</v>
+        <v>197170.0</v>
       </c>
       <c r="Y74" s="14" t="inlineStr"/>
       <c r="Z74" s="14" t="n">
-        <v>1.9384414E7</v>
+        <v>1.9581584E7</v>
       </c>
       <c r="AA74" s="14" t="inlineStr"/>
       <c r="AB74" s="14" t="inlineStr"/>
       <c r="AC74" s="15" t="n">
-        <v>0.9790108080808081</v>
+        <v>0.9889688888888889</v>
       </c>
       <c r="AD74" s="15" t="inlineStr"/>
       <c r="AE74" s="14" t="n">
-        <v>415586.0</v>
+        <v>218416.0</v>
       </c>
       <c r="AF74" s="14" t="inlineStr"/>
       <c r="AG74" s="14" t="inlineStr"/>
@@ -4926,20 +4926,20 @@
         <v>1853398.0</v>
       </c>
       <c r="X75" s="14" t="n">
-        <v>0.0</v>
+        <v>197170.0</v>
       </c>
       <c r="Y75" s="14" t="inlineStr"/>
       <c r="Z75" s="14" t="n">
-        <v>1853398.0</v>
+        <v>2050568.0</v>
       </c>
       <c r="AA75" s="14" t="inlineStr"/>
       <c r="AB75" s="14" t="inlineStr"/>
       <c r="AC75" s="15" t="n">
-        <v>0.7722491666666667</v>
+        <v>0.8544033333333333</v>
       </c>
       <c r="AD75" s="15" t="inlineStr"/>
       <c r="AE75" s="14" t="n">
-        <v>546602.0</v>
+        <v>349432.0</v>
       </c>
       <c r="AF75" s="14" t="inlineStr"/>
       <c r="AG75" s="14" t="inlineStr"/>
@@ -5103,20 +5103,20 @@
         <v>8.72661E7</v>
       </c>
       <c r="X78" s="14" t="n">
-        <v>1158720.0</v>
+        <v>8617980.0</v>
       </c>
       <c r="Y78" s="14" t="inlineStr"/>
       <c r="Z78" s="14" t="n">
-        <v>8.842482E7</v>
+        <v>9.588408E7</v>
       </c>
       <c r="AA78" s="14" t="inlineStr"/>
       <c r="AB78" s="14" t="inlineStr"/>
       <c r="AC78" s="15" t="n">
-        <v>0.7017842857142857</v>
+        <v>0.7609847619047619</v>
       </c>
       <c r="AD78" s="15" t="inlineStr"/>
       <c r="AE78" s="14" t="n">
-        <v>3.757518E7</v>
+        <v>3.011592E7</v>
       </c>
       <c r="AF78" s="14" t="inlineStr"/>
       <c r="AG78" s="14" t="inlineStr"/>
@@ -5160,20 +5160,20 @@
         <v>6.974046E7</v>
       </c>
       <c r="X79" s="14" t="n">
-        <v>1158720.0</v>
+        <v>8617980.0</v>
       </c>
       <c r="Y79" s="14" t="inlineStr"/>
       <c r="Z79" s="14" t="n">
-        <v>7.089918E7</v>
+        <v>7.835844E7</v>
       </c>
       <c r="AA79" s="14" t="inlineStr"/>
       <c r="AB79" s="14" t="inlineStr"/>
       <c r="AC79" s="15" t="n">
-        <v>0.6564738888888889</v>
+        <v>0.7255411111111111</v>
       </c>
       <c r="AD79" s="15" t="inlineStr"/>
       <c r="AE79" s="14" t="n">
-        <v>3.710082E7</v>
+        <v>2.964156E7</v>
       </c>
       <c r="AF79" s="14" t="inlineStr"/>
       <c r="AG79" s="14" t="inlineStr"/>
@@ -5571,20 +5571,20 @@
         <v>4.044E7</v>
       </c>
       <c r="X86" s="14" t="n">
-        <v>375000.0</v>
+        <v>4255000.0</v>
       </c>
       <c r="Y86" s="14" t="inlineStr"/>
       <c r="Z86" s="14" t="n">
-        <v>4.0815E7</v>
+        <v>4.4695E7</v>
       </c>
       <c r="AA86" s="14" t="inlineStr"/>
       <c r="AB86" s="14" t="inlineStr"/>
       <c r="AC86" s="15" t="n">
-        <v>0.6478571428571429</v>
+        <v>0.7094444444444444</v>
       </c>
       <c r="AD86" s="15" t="inlineStr"/>
       <c r="AE86" s="14" t="n">
-        <v>2.2185E7</v>
+        <v>1.8305E7</v>
       </c>
       <c r="AF86" s="14" t="inlineStr"/>
       <c r="AG86" s="14" t="inlineStr"/>
@@ -5628,20 +5628,20 @@
         <v>3.251E7</v>
       </c>
       <c r="X87" s="14" t="n">
-        <v>375000.0</v>
+        <v>4255000.0</v>
       </c>
       <c r="Y87" s="14" t="inlineStr"/>
       <c r="Z87" s="14" t="n">
-        <v>3.2885E7</v>
+        <v>3.6765E7</v>
       </c>
       <c r="AA87" s="14" t="inlineStr"/>
       <c r="AB87" s="14" t="inlineStr"/>
       <c r="AC87" s="15" t="n">
-        <v>0.6089814814814815</v>
+        <v>0.6808333333333333</v>
       </c>
       <c r="AD87" s="15" t="inlineStr"/>
       <c r="AE87" s="14" t="n">
-        <v>2.1115E7</v>
+        <v>1.7235E7</v>
       </c>
       <c r="AF87" s="14" t="inlineStr"/>
       <c r="AG87" s="14" t="inlineStr"/>
@@ -7946,20 +7946,20 @@
         <v>3.5544999187E10</v>
       </c>
       <c r="X127" s="14" t="n">
-        <v>1.897709787E9</v>
+        <v>3.871887838E9</v>
       </c>
       <c r="Y127" s="14" t="inlineStr"/>
       <c r="Z127" s="14" t="n">
-        <v>3.7442708974E10</v>
+        <v>3.9416887025E10</v>
       </c>
       <c r="AA127" s="14" t="inlineStr"/>
       <c r="AB127" s="14" t="inlineStr"/>
       <c r="AC127" s="15" t="n">
-        <v>0.7079492404976508</v>
+        <v>0.7452760763519444</v>
       </c>
       <c r="AD127" s="15" t="inlineStr"/>
       <c r="AE127" s="14" t="n">
-        <v>1.5446265026E10</v>
+        <v>1.3472086975E10</v>
       </c>
       <c r="AF127" s="14" t="inlineStr"/>
       <c r="AG127" s="14" t="inlineStr"/>
@@ -8009,20 +8009,20 @@
         <v>1.23832303E10</v>
       </c>
       <c r="X128" s="14" t="n">
-        <v>1.190934E9</v>
+        <v>1.1920816E9</v>
       </c>
       <c r="Y128" s="14" t="inlineStr"/>
       <c r="Z128" s="14" t="n">
-        <v>1.35741643E10</v>
+        <v>1.35753119E10</v>
       </c>
       <c r="AA128" s="14" t="inlineStr"/>
       <c r="AB128" s="14" t="inlineStr"/>
       <c r="AC128" s="15" t="n">
-        <v>1.0321997168975223</v>
+        <v>1.0322869821146607</v>
       </c>
       <c r="AD128" s="15" t="inlineStr"/>
       <c r="AE128" s="14" t="n">
-        <v>-4.234493E8</v>
+        <v>-4.245969E8</v>
       </c>
       <c r="AF128" s="14" t="inlineStr"/>
       <c r="AG128" s="14" t="inlineStr"/>
@@ -8066,20 +8066,20 @@
         <v>9.8924769E9</v>
       </c>
       <c r="X129" s="14" t="n">
-        <v>1.190934E9</v>
+        <v>1.1920816E9</v>
       </c>
       <c r="Y129" s="14" t="inlineStr"/>
       <c r="Z129" s="14" t="n">
-        <v>1.10834109E10</v>
+        <v>1.10845585E10</v>
       </c>
       <c r="AA129" s="14" t="inlineStr"/>
       <c r="AB129" s="14" t="inlineStr"/>
       <c r="AC129" s="15" t="n">
-        <v>1.0458715978113662</v>
+        <v>1.0459798895869286</v>
       </c>
       <c r="AD129" s="15" t="inlineStr"/>
       <c r="AE129" s="14" t="n">
-        <v>-4.861149E8</v>
+        <v>-4.872625E8</v>
       </c>
       <c r="AF129" s="14" t="inlineStr"/>
       <c r="AG129" s="14" t="inlineStr"/>
@@ -8243,20 +8243,20 @@
         <v>168114.0</v>
       </c>
       <c r="X132" s="14" t="n">
-        <v>15731.0</v>
+        <v>15735.0</v>
       </c>
       <c r="Y132" s="14" t="inlineStr"/>
       <c r="Z132" s="14" t="n">
-        <v>183845.0</v>
+        <v>183849.0</v>
       </c>
       <c r="AA132" s="14" t="inlineStr"/>
       <c r="AB132" s="14" t="inlineStr"/>
       <c r="AC132" s="15" t="n">
-        <v>0.7724579831932773</v>
+        <v>0.7724747899159664</v>
       </c>
       <c r="AD132" s="15" t="inlineStr"/>
       <c r="AE132" s="14" t="n">
-        <v>54155.0</v>
+        <v>54151.0</v>
       </c>
       <c r="AF132" s="14" t="inlineStr"/>
       <c r="AG132" s="14" t="inlineStr"/>
@@ -8300,20 +8300,20 @@
         <v>134340.0</v>
       </c>
       <c r="X133" s="14" t="n">
-        <v>15731.0</v>
+        <v>15735.0</v>
       </c>
       <c r="Y133" s="14" t="inlineStr"/>
       <c r="Z133" s="14" t="n">
-        <v>150071.0</v>
+        <v>150075.0</v>
       </c>
       <c r="AA133" s="14" t="inlineStr"/>
       <c r="AB133" s="14" t="inlineStr"/>
       <c r="AC133" s="15" t="n">
-        <v>0.7356421568627451</v>
+        <v>0.7356617647058824</v>
       </c>
       <c r="AD133" s="15" t="inlineStr"/>
       <c r="AE133" s="14" t="n">
-        <v>53929.0</v>
+        <v>53925.0</v>
       </c>
       <c r="AF133" s="14" t="inlineStr"/>
       <c r="AG133" s="14" t="inlineStr"/>
@@ -8477,20 +8477,20 @@
         <v>9.7329066E8</v>
       </c>
       <c r="X136" s="14" t="n">
-        <v>9.414094E7</v>
+        <v>9.423332E7</v>
       </c>
       <c r="Y136" s="14" t="inlineStr"/>
       <c r="Z136" s="14" t="n">
-        <v>1.0674316E9</v>
+        <v>1.06752398E9</v>
       </c>
       <c r="AA136" s="14" t="inlineStr"/>
       <c r="AB136" s="14" t="inlineStr"/>
       <c r="AC136" s="15" t="n">
-        <v>0.7782666326419015</v>
+        <v>0.7783339870948927</v>
       </c>
       <c r="AD136" s="15" t="inlineStr"/>
       <c r="AE136" s="14" t="n">
-        <v>3.041184E8</v>
+        <v>3.0402602E8</v>
       </c>
       <c r="AF136" s="14" t="inlineStr"/>
       <c r="AG136" s="14" t="inlineStr"/>
@@ -8534,20 +8534,20 @@
         <v>7.783056E8</v>
       </c>
       <c r="X137" s="14" t="n">
-        <v>9.414094E7</v>
+        <v>9.423332E7</v>
       </c>
       <c r="Y137" s="14" t="inlineStr"/>
       <c r="Z137" s="14" t="n">
-        <v>8.7244654E8</v>
+        <v>8.7253892E8</v>
       </c>
       <c r="AA137" s="14" t="inlineStr"/>
       <c r="AB137" s="14" t="inlineStr"/>
       <c r="AC137" s="15" t="n">
-        <v>0.7418763095238096</v>
+        <v>0.7419548639455782</v>
       </c>
       <c r="AD137" s="15" t="inlineStr"/>
       <c r="AE137" s="14" t="n">
-        <v>3.0355346E8</v>
+        <v>3.0346108E8</v>
       </c>
       <c r="AF137" s="14" t="inlineStr"/>
       <c r="AG137" s="14" t="inlineStr"/>
@@ -8711,20 +8711,20 @@
         <v>3.02306822E8</v>
       </c>
       <c r="X140" s="14" t="n">
-        <v>2.9613198E7</v>
+        <v>2.9627484E7</v>
       </c>
       <c r="Y140" s="14" t="inlineStr"/>
       <c r="Z140" s="14" t="n">
-        <v>3.3192002E8</v>
+        <v>3.31934306E8</v>
       </c>
       <c r="AA140" s="14" t="inlineStr"/>
       <c r="AB140" s="14" t="inlineStr"/>
       <c r="AC140" s="15" t="n">
-        <v>0.7661042291295929</v>
+        <v>0.7661372026303095</v>
       </c>
       <c r="AD140" s="15" t="inlineStr"/>
       <c r="AE140" s="14" t="n">
-        <v>1.0133698E8</v>
+        <v>1.01322694E8</v>
       </c>
       <c r="AF140" s="14" t="inlineStr"/>
       <c r="AG140" s="14" t="inlineStr"/>
@@ -8768,20 +8768,20 @@
         <v>2.41915966E8</v>
       </c>
       <c r="X141" s="14" t="n">
-        <v>2.9613198E7</v>
+        <v>2.9627484E7</v>
       </c>
       <c r="Y141" s="14" t="inlineStr"/>
       <c r="Z141" s="14" t="n">
-        <v>2.71529164E8</v>
+        <v>2.7154345E8</v>
       </c>
       <c r="AA141" s="14" t="inlineStr"/>
       <c r="AB141" s="14" t="inlineStr"/>
       <c r="AC141" s="15" t="n">
-        <v>0.7299171075268818</v>
+        <v>0.7299555107526882</v>
       </c>
       <c r="AD141" s="15" t="inlineStr"/>
       <c r="AE141" s="14" t="n">
-        <v>1.00470836E8</v>
+        <v>1.0045655E8</v>
       </c>
       <c r="AF141" s="14" t="inlineStr"/>
       <c r="AG141" s="14" t="inlineStr"/>
@@ -10158,20 +10158,20 @@
         <v>1.7062639415E10</v>
       </c>
       <c r="X165" s="14" t="n">
-        <v>0.0</v>
+        <v>1.972923781E9</v>
       </c>
       <c r="Y165" s="14" t="inlineStr"/>
       <c r="Z165" s="14" t="n">
-        <v>1.7062639415E10</v>
+        <v>1.9035563196E10</v>
       </c>
       <c r="AA165" s="14" t="inlineStr"/>
       <c r="AB165" s="14" t="inlineStr"/>
       <c r="AC165" s="15" t="n">
-        <v>0.5642407213955026</v>
+        <v>0.6294829099206349</v>
       </c>
       <c r="AD165" s="15" t="inlineStr"/>
       <c r="AE165" s="14" t="n">
-        <v>1.3177360585E10</v>
+        <v>1.1204436804E10</v>
       </c>
       <c r="AF165" s="14" t="inlineStr"/>
       <c r="AG165" s="14" t="inlineStr"/>
@@ -10215,20 +10215,20 @@
         <v>1.2285354215E10</v>
       </c>
       <c r="X166" s="14" t="n">
-        <v>0.0</v>
+        <v>1.972923781E9</v>
       </c>
       <c r="Y166" s="14" t="inlineStr"/>
       <c r="Z166" s="14" t="n">
-        <v>1.2285354215E10</v>
+        <v>1.4258277996E10</v>
       </c>
       <c r="AA166" s="14" t="inlineStr"/>
       <c r="AB166" s="14" t="inlineStr"/>
       <c r="AC166" s="15" t="n">
-        <v>0.4833001392226193</v>
+        <v>0.5609140461027895</v>
       </c>
       <c r="AD166" s="15" t="inlineStr"/>
       <c r="AE166" s="14" t="n">
-        <v>1.3134365785E10</v>
+        <v>1.1161442004E10</v>
       </c>
       <c r="AF166" s="14" t="inlineStr"/>
       <c r="AG166" s="14" t="inlineStr"/>
@@ -10392,20 +10392,20 @@
         <v>1.3597237554E10</v>
       </c>
       <c r="X169" s="14" t="n">
-        <v>8.58589154E8</v>
+        <v>1.623608507E9</v>
       </c>
       <c r="Y169" s="14" t="inlineStr"/>
       <c r="Z169" s="14" t="n">
-        <v>1.4455826708E10</v>
+        <v>1.5220846061E10</v>
       </c>
       <c r="AA169" s="14" t="inlineStr"/>
       <c r="AB169" s="14" t="inlineStr"/>
       <c r="AC169" s="15" t="n">
-        <v>0.9641081950979286</v>
+        <v>1.0151299348112057</v>
       </c>
       <c r="AD169" s="15" t="inlineStr"/>
       <c r="AE169" s="14" t="n">
-        <v>5.38161292E8</v>
+        <v>-2.26858061E8</v>
       </c>
       <c r="AF169" s="14" t="inlineStr"/>
       <c r="AG169" s="14" t="inlineStr"/>
@@ -12079,20 +12079,20 @@
         <v>5.981030439E9</v>
       </c>
       <c r="X198" s="14" t="n">
-        <v>0.0</v>
+        <v>7.65019353E8</v>
       </c>
       <c r="Y198" s="14" t="inlineStr"/>
       <c r="Z198" s="14" t="n">
-        <v>5.981030439E9</v>
+        <v>6.746049792E9</v>
       </c>
       <c r="AA198" s="14" t="inlineStr"/>
       <c r="AB198" s="14" t="inlineStr"/>
       <c r="AC198" s="15" t="n">
-        <v>0.7650068927013265</v>
+        <v>0.8628571016350164</v>
       </c>
       <c r="AD198" s="15" t="inlineStr"/>
       <c r="AE198" s="14" t="n">
-        <v>1.837239561E9</v>
+        <v>1.072220208E9</v>
       </c>
       <c r="AF198" s="14" t="inlineStr"/>
       <c r="AG198" s="14" t="inlineStr"/>
@@ -12136,20 +12136,20 @@
         <v>4.406587063E9</v>
       </c>
       <c r="X199" s="14" t="n">
-        <v>0.0</v>
+        <v>7.65019353E8</v>
       </c>
       <c r="Y199" s="14" t="inlineStr"/>
       <c r="Z199" s="14" t="n">
-        <v>4.406587063E9</v>
+        <v>5.171606416E9</v>
       </c>
       <c r="AA199" s="14" t="inlineStr"/>
       <c r="AB199" s="14" t="inlineStr"/>
       <c r="AC199" s="15" t="n">
-        <v>0.706183824198718</v>
+        <v>0.8287830794871794</v>
       </c>
       <c r="AD199" s="15" t="inlineStr"/>
       <c r="AE199" s="14" t="n">
-        <v>1.833412937E9</v>
+        <v>1.068393584E9</v>
       </c>
       <c r="AF199" s="14" t="inlineStr"/>
       <c r="AG199" s="14" t="inlineStr"/>
@@ -12356,20 +12356,20 @@
         <v>4.15571698E9</v>
       </c>
       <c r="X203" s="25" t="n">
-        <v>1.69768922E8</v>
+        <v>2.39337522E8</v>
       </c>
       <c r="Y203" s="25" t="inlineStr"/>
       <c r="Z203" s="25" t="n">
-        <v>4.325485902E9</v>
+        <v>4.395054502E9</v>
       </c>
       <c r="AA203" s="25" t="inlineStr"/>
       <c r="AB203" s="25" t="inlineStr"/>
       <c r="AC203" s="26" t="n">
-        <v>0.7647918261866777</v>
+        <v>0.7770922931965574</v>
       </c>
       <c r="AD203" s="26" t="inlineStr"/>
       <c r="AE203" s="25" t="n">
-        <v>1.330283098E9</v>
+        <v>1.260714498E9</v>
       </c>
       <c r="AF203" s="25" t="inlineStr"/>
       <c r="AG203" s="25" t="inlineStr"/>
@@ -12419,20 +12419,20 @@
         <v>3.258757999E9</v>
       </c>
       <c r="X204" s="14" t="n">
-        <v>7.5668436E7</v>
+        <v>1.39228436E8</v>
       </c>
       <c r="Y204" s="14" t="inlineStr"/>
       <c r="Z204" s="14" t="n">
-        <v>3.334426435E9</v>
+        <v>3.397986435E9</v>
       </c>
       <c r="AA204" s="14" t="inlineStr"/>
       <c r="AB204" s="14" t="inlineStr"/>
       <c r="AC204" s="15" t="n">
-        <v>0.8583586684940281</v>
+        <v>0.8747204860458615</v>
       </c>
       <c r="AD204" s="15" t="inlineStr"/>
       <c r="AE204" s="14" t="n">
-        <v>5.50227565E8</v>
+        <v>4.86667565E8</v>
       </c>
       <c r="AF204" s="14" t="inlineStr"/>
       <c r="AG204" s="14" t="inlineStr"/>
@@ -12482,20 +12482,20 @@
         <v>5.46628803E8</v>
       </c>
       <c r="X205" s="14" t="n">
-        <v>2017000.0</v>
+        <v>6.5577E7</v>
       </c>
       <c r="Y205" s="14" t="inlineStr"/>
       <c r="Z205" s="14" t="n">
-        <v>5.48645803E8</v>
+        <v>6.12205803E8</v>
       </c>
       <c r="AA205" s="14" t="inlineStr"/>
       <c r="AB205" s="14" t="inlineStr"/>
       <c r="AC205" s="15" t="n">
-        <v>0.7467443968221777</v>
+        <v>0.833253896398205</v>
       </c>
       <c r="AD205" s="15" t="inlineStr"/>
       <c r="AE205" s="14" t="n">
-        <v>1.86071197E8</v>
+        <v>1.22511197E8</v>
       </c>
       <c r="AF205" s="14" t="inlineStr"/>
       <c r="AG205" s="14" t="inlineStr"/>
@@ -12539,20 +12539,20 @@
         <v>5.115E8</v>
       </c>
       <c r="X206" s="14" t="n">
-        <v>0.0</v>
+        <v>6.35E7</v>
       </c>
       <c r="Y206" s="14" t="inlineStr"/>
       <c r="Z206" s="14" t="n">
-        <v>5.115E8</v>
+        <v>5.75E8</v>
       </c>
       <c r="AA206" s="14" t="inlineStr"/>
       <c r="AB206" s="14" t="inlineStr"/>
       <c r="AC206" s="15" t="n">
-        <v>0.7522058823529412</v>
+        <v>0.8455882352941176</v>
       </c>
       <c r="AD206" s="15" t="inlineStr"/>
       <c r="AE206" s="14" t="n">
-        <v>1.685E8</v>
+        <v>1.05E8</v>
       </c>
       <c r="AF206" s="14" t="inlineStr"/>
       <c r="AG206" s="14" t="inlineStr"/>
@@ -12653,20 +12653,20 @@
         <v>3.2709603E7</v>
       </c>
       <c r="X208" s="14" t="n">
-        <v>2017000.0</v>
+        <v>2077000.0</v>
       </c>
       <c r="Y208" s="14" t="inlineStr"/>
       <c r="Z208" s="14" t="n">
-        <v>3.4726603E7</v>
+        <v>3.4786603E7</v>
       </c>
       <c r="AA208" s="14" t="inlineStr"/>
       <c r="AB208" s="14" t="inlineStr"/>
       <c r="AC208" s="15" t="n">
-        <v>0.6729961821705427</v>
+        <v>0.674158972868217</v>
       </c>
       <c r="AD208" s="15" t="inlineStr"/>
       <c r="AE208" s="14" t="n">
-        <v>1.6873397E7</v>
+        <v>1.6813397E7</v>
       </c>
       <c r="AF208" s="14" t="inlineStr"/>
       <c r="AG208" s="14" t="inlineStr"/>
@@ -13481,20 +13481,20 @@
         <v>4.32620013E8</v>
       </c>
       <c r="X222" s="14" t="n">
-        <v>5.1920911E7</v>
+        <v>5.2453711E7</v>
       </c>
       <c r="Y222" s="14" t="inlineStr"/>
       <c r="Z222" s="14" t="n">
-        <v>4.84540924E8</v>
+        <v>4.85073724E8</v>
       </c>
       <c r="AA222" s="14" t="inlineStr"/>
       <c r="AB222" s="14" t="inlineStr"/>
       <c r="AC222" s="15" t="n">
-        <v>0.5205639492909325</v>
+        <v>0.5211363601203266</v>
       </c>
       <c r="AD222" s="15" t="inlineStr"/>
       <c r="AE222" s="14" t="n">
-        <v>4.46259076E8</v>
+        <v>4.45726276E8</v>
       </c>
       <c r="AF222" s="14" t="inlineStr"/>
       <c r="AG222" s="14" t="inlineStr"/>
@@ -13947,20 +13947,20 @@
         <v>9.2465706E7</v>
       </c>
       <c r="X230" s="14" t="n">
-        <v>9250750.0</v>
+        <v>9783550.0</v>
       </c>
       <c r="Y230" s="14" t="inlineStr"/>
       <c r="Z230" s="14" t="n">
-        <v>1.01716456E8</v>
+        <v>1.02249256E8</v>
       </c>
       <c r="AA230" s="14" t="inlineStr"/>
       <c r="AB230" s="14" t="inlineStr"/>
       <c r="AC230" s="15" t="n">
-        <v>0.6587853367875648</v>
+        <v>0.6622361139896373</v>
       </c>
       <c r="AD230" s="15" t="inlineStr"/>
       <c r="AE230" s="14" t="n">
-        <v>5.2683544E7</v>
+        <v>5.2150744E7</v>
       </c>
       <c r="AF230" s="14" t="inlineStr"/>
       <c r="AG230" s="14" t="inlineStr"/>
@@ -14061,20 +14061,20 @@
         <v>2.6608806E7</v>
       </c>
       <c r="X232" s="14" t="n">
-        <v>0.0</v>
+        <v>532800.0</v>
       </c>
       <c r="Y232" s="14" t="inlineStr"/>
       <c r="Z232" s="14" t="n">
-        <v>2.6608806E7</v>
+        <v>2.7141606E7</v>
       </c>
       <c r="AA232" s="14" t="inlineStr"/>
       <c r="AB232" s="14" t="inlineStr"/>
       <c r="AC232" s="15" t="n">
-        <v>0.9675929454545454</v>
+        <v>0.9869674909090909</v>
       </c>
       <c r="AD232" s="15" t="inlineStr"/>
       <c r="AE232" s="14" t="n">
-        <v>891194.0</v>
+        <v>358394.0</v>
       </c>
       <c r="AF232" s="14" t="inlineStr"/>
       <c r="AG232" s="14" t="inlineStr"/>
@@ -14124,20 +14124,20 @@
         <v>3.84588968E8</v>
       </c>
       <c r="X233" s="14" t="n">
-        <v>4.2179575E7</v>
+        <v>4.7655375E7</v>
       </c>
       <c r="Y233" s="14" t="inlineStr"/>
       <c r="Z233" s="14" t="n">
-        <v>4.26768543E8</v>
+        <v>4.32244343E8</v>
       </c>
       <c r="AA233" s="14" t="inlineStr"/>
       <c r="AB233" s="14" t="inlineStr"/>
       <c r="AC233" s="15" t="n">
-        <v>0.6026655129318562</v>
+        <v>0.6103982192661004</v>
       </c>
       <c r="AD233" s="15" t="inlineStr"/>
       <c r="AE233" s="14" t="n">
-        <v>2.81366457E8</v>
+        <v>2.75890657E8</v>
       </c>
       <c r="AF233" s="14" t="inlineStr"/>
       <c r="AG233" s="14" t="inlineStr"/>
@@ -15288,20 +15288,20 @@
         <v>8.8386927E7</v>
       </c>
       <c r="X253" s="14" t="n">
-        <v>6689575.0</v>
+        <v>1.2165375E7</v>
       </c>
       <c r="Y253" s="14" t="inlineStr"/>
       <c r="Z253" s="14" t="n">
-        <v>9.5076502E7</v>
+        <v>1.00552302E8</v>
       </c>
       <c r="AA253" s="14" t="inlineStr"/>
       <c r="AB253" s="14" t="inlineStr"/>
       <c r="AC253" s="15" t="n">
-        <v>0.4663813499460414</v>
+        <v>0.49324194054743453</v>
       </c>
       <c r="AD253" s="15" t="inlineStr"/>
       <c r="AE253" s="14" t="n">
-        <v>1.08783498E8</v>
+        <v>1.03307698E8</v>
       </c>
       <c r="AF253" s="14" t="inlineStr"/>
       <c r="AG253" s="14" t="inlineStr"/>
@@ -15559,20 +15559,20 @@
         <v>6.6116077E7</v>
       </c>
       <c r="X258" s="14" t="n">
-        <v>1225000.0</v>
+        <v>4737800.0</v>
       </c>
       <c r="Y258" s="14" t="inlineStr"/>
       <c r="Z258" s="14" t="n">
-        <v>6.7341077E7</v>
+        <v>7.0853877E7</v>
       </c>
       <c r="AA258" s="14" t="inlineStr"/>
       <c r="AB258" s="14" t="inlineStr"/>
       <c r="AC258" s="15" t="n">
-        <v>0.5404580818619583</v>
+        <v>0.5686506982343499</v>
       </c>
       <c r="AD258" s="15" t="inlineStr"/>
       <c r="AE258" s="14" t="n">
-        <v>5.7258923E7</v>
+        <v>5.3746123E7</v>
       </c>
       <c r="AF258" s="14" t="inlineStr"/>
       <c r="AG258" s="14" t="inlineStr"/>
@@ -15844,20 +15844,20 @@
         <v>3707013.0</v>
       </c>
       <c r="X263" s="14" t="n">
-        <v>385700.0</v>
+        <v>2348700.0</v>
       </c>
       <c r="Y263" s="14" t="inlineStr"/>
       <c r="Z263" s="14" t="n">
-        <v>4092713.0</v>
+        <v>6055713.0</v>
       </c>
       <c r="AA263" s="14" t="inlineStr"/>
       <c r="AB263" s="14" t="inlineStr"/>
       <c r="AC263" s="15" t="n">
-        <v>0.4092713</v>
+        <v>0.6055713</v>
       </c>
       <c r="AD263" s="15" t="inlineStr"/>
       <c r="AE263" s="14" t="n">
-        <v>5907287.0</v>
+        <v>3944287.0</v>
       </c>
       <c r="AF263" s="14" t="inlineStr"/>
       <c r="AG263" s="14" t="inlineStr"/>

--- a/Database/Akrual.xlsx
+++ b/Database/Akrual.xlsx
@@ -601,7 +601,7 @@
       <c r="A3" s="4" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Periode Agustus 2025</t>
+            <t xml:space="preserve">Periode September 2025</t>
           </r>
         </is>
       </c>
@@ -979,22 +979,22 @@
       <c r="U9" s="10" t="inlineStr"/>
       <c r="V9" s="10" t="inlineStr"/>
       <c r="W9" s="11" t="n">
-        <v>6.1530207365E10</v>
+        <v>6.7689543395E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>5.974419026E9</v>
+        <v>6.293932321E9</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>6.7504626391E10</v>
+        <v>7.3983475716E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.7940711814381232</v>
+        <v>0.8702832547864506</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>1.7506173609E10</v>
+        <v>1.1027324284E10</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1032,7 +1032,7 @@
       <c r="O10" s="13" t="inlineStr"/>
       <c r="P10" s="13" t="inlineStr"/>
       <c r="Q10" s="14" t="n">
-        <v>5.045936E9</v>
+        <v>4.0334E9</v>
       </c>
       <c r="R10" s="14" t="inlineStr"/>
       <c r="S10" s="14" t="n">
@@ -1054,11 +1054,11 @@
       <c r="AA10" s="14" t="inlineStr"/>
       <c r="AB10" s="14" t="inlineStr"/>
       <c r="AC10" s="15" t="n">
-        <v>0.7993300033928294</v>
+        <v>0.9999920761640303</v>
       </c>
       <c r="AD10" s="15" t="inlineStr"/>
       <c r="AE10" s="14" t="n">
-        <v>1.01256796E9</v>
+        <v>31960.0</v>
       </c>
       <c r="AF10" s="14" t="inlineStr"/>
       <c r="AG10" s="14" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       <c r="O11" s="13" t="inlineStr"/>
       <c r="P11" s="13" t="inlineStr"/>
       <c r="Q11" s="14" t="n">
-        <v>5.045936E9</v>
+        <v>4.0334E9</v>
       </c>
       <c r="R11" s="14" t="inlineStr"/>
       <c r="S11" s="14" t="n">
@@ -1117,11 +1117,11 @@
       <c r="AA11" s="14" t="inlineStr"/>
       <c r="AB11" s="14" t="inlineStr"/>
       <c r="AC11" s="15" t="n">
-        <v>0.7993300033928294</v>
+        <v>0.9999920761640303</v>
       </c>
       <c r="AD11" s="15" t="inlineStr"/>
       <c r="AE11" s="14" t="n">
-        <v>1.01256796E9</v>
+        <v>31960.0</v>
       </c>
       <c r="AF11" s="14" t="inlineStr"/>
       <c r="AG11" s="14" t="inlineStr"/>
@@ -1158,7 +1158,7 @@
       <c r="O12" s="16" t="inlineStr"/>
       <c r="P12" s="16" t="inlineStr"/>
       <c r="Q12" s="17" t="n">
-        <v>5.045936E9</v>
+        <v>4.0334E9</v>
       </c>
       <c r="R12" s="17" t="inlineStr"/>
       <c r="S12" s="17" t="n">
@@ -1180,11 +1180,11 @@
       <c r="AA12" s="17" t="inlineStr"/>
       <c r="AB12" s="17" t="inlineStr"/>
       <c r="AC12" s="18" t="n">
-        <v>0.7993300033928294</v>
+        <v>0.9999920761640303</v>
       </c>
       <c r="AD12" s="18" t="inlineStr"/>
       <c r="AE12" s="17" t="n">
-        <v>1.01256796E9</v>
+        <v>31960.0</v>
       </c>
       <c r="AF12" s="17" t="inlineStr"/>
       <c r="AG12" s="17" t="inlineStr"/>
@@ -1221,7 +1221,7 @@
       <c r="O13" s="20" t="inlineStr"/>
       <c r="P13" s="20" t="inlineStr"/>
       <c r="Q13" s="21" t="n">
-        <v>5.045936E9</v>
+        <v>4.0334E9</v>
       </c>
       <c r="R13" s="21" t="inlineStr"/>
       <c r="S13" s="21" t="n">
@@ -1243,11 +1243,11 @@
       <c r="AA13" s="21" t="inlineStr"/>
       <c r="AB13" s="21" t="inlineStr"/>
       <c r="AC13" s="23" t="n">
-        <v>0.7993300033928294</v>
+        <v>0.9999920761640303</v>
       </c>
       <c r="AD13" s="23" t="inlineStr"/>
       <c r="AE13" s="21" t="n">
-        <v>1.01256796E9</v>
+        <v>31960.0</v>
       </c>
       <c r="AF13" s="21" t="inlineStr"/>
       <c r="AG13" s="21" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
       <c r="O14" s="24" t="inlineStr"/>
       <c r="P14" s="24" t="inlineStr"/>
       <c r="Q14" s="25" t="n">
-        <v>5.045936E9</v>
+        <v>4.0334E9</v>
       </c>
       <c r="R14" s="25" t="inlineStr"/>
       <c r="S14" s="25" t="n">
@@ -1306,11 +1306,11 @@
       <c r="AA14" s="25" t="inlineStr"/>
       <c r="AB14" s="25" t="inlineStr"/>
       <c r="AC14" s="26" t="n">
-        <v>0.7993300033928294</v>
+        <v>0.9999920761640303</v>
       </c>
       <c r="AD14" s="26" t="inlineStr"/>
       <c r="AE14" s="25" t="n">
-        <v>1.01256796E9</v>
+        <v>31960.0</v>
       </c>
       <c r="AF14" s="25" t="inlineStr"/>
       <c r="AG14" s="25" t="inlineStr"/>
@@ -1347,7 +1347,7 @@
       <c r="O15" s="13" t="inlineStr"/>
       <c r="P15" s="13" t="inlineStr"/>
       <c r="Q15" s="14" t="n">
-        <v>5.045936E9</v>
+        <v>4.0334E9</v>
       </c>
       <c r="R15" s="14" t="inlineStr"/>
       <c r="S15" s="14" t="n">
@@ -1369,11 +1369,11 @@
       <c r="AA15" s="14" t="inlineStr"/>
       <c r="AB15" s="14" t="inlineStr"/>
       <c r="AC15" s="15" t="n">
-        <v>0.7993300033928294</v>
+        <v>0.9999920761640303</v>
       </c>
       <c r="AD15" s="15" t="inlineStr"/>
       <c r="AE15" s="14" t="n">
-        <v>1.01256796E9</v>
+        <v>31960.0</v>
       </c>
       <c r="AF15" s="14" t="inlineStr"/>
       <c r="AG15" s="14" t="inlineStr"/>
@@ -1410,7 +1410,7 @@
       <c r="O16" s="13" t="inlineStr"/>
       <c r="P16" s="13" t="inlineStr"/>
       <c r="Q16" s="14" t="n">
-        <v>5.045936E9</v>
+        <v>4.0334E9</v>
       </c>
       <c r="R16" s="14" t="inlineStr"/>
       <c r="S16" s="14" t="n">
@@ -1432,11 +1432,11 @@
       <c r="AA16" s="14" t="inlineStr"/>
       <c r="AB16" s="14" t="inlineStr"/>
       <c r="AC16" s="15" t="n">
-        <v>0.7993300033928294</v>
+        <v>0.9999920761640303</v>
       </c>
       <c r="AD16" s="15" t="inlineStr"/>
       <c r="AE16" s="14" t="n">
-        <v>1.01256796E9</v>
+        <v>31960.0</v>
       </c>
       <c r="AF16" s="14" t="inlineStr"/>
       <c r="AG16" s="14" t="inlineStr"/>
@@ -1467,7 +1467,7 @@
       <c r="O17" s="13" t="inlineStr"/>
       <c r="P17" s="13" t="inlineStr"/>
       <c r="Q17" s="14" t="n">
-        <v>4.32E8</v>
+        <v>3.456E8</v>
       </c>
       <c r="R17" s="14" t="inlineStr"/>
       <c r="S17" s="14" t="n">
@@ -1489,11 +1489,11 @@
       <c r="AA17" s="14" t="inlineStr"/>
       <c r="AB17" s="14" t="inlineStr"/>
       <c r="AC17" s="15" t="n">
-        <v>0.8</v>
+        <v>1.0</v>
       </c>
       <c r="AD17" s="15" t="inlineStr"/>
       <c r="AE17" s="14" t="n">
-        <v>8.64E7</v>
+        <v>0.0</v>
       </c>
       <c r="AF17" s="14" t="inlineStr"/>
       <c r="AG17" s="14" t="inlineStr"/>
@@ -1524,7 +1524,7 @@
       <c r="O18" s="13" t="inlineStr"/>
       <c r="P18" s="13" t="inlineStr"/>
       <c r="Q18" s="14" t="n">
-        <v>4.446E9</v>
+        <v>3.5568E9</v>
       </c>
       <c r="R18" s="14" t="inlineStr"/>
       <c r="S18" s="14" t="n">
@@ -1546,11 +1546,11 @@
       <c r="AA18" s="14" t="inlineStr"/>
       <c r="AB18" s="14" t="inlineStr"/>
       <c r="AC18" s="15" t="n">
-        <v>0.8</v>
+        <v>1.0</v>
       </c>
       <c r="AD18" s="15" t="inlineStr"/>
       <c r="AE18" s="14" t="n">
-        <v>8.892E8</v>
+        <v>0.0</v>
       </c>
       <c r="AF18" s="14" t="inlineStr"/>
       <c r="AG18" s="14" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
       <c r="O19" s="13" t="inlineStr"/>
       <c r="P19" s="13" t="inlineStr"/>
       <c r="Q19" s="14" t="n">
-        <v>1.4E8</v>
+        <v>1.12E8</v>
       </c>
       <c r="R19" s="14" t="inlineStr"/>
       <c r="S19" s="14" t="n">
@@ -1603,11 +1603,11 @@
       <c r="AA19" s="14" t="inlineStr"/>
       <c r="AB19" s="14" t="inlineStr"/>
       <c r="AC19" s="15" t="n">
-        <v>0.8</v>
+        <v>1.0</v>
       </c>
       <c r="AD19" s="15" t="inlineStr"/>
       <c r="AE19" s="14" t="n">
-        <v>2.8E7</v>
+        <v>0.0</v>
       </c>
       <c r="AF19" s="14" t="inlineStr"/>
       <c r="AG19" s="14" t="inlineStr"/>
@@ -1638,7 +1638,7 @@
       <c r="O20" s="13" t="inlineStr"/>
       <c r="P20" s="13" t="inlineStr"/>
       <c r="Q20" s="14" t="n">
-        <v>2.7936E7</v>
+        <v>1.9E7</v>
       </c>
       <c r="R20" s="14" t="inlineStr"/>
       <c r="S20" s="14" t="n">
@@ -1660,11 +1660,11 @@
       <c r="AA20" s="14" t="inlineStr"/>
       <c r="AB20" s="14" t="inlineStr"/>
       <c r="AC20" s="15" t="n">
-        <v>0.6789819587628866</v>
+        <v>0.9983178947368421</v>
       </c>
       <c r="AD20" s="15" t="inlineStr"/>
       <c r="AE20" s="14" t="n">
-        <v>8967960.0</v>
+        <v>31960.0</v>
       </c>
       <c r="AF20" s="14" t="inlineStr"/>
       <c r="AG20" s="14" t="inlineStr"/>
@@ -1701,7 +1701,7 @@
       <c r="O21" s="13" t="inlineStr"/>
       <c r="P21" s="13" t="inlineStr"/>
       <c r="Q21" s="14" t="n">
-        <v>7.9964864E10</v>
+        <v>8.09774E10</v>
       </c>
       <c r="R21" s="14" t="inlineStr"/>
       <c r="S21" s="14" t="n">
@@ -1711,23 +1711,23 @@
       <c r="U21" s="14" t="inlineStr"/>
       <c r="V21" s="14" t="inlineStr"/>
       <c r="W21" s="14" t="n">
-        <v>5.7496839325E10</v>
+        <v>6.3656175355E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>5.974419026E9</v>
+        <v>6.293932321E9</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>6.3471258351E10</v>
+        <v>6.9950107676E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.7937393397054987</v>
+        <v>0.8638225934149528</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>1.6493605649E10</v>
+        <v>1.1027292324E10</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1764,7 +1764,7 @@
       <c r="O22" s="13" t="inlineStr"/>
       <c r="P22" s="13" t="inlineStr"/>
       <c r="Q22" s="14" t="n">
-        <v>7.9964864E10</v>
+        <v>8.09774E10</v>
       </c>
       <c r="R22" s="14" t="inlineStr"/>
       <c r="S22" s="14" t="n">
@@ -1774,23 +1774,23 @@
       <c r="U22" s="14" t="inlineStr"/>
       <c r="V22" s="14" t="inlineStr"/>
       <c r="W22" s="14" t="n">
-        <v>5.7496839325E10</v>
+        <v>6.3656175355E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>5.974419026E9</v>
+        <v>6.293932321E9</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>6.3471258351E10</v>
+        <v>6.9950107676E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.7937393397054987</v>
+        <v>0.8638225934149528</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>1.6493605649E10</v>
+        <v>1.1027292324E10</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1827,7 +1827,7 @@
       <c r="O23" s="16" t="inlineStr"/>
       <c r="P23" s="16" t="inlineStr"/>
       <c r="Q23" s="17" t="n">
-        <v>7.9964264E10</v>
+        <v>8.09768E10</v>
       </c>
       <c r="R23" s="17" t="inlineStr"/>
       <c r="S23" s="17" t="n">
@@ -1837,23 +1837,23 @@
       <c r="U23" s="17" t="inlineStr"/>
       <c r="V23" s="17" t="inlineStr"/>
       <c r="W23" s="17" t="n">
-        <v>5.7496239325E10</v>
+        <v>6.3655575355E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>5.974419026E9</v>
+        <v>6.293932321E9</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>6.3470658351E10</v>
+        <v>6.9949507676E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.7937377920592128</v>
+        <v>0.863821584404422</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>1.6493605649E10</v>
+        <v>1.1027292324E10</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -2561,23 +2561,23 @@
       <c r="U35" s="21" t="inlineStr"/>
       <c r="V35" s="21" t="inlineStr"/>
       <c r="W35" s="22" t="n">
-        <v>9686100.0</v>
+        <v>1.20161E7</v>
       </c>
       <c r="X35" s="22" t="n">
-        <v>0.0</v>
+        <v>1700452.0</v>
       </c>
       <c r="Y35" s="22" t="inlineStr"/>
       <c r="Z35" s="21" t="n">
-        <v>9686100.0</v>
+        <v>1.3716552E7</v>
       </c>
       <c r="AA35" s="21" t="inlineStr"/>
       <c r="AB35" s="21" t="inlineStr"/>
       <c r="AC35" s="23" t="n">
-        <v>0.55412471395881</v>
+        <v>0.784699771167048</v>
       </c>
       <c r="AD35" s="23" t="inlineStr"/>
       <c r="AE35" s="21" t="n">
-        <v>7793900.0</v>
+        <v>3763448.0</v>
       </c>
       <c r="AF35" s="21" t="inlineStr"/>
       <c r="AG35" s="21" t="inlineStr"/>
@@ -2624,23 +2624,23 @@
       <c r="U36" s="25" t="inlineStr"/>
       <c r="V36" s="25" t="inlineStr"/>
       <c r="W36" s="25" t="n">
-        <v>9686100.0</v>
+        <v>1.20161E7</v>
       </c>
       <c r="X36" s="25" t="n">
-        <v>0.0</v>
+        <v>1700452.0</v>
       </c>
       <c r="Y36" s="25" t="inlineStr"/>
       <c r="Z36" s="25" t="n">
-        <v>9686100.0</v>
+        <v>1.3716552E7</v>
       </c>
       <c r="AA36" s="25" t="inlineStr"/>
       <c r="AB36" s="25" t="inlineStr"/>
       <c r="AC36" s="26" t="n">
-        <v>0.55412471395881</v>
+        <v>0.784699771167048</v>
       </c>
       <c r="AD36" s="26" t="inlineStr"/>
       <c r="AE36" s="25" t="n">
-        <v>7793900.0</v>
+        <v>3763448.0</v>
       </c>
       <c r="AF36" s="25" t="inlineStr"/>
       <c r="AG36" s="25" t="inlineStr"/>
@@ -2990,23 +2990,23 @@
       <c r="U42" s="14" t="inlineStr"/>
       <c r="V42" s="14" t="inlineStr"/>
       <c r="W42" s="14" t="n">
-        <v>7286100.0</v>
+        <v>9616100.0</v>
       </c>
       <c r="X42" s="14" t="n">
-        <v>0.0</v>
+        <v>1700452.0</v>
       </c>
       <c r="Y42" s="14" t="inlineStr"/>
       <c r="Z42" s="14" t="n">
-        <v>7286100.0</v>
+        <v>1.1316552E7</v>
       </c>
       <c r="AA42" s="14" t="inlineStr"/>
       <c r="AB42" s="14" t="inlineStr"/>
       <c r="AC42" s="15" t="n">
-        <v>0.4831631299734748</v>
+        <v>0.7504344827586207</v>
       </c>
       <c r="AD42" s="15" t="inlineStr"/>
       <c r="AE42" s="14" t="n">
-        <v>7793900.0</v>
+        <v>3763448.0</v>
       </c>
       <c r="AF42" s="14" t="inlineStr"/>
       <c r="AG42" s="14" t="inlineStr"/>
@@ -3053,23 +3053,23 @@
       <c r="U43" s="14" t="inlineStr"/>
       <c r="V43" s="14" t="inlineStr"/>
       <c r="W43" s="14" t="n">
-        <v>7286100.0</v>
+        <v>9616100.0</v>
       </c>
       <c r="X43" s="14" t="n">
-        <v>0.0</v>
+        <v>1700452.0</v>
       </c>
       <c r="Y43" s="14" t="inlineStr"/>
       <c r="Z43" s="14" t="n">
-        <v>7286100.0</v>
+        <v>1.1316552E7</v>
       </c>
       <c r="AA43" s="14" t="inlineStr"/>
       <c r="AB43" s="14" t="inlineStr"/>
       <c r="AC43" s="15" t="n">
-        <v>0.4831631299734748</v>
+        <v>0.7504344827586207</v>
       </c>
       <c r="AD43" s="15" t="inlineStr"/>
       <c r="AE43" s="14" t="n">
-        <v>7793900.0</v>
+        <v>3763448.0</v>
       </c>
       <c r="AF43" s="14" t="inlineStr"/>
       <c r="AG43" s="14" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
       <c r="O44" s="13" t="inlineStr"/>
       <c r="P44" s="13" t="inlineStr"/>
       <c r="Q44" s="14" t="n">
-        <v>1.29E7</v>
+        <v>1.376E7</v>
       </c>
       <c r="R44" s="14" t="inlineStr"/>
       <c r="S44" s="14" t="n">
@@ -3110,23 +3110,23 @@
       <c r="U44" s="14" t="inlineStr"/>
       <c r="V44" s="14" t="inlineStr"/>
       <c r="W44" s="14" t="n">
-        <v>6537000.0</v>
+        <v>8867000.0</v>
       </c>
       <c r="X44" s="14" t="n">
-        <v>0.0</v>
+        <v>1700452.0</v>
       </c>
       <c r="Y44" s="14" t="inlineStr"/>
       <c r="Z44" s="14" t="n">
-        <v>6537000.0</v>
+        <v>1.0567452E7</v>
       </c>
       <c r="AA44" s="14" t="inlineStr"/>
       <c r="AB44" s="14" t="inlineStr"/>
       <c r="AC44" s="15" t="n">
-        <v>0.5067441860465116</v>
+        <v>0.7679834302325581</v>
       </c>
       <c r="AD44" s="15" t="inlineStr"/>
       <c r="AE44" s="14" t="n">
-        <v>6363000.0</v>
+        <v>3192548.0</v>
       </c>
       <c r="AF44" s="14" t="inlineStr"/>
       <c r="AG44" s="14" t="inlineStr"/>
@@ -3157,7 +3157,7 @@
       <c r="O45" s="13" t="inlineStr"/>
       <c r="P45" s="13" t="inlineStr"/>
       <c r="Q45" s="14" t="n">
-        <v>2180000.0</v>
+        <v>1320000.0</v>
       </c>
       <c r="R45" s="14" t="inlineStr"/>
       <c r="S45" s="14" t="n">
@@ -3179,11 +3179,11 @@
       <c r="AA45" s="14" t="inlineStr"/>
       <c r="AB45" s="14" t="inlineStr"/>
       <c r="AC45" s="15" t="n">
-        <v>0.3436238532110092</v>
+        <v>0.5675</v>
       </c>
       <c r="AD45" s="15" t="inlineStr"/>
       <c r="AE45" s="14" t="n">
-        <v>1430900.0</v>
+        <v>570900.0</v>
       </c>
       <c r="AF45" s="14" t="inlineStr"/>
       <c r="AG45" s="14" t="inlineStr"/>
@@ -3220,7 +3220,7 @@
       <c r="O46" s="20" t="inlineStr"/>
       <c r="P46" s="20" t="inlineStr"/>
       <c r="Q46" s="21" t="n">
-        <v>7.9945734E10</v>
+        <v>8.095827E10</v>
       </c>
       <c r="R46" s="21" t="inlineStr"/>
       <c r="S46" s="21" t="n">
@@ -3230,23 +3230,23 @@
       <c r="U46" s="21" t="inlineStr"/>
       <c r="V46" s="21" t="inlineStr"/>
       <c r="W46" s="22" t="n">
-        <v>5.7485503225E10</v>
+        <v>6.3642509255E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>5.974419026E9</v>
+        <v>6.292231869E9</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>6.3459922251E10</v>
+        <v>6.9934741124E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.7937874740258186</v>
+        <v>0.8638369017025685</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>1.6485811749E10</v>
+        <v>1.1023528876E10</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -3293,23 +3293,23 @@
       <c r="U47" s="25" t="inlineStr"/>
       <c r="V47" s="25" t="inlineStr"/>
       <c r="W47" s="25" t="n">
-        <v>5.3329786245E10</v>
+        <v>5.9247454753E10</v>
       </c>
       <c r="X47" s="25" t="n">
-        <v>5.735081504E9</v>
+        <v>5.60949684E9</v>
       </c>
       <c r="Y47" s="25" t="inlineStr"/>
       <c r="Z47" s="25" t="n">
-        <v>5.9064867749E10</v>
+        <v>6.4856951593E10</v>
       </c>
       <c r="AA47" s="25" t="inlineStr"/>
       <c r="AB47" s="25" t="inlineStr"/>
       <c r="AC47" s="26" t="n">
-        <v>0.7950584947644006</v>
+        <v>0.8730243929042099</v>
       </c>
       <c r="AD47" s="26" t="inlineStr"/>
       <c r="AE47" s="25" t="n">
-        <v>1.5225097251E10</v>
+        <v>9.433013407E9</v>
       </c>
       <c r="AF47" s="25" t="inlineStr"/>
       <c r="AG47" s="25" t="inlineStr"/>
@@ -3356,23 +3356,23 @@
       <c r="U48" s="14" t="inlineStr"/>
       <c r="V48" s="14" t="inlineStr"/>
       <c r="W48" s="14" t="n">
-        <v>4.187549504E9</v>
+        <v>4.609721667E9</v>
       </c>
       <c r="X48" s="14" t="n">
-        <v>2.39585159E8</v>
+        <v>2.35173209E8</v>
       </c>
       <c r="Y48" s="14" t="inlineStr"/>
       <c r="Z48" s="14" t="n">
-        <v>4.427134663E9</v>
+        <v>4.844894876E9</v>
       </c>
       <c r="AA48" s="14" t="inlineStr"/>
       <c r="AB48" s="14" t="inlineStr"/>
       <c r="AC48" s="15" t="n">
-        <v>0.6909982635821434</v>
+        <v>0.7562033236832724</v>
       </c>
       <c r="AD48" s="15" t="inlineStr"/>
       <c r="AE48" s="14" t="n">
-        <v>1.979733337E9</v>
+        <v>1.561973124E9</v>
       </c>
       <c r="AF48" s="14" t="inlineStr"/>
       <c r="AG48" s="14" t="inlineStr"/>
@@ -3419,23 +3419,23 @@
       <c r="U49" s="14" t="inlineStr"/>
       <c r="V49" s="14" t="inlineStr"/>
       <c r="W49" s="14" t="n">
-        <v>1.6503171E9</v>
+        <v>1.8149987E9</v>
       </c>
       <c r="X49" s="14" t="n">
         <v>1.646816E8</v>
       </c>
       <c r="Y49" s="14" t="inlineStr"/>
       <c r="Z49" s="14" t="n">
-        <v>1.8149987E9</v>
+        <v>1.9796803E9</v>
       </c>
       <c r="AA49" s="14" t="inlineStr"/>
       <c r="AB49" s="14" t="inlineStr"/>
       <c r="AC49" s="15" t="n">
-        <v>0.6476568365491392</v>
+        <v>0.7064211563769444</v>
       </c>
       <c r="AD49" s="15" t="inlineStr"/>
       <c r="AE49" s="14" t="n">
-        <v>9.874093E8</v>
+        <v>8.227277E8</v>
       </c>
       <c r="AF49" s="14" t="inlineStr"/>
       <c r="AG49" s="14" t="inlineStr"/>
@@ -3466,7 +3466,7 @@
       <c r="O50" s="13" t="inlineStr"/>
       <c r="P50" s="13" t="inlineStr"/>
       <c r="Q50" s="14" t="n">
-        <v>2.4588E9</v>
+        <v>2.472216E9</v>
       </c>
       <c r="R50" s="14" t="inlineStr"/>
       <c r="S50" s="14" t="n">
@@ -3476,23 +3476,23 @@
       <c r="U50" s="14" t="inlineStr"/>
       <c r="V50" s="14" t="inlineStr"/>
       <c r="W50" s="14" t="n">
-        <v>1.3201367E9</v>
+        <v>1.4848183E9</v>
       </c>
       <c r="X50" s="14" t="n">
         <v>1.646816E8</v>
       </c>
       <c r="Y50" s="14" t="inlineStr"/>
       <c r="Z50" s="14" t="n">
-        <v>1.4848183E9</v>
+        <v>1.6494999E9</v>
       </c>
       <c r="AA50" s="14" t="inlineStr"/>
       <c r="AB50" s="14" t="inlineStr"/>
       <c r="AC50" s="15" t="n">
-        <v>0.6038792500406702</v>
+        <v>0.6672151219796328</v>
       </c>
       <c r="AD50" s="15" t="inlineStr"/>
       <c r="AE50" s="14" t="n">
-        <v>9.739817E8</v>
+        <v>8.227161E8</v>
       </c>
       <c r="AF50" s="14" t="inlineStr"/>
       <c r="AG50" s="14" t="inlineStr"/>
@@ -3523,7 +3523,7 @@
       <c r="O51" s="13" t="inlineStr"/>
       <c r="P51" s="13" t="inlineStr"/>
       <c r="Q51" s="14" t="n">
-        <v>1.77225E8</v>
+        <v>1.63809E8</v>
       </c>
       <c r="R51" s="14" t="inlineStr"/>
       <c r="S51" s="14" t="n">
@@ -3545,11 +3545,11 @@
       <c r="AA51" s="14" t="inlineStr"/>
       <c r="AB51" s="14" t="inlineStr"/>
       <c r="AC51" s="15" t="n">
-        <v>0.9242341656086895</v>
+        <v>0.999929185820071</v>
       </c>
       <c r="AD51" s="15" t="inlineStr"/>
       <c r="AE51" s="14" t="n">
-        <v>1.34276E7</v>
+        <v>11600.0</v>
       </c>
       <c r="AF51" s="14" t="inlineStr"/>
       <c r="AG51" s="14" t="inlineStr"/>
@@ -3653,23 +3653,23 @@
       <c r="U53" s="14" t="inlineStr"/>
       <c r="V53" s="14" t="inlineStr"/>
       <c r="W53" s="14" t="n">
-        <v>19549.0</v>
+        <v>21374.0</v>
       </c>
       <c r="X53" s="14" t="n">
-        <v>1825.0</v>
+        <v>1875.0</v>
       </c>
       <c r="Y53" s="14" t="inlineStr"/>
       <c r="Z53" s="14" t="n">
-        <v>21374.0</v>
+        <v>23249.0</v>
       </c>
       <c r="AA53" s="14" t="inlineStr"/>
       <c r="AB53" s="14" t="inlineStr"/>
       <c r="AC53" s="15" t="n">
-        <v>0.7124666666666667</v>
+        <v>0.7749666666666667</v>
       </c>
       <c r="AD53" s="15" t="inlineStr"/>
       <c r="AE53" s="14" t="n">
-        <v>8626.0</v>
+        <v>6751.0</v>
       </c>
       <c r="AF53" s="14" t="inlineStr"/>
       <c r="AG53" s="14" t="inlineStr"/>
@@ -3710,23 +3710,23 @@
       <c r="U54" s="14" t="inlineStr"/>
       <c r="V54" s="14" t="inlineStr"/>
       <c r="W54" s="14" t="n">
-        <v>14967.0</v>
+        <v>16792.0</v>
       </c>
       <c r="X54" s="14" t="n">
-        <v>1825.0</v>
+        <v>1875.0</v>
       </c>
       <c r="Y54" s="14" t="inlineStr"/>
       <c r="Z54" s="14" t="n">
-        <v>16792.0</v>
+        <v>18667.0</v>
       </c>
       <c r="AA54" s="14" t="inlineStr"/>
       <c r="AB54" s="14" t="inlineStr"/>
       <c r="AC54" s="15" t="n">
-        <v>0.6996666666666667</v>
+        <v>0.7777916666666667</v>
       </c>
       <c r="AD54" s="15" t="inlineStr"/>
       <c r="AE54" s="14" t="n">
-        <v>7208.0</v>
+        <v>5333.0</v>
       </c>
       <c r="AF54" s="14" t="inlineStr"/>
       <c r="AG54" s="14" t="inlineStr"/>
@@ -3887,23 +3887,23 @@
       <c r="U57" s="14" t="inlineStr"/>
       <c r="V57" s="14" t="inlineStr"/>
       <c r="W57" s="14" t="n">
-        <v>1.2585432E8</v>
+        <v>1.3838814E8</v>
       </c>
       <c r="X57" s="14" t="n">
         <v>1.253382E7</v>
       </c>
       <c r="Y57" s="14" t="inlineStr"/>
       <c r="Z57" s="14" t="n">
-        <v>1.3838814E8</v>
+        <v>1.5092196E8</v>
       </c>
       <c r="AA57" s="14" t="inlineStr"/>
       <c r="AB57" s="14" t="inlineStr"/>
       <c r="AC57" s="15" t="n">
-        <v>0.7603743956043956</v>
+        <v>0.8292415384615385</v>
       </c>
       <c r="AD57" s="15" t="inlineStr"/>
       <c r="AE57" s="14" t="n">
-        <v>4.361186E7</v>
+        <v>3.107804E7</v>
       </c>
       <c r="AF57" s="14" t="inlineStr"/>
       <c r="AG57" s="14" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       <c r="O58" s="13" t="inlineStr"/>
       <c r="P58" s="13" t="inlineStr"/>
       <c r="Q58" s="14" t="n">
-        <v>1.56E8</v>
+        <v>1.56792E8</v>
       </c>
       <c r="R58" s="14" t="inlineStr"/>
       <c r="S58" s="14" t="n">
@@ -3944,23 +3944,23 @@
       <c r="U58" s="14" t="inlineStr"/>
       <c r="V58" s="14" t="inlineStr"/>
       <c r="W58" s="14" t="n">
-        <v>1.00656E8</v>
+        <v>1.1318982E8</v>
       </c>
       <c r="X58" s="14" t="n">
         <v>1.253382E7</v>
       </c>
       <c r="Y58" s="14" t="inlineStr"/>
       <c r="Z58" s="14" t="n">
-        <v>1.1318982E8</v>
+        <v>1.2572364E8</v>
       </c>
       <c r="AA58" s="14" t="inlineStr"/>
       <c r="AB58" s="14" t="inlineStr"/>
       <c r="AC58" s="15" t="n">
-        <v>0.7255757692307693</v>
+        <v>0.8018498392775142</v>
       </c>
       <c r="AD58" s="15" t="inlineStr"/>
       <c r="AE58" s="14" t="n">
-        <v>4.281018E7</v>
+        <v>3.106836E7</v>
       </c>
       <c r="AF58" s="14" t="inlineStr"/>
       <c r="AG58" s="14" t="inlineStr"/>
@@ -3991,7 +3991,7 @@
       <c r="O59" s="13" t="inlineStr"/>
       <c r="P59" s="13" t="inlineStr"/>
       <c r="Q59" s="14" t="n">
-        <v>1.3E7</v>
+        <v>1.246E7</v>
       </c>
       <c r="R59" s="14" t="inlineStr"/>
       <c r="S59" s="14" t="n">
@@ -4013,11 +4013,11 @@
       <c r="AA59" s="14" t="inlineStr"/>
       <c r="AB59" s="14" t="inlineStr"/>
       <c r="AC59" s="15" t="n">
-        <v>0.9584530769230769</v>
+        <v>0.9999911717495987</v>
       </c>
       <c r="AD59" s="15" t="inlineStr"/>
       <c r="AE59" s="14" t="n">
-        <v>540110.0</v>
+        <v>110.0</v>
       </c>
       <c r="AF59" s="14" t="inlineStr"/>
       <c r="AG59" s="14" t="inlineStr"/>
@@ -4048,7 +4048,7 @@
       <c r="O60" s="13" t="inlineStr"/>
       <c r="P60" s="13" t="inlineStr"/>
       <c r="Q60" s="14" t="n">
-        <v>1.3E7</v>
+        <v>1.2748E7</v>
       </c>
       <c r="R60" s="14" t="inlineStr"/>
       <c r="S60" s="14" t="n">
@@ -4070,11 +4070,11 @@
       <c r="AA60" s="14" t="inlineStr"/>
       <c r="AB60" s="14" t="inlineStr"/>
       <c r="AC60" s="15" t="n">
-        <v>0.9798792307692308</v>
+        <v>0.999249294006903</v>
       </c>
       <c r="AD60" s="15" t="inlineStr"/>
       <c r="AE60" s="14" t="n">
-        <v>261570.0</v>
+        <v>9570.0</v>
       </c>
       <c r="AF60" s="14" t="inlineStr"/>
       <c r="AG60" s="14" t="inlineStr"/>
@@ -4164,23 +4164,23 @@
       <c r="U62" s="14" t="inlineStr"/>
       <c r="V62" s="14" t="inlineStr"/>
       <c r="W62" s="14" t="n">
-        <v>3.8237084E7</v>
+        <v>4.2035848E7</v>
       </c>
       <c r="X62" s="14" t="n">
         <v>3798764.0</v>
       </c>
       <c r="Y62" s="14" t="inlineStr"/>
       <c r="Z62" s="14" t="n">
-        <v>4.2035848E7</v>
+        <v>4.5834612E7</v>
       </c>
       <c r="AA62" s="14" t="inlineStr"/>
       <c r="AB62" s="14" t="inlineStr"/>
       <c r="AC62" s="15" t="n">
-        <v>0.7506401428571429</v>
+        <v>0.8184752142857142</v>
       </c>
       <c r="AD62" s="15" t="inlineStr"/>
       <c r="AE62" s="14" t="n">
-        <v>1.3964152E7</v>
+        <v>1.0165388E7</v>
       </c>
       <c r="AF62" s="14" t="inlineStr"/>
       <c r="AG62" s="14" t="inlineStr"/>
@@ -4211,7 +4211,7 @@
       <c r="O63" s="13" t="inlineStr"/>
       <c r="P63" s="13" t="inlineStr"/>
       <c r="Q63" s="14" t="n">
-        <v>4.8E7</v>
+        <v>4.8312E7</v>
       </c>
       <c r="R63" s="14" t="inlineStr"/>
       <c r="S63" s="14" t="n">
@@ -4221,23 +4221,23 @@
       <c r="U63" s="14" t="inlineStr"/>
       <c r="V63" s="14" t="inlineStr"/>
       <c r="W63" s="14" t="n">
-        <v>3.0561026E7</v>
+        <v>3.435979E7</v>
       </c>
       <c r="X63" s="14" t="n">
         <v>3798764.0</v>
       </c>
       <c r="Y63" s="14" t="inlineStr"/>
       <c r="Z63" s="14" t="n">
-        <v>3.435979E7</v>
+        <v>3.8158554E7</v>
       </c>
       <c r="AA63" s="14" t="inlineStr"/>
       <c r="AB63" s="14" t="inlineStr"/>
       <c r="AC63" s="15" t="n">
-        <v>0.7158289583333334</v>
+        <v>0.7898359413810233</v>
       </c>
       <c r="AD63" s="15" t="inlineStr"/>
       <c r="AE63" s="14" t="n">
-        <v>1.364021E7</v>
+        <v>1.0153446E7</v>
       </c>
       <c r="AF63" s="14" t="inlineStr"/>
       <c r="AG63" s="14" t="inlineStr"/>
@@ -4268,7 +4268,7 @@
       <c r="O64" s="13" t="inlineStr"/>
       <c r="P64" s="13" t="inlineStr"/>
       <c r="Q64" s="14" t="n">
-        <v>4000000.0</v>
+        <v>3790000.0</v>
       </c>
       <c r="R64" s="14" t="inlineStr"/>
       <c r="S64" s="14" t="n">
@@ -4290,11 +4290,11 @@
       <c r="AA64" s="14" t="inlineStr"/>
       <c r="AB64" s="14" t="inlineStr"/>
       <c r="AC64" s="15" t="n">
-        <v>0.944526</v>
+        <v>0.9968612137203167</v>
       </c>
       <c r="AD64" s="15" t="inlineStr"/>
       <c r="AE64" s="14" t="n">
-        <v>221896.0</v>
+        <v>11896.0</v>
       </c>
       <c r="AF64" s="14" t="inlineStr"/>
       <c r="AG64" s="14" t="inlineStr"/>
@@ -4325,7 +4325,7 @@
       <c r="O65" s="13" t="inlineStr"/>
       <c r="P65" s="13" t="inlineStr"/>
       <c r="Q65" s="14" t="n">
-        <v>4000000.0</v>
+        <v>3898000.0</v>
       </c>
       <c r="R65" s="14" t="inlineStr"/>
       <c r="S65" s="14" t="n">
@@ -4347,11 +4347,11 @@
       <c r="AA65" s="14" t="inlineStr"/>
       <c r="AB65" s="14" t="inlineStr"/>
       <c r="AC65" s="15" t="n">
-        <v>0.9744885</v>
+        <v>0.9999881990764494</v>
       </c>
       <c r="AD65" s="15" t="inlineStr"/>
       <c r="AE65" s="14" t="n">
-        <v>102046.0</v>
+        <v>46.0</v>
       </c>
       <c r="AF65" s="14" t="inlineStr"/>
       <c r="AG65" s="14" t="inlineStr"/>
@@ -4398,23 +4398,23 @@
       <c r="U66" s="14" t="inlineStr"/>
       <c r="V66" s="14" t="inlineStr"/>
       <c r="W66" s="14" t="n">
-        <v>1.8E7</v>
+        <v>1.98E7</v>
       </c>
       <c r="X66" s="14" t="n">
         <v>1800000.0</v>
       </c>
       <c r="Y66" s="14" t="inlineStr"/>
       <c r="Z66" s="14" t="n">
-        <v>1.98E7</v>
+        <v>2.16E7</v>
       </c>
       <c r="AA66" s="14" t="inlineStr"/>
       <c r="AB66" s="14" t="inlineStr"/>
       <c r="AC66" s="15" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AD66" s="15" t="inlineStr"/>
       <c r="AE66" s="14" t="n">
-        <v>5400000.0</v>
+        <v>3600000.0</v>
       </c>
       <c r="AF66" s="14" t="inlineStr"/>
       <c r="AG66" s="14" t="inlineStr"/>
@@ -4455,23 +4455,23 @@
       <c r="U67" s="14" t="inlineStr"/>
       <c r="V67" s="14" t="inlineStr"/>
       <c r="W67" s="14" t="n">
-        <v>1.44E7</v>
+        <v>1.62E7</v>
       </c>
       <c r="X67" s="14" t="n">
         <v>1800000.0</v>
       </c>
       <c r="Y67" s="14" t="inlineStr"/>
       <c r="Z67" s="14" t="n">
-        <v>1.62E7</v>
+        <v>1.8E7</v>
       </c>
       <c r="AA67" s="14" t="inlineStr"/>
       <c r="AB67" s="14" t="inlineStr"/>
       <c r="AC67" s="15" t="n">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AD67" s="15" t="inlineStr"/>
       <c r="AE67" s="14" t="n">
-        <v>5400000.0</v>
+        <v>3600000.0</v>
       </c>
       <c r="AF67" s="14" t="inlineStr"/>
       <c r="AG67" s="14" t="inlineStr"/>
@@ -4632,23 +4632,23 @@
       <c r="U70" s="14" t="inlineStr"/>
       <c r="V70" s="14" t="inlineStr"/>
       <c r="W70" s="14" t="n">
-        <v>1.1796E8</v>
+        <v>1.28894E8</v>
       </c>
       <c r="X70" s="14" t="n">
-        <v>1.0934E7</v>
+        <v>1.0394E7</v>
       </c>
       <c r="Y70" s="14" t="inlineStr"/>
       <c r="Z70" s="14" t="n">
-        <v>1.28894E8</v>
+        <v>1.39288E8</v>
       </c>
       <c r="AA70" s="14" t="inlineStr"/>
       <c r="AB70" s="14" t="inlineStr"/>
       <c r="AC70" s="15" t="n">
-        <v>0.8888383190588495</v>
+        <v>0.9605141572537824</v>
       </c>
       <c r="AD70" s="15" t="inlineStr"/>
       <c r="AE70" s="14" t="n">
-        <v>1.612E7</v>
+        <v>5726000.0</v>
       </c>
       <c r="AF70" s="14" t="inlineStr"/>
       <c r="AG70" s="14" t="inlineStr"/>
@@ -4679,7 +4679,7 @@
       <c r="O71" s="13" t="inlineStr"/>
       <c r="P71" s="13" t="inlineStr"/>
       <c r="Q71" s="14" t="n">
-        <v>1.2E8</v>
+        <v>1.20984E8</v>
       </c>
       <c r="R71" s="14" t="inlineStr"/>
       <c r="S71" s="14" t="n">
@@ -4689,23 +4689,23 @@
       <c r="U71" s="14" t="inlineStr"/>
       <c r="V71" s="14" t="inlineStr"/>
       <c r="W71" s="14" t="n">
-        <v>9.3932E7</v>
+        <v>1.04866E8</v>
       </c>
       <c r="X71" s="14" t="n">
-        <v>1.0934E7</v>
+        <v>1.0394E7</v>
       </c>
       <c r="Y71" s="14" t="inlineStr"/>
       <c r="Z71" s="14" t="n">
-        <v>1.04866E8</v>
+        <v>1.1526E8</v>
       </c>
       <c r="AA71" s="14" t="inlineStr"/>
       <c r="AB71" s="14" t="inlineStr"/>
       <c r="AC71" s="15" t="n">
-        <v>0.8738833333333333</v>
+        <v>0.9526879587383456</v>
       </c>
       <c r="AD71" s="15" t="inlineStr"/>
       <c r="AE71" s="14" t="n">
-        <v>1.5134E7</v>
+        <v>5724000.0</v>
       </c>
       <c r="AF71" s="14" t="inlineStr"/>
       <c r="AG71" s="14" t="inlineStr"/>
@@ -4736,7 +4736,7 @@
       <c r="O72" s="13" t="inlineStr"/>
       <c r="P72" s="13" t="inlineStr"/>
       <c r="Q72" s="14" t="n">
-        <v>1.3E7</v>
+        <v>1.2016E7</v>
       </c>
       <c r="R72" s="14" t="inlineStr"/>
       <c r="S72" s="14" t="n">
@@ -4758,11 +4758,11 @@
       <c r="AA72" s="14" t="inlineStr"/>
       <c r="AB72" s="14" t="inlineStr"/>
       <c r="AC72" s="15" t="n">
-        <v>0.9241538461538461</v>
+        <v>0.9998335552596538</v>
       </c>
       <c r="AD72" s="15" t="inlineStr"/>
       <c r="AE72" s="14" t="n">
-        <v>986000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="AF72" s="14" t="inlineStr"/>
       <c r="AG72" s="14" t="inlineStr"/>
@@ -4866,23 +4866,23 @@
       <c r="U74" s="14" t="inlineStr"/>
       <c r="V74" s="14" t="inlineStr"/>
       <c r="W74" s="14" t="n">
-        <v>1.9384414E7</v>
+        <v>1.9581584E7</v>
       </c>
       <c r="X74" s="14" t="n">
         <v>197170.0</v>
       </c>
       <c r="Y74" s="14" t="inlineStr"/>
       <c r="Z74" s="14" t="n">
-        <v>1.9581584E7</v>
+        <v>1.9778754E7</v>
       </c>
       <c r="AA74" s="14" t="inlineStr"/>
       <c r="AB74" s="14" t="inlineStr"/>
       <c r="AC74" s="15" t="n">
-        <v>0.9889688888888889</v>
+        <v>0.9989269696969697</v>
       </c>
       <c r="AD74" s="15" t="inlineStr"/>
       <c r="AE74" s="14" t="n">
-        <v>218416.0</v>
+        <v>21246.0</v>
       </c>
       <c r="AF74" s="14" t="inlineStr"/>
       <c r="AG74" s="14" t="inlineStr"/>
@@ -4913,7 +4913,7 @@
       <c r="O75" s="13" t="inlineStr"/>
       <c r="P75" s="13" t="inlineStr"/>
       <c r="Q75" s="14" t="n">
-        <v>2400000.0</v>
+        <v>2256000.0</v>
       </c>
       <c r="R75" s="14" t="inlineStr"/>
       <c r="S75" s="14" t="n">
@@ -4923,23 +4923,23 @@
       <c r="U75" s="14" t="inlineStr"/>
       <c r="V75" s="14" t="inlineStr"/>
       <c r="W75" s="14" t="n">
-        <v>1853398.0</v>
+        <v>2050568.0</v>
       </c>
       <c r="X75" s="14" t="n">
         <v>197170.0</v>
       </c>
       <c r="Y75" s="14" t="inlineStr"/>
       <c r="Z75" s="14" t="n">
-        <v>2050568.0</v>
+        <v>2247738.0</v>
       </c>
       <c r="AA75" s="14" t="inlineStr"/>
       <c r="AB75" s="14" t="inlineStr"/>
       <c r="AC75" s="15" t="n">
-        <v>0.8544033333333333</v>
+        <v>0.9963377659574468</v>
       </c>
       <c r="AD75" s="15" t="inlineStr"/>
       <c r="AE75" s="14" t="n">
-        <v>349432.0</v>
+        <v>8262.0</v>
       </c>
       <c r="AF75" s="14" t="inlineStr"/>
       <c r="AG75" s="14" t="inlineStr"/>
@@ -4970,7 +4970,7 @@
       <c r="O76" s="13" t="inlineStr"/>
       <c r="P76" s="13" t="inlineStr"/>
       <c r="Q76" s="14" t="n">
-        <v>8700000.0</v>
+        <v>8844000.0</v>
       </c>
       <c r="R76" s="14" t="inlineStr"/>
       <c r="S76" s="14" t="n">
@@ -4992,11 +4992,11 @@
       <c r="AA76" s="14" t="inlineStr"/>
       <c r="AB76" s="14" t="inlineStr"/>
       <c r="AC76" s="15" t="n">
-        <v>1.0152233333333334</v>
+        <v>0.9986932383536861</v>
       </c>
       <c r="AD76" s="15" t="inlineStr"/>
       <c r="AE76" s="14" t="n">
-        <v>-132443.0</v>
+        <v>11557.0</v>
       </c>
       <c r="AF76" s="14" t="inlineStr"/>
       <c r="AG76" s="14" t="inlineStr"/>
@@ -5100,23 +5100,23 @@
       <c r="U78" s="14" t="inlineStr"/>
       <c r="V78" s="14" t="inlineStr"/>
       <c r="W78" s="14" t="n">
-        <v>8.72661E7</v>
+        <v>9.588408E7</v>
       </c>
       <c r="X78" s="14" t="n">
         <v>8617980.0</v>
       </c>
       <c r="Y78" s="14" t="inlineStr"/>
       <c r="Z78" s="14" t="n">
-        <v>9.588408E7</v>
+        <v>1.0450206E8</v>
       </c>
       <c r="AA78" s="14" t="inlineStr"/>
       <c r="AB78" s="14" t="inlineStr"/>
       <c r="AC78" s="15" t="n">
-        <v>0.7609847619047619</v>
+        <v>0.8293814285714286</v>
       </c>
       <c r="AD78" s="15" t="inlineStr"/>
       <c r="AE78" s="14" t="n">
-        <v>3.011592E7</v>
+        <v>2.149794E7</v>
       </c>
       <c r="AF78" s="14" t="inlineStr"/>
       <c r="AG78" s="14" t="inlineStr"/>
@@ -5147,7 +5147,7 @@
       <c r="O79" s="13" t="inlineStr"/>
       <c r="P79" s="13" t="inlineStr"/>
       <c r="Q79" s="14" t="n">
-        <v>1.08E8</v>
+        <v>1.08468E8</v>
       </c>
       <c r="R79" s="14" t="inlineStr"/>
       <c r="S79" s="14" t="n">
@@ -5157,23 +5157,23 @@
       <c r="U79" s="14" t="inlineStr"/>
       <c r="V79" s="14" t="inlineStr"/>
       <c r="W79" s="14" t="n">
-        <v>6.974046E7</v>
+        <v>7.835844E7</v>
       </c>
       <c r="X79" s="14" t="n">
         <v>8617980.0</v>
       </c>
       <c r="Y79" s="14" t="inlineStr"/>
       <c r="Z79" s="14" t="n">
-        <v>7.835844E7</v>
+        <v>8.697642E7</v>
       </c>
       <c r="AA79" s="14" t="inlineStr"/>
       <c r="AB79" s="14" t="inlineStr"/>
       <c r="AC79" s="15" t="n">
-        <v>0.7255411111111111</v>
+        <v>0.8018624847881403</v>
       </c>
       <c r="AD79" s="15" t="inlineStr"/>
       <c r="AE79" s="14" t="n">
-        <v>2.964156E7</v>
+        <v>2.149158E7</v>
       </c>
       <c r="AF79" s="14" t="inlineStr"/>
       <c r="AG79" s="14" t="inlineStr"/>
@@ -5204,7 +5204,7 @@
       <c r="O80" s="13" t="inlineStr"/>
       <c r="P80" s="13" t="inlineStr"/>
       <c r="Q80" s="14" t="n">
-        <v>9000000.0</v>
+        <v>8622000.0</v>
       </c>
       <c r="R80" s="14" t="inlineStr"/>
       <c r="S80" s="14" t="n">
@@ -5226,11 +5226,11 @@
       <c r="AA80" s="14" t="inlineStr"/>
       <c r="AB80" s="14" t="inlineStr"/>
       <c r="AC80" s="15" t="n">
-        <v>0.9575533333333334</v>
+        <v>0.9995337508698677</v>
       </c>
       <c r="AD80" s="15" t="inlineStr"/>
       <c r="AE80" s="14" t="n">
-        <v>382020.0</v>
+        <v>4020.0</v>
       </c>
       <c r="AF80" s="14" t="inlineStr"/>
       <c r="AG80" s="14" t="inlineStr"/>
@@ -5261,7 +5261,7 @@
       <c r="O81" s="13" t="inlineStr"/>
       <c r="P81" s="13" t="inlineStr"/>
       <c r="Q81" s="14" t="n">
-        <v>9000000.0</v>
+        <v>8910000.0</v>
       </c>
       <c r="R81" s="14" t="inlineStr"/>
       <c r="S81" s="14" t="n">
@@ -5283,11 +5283,11 @@
       <c r="AA81" s="14" t="inlineStr"/>
       <c r="AB81" s="14" t="inlineStr"/>
       <c r="AC81" s="15" t="n">
-        <v>0.98974</v>
+        <v>0.9997373737373737</v>
       </c>
       <c r="AD81" s="15" t="inlineStr"/>
       <c r="AE81" s="14" t="n">
-        <v>92340.0</v>
+        <v>2340.0</v>
       </c>
       <c r="AF81" s="14" t="inlineStr"/>
       <c r="AG81" s="14" t="inlineStr"/>
@@ -5334,23 +5334,23 @@
       <c r="U82" s="14" t="inlineStr"/>
       <c r="V82" s="14" t="inlineStr"/>
       <c r="W82" s="14" t="n">
-        <v>1.54008E8</v>
+        <v>1.86773E8</v>
       </c>
       <c r="X82" s="14" t="n">
-        <v>3.2765E7</v>
+        <v>2.8708E7</v>
       </c>
       <c r="Y82" s="14" t="inlineStr"/>
       <c r="Z82" s="14" t="n">
-        <v>1.86773E8</v>
+        <v>2.15481E8</v>
       </c>
       <c r="AA82" s="14" t="inlineStr"/>
       <c r="AB82" s="14" t="inlineStr"/>
       <c r="AC82" s="15" t="n">
-        <v>0.5959268193072466</v>
+        <v>0.6875239298568038</v>
       </c>
       <c r="AD82" s="15" t="inlineStr"/>
       <c r="AE82" s="14" t="n">
-        <v>1.26643E8</v>
+        <v>9.7935E7</v>
       </c>
       <c r="AF82" s="14" t="inlineStr"/>
       <c r="AG82" s="14" t="inlineStr"/>
@@ -5391,23 +5391,23 @@
       <c r="U83" s="14" t="inlineStr"/>
       <c r="V83" s="14" t="inlineStr"/>
       <c r="W83" s="14" t="n">
-        <v>9450000.0</v>
+        <v>1.106E7</v>
       </c>
       <c r="X83" s="14" t="n">
-        <v>1610000.0</v>
+        <v>1400000.0</v>
       </c>
       <c r="Y83" s="14" t="inlineStr"/>
       <c r="Z83" s="14" t="n">
-        <v>1.106E7</v>
+        <v>1.246E7</v>
       </c>
       <c r="AA83" s="14" t="inlineStr"/>
       <c r="AB83" s="14" t="inlineStr"/>
       <c r="AC83" s="15" t="n">
-        <v>0.36574074074074076</v>
+        <v>0.41203703703703703</v>
       </c>
       <c r="AD83" s="15" t="inlineStr"/>
       <c r="AE83" s="14" t="n">
-        <v>1.918E7</v>
+        <v>1.778E7</v>
       </c>
       <c r="AF83" s="14" t="inlineStr"/>
       <c r="AG83" s="14" t="inlineStr"/>
@@ -5448,23 +5448,23 @@
       <c r="U84" s="14" t="inlineStr"/>
       <c r="V84" s="14" t="inlineStr"/>
       <c r="W84" s="14" t="n">
-        <v>1.25985E8</v>
+        <v>1.52958E8</v>
       </c>
       <c r="X84" s="14" t="n">
-        <v>2.6973E7</v>
+        <v>2.3495E7</v>
       </c>
       <c r="Y84" s="14" t="inlineStr"/>
       <c r="Z84" s="14" t="n">
-        <v>1.52958E8</v>
+        <v>1.76453E8</v>
       </c>
       <c r="AA84" s="14" t="inlineStr"/>
       <c r="AB84" s="14" t="inlineStr"/>
       <c r="AC84" s="15" t="n">
-        <v>0.6173835125448028</v>
+        <v>0.7122162485065711</v>
       </c>
       <c r="AD84" s="15" t="inlineStr"/>
       <c r="AE84" s="14" t="n">
-        <v>9.4794E7</v>
+        <v>7.1299E7</v>
       </c>
       <c r="AF84" s="14" t="inlineStr"/>
       <c r="AG84" s="14" t="inlineStr"/>
@@ -5505,23 +5505,23 @@
       <c r="U85" s="14" t="inlineStr"/>
       <c r="V85" s="14" t="inlineStr"/>
       <c r="W85" s="14" t="n">
-        <v>1.8573E7</v>
+        <v>2.2755E7</v>
       </c>
       <c r="X85" s="14" t="n">
-        <v>4182000.0</v>
+        <v>3813000.0</v>
       </c>
       <c r="Y85" s="14" t="inlineStr"/>
       <c r="Z85" s="14" t="n">
-        <v>2.2755E7</v>
+        <v>2.6568E7</v>
       </c>
       <c r="AA85" s="14" t="inlineStr"/>
       <c r="AB85" s="14" t="inlineStr"/>
       <c r="AC85" s="15" t="n">
-        <v>0.6423611111111112</v>
+        <v>0.75</v>
       </c>
       <c r="AD85" s="15" t="inlineStr"/>
       <c r="AE85" s="14" t="n">
-        <v>1.2669E7</v>
+        <v>8856000.0</v>
       </c>
       <c r="AF85" s="14" t="inlineStr"/>
       <c r="AG85" s="14" t="inlineStr"/>
@@ -5568,23 +5568,23 @@
       <c r="U86" s="14" t="inlineStr"/>
       <c r="V86" s="14" t="inlineStr"/>
       <c r="W86" s="14" t="n">
-        <v>4.044E7</v>
+        <v>4.4695E7</v>
       </c>
       <c r="X86" s="14" t="n">
-        <v>4255000.0</v>
+        <v>4440000.0</v>
       </c>
       <c r="Y86" s="14" t="inlineStr"/>
       <c r="Z86" s="14" t="n">
-        <v>4.4695E7</v>
+        <v>4.9135E7</v>
       </c>
       <c r="AA86" s="14" t="inlineStr"/>
       <c r="AB86" s="14" t="inlineStr"/>
       <c r="AC86" s="15" t="n">
-        <v>0.7094444444444444</v>
+        <v>0.7799206349206349</v>
       </c>
       <c r="AD86" s="15" t="inlineStr"/>
       <c r="AE86" s="14" t="n">
-        <v>1.8305E7</v>
+        <v>1.3865E7</v>
       </c>
       <c r="AF86" s="14" t="inlineStr"/>
       <c r="AG86" s="14" t="inlineStr"/>
@@ -5615,7 +5615,7 @@
       <c r="O87" s="13" t="inlineStr"/>
       <c r="P87" s="13" t="inlineStr"/>
       <c r="Q87" s="14" t="n">
-        <v>5.4E7</v>
+        <v>5.502E7</v>
       </c>
       <c r="R87" s="14" t="inlineStr"/>
       <c r="S87" s="14" t="n">
@@ -5625,23 +5625,23 @@
       <c r="U87" s="14" t="inlineStr"/>
       <c r="V87" s="14" t="inlineStr"/>
       <c r="W87" s="14" t="n">
-        <v>3.251E7</v>
+        <v>3.6765E7</v>
       </c>
       <c r="X87" s="14" t="n">
-        <v>4255000.0</v>
+        <v>4440000.0</v>
       </c>
       <c r="Y87" s="14" t="inlineStr"/>
       <c r="Z87" s="14" t="n">
-        <v>3.6765E7</v>
+        <v>4.1205E7</v>
       </c>
       <c r="AA87" s="14" t="inlineStr"/>
       <c r="AB87" s="14" t="inlineStr"/>
       <c r="AC87" s="15" t="n">
-        <v>0.6808333333333333</v>
+        <v>0.7489094874591058</v>
       </c>
       <c r="AD87" s="15" t="inlineStr"/>
       <c r="AE87" s="14" t="n">
-        <v>1.7235E7</v>
+        <v>1.3815E7</v>
       </c>
       <c r="AF87" s="14" t="inlineStr"/>
       <c r="AG87" s="14" t="inlineStr"/>
@@ -5672,7 +5672,7 @@
       <c r="O88" s="13" t="inlineStr"/>
       <c r="P88" s="13" t="inlineStr"/>
       <c r="Q88" s="14" t="n">
-        <v>4500000.0</v>
+        <v>3900000.0</v>
       </c>
       <c r="R88" s="14" t="inlineStr"/>
       <c r="S88" s="14" t="n">
@@ -5694,11 +5694,11 @@
       <c r="AA88" s="14" t="inlineStr"/>
       <c r="AB88" s="14" t="inlineStr"/>
       <c r="AC88" s="15" t="n">
-        <v>0.8611111111111112</v>
+        <v>0.9935897435897436</v>
       </c>
       <c r="AD88" s="15" t="inlineStr"/>
       <c r="AE88" s="14" t="n">
-        <v>625000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="AF88" s="14" t="inlineStr"/>
       <c r="AG88" s="14" t="inlineStr"/>
@@ -5772,7 +5772,7 @@
       <c r="O90" s="13" t="inlineStr"/>
       <c r="P90" s="13" t="inlineStr"/>
       <c r="Q90" s="14" t="n">
-        <v>4500000.0</v>
+        <v>4080000.0</v>
       </c>
       <c r="R90" s="14" t="inlineStr"/>
       <c r="S90" s="14" t="n">
@@ -5794,11 +5794,11 @@
       <c r="AA90" s="14" t="inlineStr"/>
       <c r="AB90" s="14" t="inlineStr"/>
       <c r="AC90" s="15" t="n">
-        <v>0.9011111111111111</v>
+        <v>0.9938725490196079</v>
       </c>
       <c r="AD90" s="15" t="inlineStr"/>
       <c r="AE90" s="14" t="n">
-        <v>445000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="AF90" s="14" t="inlineStr"/>
       <c r="AG90" s="14" t="inlineStr"/>
@@ -5845,23 +5845,23 @@
       <c r="U91" s="14" t="inlineStr"/>
       <c r="V91" s="14" t="inlineStr"/>
       <c r="W91" s="14" t="n">
-        <v>1.936062937E9</v>
+        <v>2.118649941E9</v>
       </c>
       <c r="X91" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y91" s="14" t="inlineStr"/>
       <c r="Z91" s="14" t="n">
-        <v>1.936062937E9</v>
+        <v>2.118649941E9</v>
       </c>
       <c r="AA91" s="14" t="inlineStr"/>
       <c r="AB91" s="14" t="inlineStr"/>
       <c r="AC91" s="15" t="n">
-        <v>0.7240325119670905</v>
+        <v>0.7923148620044876</v>
       </c>
       <c r="AD91" s="15" t="inlineStr"/>
       <c r="AE91" s="14" t="n">
-        <v>7.37937063E8</v>
+        <v>5.55350059E8</v>
       </c>
       <c r="AF91" s="14" t="inlineStr"/>
       <c r="AG91" s="14" t="inlineStr"/>
@@ -5892,7 +5892,7 @@
       <c r="O92" s="13" t="inlineStr"/>
       <c r="P92" s="13" t="inlineStr"/>
       <c r="Q92" s="14" t="n">
-        <v>2.2296E9</v>
+        <v>2.231376E9</v>
       </c>
       <c r="R92" s="14" t="inlineStr"/>
       <c r="S92" s="14" t="n">
@@ -5902,23 +5902,23 @@
       <c r="U92" s="14" t="inlineStr"/>
       <c r="V92" s="14" t="inlineStr"/>
       <c r="W92" s="14" t="n">
-        <v>1.493448145E9</v>
+        <v>1.676035149E9</v>
       </c>
       <c r="X92" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y92" s="14" t="inlineStr"/>
       <c r="Z92" s="14" t="n">
-        <v>1.493448145E9</v>
+        <v>1.676035149E9</v>
       </c>
       <c r="AA92" s="14" t="inlineStr"/>
       <c r="AB92" s="14" t="inlineStr"/>
       <c r="AC92" s="15" t="n">
-        <v>0.6698278368317186</v>
+        <v>0.75112179614731</v>
       </c>
       <c r="AD92" s="15" t="inlineStr"/>
       <c r="AE92" s="14" t="n">
-        <v>7.36151855E8</v>
+        <v>5.55340851E8</v>
       </c>
       <c r="AF92" s="14" t="inlineStr"/>
       <c r="AG92" s="14" t="inlineStr"/>
@@ -5949,7 +5949,7 @@
       <c r="O93" s="13" t="inlineStr"/>
       <c r="P93" s="13" t="inlineStr"/>
       <c r="Q93" s="14" t="n">
-        <v>2.2227E8</v>
+        <v>2.20494E8</v>
       </c>
       <c r="R93" s="14" t="inlineStr"/>
       <c r="S93" s="14" t="n">
@@ -5971,11 +5971,11 @@
       <c r="AA93" s="14" t="inlineStr"/>
       <c r="AB93" s="14" t="inlineStr"/>
       <c r="AC93" s="15" t="n">
-        <v>0.9919732217573222</v>
+        <v>0.9999632098832621</v>
       </c>
       <c r="AD93" s="15" t="inlineStr"/>
       <c r="AE93" s="14" t="n">
-        <v>1784112.0</v>
+        <v>8112.0</v>
       </c>
       <c r="AF93" s="14" t="inlineStr"/>
       <c r="AG93" s="14" t="inlineStr"/>
@@ -7943,23 +7943,23 @@
       <c r="U127" s="14" t="inlineStr"/>
       <c r="V127" s="14" t="inlineStr"/>
       <c r="W127" s="14" t="n">
-        <v>3.5544999187E10</v>
+        <v>3.9416887025E10</v>
       </c>
       <c r="X127" s="14" t="n">
-        <v>3.871887838E9</v>
+        <v>3.768823923E9</v>
       </c>
       <c r="Y127" s="14" t="inlineStr"/>
       <c r="Z127" s="14" t="n">
-        <v>3.9416887025E10</v>
+        <v>4.3185710948E10</v>
       </c>
       <c r="AA127" s="14" t="inlineStr"/>
       <c r="AB127" s="14" t="inlineStr"/>
       <c r="AC127" s="15" t="n">
-        <v>0.7452760763519444</v>
+        <v>0.8165352375336303</v>
       </c>
       <c r="AD127" s="15" t="inlineStr"/>
       <c r="AE127" s="14" t="n">
-        <v>1.3472086975E10</v>
+        <v>9.703263052E9</v>
       </c>
       <c r="AF127" s="14" t="inlineStr"/>
       <c r="AG127" s="14" t="inlineStr"/>
@@ -7996,7 +7996,7 @@
       <c r="O128" s="13" t="inlineStr"/>
       <c r="P128" s="13" t="inlineStr"/>
       <c r="Q128" s="14" t="n">
-        <v>1.3150715E10</v>
+        <v>1.3150714E10</v>
       </c>
       <c r="R128" s="14" t="inlineStr"/>
       <c r="S128" s="14" t="n">
@@ -8006,23 +8006,23 @@
       <c r="U128" s="14" t="inlineStr"/>
       <c r="V128" s="14" t="inlineStr"/>
       <c r="W128" s="14" t="n">
-        <v>1.23832303E10</v>
+        <v>1.35753119E10</v>
       </c>
       <c r="X128" s="14" t="n">
-        <v>1.1920816E9</v>
+        <v>1.1818642E9</v>
       </c>
       <c r="Y128" s="14" t="inlineStr"/>
       <c r="Z128" s="14" t="n">
-        <v>1.35753119E10</v>
+        <v>1.47571761E10</v>
       </c>
       <c r="AA128" s="14" t="inlineStr"/>
       <c r="AB128" s="14" t="inlineStr"/>
       <c r="AC128" s="15" t="n">
-        <v>1.0322869821146607</v>
+        <v>1.1221577855012284</v>
       </c>
       <c r="AD128" s="15" t="inlineStr"/>
       <c r="AE128" s="14" t="n">
-        <v>-4.245969E8</v>
+        <v>-1.6064621E9</v>
       </c>
       <c r="AF128" s="14" t="inlineStr"/>
       <c r="AG128" s="14" t="inlineStr"/>
@@ -8053,7 +8053,7 @@
       <c r="O129" s="13" t="inlineStr"/>
       <c r="P129" s="13" t="inlineStr"/>
       <c r="Q129" s="14" t="n">
-        <v>1.0597296E10</v>
+        <v>1.065996E10</v>
       </c>
       <c r="R129" s="14" t="inlineStr"/>
       <c r="S129" s="14" t="n">
@@ -8063,23 +8063,23 @@
       <c r="U129" s="14" t="inlineStr"/>
       <c r="V129" s="14" t="inlineStr"/>
       <c r="W129" s="14" t="n">
-        <v>9.8924769E9</v>
+        <v>1.10845585E10</v>
       </c>
       <c r="X129" s="14" t="n">
-        <v>1.1920816E9</v>
+        <v>1.1818642E9</v>
       </c>
       <c r="Y129" s="14" t="inlineStr"/>
       <c r="Z129" s="14" t="n">
-        <v>1.10845585E10</v>
+        <v>1.22664227E10</v>
       </c>
       <c r="AA129" s="14" t="inlineStr"/>
       <c r="AB129" s="14" t="inlineStr"/>
       <c r="AC129" s="15" t="n">
-        <v>1.0459798895869286</v>
+        <v>1.1507006311468335</v>
       </c>
       <c r="AD129" s="15" t="inlineStr"/>
       <c r="AE129" s="14" t="n">
-        <v>-4.872625E8</v>
+        <v>-1.6064627E9</v>
       </c>
       <c r="AF129" s="14" t="inlineStr"/>
       <c r="AG129" s="14" t="inlineStr"/>
@@ -8110,7 +8110,7 @@
       <c r="O130" s="13" t="inlineStr"/>
       <c r="P130" s="13" t="inlineStr"/>
       <c r="Q130" s="14" t="n">
-        <v>1.3E9</v>
+        <v>1.237335E9</v>
       </c>
       <c r="R130" s="14" t="inlineStr"/>
       <c r="S130" s="14" t="n">
@@ -8132,11 +8132,11 @@
       <c r="AA130" s="14" t="inlineStr"/>
       <c r="AB130" s="14" t="inlineStr"/>
       <c r="AC130" s="15" t="n">
-        <v>0.9517958461538462</v>
+        <v>0.9999996767245733</v>
       </c>
       <c r="AD130" s="15" t="inlineStr"/>
       <c r="AE130" s="14" t="n">
-        <v>6.26654E7</v>
+        <v>400.0</v>
       </c>
       <c r="AF130" s="14" t="inlineStr"/>
       <c r="AG130" s="14" t="inlineStr"/>
@@ -8230,7 +8230,7 @@
       <c r="O132" s="13" t="inlineStr"/>
       <c r="P132" s="13" t="inlineStr"/>
       <c r="Q132" s="14" t="n">
-        <v>238000.0</v>
+        <v>239000.0</v>
       </c>
       <c r="R132" s="14" t="inlineStr"/>
       <c r="S132" s="14" t="n">
@@ -8240,23 +8240,23 @@
       <c r="U132" s="14" t="inlineStr"/>
       <c r="V132" s="14" t="inlineStr"/>
       <c r="W132" s="14" t="n">
-        <v>168114.0</v>
+        <v>183849.0</v>
       </c>
       <c r="X132" s="14" t="n">
-        <v>15735.0</v>
+        <v>15535.0</v>
       </c>
       <c r="Y132" s="14" t="inlineStr"/>
       <c r="Z132" s="14" t="n">
-        <v>183849.0</v>
+        <v>199384.0</v>
       </c>
       <c r="AA132" s="14" t="inlineStr"/>
       <c r="AB132" s="14" t="inlineStr"/>
       <c r="AC132" s="15" t="n">
-        <v>0.7724747899159664</v>
+        <v>0.8342426778242678</v>
       </c>
       <c r="AD132" s="15" t="inlineStr"/>
       <c r="AE132" s="14" t="n">
-        <v>54151.0</v>
+        <v>39616.0</v>
       </c>
       <c r="AF132" s="14" t="inlineStr"/>
       <c r="AG132" s="14" t="inlineStr"/>
@@ -8297,23 +8297,23 @@
       <c r="U133" s="14" t="inlineStr"/>
       <c r="V133" s="14" t="inlineStr"/>
       <c r="W133" s="14" t="n">
-        <v>134340.0</v>
+        <v>150075.0</v>
       </c>
       <c r="X133" s="14" t="n">
-        <v>15735.0</v>
+        <v>15535.0</v>
       </c>
       <c r="Y133" s="14" t="inlineStr"/>
       <c r="Z133" s="14" t="n">
-        <v>150075.0</v>
+        <v>165610.0</v>
       </c>
       <c r="AA133" s="14" t="inlineStr"/>
       <c r="AB133" s="14" t="inlineStr"/>
       <c r="AC133" s="15" t="n">
-        <v>0.7356617647058824</v>
+        <v>0.811813725490196</v>
       </c>
       <c r="AD133" s="15" t="inlineStr"/>
       <c r="AE133" s="14" t="n">
-        <v>53925.0</v>
+        <v>38390.0</v>
       </c>
       <c r="AF133" s="14" t="inlineStr"/>
       <c r="AG133" s="14" t="inlineStr"/>
@@ -8344,7 +8344,7 @@
       <c r="O134" s="13" t="inlineStr"/>
       <c r="P134" s="13" t="inlineStr"/>
       <c r="Q134" s="14" t="n">
-        <v>17000.0</v>
+        <v>18000.0</v>
       </c>
       <c r="R134" s="14" t="inlineStr"/>
       <c r="S134" s="14" t="n">
@@ -8366,11 +8366,11 @@
       <c r="AA134" s="14" t="inlineStr"/>
       <c r="AB134" s="14" t="inlineStr"/>
       <c r="AC134" s="15" t="n">
-        <v>1.0038823529411764</v>
+        <v>0.9481111111111111</v>
       </c>
       <c r="AD134" s="15" t="inlineStr"/>
       <c r="AE134" s="14" t="n">
-        <v>-66.0</v>
+        <v>934.0</v>
       </c>
       <c r="AF134" s="14" t="inlineStr"/>
       <c r="AG134" s="14" t="inlineStr"/>
@@ -8474,23 +8474,23 @@
       <c r="U136" s="14" t="inlineStr"/>
       <c r="V136" s="14" t="inlineStr"/>
       <c r="W136" s="14" t="n">
-        <v>9.7329066E8</v>
+        <v>1.06752398E9</v>
       </c>
       <c r="X136" s="14" t="n">
-        <v>9.423332E7</v>
+        <v>9.321798E7</v>
       </c>
       <c r="Y136" s="14" t="inlineStr"/>
       <c r="Z136" s="14" t="n">
-        <v>1.06752398E9</v>
+        <v>1.16074196E9</v>
       </c>
       <c r="AA136" s="14" t="inlineStr"/>
       <c r="AB136" s="14" t="inlineStr"/>
       <c r="AC136" s="15" t="n">
-        <v>0.7783339870948927</v>
+        <v>0.8462994130728009</v>
       </c>
       <c r="AD136" s="15" t="inlineStr"/>
       <c r="AE136" s="14" t="n">
-        <v>3.0402602E8</v>
+        <v>2.1080804E8</v>
       </c>
       <c r="AF136" s="14" t="inlineStr"/>
       <c r="AG136" s="14" t="inlineStr"/>
@@ -8521,7 +8521,7 @@
       <c r="O137" s="13" t="inlineStr"/>
       <c r="P137" s="13" t="inlineStr"/>
       <c r="Q137" s="14" t="n">
-        <v>1.176E9</v>
+        <v>1.176564E9</v>
       </c>
       <c r="R137" s="14" t="inlineStr"/>
       <c r="S137" s="14" t="n">
@@ -8531,23 +8531,23 @@
       <c r="U137" s="14" t="inlineStr"/>
       <c r="V137" s="14" t="inlineStr"/>
       <c r="W137" s="14" t="n">
-        <v>7.783056E8</v>
+        <v>8.7253892E8</v>
       </c>
       <c r="X137" s="14" t="n">
-        <v>9.423332E7</v>
+        <v>9.321798E7</v>
       </c>
       <c r="Y137" s="14" t="inlineStr"/>
       <c r="Z137" s="14" t="n">
-        <v>8.7253892E8</v>
+        <v>9.657569E8</v>
       </c>
       <c r="AA137" s="14" t="inlineStr"/>
       <c r="AB137" s="14" t="inlineStr"/>
       <c r="AC137" s="15" t="n">
-        <v>0.7419548639455782</v>
+        <v>0.8208281912416154</v>
       </c>
       <c r="AD137" s="15" t="inlineStr"/>
       <c r="AE137" s="14" t="n">
-        <v>3.0346108E8</v>
+        <v>2.108071E8</v>
       </c>
       <c r="AF137" s="14" t="inlineStr"/>
       <c r="AG137" s="14" t="inlineStr"/>
@@ -8578,7 +8578,7 @@
       <c r="O138" s="13" t="inlineStr"/>
       <c r="P138" s="13" t="inlineStr"/>
       <c r="Q138" s="14" t="n">
-        <v>9.8E7</v>
+        <v>9.7436E7</v>
       </c>
       <c r="R138" s="14" t="inlineStr"/>
       <c r="S138" s="14" t="n">
@@ -8600,11 +8600,11 @@
       <c r="AA138" s="14" t="inlineStr"/>
       <c r="AB138" s="14" t="inlineStr"/>
       <c r="AC138" s="15" t="n">
-        <v>0.9942412244897959</v>
+        <v>0.9999963052670471</v>
       </c>
       <c r="AD138" s="15" t="inlineStr"/>
       <c r="AE138" s="14" t="n">
-        <v>564360.0</v>
+        <v>360.0</v>
       </c>
       <c r="AF138" s="14" t="inlineStr"/>
       <c r="AG138" s="14" t="inlineStr"/>
@@ -8708,23 +8708,23 @@
       <c r="U140" s="14" t="inlineStr"/>
       <c r="V140" s="14" t="inlineStr"/>
       <c r="W140" s="14" t="n">
-        <v>3.02306822E8</v>
+        <v>3.31934306E8</v>
       </c>
       <c r="X140" s="14" t="n">
-        <v>2.9627484E7</v>
+        <v>2.9743684E7</v>
       </c>
       <c r="Y140" s="14" t="inlineStr"/>
       <c r="Z140" s="14" t="n">
-        <v>3.31934306E8</v>
+        <v>3.6167799E8</v>
       </c>
       <c r="AA140" s="14" t="inlineStr"/>
       <c r="AB140" s="14" t="inlineStr"/>
       <c r="AC140" s="15" t="n">
-        <v>0.7661372026303095</v>
+        <v>0.8347885666013475</v>
       </c>
       <c r="AD140" s="15" t="inlineStr"/>
       <c r="AE140" s="14" t="n">
-        <v>1.01322694E8</v>
+        <v>7.157901E7</v>
       </c>
       <c r="AF140" s="14" t="inlineStr"/>
       <c r="AG140" s="14" t="inlineStr"/>
@@ -8755,7 +8755,7 @@
       <c r="O141" s="13" t="inlineStr"/>
       <c r="P141" s="13" t="inlineStr"/>
       <c r="Q141" s="14" t="n">
-        <v>3.72E8</v>
+        <v>3.72864E8</v>
       </c>
       <c r="R141" s="14" t="inlineStr"/>
       <c r="S141" s="14" t="n">
@@ -8765,23 +8765,23 @@
       <c r="U141" s="14" t="inlineStr"/>
       <c r="V141" s="14" t="inlineStr"/>
       <c r="W141" s="14" t="n">
-        <v>2.41915966E8</v>
+        <v>2.7154345E8</v>
       </c>
       <c r="X141" s="14" t="n">
-        <v>2.9627484E7</v>
+        <v>2.9743684E7</v>
       </c>
       <c r="Y141" s="14" t="inlineStr"/>
       <c r="Z141" s="14" t="n">
-        <v>2.7154345E8</v>
+        <v>3.01287134E8</v>
       </c>
       <c r="AA141" s="14" t="inlineStr"/>
       <c r="AB141" s="14" t="inlineStr"/>
       <c r="AC141" s="15" t="n">
-        <v>0.7299555107526882</v>
+        <v>0.8080349242619292</v>
       </c>
       <c r="AD141" s="15" t="inlineStr"/>
       <c r="AE141" s="14" t="n">
-        <v>1.0045655E8</v>
+        <v>7.1576866E7</v>
       </c>
       <c r="AF141" s="14" t="inlineStr"/>
       <c r="AG141" s="14" t="inlineStr"/>
@@ -8812,7 +8812,7 @@
       <c r="O142" s="13" t="inlineStr"/>
       <c r="P142" s="13" t="inlineStr"/>
       <c r="Q142" s="14" t="n">
-        <v>3.1E7</v>
+        <v>3.0136E7</v>
       </c>
       <c r="R142" s="14" t="inlineStr"/>
       <c r="S142" s="14" t="n">
@@ -8834,11 +8834,11 @@
       <c r="AA142" s="14" t="inlineStr"/>
       <c r="AB142" s="14" t="inlineStr"/>
       <c r="AC142" s="15" t="n">
-        <v>0.9720698064516129</v>
+        <v>0.999939076187948</v>
       </c>
       <c r="AD142" s="15" t="inlineStr"/>
       <c r="AE142" s="14" t="n">
-        <v>865836.0</v>
+        <v>1836.0</v>
       </c>
       <c r="AF142" s="14" t="inlineStr"/>
       <c r="AG142" s="14" t="inlineStr"/>
@@ -8942,23 +8942,23 @@
       <c r="U144" s="14" t="inlineStr"/>
       <c r="V144" s="14" t="inlineStr"/>
       <c r="W144" s="14" t="n">
-        <v>2.67431E9</v>
+        <v>2.93033E9</v>
       </c>
       <c r="X144" s="14" t="n">
-        <v>2.5602E8</v>
+        <v>2.5398E8</v>
       </c>
       <c r="Y144" s="14" t="inlineStr"/>
       <c r="Z144" s="14" t="n">
-        <v>2.93033E9</v>
+        <v>3.18431E9</v>
       </c>
       <c r="AA144" s="14" t="inlineStr"/>
       <c r="AB144" s="14" t="inlineStr"/>
       <c r="AC144" s="15" t="n">
-        <v>0.7611246753246753</v>
+        <v>0.8270935064935065</v>
       </c>
       <c r="AD144" s="15" t="inlineStr"/>
       <c r="AE144" s="14" t="n">
-        <v>9.1967E8</v>
+        <v>6.6569E8</v>
       </c>
       <c r="AF144" s="14" t="inlineStr"/>
       <c r="AG144" s="14" t="inlineStr"/>
@@ -9032,7 +9032,7 @@
       <c r="O146" s="13" t="inlineStr"/>
       <c r="P146" s="13" t="inlineStr"/>
       <c r="Q146" s="14" t="n">
-        <v>3.3E9</v>
+        <v>3.311736E9</v>
       </c>
       <c r="R146" s="14" t="inlineStr"/>
       <c r="S146" s="14" t="n">
@@ -9042,23 +9042,23 @@
       <c r="U146" s="14" t="inlineStr"/>
       <c r="V146" s="14" t="inlineStr"/>
       <c r="W146" s="14" t="n">
-        <v>2.13605E9</v>
+        <v>2.39207E9</v>
       </c>
       <c r="X146" s="14" t="n">
-        <v>2.5602E8</v>
+        <v>2.5398E8</v>
       </c>
       <c r="Y146" s="14" t="inlineStr"/>
       <c r="Z146" s="14" t="n">
-        <v>2.39207E9</v>
+        <v>2.64605E9</v>
       </c>
       <c r="AA146" s="14" t="inlineStr"/>
       <c r="AB146" s="14" t="inlineStr"/>
       <c r="AC146" s="15" t="n">
-        <v>0.7248696969696969</v>
+        <v>0.7989918278510123</v>
       </c>
       <c r="AD146" s="15" t="inlineStr"/>
       <c r="AE146" s="14" t="n">
-        <v>9.0793E8</v>
+        <v>6.65686E8</v>
       </c>
       <c r="AF146" s="14" t="inlineStr"/>
       <c r="AG146" s="14" t="inlineStr"/>
@@ -9089,7 +9089,7 @@
       <c r="O147" s="13" t="inlineStr"/>
       <c r="P147" s="13" t="inlineStr"/>
       <c r="Q147" s="14" t="n">
-        <v>2.75E8</v>
+        <v>2.66074E8</v>
       </c>
       <c r="R147" s="14" t="inlineStr"/>
       <c r="S147" s="14" t="n">
@@ -9111,11 +9111,11 @@
       <c r="AA147" s="14" t="inlineStr"/>
       <c r="AB147" s="14" t="inlineStr"/>
       <c r="AC147" s="15" t="n">
-        <v>0.9675272727272727</v>
+        <v>0.9999849665882423</v>
       </c>
       <c r="AD147" s="15" t="inlineStr"/>
       <c r="AE147" s="14" t="n">
-        <v>8930000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="AF147" s="14" t="inlineStr"/>
       <c r="AG147" s="14" t="inlineStr"/>
@@ -9146,7 +9146,7 @@
       <c r="O148" s="13" t="inlineStr"/>
       <c r="P148" s="13" t="inlineStr"/>
       <c r="Q148" s="14" t="n">
-        <v>2.75E8</v>
+        <v>2.7219E8</v>
       </c>
       <c r="R148" s="14" t="inlineStr"/>
       <c r="S148" s="14" t="n">
@@ -9168,11 +9168,11 @@
       <c r="AA148" s="14" t="inlineStr"/>
       <c r="AB148" s="14" t="inlineStr"/>
       <c r="AC148" s="15" t="n">
-        <v>0.9897818181818182</v>
+        <v>1.0</v>
       </c>
       <c r="AD148" s="15" t="inlineStr"/>
       <c r="AE148" s="14" t="n">
-        <v>2810000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF148" s="14" t="inlineStr"/>
       <c r="AG148" s="14" t="inlineStr"/>
@@ -9219,23 +9219,23 @@
       <c r="U149" s="14" t="inlineStr"/>
       <c r="V149" s="14" t="inlineStr"/>
       <c r="W149" s="14" t="n">
-        <v>2.17635496E8</v>
+        <v>2.20978694E8</v>
       </c>
       <c r="X149" s="14" t="n">
-        <v>3343198.0</v>
+        <v>3236926.0</v>
       </c>
       <c r="Y149" s="14" t="inlineStr"/>
       <c r="Z149" s="14" t="n">
-        <v>2.20978694E8</v>
+        <v>2.2421562E8</v>
       </c>
       <c r="AA149" s="14" t="inlineStr"/>
       <c r="AB149" s="14" t="inlineStr"/>
       <c r="AC149" s="15" t="n">
-        <v>0.8992743824522851</v>
+        <v>0.9124470760590893</v>
       </c>
       <c r="AD149" s="15" t="inlineStr"/>
       <c r="AE149" s="14" t="n">
-        <v>2.4751306E7</v>
+        <v>2.151438E7</v>
       </c>
       <c r="AF149" s="14" t="inlineStr"/>
       <c r="AG149" s="14" t="inlineStr"/>
@@ -9266,7 +9266,7 @@
       <c r="O150" s="13" t="inlineStr"/>
       <c r="P150" s="13" t="inlineStr"/>
       <c r="Q150" s="14" t="n">
-        <v>6.0E7</v>
+        <v>6.0264E7</v>
       </c>
       <c r="R150" s="14" t="inlineStr"/>
       <c r="S150" s="14" t="n">
@@ -9276,23 +9276,23 @@
       <c r="U150" s="14" t="inlineStr"/>
       <c r="V150" s="14" t="inlineStr"/>
       <c r="W150" s="14" t="n">
-        <v>3.2179365E7</v>
+        <v>3.5522563E7</v>
       </c>
       <c r="X150" s="14" t="n">
-        <v>3343198.0</v>
+        <v>3236926.0</v>
       </c>
       <c r="Y150" s="14" t="inlineStr"/>
       <c r="Z150" s="14" t="n">
-        <v>3.5522563E7</v>
+        <v>3.8759489E7</v>
       </c>
       <c r="AA150" s="14" t="inlineStr"/>
       <c r="AB150" s="14" t="inlineStr"/>
       <c r="AC150" s="15" t="n">
-        <v>0.5920427166666666</v>
+        <v>0.6431615724147086</v>
       </c>
       <c r="AD150" s="15" t="inlineStr"/>
       <c r="AE150" s="14" t="n">
-        <v>2.4477437E7</v>
+        <v>2.1504511E7</v>
       </c>
       <c r="AF150" s="14" t="inlineStr"/>
       <c r="AG150" s="14" t="inlineStr"/>
@@ -9323,7 +9323,7 @@
       <c r="O151" s="13" t="inlineStr"/>
       <c r="P151" s="13" t="inlineStr"/>
       <c r="Q151" s="14" t="n">
-        <v>9.3E7</v>
+        <v>9.2736E7</v>
       </c>
       <c r="R151" s="14" t="inlineStr"/>
       <c r="S151" s="14" t="n">
@@ -9345,11 +9345,11 @@
       <c r="AA151" s="14" t="inlineStr"/>
       <c r="AB151" s="14" t="inlineStr"/>
       <c r="AC151" s="15" t="n">
-        <v>0.9970770752688172</v>
+        <v>0.9999155452035887</v>
       </c>
       <c r="AD151" s="15" t="inlineStr"/>
       <c r="AE151" s="14" t="n">
-        <v>271832.0</v>
+        <v>7832.0</v>
       </c>
       <c r="AF151" s="14" t="inlineStr"/>
       <c r="AG151" s="14" t="inlineStr"/>
@@ -9453,23 +9453,23 @@
       <c r="U153" s="14" t="inlineStr"/>
       <c r="V153" s="14" t="inlineStr"/>
       <c r="W153" s="14" t="n">
-        <v>6.7995138E8</v>
+        <v>7.462881E8</v>
       </c>
       <c r="X153" s="14" t="n">
-        <v>6.633672E7</v>
+        <v>6.611946E7</v>
       </c>
       <c r="Y153" s="14" t="inlineStr"/>
       <c r="Z153" s="14" t="n">
-        <v>7.462881E8</v>
+        <v>8.1240756E8</v>
       </c>
       <c r="AA153" s="14" t="inlineStr"/>
       <c r="AB153" s="14" t="inlineStr"/>
       <c r="AC153" s="15" t="n">
-        <v>0.7615184693877551</v>
+        <v>0.828987306122449</v>
       </c>
       <c r="AD153" s="15" t="inlineStr"/>
       <c r="AE153" s="14" t="n">
-        <v>2.337119E8</v>
+        <v>1.6759244E8</v>
       </c>
       <c r="AF153" s="14" t="inlineStr"/>
       <c r="AG153" s="14" t="inlineStr"/>
@@ -9500,7 +9500,7 @@
       <c r="O154" s="13" t="inlineStr"/>
       <c r="P154" s="13" t="inlineStr"/>
       <c r="Q154" s="14" t="n">
-        <v>8.4E8</v>
+        <v>8.43264E8</v>
       </c>
       <c r="R154" s="14" t="inlineStr"/>
       <c r="S154" s="14" t="n">
@@ -9510,23 +9510,23 @@
       <c r="U154" s="14" t="inlineStr"/>
       <c r="V154" s="14" t="inlineStr"/>
       <c r="W154" s="14" t="n">
-        <v>5.4322242E8</v>
+        <v>6.0955914E8</v>
       </c>
       <c r="X154" s="14" t="n">
-        <v>6.633672E7</v>
+        <v>6.611946E7</v>
       </c>
       <c r="Y154" s="14" t="inlineStr"/>
       <c r="Z154" s="14" t="n">
-        <v>6.0955914E8</v>
+        <v>6.756786E8</v>
       </c>
       <c r="AA154" s="14" t="inlineStr"/>
       <c r="AB154" s="14" t="inlineStr"/>
       <c r="AC154" s="15" t="n">
-        <v>0.7256656428571429</v>
+        <v>0.8012657957650273</v>
       </c>
       <c r="AD154" s="15" t="inlineStr"/>
       <c r="AE154" s="14" t="n">
-        <v>2.3044086E8</v>
+        <v>1.675854E8</v>
       </c>
       <c r="AF154" s="14" t="inlineStr"/>
       <c r="AG154" s="14" t="inlineStr"/>
@@ -9557,7 +9557,7 @@
       <c r="O155" s="13" t="inlineStr"/>
       <c r="P155" s="13" t="inlineStr"/>
       <c r="Q155" s="14" t="n">
-        <v>7.0E7</v>
+        <v>6.8005E7</v>
       </c>
       <c r="R155" s="14" t="inlineStr"/>
       <c r="S155" s="14" t="n">
@@ -9579,11 +9579,11 @@
       <c r="AA155" s="14" t="inlineStr"/>
       <c r="AB155" s="14" t="inlineStr"/>
       <c r="AC155" s="15" t="n">
-        <v>0.9714625714285714</v>
+        <v>0.999961473421072</v>
       </c>
       <c r="AD155" s="15" t="inlineStr"/>
       <c r="AE155" s="14" t="n">
-        <v>1997620.0</v>
+        <v>2620.0</v>
       </c>
       <c r="AF155" s="14" t="inlineStr"/>
       <c r="AG155" s="14" t="inlineStr"/>
@@ -9614,7 +9614,7 @@
       <c r="O156" s="13" t="inlineStr"/>
       <c r="P156" s="13" t="inlineStr"/>
       <c r="Q156" s="14" t="n">
-        <v>7.0E7</v>
+        <v>6.8731E7</v>
       </c>
       <c r="R156" s="14" t="inlineStr"/>
       <c r="S156" s="14" t="n">
@@ -9636,11 +9636,11 @@
       <c r="AA156" s="14" t="inlineStr"/>
       <c r="AB156" s="14" t="inlineStr"/>
       <c r="AC156" s="15" t="n">
-        <v>0.9818082857142857</v>
+        <v>0.9999356913183279</v>
       </c>
       <c r="AD156" s="15" t="inlineStr"/>
       <c r="AE156" s="14" t="n">
-        <v>1273420.0</v>
+        <v>4420.0</v>
       </c>
       <c r="AF156" s="14" t="inlineStr"/>
       <c r="AG156" s="14" t="inlineStr"/>
@@ -9687,23 +9687,23 @@
       <c r="U157" s="14" t="inlineStr"/>
       <c r="V157" s="14" t="inlineStr"/>
       <c r="W157" s="14" t="n">
-        <v>1.249247E9</v>
+        <v>1.506368E9</v>
       </c>
       <c r="X157" s="14" t="n">
-        <v>2.57121E8</v>
+        <v>2.21436E8</v>
       </c>
       <c r="Y157" s="14" t="inlineStr"/>
       <c r="Z157" s="14" t="n">
-        <v>1.506368E9</v>
+        <v>1.727804E9</v>
       </c>
       <c r="AA157" s="14" t="inlineStr"/>
       <c r="AB157" s="14" t="inlineStr"/>
       <c r="AC157" s="15" t="n">
-        <v>0.5766434534418658</v>
+        <v>0.6614100043486516</v>
       </c>
       <c r="AD157" s="15" t="inlineStr"/>
       <c r="AE157" s="14" t="n">
-        <v>1.105936E9</v>
+        <v>8.845E8</v>
       </c>
       <c r="AF157" s="14" t="inlineStr"/>
       <c r="AG157" s="14" t="inlineStr"/>
@@ -9744,23 +9744,23 @@
       <c r="U158" s="14" t="inlineStr"/>
       <c r="V158" s="14" t="inlineStr"/>
       <c r="W158" s="14" t="n">
-        <v>1.09165E8</v>
+        <v>1.3272E8</v>
       </c>
       <c r="X158" s="14" t="n">
-        <v>2.3555E7</v>
+        <v>2.072E7</v>
       </c>
       <c r="Y158" s="14" t="inlineStr"/>
       <c r="Z158" s="14" t="n">
-        <v>1.3272E8</v>
+        <v>1.5344E8</v>
       </c>
       <c r="AA158" s="14" t="inlineStr"/>
       <c r="AB158" s="14" t="inlineStr"/>
       <c r="AC158" s="15" t="n">
-        <v>0.5163398692810458</v>
+        <v>0.5969498910675382</v>
       </c>
       <c r="AD158" s="15" t="inlineStr"/>
       <c r="AE158" s="14" t="n">
-        <v>1.2432E8</v>
+        <v>1.036E8</v>
       </c>
       <c r="AF158" s="14" t="inlineStr"/>
       <c r="AG158" s="14" t="inlineStr"/>
@@ -9801,23 +9801,23 @@
       <c r="U159" s="14" t="inlineStr"/>
       <c r="V159" s="14" t="inlineStr"/>
       <c r="W159" s="14" t="n">
-        <v>8.87112E8</v>
+        <v>1.07115E9</v>
       </c>
       <c r="X159" s="14" t="n">
-        <v>1.84038E8</v>
+        <v>1.5947E8</v>
       </c>
       <c r="Y159" s="14" t="inlineStr"/>
       <c r="Z159" s="14" t="n">
-        <v>1.07115E9</v>
+        <v>1.23062E9</v>
       </c>
       <c r="AA159" s="14" t="inlineStr"/>
       <c r="AB159" s="14" t="inlineStr"/>
       <c r="AC159" s="15" t="n">
-        <v>0.5930432645034415</v>
+        <v>0.6813339888561127</v>
       </c>
       <c r="AD159" s="15" t="inlineStr"/>
       <c r="AE159" s="14" t="n">
-        <v>7.35042E8</v>
+        <v>5.75572E8</v>
       </c>
       <c r="AF159" s="14" t="inlineStr"/>
       <c r="AG159" s="14" t="inlineStr"/>
@@ -9858,23 +9858,23 @@
       <c r="U160" s="14" t="inlineStr"/>
       <c r="V160" s="14" t="inlineStr"/>
       <c r="W160" s="14" t="n">
-        <v>2.5297E8</v>
+        <v>3.02498E8</v>
       </c>
       <c r="X160" s="14" t="n">
-        <v>4.9528E7</v>
+        <v>4.1246E7</v>
       </c>
       <c r="Y160" s="14" t="inlineStr"/>
       <c r="Z160" s="14" t="n">
-        <v>3.02498E8</v>
+        <v>3.43744E8</v>
       </c>
       <c r="AA160" s="14" t="inlineStr"/>
       <c r="AB160" s="14" t="inlineStr"/>
       <c r="AC160" s="15" t="n">
-        <v>0.5509259259259259</v>
+        <v>0.6260454002389486</v>
       </c>
       <c r="AD160" s="15" t="inlineStr"/>
       <c r="AE160" s="14" t="n">
-        <v>2.46574E8</v>
+        <v>2.05328E8</v>
       </c>
       <c r="AF160" s="14" t="inlineStr"/>
       <c r="AG160" s="14" t="inlineStr"/>
@@ -9921,23 +9921,23 @@
       <c r="U161" s="14" t="inlineStr"/>
       <c r="V161" s="14" t="inlineStr"/>
       <c r="W161" s="14" t="n">
-        <v>2220000.0</v>
+        <v>2405000.0</v>
       </c>
       <c r="X161" s="14" t="n">
         <v>185000.0</v>
       </c>
       <c r="Y161" s="14" t="inlineStr"/>
       <c r="Z161" s="14" t="n">
-        <v>2405000.0</v>
+        <v>2590000.0</v>
       </c>
       <c r="AA161" s="14" t="inlineStr"/>
       <c r="AB161" s="14" t="inlineStr"/>
       <c r="AC161" s="15" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.5</v>
       </c>
       <c r="AD161" s="15" t="inlineStr"/>
       <c r="AE161" s="14" t="n">
-        <v>2775000.0</v>
+        <v>2590000.0</v>
       </c>
       <c r="AF161" s="14" t="inlineStr"/>
       <c r="AG161" s="14" t="inlineStr"/>
@@ -9968,7 +9968,7 @@
       <c r="O162" s="13" t="inlineStr"/>
       <c r="P162" s="13" t="inlineStr"/>
       <c r="Q162" s="14" t="n">
-        <v>4440000.0</v>
+        <v>4620000.0</v>
       </c>
       <c r="R162" s="14" t="inlineStr"/>
       <c r="S162" s="14" t="n">
@@ -9978,23 +9978,23 @@
       <c r="U162" s="14" t="inlineStr"/>
       <c r="V162" s="14" t="inlineStr"/>
       <c r="W162" s="14" t="n">
-        <v>1665000.0</v>
+        <v>1850000.0</v>
       </c>
       <c r="X162" s="14" t="n">
         <v>185000.0</v>
       </c>
       <c r="Y162" s="14" t="inlineStr"/>
       <c r="Z162" s="14" t="n">
-        <v>1850000.0</v>
+        <v>2035000.0</v>
       </c>
       <c r="AA162" s="14" t="inlineStr"/>
       <c r="AB162" s="14" t="inlineStr"/>
       <c r="AC162" s="15" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.44047619047619047</v>
       </c>
       <c r="AD162" s="15" t="inlineStr"/>
       <c r="AE162" s="14" t="n">
-        <v>2590000.0</v>
+        <v>2585000.0</v>
       </c>
       <c r="AF162" s="14" t="inlineStr"/>
       <c r="AG162" s="14" t="inlineStr"/>
@@ -10025,7 +10025,7 @@
       <c r="O163" s="13" t="inlineStr"/>
       <c r="P163" s="13" t="inlineStr"/>
       <c r="Q163" s="14" t="n">
-        <v>370000.0</v>
+        <v>190000.0</v>
       </c>
       <c r="R163" s="14" t="inlineStr"/>
       <c r="S163" s="14" t="n">
@@ -10047,11 +10047,11 @@
       <c r="AA163" s="14" t="inlineStr"/>
       <c r="AB163" s="14" t="inlineStr"/>
       <c r="AC163" s="15" t="n">
-        <v>0.5</v>
+        <v>0.9736842105263158</v>
       </c>
       <c r="AD163" s="15" t="inlineStr"/>
       <c r="AE163" s="14" t="n">
-        <v>185000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="AF163" s="14" t="inlineStr"/>
       <c r="AG163" s="14" t="inlineStr"/>
@@ -10155,23 +10155,23 @@
       <c r="U165" s="14" t="inlineStr"/>
       <c r="V165" s="14" t="inlineStr"/>
       <c r="W165" s="14" t="n">
-        <v>1.7062639415E10</v>
+        <v>1.9035563196E10</v>
       </c>
       <c r="X165" s="14" t="n">
-        <v>1.972923781E9</v>
+        <v>1.919025138E9</v>
       </c>
       <c r="Y165" s="14" t="inlineStr"/>
       <c r="Z165" s="14" t="n">
-        <v>1.9035563196E10</v>
+        <v>2.0954588334E10</v>
       </c>
       <c r="AA165" s="14" t="inlineStr"/>
       <c r="AB165" s="14" t="inlineStr"/>
       <c r="AC165" s="15" t="n">
-        <v>0.6294829099206349</v>
+        <v>0.6929427359126984</v>
       </c>
       <c r="AD165" s="15" t="inlineStr"/>
       <c r="AE165" s="14" t="n">
-        <v>1.1204436804E10</v>
+        <v>9.285411666E9</v>
       </c>
       <c r="AF165" s="14" t="inlineStr"/>
       <c r="AG165" s="14" t="inlineStr"/>
@@ -10202,7 +10202,7 @@
       <c r="O166" s="13" t="inlineStr"/>
       <c r="P166" s="13" t="inlineStr"/>
       <c r="Q166" s="14" t="n">
-        <v>2.541972E10</v>
+        <v>2.5462704E10</v>
       </c>
       <c r="R166" s="14" t="inlineStr"/>
       <c r="S166" s="14" t="n">
@@ -10212,23 +10212,23 @@
       <c r="U166" s="14" t="inlineStr"/>
       <c r="V166" s="14" t="inlineStr"/>
       <c r="W166" s="14" t="n">
-        <v>1.2285354215E10</v>
+        <v>1.4258277996E10</v>
       </c>
       <c r="X166" s="14" t="n">
-        <v>1.972923781E9</v>
+        <v>1.919025138E9</v>
       </c>
       <c r="Y166" s="14" t="inlineStr"/>
       <c r="Z166" s="14" t="n">
-        <v>1.4258277996E10</v>
+        <v>1.6177303134E10</v>
       </c>
       <c r="AA166" s="14" t="inlineStr"/>
       <c r="AB166" s="14" t="inlineStr"/>
       <c r="AC166" s="15" t="n">
-        <v>0.5609140461027895</v>
+        <v>0.6353332754447446</v>
       </c>
       <c r="AD166" s="15" t="inlineStr"/>
       <c r="AE166" s="14" t="n">
-        <v>1.1161442004E10</v>
+        <v>9.285400866E9</v>
       </c>
       <c r="AF166" s="14" t="inlineStr"/>
       <c r="AG166" s="14" t="inlineStr"/>
@@ -10259,7 +10259,7 @@
       <c r="O167" s="13" t="inlineStr"/>
       <c r="P167" s="13" t="inlineStr"/>
       <c r="Q167" s="14" t="n">
-        <v>2.41014E9</v>
+        <v>2.367156E9</v>
       </c>
       <c r="R167" s="14" t="inlineStr"/>
       <c r="S167" s="14" t="n">
@@ -10281,11 +10281,11 @@
       <c r="AA167" s="14" t="inlineStr"/>
       <c r="AB167" s="14" t="inlineStr"/>
       <c r="AC167" s="15" t="n">
-        <v>0.9821613769324603</v>
+        <v>0.9999959533718944</v>
       </c>
       <c r="AD167" s="15" t="inlineStr"/>
       <c r="AE167" s="14" t="n">
-        <v>4.2993579E7</v>
+        <v>9579.0</v>
       </c>
       <c r="AF167" s="14" t="inlineStr"/>
       <c r="AG167" s="14" t="inlineStr"/>
@@ -10389,23 +10389,23 @@
       <c r="U169" s="14" t="inlineStr"/>
       <c r="V169" s="14" t="inlineStr"/>
       <c r="W169" s="14" t="n">
-        <v>1.3597237554E10</v>
+        <v>1.5220846061E10</v>
       </c>
       <c r="X169" s="14" t="n">
-        <v>1.623608507E9</v>
+        <v>1.605499708E9</v>
       </c>
       <c r="Y169" s="14" t="inlineStr"/>
       <c r="Z169" s="14" t="n">
-        <v>1.5220846061E10</v>
+        <v>1.6826345769E10</v>
       </c>
       <c r="AA169" s="14" t="inlineStr"/>
       <c r="AB169" s="14" t="inlineStr"/>
       <c r="AC169" s="15" t="n">
-        <v>1.0151299348112057</v>
+        <v>1.122206164830864</v>
       </c>
       <c r="AD169" s="15" t="inlineStr"/>
       <c r="AE169" s="14" t="n">
-        <v>-2.26858061E8</v>
+        <v>-1.832357769E9</v>
       </c>
       <c r="AF169" s="14" t="inlineStr"/>
       <c r="AG169" s="14" t="inlineStr"/>
@@ -10452,23 +10452,23 @@
       <c r="U170" s="14" t="inlineStr"/>
       <c r="V170" s="14" t="inlineStr"/>
       <c r="W170" s="14" t="n">
-        <v>5.311759666E9</v>
+        <v>5.861130466E9</v>
       </c>
       <c r="X170" s="14" t="n">
         <v>5.493708E8</v>
       </c>
       <c r="Y170" s="14" t="inlineStr"/>
       <c r="Z170" s="14" t="n">
-        <v>5.861130466E9</v>
+        <v>6.410501266E9</v>
       </c>
       <c r="AA170" s="14" t="inlineStr"/>
       <c r="AB170" s="14" t="inlineStr"/>
       <c r="AC170" s="15" t="n">
-        <v>1.3145739439794482</v>
+        <v>1.4377905390463057</v>
       </c>
       <c r="AD170" s="15" t="inlineStr"/>
       <c r="AE170" s="14" t="n">
-        <v>-1.402552466E9</v>
+        <v>-1.951923266E9</v>
       </c>
       <c r="AF170" s="14" t="inlineStr"/>
       <c r="AG170" s="14" t="inlineStr"/>
@@ -10499,7 +10499,7 @@
       <c r="O171" s="13" t="inlineStr"/>
       <c r="P171" s="13" t="inlineStr"/>
       <c r="Q171" s="14" t="n">
-        <v>3.366792E9</v>
+        <v>3.369456E9</v>
       </c>
       <c r="R171" s="14" t="inlineStr"/>
       <c r="S171" s="14" t="n">
@@ -10509,23 +10509,23 @@
       <c r="U171" s="14" t="inlineStr"/>
       <c r="V171" s="14" t="inlineStr"/>
       <c r="W171" s="14" t="n">
-        <v>4.222646E9</v>
+        <v>4.7720168E9</v>
       </c>
       <c r="X171" s="14" t="n">
         <v>5.493708E8</v>
       </c>
       <c r="Y171" s="14" t="inlineStr"/>
       <c r="Z171" s="14" t="n">
-        <v>4.7720168E9</v>
+        <v>5.3213876E9</v>
       </c>
       <c r="AA171" s="14" t="inlineStr"/>
       <c r="AB171" s="14" t="inlineStr"/>
       <c r="AC171" s="15" t="n">
-        <v>1.4173779669192512</v>
+        <v>1.5793017033016605</v>
       </c>
       <c r="AD171" s="15" t="inlineStr"/>
       <c r="AE171" s="14" t="n">
-        <v>-1.4052248E9</v>
+        <v>-1.9519316E9</v>
       </c>
       <c r="AF171" s="14" t="inlineStr"/>
       <c r="AG171" s="14" t="inlineStr"/>
@@ -10556,7 +10556,7 @@
       <c r="O172" s="13" t="inlineStr"/>
       <c r="P172" s="13" t="inlineStr"/>
       <c r="Q172" s="14" t="n">
-        <v>5.45894E8</v>
+        <v>5.4323E8</v>
       </c>
       <c r="R172" s="14" t="inlineStr"/>
       <c r="S172" s="14" t="n">
@@ -10578,11 +10578,11 @@
       <c r="AA172" s="14" t="inlineStr"/>
       <c r="AB172" s="14" t="inlineStr"/>
       <c r="AC172" s="15" t="n">
-        <v>0.9951052768486189</v>
+        <v>0.999985273272831</v>
       </c>
       <c r="AD172" s="15" t="inlineStr"/>
       <c r="AE172" s="14" t="n">
-        <v>2672000.0</v>
+        <v>8000.0</v>
       </c>
       <c r="AF172" s="14" t="inlineStr"/>
       <c r="AG172" s="14" t="inlineStr"/>
@@ -10729,23 +10729,23 @@
       <c r="U175" s="14" t="inlineStr"/>
       <c r="V175" s="14" t="inlineStr"/>
       <c r="W175" s="14" t="n">
-        <v>101733.0</v>
+        <v>111771.0</v>
       </c>
       <c r="X175" s="14" t="n">
-        <v>10038.0</v>
+        <v>10020.0</v>
       </c>
       <c r="Y175" s="14" t="inlineStr"/>
       <c r="Z175" s="14" t="n">
-        <v>111771.0</v>
+        <v>121791.0</v>
       </c>
       <c r="AA175" s="14" t="inlineStr"/>
       <c r="AB175" s="14" t="inlineStr"/>
       <c r="AC175" s="15" t="n">
-        <v>0.7074113924050633</v>
+        <v>0.7708291139240506</v>
       </c>
       <c r="AD175" s="15" t="inlineStr"/>
       <c r="AE175" s="14" t="n">
-        <v>46229.0</v>
+        <v>36209.0</v>
       </c>
       <c r="AF175" s="14" t="inlineStr"/>
       <c r="AG175" s="14" t="inlineStr"/>
@@ -10786,23 +10786,23 @@
       <c r="U176" s="14" t="inlineStr"/>
       <c r="V176" s="14" t="inlineStr"/>
       <c r="W176" s="14" t="n">
-        <v>88613.0</v>
+        <v>98651.0</v>
       </c>
       <c r="X176" s="14" t="n">
-        <v>10038.0</v>
+        <v>10020.0</v>
       </c>
       <c r="Y176" s="14" t="inlineStr"/>
       <c r="Z176" s="14" t="n">
-        <v>98651.0</v>
+        <v>108671.0</v>
       </c>
       <c r="AA176" s="14" t="inlineStr"/>
       <c r="AB176" s="14" t="inlineStr"/>
       <c r="AC176" s="15" t="n">
-        <v>0.6850763888888889</v>
+        <v>0.7546597222222222</v>
       </c>
       <c r="AD176" s="15" t="inlineStr"/>
       <c r="AE176" s="14" t="n">
-        <v>45349.0</v>
+        <v>35329.0</v>
       </c>
       <c r="AF176" s="14" t="inlineStr"/>
       <c r="AG176" s="14" t="inlineStr"/>
@@ -10963,23 +10963,23 @@
       <c r="U179" s="14" t="inlineStr"/>
       <c r="V179" s="14" t="inlineStr"/>
       <c r="W179" s="14" t="n">
-        <v>3.5985017E8</v>
+        <v>3.9715681E8</v>
       </c>
       <c r="X179" s="14" t="n">
-        <v>3.730664E7</v>
+        <v>3.791288E7</v>
       </c>
       <c r="Y179" s="14" t="inlineStr"/>
       <c r="Z179" s="14" t="n">
-        <v>3.9715681E8</v>
+        <v>4.3506969E8</v>
       </c>
       <c r="AA179" s="14" t="inlineStr"/>
       <c r="AB179" s="14" t="inlineStr"/>
       <c r="AC179" s="15" t="n">
-        <v>1.0999562683830657</v>
+        <v>1.2049588994809812</v>
       </c>
       <c r="AD179" s="15" t="inlineStr"/>
       <c r="AE179" s="14" t="n">
-        <v>-3.609081E7</v>
+        <v>-7.400369E7</v>
       </c>
       <c r="AF179" s="14" t="inlineStr"/>
       <c r="AG179" s="14" t="inlineStr"/>
@@ -11010,7 +11010,7 @@
       <c r="O180" s="13" t="inlineStr"/>
       <c r="P180" s="13" t="inlineStr"/>
       <c r="Q180" s="14" t="n">
-        <v>2.88E8</v>
+        <v>2.8734E8</v>
       </c>
       <c r="R180" s="14" t="inlineStr"/>
       <c r="S180" s="14" t="n">
@@ -11020,23 +11020,23 @@
       <c r="U180" s="14" t="inlineStr"/>
       <c r="V180" s="14" t="inlineStr"/>
       <c r="W180" s="14" t="n">
-        <v>2.861254E8</v>
+        <v>3.2343204E8</v>
       </c>
       <c r="X180" s="14" t="n">
-        <v>3.730664E7</v>
+        <v>3.791288E7</v>
       </c>
       <c r="Y180" s="14" t="inlineStr"/>
       <c r="Z180" s="14" t="n">
-        <v>3.2343204E8</v>
+        <v>3.6134492E8</v>
       </c>
       <c r="AA180" s="14" t="inlineStr"/>
       <c r="AB180" s="14" t="inlineStr"/>
       <c r="AC180" s="15" t="n">
-        <v>1.1230279166666666</v>
+        <v>1.2575517505394307</v>
       </c>
       <c r="AD180" s="15" t="inlineStr"/>
       <c r="AE180" s="14" t="n">
-        <v>-3.543204E7</v>
+        <v>-7.400492E7</v>
       </c>
       <c r="AF180" s="14" t="inlineStr"/>
       <c r="AG180" s="14" t="inlineStr"/>
@@ -11067,7 +11067,7 @@
       <c r="O181" s="13" t="inlineStr"/>
       <c r="P181" s="13" t="inlineStr"/>
       <c r="Q181" s="14" t="n">
-        <v>3.6533E7</v>
+        <v>3.7193E7</v>
       </c>
       <c r="R181" s="14" t="inlineStr"/>
       <c r="S181" s="14" t="n">
@@ -11089,11 +11089,11 @@
       <c r="AA181" s="14" t="inlineStr"/>
       <c r="AB181" s="14" t="inlineStr"/>
       <c r="AC181" s="15" t="n">
-        <v>1.0180409492787343</v>
+        <v>0.999975533030409</v>
       </c>
       <c r="AD181" s="15" t="inlineStr"/>
       <c r="AE181" s="14" t="n">
-        <v>-659090.0</v>
+        <v>910.0</v>
       </c>
       <c r="AF181" s="14" t="inlineStr"/>
       <c r="AG181" s="14" t="inlineStr"/>
@@ -11197,23 +11197,23 @@
       <c r="U183" s="14" t="inlineStr"/>
       <c r="V183" s="14" t="inlineStr"/>
       <c r="W183" s="14" t="n">
-        <v>1.07733296E8</v>
+        <v>1.18776192E8</v>
       </c>
       <c r="X183" s="14" t="n">
         <v>1.1042896E7</v>
       </c>
       <c r="Y183" s="14" t="inlineStr"/>
       <c r="Z183" s="14" t="n">
-        <v>1.18776192E8</v>
+        <v>1.29819088E8</v>
       </c>
       <c r="AA183" s="14" t="inlineStr"/>
       <c r="AB183" s="14" t="inlineStr"/>
       <c r="AC183" s="15" t="n">
-        <v>1.0598582289324339</v>
+        <v>1.158395688332084</v>
       </c>
       <c r="AD183" s="15" t="inlineStr"/>
       <c r="AE183" s="14" t="n">
-        <v>-6708192.0</v>
+        <v>-1.7751088E7</v>
       </c>
       <c r="AF183" s="14" t="inlineStr"/>
       <c r="AG183" s="14" t="inlineStr"/>
@@ -11244,7 +11244,7 @@
       <c r="O184" s="13" t="inlineStr"/>
       <c r="P184" s="13" t="inlineStr"/>
       <c r="Q184" s="14" t="n">
-        <v>9.0E7</v>
+        <v>9.018E7</v>
       </c>
       <c r="R184" s="14" t="inlineStr"/>
       <c r="S184" s="14" t="n">
@@ -11254,23 +11254,23 @@
       <c r="U184" s="14" t="inlineStr"/>
       <c r="V184" s="14" t="inlineStr"/>
       <c r="W184" s="14" t="n">
-        <v>8.5850712E7</v>
+        <v>9.6893608E7</v>
       </c>
       <c r="X184" s="14" t="n">
         <v>1.1042896E7</v>
       </c>
       <c r="Y184" s="14" t="inlineStr"/>
       <c r="Z184" s="14" t="n">
-        <v>9.6893608E7</v>
+        <v>1.07936504E8</v>
       </c>
       <c r="AA184" s="14" t="inlineStr"/>
       <c r="AB184" s="14" t="inlineStr"/>
       <c r="AC184" s="15" t="n">
-        <v>1.0765956444444444</v>
+        <v>1.1969006875138613</v>
       </c>
       <c r="AD184" s="15" t="inlineStr"/>
       <c r="AE184" s="14" t="n">
-        <v>-6893608.0</v>
+        <v>-1.7756504E7</v>
       </c>
       <c r="AF184" s="14" t="inlineStr"/>
       <c r="AG184" s="14" t="inlineStr"/>
@@ -11301,7 +11301,7 @@
       <c r="O185" s="13" t="inlineStr"/>
       <c r="P185" s="13" t="inlineStr"/>
       <c r="Q185" s="14" t="n">
-        <v>1.1034E7</v>
+        <v>1.0854E7</v>
       </c>
       <c r="R185" s="14" t="inlineStr"/>
       <c r="S185" s="14" t="n">
@@ -11323,11 +11323,11 @@
       <c r="AA185" s="14" t="inlineStr"/>
       <c r="AB185" s="14" t="inlineStr"/>
       <c r="AC185" s="15" t="n">
-        <v>0.983200290012688</v>
+        <v>0.9995054357840427</v>
       </c>
       <c r="AD185" s="15" t="inlineStr"/>
       <c r="AE185" s="14" t="n">
-        <v>185368.0</v>
+        <v>5368.0</v>
       </c>
       <c r="AF185" s="14" t="inlineStr"/>
       <c r="AG185" s="14" t="inlineStr"/>
@@ -11431,23 +11431,23 @@
       <c r="U187" s="14" t="inlineStr"/>
       <c r="V187" s="14" t="inlineStr"/>
       <c r="W187" s="14" t="n">
-        <v>8.6691E8</v>
+        <v>9.5565E8</v>
       </c>
       <c r="X187" s="14" t="n">
         <v>8.874E7</v>
       </c>
       <c r="Y187" s="14" t="inlineStr"/>
       <c r="Z187" s="14" t="n">
-        <v>9.5565E8</v>
+        <v>1.04439E9</v>
       </c>
       <c r="AA187" s="14" t="inlineStr"/>
       <c r="AB187" s="14" t="inlineStr"/>
       <c r="AC187" s="15" t="n">
-        <v>1.064032333489211</v>
+        <v>1.162836528826241</v>
       </c>
       <c r="AD187" s="15" t="inlineStr"/>
       <c r="AE187" s="14" t="n">
-        <v>-5.751E7</v>
+        <v>-1.4625E8</v>
       </c>
       <c r="AF187" s="14" t="inlineStr"/>
       <c r="AG187" s="14" t="inlineStr"/>
@@ -11478,7 +11478,7 @@
       <c r="O188" s="13" t="inlineStr"/>
       <c r="P188" s="13" t="inlineStr"/>
       <c r="Q188" s="14" t="n">
-        <v>7.2E8</v>
+        <v>7.20324E8</v>
       </c>
       <c r="R188" s="14" t="inlineStr"/>
       <c r="S188" s="14" t="n">
@@ -11488,23 +11488,23 @@
       <c r="U188" s="14" t="inlineStr"/>
       <c r="V188" s="14" t="inlineStr"/>
       <c r="W188" s="14" t="n">
-        <v>6.891E8</v>
+        <v>7.7784E8</v>
       </c>
       <c r="X188" s="14" t="n">
         <v>8.874E7</v>
       </c>
       <c r="Y188" s="14" t="inlineStr"/>
       <c r="Z188" s="14" t="n">
-        <v>7.7784E8</v>
+        <v>8.6658E8</v>
       </c>
       <c r="AA188" s="14" t="inlineStr"/>
       <c r="AB188" s="14" t="inlineStr"/>
       <c r="AC188" s="15" t="n">
-        <v>1.0803333333333334</v>
+        <v>1.203041964449331</v>
       </c>
       <c r="AD188" s="15" t="inlineStr"/>
       <c r="AE188" s="14" t="n">
-        <v>-5.784E7</v>
+        <v>-1.46256E8</v>
       </c>
       <c r="AF188" s="14" t="inlineStr"/>
       <c r="AG188" s="14" t="inlineStr"/>
@@ -11535,7 +11535,7 @@
       <c r="O189" s="13" t="inlineStr"/>
       <c r="P189" s="13" t="inlineStr"/>
       <c r="Q189" s="14" t="n">
-        <v>8.907E7</v>
+        <v>8.8746E7</v>
       </c>
       <c r="R189" s="14" t="inlineStr"/>
       <c r="S189" s="14" t="n">
@@ -11557,11 +11557,11 @@
       <c r="AA189" s="14" t="inlineStr"/>
       <c r="AB189" s="14" t="inlineStr"/>
       <c r="AC189" s="15" t="n">
-        <v>0.9962950488379926</v>
+        <v>0.9999323913190453</v>
       </c>
       <c r="AD189" s="15" t="inlineStr"/>
       <c r="AE189" s="14" t="n">
-        <v>330000.0</v>
+        <v>6000.0</v>
       </c>
       <c r="AF189" s="14" t="inlineStr"/>
       <c r="AG189" s="14" t="inlineStr"/>
@@ -11665,23 +11665,23 @@
       <c r="U191" s="14" t="inlineStr"/>
       <c r="V191" s="14" t="inlineStr"/>
       <c r="W191" s="14" t="n">
-        <v>3.2558825E8</v>
+        <v>3.5882903E8</v>
       </c>
       <c r="X191" s="14" t="n">
-        <v>3.324078E7</v>
+        <v>3.338562E7</v>
       </c>
       <c r="Y191" s="14" t="inlineStr"/>
       <c r="Z191" s="14" t="n">
-        <v>3.5882903E8</v>
+        <v>3.9221465E8</v>
       </c>
       <c r="AA191" s="14" t="inlineStr"/>
       <c r="AB191" s="14" t="inlineStr"/>
       <c r="AC191" s="15" t="n">
-        <v>1.0849015867064955</v>
+        <v>1.1858413353973418</v>
       </c>
       <c r="AD191" s="15" t="inlineStr"/>
       <c r="AE191" s="14" t="n">
-        <v>-2.808103E7</v>
+        <v>-6.146665E7</v>
       </c>
       <c r="AF191" s="14" t="inlineStr"/>
       <c r="AG191" s="14" t="inlineStr"/>
@@ -11712,7 +11712,7 @@
       <c r="O192" s="13" t="inlineStr"/>
       <c r="P192" s="13" t="inlineStr"/>
       <c r="Q192" s="14" t="n">
-        <v>2.64E8</v>
+        <v>2.64204E8</v>
       </c>
       <c r="R192" s="14" t="inlineStr"/>
       <c r="S192" s="14" t="n">
@@ -11722,23 +11722,23 @@
       <c r="U192" s="14" t="inlineStr"/>
       <c r="V192" s="14" t="inlineStr"/>
       <c r="W192" s="14" t="n">
-        <v>2.5904634E8</v>
+        <v>2.9228712E8</v>
       </c>
       <c r="X192" s="14" t="n">
-        <v>3.324078E7</v>
+        <v>3.338562E7</v>
       </c>
       <c r="Y192" s="14" t="inlineStr"/>
       <c r="Z192" s="14" t="n">
-        <v>2.9228712E8</v>
+        <v>3.2567274E8</v>
       </c>
       <c r="AA192" s="14" t="inlineStr"/>
       <c r="AB192" s="14" t="inlineStr"/>
       <c r="AC192" s="15" t="n">
-        <v>1.1071481818181819</v>
+        <v>1.2326563564518327</v>
       </c>
       <c r="AD192" s="15" t="inlineStr"/>
       <c r="AE192" s="14" t="n">
-        <v>-2.828712E7</v>
+        <v>-6.146874E7</v>
       </c>
       <c r="AF192" s="14" t="inlineStr"/>
       <c r="AG192" s="14" t="inlineStr"/>
@@ -11769,7 +11769,7 @@
       <c r="O193" s="13" t="inlineStr"/>
       <c r="P193" s="13" t="inlineStr"/>
       <c r="Q193" s="14" t="n">
-        <v>3.3374E7</v>
+        <v>3.317E7</v>
       </c>
       <c r="R193" s="14" t="inlineStr"/>
       <c r="S193" s="14" t="n">
@@ -11791,11 +11791,11 @@
       <c r="AA193" s="14" t="inlineStr"/>
       <c r="AB193" s="14" t="inlineStr"/>
       <c r="AC193" s="15" t="n">
-        <v>0.9938383172529514</v>
+        <v>0.9999505577328912</v>
       </c>
       <c r="AD193" s="15" t="inlineStr"/>
       <c r="AE193" s="14" t="n">
-        <v>205640.0</v>
+        <v>1640.0</v>
       </c>
       <c r="AF193" s="14" t="inlineStr"/>
       <c r="AG193" s="14" t="inlineStr"/>
@@ -11899,23 +11899,23 @@
       <c r="U195" s="14" t="inlineStr"/>
       <c r="V195" s="14" t="inlineStr"/>
       <c r="W195" s="14" t="n">
-        <v>6.44264E8</v>
+        <v>7.83142E8</v>
       </c>
       <c r="X195" s="14" t="n">
-        <v>1.38878E8</v>
+        <v>1.19882E8</v>
       </c>
       <c r="Y195" s="14" t="inlineStr"/>
       <c r="Z195" s="14" t="n">
-        <v>7.83142E8</v>
+        <v>9.03024E8</v>
       </c>
       <c r="AA195" s="14" t="inlineStr"/>
       <c r="AB195" s="14" t="inlineStr"/>
       <c r="AC195" s="15" t="n">
-        <v>0.7715988807440687</v>
+        <v>0.8897138803499646</v>
       </c>
       <c r="AD195" s="15" t="inlineStr"/>
       <c r="AE195" s="14" t="n">
-        <v>2.31818E8</v>
+        <v>1.11936E8</v>
       </c>
       <c r="AF195" s="14" t="inlineStr"/>
       <c r="AG195" s="14" t="inlineStr"/>
@@ -11956,23 +11956,23 @@
       <c r="U196" s="14" t="inlineStr"/>
       <c r="V196" s="14" t="inlineStr"/>
       <c r="W196" s="14" t="n">
-        <v>6.181E7</v>
+        <v>7.511E7</v>
       </c>
       <c r="X196" s="14" t="n">
-        <v>1.33E7</v>
+        <v>1.162E7</v>
       </c>
       <c r="Y196" s="14" t="inlineStr"/>
       <c r="Z196" s="14" t="n">
-        <v>7.511E7</v>
+        <v>8.673E7</v>
       </c>
       <c r="AA196" s="14" t="inlineStr"/>
       <c r="AB196" s="14" t="inlineStr"/>
       <c r="AC196" s="15" t="n">
-        <v>0.6878205128205128</v>
+        <v>0.7942307692307692</v>
       </c>
       <c r="AD196" s="15" t="inlineStr"/>
       <c r="AE196" s="14" t="n">
-        <v>3.409E7</v>
+        <v>2.247E7</v>
       </c>
       <c r="AF196" s="14" t="inlineStr"/>
       <c r="AG196" s="14" t="inlineStr"/>
@@ -12013,23 +12013,23 @@
       <c r="U197" s="14" t="inlineStr"/>
       <c r="V197" s="14" t="inlineStr"/>
       <c r="W197" s="14" t="n">
-        <v>5.82454E8</v>
+        <v>7.08032E8</v>
       </c>
       <c r="X197" s="14" t="n">
-        <v>1.25578E8</v>
+        <v>1.08262E8</v>
       </c>
       <c r="Y197" s="14" t="inlineStr"/>
       <c r="Z197" s="14" t="n">
-        <v>7.08032E8</v>
+        <v>8.16294E8</v>
       </c>
       <c r="AA197" s="14" t="inlineStr"/>
       <c r="AB197" s="14" t="inlineStr"/>
       <c r="AC197" s="15" t="n">
-        <v>0.7816993464052288</v>
+        <v>0.9012254901960784</v>
       </c>
       <c r="AD197" s="15" t="inlineStr"/>
       <c r="AE197" s="14" t="n">
-        <v>1.97728E8</v>
+        <v>8.9466E7</v>
       </c>
       <c r="AF197" s="14" t="inlineStr"/>
       <c r="AG197" s="14" t="inlineStr"/>
@@ -12076,23 +12076,23 @@
       <c r="U198" s="14" t="inlineStr"/>
       <c r="V198" s="14" t="inlineStr"/>
       <c r="W198" s="14" t="n">
-        <v>5.981030439E9</v>
+        <v>6.746049792E9</v>
       </c>
       <c r="X198" s="14" t="n">
-        <v>7.65019353E8</v>
+        <v>7.65155492E8</v>
       </c>
       <c r="Y198" s="14" t="inlineStr"/>
       <c r="Z198" s="14" t="n">
-        <v>6.746049792E9</v>
+        <v>7.511205284E9</v>
       </c>
       <c r="AA198" s="14" t="inlineStr"/>
       <c r="AB198" s="14" t="inlineStr"/>
       <c r="AC198" s="15" t="n">
-        <v>0.8628571016350164</v>
+        <v>0.9607247235002117</v>
       </c>
       <c r="AD198" s="15" t="inlineStr"/>
       <c r="AE198" s="14" t="n">
-        <v>1.072220208E9</v>
+        <v>3.07064716E8</v>
       </c>
       <c r="AF198" s="14" t="inlineStr"/>
       <c r="AG198" s="14" t="inlineStr"/>
@@ -12123,7 +12123,7 @@
       <c r="O199" s="13" t="inlineStr"/>
       <c r="P199" s="13" t="inlineStr"/>
       <c r="Q199" s="14" t="n">
-        <v>6.24E9</v>
+        <v>6.243816E9</v>
       </c>
       <c r="R199" s="14" t="inlineStr"/>
       <c r="S199" s="14" t="n">
@@ -12133,23 +12133,23 @@
       <c r="U199" s="14" t="inlineStr"/>
       <c r="V199" s="14" t="inlineStr"/>
       <c r="W199" s="14" t="n">
-        <v>4.406587063E9</v>
+        <v>5.171606416E9</v>
       </c>
       <c r="X199" s="14" t="n">
-        <v>7.65019353E8</v>
+        <v>7.65155492E8</v>
       </c>
       <c r="Y199" s="14" t="inlineStr"/>
       <c r="Z199" s="14" t="n">
-        <v>5.171606416E9</v>
+        <v>5.936761908E9</v>
       </c>
       <c r="AA199" s="14" t="inlineStr"/>
       <c r="AB199" s="14" t="inlineStr"/>
       <c r="AC199" s="15" t="n">
-        <v>0.8287830794871794</v>
+        <v>0.950822687279702</v>
       </c>
       <c r="AD199" s="15" t="inlineStr"/>
       <c r="AE199" s="14" t="n">
-        <v>1.068393584E9</v>
+        <v>3.07054092E8</v>
       </c>
       <c r="AF199" s="14" t="inlineStr"/>
       <c r="AG199" s="14" t="inlineStr"/>
@@ -12180,7 +12180,7 @@
       <c r="O200" s="13" t="inlineStr"/>
       <c r="P200" s="13" t="inlineStr"/>
       <c r="Q200" s="14" t="n">
-        <v>7.89135E8</v>
+        <v>7.85319E8</v>
       </c>
       <c r="R200" s="14" t="inlineStr"/>
       <c r="S200" s="14" t="n">
@@ -12202,11 +12202,11 @@
       <c r="AA200" s="14" t="inlineStr"/>
       <c r="AB200" s="14" t="inlineStr"/>
       <c r="AC200" s="15" t="n">
-        <v>0.995151392347317</v>
+        <v>0.9999870040072888</v>
       </c>
       <c r="AD200" s="15" t="inlineStr"/>
       <c r="AE200" s="14" t="n">
-        <v>3826206.0</v>
+        <v>10206.0</v>
       </c>
       <c r="AF200" s="14" t="inlineStr"/>
       <c r="AG200" s="14" t="inlineStr"/>
@@ -12343,7 +12343,7 @@
       <c r="O203" s="24" t="inlineStr"/>
       <c r="P203" s="24" t="inlineStr"/>
       <c r="Q203" s="25" t="n">
-        <v>5.655769E9</v>
+        <v>6.668305E9</v>
       </c>
       <c r="R203" s="25" t="inlineStr"/>
       <c r="S203" s="25" t="n">
@@ -12353,23 +12353,23 @@
       <c r="U203" s="25" t="inlineStr"/>
       <c r="V203" s="25" t="inlineStr"/>
       <c r="W203" s="25" t="n">
-        <v>4.15571698E9</v>
+        <v>4.395054502E9</v>
       </c>
       <c r="X203" s="25" t="n">
-        <v>2.39337522E8</v>
+        <v>6.82735029E8</v>
       </c>
       <c r="Y203" s="25" t="inlineStr"/>
       <c r="Z203" s="25" t="n">
-        <v>4.395054502E9</v>
+        <v>5.077789531E9</v>
       </c>
       <c r="AA203" s="25" t="inlineStr"/>
       <c r="AB203" s="25" t="inlineStr"/>
       <c r="AC203" s="26" t="n">
-        <v>0.7770922931965574</v>
+        <v>0.7614812956216009</v>
       </c>
       <c r="AD203" s="26" t="inlineStr"/>
       <c r="AE203" s="25" t="n">
-        <v>1.260714498E9</v>
+        <v>1.590515469E9</v>
       </c>
       <c r="AF203" s="25" t="inlineStr"/>
       <c r="AG203" s="25" t="inlineStr"/>
@@ -12406,7 +12406,7 @@
       <c r="O204" s="13" t="inlineStr"/>
       <c r="P204" s="13" t="inlineStr"/>
       <c r="Q204" s="14" t="n">
-        <v>3.884654E9</v>
+        <v>4.91939E9</v>
       </c>
       <c r="R204" s="14" t="inlineStr"/>
       <c r="S204" s="14" t="n">
@@ -12416,23 +12416,23 @@
       <c r="U204" s="14" t="inlineStr"/>
       <c r="V204" s="14" t="inlineStr"/>
       <c r="W204" s="14" t="n">
-        <v>3.258757999E9</v>
+        <v>3.397986435E9</v>
       </c>
       <c r="X204" s="14" t="n">
-        <v>1.39228436E8</v>
+        <v>5.89124467E8</v>
       </c>
       <c r="Y204" s="14" t="inlineStr"/>
       <c r="Z204" s="14" t="n">
-        <v>3.397986435E9</v>
+        <v>3.987110902E9</v>
       </c>
       <c r="AA204" s="14" t="inlineStr"/>
       <c r="AB204" s="14" t="inlineStr"/>
       <c r="AC204" s="15" t="n">
-        <v>0.8747204860458615</v>
+        <v>0.8104888821581537</v>
       </c>
       <c r="AD204" s="15" t="inlineStr"/>
       <c r="AE204" s="14" t="n">
-        <v>4.86667565E8</v>
+        <v>9.32279098E8</v>
       </c>
       <c r="AF204" s="14" t="inlineStr"/>
       <c r="AG204" s="14" t="inlineStr"/>
@@ -12469,7 +12469,7 @@
       <c r="O205" s="13" t="inlineStr"/>
       <c r="P205" s="13" t="inlineStr"/>
       <c r="Q205" s="14" t="n">
-        <v>7.34717E8</v>
+        <v>1.754348E9</v>
       </c>
       <c r="R205" s="14" t="inlineStr"/>
       <c r="S205" s="14" t="n">
@@ -12479,23 +12479,23 @@
       <c r="U205" s="14" t="inlineStr"/>
       <c r="V205" s="14" t="inlineStr"/>
       <c r="W205" s="14" t="n">
-        <v>5.46628803E8</v>
+        <v>6.12205803E8</v>
       </c>
       <c r="X205" s="14" t="n">
-        <v>6.5577E7</v>
+        <v>5.08794051E8</v>
       </c>
       <c r="Y205" s="14" t="inlineStr"/>
       <c r="Z205" s="14" t="n">
-        <v>6.12205803E8</v>
+        <v>1.120999854E9</v>
       </c>
       <c r="AA205" s="14" t="inlineStr"/>
       <c r="AB205" s="14" t="inlineStr"/>
       <c r="AC205" s="15" t="n">
-        <v>0.833253896398205</v>
+        <v>0.6389837443882286</v>
       </c>
       <c r="AD205" s="15" t="inlineStr"/>
       <c r="AE205" s="14" t="n">
-        <v>1.22511197E8</v>
+        <v>6.33348146E8</v>
       </c>
       <c r="AF205" s="14" t="inlineStr"/>
       <c r="AG205" s="14" t="inlineStr"/>
@@ -12536,10 +12536,10 @@
       <c r="U206" s="14" t="inlineStr"/>
       <c r="V206" s="14" t="inlineStr"/>
       <c r="W206" s="14" t="n">
-        <v>5.115E8</v>
+        <v>5.75E8</v>
       </c>
       <c r="X206" s="14" t="n">
-        <v>6.35E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y206" s="14" t="inlineStr"/>
       <c r="Z206" s="14" t="n">
@@ -12596,20 +12596,20 @@
         <v>2419200.0</v>
       </c>
       <c r="X207" s="14" t="n">
-        <v>0.0</v>
+        <v>342900.0</v>
       </c>
       <c r="Y207" s="14" t="inlineStr"/>
       <c r="Z207" s="14" t="n">
-        <v>2419200.0</v>
+        <v>2762100.0</v>
       </c>
       <c r="AA207" s="14" t="inlineStr"/>
       <c r="AB207" s="14" t="inlineStr"/>
       <c r="AC207" s="15" t="n">
-        <v>0.7761308950914341</v>
+        <v>0.8861405197305101</v>
       </c>
       <c r="AD207" s="15" t="inlineStr"/>
       <c r="AE207" s="14" t="n">
-        <v>697800.0</v>
+        <v>354900.0</v>
       </c>
       <c r="AF207" s="14" t="inlineStr"/>
       <c r="AG207" s="14" t="inlineStr"/>
@@ -12640,7 +12640,7 @@
       <c r="O208" s="13" t="inlineStr"/>
       <c r="P208" s="13" t="inlineStr"/>
       <c r="Q208" s="14" t="n">
-        <v>5.16E7</v>
+        <v>5.8695E7</v>
       </c>
       <c r="R208" s="14" t="inlineStr"/>
       <c r="S208" s="14" t="n">
@@ -12650,23 +12650,23 @@
       <c r="U208" s="14" t="inlineStr"/>
       <c r="V208" s="14" t="inlineStr"/>
       <c r="W208" s="14" t="n">
-        <v>3.2709603E7</v>
+        <v>3.4786603E7</v>
       </c>
       <c r="X208" s="14" t="n">
-        <v>2077000.0</v>
+        <v>3941431.0</v>
       </c>
       <c r="Y208" s="14" t="inlineStr"/>
       <c r="Z208" s="14" t="n">
-        <v>3.4786603E7</v>
+        <v>3.8728034E7</v>
       </c>
       <c r="AA208" s="14" t="inlineStr"/>
       <c r="AB208" s="14" t="inlineStr"/>
       <c r="AC208" s="15" t="n">
-        <v>0.674158972868217</v>
+        <v>0.6598182809438623</v>
       </c>
       <c r="AD208" s="15" t="inlineStr"/>
       <c r="AE208" s="14" t="n">
-        <v>1.6813397E7</v>
+        <v>1.9966966E7</v>
       </c>
       <c r="AF208" s="14" t="inlineStr"/>
       <c r="AG208" s="14" t="inlineStr"/>
@@ -12681,29 +12681,23 @@
       <c r="E209" s="2" t="inlineStr"/>
       <c r="F209" s="2" t="inlineStr"/>
       <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521119</t>
-          </r>
-        </is>
-      </c>
-      <c r="I209" s="13" t="inlineStr"/>
-      <c r="J209" s="13" t="inlineStr"/>
-      <c r="K209" s="13" t="inlineStr"/>
-      <c r="L209" s="13" t="inlineStr"/>
-      <c r="M209" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N209" s="13" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr"/>
+      <c r="I209" s="2" t="inlineStr"/>
+      <c r="J209" s="2" t="inlineStr"/>
+      <c r="K209" s="2" t="inlineStr"/>
+      <c r="L209" s="2" t="inlineStr"/>
+      <c r="M209" s="2" t="inlineStr"/>
+      <c r="N209" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000288. Honor Penyuluh Non PNS (Sarjana Muda)</t>
+          </r>
+        </is>
+      </c>
       <c r="O209" s="13" t="inlineStr"/>
       <c r="P209" s="13" t="inlineStr"/>
       <c r="Q209" s="14" t="n">
-        <v>1.3E7</v>
+        <v>8.64E7</v>
       </c>
       <c r="R209" s="14" t="inlineStr"/>
       <c r="S209" s="14" t="n">
@@ -12713,23 +12707,23 @@
       <c r="U209" s="14" t="inlineStr"/>
       <c r="V209" s="14" t="inlineStr"/>
       <c r="W209" s="14" t="n">
-        <v>5144000.0</v>
+        <v>0.0</v>
       </c>
       <c r="X209" s="14" t="n">
-        <v>222500.0</v>
+        <v>4.32E7</v>
       </c>
       <c r="Y209" s="14" t="inlineStr"/>
       <c r="Z209" s="14" t="n">
-        <v>5366500.0</v>
+        <v>4.32E7</v>
       </c>
       <c r="AA209" s="14" t="inlineStr"/>
       <c r="AB209" s="14" t="inlineStr"/>
       <c r="AC209" s="15" t="n">
-        <v>0.4128076923076923</v>
+        <v>0.5</v>
       </c>
       <c r="AD209" s="15" t="inlineStr"/>
       <c r="AE209" s="14" t="n">
-        <v>7633500.0</v>
+        <v>4.32E7</v>
       </c>
       <c r="AF209" s="14" t="inlineStr"/>
       <c r="AG209" s="14" t="inlineStr"/>
@@ -12753,14 +12747,14 @@
       <c r="N210" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000133. Biaya Tol</t>
+            <t xml:space="preserve">000289. Honor Penyuluh Non PNS (Sarjana)</t>
           </r>
         </is>
       </c>
       <c r="O210" s="13" t="inlineStr"/>
       <c r="P210" s="13" t="inlineStr"/>
       <c r="Q210" s="14" t="n">
-        <v>5800000.0</v>
+        <v>8.892E8</v>
       </c>
       <c r="R210" s="14" t="inlineStr"/>
       <c r="S210" s="14" t="n">
@@ -12770,23 +12764,23 @@
       <c r="U210" s="14" t="inlineStr"/>
       <c r="V210" s="14" t="inlineStr"/>
       <c r="W210" s="14" t="n">
-        <v>2720000.0</v>
+        <v>0.0</v>
       </c>
       <c r="X210" s="14" t="n">
-        <v>222500.0</v>
+        <v>4.446E8</v>
       </c>
       <c r="Y210" s="14" t="inlineStr"/>
       <c r="Z210" s="14" t="n">
-        <v>2942500.0</v>
+        <v>4.446E8</v>
       </c>
       <c r="AA210" s="14" t="inlineStr"/>
       <c r="AB210" s="14" t="inlineStr"/>
       <c r="AC210" s="15" t="n">
-        <v>0.5073275862068966</v>
+        <v>0.5</v>
       </c>
       <c r="AD210" s="15" t="inlineStr"/>
       <c r="AE210" s="14" t="n">
-        <v>2857500.0</v>
+        <v>4.446E8</v>
       </c>
       <c r="AF210" s="14" t="inlineStr"/>
       <c r="AG210" s="14" t="inlineStr"/>
@@ -12810,14 +12804,14 @@
       <c r="N211" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000134. Biaya Angkut Sampah</t>
+            <t xml:space="preserve">000290. Honor Penyuluh Non PNS (Master)</t>
           </r>
         </is>
       </c>
       <c r="O211" s="13" t="inlineStr"/>
       <c r="P211" s="13" t="inlineStr"/>
       <c r="Q211" s="14" t="n">
-        <v>7200000.0</v>
+        <v>2.8E7</v>
       </c>
       <c r="R211" s="14" t="inlineStr"/>
       <c r="S211" s="14" t="n">
@@ -12827,23 +12821,23 @@
       <c r="U211" s="14" t="inlineStr"/>
       <c r="V211" s="14" t="inlineStr"/>
       <c r="W211" s="14" t="n">
-        <v>2424000.0</v>
+        <v>0.0</v>
       </c>
       <c r="X211" s="14" t="n">
-        <v>0.0</v>
+        <v>1.4E7</v>
       </c>
       <c r="Y211" s="14" t="inlineStr"/>
       <c r="Z211" s="14" t="n">
-        <v>2424000.0</v>
+        <v>1.4E7</v>
       </c>
       <c r="AA211" s="14" t="inlineStr"/>
       <c r="AB211" s="14" t="inlineStr"/>
       <c r="AC211" s="15" t="n">
-        <v>0.33666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="AD211" s="15" t="inlineStr"/>
       <c r="AE211" s="14" t="n">
-        <v>4776000.0</v>
+        <v>1.4E7</v>
       </c>
       <c r="AF211" s="14" t="inlineStr"/>
       <c r="AG211" s="14" t="inlineStr"/>
@@ -12858,29 +12852,23 @@
       <c r="E212" s="2" t="inlineStr"/>
       <c r="F212" s="2" t="inlineStr"/>
       <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521211</t>
-          </r>
-        </is>
-      </c>
-      <c r="I212" s="13" t="inlineStr"/>
-      <c r="J212" s="13" t="inlineStr"/>
-      <c r="K212" s="13" t="inlineStr"/>
-      <c r="L212" s="13" t="inlineStr"/>
-      <c r="M212" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Bahan</t>
-          </r>
-        </is>
-      </c>
-      <c r="N212" s="13" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr"/>
+      <c r="I212" s="2" t="inlineStr"/>
+      <c r="J212" s="2" t="inlineStr"/>
+      <c r="K212" s="2" t="inlineStr"/>
+      <c r="L212" s="2" t="inlineStr"/>
+      <c r="M212" s="2" t="inlineStr"/>
+      <c r="N212" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000291. BPJS Ketenagakerjaan</t>
+          </r>
+        </is>
+      </c>
       <c r="O212" s="13" t="inlineStr"/>
       <c r="P212" s="13" t="inlineStr"/>
       <c r="Q212" s="14" t="n">
-        <v>1.7499E7</v>
+        <v>8936000.0</v>
       </c>
       <c r="R212" s="14" t="inlineStr"/>
       <c r="S212" s="14" t="n">
@@ -12890,23 +12878,23 @@
       <c r="U212" s="14" t="inlineStr"/>
       <c r="V212" s="14" t="inlineStr"/>
       <c r="W212" s="14" t="n">
-        <v>1.280558E7</v>
+        <v>0.0</v>
       </c>
       <c r="X212" s="14" t="n">
-        <v>4279000.0</v>
+        <v>2709720.0</v>
       </c>
       <c r="Y212" s="14" t="inlineStr"/>
       <c r="Z212" s="14" t="n">
-        <v>1.708458E7</v>
+        <v>2709720.0</v>
       </c>
       <c r="AA212" s="14" t="inlineStr"/>
       <c r="AB212" s="14" t="inlineStr"/>
       <c r="AC212" s="15" t="n">
-        <v>0.9763175038573633</v>
+        <v>0.3032363473589973</v>
       </c>
       <c r="AD212" s="15" t="inlineStr"/>
       <c r="AE212" s="14" t="n">
-        <v>414420.0</v>
+        <v>6226280.0</v>
       </c>
       <c r="AF212" s="14" t="inlineStr"/>
       <c r="AG212" s="14" t="inlineStr"/>
@@ -12921,23 +12909,29 @@
       <c r="E213" s="2" t="inlineStr"/>
       <c r="F213" s="2" t="inlineStr"/>
       <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr"/>
-      <c r="I213" s="2" t="inlineStr"/>
-      <c r="J213" s="2" t="inlineStr"/>
-      <c r="K213" s="2" t="inlineStr"/>
-      <c r="L213" s="2" t="inlineStr"/>
-      <c r="M213" s="2" t="inlineStr"/>
-      <c r="N213" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000135. Jamuan Tamu/Delegasi</t>
-          </r>
-        </is>
-      </c>
+      <c r="H213" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521119</t>
+          </r>
+        </is>
+      </c>
+      <c r="I213" s="13" t="inlineStr"/>
+      <c r="J213" s="13" t="inlineStr"/>
+      <c r="K213" s="13" t="inlineStr"/>
+      <c r="L213" s="13" t="inlineStr"/>
+      <c r="M213" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N213" s="13" t="inlineStr"/>
       <c r="O213" s="13" t="inlineStr"/>
       <c r="P213" s="13" t="inlineStr"/>
       <c r="Q213" s="14" t="n">
-        <v>1.7499E7</v>
+        <v>1.0E7</v>
       </c>
       <c r="R213" s="14" t="inlineStr"/>
       <c r="S213" s="14" t="n">
@@ -12947,23 +12941,23 @@
       <c r="U213" s="14" t="inlineStr"/>
       <c r="V213" s="14" t="inlineStr"/>
       <c r="W213" s="14" t="n">
-        <v>1.280558E7</v>
+        <v>5366500.0</v>
       </c>
       <c r="X213" s="14" t="n">
-        <v>4279000.0</v>
+        <v>1484500.0</v>
       </c>
       <c r="Y213" s="14" t="inlineStr"/>
       <c r="Z213" s="14" t="n">
-        <v>1.708458E7</v>
+        <v>6851000.0</v>
       </c>
       <c r="AA213" s="14" t="inlineStr"/>
       <c r="AB213" s="14" t="inlineStr"/>
       <c r="AC213" s="15" t="n">
-        <v>0.9763175038573633</v>
+        <v>0.6851</v>
       </c>
       <c r="AD213" s="15" t="inlineStr"/>
       <c r="AE213" s="14" t="n">
-        <v>414420.0</v>
+        <v>3149000.0</v>
       </c>
       <c r="AF213" s="14" t="inlineStr"/>
       <c r="AG213" s="14" t="inlineStr"/>
@@ -12978,29 +12972,23 @@
       <c r="E214" s="2" t="inlineStr"/>
       <c r="F214" s="2" t="inlineStr"/>
       <c r="G214" s="2" t="inlineStr"/>
-      <c r="H214" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521811</t>
-          </r>
-        </is>
-      </c>
-      <c r="I214" s="13" t="inlineStr"/>
-      <c r="J214" s="13" t="inlineStr"/>
-      <c r="K214" s="13" t="inlineStr"/>
-      <c r="L214" s="13" t="inlineStr"/>
-      <c r="M214" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
-          </r>
-        </is>
-      </c>
-      <c r="N214" s="13" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr"/>
+      <c r="I214" s="2" t="inlineStr"/>
+      <c r="J214" s="2" t="inlineStr"/>
+      <c r="K214" s="2" t="inlineStr"/>
+      <c r="L214" s="2" t="inlineStr"/>
+      <c r="M214" s="2" t="inlineStr"/>
+      <c r="N214" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000133. Biaya Tol</t>
+          </r>
+        </is>
+      </c>
       <c r="O214" s="13" t="inlineStr"/>
       <c r="P214" s="13" t="inlineStr"/>
       <c r="Q214" s="14" t="n">
-        <v>3000000.0</v>
+        <v>5800000.0</v>
       </c>
       <c r="R214" s="14" t="inlineStr"/>
       <c r="S214" s="14" t="n">
@@ -13010,23 +12998,23 @@
       <c r="U214" s="14" t="inlineStr"/>
       <c r="V214" s="14" t="inlineStr"/>
       <c r="W214" s="14" t="n">
-        <v>1990000.0</v>
+        <v>2942500.0</v>
       </c>
       <c r="X214" s="14" t="n">
-        <v>0.0</v>
+        <v>1484500.0</v>
       </c>
       <c r="Y214" s="14" t="inlineStr"/>
       <c r="Z214" s="14" t="n">
-        <v>1990000.0</v>
+        <v>4427000.0</v>
       </c>
       <c r="AA214" s="14" t="inlineStr"/>
       <c r="AB214" s="14" t="inlineStr"/>
       <c r="AC214" s="15" t="n">
-        <v>0.6633333333333333</v>
+        <v>0.7632758620689655</v>
       </c>
       <c r="AD214" s="15" t="inlineStr"/>
       <c r="AE214" s="14" t="n">
-        <v>1010000.0</v>
+        <v>1373000.0</v>
       </c>
       <c r="AF214" s="14" t="inlineStr"/>
       <c r="AG214" s="14" t="inlineStr"/>
@@ -13050,14 +13038,14 @@
       <c r="N215" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000137. Bahan Komputer</t>
+            <t xml:space="preserve">000134. Biaya Angkut Sampah</t>
           </r>
         </is>
       </c>
       <c r="O215" s="13" t="inlineStr"/>
       <c r="P215" s="13" t="inlineStr"/>
       <c r="Q215" s="14" t="n">
-        <v>3000000.0</v>
+        <v>4200000.0</v>
       </c>
       <c r="R215" s="14" t="inlineStr"/>
       <c r="S215" s="14" t="n">
@@ -13067,23 +13055,23 @@
       <c r="U215" s="14" t="inlineStr"/>
       <c r="V215" s="14" t="inlineStr"/>
       <c r="W215" s="14" t="n">
-        <v>1990000.0</v>
+        <v>2424000.0</v>
       </c>
       <c r="X215" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y215" s="14" t="inlineStr"/>
       <c r="Z215" s="14" t="n">
-        <v>1990000.0</v>
+        <v>2424000.0</v>
       </c>
       <c r="AA215" s="14" t="inlineStr"/>
       <c r="AB215" s="14" t="inlineStr"/>
       <c r="AC215" s="15" t="n">
-        <v>0.6633333333333333</v>
+        <v>0.5771428571428572</v>
       </c>
       <c r="AD215" s="15" t="inlineStr"/>
       <c r="AE215" s="14" t="n">
-        <v>1010000.0</v>
+        <v>1776000.0</v>
       </c>
       <c r="AF215" s="14" t="inlineStr"/>
       <c r="AG215" s="14" t="inlineStr"/>
@@ -13101,7 +13089,7 @@
       <c r="H216" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">522191</t>
+            <t xml:space="preserve">521211</t>
           </r>
         </is>
       </c>
@@ -13112,7 +13100,7 @@
       <c r="M216" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Belanja Jasa Lainnya</t>
+            <t xml:space="preserve">Belanja Bahan</t>
           </r>
         </is>
       </c>
@@ -13120,7 +13108,7 @@
       <c r="O216" s="13" t="inlineStr"/>
       <c r="P216" s="13" t="inlineStr"/>
       <c r="Q216" s="14" t="n">
-        <v>3.116438E9</v>
+        <v>3.2604E7</v>
       </c>
       <c r="R216" s="14" t="inlineStr"/>
       <c r="S216" s="14" t="n">
@@ -13130,30 +13118,30 @@
       <c r="U216" s="14" t="inlineStr"/>
       <c r="V216" s="14" t="inlineStr"/>
       <c r="W216" s="14" t="n">
-        <v>2.692189616E9</v>
+        <v>1.708458E7</v>
       </c>
       <c r="X216" s="14" t="n">
-        <v>6.9149936E7</v>
+        <v>8738180.0</v>
       </c>
       <c r="Y216" s="14" t="inlineStr"/>
       <c r="Z216" s="14" t="n">
-        <v>2.761339552E9</v>
+        <v>2.582276E7</v>
       </c>
       <c r="AA216" s="14" t="inlineStr"/>
       <c r="AB216" s="14" t="inlineStr"/>
       <c r="AC216" s="15" t="n">
-        <v>0.8860563091580836</v>
+        <v>0.7920120230646547</v>
       </c>
       <c r="AD216" s="15" t="inlineStr"/>
       <c r="AE216" s="14" t="n">
-        <v>3.55098448E8</v>
+        <v>6781240.0</v>
       </c>
       <c r="AF216" s="14" t="inlineStr"/>
       <c r="AG216" s="14" t="inlineStr"/>
       <c r="AH216" s="14" t="inlineStr"/>
       <c r="AI216" s="14" t="inlineStr"/>
     </row>
-    <row r="217" customHeight="1" ht="18">
+    <row r="217" customHeight="1" ht="15">
       <c r="A217" s="2" t="inlineStr"/>
       <c r="B217" s="2" t="inlineStr"/>
       <c r="C217" s="2" t="inlineStr"/>
@@ -13170,14 +13158,14 @@
       <c r="N217" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000139. Biaya Outsourcing Perorangan Tenaga Kebersihan (9 ORG)</t>
+            <t xml:space="preserve">000135. Jamuan Tamu/Delegasi</t>
           </r>
         </is>
       </c>
       <c r="O217" s="13" t="inlineStr"/>
       <c r="P217" s="13" t="inlineStr"/>
       <c r="Q217" s="14" t="n">
-        <v>5.4E8</v>
+        <v>3.2604E7</v>
       </c>
       <c r="R217" s="14" t="inlineStr"/>
       <c r="S217" s="14" t="n">
@@ -13187,23 +13175,23 @@
       <c r="U217" s="14" t="inlineStr"/>
       <c r="V217" s="14" t="inlineStr"/>
       <c r="W217" s="14" t="n">
-        <v>2.85881376E8</v>
+        <v>1.708458E7</v>
       </c>
       <c r="X217" s="14" t="n">
-        <v>4.1321696E7</v>
+        <v>8738180.0</v>
       </c>
       <c r="Y217" s="14" t="inlineStr"/>
       <c r="Z217" s="14" t="n">
-        <v>3.27203072E8</v>
+        <v>2.582276E7</v>
       </c>
       <c r="AA217" s="14" t="inlineStr"/>
       <c r="AB217" s="14" t="inlineStr"/>
       <c r="AC217" s="15" t="n">
-        <v>0.6059316148148148</v>
+        <v>0.7920120230646547</v>
       </c>
       <c r="AD217" s="15" t="inlineStr"/>
       <c r="AE217" s="14" t="n">
-        <v>2.12796928E8</v>
+        <v>6781240.0</v>
       </c>
       <c r="AF217" s="14" t="inlineStr"/>
       <c r="AG217" s="14" t="inlineStr"/>
@@ -13218,23 +13206,29 @@
       <c r="E218" s="2" t="inlineStr"/>
       <c r="F218" s="2" t="inlineStr"/>
       <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="2" t="inlineStr"/>
-      <c r="I218" s="2" t="inlineStr"/>
-      <c r="J218" s="2" t="inlineStr"/>
-      <c r="K218" s="2" t="inlineStr"/>
-      <c r="L218" s="2" t="inlineStr"/>
-      <c r="M218" s="2" t="inlineStr"/>
-      <c r="N218" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000140. Biaya Outsourcing Perorangan Pengemudi (2 ORG)</t>
-          </r>
-        </is>
-      </c>
+      <c r="H218" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521811</t>
+          </r>
+        </is>
+      </c>
+      <c r="I218" s="13" t="inlineStr"/>
+      <c r="J218" s="13" t="inlineStr"/>
+      <c r="K218" s="13" t="inlineStr"/>
+      <c r="L218" s="13" t="inlineStr"/>
+      <c r="M218" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
+          </r>
+        </is>
+      </c>
+      <c r="N218" s="13" t="inlineStr"/>
       <c r="O218" s="13" t="inlineStr"/>
       <c r="P218" s="13" t="inlineStr"/>
       <c r="Q218" s="14" t="n">
-        <v>1.226E8</v>
+        <v>6000000.0</v>
       </c>
       <c r="R218" s="14" t="inlineStr"/>
       <c r="S218" s="14" t="n">
@@ -13244,30 +13238,30 @@
       <c r="U218" s="14" t="inlineStr"/>
       <c r="V218" s="14" t="inlineStr"/>
       <c r="W218" s="14" t="n">
-        <v>6.5444768E7</v>
+        <v>1990000.0</v>
       </c>
       <c r="X218" s="14" t="n">
-        <v>9468528.0</v>
+        <v>957800.0</v>
       </c>
       <c r="Y218" s="14" t="inlineStr"/>
       <c r="Z218" s="14" t="n">
-        <v>7.4913296E7</v>
+        <v>2947800.0</v>
       </c>
       <c r="AA218" s="14" t="inlineStr"/>
       <c r="AB218" s="14" t="inlineStr"/>
       <c r="AC218" s="15" t="n">
-        <v>0.6110383034257749</v>
+        <v>0.4913</v>
       </c>
       <c r="AD218" s="15" t="inlineStr"/>
       <c r="AE218" s="14" t="n">
-        <v>4.7686704E7</v>
+        <v>3052200.0</v>
       </c>
       <c r="AF218" s="14" t="inlineStr"/>
       <c r="AG218" s="14" t="inlineStr"/>
       <c r="AH218" s="14" t="inlineStr"/>
       <c r="AI218" s="14" t="inlineStr"/>
     </row>
-    <row r="219" customHeight="1" ht="18">
+    <row r="219" customHeight="1" ht="15">
       <c r="A219" s="2" t="inlineStr"/>
       <c r="B219" s="2" t="inlineStr"/>
       <c r="C219" s="2" t="inlineStr"/>
@@ -13284,14 +13278,14 @@
       <c r="N219" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000141. Biaya Outsourcing Perorangan Petugas Kolam (3 ORG)</t>
+            <t xml:space="preserve">000137. Bahan Komputer</t>
           </r>
         </is>
       </c>
       <c r="O219" s="13" t="inlineStr"/>
       <c r="P219" s="13" t="inlineStr"/>
       <c r="Q219" s="14" t="n">
-        <v>1.8E8</v>
+        <v>4000000.0</v>
       </c>
       <c r="R219" s="14" t="inlineStr"/>
       <c r="S219" s="14" t="n">
@@ -13301,30 +13295,30 @@
       <c r="U219" s="14" t="inlineStr"/>
       <c r="V219" s="14" t="inlineStr"/>
       <c r="W219" s="14" t="n">
-        <v>9.5029104E7</v>
+        <v>1990000.0</v>
       </c>
       <c r="X219" s="14" t="n">
-        <v>1.3729784E7</v>
+        <v>957800.0</v>
       </c>
       <c r="Y219" s="14" t="inlineStr"/>
       <c r="Z219" s="14" t="n">
-        <v>1.08758888E8</v>
+        <v>2947800.0</v>
       </c>
       <c r="AA219" s="14" t="inlineStr"/>
       <c r="AB219" s="14" t="inlineStr"/>
       <c r="AC219" s="15" t="n">
-        <v>0.6042160444444444</v>
+        <v>0.73695</v>
       </c>
       <c r="AD219" s="15" t="inlineStr"/>
       <c r="AE219" s="14" t="n">
-        <v>7.1241112E7</v>
+        <v>1052200.0</v>
       </c>
       <c r="AF219" s="14" t="inlineStr"/>
       <c r="AG219" s="14" t="inlineStr"/>
       <c r="AH219" s="14" t="inlineStr"/>
       <c r="AI219" s="14" t="inlineStr"/>
     </row>
-    <row r="220" customHeight="1" ht="18">
+    <row r="220" customHeight="1" ht="15">
       <c r="A220" s="2" t="inlineStr"/>
       <c r="B220" s="2" t="inlineStr"/>
       <c r="C220" s="2" t="inlineStr"/>
@@ -13341,14 +13335,14 @@
       <c r="N220" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000142. Biaya Outsourcing Perorangan Petugas Layanan Informasi (1 ORG)</t>
+            <t xml:space="preserve">000292. ATK</t>
           </r>
         </is>
       </c>
       <c r="O220" s="13" t="inlineStr"/>
       <c r="P220" s="13" t="inlineStr"/>
       <c r="Q220" s="14" t="n">
-        <v>6.0E7</v>
+        <v>2000000.0</v>
       </c>
       <c r="R220" s="14" t="inlineStr"/>
       <c r="S220" s="14" t="n">
@@ -13358,23 +13352,23 @@
       <c r="U220" s="14" t="inlineStr"/>
       <c r="V220" s="14" t="inlineStr"/>
       <c r="W220" s="14" t="n">
-        <v>3.1996368E7</v>
+        <v>0.0</v>
       </c>
       <c r="X220" s="14" t="n">
-        <v>4629928.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y220" s="14" t="inlineStr"/>
       <c r="Z220" s="14" t="n">
-        <v>3.6626296E7</v>
+        <v>0.0</v>
       </c>
       <c r="AA220" s="14" t="inlineStr"/>
       <c r="AB220" s="14" t="inlineStr"/>
       <c r="AC220" s="15" t="n">
-        <v>0.6104382666666667</v>
+        <v>0.0</v>
       </c>
       <c r="AD220" s="15" t="inlineStr"/>
       <c r="AE220" s="14" t="n">
-        <v>2.3373704E7</v>
+        <v>2000000.0</v>
       </c>
       <c r="AF220" s="14" t="inlineStr"/>
       <c r="AG220" s="14" t="inlineStr"/>
@@ -13389,23 +13383,29 @@
       <c r="E221" s="2" t="inlineStr"/>
       <c r="F221" s="2" t="inlineStr"/>
       <c r="G221" s="2" t="inlineStr"/>
-      <c r="H221" s="2" t="inlineStr"/>
-      <c r="I221" s="2" t="inlineStr"/>
-      <c r="J221" s="2" t="inlineStr"/>
-      <c r="K221" s="2" t="inlineStr"/>
-      <c r="L221" s="2" t="inlineStr"/>
-      <c r="M221" s="2" t="inlineStr"/>
-      <c r="N221" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000144. Biaya Outsourcing Satpam (24 ORG)</t>
-          </r>
-        </is>
-      </c>
+      <c r="H221" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522191</t>
+          </r>
+        </is>
+      </c>
+      <c r="I221" s="13" t="inlineStr"/>
+      <c r="J221" s="13" t="inlineStr"/>
+      <c r="K221" s="13" t="inlineStr"/>
+      <c r="L221" s="13" t="inlineStr"/>
+      <c r="M221" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Jasa Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N221" s="13" t="inlineStr"/>
       <c r="O221" s="13" t="inlineStr"/>
       <c r="P221" s="13" t="inlineStr"/>
       <c r="Q221" s="14" t="n">
-        <v>2.213838E9</v>
+        <v>3.116438E9</v>
       </c>
       <c r="R221" s="14" t="inlineStr"/>
       <c r="S221" s="14" t="n">
@@ -13415,60 +13415,54 @@
       <c r="U221" s="14" t="inlineStr"/>
       <c r="V221" s="14" t="inlineStr"/>
       <c r="W221" s="14" t="n">
-        <v>2.213838E9</v>
+        <v>2.761339552E9</v>
       </c>
       <c r="X221" s="14" t="n">
-        <v>0.0</v>
+        <v>6.9149936E7</v>
       </c>
       <c r="Y221" s="14" t="inlineStr"/>
       <c r="Z221" s="14" t="n">
-        <v>2.213838E9</v>
+        <v>2.830489488E9</v>
       </c>
       <c r="AA221" s="14" t="inlineStr"/>
       <c r="AB221" s="14" t="inlineStr"/>
       <c r="AC221" s="15" t="n">
-        <v>1.0</v>
+        <v>0.908245082366471</v>
       </c>
       <c r="AD221" s="15" t="inlineStr"/>
       <c r="AE221" s="14" t="n">
-        <v>0.0</v>
+        <v>2.85948512E8</v>
       </c>
       <c r="AF221" s="14" t="inlineStr"/>
       <c r="AG221" s="14" t="inlineStr"/>
       <c r="AH221" s="14" t="inlineStr"/>
       <c r="AI221" s="14" t="inlineStr"/>
     </row>
-    <row r="222" customHeight="1" ht="15">
+    <row r="222" customHeight="1" ht="18">
       <c r="A222" s="2" t="inlineStr"/>
       <c r="B222" s="2" t="inlineStr"/>
       <c r="C222" s="2" t="inlineStr"/>
       <c r="D222" s="2" t="inlineStr"/>
       <c r="E222" s="2" t="inlineStr"/>
-      <c r="F222" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">002.DB</t>
-          </r>
-        </is>
-      </c>
-      <c r="G222" s="13" t="inlineStr"/>
-      <c r="H222" s="13" t="inlineStr"/>
-      <c r="I222" s="13" t="inlineStr"/>
-      <c r="J222" s="13" t="inlineStr"/>
-      <c r="K222" s="13" t="inlineStr"/>
-      <c r="L222" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Langganan Daya dan Jasa</t>
-          </r>
-        </is>
-      </c>
-      <c r="M222" s="13" t="inlineStr"/>
-      <c r="N222" s="13" t="inlineStr"/>
+      <c r="F222" s="2" t="inlineStr"/>
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr"/>
+      <c r="I222" s="2" t="inlineStr"/>
+      <c r="J222" s="2" t="inlineStr"/>
+      <c r="K222" s="2" t="inlineStr"/>
+      <c r="L222" s="2" t="inlineStr"/>
+      <c r="M222" s="2" t="inlineStr"/>
+      <c r="N222" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000139. Biaya Outsourcing Perorangan Tenaga Kebersihan (9 ORG)</t>
+          </r>
+        </is>
+      </c>
       <c r="O222" s="13" t="inlineStr"/>
       <c r="P222" s="13" t="inlineStr"/>
       <c r="Q222" s="14" t="n">
-        <v>9.308E8</v>
+        <v>5.4E8</v>
       </c>
       <c r="R222" s="14" t="inlineStr"/>
       <c r="S222" s="14" t="n">
@@ -13478,23 +13472,23 @@
       <c r="U222" s="14" t="inlineStr"/>
       <c r="V222" s="14" t="inlineStr"/>
       <c r="W222" s="14" t="n">
-        <v>4.32620013E8</v>
+        <v>3.27203072E8</v>
       </c>
       <c r="X222" s="14" t="n">
-        <v>5.2453711E7</v>
+        <v>4.1321696E7</v>
       </c>
       <c r="Y222" s="14" t="inlineStr"/>
       <c r="Z222" s="14" t="n">
-        <v>4.85073724E8</v>
+        <v>3.68524768E8</v>
       </c>
       <c r="AA222" s="14" t="inlineStr"/>
       <c r="AB222" s="14" t="inlineStr"/>
       <c r="AC222" s="15" t="n">
-        <v>0.5211363601203266</v>
+        <v>0.6824532740740741</v>
       </c>
       <c r="AD222" s="15" t="inlineStr"/>
       <c r="AE222" s="14" t="n">
-        <v>4.45726276E8</v>
+        <v>1.71475232E8</v>
       </c>
       <c r="AF222" s="14" t="inlineStr"/>
       <c r="AG222" s="14" t="inlineStr"/>
@@ -13509,29 +13503,23 @@
       <c r="E223" s="2" t="inlineStr"/>
       <c r="F223" s="2" t="inlineStr"/>
       <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522111</t>
-          </r>
-        </is>
-      </c>
-      <c r="I223" s="13" t="inlineStr"/>
-      <c r="J223" s="13" t="inlineStr"/>
-      <c r="K223" s="13" t="inlineStr"/>
-      <c r="L223" s="13" t="inlineStr"/>
-      <c r="M223" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Listrik</t>
-          </r>
-        </is>
-      </c>
-      <c r="N223" s="13" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr"/>
+      <c r="I223" s="2" t="inlineStr"/>
+      <c r="J223" s="2" t="inlineStr"/>
+      <c r="K223" s="2" t="inlineStr"/>
+      <c r="L223" s="2" t="inlineStr"/>
+      <c r="M223" s="2" t="inlineStr"/>
+      <c r="N223" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000140. Biaya Outsourcing Perorangan Pengemudi (2 ORG)</t>
+          </r>
+        </is>
+      </c>
       <c r="O223" s="13" t="inlineStr"/>
       <c r="P223" s="13" t="inlineStr"/>
       <c r="Q223" s="14" t="n">
-        <v>7.32E8</v>
+        <v>1.226E8</v>
       </c>
       <c r="R223" s="14" t="inlineStr"/>
       <c r="S223" s="14" t="n">
@@ -13541,30 +13529,30 @@
       <c r="U223" s="14" t="inlineStr"/>
       <c r="V223" s="14" t="inlineStr"/>
       <c r="W223" s="14" t="n">
-        <v>3.10883859E8</v>
+        <v>7.4913296E7</v>
       </c>
       <c r="X223" s="14" t="n">
-        <v>4.1758847E7</v>
+        <v>9468528.0</v>
       </c>
       <c r="Y223" s="14" t="inlineStr"/>
       <c r="Z223" s="14" t="n">
-        <v>3.52642706E8</v>
+        <v>8.4381824E7</v>
       </c>
       <c r="AA223" s="14" t="inlineStr"/>
       <c r="AB223" s="14" t="inlineStr"/>
       <c r="AC223" s="15" t="n">
-        <v>0.4817523306010929</v>
+        <v>0.6882693637846656</v>
       </c>
       <c r="AD223" s="15" t="inlineStr"/>
       <c r="AE223" s="14" t="n">
-        <v>3.79357294E8</v>
+        <v>3.8218176E7</v>
       </c>
       <c r="AF223" s="14" t="inlineStr"/>
       <c r="AG223" s="14" t="inlineStr"/>
       <c r="AH223" s="14" t="inlineStr"/>
       <c r="AI223" s="14" t="inlineStr"/>
     </row>
-    <row r="224" customHeight="1" ht="15">
+    <row r="224" customHeight="1" ht="18">
       <c r="A224" s="2" t="inlineStr"/>
       <c r="B224" s="2" t="inlineStr"/>
       <c r="C224" s="2" t="inlineStr"/>
@@ -13581,14 +13569,14 @@
       <c r="N224" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000145. Langganan Listrik</t>
+            <t xml:space="preserve">000141. Biaya Outsourcing Perorangan Petugas Kolam (3 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O224" s="13" t="inlineStr"/>
       <c r="P224" s="13" t="inlineStr"/>
       <c r="Q224" s="14" t="n">
-        <v>7.32E8</v>
+        <v>1.8E8</v>
       </c>
       <c r="R224" s="14" t="inlineStr"/>
       <c r="S224" s="14" t="n">
@@ -13598,30 +13586,30 @@
       <c r="U224" s="14" t="inlineStr"/>
       <c r="V224" s="14" t="inlineStr"/>
       <c r="W224" s="14" t="n">
-        <v>3.10883859E8</v>
+        <v>1.08758888E8</v>
       </c>
       <c r="X224" s="14" t="n">
-        <v>4.1758847E7</v>
+        <v>1.3729784E7</v>
       </c>
       <c r="Y224" s="14" t="inlineStr"/>
       <c r="Z224" s="14" t="n">
-        <v>3.52642706E8</v>
+        <v>1.22488672E8</v>
       </c>
       <c r="AA224" s="14" t="inlineStr"/>
       <c r="AB224" s="14" t="inlineStr"/>
       <c r="AC224" s="15" t="n">
-        <v>0.4817523306010929</v>
+        <v>0.6804926222222222</v>
       </c>
       <c r="AD224" s="15" t="inlineStr"/>
       <c r="AE224" s="14" t="n">
-        <v>3.79357294E8</v>
+        <v>5.7511328E7</v>
       </c>
       <c r="AF224" s="14" t="inlineStr"/>
       <c r="AG224" s="14" t="inlineStr"/>
       <c r="AH224" s="14" t="inlineStr"/>
       <c r="AI224" s="14" t="inlineStr"/>
     </row>
-    <row r="225" customHeight="1" ht="15">
+    <row r="225" customHeight="1" ht="18">
       <c r="A225" s="2" t="inlineStr"/>
       <c r="B225" s="2" t="inlineStr"/>
       <c r="C225" s="2" t="inlineStr"/>
@@ -13629,29 +13617,23 @@
       <c r="E225" s="2" t="inlineStr"/>
       <c r="F225" s="2" t="inlineStr"/>
       <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522112</t>
-          </r>
-        </is>
-      </c>
-      <c r="I225" s="13" t="inlineStr"/>
-      <c r="J225" s="13" t="inlineStr"/>
-      <c r="K225" s="13" t="inlineStr"/>
-      <c r="L225" s="13" t="inlineStr"/>
-      <c r="M225" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Telepon</t>
-          </r>
-        </is>
-      </c>
-      <c r="N225" s="13" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr"/>
+      <c r="I225" s="2" t="inlineStr"/>
+      <c r="J225" s="2" t="inlineStr"/>
+      <c r="K225" s="2" t="inlineStr"/>
+      <c r="L225" s="2" t="inlineStr"/>
+      <c r="M225" s="2" t="inlineStr"/>
+      <c r="N225" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000142. Biaya Outsourcing Perorangan Petugas Layanan Informasi (1 ORG)</t>
+          </r>
+        </is>
+      </c>
       <c r="O225" s="13" t="inlineStr"/>
       <c r="P225" s="13" t="inlineStr"/>
       <c r="Q225" s="14" t="n">
-        <v>4800000.0</v>
+        <v>6.0E7</v>
       </c>
       <c r="R225" s="14" t="inlineStr"/>
       <c r="S225" s="14" t="n">
@@ -13661,23 +13643,23 @@
       <c r="U225" s="14" t="inlineStr"/>
       <c r="V225" s="14" t="inlineStr"/>
       <c r="W225" s="14" t="n">
-        <v>4425348.0</v>
+        <v>3.6626296E7</v>
       </c>
       <c r="X225" s="14" t="n">
-        <v>263514.0</v>
+        <v>4629928.0</v>
       </c>
       <c r="Y225" s="14" t="inlineStr"/>
       <c r="Z225" s="14" t="n">
-        <v>4688862.0</v>
+        <v>4.1256224E7</v>
       </c>
       <c r="AA225" s="14" t="inlineStr"/>
       <c r="AB225" s="14" t="inlineStr"/>
       <c r="AC225" s="15" t="n">
-        <v>0.97684625</v>
+        <v>0.6876037333333334</v>
       </c>
       <c r="AD225" s="15" t="inlineStr"/>
       <c r="AE225" s="14" t="n">
-        <v>111138.0</v>
+        <v>1.8743776E7</v>
       </c>
       <c r="AF225" s="14" t="inlineStr"/>
       <c r="AG225" s="14" t="inlineStr"/>
@@ -13701,14 +13683,14 @@
       <c r="N226" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000146. Langganan Telepon</t>
+            <t xml:space="preserve">000144. Biaya Outsourcing Satpam (24 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O226" s="13" t="inlineStr"/>
       <c r="P226" s="13" t="inlineStr"/>
       <c r="Q226" s="14" t="n">
-        <v>4800000.0</v>
+        <v>2.213838E9</v>
       </c>
       <c r="R226" s="14" t="inlineStr"/>
       <c r="S226" s="14" t="n">
@@ -13718,23 +13700,23 @@
       <c r="U226" s="14" t="inlineStr"/>
       <c r="V226" s="14" t="inlineStr"/>
       <c r="W226" s="14" t="n">
-        <v>4425348.0</v>
+        <v>2.213838E9</v>
       </c>
       <c r="X226" s="14" t="n">
-        <v>263514.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y226" s="14" t="inlineStr"/>
       <c r="Z226" s="14" t="n">
-        <v>4688862.0</v>
+        <v>2.213838E9</v>
       </c>
       <c r="AA226" s="14" t="inlineStr"/>
       <c r="AB226" s="14" t="inlineStr"/>
       <c r="AC226" s="15" t="n">
-        <v>0.97684625</v>
+        <v>1.0</v>
       </c>
       <c r="AD226" s="15" t="inlineStr"/>
       <c r="AE226" s="14" t="n">
-        <v>111138.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF226" s="14" t="inlineStr"/>
       <c r="AG226" s="14" t="inlineStr"/>
@@ -13747,31 +13729,31 @@
       <c r="C227" s="2" t="inlineStr"/>
       <c r="D227" s="2" t="inlineStr"/>
       <c r="E227" s="2" t="inlineStr"/>
-      <c r="F227" s="2" t="inlineStr"/>
-      <c r="G227" s="2" t="inlineStr"/>
-      <c r="H227" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522113</t>
-          </r>
-        </is>
-      </c>
+      <c r="F227" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">002.DB</t>
+          </r>
+        </is>
+      </c>
+      <c r="G227" s="13" t="inlineStr"/>
+      <c r="H227" s="13" t="inlineStr"/>
       <c r="I227" s="13" t="inlineStr"/>
       <c r="J227" s="13" t="inlineStr"/>
       <c r="K227" s="13" t="inlineStr"/>
-      <c r="L227" s="13" t="inlineStr"/>
-      <c r="M227" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Air</t>
-          </r>
-        </is>
-      </c>
+      <c r="L227" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Langganan Daya dan Jasa</t>
+          </r>
+        </is>
+      </c>
+      <c r="M227" s="13" t="inlineStr"/>
       <c r="N227" s="13" t="inlineStr"/>
       <c r="O227" s="13" t="inlineStr"/>
       <c r="P227" s="13" t="inlineStr"/>
       <c r="Q227" s="14" t="n">
-        <v>3.96E7</v>
+        <v>8.72E8</v>
       </c>
       <c r="R227" s="14" t="inlineStr"/>
       <c r="S227" s="14" t="n">
@@ -13781,23 +13763,23 @@
       <c r="U227" s="14" t="inlineStr"/>
       <c r="V227" s="14" t="inlineStr"/>
       <c r="W227" s="14" t="n">
-        <v>2.48451E7</v>
+        <v>4.85073724E8</v>
       </c>
       <c r="X227" s="14" t="n">
-        <v>647800.0</v>
+        <v>5.0720588E7</v>
       </c>
       <c r="Y227" s="14" t="inlineStr"/>
       <c r="Z227" s="14" t="n">
-        <v>2.54929E7</v>
+        <v>5.35794312E8</v>
       </c>
       <c r="AA227" s="14" t="inlineStr"/>
       <c r="AB227" s="14" t="inlineStr"/>
       <c r="AC227" s="15" t="n">
-        <v>0.6437601010101011</v>
+        <v>0.6144430183486238</v>
       </c>
       <c r="AD227" s="15" t="inlineStr"/>
       <c r="AE227" s="14" t="n">
-        <v>1.41071E7</v>
+        <v>3.36205688E8</v>
       </c>
       <c r="AF227" s="14" t="inlineStr"/>
       <c r="AG227" s="14" t="inlineStr"/>
@@ -13855,23 +13837,29 @@
       <c r="E229" s="2" t="inlineStr"/>
       <c r="F229" s="2" t="inlineStr"/>
       <c r="G229" s="2" t="inlineStr"/>
-      <c r="H229" s="2" t="inlineStr"/>
-      <c r="I229" s="2" t="inlineStr"/>
-      <c r="J229" s="2" t="inlineStr"/>
-      <c r="K229" s="2" t="inlineStr"/>
-      <c r="L229" s="2" t="inlineStr"/>
-      <c r="M229" s="2" t="inlineStr"/>
-      <c r="N229" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000147. Langganan Air (PAM)</t>
-          </r>
-        </is>
-      </c>
+      <c r="H229" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522111</t>
+          </r>
+        </is>
+      </c>
+      <c r="I229" s="13" t="inlineStr"/>
+      <c r="J229" s="13" t="inlineStr"/>
+      <c r="K229" s="13" t="inlineStr"/>
+      <c r="L229" s="13" t="inlineStr"/>
+      <c r="M229" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Listrik</t>
+          </r>
+        </is>
+      </c>
+      <c r="N229" s="13" t="inlineStr"/>
       <c r="O229" s="13" t="inlineStr"/>
       <c r="P229" s="13" t="inlineStr"/>
       <c r="Q229" s="14" t="n">
-        <v>3.96E7</v>
+        <v>6.72E8</v>
       </c>
       <c r="R229" s="14" t="inlineStr"/>
       <c r="S229" s="14" t="n">
@@ -13881,23 +13869,23 @@
       <c r="U229" s="14" t="inlineStr"/>
       <c r="V229" s="14" t="inlineStr"/>
       <c r="W229" s="14" t="n">
-        <v>2.48451E7</v>
+        <v>3.52642706E8</v>
       </c>
       <c r="X229" s="14" t="n">
-        <v>647800.0</v>
+        <v>3.8612524E7</v>
       </c>
       <c r="Y229" s="14" t="inlineStr"/>
       <c r="Z229" s="14" t="n">
-        <v>2.54929E7</v>
+        <v>3.9125523E8</v>
       </c>
       <c r="AA229" s="14" t="inlineStr"/>
       <c r="AB229" s="14" t="inlineStr"/>
       <c r="AC229" s="15" t="n">
-        <v>0.6437601010101011</v>
+        <v>0.5822250446428572</v>
       </c>
       <c r="AD229" s="15" t="inlineStr"/>
       <c r="AE229" s="14" t="n">
-        <v>1.41071E7</v>
+        <v>2.8074477E8</v>
       </c>
       <c r="AF229" s="14" t="inlineStr"/>
       <c r="AG229" s="14" t="inlineStr"/>
@@ -13912,29 +13900,23 @@
       <c r="E230" s="2" t="inlineStr"/>
       <c r="F230" s="2" t="inlineStr"/>
       <c r="G230" s="2" t="inlineStr"/>
-      <c r="H230" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522119</t>
-          </r>
-        </is>
-      </c>
-      <c r="I230" s="13" t="inlineStr"/>
-      <c r="J230" s="13" t="inlineStr"/>
-      <c r="K230" s="13" t="inlineStr"/>
-      <c r="L230" s="13" t="inlineStr"/>
-      <c r="M230" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Daya dan Jasa Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N230" s="13" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr"/>
+      <c r="I230" s="2" t="inlineStr"/>
+      <c r="J230" s="2" t="inlineStr"/>
+      <c r="K230" s="2" t="inlineStr"/>
+      <c r="L230" s="2" t="inlineStr"/>
+      <c r="M230" s="2" t="inlineStr"/>
+      <c r="N230" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000145. Langganan Listrik</t>
+          </r>
+        </is>
+      </c>
       <c r="O230" s="13" t="inlineStr"/>
       <c r="P230" s="13" t="inlineStr"/>
       <c r="Q230" s="14" t="n">
-        <v>1.544E8</v>
+        <v>6.72E8</v>
       </c>
       <c r="R230" s="14" t="inlineStr"/>
       <c r="S230" s="14" t="n">
@@ -13944,23 +13926,23 @@
       <c r="U230" s="14" t="inlineStr"/>
       <c r="V230" s="14" t="inlineStr"/>
       <c r="W230" s="14" t="n">
-        <v>9.2465706E7</v>
+        <v>3.52642706E8</v>
       </c>
       <c r="X230" s="14" t="n">
-        <v>9783550.0</v>
+        <v>3.8612524E7</v>
       </c>
       <c r="Y230" s="14" t="inlineStr"/>
       <c r="Z230" s="14" t="n">
-        <v>1.02249256E8</v>
+        <v>3.9125523E8</v>
       </c>
       <c r="AA230" s="14" t="inlineStr"/>
       <c r="AB230" s="14" t="inlineStr"/>
       <c r="AC230" s="15" t="n">
-        <v>0.6622361139896373</v>
+        <v>0.5822250446428572</v>
       </c>
       <c r="AD230" s="15" t="inlineStr"/>
       <c r="AE230" s="14" t="n">
-        <v>5.2150744E7</v>
+        <v>2.8074477E8</v>
       </c>
       <c r="AF230" s="14" t="inlineStr"/>
       <c r="AG230" s="14" t="inlineStr"/>
@@ -13975,23 +13957,29 @@
       <c r="E231" s="2" t="inlineStr"/>
       <c r="F231" s="2" t="inlineStr"/>
       <c r="G231" s="2" t="inlineStr"/>
-      <c r="H231" s="2" t="inlineStr"/>
-      <c r="I231" s="2" t="inlineStr"/>
-      <c r="J231" s="2" t="inlineStr"/>
-      <c r="K231" s="2" t="inlineStr"/>
-      <c r="L231" s="2" t="inlineStr"/>
-      <c r="M231" s="2" t="inlineStr"/>
-      <c r="N231" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000148. Langganan Internet</t>
-          </r>
-        </is>
-      </c>
+      <c r="H231" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522112</t>
+          </r>
+        </is>
+      </c>
+      <c r="I231" s="13" t="inlineStr"/>
+      <c r="J231" s="13" t="inlineStr"/>
+      <c r="K231" s="13" t="inlineStr"/>
+      <c r="L231" s="13" t="inlineStr"/>
+      <c r="M231" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Telepon</t>
+          </r>
+        </is>
+      </c>
+      <c r="N231" s="13" t="inlineStr"/>
       <c r="O231" s="13" t="inlineStr"/>
       <c r="P231" s="13" t="inlineStr"/>
       <c r="Q231" s="14" t="n">
-        <v>1.269E8</v>
+        <v>6000000.0</v>
       </c>
       <c r="R231" s="14" t="inlineStr"/>
       <c r="S231" s="14" t="n">
@@ -14001,23 +13989,23 @@
       <c r="U231" s="14" t="inlineStr"/>
       <c r="V231" s="14" t="inlineStr"/>
       <c r="W231" s="14" t="n">
-        <v>6.58569E7</v>
+        <v>4688862.0</v>
       </c>
       <c r="X231" s="14" t="n">
-        <v>9250750.0</v>
+        <v>263514.0</v>
       </c>
       <c r="Y231" s="14" t="inlineStr"/>
       <c r="Z231" s="14" t="n">
-        <v>7.510765E7</v>
+        <v>4952376.0</v>
       </c>
       <c r="AA231" s="14" t="inlineStr"/>
       <c r="AB231" s="14" t="inlineStr"/>
       <c r="AC231" s="15" t="n">
-        <v>0.5918648542159181</v>
+        <v>0.825396</v>
       </c>
       <c r="AD231" s="15" t="inlineStr"/>
       <c r="AE231" s="14" t="n">
-        <v>5.179235E7</v>
+        <v>1047624.0</v>
       </c>
       <c r="AF231" s="14" t="inlineStr"/>
       <c r="AG231" s="14" t="inlineStr"/>
@@ -14041,14 +14029,14 @@
       <c r="N232" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000240. Langganan aplikasi perkantoran</t>
+            <t xml:space="preserve">000146. Langganan Telepon</t>
           </r>
         </is>
       </c>
       <c r="O232" s="13" t="inlineStr"/>
       <c r="P232" s="13" t="inlineStr"/>
       <c r="Q232" s="14" t="n">
-        <v>2.75E7</v>
+        <v>6000000.0</v>
       </c>
       <c r="R232" s="14" t="inlineStr"/>
       <c r="S232" s="14" t="n">
@@ -14058,23 +14046,23 @@
       <c r="U232" s="14" t="inlineStr"/>
       <c r="V232" s="14" t="inlineStr"/>
       <c r="W232" s="14" t="n">
-        <v>2.6608806E7</v>
+        <v>4688862.0</v>
       </c>
       <c r="X232" s="14" t="n">
-        <v>532800.0</v>
+        <v>263514.0</v>
       </c>
       <c r="Y232" s="14" t="inlineStr"/>
       <c r="Z232" s="14" t="n">
-        <v>2.7141606E7</v>
+        <v>4952376.0</v>
       </c>
       <c r="AA232" s="14" t="inlineStr"/>
       <c r="AB232" s="14" t="inlineStr"/>
       <c r="AC232" s="15" t="n">
-        <v>0.9869674909090909</v>
+        <v>0.825396</v>
       </c>
       <c r="AD232" s="15" t="inlineStr"/>
       <c r="AE232" s="14" t="n">
-        <v>358394.0</v>
+        <v>1047624.0</v>
       </c>
       <c r="AF232" s="14" t="inlineStr"/>
       <c r="AG232" s="14" t="inlineStr"/>
@@ -14087,31 +14075,31 @@
       <c r="C233" s="2" t="inlineStr"/>
       <c r="D233" s="2" t="inlineStr"/>
       <c r="E233" s="2" t="inlineStr"/>
-      <c r="F233" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">002.DC</t>
-          </r>
-        </is>
-      </c>
-      <c r="G233" s="13" t="inlineStr"/>
-      <c r="H233" s="13" t="inlineStr"/>
+      <c r="F233" s="2" t="inlineStr"/>
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522113</t>
+          </r>
+        </is>
+      </c>
       <c r="I233" s="13" t="inlineStr"/>
       <c r="J233" s="13" t="inlineStr"/>
       <c r="K233" s="13" t="inlineStr"/>
-      <c r="L233" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pemeliharaan Kantor</t>
-          </r>
-        </is>
-      </c>
-      <c r="M233" s="13" t="inlineStr"/>
+      <c r="L233" s="13" t="inlineStr"/>
+      <c r="M233" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Air</t>
+          </r>
+        </is>
+      </c>
       <c r="N233" s="13" t="inlineStr"/>
       <c r="O233" s="13" t="inlineStr"/>
       <c r="P233" s="13" t="inlineStr"/>
       <c r="Q233" s="14" t="n">
-        <v>7.08135E8</v>
+        <v>3.96E7</v>
       </c>
       <c r="R233" s="14" t="inlineStr"/>
       <c r="S233" s="14" t="n">
@@ -14121,23 +14109,23 @@
       <c r="U233" s="14" t="inlineStr"/>
       <c r="V233" s="14" t="inlineStr"/>
       <c r="W233" s="14" t="n">
-        <v>3.84588968E8</v>
+        <v>2.54929E7</v>
       </c>
       <c r="X233" s="14" t="n">
-        <v>4.7655375E7</v>
+        <v>2068600.0</v>
       </c>
       <c r="Y233" s="14" t="inlineStr"/>
       <c r="Z233" s="14" t="n">
-        <v>4.32244343E8</v>
+        <v>2.75615E7</v>
       </c>
       <c r="AA233" s="14" t="inlineStr"/>
       <c r="AB233" s="14" t="inlineStr"/>
       <c r="AC233" s="15" t="n">
-        <v>0.6103982192661004</v>
+        <v>0.6959974747474748</v>
       </c>
       <c r="AD233" s="15" t="inlineStr"/>
       <c r="AE233" s="14" t="n">
-        <v>2.75890657E8</v>
+        <v>1.20385E7</v>
       </c>
       <c r="AF233" s="14" t="inlineStr"/>
       <c r="AG233" s="14" t="inlineStr"/>
@@ -14152,29 +14140,23 @@
       <c r="E234" s="2" t="inlineStr"/>
       <c r="F234" s="2" t="inlineStr"/>
       <c r="G234" s="2" t="inlineStr"/>
-      <c r="H234" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521811</t>
-          </r>
-        </is>
-      </c>
-      <c r="I234" s="13" t="inlineStr"/>
-      <c r="J234" s="13" t="inlineStr"/>
-      <c r="K234" s="13" t="inlineStr"/>
-      <c r="L234" s="13" t="inlineStr"/>
-      <c r="M234" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
-          </r>
-        </is>
-      </c>
-      <c r="N234" s="13" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr"/>
+      <c r="I234" s="2" t="inlineStr"/>
+      <c r="J234" s="2" t="inlineStr"/>
+      <c r="K234" s="2" t="inlineStr"/>
+      <c r="L234" s="2" t="inlineStr"/>
+      <c r="M234" s="2" t="inlineStr"/>
+      <c r="N234" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000147. Langganan Air (PAM)</t>
+          </r>
+        </is>
+      </c>
       <c r="O234" s="13" t="inlineStr"/>
       <c r="P234" s="13" t="inlineStr"/>
       <c r="Q234" s="14" t="n">
-        <v>2.0E8</v>
+        <v>3.96E7</v>
       </c>
       <c r="R234" s="14" t="inlineStr"/>
       <c r="S234" s="14" t="n">
@@ -14184,23 +14166,23 @@
       <c r="U234" s="14" t="inlineStr"/>
       <c r="V234" s="14" t="inlineStr"/>
       <c r="W234" s="14" t="n">
-        <v>9.9195E7</v>
+        <v>2.54929E7</v>
       </c>
       <c r="X234" s="14" t="n">
-        <v>3.474E7</v>
+        <v>2068600.0</v>
       </c>
       <c r="Y234" s="14" t="inlineStr"/>
       <c r="Z234" s="14" t="n">
-        <v>1.33935E8</v>
+        <v>2.75615E7</v>
       </c>
       <c r="AA234" s="14" t="inlineStr"/>
       <c r="AB234" s="14" t="inlineStr"/>
       <c r="AC234" s="15" t="n">
-        <v>0.669675</v>
+        <v>0.6959974747474748</v>
       </c>
       <c r="AD234" s="15" t="inlineStr"/>
       <c r="AE234" s="14" t="n">
-        <v>6.6065E7</v>
+        <v>1.20385E7</v>
       </c>
       <c r="AF234" s="14" t="inlineStr"/>
       <c r="AG234" s="14" t="inlineStr"/>
@@ -14215,23 +14197,29 @@
       <c r="E235" s="2" t="inlineStr"/>
       <c r="F235" s="2" t="inlineStr"/>
       <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="2" t="inlineStr"/>
-      <c r="I235" s="2" t="inlineStr"/>
-      <c r="J235" s="2" t="inlineStr"/>
-      <c r="K235" s="2" t="inlineStr"/>
-      <c r="L235" s="2" t="inlineStr"/>
-      <c r="M235" s="2" t="inlineStr"/>
-      <c r="N235" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000149. Pakan Induk Ikan Koleksi</t>
-          </r>
-        </is>
-      </c>
+      <c r="H235" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522119</t>
+          </r>
+        </is>
+      </c>
+      <c r="I235" s="13" t="inlineStr"/>
+      <c r="J235" s="13" t="inlineStr"/>
+      <c r="K235" s="13" t="inlineStr"/>
+      <c r="L235" s="13" t="inlineStr"/>
+      <c r="M235" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Daya dan Jasa Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N235" s="13" t="inlineStr"/>
       <c r="O235" s="13" t="inlineStr"/>
       <c r="P235" s="13" t="inlineStr"/>
       <c r="Q235" s="14" t="n">
-        <v>1.8E8</v>
+        <v>1.544E8</v>
       </c>
       <c r="R235" s="14" t="inlineStr"/>
       <c r="S235" s="14" t="n">
@@ -14241,23 +14229,23 @@
       <c r="U235" s="14" t="inlineStr"/>
       <c r="V235" s="14" t="inlineStr"/>
       <c r="W235" s="14" t="n">
-        <v>8.8315E7</v>
+        <v>1.02249256E8</v>
       </c>
       <c r="X235" s="14" t="n">
-        <v>2.5625E7</v>
+        <v>9775950.0</v>
       </c>
       <c r="Y235" s="14" t="inlineStr"/>
       <c r="Z235" s="14" t="n">
-        <v>1.1394E8</v>
+        <v>1.12025206E8</v>
       </c>
       <c r="AA235" s="14" t="inlineStr"/>
       <c r="AB235" s="14" t="inlineStr"/>
       <c r="AC235" s="15" t="n">
-        <v>0.633</v>
+        <v>0.7255518523316062</v>
       </c>
       <c r="AD235" s="15" t="inlineStr"/>
       <c r="AE235" s="14" t="n">
-        <v>6.606E7</v>
+        <v>4.2374794E7</v>
       </c>
       <c r="AF235" s="14" t="inlineStr"/>
       <c r="AG235" s="14" t="inlineStr"/>
@@ -14281,14 +14269,14 @@
       <c r="N236" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000286. Bahan Baku Pakan Ikan</t>
+            <t xml:space="preserve">000148. Langganan Internet</t>
           </r>
         </is>
       </c>
       <c r="O236" s="13" t="inlineStr"/>
       <c r="P236" s="13" t="inlineStr"/>
       <c r="Q236" s="14" t="n">
-        <v>2.0E7</v>
+        <v>1.269E8</v>
       </c>
       <c r="R236" s="14" t="inlineStr"/>
       <c r="S236" s="14" t="n">
@@ -14298,23 +14286,23 @@
       <c r="U236" s="14" t="inlineStr"/>
       <c r="V236" s="14" t="inlineStr"/>
       <c r="W236" s="14" t="n">
-        <v>1.088E7</v>
+        <v>7.510765E7</v>
       </c>
       <c r="X236" s="14" t="n">
-        <v>9115000.0</v>
+        <v>9775950.0</v>
       </c>
       <c r="Y236" s="14" t="inlineStr"/>
       <c r="Z236" s="14" t="n">
-        <v>1.9995E7</v>
+        <v>8.48836E7</v>
       </c>
       <c r="AA236" s="14" t="inlineStr"/>
       <c r="AB236" s="14" t="inlineStr"/>
       <c r="AC236" s="15" t="n">
-        <v>0.99975</v>
+        <v>0.6689014972419228</v>
       </c>
       <c r="AD236" s="15" t="inlineStr"/>
       <c r="AE236" s="14" t="n">
-        <v>5000.0</v>
+        <v>4.20164E7</v>
       </c>
       <c r="AF236" s="14" t="inlineStr"/>
       <c r="AG236" s="14" t="inlineStr"/>
@@ -14329,29 +14317,23 @@
       <c r="E237" s="2" t="inlineStr"/>
       <c r="F237" s="2" t="inlineStr"/>
       <c r="G237" s="2" t="inlineStr"/>
-      <c r="H237" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522191</t>
-          </r>
-        </is>
-      </c>
-      <c r="I237" s="13" t="inlineStr"/>
-      <c r="J237" s="13" t="inlineStr"/>
-      <c r="K237" s="13" t="inlineStr"/>
-      <c r="L237" s="13" t="inlineStr"/>
-      <c r="M237" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Jasa Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N237" s="13" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr"/>
+      <c r="I237" s="2" t="inlineStr"/>
+      <c r="J237" s="2" t="inlineStr"/>
+      <c r="K237" s="2" t="inlineStr"/>
+      <c r="L237" s="2" t="inlineStr"/>
+      <c r="M237" s="2" t="inlineStr"/>
+      <c r="N237" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000240. Langganan aplikasi perkantoran</t>
+          </r>
+        </is>
+      </c>
       <c r="O237" s="13" t="inlineStr"/>
       <c r="P237" s="13" t="inlineStr"/>
       <c r="Q237" s="14" t="n">
-        <v>2.526E7</v>
+        <v>2.75E7</v>
       </c>
       <c r="R237" s="14" t="inlineStr"/>
       <c r="S237" s="14" t="n">
@@ -14361,23 +14343,23 @@
       <c r="U237" s="14" t="inlineStr"/>
       <c r="V237" s="14" t="inlineStr"/>
       <c r="W237" s="14" t="n">
-        <v>2.5259715E7</v>
+        <v>2.7141606E7</v>
       </c>
       <c r="X237" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y237" s="14" t="inlineStr"/>
       <c r="Z237" s="14" t="n">
-        <v>2.5259715E7</v>
+        <v>2.7141606E7</v>
       </c>
       <c r="AA237" s="14" t="inlineStr"/>
       <c r="AB237" s="14" t="inlineStr"/>
       <c r="AC237" s="15" t="n">
-        <v>0.9999887173396674</v>
+        <v>0.9869674909090909</v>
       </c>
       <c r="AD237" s="15" t="inlineStr"/>
       <c r="AE237" s="14" t="n">
-        <v>285.0</v>
+        <v>358394.0</v>
       </c>
       <c r="AF237" s="14" t="inlineStr"/>
       <c r="AG237" s="14" t="inlineStr"/>
@@ -14390,25 +14372,31 @@
       <c r="C238" s="2" t="inlineStr"/>
       <c r="D238" s="2" t="inlineStr"/>
       <c r="E238" s="2" t="inlineStr"/>
-      <c r="F238" s="2" t="inlineStr"/>
-      <c r="G238" s="2" t="inlineStr"/>
-      <c r="H238" s="2" t="inlineStr"/>
-      <c r="I238" s="2" t="inlineStr"/>
-      <c r="J238" s="2" t="inlineStr"/>
-      <c r="K238" s="2" t="inlineStr"/>
-      <c r="L238" s="2" t="inlineStr"/>
-      <c r="M238" s="2" t="inlineStr"/>
-      <c r="N238" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000242. Jasa Penanganan Rayap</t>
-          </r>
-        </is>
-      </c>
+      <c r="F238" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">002.DC</t>
+          </r>
+        </is>
+      </c>
+      <c r="G238" s="13" t="inlineStr"/>
+      <c r="H238" s="13" t="inlineStr"/>
+      <c r="I238" s="13" t="inlineStr"/>
+      <c r="J238" s="13" t="inlineStr"/>
+      <c r="K238" s="13" t="inlineStr"/>
+      <c r="L238" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pemeliharaan Kantor</t>
+          </r>
+        </is>
+      </c>
+      <c r="M238" s="13" t="inlineStr"/>
+      <c r="N238" s="13" t="inlineStr"/>
       <c r="O238" s="13" t="inlineStr"/>
       <c r="P238" s="13" t="inlineStr"/>
       <c r="Q238" s="14" t="n">
-        <v>2.526E7</v>
+        <v>7.44735E8</v>
       </c>
       <c r="R238" s="14" t="inlineStr"/>
       <c r="S238" s="14" t="n">
@@ -14418,23 +14406,23 @@
       <c r="U238" s="14" t="inlineStr"/>
       <c r="V238" s="14" t="inlineStr"/>
       <c r="W238" s="14" t="n">
-        <v>2.5259715E7</v>
+        <v>4.32244343E8</v>
       </c>
       <c r="X238" s="14" t="n">
-        <v>0.0</v>
+        <v>3.2499974E7</v>
       </c>
       <c r="Y238" s="14" t="inlineStr"/>
       <c r="Z238" s="14" t="n">
-        <v>2.5259715E7</v>
+        <v>4.64744317E8</v>
       </c>
       <c r="AA238" s="14" t="inlineStr"/>
       <c r="AB238" s="14" t="inlineStr"/>
       <c r="AC238" s="15" t="n">
-        <v>0.9999887173396674</v>
+        <v>0.6240398490738316</v>
       </c>
       <c r="AD238" s="15" t="inlineStr"/>
       <c r="AE238" s="14" t="n">
-        <v>285.0</v>
+        <v>2.79990683E8</v>
       </c>
       <c r="AF238" s="14" t="inlineStr"/>
       <c r="AG238" s="14" t="inlineStr"/>
@@ -14452,7 +14440,7 @@
       <c r="H239" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">523111</t>
+            <t xml:space="preserve">521811</t>
           </r>
         </is>
       </c>
@@ -14463,7 +14451,7 @@
       <c r="M239" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Belanja Pemeliharaan Gedung dan Bangunan</t>
+            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
           </r>
         </is>
       </c>
@@ -14471,7 +14459,7 @@
       <c r="O239" s="13" t="inlineStr"/>
       <c r="P239" s="13" t="inlineStr"/>
       <c r="Q239" s="14" t="n">
-        <v>1.97915E8</v>
+        <v>2.2E8</v>
       </c>
       <c r="R239" s="14" t="inlineStr"/>
       <c r="S239" s="14" t="n">
@@ -14481,23 +14469,23 @@
       <c r="U239" s="14" t="inlineStr"/>
       <c r="V239" s="14" t="inlineStr"/>
       <c r="W239" s="14" t="n">
-        <v>1.10331326E8</v>
+        <v>1.33935E8</v>
       </c>
       <c r="X239" s="14" t="n">
-        <v>750000.0</v>
+        <v>1.9675E7</v>
       </c>
       <c r="Y239" s="14" t="inlineStr"/>
       <c r="Z239" s="14" t="n">
-        <v>1.11081326E8</v>
+        <v>1.5361E8</v>
       </c>
       <c r="AA239" s="14" t="inlineStr"/>
       <c r="AB239" s="14" t="inlineStr"/>
       <c r="AC239" s="15" t="n">
-        <v>0.5612577419599323</v>
+        <v>0.6982272727272727</v>
       </c>
       <c r="AD239" s="15" t="inlineStr"/>
       <c r="AE239" s="14" t="n">
-        <v>8.6833674E7</v>
+        <v>6.639E7</v>
       </c>
       <c r="AF239" s="14" t="inlineStr"/>
       <c r="AG239" s="14" t="inlineStr"/>
@@ -14521,14 +14509,14 @@
       <c r="N240" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000157. Pemeliharaan Kantor Cibalagung</t>
+            <t xml:space="preserve">000149. Pakan Induk Ikan Koleksi</t>
           </r>
         </is>
       </c>
       <c r="O240" s="13" t="inlineStr"/>
       <c r="P240" s="13" t="inlineStr"/>
       <c r="Q240" s="14" t="n">
-        <v>2.56E7</v>
+        <v>1.8E8</v>
       </c>
       <c r="R240" s="14" t="inlineStr"/>
       <c r="S240" s="14" t="n">
@@ -14538,30 +14526,30 @@
       <c r="U240" s="14" t="inlineStr"/>
       <c r="V240" s="14" t="inlineStr"/>
       <c r="W240" s="14" t="n">
-        <v>1.6931622E7</v>
+        <v>1.1394E8</v>
       </c>
       <c r="X240" s="14" t="n">
-        <v>0.0</v>
+        <v>1.9675E7</v>
       </c>
       <c r="Y240" s="14" t="inlineStr"/>
       <c r="Z240" s="14" t="n">
-        <v>1.6931622E7</v>
+        <v>1.33615E8</v>
       </c>
       <c r="AA240" s="14" t="inlineStr"/>
       <c r="AB240" s="14" t="inlineStr"/>
       <c r="AC240" s="15" t="n">
-        <v>0.661391484375</v>
+        <v>0.7423055555555556</v>
       </c>
       <c r="AD240" s="15" t="inlineStr"/>
       <c r="AE240" s="14" t="n">
-        <v>8668378.0</v>
+        <v>4.6385E7</v>
       </c>
       <c r="AF240" s="14" t="inlineStr"/>
       <c r="AG240" s="14" t="inlineStr"/>
       <c r="AH240" s="14" t="inlineStr"/>
       <c r="AI240" s="14" t="inlineStr"/>
     </row>
-    <row r="241" customHeight="1" ht="18">
+    <row r="241" customHeight="1" ht="15">
       <c r="A241" s="2" t="inlineStr"/>
       <c r="B241" s="2" t="inlineStr"/>
       <c r="C241" s="2" t="inlineStr"/>
@@ -14578,14 +14566,14 @@
       <c r="N241" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000158. Pemeliharaan Hatchery dan Laboratorium Cibalagung</t>
+            <t xml:space="preserve">000286. Bahan Baku Pakan Ikan</t>
           </r>
         </is>
       </c>
       <c r="O241" s="13" t="inlineStr"/>
       <c r="P241" s="13" t="inlineStr"/>
       <c r="Q241" s="14" t="n">
-        <v>1.575E7</v>
+        <v>4.0E7</v>
       </c>
       <c r="R241" s="14" t="inlineStr"/>
       <c r="S241" s="14" t="n">
@@ -14595,23 +14583,23 @@
       <c r="U241" s="14" t="inlineStr"/>
       <c r="V241" s="14" t="inlineStr"/>
       <c r="W241" s="14" t="n">
-        <v>1.1156299E7</v>
+        <v>1.9995E7</v>
       </c>
       <c r="X241" s="14" t="n">
-        <v>750000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y241" s="14" t="inlineStr"/>
       <c r="Z241" s="14" t="n">
-        <v>1.1906299E7</v>
+        <v>1.9995E7</v>
       </c>
       <c r="AA241" s="14" t="inlineStr"/>
       <c r="AB241" s="14" t="inlineStr"/>
       <c r="AC241" s="15" t="n">
-        <v>0.7559554920634921</v>
+        <v>0.499875</v>
       </c>
       <c r="AD241" s="15" t="inlineStr"/>
       <c r="AE241" s="14" t="n">
-        <v>3843701.0</v>
+        <v>2.0005E7</v>
       </c>
       <c r="AF241" s="14" t="inlineStr"/>
       <c r="AG241" s="14" t="inlineStr"/>
@@ -14626,23 +14614,29 @@
       <c r="E242" s="2" t="inlineStr"/>
       <c r="F242" s="2" t="inlineStr"/>
       <c r="G242" s="2" t="inlineStr"/>
-      <c r="H242" s="2" t="inlineStr"/>
-      <c r="I242" s="2" t="inlineStr"/>
-      <c r="J242" s="2" t="inlineStr"/>
-      <c r="K242" s="2" t="inlineStr"/>
-      <c r="L242" s="2" t="inlineStr"/>
-      <c r="M242" s="2" t="inlineStr"/>
-      <c r="N242" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000159. Pemeliharaan Kolam Cibalagung</t>
-          </r>
-        </is>
-      </c>
+      <c r="H242" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522191</t>
+          </r>
+        </is>
+      </c>
+      <c r="I242" s="13" t="inlineStr"/>
+      <c r="J242" s="13" t="inlineStr"/>
+      <c r="K242" s="13" t="inlineStr"/>
+      <c r="L242" s="13" t="inlineStr"/>
+      <c r="M242" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Jasa Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N242" s="13" t="inlineStr"/>
       <c r="O242" s="13" t="inlineStr"/>
       <c r="P242" s="13" t="inlineStr"/>
       <c r="Q242" s="14" t="n">
-        <v>2.595E7</v>
+        <v>3.526E7</v>
       </c>
       <c r="R242" s="14" t="inlineStr"/>
       <c r="S242" s="14" t="n">
@@ -14652,23 +14646,23 @@
       <c r="U242" s="14" t="inlineStr"/>
       <c r="V242" s="14" t="inlineStr"/>
       <c r="W242" s="14" t="n">
-        <v>2.5327E7</v>
+        <v>2.5259715E7</v>
       </c>
       <c r="X242" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y242" s="14" t="inlineStr"/>
       <c r="Z242" s="14" t="n">
-        <v>2.5327E7</v>
+        <v>2.5259715E7</v>
       </c>
       <c r="AA242" s="14" t="inlineStr"/>
       <c r="AB242" s="14" t="inlineStr"/>
       <c r="AC242" s="15" t="n">
-        <v>0.9759922928709056</v>
+        <v>0.7163844299489507</v>
       </c>
       <c r="AD242" s="15" t="inlineStr"/>
       <c r="AE242" s="14" t="n">
-        <v>623000.0</v>
+        <v>1.0000285E7</v>
       </c>
       <c r="AF242" s="14" t="inlineStr"/>
       <c r="AG242" s="14" t="inlineStr"/>
@@ -14692,14 +14686,14 @@
       <c r="N243" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000160. Pemeliharaan Pagar Keliling Cibalagung</t>
+            <t xml:space="preserve">000242. Jasa Penanganan Rayap</t>
           </r>
         </is>
       </c>
       <c r="O243" s="13" t="inlineStr"/>
       <c r="P243" s="13" t="inlineStr"/>
       <c r="Q243" s="14" t="n">
-        <v>2170000.0</v>
+        <v>3.526E7</v>
       </c>
       <c r="R243" s="14" t="inlineStr"/>
       <c r="S243" s="14" t="n">
@@ -14709,23 +14703,23 @@
       <c r="U243" s="14" t="inlineStr"/>
       <c r="V243" s="14" t="inlineStr"/>
       <c r="W243" s="14" t="n">
-        <v>2167000.0</v>
+        <v>2.5259715E7</v>
       </c>
       <c r="X243" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y243" s="14" t="inlineStr"/>
       <c r="Z243" s="14" t="n">
-        <v>2167000.0</v>
+        <v>2.5259715E7</v>
       </c>
       <c r="AA243" s="14" t="inlineStr"/>
       <c r="AB243" s="14" t="inlineStr"/>
       <c r="AC243" s="15" t="n">
-        <v>0.9986175115207373</v>
+        <v>0.7163844299489507</v>
       </c>
       <c r="AD243" s="15" t="inlineStr"/>
       <c r="AE243" s="14" t="n">
-        <v>3000.0</v>
+        <v>1.0000285E7</v>
       </c>
       <c r="AF243" s="14" t="inlineStr"/>
       <c r="AG243" s="14" t="inlineStr"/>
@@ -14740,23 +14734,29 @@
       <c r="E244" s="2" t="inlineStr"/>
       <c r="F244" s="2" t="inlineStr"/>
       <c r="G244" s="2" t="inlineStr"/>
-      <c r="H244" s="2" t="inlineStr"/>
-      <c r="I244" s="2" t="inlineStr"/>
-      <c r="J244" s="2" t="inlineStr"/>
-      <c r="K244" s="2" t="inlineStr"/>
-      <c r="L244" s="2" t="inlineStr"/>
-      <c r="M244" s="2" t="inlineStr"/>
-      <c r="N244" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000161. Pemeliharaan Kantor Sempur</t>
-          </r>
-        </is>
-      </c>
+      <c r="H244" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">523111</t>
+          </r>
+        </is>
+      </c>
+      <c r="I244" s="13" t="inlineStr"/>
+      <c r="J244" s="13" t="inlineStr"/>
+      <c r="K244" s="13" t="inlineStr"/>
+      <c r="L244" s="13" t="inlineStr"/>
+      <c r="M244" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Pemeliharaan Gedung dan Bangunan</t>
+          </r>
+        </is>
+      </c>
+      <c r="N244" s="13" t="inlineStr"/>
       <c r="O244" s="13" t="inlineStr"/>
       <c r="P244" s="13" t="inlineStr"/>
       <c r="Q244" s="14" t="n">
-        <v>2.69E7</v>
+        <v>1.97915E8</v>
       </c>
       <c r="R244" s="14" t="inlineStr"/>
       <c r="S244" s="14" t="n">
@@ -14766,23 +14766,23 @@
       <c r="U244" s="14" t="inlineStr"/>
       <c r="V244" s="14" t="inlineStr"/>
       <c r="W244" s="14" t="n">
-        <v>2475000.0</v>
+        <v>1.11081326E8</v>
       </c>
       <c r="X244" s="14" t="n">
-        <v>0.0</v>
+        <v>6040207.0</v>
       </c>
       <c r="Y244" s="14" t="inlineStr"/>
       <c r="Z244" s="14" t="n">
-        <v>2475000.0</v>
+        <v>1.17121533E8</v>
       </c>
       <c r="AA244" s="14" t="inlineStr"/>
       <c r="AB244" s="14" t="inlineStr"/>
       <c r="AC244" s="15" t="n">
-        <v>0.09200743494423792</v>
+        <v>0.5917769395952808</v>
       </c>
       <c r="AD244" s="15" t="inlineStr"/>
       <c r="AE244" s="14" t="n">
-        <v>2.4425E7</v>
+        <v>8.0793467E7</v>
       </c>
       <c r="AF244" s="14" t="inlineStr"/>
       <c r="AG244" s="14" t="inlineStr"/>
@@ -14806,14 +14806,14 @@
       <c r="N245" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000164. Pemeliharaan Kantor Depok</t>
+            <t xml:space="preserve">000157. Pemeliharaan Kantor Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O245" s="13" t="inlineStr"/>
       <c r="P245" s="13" t="inlineStr"/>
       <c r="Q245" s="14" t="n">
-        <v>2800000.0</v>
+        <v>2.56E7</v>
       </c>
       <c r="R245" s="14" t="inlineStr"/>
       <c r="S245" s="14" t="n">
@@ -14823,30 +14823,30 @@
       <c r="U245" s="14" t="inlineStr"/>
       <c r="V245" s="14" t="inlineStr"/>
       <c r="W245" s="14" t="n">
-        <v>1360000.0</v>
+        <v>1.6931622E7</v>
       </c>
       <c r="X245" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y245" s="14" t="inlineStr"/>
       <c r="Z245" s="14" t="n">
-        <v>1360000.0</v>
+        <v>1.6931622E7</v>
       </c>
       <c r="AA245" s="14" t="inlineStr"/>
       <c r="AB245" s="14" t="inlineStr"/>
       <c r="AC245" s="15" t="n">
-        <v>0.4857142857142857</v>
+        <v>0.661391484375</v>
       </c>
       <c r="AD245" s="15" t="inlineStr"/>
       <c r="AE245" s="14" t="n">
-        <v>1440000.0</v>
+        <v>8668378.0</v>
       </c>
       <c r="AF245" s="14" t="inlineStr"/>
       <c r="AG245" s="14" t="inlineStr"/>
       <c r="AH245" s="14" t="inlineStr"/>
       <c r="AI245" s="14" t="inlineStr"/>
     </row>
-    <row r="246" customHeight="1" ht="15">
+    <row r="246" customHeight="1" ht="18">
       <c r="A246" s="2" t="inlineStr"/>
       <c r="B246" s="2" t="inlineStr"/>
       <c r="C246" s="2" t="inlineStr"/>
@@ -14863,14 +14863,14 @@
       <c r="N246" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000165. Pemeliharaan Gedung Laboratorium Depok</t>
+            <t xml:space="preserve">000158. Pemeliharaan Hatchery dan Laboratorium Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O246" s="13" t="inlineStr"/>
       <c r="P246" s="13" t="inlineStr"/>
       <c r="Q246" s="14" t="n">
-        <v>2.66E7</v>
+        <v>1.575E7</v>
       </c>
       <c r="R246" s="14" t="inlineStr"/>
       <c r="S246" s="14" t="n">
@@ -14880,23 +14880,23 @@
       <c r="U246" s="14" t="inlineStr"/>
       <c r="V246" s="14" t="inlineStr"/>
       <c r="W246" s="14" t="n">
-        <v>6578415.0</v>
+        <v>1.1906299E7</v>
       </c>
       <c r="X246" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y246" s="14" t="inlineStr"/>
       <c r="Z246" s="14" t="n">
-        <v>6578415.0</v>
+        <v>1.1906299E7</v>
       </c>
       <c r="AA246" s="14" t="inlineStr"/>
       <c r="AB246" s="14" t="inlineStr"/>
       <c r="AC246" s="15" t="n">
-        <v>0.24730883458646616</v>
+        <v>0.7559554920634921</v>
       </c>
       <c r="AD246" s="15" t="inlineStr"/>
       <c r="AE246" s="14" t="n">
-        <v>2.0021585E7</v>
+        <v>3843701.0</v>
       </c>
       <c r="AF246" s="14" t="inlineStr"/>
       <c r="AG246" s="14" t="inlineStr"/>
@@ -14920,14 +14920,14 @@
       <c r="N247" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000167. Pemeliharaan Halaman Kantor Depok</t>
+            <t xml:space="preserve">000159. Pemeliharaan Kolam Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O247" s="13" t="inlineStr"/>
       <c r="P247" s="13" t="inlineStr"/>
       <c r="Q247" s="14" t="n">
-        <v>1.443E7</v>
+        <v>2.595E7</v>
       </c>
       <c r="R247" s="14" t="inlineStr"/>
       <c r="S247" s="14" t="n">
@@ -14937,23 +14937,23 @@
       <c r="U247" s="14" t="inlineStr"/>
       <c r="V247" s="14" t="inlineStr"/>
       <c r="W247" s="14" t="n">
-        <v>1.443E7</v>
+        <v>2.5327E7</v>
       </c>
       <c r="X247" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y247" s="14" t="inlineStr"/>
       <c r="Z247" s="14" t="n">
-        <v>1.443E7</v>
+        <v>2.5327E7</v>
       </c>
       <c r="AA247" s="14" t="inlineStr"/>
       <c r="AB247" s="14" t="inlineStr"/>
       <c r="AC247" s="15" t="n">
-        <v>1.0</v>
+        <v>0.9759922928709056</v>
       </c>
       <c r="AD247" s="15" t="inlineStr"/>
       <c r="AE247" s="14" t="n">
-        <v>0.0</v>
+        <v>623000.0</v>
       </c>
       <c r="AF247" s="14" t="inlineStr"/>
       <c r="AG247" s="14" t="inlineStr"/>
@@ -14977,14 +14977,14 @@
       <c r="N248" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000170. Pemeliharaan Halaman Kantor Sempur</t>
+            <t xml:space="preserve">000160. Pemeliharaan Pagar Keliling Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O248" s="13" t="inlineStr"/>
       <c r="P248" s="13" t="inlineStr"/>
       <c r="Q248" s="14" t="n">
-        <v>4115000.0</v>
+        <v>2170000.0</v>
       </c>
       <c r="R248" s="14" t="inlineStr"/>
       <c r="S248" s="14" t="n">
@@ -14994,23 +14994,23 @@
       <c r="U248" s="14" t="inlineStr"/>
       <c r="V248" s="14" t="inlineStr"/>
       <c r="W248" s="14" t="n">
-        <v>1101500.0</v>
+        <v>2167000.0</v>
       </c>
       <c r="X248" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y248" s="14" t="inlineStr"/>
       <c r="Z248" s="14" t="n">
-        <v>1101500.0</v>
+        <v>2167000.0</v>
       </c>
       <c r="AA248" s="14" t="inlineStr"/>
       <c r="AB248" s="14" t="inlineStr"/>
       <c r="AC248" s="15" t="n">
-        <v>0.26767922235722963</v>
+        <v>0.9986175115207373</v>
       </c>
       <c r="AD248" s="15" t="inlineStr"/>
       <c r="AE248" s="14" t="n">
-        <v>3013500.0</v>
+        <v>3000.0</v>
       </c>
       <c r="AF248" s="14" t="inlineStr"/>
       <c r="AG248" s="14" t="inlineStr"/>
@@ -15034,14 +15034,14 @@
       <c r="N249" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000241. Pemeliharaan Rumah Dinas Cibalagung</t>
+            <t xml:space="preserve">000161. Pemeliharaan Kantor Sempur</t>
           </r>
         </is>
       </c>
       <c r="O249" s="13" t="inlineStr"/>
       <c r="P249" s="13" t="inlineStr"/>
       <c r="Q249" s="14" t="n">
-        <v>7000000.0</v>
+        <v>2.69E7</v>
       </c>
       <c r="R249" s="14" t="inlineStr"/>
       <c r="S249" s="14" t="n">
@@ -15051,23 +15051,23 @@
       <c r="U249" s="14" t="inlineStr"/>
       <c r="V249" s="14" t="inlineStr"/>
       <c r="W249" s="14" t="n">
-        <v>3880000.0</v>
+        <v>2475000.0</v>
       </c>
       <c r="X249" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y249" s="14" t="inlineStr"/>
       <c r="Z249" s="14" t="n">
-        <v>3880000.0</v>
+        <v>2475000.0</v>
       </c>
       <c r="AA249" s="14" t="inlineStr"/>
       <c r="AB249" s="14" t="inlineStr"/>
       <c r="AC249" s="15" t="n">
-        <v>0.5542857142857143</v>
+        <v>0.09200743494423792</v>
       </c>
       <c r="AD249" s="15" t="inlineStr"/>
       <c r="AE249" s="14" t="n">
-        <v>3120000.0</v>
+        <v>2.4425E7</v>
       </c>
       <c r="AF249" s="14" t="inlineStr"/>
       <c r="AG249" s="14" t="inlineStr"/>
@@ -15091,14 +15091,14 @@
       <c r="N250" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000264. Pemeliharaan Kolam Cijeruk</t>
+            <t xml:space="preserve">000164. Pemeliharaan Kantor Depok</t>
           </r>
         </is>
       </c>
       <c r="O250" s="13" t="inlineStr"/>
       <c r="P250" s="13" t="inlineStr"/>
       <c r="Q250" s="14" t="n">
-        <v>2.07E7</v>
+        <v>2800000.0</v>
       </c>
       <c r="R250" s="14" t="inlineStr"/>
       <c r="S250" s="14" t="n">
@@ -15108,23 +15108,23 @@
       <c r="U250" s="14" t="inlineStr"/>
       <c r="V250" s="14" t="inlineStr"/>
       <c r="W250" s="14" t="n">
-        <v>1.5284E7</v>
+        <v>1360000.0</v>
       </c>
       <c r="X250" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y250" s="14" t="inlineStr"/>
       <c r="Z250" s="14" t="n">
-        <v>1.5284E7</v>
+        <v>1360000.0</v>
       </c>
       <c r="AA250" s="14" t="inlineStr"/>
       <c r="AB250" s="14" t="inlineStr"/>
       <c r="AC250" s="15" t="n">
-        <v>0.7383574879227053</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="AD250" s="15" t="inlineStr"/>
       <c r="AE250" s="14" t="n">
-        <v>5416000.0</v>
+        <v>1440000.0</v>
       </c>
       <c r="AF250" s="14" t="inlineStr"/>
       <c r="AG250" s="14" t="inlineStr"/>
@@ -15148,14 +15148,14 @@
       <c r="N251" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000280. Pemeliharaan Kantor Cijeruk</t>
+            <t xml:space="preserve">000165. Pemeliharaan Gedung Laboratorium Depok</t>
           </r>
         </is>
       </c>
       <c r="O251" s="13" t="inlineStr"/>
       <c r="P251" s="13" t="inlineStr"/>
       <c r="Q251" s="14" t="n">
-        <v>1.59E7</v>
+        <v>2.66E7</v>
       </c>
       <c r="R251" s="14" t="inlineStr"/>
       <c r="S251" s="14" t="n">
@@ -15165,23 +15165,23 @@
       <c r="U251" s="14" t="inlineStr"/>
       <c r="V251" s="14" t="inlineStr"/>
       <c r="W251" s="14" t="n">
-        <v>0.0</v>
+        <v>6578415.0</v>
       </c>
       <c r="X251" s="14" t="n">
-        <v>0.0</v>
+        <v>5565207.0</v>
       </c>
       <c r="Y251" s="14" t="inlineStr"/>
       <c r="Z251" s="14" t="n">
-        <v>0.0</v>
+        <v>1.2143622E7</v>
       </c>
       <c r="AA251" s="14" t="inlineStr"/>
       <c r="AB251" s="14" t="inlineStr"/>
       <c r="AC251" s="15" t="n">
-        <v>0.0</v>
+        <v>0.45652714285714285</v>
       </c>
       <c r="AD251" s="15" t="inlineStr"/>
       <c r="AE251" s="14" t="n">
-        <v>1.59E7</v>
+        <v>1.4456378E7</v>
       </c>
       <c r="AF251" s="14" t="inlineStr"/>
       <c r="AG251" s="14" t="inlineStr"/>
@@ -15205,14 +15205,14 @@
       <c r="N252" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000281. Pemeliharaan Pagar Keliling Depok</t>
+            <t xml:space="preserve">000167. Pemeliharaan Halaman Kantor Depok</t>
           </r>
         </is>
       </c>
       <c r="O252" s="13" t="inlineStr"/>
       <c r="P252" s="13" t="inlineStr"/>
       <c r="Q252" s="14" t="n">
-        <v>1.0E7</v>
+        <v>1.443E7</v>
       </c>
       <c r="R252" s="14" t="inlineStr"/>
       <c r="S252" s="14" t="n">
@@ -15222,23 +15222,23 @@
       <c r="U252" s="14" t="inlineStr"/>
       <c r="V252" s="14" t="inlineStr"/>
       <c r="W252" s="14" t="n">
-        <v>9640490.0</v>
+        <v>1.443E7</v>
       </c>
       <c r="X252" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y252" s="14" t="inlineStr"/>
       <c r="Z252" s="14" t="n">
-        <v>9640490.0</v>
+        <v>1.443E7</v>
       </c>
       <c r="AA252" s="14" t="inlineStr"/>
       <c r="AB252" s="14" t="inlineStr"/>
       <c r="AC252" s="15" t="n">
-        <v>0.964049</v>
+        <v>1.0</v>
       </c>
       <c r="AD252" s="15" t="inlineStr"/>
       <c r="AE252" s="14" t="n">
-        <v>359510.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF252" s="14" t="inlineStr"/>
       <c r="AG252" s="14" t="inlineStr"/>
@@ -15253,29 +15253,23 @@
       <c r="E253" s="2" t="inlineStr"/>
       <c r="F253" s="2" t="inlineStr"/>
       <c r="G253" s="2" t="inlineStr"/>
-      <c r="H253" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">523121</t>
-          </r>
-        </is>
-      </c>
-      <c r="I253" s="13" t="inlineStr"/>
-      <c r="J253" s="13" t="inlineStr"/>
-      <c r="K253" s="13" t="inlineStr"/>
-      <c r="L253" s="13" t="inlineStr"/>
-      <c r="M253" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Pemeliharaan Peralatan dan Mesin</t>
-          </r>
-        </is>
-      </c>
-      <c r="N253" s="13" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr"/>
+      <c r="I253" s="2" t="inlineStr"/>
+      <c r="J253" s="2" t="inlineStr"/>
+      <c r="K253" s="2" t="inlineStr"/>
+      <c r="L253" s="2" t="inlineStr"/>
+      <c r="M253" s="2" t="inlineStr"/>
+      <c r="N253" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000170. Pemeliharaan Halaman Kantor Sempur</t>
+          </r>
+        </is>
+      </c>
       <c r="O253" s="13" t="inlineStr"/>
       <c r="P253" s="13" t="inlineStr"/>
       <c r="Q253" s="14" t="n">
-        <v>2.0386E8</v>
+        <v>4115000.0</v>
       </c>
       <c r="R253" s="14" t="inlineStr"/>
       <c r="S253" s="14" t="n">
@@ -15285,23 +15279,23 @@
       <c r="U253" s="14" t="inlineStr"/>
       <c r="V253" s="14" t="inlineStr"/>
       <c r="W253" s="14" t="n">
-        <v>8.8386927E7</v>
+        <v>1101500.0</v>
       </c>
       <c r="X253" s="14" t="n">
-        <v>1.2165375E7</v>
+        <v>475000.0</v>
       </c>
       <c r="Y253" s="14" t="inlineStr"/>
       <c r="Z253" s="14" t="n">
-        <v>1.00552302E8</v>
+        <v>1576500.0</v>
       </c>
       <c r="AA253" s="14" t="inlineStr"/>
       <c r="AB253" s="14" t="inlineStr"/>
       <c r="AC253" s="15" t="n">
-        <v>0.49324194054743453</v>
+        <v>0.3831105710814095</v>
       </c>
       <c r="AD253" s="15" t="inlineStr"/>
       <c r="AE253" s="14" t="n">
-        <v>1.03307698E8</v>
+        <v>2538500.0</v>
       </c>
       <c r="AF253" s="14" t="inlineStr"/>
       <c r="AG253" s="14" t="inlineStr"/>
@@ -15325,14 +15319,14 @@
       <c r="N254" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000175. Pemeliharaan AC Split</t>
+            <t xml:space="preserve">000241. Pemeliharaan Rumah Dinas Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O254" s="13" t="inlineStr"/>
       <c r="P254" s="13" t="inlineStr"/>
       <c r="Q254" s="14" t="n">
-        <v>1.07E7</v>
+        <v>7000000.0</v>
       </c>
       <c r="R254" s="14" t="inlineStr"/>
       <c r="S254" s="14" t="n">
@@ -15342,23 +15336,23 @@
       <c r="U254" s="14" t="inlineStr"/>
       <c r="V254" s="14" t="inlineStr"/>
       <c r="W254" s="14" t="n">
-        <v>4080000.0</v>
+        <v>3880000.0</v>
       </c>
       <c r="X254" s="14" t="n">
-        <v>4845000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y254" s="14" t="inlineStr"/>
       <c r="Z254" s="14" t="n">
-        <v>8925000.0</v>
+        <v>3880000.0</v>
       </c>
       <c r="AA254" s="14" t="inlineStr"/>
       <c r="AB254" s="14" t="inlineStr"/>
       <c r="AC254" s="15" t="n">
-        <v>0.8341121495327103</v>
+        <v>0.5542857142857143</v>
       </c>
       <c r="AD254" s="15" t="inlineStr"/>
       <c r="AE254" s="14" t="n">
-        <v>1775000.0</v>
+        <v>3120000.0</v>
       </c>
       <c r="AF254" s="14" t="inlineStr"/>
       <c r="AG254" s="14" t="inlineStr"/>
@@ -15425,14 +15419,14 @@
       <c r="N256" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000176. Pemeliharaan Laptop</t>
+            <t xml:space="preserve">000264. Pemeliharaan Kolam Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O256" s="13" t="inlineStr"/>
       <c r="P256" s="13" t="inlineStr"/>
       <c r="Q256" s="14" t="n">
-        <v>5000000.0</v>
+        <v>2.07E7</v>
       </c>
       <c r="R256" s="14" t="inlineStr"/>
       <c r="S256" s="14" t="n">
@@ -15442,23 +15436,23 @@
       <c r="U256" s="14" t="inlineStr"/>
       <c r="V256" s="14" t="inlineStr"/>
       <c r="W256" s="14" t="n">
-        <v>0.0</v>
+        <v>1.5284E7</v>
       </c>
       <c r="X256" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y256" s="14" t="inlineStr"/>
       <c r="Z256" s="14" t="n">
-        <v>0.0</v>
+        <v>1.5284E7</v>
       </c>
       <c r="AA256" s="14" t="inlineStr"/>
       <c r="AB256" s="14" t="inlineStr"/>
       <c r="AC256" s="15" t="n">
-        <v>0.0</v>
+        <v>0.7383574879227053</v>
       </c>
       <c r="AD256" s="15" t="inlineStr"/>
       <c r="AE256" s="14" t="n">
-        <v>5000000.0</v>
+        <v>5416000.0</v>
       </c>
       <c r="AF256" s="14" t="inlineStr"/>
       <c r="AG256" s="14" t="inlineStr"/>
@@ -15482,14 +15476,14 @@
       <c r="N257" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000182. Pemeliharaan Instalasi Listrik</t>
+            <t xml:space="preserve">000280. Pemeliharaan Kantor Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O257" s="13" t="inlineStr"/>
       <c r="P257" s="13" t="inlineStr"/>
       <c r="Q257" s="14" t="n">
-        <v>2.7E7</v>
+        <v>1.59E7</v>
       </c>
       <c r="R257" s="14" t="inlineStr"/>
       <c r="S257" s="14" t="n">
@@ -15499,23 +15493,23 @@
       <c r="U257" s="14" t="inlineStr"/>
       <c r="V257" s="14" t="inlineStr"/>
       <c r="W257" s="14" t="n">
-        <v>3861718.0</v>
+        <v>0.0</v>
       </c>
       <c r="X257" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y257" s="14" t="inlineStr"/>
       <c r="Z257" s="14" t="n">
-        <v>3861718.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA257" s="14" t="inlineStr"/>
       <c r="AB257" s="14" t="inlineStr"/>
       <c r="AC257" s="15" t="n">
-        <v>0.1430265925925926</v>
+        <v>0.0</v>
       </c>
       <c r="AD257" s="15" t="inlineStr"/>
       <c r="AE257" s="14" t="n">
-        <v>2.3138282E7</v>
+        <v>1.59E7</v>
       </c>
       <c r="AF257" s="14" t="inlineStr"/>
       <c r="AG257" s="14" t="inlineStr"/>
@@ -15539,14 +15533,14 @@
       <c r="N258" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000183. Pemeliharaan Kendaraan Roda 4</t>
+            <t xml:space="preserve">000281. Pemeliharaan Pagar Keliling Depok</t>
           </r>
         </is>
       </c>
       <c r="O258" s="13" t="inlineStr"/>
       <c r="P258" s="13" t="inlineStr"/>
       <c r="Q258" s="14" t="n">
-        <v>1.246E8</v>
+        <v>1.0E7</v>
       </c>
       <c r="R258" s="14" t="inlineStr"/>
       <c r="S258" s="14" t="n">
@@ -15556,23 +15550,23 @@
       <c r="U258" s="14" t="inlineStr"/>
       <c r="V258" s="14" t="inlineStr"/>
       <c r="W258" s="14" t="n">
-        <v>6.6116077E7</v>
+        <v>9640490.0</v>
       </c>
       <c r="X258" s="14" t="n">
-        <v>4737800.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y258" s="14" t="inlineStr"/>
       <c r="Z258" s="14" t="n">
-        <v>7.0853877E7</v>
+        <v>9640490.0</v>
       </c>
       <c r="AA258" s="14" t="inlineStr"/>
       <c r="AB258" s="14" t="inlineStr"/>
       <c r="AC258" s="15" t="n">
-        <v>0.5686506982343499</v>
+        <v>0.964049</v>
       </c>
       <c r="AD258" s="15" t="inlineStr"/>
       <c r="AE258" s="14" t="n">
-        <v>5.3746123E7</v>
+        <v>359510.0</v>
       </c>
       <c r="AF258" s="14" t="inlineStr"/>
       <c r="AG258" s="14" t="inlineStr"/>
@@ -15587,23 +15581,29 @@
       <c r="E259" s="2" t="inlineStr"/>
       <c r="F259" s="2" t="inlineStr"/>
       <c r="G259" s="2" t="inlineStr"/>
-      <c r="H259" s="2" t="inlineStr"/>
-      <c r="I259" s="2" t="inlineStr"/>
-      <c r="J259" s="2" t="inlineStr"/>
-      <c r="K259" s="2" t="inlineStr"/>
-      <c r="L259" s="2" t="inlineStr"/>
-      <c r="M259" s="2" t="inlineStr"/>
-      <c r="N259" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000184. Pemeliharaan Kendaraan Roda 2</t>
-          </r>
-        </is>
-      </c>
+      <c r="H259" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">523121</t>
+          </r>
+        </is>
+      </c>
+      <c r="I259" s="13" t="inlineStr"/>
+      <c r="J259" s="13" t="inlineStr"/>
+      <c r="K259" s="13" t="inlineStr"/>
+      <c r="L259" s="13" t="inlineStr"/>
+      <c r="M259" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Pemeliharaan Peralatan dan Mesin</t>
+          </r>
+        </is>
+      </c>
+      <c r="N259" s="13" t="inlineStr"/>
       <c r="O259" s="13" t="inlineStr"/>
       <c r="P259" s="13" t="inlineStr"/>
       <c r="Q259" s="14" t="n">
-        <v>3000000.0</v>
+        <v>2.1046E8</v>
       </c>
       <c r="R259" s="14" t="inlineStr"/>
       <c r="S259" s="14" t="n">
@@ -15613,23 +15613,23 @@
       <c r="U259" s="14" t="inlineStr"/>
       <c r="V259" s="14" t="inlineStr"/>
       <c r="W259" s="14" t="n">
-        <v>2177000.0</v>
+        <v>1.00552302E8</v>
       </c>
       <c r="X259" s="14" t="n">
-        <v>233875.0</v>
+        <v>6784767.0</v>
       </c>
       <c r="Y259" s="14" t="inlineStr"/>
       <c r="Z259" s="14" t="n">
-        <v>2410875.0</v>
+        <v>1.07337069E8</v>
       </c>
       <c r="AA259" s="14" t="inlineStr"/>
       <c r="AB259" s="14" t="inlineStr"/>
       <c r="AC259" s="15" t="n">
-        <v>0.803625</v>
+        <v>0.5100117314454053</v>
       </c>
       <c r="AD259" s="15" t="inlineStr"/>
       <c r="AE259" s="14" t="n">
-        <v>589125.0</v>
+        <v>1.03122931E8</v>
       </c>
       <c r="AF259" s="14" t="inlineStr"/>
       <c r="AG259" s="14" t="inlineStr"/>
@@ -15653,14 +15653,14 @@
       <c r="N260" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000185. Pemeliharaan CCTV</t>
+            <t xml:space="preserve">000175. Pemeliharaan AC Split</t>
           </r>
         </is>
       </c>
       <c r="O260" s="13" t="inlineStr"/>
       <c r="P260" s="13" t="inlineStr"/>
       <c r="Q260" s="14" t="n">
-        <v>6000000.0</v>
+        <v>1.43E7</v>
       </c>
       <c r="R260" s="14" t="inlineStr"/>
       <c r="S260" s="14" t="n">
@@ -15670,23 +15670,23 @@
       <c r="U260" s="14" t="inlineStr"/>
       <c r="V260" s="14" t="inlineStr"/>
       <c r="W260" s="14" t="n">
-        <v>4737535.0</v>
+        <v>8925000.0</v>
       </c>
       <c r="X260" s="14" t="n">
-        <v>0.0</v>
+        <v>1370000.0</v>
       </c>
       <c r="Y260" s="14" t="inlineStr"/>
       <c r="Z260" s="14" t="n">
-        <v>4737535.0</v>
+        <v>1.0295E7</v>
       </c>
       <c r="AA260" s="14" t="inlineStr"/>
       <c r="AB260" s="14" t="inlineStr"/>
       <c r="AC260" s="15" t="n">
-        <v>0.7895891666666667</v>
+        <v>0.7199300699300699</v>
       </c>
       <c r="AD260" s="15" t="inlineStr"/>
       <c r="AE260" s="14" t="n">
-        <v>1262465.0</v>
+        <v>4005000.0</v>
       </c>
       <c r="AF260" s="14" t="inlineStr"/>
       <c r="AG260" s="14" t="inlineStr"/>
@@ -15710,14 +15710,14 @@
       <c r="N261" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000186. Pemeliharaan Genset 250 KVA</t>
+            <t xml:space="preserve">000176. Pemeliharaan Laptop</t>
           </r>
         </is>
       </c>
       <c r="O261" s="13" t="inlineStr"/>
       <c r="P261" s="13" t="inlineStr"/>
       <c r="Q261" s="14" t="n">
-        <v>6010000.0</v>
+        <v>5000000.0</v>
       </c>
       <c r="R261" s="14" t="inlineStr"/>
       <c r="S261" s="14" t="n">
@@ -15727,23 +15727,23 @@
       <c r="U261" s="14" t="inlineStr"/>
       <c r="V261" s="14" t="inlineStr"/>
       <c r="W261" s="14" t="n">
-        <v>1000052.0</v>
+        <v>0.0</v>
       </c>
       <c r="X261" s="14" t="n">
-        <v>0.0</v>
+        <v>350000.0</v>
       </c>
       <c r="Y261" s="14" t="inlineStr"/>
       <c r="Z261" s="14" t="n">
-        <v>1000052.0</v>
+        <v>350000.0</v>
       </c>
       <c r="AA261" s="14" t="inlineStr"/>
       <c r="AB261" s="14" t="inlineStr"/>
       <c r="AC261" s="15" t="n">
-        <v>0.166398003327787</v>
+        <v>0.07</v>
       </c>
       <c r="AD261" s="15" t="inlineStr"/>
       <c r="AE261" s="14" t="n">
-        <v>5009948.0</v>
+        <v>4650000.0</v>
       </c>
       <c r="AF261" s="14" t="inlineStr"/>
       <c r="AG261" s="14" t="inlineStr"/>
@@ -15767,14 +15767,14 @@
       <c r="N262" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000187. Pemeliharaan Genset 40 KVA</t>
+            <t xml:space="preserve">000182. Pemeliharaan Instalasi Listrik</t>
           </r>
         </is>
       </c>
       <c r="O262" s="13" t="inlineStr"/>
       <c r="P262" s="13" t="inlineStr"/>
       <c r="Q262" s="14" t="n">
-        <v>4050000.0</v>
+        <v>3.0E7</v>
       </c>
       <c r="R262" s="14" t="inlineStr"/>
       <c r="S262" s="14" t="n">
@@ -15784,23 +15784,23 @@
       <c r="U262" s="14" t="inlineStr"/>
       <c r="V262" s="14" t="inlineStr"/>
       <c r="W262" s="14" t="n">
-        <v>1050000.0</v>
+        <v>3861718.0</v>
       </c>
       <c r="X262" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y262" s="14" t="inlineStr"/>
       <c r="Z262" s="14" t="n">
-        <v>1050000.0</v>
+        <v>3861718.0</v>
       </c>
       <c r="AA262" s="14" t="inlineStr"/>
       <c r="AB262" s="14" t="inlineStr"/>
       <c r="AC262" s="15" t="n">
-        <v>0.25925925925925924</v>
+        <v>0.12872393333333335</v>
       </c>
       <c r="AD262" s="15" t="inlineStr"/>
       <c r="AE262" s="14" t="n">
-        <v>3000000.0</v>
+        <v>2.6138282E7</v>
       </c>
       <c r="AF262" s="14" t="inlineStr"/>
       <c r="AG262" s="14" t="inlineStr"/>
@@ -15824,14 +15824,14 @@
       <c r="N263" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000190. Pemeliharaan Mesin Potong Rumput</t>
+            <t xml:space="preserve">000183. Pemeliharaan Kendaraan Roda 4</t>
           </r>
         </is>
       </c>
       <c r="O263" s="13" t="inlineStr"/>
       <c r="P263" s="13" t="inlineStr"/>
       <c r="Q263" s="14" t="n">
-        <v>1.0E7</v>
+        <v>1.246E8</v>
       </c>
       <c r="R263" s="14" t="inlineStr"/>
       <c r="S263" s="14" t="n">
@@ -15841,23 +15841,23 @@
       <c r="U263" s="14" t="inlineStr"/>
       <c r="V263" s="14" t="inlineStr"/>
       <c r="W263" s="14" t="n">
-        <v>3707013.0</v>
+        <v>7.0853877E7</v>
       </c>
       <c r="X263" s="14" t="n">
-        <v>2348700.0</v>
+        <v>3390000.0</v>
       </c>
       <c r="Y263" s="14" t="inlineStr"/>
       <c r="Z263" s="14" t="n">
-        <v>6055713.0</v>
+        <v>7.4243877E7</v>
       </c>
       <c r="AA263" s="14" t="inlineStr"/>
       <c r="AB263" s="14" t="inlineStr"/>
       <c r="AC263" s="15" t="n">
-        <v>0.6055713</v>
+        <v>0.5958577608346709</v>
       </c>
       <c r="AD263" s="15" t="inlineStr"/>
       <c r="AE263" s="14" t="n">
-        <v>3944287.0</v>
+        <v>5.0356123E7</v>
       </c>
       <c r="AF263" s="14" t="inlineStr"/>
       <c r="AG263" s="14" t="inlineStr"/>
@@ -15881,14 +15881,14 @@
       <c r="N264" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000191. Pemeliharaan Printer</t>
+            <t xml:space="preserve">000184. Pemeliharaan Kendaraan Roda 2</t>
           </r>
         </is>
       </c>
       <c r="O264" s="13" t="inlineStr"/>
       <c r="P264" s="13" t="inlineStr"/>
       <c r="Q264" s="14" t="n">
-        <v>500000.0</v>
+        <v>4500000.0</v>
       </c>
       <c r="R264" s="14" t="inlineStr"/>
       <c r="S264" s="14" t="n">
@@ -15898,23 +15898,23 @@
       <c r="U264" s="14" t="inlineStr"/>
       <c r="V264" s="14" t="inlineStr"/>
       <c r="W264" s="14" t="n">
-        <v>417558.0</v>
+        <v>2410875.0</v>
       </c>
       <c r="X264" s="14" t="n">
-        <v>0.0</v>
+        <v>544027.0</v>
       </c>
       <c r="Y264" s="14" t="inlineStr"/>
       <c r="Z264" s="14" t="n">
-        <v>417558.0</v>
+        <v>2954902.0</v>
       </c>
       <c r="AA264" s="14" t="inlineStr"/>
       <c r="AB264" s="14" t="inlineStr"/>
       <c r="AC264" s="15" t="n">
-        <v>0.835116</v>
+        <v>0.6566448888888888</v>
       </c>
       <c r="AD264" s="15" t="inlineStr"/>
       <c r="AE264" s="14" t="n">
-        <v>82442.0</v>
+        <v>1545098.0</v>
       </c>
       <c r="AF264" s="14" t="inlineStr"/>
       <c r="AG264" s="14" t="inlineStr"/>
@@ -15938,14 +15938,14 @@
       <c r="N265" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000192. Pemeliharaan Komputer/PC</t>
+            <t xml:space="preserve">000185. Pemeliharaan CCTV</t>
           </r>
         </is>
       </c>
       <c r="O265" s="13" t="inlineStr"/>
       <c r="P265" s="13" t="inlineStr"/>
       <c r="Q265" s="14" t="n">
-        <v>5000000.0</v>
+        <v>6000000.0</v>
       </c>
       <c r="R265" s="14" t="inlineStr"/>
       <c r="S265" s="14" t="n">
@@ -15955,23 +15955,23 @@
       <c r="U265" s="14" t="inlineStr"/>
       <c r="V265" s="14" t="inlineStr"/>
       <c r="W265" s="14" t="n">
-        <v>969974.0</v>
+        <v>4737535.0</v>
       </c>
       <c r="X265" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y265" s="14" t="inlineStr"/>
       <c r="Z265" s="14" t="n">
-        <v>969974.0</v>
+        <v>4737535.0</v>
       </c>
       <c r="AA265" s="14" t="inlineStr"/>
       <c r="AB265" s="14" t="inlineStr"/>
       <c r="AC265" s="15" t="n">
-        <v>0.1939948</v>
+        <v>0.7895891666666667</v>
       </c>
       <c r="AD265" s="15" t="inlineStr"/>
       <c r="AE265" s="14" t="n">
-        <v>4030026.0</v>
+        <v>1262465.0</v>
       </c>
       <c r="AF265" s="14" t="inlineStr"/>
       <c r="AG265" s="14" t="inlineStr"/>
@@ -15995,14 +15995,14 @@
       <c r="N266" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000283. Pemeliharaan Kulkas</t>
+            <t xml:space="preserve">000186. Pemeliharaan Genset 250 KVA</t>
           </r>
         </is>
       </c>
       <c r="O266" s="13" t="inlineStr"/>
       <c r="P266" s="13" t="inlineStr"/>
       <c r="Q266" s="14" t="n">
-        <v>2000000.0</v>
+        <v>6010000.0</v>
       </c>
       <c r="R266" s="14" t="inlineStr"/>
       <c r="S266" s="14" t="n">
@@ -16012,23 +16012,23 @@
       <c r="U266" s="14" t="inlineStr"/>
       <c r="V266" s="14" t="inlineStr"/>
       <c r="W266" s="14" t="n">
-        <v>270000.0</v>
+        <v>1000052.0</v>
       </c>
       <c r="X266" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y266" s="14" t="inlineStr"/>
       <c r="Z266" s="14" t="n">
-        <v>270000.0</v>
+        <v>1000052.0</v>
       </c>
       <c r="AA266" s="14" t="inlineStr"/>
       <c r="AB266" s="14" t="inlineStr"/>
       <c r="AC266" s="15" t="n">
-        <v>0.135</v>
+        <v>0.166398003327787</v>
       </c>
       <c r="AD266" s="15" t="inlineStr"/>
       <c r="AE266" s="14" t="n">
-        <v>1730000.0</v>
+        <v>5009948.0</v>
       </c>
       <c r="AF266" s="14" t="inlineStr"/>
       <c r="AG266" s="14" t="inlineStr"/>
@@ -16043,29 +16043,23 @@
       <c r="E267" s="2" t="inlineStr"/>
       <c r="F267" s="2" t="inlineStr"/>
       <c r="G267" s="2" t="inlineStr"/>
-      <c r="H267" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">523132</t>
-          </r>
-        </is>
-      </c>
-      <c r="I267" s="13" t="inlineStr"/>
-      <c r="J267" s="13" t="inlineStr"/>
-      <c r="K267" s="13" t="inlineStr"/>
-      <c r="L267" s="13" t="inlineStr"/>
-      <c r="M267" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Pemeliharaan Irigasi</t>
-          </r>
-        </is>
-      </c>
-      <c r="N267" s="13" t="inlineStr"/>
+      <c r="H267" s="2" t="inlineStr"/>
+      <c r="I267" s="2" t="inlineStr"/>
+      <c r="J267" s="2" t="inlineStr"/>
+      <c r="K267" s="2" t="inlineStr"/>
+      <c r="L267" s="2" t="inlineStr"/>
+      <c r="M267" s="2" t="inlineStr"/>
+      <c r="N267" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000187. Pemeliharaan Genset 40 KVA</t>
+          </r>
+        </is>
+      </c>
       <c r="O267" s="13" t="inlineStr"/>
       <c r="P267" s="13" t="inlineStr"/>
       <c r="Q267" s="14" t="n">
-        <v>8.11E7</v>
+        <v>4050000.0</v>
       </c>
       <c r="R267" s="14" t="inlineStr"/>
       <c r="S267" s="14" t="n">
@@ -16075,23 +16069,23 @@
       <c r="U267" s="14" t="inlineStr"/>
       <c r="V267" s="14" t="inlineStr"/>
       <c r="W267" s="14" t="n">
-        <v>6.1416E7</v>
+        <v>1050000.0</v>
       </c>
       <c r="X267" s="14" t="n">
-        <v>0.0</v>
+        <v>158480.0</v>
       </c>
       <c r="Y267" s="14" t="inlineStr"/>
       <c r="Z267" s="14" t="n">
-        <v>6.1416E7</v>
+        <v>1208480.0</v>
       </c>
       <c r="AA267" s="14" t="inlineStr"/>
       <c r="AB267" s="14" t="inlineStr"/>
       <c r="AC267" s="15" t="n">
-        <v>0.7572872996300863</v>
+        <v>0.2983901234567901</v>
       </c>
       <c r="AD267" s="15" t="inlineStr"/>
       <c r="AE267" s="14" t="n">
-        <v>1.9684E7</v>
+        <v>2841520.0</v>
       </c>
       <c r="AF267" s="14" t="inlineStr"/>
       <c r="AG267" s="14" t="inlineStr"/>
@@ -16115,14 +16109,14 @@
       <c r="N268" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000195. Pemeliharaan Talud Cijeruk</t>
+            <t xml:space="preserve">000190. Pemeliharaan Mesin Potong Rumput</t>
           </r>
         </is>
       </c>
       <c r="O268" s="13" t="inlineStr"/>
       <c r="P268" s="13" t="inlineStr"/>
       <c r="Q268" s="14" t="n">
-        <v>3.91E7</v>
+        <v>1.0E7</v>
       </c>
       <c r="R268" s="14" t="inlineStr"/>
       <c r="S268" s="14" t="n">
@@ -16132,23 +16126,23 @@
       <c r="U268" s="14" t="inlineStr"/>
       <c r="V268" s="14" t="inlineStr"/>
       <c r="W268" s="14" t="n">
-        <v>3.909E7</v>
+        <v>6055713.0</v>
       </c>
       <c r="X268" s="14" t="n">
-        <v>0.0</v>
+        <v>728900.0</v>
       </c>
       <c r="Y268" s="14" t="inlineStr"/>
       <c r="Z268" s="14" t="n">
-        <v>3.909E7</v>
+        <v>6784613.0</v>
       </c>
       <c r="AA268" s="14" t="inlineStr"/>
       <c r="AB268" s="14" t="inlineStr"/>
       <c r="AC268" s="15" t="n">
-        <v>0.9997442455242966</v>
+        <v>0.6784613</v>
       </c>
       <c r="AD268" s="15" t="inlineStr"/>
       <c r="AE268" s="14" t="n">
-        <v>10000.0</v>
+        <v>3215387.0</v>
       </c>
       <c r="AF268" s="14" t="inlineStr"/>
       <c r="AG268" s="14" t="inlineStr"/>
@@ -16172,14 +16166,14 @@
       <c r="N269" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000284. Pemeliharaan Talud Cibalagung</t>
+            <t xml:space="preserve">000191. Pemeliharaan Printer</t>
           </r>
         </is>
       </c>
       <c r="O269" s="13" t="inlineStr"/>
       <c r="P269" s="13" t="inlineStr"/>
       <c r="Q269" s="14" t="n">
-        <v>3.0E7</v>
+        <v>500000.0</v>
       </c>
       <c r="R269" s="14" t="inlineStr"/>
       <c r="S269" s="14" t="n">
@@ -16189,23 +16183,23 @@
       <c r="U269" s="14" t="inlineStr"/>
       <c r="V269" s="14" t="inlineStr"/>
       <c r="W269" s="14" t="n">
-        <v>1.155E7</v>
+        <v>417558.0</v>
       </c>
       <c r="X269" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y269" s="14" t="inlineStr"/>
       <c r="Z269" s="14" t="n">
-        <v>1.155E7</v>
+        <v>417558.0</v>
       </c>
       <c r="AA269" s="14" t="inlineStr"/>
       <c r="AB269" s="14" t="inlineStr"/>
       <c r="AC269" s="15" t="n">
-        <v>0.385</v>
+        <v>0.835116</v>
       </c>
       <c r="AD269" s="15" t="inlineStr"/>
       <c r="AE269" s="14" t="n">
-        <v>1.845E7</v>
+        <v>82442.0</v>
       </c>
       <c r="AF269" s="14" t="inlineStr"/>
       <c r="AG269" s="14" t="inlineStr"/>
@@ -16229,14 +16223,14 @@
       <c r="N270" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000285. Pemeliharaan Saluran Air Cijeruk</t>
+            <t xml:space="preserve">000192. Pemeliharaan Komputer/PC</t>
           </r>
         </is>
       </c>
       <c r="O270" s="13" t="inlineStr"/>
       <c r="P270" s="13" t="inlineStr"/>
       <c r="Q270" s="14" t="n">
-        <v>1.2E7</v>
+        <v>5000000.0</v>
       </c>
       <c r="R270" s="14" t="inlineStr"/>
       <c r="S270" s="14" t="n">
@@ -16246,23 +16240,23 @@
       <c r="U270" s="14" t="inlineStr"/>
       <c r="V270" s="14" t="inlineStr"/>
       <c r="W270" s="14" t="n">
-        <v>1.0776E7</v>
+        <v>969974.0</v>
       </c>
       <c r="X270" s="14" t="n">
-        <v>0.0</v>
+        <v>243360.0</v>
       </c>
       <c r="Y270" s="14" t="inlineStr"/>
       <c r="Z270" s="14" t="n">
-        <v>1.0776E7</v>
+        <v>1213334.0</v>
       </c>
       <c r="AA270" s="14" t="inlineStr"/>
       <c r="AB270" s="14" t="inlineStr"/>
       <c r="AC270" s="15" t="n">
-        <v>0.898</v>
+        <v>0.2426668</v>
       </c>
       <c r="AD270" s="15" t="inlineStr"/>
       <c r="AE270" s="14" t="n">
-        <v>1224000.0</v>
+        <v>3786666.0</v>
       </c>
       <c r="AF270" s="14" t="inlineStr"/>
       <c r="AG270" s="14" t="inlineStr"/>
@@ -16275,31 +16269,25 @@
       <c r="C271" s="2" t="inlineStr"/>
       <c r="D271" s="2" t="inlineStr"/>
       <c r="E271" s="2" t="inlineStr"/>
-      <c r="F271" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">002.DD</t>
-          </r>
-        </is>
-      </c>
-      <c r="G271" s="13" t="inlineStr"/>
-      <c r="H271" s="13" t="inlineStr"/>
-      <c r="I271" s="13" t="inlineStr"/>
-      <c r="J271" s="13" t="inlineStr"/>
-      <c r="K271" s="13" t="inlineStr"/>
-      <c r="L271" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pembayaran Terkait Pelaksanaan Operasional Kantor</t>
-          </r>
-        </is>
-      </c>
-      <c r="M271" s="13" t="inlineStr"/>
-      <c r="N271" s="13" t="inlineStr"/>
+      <c r="F271" s="2" t="inlineStr"/>
+      <c r="G271" s="2" t="inlineStr"/>
+      <c r="H271" s="2" t="inlineStr"/>
+      <c r="I271" s="2" t="inlineStr"/>
+      <c r="J271" s="2" t="inlineStr"/>
+      <c r="K271" s="2" t="inlineStr"/>
+      <c r="L271" s="2" t="inlineStr"/>
+      <c r="M271" s="2" t="inlineStr"/>
+      <c r="N271" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000283. Pemeliharaan Kulkas</t>
+          </r>
+        </is>
+      </c>
       <c r="O271" s="13" t="inlineStr"/>
       <c r="P271" s="13" t="inlineStr"/>
       <c r="Q271" s="14" t="n">
-        <v>1.3218E8</v>
+        <v>500000.0</v>
       </c>
       <c r="R271" s="14" t="inlineStr"/>
       <c r="S271" s="14" t="n">
@@ -16309,23 +16297,23 @@
       <c r="U271" s="14" t="inlineStr"/>
       <c r="V271" s="14" t="inlineStr"/>
       <c r="W271" s="14" t="n">
-        <v>7.975E7</v>
+        <v>270000.0</v>
       </c>
       <c r="X271" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y271" s="14" t="inlineStr"/>
       <c r="Z271" s="14" t="n">
-        <v>7.975E7</v>
+        <v>270000.0</v>
       </c>
       <c r="AA271" s="14" t="inlineStr"/>
       <c r="AB271" s="14" t="inlineStr"/>
       <c r="AC271" s="15" t="n">
-        <v>0.6033439249508247</v>
+        <v>0.54</v>
       </c>
       <c r="AD271" s="15" t="inlineStr"/>
       <c r="AE271" s="14" t="n">
-        <v>5.243E7</v>
+        <v>230000.0</v>
       </c>
       <c r="AF271" s="14" t="inlineStr"/>
       <c r="AG271" s="14" t="inlineStr"/>
@@ -16343,7 +16331,7 @@
       <c r="H272" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">521115</t>
+            <t xml:space="preserve">523132</t>
           </r>
         </is>
       </c>
@@ -16354,7 +16342,7 @@
       <c r="M272" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Belanja Honor Operasional Satuan Kerja</t>
+            <t xml:space="preserve">Belanja Pemeliharaan Irigasi</t>
           </r>
         </is>
       </c>
@@ -16362,7 +16350,7 @@
       <c r="O272" s="13" t="inlineStr"/>
       <c r="P272" s="13" t="inlineStr"/>
       <c r="Q272" s="14" t="n">
-        <v>1.2468E8</v>
+        <v>8.11E7</v>
       </c>
       <c r="R272" s="14" t="inlineStr"/>
       <c r="S272" s="14" t="n">
@@ -16372,23 +16360,23 @@
       <c r="U272" s="14" t="inlineStr"/>
       <c r="V272" s="14" t="inlineStr"/>
       <c r="W272" s="14" t="n">
-        <v>7.225E7</v>
+        <v>6.1416E7</v>
       </c>
       <c r="X272" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y272" s="14" t="inlineStr"/>
       <c r="Z272" s="14" t="n">
-        <v>7.225E7</v>
+        <v>6.1416E7</v>
       </c>
       <c r="AA272" s="14" t="inlineStr"/>
       <c r="AB272" s="14" t="inlineStr"/>
       <c r="AC272" s="15" t="n">
-        <v>0.5794834777029195</v>
+        <v>0.7572872996300863</v>
       </c>
       <c r="AD272" s="15" t="inlineStr"/>
       <c r="AE272" s="14" t="n">
-        <v>5.243E7</v>
+        <v>1.9684E7</v>
       </c>
       <c r="AF272" s="14" t="inlineStr"/>
       <c r="AG272" s="14" t="inlineStr"/>
@@ -16412,14 +16400,14 @@
       <c r="N273" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000197. Honorarium Pejabat Kuasa Pengguna Anggaran</t>
+            <t xml:space="preserve">000195. Pemeliharaan Talud Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O273" s="13" t="inlineStr"/>
       <c r="P273" s="13" t="inlineStr"/>
       <c r="Q273" s="14" t="n">
-        <v>3.06E7</v>
+        <v>3.91E7</v>
       </c>
       <c r="R273" s="14" t="inlineStr"/>
       <c r="S273" s="14" t="n">
@@ -16429,23 +16417,23 @@
       <c r="U273" s="14" t="inlineStr"/>
       <c r="V273" s="14" t="inlineStr"/>
       <c r="W273" s="14" t="n">
-        <v>1.785E7</v>
+        <v>3.909E7</v>
       </c>
       <c r="X273" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y273" s="14" t="inlineStr"/>
       <c r="Z273" s="14" t="n">
-        <v>1.785E7</v>
+        <v>3.909E7</v>
       </c>
       <c r="AA273" s="14" t="inlineStr"/>
       <c r="AB273" s="14" t="inlineStr"/>
       <c r="AC273" s="15" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.9997442455242966</v>
       </c>
       <c r="AD273" s="15" t="inlineStr"/>
       <c r="AE273" s="14" t="n">
-        <v>1.275E7</v>
+        <v>10000.0</v>
       </c>
       <c r="AF273" s="14" t="inlineStr"/>
       <c r="AG273" s="14" t="inlineStr"/>
@@ -16469,14 +16457,14 @@
       <c r="N274" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000198. Honorarium Pejabat Pembuat Komitmen</t>
+            <t xml:space="preserve">000284. Pemeliharaan Talud Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O274" s="13" t="inlineStr"/>
       <c r="P274" s="13" t="inlineStr"/>
       <c r="Q274" s="14" t="n">
-        <v>2.976E7</v>
+        <v>3.0E7</v>
       </c>
       <c r="R274" s="14" t="inlineStr"/>
       <c r="S274" s="14" t="n">
@@ -16486,30 +16474,30 @@
       <c r="U274" s="14" t="inlineStr"/>
       <c r="V274" s="14" t="inlineStr"/>
       <c r="W274" s="14" t="n">
-        <v>1.736E7</v>
+        <v>1.155E7</v>
       </c>
       <c r="X274" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y274" s="14" t="inlineStr"/>
       <c r="Z274" s="14" t="n">
-        <v>1.736E7</v>
+        <v>1.155E7</v>
       </c>
       <c r="AA274" s="14" t="inlineStr"/>
       <c r="AB274" s="14" t="inlineStr"/>
       <c r="AC274" s="15" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.385</v>
       </c>
       <c r="AD274" s="15" t="inlineStr"/>
       <c r="AE274" s="14" t="n">
-        <v>1.24E7</v>
+        <v>1.845E7</v>
       </c>
       <c r="AF274" s="14" t="inlineStr"/>
       <c r="AG274" s="14" t="inlineStr"/>
       <c r="AH274" s="14" t="inlineStr"/>
       <c r="AI274" s="14" t="inlineStr"/>
     </row>
-    <row r="275" customHeight="1" ht="18">
+    <row r="275" customHeight="1" ht="15">
       <c r="A275" s="2" t="inlineStr"/>
       <c r="B275" s="2" t="inlineStr"/>
       <c r="C275" s="2" t="inlineStr"/>
@@ -16526,14 +16514,14 @@
       <c r="N275" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000199. Honorarium Pejabat  Penguji Tagihan   Penandatangan  Spm</t>
+            <t xml:space="preserve">000285. Pemeliharaan Saluran Air Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O275" s="13" t="inlineStr"/>
       <c r="P275" s="13" t="inlineStr"/>
       <c r="Q275" s="14" t="n">
-        <v>1.476E7</v>
+        <v>1.2E7</v>
       </c>
       <c r="R275" s="14" t="inlineStr"/>
       <c r="S275" s="14" t="n">
@@ -16543,23 +16531,23 @@
       <c r="U275" s="14" t="inlineStr"/>
       <c r="V275" s="14" t="inlineStr"/>
       <c r="W275" s="14" t="n">
-        <v>8610000.0</v>
+        <v>1.0776E7</v>
       </c>
       <c r="X275" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y275" s="14" t="inlineStr"/>
       <c r="Z275" s="14" t="n">
-        <v>8610000.0</v>
+        <v>1.0776E7</v>
       </c>
       <c r="AA275" s="14" t="inlineStr"/>
       <c r="AB275" s="14" t="inlineStr"/>
       <c r="AC275" s="15" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.898</v>
       </c>
       <c r="AD275" s="15" t="inlineStr"/>
       <c r="AE275" s="14" t="n">
-        <v>6150000.0</v>
+        <v>1224000.0</v>
       </c>
       <c r="AF275" s="14" t="inlineStr"/>
       <c r="AG275" s="14" t="inlineStr"/>
@@ -16572,25 +16560,31 @@
       <c r="C276" s="2" t="inlineStr"/>
       <c r="D276" s="2" t="inlineStr"/>
       <c r="E276" s="2" t="inlineStr"/>
-      <c r="F276" s="2" t="inlineStr"/>
-      <c r="G276" s="2" t="inlineStr"/>
-      <c r="H276" s="2" t="inlineStr"/>
-      <c r="I276" s="2" t="inlineStr"/>
-      <c r="J276" s="2" t="inlineStr"/>
-      <c r="K276" s="2" t="inlineStr"/>
-      <c r="L276" s="2" t="inlineStr"/>
-      <c r="M276" s="2" t="inlineStr"/>
-      <c r="N276" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000200. Honorarium Bendahara  Pengeluaran</t>
-          </r>
-        </is>
-      </c>
+      <c r="F276" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">002.DD</t>
+          </r>
+        </is>
+      </c>
+      <c r="G276" s="13" t="inlineStr"/>
+      <c r="H276" s="13" t="inlineStr"/>
+      <c r="I276" s="13" t="inlineStr"/>
+      <c r="J276" s="13" t="inlineStr"/>
+      <c r="K276" s="13" t="inlineStr"/>
+      <c r="L276" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pembayaran Terkait Pelaksanaan Operasional Kantor</t>
+          </r>
+        </is>
+      </c>
+      <c r="M276" s="13" t="inlineStr"/>
+      <c r="N276" s="13" t="inlineStr"/>
       <c r="O276" s="13" t="inlineStr"/>
       <c r="P276" s="13" t="inlineStr"/>
       <c r="Q276" s="14" t="n">
-        <v>1.284E7</v>
+        <v>1.3218E8</v>
       </c>
       <c r="R276" s="14" t="inlineStr"/>
       <c r="S276" s="14" t="n">
@@ -16600,23 +16594,23 @@
       <c r="U276" s="14" t="inlineStr"/>
       <c r="V276" s="14" t="inlineStr"/>
       <c r="W276" s="14" t="n">
-        <v>7490000.0</v>
+        <v>7.975E7</v>
       </c>
       <c r="X276" s="14" t="n">
-        <v>0.0</v>
+        <v>1.039E7</v>
       </c>
       <c r="Y276" s="14" t="inlineStr"/>
       <c r="Z276" s="14" t="n">
-        <v>7490000.0</v>
+        <v>9.014E7</v>
       </c>
       <c r="AA276" s="14" t="inlineStr"/>
       <c r="AB276" s="14" t="inlineStr"/>
       <c r="AC276" s="15" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6819488576183992</v>
       </c>
       <c r="AD276" s="15" t="inlineStr"/>
       <c r="AE276" s="14" t="n">
-        <v>5350000.0</v>
+        <v>4.204E7</v>
       </c>
       <c r="AF276" s="14" t="inlineStr"/>
       <c r="AG276" s="14" t="inlineStr"/>
@@ -16631,23 +16625,29 @@
       <c r="E277" s="2" t="inlineStr"/>
       <c r="F277" s="2" t="inlineStr"/>
       <c r="G277" s="2" t="inlineStr"/>
-      <c r="H277" s="2" t="inlineStr"/>
-      <c r="I277" s="2" t="inlineStr"/>
-      <c r="J277" s="2" t="inlineStr"/>
-      <c r="K277" s="2" t="inlineStr"/>
-      <c r="L277" s="2" t="inlineStr"/>
-      <c r="M277" s="2" t="inlineStr"/>
-      <c r="N277" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000201. Honorarium Staf  Pengelola</t>
-          </r>
-        </is>
-      </c>
+      <c r="H277" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521115</t>
+          </r>
+        </is>
+      </c>
+      <c r="I277" s="13" t="inlineStr"/>
+      <c r="J277" s="13" t="inlineStr"/>
+      <c r="K277" s="13" t="inlineStr"/>
+      <c r="L277" s="13" t="inlineStr"/>
+      <c r="M277" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Honor Operasional Satuan Kerja</t>
+          </r>
+        </is>
+      </c>
+      <c r="N277" s="13" t="inlineStr"/>
       <c r="O277" s="13" t="inlineStr"/>
       <c r="P277" s="13" t="inlineStr"/>
       <c r="Q277" s="14" t="n">
-        <v>2.88E7</v>
+        <v>1.2468E8</v>
       </c>
       <c r="R277" s="14" t="inlineStr"/>
       <c r="S277" s="14" t="n">
@@ -16657,23 +16657,23 @@
       <c r="U277" s="14" t="inlineStr"/>
       <c r="V277" s="14" t="inlineStr"/>
       <c r="W277" s="14" t="n">
-        <v>1.68E7</v>
+        <v>7.225E7</v>
       </c>
       <c r="X277" s="14" t="n">
-        <v>0.0</v>
+        <v>1.039E7</v>
       </c>
       <c r="Y277" s="14" t="inlineStr"/>
       <c r="Z277" s="14" t="n">
-        <v>1.68E7</v>
+        <v>8.264E7</v>
       </c>
       <c r="AA277" s="14" t="inlineStr"/>
       <c r="AB277" s="14" t="inlineStr"/>
       <c r="AC277" s="15" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6628168110362528</v>
       </c>
       <c r="AD277" s="15" t="inlineStr"/>
       <c r="AE277" s="14" t="n">
-        <v>1.2E7</v>
+        <v>4.204E7</v>
       </c>
       <c r="AF277" s="14" t="inlineStr"/>
       <c r="AG277" s="14" t="inlineStr"/>
@@ -16697,14 +16697,14 @@
       <c r="N278" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000202. Honorarium Anggota/Petugas (UAKPA/Barang)</t>
+            <t xml:space="preserve">000197. Honorarium Pejabat Kuasa Pengguna Anggaran</t>
           </r>
         </is>
       </c>
       <c r="O278" s="13" t="inlineStr"/>
       <c r="P278" s="13" t="inlineStr"/>
       <c r="Q278" s="14" t="n">
-        <v>3600000.0</v>
+        <v>3.06E7</v>
       </c>
       <c r="R278" s="14" t="inlineStr"/>
       <c r="S278" s="14" t="n">
@@ -16714,30 +16714,30 @@
       <c r="U278" s="14" t="inlineStr"/>
       <c r="V278" s="14" t="inlineStr"/>
       <c r="W278" s="14" t="n">
-        <v>1800000.0</v>
+        <v>1.785E7</v>
       </c>
       <c r="X278" s="14" t="n">
-        <v>0.0</v>
+        <v>2550000.0</v>
       </c>
       <c r="Y278" s="14" t="inlineStr"/>
       <c r="Z278" s="14" t="n">
-        <v>1800000.0</v>
+        <v>2.04E7</v>
       </c>
       <c r="AA278" s="14" t="inlineStr"/>
       <c r="AB278" s="14" t="inlineStr"/>
       <c r="AC278" s="15" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AD278" s="15" t="inlineStr"/>
       <c r="AE278" s="14" t="n">
-        <v>1800000.0</v>
+        <v>1.02E7</v>
       </c>
       <c r="AF278" s="14" t="inlineStr"/>
       <c r="AG278" s="14" t="inlineStr"/>
       <c r="AH278" s="14" t="inlineStr"/>
       <c r="AI278" s="14" t="inlineStr"/>
     </row>
-    <row r="279" customHeight="1" ht="18">
+    <row r="279" customHeight="1" ht="15">
       <c r="A279" s="2" t="inlineStr"/>
       <c r="B279" s="2" t="inlineStr"/>
       <c r="C279" s="2" t="inlineStr"/>
@@ -16754,14 +16754,14 @@
       <c r="N279" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000203. Honorarium Pengurus/Penyimpan Bmn Tingkat Kuasa Pengguna Barang</t>
+            <t xml:space="preserve">000198. Honorarium Pejabat Pembuat Komitmen</t>
           </r>
         </is>
       </c>
       <c r="O279" s="13" t="inlineStr"/>
       <c r="P279" s="13" t="inlineStr"/>
       <c r="Q279" s="14" t="n">
-        <v>4320000.0</v>
+        <v>2.976E7</v>
       </c>
       <c r="R279" s="14" t="inlineStr"/>
       <c r="S279" s="14" t="n">
@@ -16771,30 +16771,30 @@
       <c r="U279" s="14" t="inlineStr"/>
       <c r="V279" s="14" t="inlineStr"/>
       <c r="W279" s="14" t="n">
-        <v>2340000.0</v>
+        <v>1.736E7</v>
       </c>
       <c r="X279" s="14" t="n">
-        <v>0.0</v>
+        <v>2480000.0</v>
       </c>
       <c r="Y279" s="14" t="inlineStr"/>
       <c r="Z279" s="14" t="n">
-        <v>2340000.0</v>
+        <v>1.984E7</v>
       </c>
       <c r="AA279" s="14" t="inlineStr"/>
       <c r="AB279" s="14" t="inlineStr"/>
       <c r="AC279" s="15" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AD279" s="15" t="inlineStr"/>
       <c r="AE279" s="14" t="n">
-        <v>1980000.0</v>
+        <v>9920000.0</v>
       </c>
       <c r="AF279" s="14" t="inlineStr"/>
       <c r="AG279" s="14" t="inlineStr"/>
       <c r="AH279" s="14" t="inlineStr"/>
       <c r="AI279" s="14" t="inlineStr"/>
     </row>
-    <row r="280" customHeight="1" ht="15">
+    <row r="280" customHeight="1" ht="18">
       <c r="A280" s="2" t="inlineStr"/>
       <c r="B280" s="2" t="inlineStr"/>
       <c r="C280" s="2" t="inlineStr"/>
@@ -16802,29 +16802,23 @@
       <c r="E280" s="2" t="inlineStr"/>
       <c r="F280" s="2" t="inlineStr"/>
       <c r="G280" s="2" t="inlineStr"/>
-      <c r="H280" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521119</t>
-          </r>
-        </is>
-      </c>
-      <c r="I280" s="13" t="inlineStr"/>
-      <c r="J280" s="13" t="inlineStr"/>
-      <c r="K280" s="13" t="inlineStr"/>
-      <c r="L280" s="13" t="inlineStr"/>
-      <c r="M280" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N280" s="13" t="inlineStr"/>
+      <c r="H280" s="2" t="inlineStr"/>
+      <c r="I280" s="2" t="inlineStr"/>
+      <c r="J280" s="2" t="inlineStr"/>
+      <c r="K280" s="2" t="inlineStr"/>
+      <c r="L280" s="2" t="inlineStr"/>
+      <c r="M280" s="2" t="inlineStr"/>
+      <c r="N280" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000199. Honorarium Pejabat  Penguji Tagihan   Penandatangan  Spm</t>
+          </r>
+        </is>
+      </c>
       <c r="O280" s="13" t="inlineStr"/>
       <c r="P280" s="13" t="inlineStr"/>
       <c r="Q280" s="14" t="n">
-        <v>7500000.0</v>
+        <v>1.476E7</v>
       </c>
       <c r="R280" s="14" t="inlineStr"/>
       <c r="S280" s="14" t="n">
@@ -16834,23 +16828,23 @@
       <c r="U280" s="14" t="inlineStr"/>
       <c r="V280" s="14" t="inlineStr"/>
       <c r="W280" s="14" t="n">
-        <v>7500000.0</v>
+        <v>8610000.0</v>
       </c>
       <c r="X280" s="14" t="n">
-        <v>0.0</v>
+        <v>1230000.0</v>
       </c>
       <c r="Y280" s="14" t="inlineStr"/>
       <c r="Z280" s="14" t="n">
-        <v>7500000.0</v>
+        <v>9840000.0</v>
       </c>
       <c r="AA280" s="14" t="inlineStr"/>
       <c r="AB280" s="14" t="inlineStr"/>
       <c r="AC280" s="15" t="n">
-        <v>1.0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AD280" s="15" t="inlineStr"/>
       <c r="AE280" s="14" t="n">
-        <v>0.0</v>
+        <v>4920000.0</v>
       </c>
       <c r="AF280" s="14" t="inlineStr"/>
       <c r="AG280" s="14" t="inlineStr"/>
@@ -16874,14 +16868,14 @@
       <c r="N281" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000243. Pakaian Kerja PJLP</t>
+            <t xml:space="preserve">000200. Honorarium Bendahara  Pengeluaran</t>
           </r>
         </is>
       </c>
       <c r="O281" s="13" t="inlineStr"/>
       <c r="P281" s="13" t="inlineStr"/>
       <c r="Q281" s="14" t="n">
-        <v>7500000.0</v>
+        <v>1.284E7</v>
       </c>
       <c r="R281" s="14" t="inlineStr"/>
       <c r="S281" s="14" t="n">
@@ -16891,23 +16885,23 @@
       <c r="U281" s="14" t="inlineStr"/>
       <c r="V281" s="14" t="inlineStr"/>
       <c r="W281" s="14" t="n">
-        <v>7500000.0</v>
+        <v>7490000.0</v>
       </c>
       <c r="X281" s="14" t="n">
-        <v>0.0</v>
+        <v>1070000.0</v>
       </c>
       <c r="Y281" s="14" t="inlineStr"/>
       <c r="Z281" s="14" t="n">
-        <v>7500000.0</v>
+        <v>8560000.0</v>
       </c>
       <c r="AA281" s="14" t="inlineStr"/>
       <c r="AB281" s="14" t="inlineStr"/>
       <c r="AC281" s="15" t="n">
-        <v>1.0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AD281" s="15" t="inlineStr"/>
       <c r="AE281" s="14" t="n">
-        <v>0.0</v>
+        <v>4280000.0</v>
       </c>
       <c r="AF281" s="14" t="inlineStr"/>
       <c r="AG281" s="14" t="inlineStr"/>
@@ -16960,191 +16954,173 @@
     <row r="283" customHeight="1" ht="15">
       <c r="A283" s="2" t="inlineStr"/>
       <c r="B283" s="2" t="inlineStr"/>
-      <c r="C283" s="16" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">EBD</t>
-          </r>
-        </is>
-      </c>
-      <c r="D283" s="16" t="inlineStr"/>
-      <c r="E283" s="16" t="inlineStr"/>
-      <c r="F283" s="16" t="inlineStr"/>
-      <c r="G283" s="16" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Manajemen Kinerja Internal</t>
-          </r>
-        </is>
-      </c>
-      <c r="H283" s="16" t="inlineStr"/>
-      <c r="I283" s="16" t="inlineStr"/>
-      <c r="J283" s="16" t="inlineStr"/>
-      <c r="K283" s="16" t="inlineStr"/>
-      <c r="L283" s="16" t="inlineStr"/>
-      <c r="M283" s="16" t="inlineStr"/>
-      <c r="N283" s="16" t="inlineStr"/>
-      <c r="O283" s="16" t="inlineStr"/>
-      <c r="P283" s="16" t="inlineStr"/>
-      <c r="Q283" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="R283" s="17" t="inlineStr"/>
-      <c r="S283" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T283" s="17" t="inlineStr"/>
-      <c r="U283" s="17" t="inlineStr"/>
-      <c r="V283" s="17" t="inlineStr"/>
-      <c r="W283" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="X283" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y283" s="17" t="inlineStr"/>
-      <c r="Z283" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="AA283" s="17" t="inlineStr"/>
-      <c r="AB283" s="17" t="inlineStr"/>
-      <c r="AC283" s="18" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AD283" s="18" t="inlineStr"/>
-      <c r="AE283" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF283" s="17" t="inlineStr"/>
-      <c r="AG283" s="17" t="inlineStr"/>
-      <c r="AH283" s="17" t="inlineStr"/>
-      <c r="AI283" s="17" t="inlineStr"/>
+      <c r="C283" s="2" t="inlineStr"/>
+      <c r="D283" s="2" t="inlineStr"/>
+      <c r="E283" s="2" t="inlineStr"/>
+      <c r="F283" s="2" t="inlineStr"/>
+      <c r="G283" s="2" t="inlineStr"/>
+      <c r="H283" s="2" t="inlineStr"/>
+      <c r="I283" s="2" t="inlineStr"/>
+      <c r="J283" s="2" t="inlineStr"/>
+      <c r="K283" s="2" t="inlineStr"/>
+      <c r="L283" s="2" t="inlineStr"/>
+      <c r="M283" s="2" t="inlineStr"/>
+      <c r="N283" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000201. Honorarium Staf  Pengelola</t>
+          </r>
+        </is>
+      </c>
+      <c r="O283" s="13" t="inlineStr"/>
+      <c r="P283" s="13" t="inlineStr"/>
+      <c r="Q283" s="14" t="n">
+        <v>2.88E7</v>
+      </c>
+      <c r="R283" s="14" t="inlineStr"/>
+      <c r="S283" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T283" s="14" t="inlineStr"/>
+      <c r="U283" s="14" t="inlineStr"/>
+      <c r="V283" s="14" t="inlineStr"/>
+      <c r="W283" s="14" t="n">
+        <v>1.68E7</v>
+      </c>
+      <c r="X283" s="14" t="n">
+        <v>2400000.0</v>
+      </c>
+      <c r="Y283" s="14" t="inlineStr"/>
+      <c r="Z283" s="14" t="n">
+        <v>1.92E7</v>
+      </c>
+      <c r="AA283" s="14" t="inlineStr"/>
+      <c r="AB283" s="14" t="inlineStr"/>
+      <c r="AC283" s="15" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AD283" s="15" t="inlineStr"/>
+      <c r="AE283" s="14" t="n">
+        <v>9600000.0</v>
+      </c>
+      <c r="AF283" s="14" t="inlineStr"/>
+      <c r="AG283" s="14" t="inlineStr"/>
+      <c r="AH283" s="14" t="inlineStr"/>
+      <c r="AI283" s="14" t="inlineStr"/>
     </row>
     <row r="284" customHeight="1" ht="15">
       <c r="A284" s="2" t="inlineStr"/>
       <c r="B284" s="2" t="inlineStr"/>
-      <c r="C284" s="28" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">EBD.955</t>
-          </r>
-        </is>
-      </c>
-      <c r="D284" s="28" t="inlineStr"/>
-      <c r="E284" s="28" t="inlineStr"/>
-      <c r="F284" s="28" t="inlineStr"/>
-      <c r="G284" s="28" t="inlineStr"/>
-      <c r="H284" s="28" t="inlineStr"/>
-      <c r="I284" s="28" t="inlineStr"/>
-      <c r="J284" s="28" t="inlineStr"/>
-      <c r="K284" s="20" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Manajemen Keuangan</t>
-          </r>
-        </is>
-      </c>
-      <c r="L284" s="20" t="inlineStr"/>
-      <c r="M284" s="20" t="inlineStr"/>
-      <c r="N284" s="20" t="inlineStr"/>
-      <c r="O284" s="20" t="inlineStr"/>
-      <c r="P284" s="20" t="inlineStr"/>
-      <c r="Q284" s="21" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="R284" s="21" t="inlineStr"/>
-      <c r="S284" s="21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T284" s="21" t="inlineStr"/>
-      <c r="U284" s="21" t="inlineStr"/>
-      <c r="V284" s="21" t="inlineStr"/>
-      <c r="W284" s="22" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="X284" s="22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y284" s="22" t="inlineStr"/>
-      <c r="Z284" s="21" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="AA284" s="21" t="inlineStr"/>
-      <c r="AB284" s="21" t="inlineStr"/>
-      <c r="AC284" s="23" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AD284" s="23" t="inlineStr"/>
-      <c r="AE284" s="21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF284" s="21" t="inlineStr"/>
-      <c r="AG284" s="21" t="inlineStr"/>
-      <c r="AH284" s="21" t="inlineStr"/>
-      <c r="AI284" s="21" t="inlineStr"/>
-    </row>
-    <row r="285" customHeight="1" ht="15">
+      <c r="C284" s="2" t="inlineStr"/>
+      <c r="D284" s="2" t="inlineStr"/>
+      <c r="E284" s="2" t="inlineStr"/>
+      <c r="F284" s="2" t="inlineStr"/>
+      <c r="G284" s="2" t="inlineStr"/>
+      <c r="H284" s="2" t="inlineStr"/>
+      <c r="I284" s="2" t="inlineStr"/>
+      <c r="J284" s="2" t="inlineStr"/>
+      <c r="K284" s="2" t="inlineStr"/>
+      <c r="L284" s="2" t="inlineStr"/>
+      <c r="M284" s="2" t="inlineStr"/>
+      <c r="N284" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000202. Honorarium Anggota/Petugas (UAKPA/Barang)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O284" s="13" t="inlineStr"/>
+      <c r="P284" s="13" t="inlineStr"/>
+      <c r="Q284" s="14" t="n">
+        <v>3600000.0</v>
+      </c>
+      <c r="R284" s="14" t="inlineStr"/>
+      <c r="S284" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T284" s="14" t="inlineStr"/>
+      <c r="U284" s="14" t="inlineStr"/>
+      <c r="V284" s="14" t="inlineStr"/>
+      <c r="W284" s="14" t="n">
+        <v>1800000.0</v>
+      </c>
+      <c r="X284" s="14" t="n">
+        <v>300000.0</v>
+      </c>
+      <c r="Y284" s="14" t="inlineStr"/>
+      <c r="Z284" s="14" t="n">
+        <v>2100000.0</v>
+      </c>
+      <c r="AA284" s="14" t="inlineStr"/>
+      <c r="AB284" s="14" t="inlineStr"/>
+      <c r="AC284" s="15" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="AD284" s="15" t="inlineStr"/>
+      <c r="AE284" s="14" t="n">
+        <v>1500000.0</v>
+      </c>
+      <c r="AF284" s="14" t="inlineStr"/>
+      <c r="AG284" s="14" t="inlineStr"/>
+      <c r="AH284" s="14" t="inlineStr"/>
+      <c r="AI284" s="14" t="inlineStr"/>
+    </row>
+    <row r="285" customHeight="1" ht="18">
       <c r="A285" s="2" t="inlineStr"/>
       <c r="B285" s="2" t="inlineStr"/>
       <c r="C285" s="2" t="inlineStr"/>
       <c r="D285" s="2" t="inlineStr"/>
-      <c r="E285" s="24" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">201</t>
-          </r>
-        </is>
-      </c>
-      <c r="F285" s="24" t="inlineStr"/>
-      <c r="G285" s="24" t="inlineStr"/>
-      <c r="H285" s="24" t="inlineStr"/>
-      <c r="I285" s="24" t="inlineStr"/>
-      <c r="J285" s="24" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pelayanan Keuangan Penyuluhan Kelautan dan Perikanan</t>
-          </r>
-        </is>
-      </c>
-      <c r="K285" s="24" t="inlineStr"/>
-      <c r="L285" s="24" t="inlineStr"/>
-      <c r="M285" s="24" t="inlineStr"/>
-      <c r="N285" s="24" t="inlineStr"/>
-      <c r="O285" s="24" t="inlineStr"/>
-      <c r="P285" s="24" t="inlineStr"/>
-      <c r="Q285" s="25" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="R285" s="25" t="inlineStr"/>
-      <c r="S285" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T285" s="25" t="inlineStr"/>
-      <c r="U285" s="25" t="inlineStr"/>
-      <c r="V285" s="25" t="inlineStr"/>
-      <c r="W285" s="25" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="X285" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y285" s="25" t="inlineStr"/>
-      <c r="Z285" s="25" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="AA285" s="25" t="inlineStr"/>
-      <c r="AB285" s="25" t="inlineStr"/>
-      <c r="AC285" s="26" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AD285" s="26" t="inlineStr"/>
-      <c r="AE285" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF285" s="25" t="inlineStr"/>
-      <c r="AG285" s="25" t="inlineStr"/>
-      <c r="AH285" s="25" t="inlineStr"/>
-      <c r="AI285" s="25" t="inlineStr"/>
+      <c r="E285" s="2" t="inlineStr"/>
+      <c r="F285" s="2" t="inlineStr"/>
+      <c r="G285" s="2" t="inlineStr"/>
+      <c r="H285" s="2" t="inlineStr"/>
+      <c r="I285" s="2" t="inlineStr"/>
+      <c r="J285" s="2" t="inlineStr"/>
+      <c r="K285" s="2" t="inlineStr"/>
+      <c r="L285" s="2" t="inlineStr"/>
+      <c r="M285" s="2" t="inlineStr"/>
+      <c r="N285" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000203. Honorarium Pengurus/Penyimpan Bmn Tingkat Kuasa Pengguna Barang</t>
+          </r>
+        </is>
+      </c>
+      <c r="O285" s="13" t="inlineStr"/>
+      <c r="P285" s="13" t="inlineStr"/>
+      <c r="Q285" s="14" t="n">
+        <v>4320000.0</v>
+      </c>
+      <c r="R285" s="14" t="inlineStr"/>
+      <c r="S285" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T285" s="14" t="inlineStr"/>
+      <c r="U285" s="14" t="inlineStr"/>
+      <c r="V285" s="14" t="inlineStr"/>
+      <c r="W285" s="14" t="n">
+        <v>2340000.0</v>
+      </c>
+      <c r="X285" s="14" t="n">
+        <v>360000.0</v>
+      </c>
+      <c r="Y285" s="14" t="inlineStr"/>
+      <c r="Z285" s="14" t="n">
+        <v>2700000.0</v>
+      </c>
+      <c r="AA285" s="14" t="inlineStr"/>
+      <c r="AB285" s="14" t="inlineStr"/>
+      <c r="AC285" s="15" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AD285" s="15" t="inlineStr"/>
+      <c r="AE285" s="14" t="n">
+        <v>1620000.0</v>
+      </c>
+      <c r="AF285" s="14" t="inlineStr"/>
+      <c r="AG285" s="14" t="inlineStr"/>
+      <c r="AH285" s="14" t="inlineStr"/>
+      <c r="AI285" s="14" t="inlineStr"/>
     </row>
     <row r="286" customHeight="1" ht="15">
       <c r="A286" s="2" t="inlineStr"/>
@@ -17152,31 +17128,31 @@
       <c r="C286" s="2" t="inlineStr"/>
       <c r="D286" s="2" t="inlineStr"/>
       <c r="E286" s="2" t="inlineStr"/>
-      <c r="F286" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">201.DA</t>
-          </r>
-        </is>
-      </c>
-      <c r="G286" s="13" t="inlineStr"/>
-      <c r="H286" s="13" t="inlineStr"/>
+      <c r="F286" s="2" t="inlineStr"/>
+      <c r="G286" s="2" t="inlineStr"/>
+      <c r="H286" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521119</t>
+          </r>
+        </is>
+      </c>
       <c r="I286" s="13" t="inlineStr"/>
       <c r="J286" s="13" t="inlineStr"/>
       <c r="K286" s="13" t="inlineStr"/>
-      <c r="L286" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Keuangan</t>
-          </r>
-        </is>
-      </c>
-      <c r="M286" s="13" t="inlineStr"/>
+      <c r="L286" s="13" t="inlineStr"/>
+      <c r="M286" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
+          </r>
+        </is>
+      </c>
       <c r="N286" s="13" t="inlineStr"/>
       <c r="O286" s="13" t="inlineStr"/>
       <c r="P286" s="13" t="inlineStr"/>
       <c r="Q286" s="14" t="n">
-        <v>600000.0</v>
+        <v>7500000.0</v>
       </c>
       <c r="R286" s="14" t="inlineStr"/>
       <c r="S286" s="14" t="n">
@@ -17186,14 +17162,14 @@
       <c r="U286" s="14" t="inlineStr"/>
       <c r="V286" s="14" t="inlineStr"/>
       <c r="W286" s="14" t="n">
-        <v>600000.0</v>
+        <v>7500000.0</v>
       </c>
       <c r="X286" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y286" s="14" t="inlineStr"/>
       <c r="Z286" s="14" t="n">
-        <v>600000.0</v>
+        <v>7500000.0</v>
       </c>
       <c r="AA286" s="14" t="inlineStr"/>
       <c r="AB286" s="14" t="inlineStr"/>
@@ -17217,29 +17193,23 @@
       <c r="E287" s="2" t="inlineStr"/>
       <c r="F287" s="2" t="inlineStr"/>
       <c r="G287" s="2" t="inlineStr"/>
-      <c r="H287" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">524111</t>
-          </r>
-        </is>
-      </c>
-      <c r="I287" s="13" t="inlineStr"/>
-      <c r="J287" s="13" t="inlineStr"/>
-      <c r="K287" s="13" t="inlineStr"/>
-      <c r="L287" s="13" t="inlineStr"/>
-      <c r="M287" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Perjalanan Dinas Biasa</t>
-          </r>
-        </is>
-      </c>
-      <c r="N287" s="13" t="inlineStr"/>
+      <c r="H287" s="2" t="inlineStr"/>
+      <c r="I287" s="2" t="inlineStr"/>
+      <c r="J287" s="2" t="inlineStr"/>
+      <c r="K287" s="2" t="inlineStr"/>
+      <c r="L287" s="2" t="inlineStr"/>
+      <c r="M287" s="2" t="inlineStr"/>
+      <c r="N287" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000243. Pakaian Kerja PJLP</t>
+          </r>
+        </is>
+      </c>
       <c r="O287" s="13" t="inlineStr"/>
       <c r="P287" s="13" t="inlineStr"/>
       <c r="Q287" s="14" t="n">
-        <v>600000.0</v>
+        <v>7500000.0</v>
       </c>
       <c r="R287" s="14" t="inlineStr"/>
       <c r="S287" s="14" t="n">
@@ -17249,14 +17219,14 @@
       <c r="U287" s="14" t="inlineStr"/>
       <c r="V287" s="14" t="inlineStr"/>
       <c r="W287" s="14" t="n">
-        <v>600000.0</v>
+        <v>7500000.0</v>
       </c>
       <c r="X287" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y287" s="14" t="inlineStr"/>
       <c r="Z287" s="14" t="n">
-        <v>600000.0</v>
+        <v>7500000.0</v>
       </c>
       <c r="AA287" s="14" t="inlineStr"/>
       <c r="AB287" s="14" t="inlineStr"/>
@@ -17275,102 +17245,417 @@
     <row r="288" customHeight="1" ht="15">
       <c r="A288" s="2" t="inlineStr"/>
       <c r="B288" s="2" t="inlineStr"/>
-      <c r="C288" s="2" t="inlineStr"/>
-      <c r="D288" s="2" t="inlineStr"/>
-      <c r="E288" s="2" t="inlineStr"/>
-      <c r="F288" s="2" t="inlineStr"/>
-      <c r="G288" s="2" t="inlineStr"/>
-      <c r="H288" s="2" t="inlineStr"/>
-      <c r="I288" s="2" t="inlineStr"/>
-      <c r="J288" s="2" t="inlineStr"/>
-      <c r="K288" s="2" t="inlineStr"/>
-      <c r="L288" s="2" t="inlineStr"/>
-      <c r="M288" s="2" t="inlineStr"/>
-      <c r="N288" s="13" t="inlineStr">
+      <c r="C288" s="16" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">EBD</t>
+          </r>
+        </is>
+      </c>
+      <c r="D288" s="16" t="inlineStr"/>
+      <c r="E288" s="16" t="inlineStr"/>
+      <c r="F288" s="16" t="inlineStr"/>
+      <c r="G288" s="16" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Manajemen Kinerja Internal</t>
+          </r>
+        </is>
+      </c>
+      <c r="H288" s="16" t="inlineStr"/>
+      <c r="I288" s="16" t="inlineStr"/>
+      <c r="J288" s="16" t="inlineStr"/>
+      <c r="K288" s="16" t="inlineStr"/>
+      <c r="L288" s="16" t="inlineStr"/>
+      <c r="M288" s="16" t="inlineStr"/>
+      <c r="N288" s="16" t="inlineStr"/>
+      <c r="O288" s="16" t="inlineStr"/>
+      <c r="P288" s="16" t="inlineStr"/>
+      <c r="Q288" s="17" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R288" s="17" t="inlineStr"/>
+      <c r="S288" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T288" s="17" t="inlineStr"/>
+      <c r="U288" s="17" t="inlineStr"/>
+      <c r="V288" s="17" t="inlineStr"/>
+      <c r="W288" s="17" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X288" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y288" s="17" t="inlineStr"/>
+      <c r="Z288" s="17" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA288" s="17" t="inlineStr"/>
+      <c r="AB288" s="17" t="inlineStr"/>
+      <c r="AC288" s="18" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD288" s="18" t="inlineStr"/>
+      <c r="AE288" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF288" s="17" t="inlineStr"/>
+      <c r="AG288" s="17" t="inlineStr"/>
+      <c r="AH288" s="17" t="inlineStr"/>
+      <c r="AI288" s="17" t="inlineStr"/>
+    </row>
+    <row r="289" customHeight="1" ht="15">
+      <c r="A289" s="2" t="inlineStr"/>
+      <c r="B289" s="2" t="inlineStr"/>
+      <c r="C289" s="28" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">EBD.955</t>
+          </r>
+        </is>
+      </c>
+      <c r="D289" s="28" t="inlineStr"/>
+      <c r="E289" s="28" t="inlineStr"/>
+      <c r="F289" s="28" t="inlineStr"/>
+      <c r="G289" s="28" t="inlineStr"/>
+      <c r="H289" s="28" t="inlineStr"/>
+      <c r="I289" s="28" t="inlineStr"/>
+      <c r="J289" s="28" t="inlineStr"/>
+      <c r="K289" s="20" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Manajemen Keuangan</t>
+          </r>
+        </is>
+      </c>
+      <c r="L289" s="20" t="inlineStr"/>
+      <c r="M289" s="20" t="inlineStr"/>
+      <c r="N289" s="20" t="inlineStr"/>
+      <c r="O289" s="20" t="inlineStr"/>
+      <c r="P289" s="20" t="inlineStr"/>
+      <c r="Q289" s="21" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R289" s="21" t="inlineStr"/>
+      <c r="S289" s="21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T289" s="21" t="inlineStr"/>
+      <c r="U289" s="21" t="inlineStr"/>
+      <c r="V289" s="21" t="inlineStr"/>
+      <c r="W289" s="22" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X289" s="22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y289" s="22" t="inlineStr"/>
+      <c r="Z289" s="21" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA289" s="21" t="inlineStr"/>
+      <c r="AB289" s="21" t="inlineStr"/>
+      <c r="AC289" s="23" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD289" s="23" t="inlineStr"/>
+      <c r="AE289" s="21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF289" s="21" t="inlineStr"/>
+      <c r="AG289" s="21" t="inlineStr"/>
+      <c r="AH289" s="21" t="inlineStr"/>
+      <c r="AI289" s="21" t="inlineStr"/>
+    </row>
+    <row r="290" customHeight="1" ht="15">
+      <c r="A290" s="2" t="inlineStr"/>
+      <c r="B290" s="2" t="inlineStr"/>
+      <c r="C290" s="2" t="inlineStr"/>
+      <c r="D290" s="2" t="inlineStr"/>
+      <c r="E290" s="24" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">201</t>
+          </r>
+        </is>
+      </c>
+      <c r="F290" s="24" t="inlineStr"/>
+      <c r="G290" s="24" t="inlineStr"/>
+      <c r="H290" s="24" t="inlineStr"/>
+      <c r="I290" s="24" t="inlineStr"/>
+      <c r="J290" s="24" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pelayanan Keuangan Penyuluhan Kelautan dan Perikanan</t>
+          </r>
+        </is>
+      </c>
+      <c r="K290" s="24" t="inlineStr"/>
+      <c r="L290" s="24" t="inlineStr"/>
+      <c r="M290" s="24" t="inlineStr"/>
+      <c r="N290" s="24" t="inlineStr"/>
+      <c r="O290" s="24" t="inlineStr"/>
+      <c r="P290" s="24" t="inlineStr"/>
+      <c r="Q290" s="25" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R290" s="25" t="inlineStr"/>
+      <c r="S290" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T290" s="25" t="inlineStr"/>
+      <c r="U290" s="25" t="inlineStr"/>
+      <c r="V290" s="25" t="inlineStr"/>
+      <c r="W290" s="25" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X290" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y290" s="25" t="inlineStr"/>
+      <c r="Z290" s="25" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA290" s="25" t="inlineStr"/>
+      <c r="AB290" s="25" t="inlineStr"/>
+      <c r="AC290" s="26" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD290" s="26" t="inlineStr"/>
+      <c r="AE290" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF290" s="25" t="inlineStr"/>
+      <c r="AG290" s="25" t="inlineStr"/>
+      <c r="AH290" s="25" t="inlineStr"/>
+      <c r="AI290" s="25" t="inlineStr"/>
+    </row>
+    <row r="291" customHeight="1" ht="15">
+      <c r="A291" s="2" t="inlineStr"/>
+      <c r="B291" s="2" t="inlineStr"/>
+      <c r="C291" s="2" t="inlineStr"/>
+      <c r="D291" s="2" t="inlineStr"/>
+      <c r="E291" s="2" t="inlineStr"/>
+      <c r="F291" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">201.DA</t>
+          </r>
+        </is>
+      </c>
+      <c r="G291" s="13" t="inlineStr"/>
+      <c r="H291" s="13" t="inlineStr"/>
+      <c r="I291" s="13" t="inlineStr"/>
+      <c r="J291" s="13" t="inlineStr"/>
+      <c r="K291" s="13" t="inlineStr"/>
+      <c r="L291" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Keuangan</t>
+          </r>
+        </is>
+      </c>
+      <c r="M291" s="13" t="inlineStr"/>
+      <c r="N291" s="13" t="inlineStr"/>
+      <c r="O291" s="13" t="inlineStr"/>
+      <c r="P291" s="13" t="inlineStr"/>
+      <c r="Q291" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R291" s="14" t="inlineStr"/>
+      <c r="S291" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T291" s="14" t="inlineStr"/>
+      <c r="U291" s="14" t="inlineStr"/>
+      <c r="V291" s="14" t="inlineStr"/>
+      <c r="W291" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X291" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y291" s="14" t="inlineStr"/>
+      <c r="Z291" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA291" s="14" t="inlineStr"/>
+      <c r="AB291" s="14" t="inlineStr"/>
+      <c r="AC291" s="15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD291" s="15" t="inlineStr"/>
+      <c r="AE291" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF291" s="14" t="inlineStr"/>
+      <c r="AG291" s="14" t="inlineStr"/>
+      <c r="AH291" s="14" t="inlineStr"/>
+      <c r="AI291" s="14" t="inlineStr"/>
+    </row>
+    <row r="292" customHeight="1" ht="15">
+      <c r="A292" s="2" t="inlineStr"/>
+      <c r="B292" s="2" t="inlineStr"/>
+      <c r="C292" s="2" t="inlineStr"/>
+      <c r="D292" s="2" t="inlineStr"/>
+      <c r="E292" s="2" t="inlineStr"/>
+      <c r="F292" s="2" t="inlineStr"/>
+      <c r="G292" s="2" t="inlineStr"/>
+      <c r="H292" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">524111</t>
+          </r>
+        </is>
+      </c>
+      <c r="I292" s="13" t="inlineStr"/>
+      <c r="J292" s="13" t="inlineStr"/>
+      <c r="K292" s="13" t="inlineStr"/>
+      <c r="L292" s="13" t="inlineStr"/>
+      <c r="M292" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Perjalanan Dinas Biasa</t>
+          </r>
+        </is>
+      </c>
+      <c r="N292" s="13" t="inlineStr"/>
+      <c r="O292" s="13" t="inlineStr"/>
+      <c r="P292" s="13" t="inlineStr"/>
+      <c r="Q292" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R292" s="14" t="inlineStr"/>
+      <c r="S292" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T292" s="14" t="inlineStr"/>
+      <c r="U292" s="14" t="inlineStr"/>
+      <c r="V292" s="14" t="inlineStr"/>
+      <c r="W292" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X292" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y292" s="14" t="inlineStr"/>
+      <c r="Z292" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA292" s="14" t="inlineStr"/>
+      <c r="AB292" s="14" t="inlineStr"/>
+      <c r="AC292" s="15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD292" s="15" t="inlineStr"/>
+      <c r="AE292" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF292" s="14" t="inlineStr"/>
+      <c r="AG292" s="14" t="inlineStr"/>
+      <c r="AH292" s="14" t="inlineStr"/>
+      <c r="AI292" s="14" t="inlineStr"/>
+    </row>
+    <row r="293" customHeight="1" ht="15">
+      <c r="A293" s="2" t="inlineStr"/>
+      <c r="B293" s="2" t="inlineStr"/>
+      <c r="C293" s="2" t="inlineStr"/>
+      <c r="D293" s="2" t="inlineStr"/>
+      <c r="E293" s="2" t="inlineStr"/>
+      <c r="F293" s="2" t="inlineStr"/>
+      <c r="G293" s="2" t="inlineStr"/>
+      <c r="H293" s="2" t="inlineStr"/>
+      <c r="I293" s="2" t="inlineStr"/>
+      <c r="J293" s="2" t="inlineStr"/>
+      <c r="K293" s="2" t="inlineStr"/>
+      <c r="L293" s="2" t="inlineStr"/>
+      <c r="M293" s="2" t="inlineStr"/>
+      <c r="N293" s="13" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">000231. Uang Harian</t>
           </r>
         </is>
       </c>
-      <c r="O288" s="13" t="inlineStr"/>
-      <c r="P288" s="13" t="inlineStr"/>
-      <c r="Q288" s="14" t="n">
+      <c r="O293" s="13" t="inlineStr"/>
+      <c r="P293" s="13" t="inlineStr"/>
+      <c r="Q293" s="14" t="n">
         <v>600000.0</v>
       </c>
-      <c r="R288" s="14" t="inlineStr"/>
-      <c r="S288" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T288" s="14" t="inlineStr"/>
-      <c r="U288" s="14" t="inlineStr"/>
-      <c r="V288" s="14" t="inlineStr"/>
-      <c r="W288" s="14" t="n">
+      <c r="R293" s="14" t="inlineStr"/>
+      <c r="S293" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T293" s="14" t="inlineStr"/>
+      <c r="U293" s="14" t="inlineStr"/>
+      <c r="V293" s="14" t="inlineStr"/>
+      <c r="W293" s="14" t="n">
         <v>600000.0</v>
       </c>
-      <c r="X288" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y288" s="14" t="inlineStr"/>
-      <c r="Z288" s="14" t="n">
+      <c r="X293" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y293" s="14" t="inlineStr"/>
+      <c r="Z293" s="14" t="n">
         <v>600000.0</v>
       </c>
-      <c r="AA288" s="14" t="inlineStr"/>
-      <c r="AB288" s="14" t="inlineStr"/>
-      <c r="AC288" s="15" t="n">
+      <c r="AA293" s="14" t="inlineStr"/>
+      <c r="AB293" s="14" t="inlineStr"/>
+      <c r="AC293" s="15" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD288" s="15" t="inlineStr"/>
-      <c r="AE288" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF288" s="14" t="inlineStr"/>
-      <c r="AG288" s="14" t="inlineStr"/>
-      <c r="AH288" s="14" t="inlineStr"/>
-      <c r="AI288" s="14" t="inlineStr"/>
-    </row>
-    <row r="289" customHeight="1" ht="12">
-      <c r="A289" s="2" t="inlineStr"/>
-      <c r="B289" s="27" t="inlineStr">
+      <c r="AD293" s="15" t="inlineStr"/>
+      <c r="AE293" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF293" s="14" t="inlineStr"/>
+      <c r="AG293" s="14" t="inlineStr"/>
+      <c r="AH293" s="14" t="inlineStr"/>
+      <c r="AI293" s="14" t="inlineStr"/>
+    </row>
+    <row r="294" customHeight="1" ht="12">
+      <c r="A294" s="2" t="inlineStr"/>
+      <c r="B294" s="27" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">*Lock Pagu adalah jumlah pagu yang sedang dalam proses usulan revisi DIPA atau POK. Lock pagu akan hilang setelah usulan revisi DIPA/POK selesai menjadi DIPA.</t>
           </r>
         </is>
       </c>
-      <c r="C289" s="27" t="inlineStr"/>
-      <c r="D289" s="27" t="inlineStr"/>
-      <c r="E289" s="27" t="inlineStr"/>
-      <c r="F289" s="27" t="inlineStr"/>
-      <c r="G289" s="27" t="inlineStr"/>
-      <c r="H289" s="27" t="inlineStr"/>
-      <c r="I289" s="27" t="inlineStr"/>
-      <c r="J289" s="27" t="inlineStr"/>
-      <c r="K289" s="27" t="inlineStr"/>
-      <c r="L289" s="27" t="inlineStr"/>
-      <c r="M289" s="27" t="inlineStr"/>
-      <c r="N289" s="27" t="inlineStr"/>
-      <c r="O289" s="27" t="inlineStr"/>
-      <c r="P289" s="27" t="inlineStr"/>
-      <c r="Q289" s="27" t="inlineStr"/>
-      <c r="R289" s="27" t="inlineStr"/>
-      <c r="S289" s="27" t="inlineStr"/>
-      <c r="T289" s="27" t="inlineStr"/>
-      <c r="U289" s="27" t="inlineStr"/>
-      <c r="V289" s="27" t="inlineStr"/>
-      <c r="W289" s="27" t="inlineStr"/>
-      <c r="X289" s="27" t="inlineStr"/>
-      <c r="Y289" s="27" t="inlineStr"/>
-      <c r="Z289" s="27" t="inlineStr"/>
-      <c r="AA289" s="27" t="inlineStr"/>
-      <c r="AB289" s="27" t="inlineStr"/>
-      <c r="AC289" s="27" t="inlineStr"/>
-      <c r="AD289" s="27" t="inlineStr"/>
-      <c r="AE289" s="27" t="inlineStr"/>
-      <c r="AF289" s="27" t="inlineStr"/>
-      <c r="AG289" s="2" t="inlineStr"/>
-      <c r="AH289" s="2" t="inlineStr"/>
-      <c r="AI289" s="2" t="inlineStr"/>
+      <c r="C294" s="27" t="inlineStr"/>
+      <c r="D294" s="27" t="inlineStr"/>
+      <c r="E294" s="27" t="inlineStr"/>
+      <c r="F294" s="27" t="inlineStr"/>
+      <c r="G294" s="27" t="inlineStr"/>
+      <c r="H294" s="27" t="inlineStr"/>
+      <c r="I294" s="27" t="inlineStr"/>
+      <c r="J294" s="27" t="inlineStr"/>
+      <c r="K294" s="27" t="inlineStr"/>
+      <c r="L294" s="27" t="inlineStr"/>
+      <c r="M294" s="27" t="inlineStr"/>
+      <c r="N294" s="27" t="inlineStr"/>
+      <c r="O294" s="27" t="inlineStr"/>
+      <c r="P294" s="27" t="inlineStr"/>
+      <c r="Q294" s="27" t="inlineStr"/>
+      <c r="R294" s="27" t="inlineStr"/>
+      <c r="S294" s="27" t="inlineStr"/>
+      <c r="T294" s="27" t="inlineStr"/>
+      <c r="U294" s="27" t="inlineStr"/>
+      <c r="V294" s="27" t="inlineStr"/>
+      <c r="W294" s="27" t="inlineStr"/>
+      <c r="X294" s="27" t="inlineStr"/>
+      <c r="Y294" s="27" t="inlineStr"/>
+      <c r="Z294" s="27" t="inlineStr"/>
+      <c r="AA294" s="27" t="inlineStr"/>
+      <c r="AB294" s="27" t="inlineStr"/>
+      <c r="AC294" s="27" t="inlineStr"/>
+      <c r="AD294" s="27" t="inlineStr"/>
+      <c r="AE294" s="27" t="inlineStr"/>
+      <c r="AF294" s="27" t="inlineStr"/>
+      <c r="AG294" s="2" t="inlineStr"/>
+      <c r="AH294" s="2" t="inlineStr"/>
+      <c r="AI294" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -18818,8 +19103,7 @@
     <mergeCell ref="Z208:AB208"/>
     <mergeCell ref="AC208:AD208"/>
     <mergeCell ref="AE208:AI208"/>
-    <mergeCell ref="H209:L209"/>
-    <mergeCell ref="M209:P209"/>
+    <mergeCell ref="N209:P209"/>
     <mergeCell ref="Q209:R209"/>
     <mergeCell ref="S209:V209"/>
     <mergeCell ref="X209:Y209"/>
@@ -18840,23 +19124,22 @@
     <mergeCell ref="Z211:AB211"/>
     <mergeCell ref="AC211:AD211"/>
     <mergeCell ref="AE211:AI211"/>
-    <mergeCell ref="H212:L212"/>
-    <mergeCell ref="M212:P212"/>
+    <mergeCell ref="N212:P212"/>
     <mergeCell ref="Q212:R212"/>
     <mergeCell ref="S212:V212"/>
     <mergeCell ref="X212:Y212"/>
     <mergeCell ref="Z212:AB212"/>
     <mergeCell ref="AC212:AD212"/>
     <mergeCell ref="AE212:AI212"/>
-    <mergeCell ref="N213:P213"/>
+    <mergeCell ref="H213:L213"/>
+    <mergeCell ref="M213:P213"/>
     <mergeCell ref="Q213:R213"/>
     <mergeCell ref="S213:V213"/>
     <mergeCell ref="X213:Y213"/>
     <mergeCell ref="Z213:AB213"/>
     <mergeCell ref="AC213:AD213"/>
     <mergeCell ref="AE213:AI213"/>
-    <mergeCell ref="H214:L214"/>
-    <mergeCell ref="M214:P214"/>
+    <mergeCell ref="N214:P214"/>
     <mergeCell ref="Q214:R214"/>
     <mergeCell ref="S214:V214"/>
     <mergeCell ref="X214:Y214"/>
@@ -18885,7 +19168,8 @@
     <mergeCell ref="Z217:AB217"/>
     <mergeCell ref="AC217:AD217"/>
     <mergeCell ref="AE217:AI217"/>
-    <mergeCell ref="N218:P218"/>
+    <mergeCell ref="H218:L218"/>
+    <mergeCell ref="M218:P218"/>
     <mergeCell ref="Q218:R218"/>
     <mergeCell ref="S218:V218"/>
     <mergeCell ref="X218:Y218"/>
@@ -18906,23 +19190,22 @@
     <mergeCell ref="Z220:AB220"/>
     <mergeCell ref="AC220:AD220"/>
     <mergeCell ref="AE220:AI220"/>
-    <mergeCell ref="N221:P221"/>
+    <mergeCell ref="H221:L221"/>
+    <mergeCell ref="M221:P221"/>
     <mergeCell ref="Q221:R221"/>
     <mergeCell ref="S221:V221"/>
     <mergeCell ref="X221:Y221"/>
     <mergeCell ref="Z221:AB221"/>
     <mergeCell ref="AC221:AD221"/>
     <mergeCell ref="AE221:AI221"/>
-    <mergeCell ref="F222:K222"/>
-    <mergeCell ref="L222:P222"/>
+    <mergeCell ref="N222:P222"/>
     <mergeCell ref="Q222:R222"/>
     <mergeCell ref="S222:V222"/>
     <mergeCell ref="X222:Y222"/>
     <mergeCell ref="Z222:AB222"/>
     <mergeCell ref="AC222:AD222"/>
     <mergeCell ref="AE222:AI222"/>
-    <mergeCell ref="H223:L223"/>
-    <mergeCell ref="M223:P223"/>
+    <mergeCell ref="N223:P223"/>
     <mergeCell ref="Q223:R223"/>
     <mergeCell ref="S223:V223"/>
     <mergeCell ref="X223:Y223"/>
@@ -18936,8 +19219,7 @@
     <mergeCell ref="Z224:AB224"/>
     <mergeCell ref="AC224:AD224"/>
     <mergeCell ref="AE224:AI224"/>
-    <mergeCell ref="H225:L225"/>
-    <mergeCell ref="M225:P225"/>
+    <mergeCell ref="N225:P225"/>
     <mergeCell ref="Q225:R225"/>
     <mergeCell ref="S225:V225"/>
     <mergeCell ref="X225:Y225"/>
@@ -18951,8 +19233,8 @@
     <mergeCell ref="Z226:AB226"/>
     <mergeCell ref="AC226:AD226"/>
     <mergeCell ref="AE226:AI226"/>
-    <mergeCell ref="H227:L227"/>
-    <mergeCell ref="M227:P227"/>
+    <mergeCell ref="F227:K227"/>
+    <mergeCell ref="L227:P227"/>
     <mergeCell ref="Q227:R227"/>
     <mergeCell ref="S227:V227"/>
     <mergeCell ref="X227:Y227"/>
@@ -18960,22 +19242,23 @@
     <mergeCell ref="AC227:AD227"/>
     <mergeCell ref="AE227:AI227"/>
     <mergeCell ref="B228:AF228"/>
-    <mergeCell ref="N229:P229"/>
+    <mergeCell ref="H229:L229"/>
+    <mergeCell ref="M229:P229"/>
     <mergeCell ref="Q229:R229"/>
     <mergeCell ref="S229:V229"/>
     <mergeCell ref="X229:Y229"/>
     <mergeCell ref="Z229:AB229"/>
     <mergeCell ref="AC229:AD229"/>
     <mergeCell ref="AE229:AI229"/>
-    <mergeCell ref="H230:L230"/>
-    <mergeCell ref="M230:P230"/>
+    <mergeCell ref="N230:P230"/>
     <mergeCell ref="Q230:R230"/>
     <mergeCell ref="S230:V230"/>
     <mergeCell ref="X230:Y230"/>
     <mergeCell ref="Z230:AB230"/>
     <mergeCell ref="AC230:AD230"/>
     <mergeCell ref="AE230:AI230"/>
-    <mergeCell ref="N231:P231"/>
+    <mergeCell ref="H231:L231"/>
+    <mergeCell ref="M231:P231"/>
     <mergeCell ref="Q231:R231"/>
     <mergeCell ref="S231:V231"/>
     <mergeCell ref="X231:Y231"/>
@@ -18989,23 +19272,23 @@
     <mergeCell ref="Z232:AB232"/>
     <mergeCell ref="AC232:AD232"/>
     <mergeCell ref="AE232:AI232"/>
-    <mergeCell ref="F233:K233"/>
-    <mergeCell ref="L233:P233"/>
+    <mergeCell ref="H233:L233"/>
+    <mergeCell ref="M233:P233"/>
     <mergeCell ref="Q233:R233"/>
     <mergeCell ref="S233:V233"/>
     <mergeCell ref="X233:Y233"/>
     <mergeCell ref="Z233:AB233"/>
     <mergeCell ref="AC233:AD233"/>
     <mergeCell ref="AE233:AI233"/>
-    <mergeCell ref="H234:L234"/>
-    <mergeCell ref="M234:P234"/>
+    <mergeCell ref="N234:P234"/>
     <mergeCell ref="Q234:R234"/>
     <mergeCell ref="S234:V234"/>
     <mergeCell ref="X234:Y234"/>
     <mergeCell ref="Z234:AB234"/>
     <mergeCell ref="AC234:AD234"/>
     <mergeCell ref="AE234:AI234"/>
-    <mergeCell ref="N235:P235"/>
+    <mergeCell ref="H235:L235"/>
+    <mergeCell ref="M235:P235"/>
     <mergeCell ref="Q235:R235"/>
     <mergeCell ref="S235:V235"/>
     <mergeCell ref="X235:Y235"/>
@@ -19019,15 +19302,15 @@
     <mergeCell ref="Z236:AB236"/>
     <mergeCell ref="AC236:AD236"/>
     <mergeCell ref="AE236:AI236"/>
-    <mergeCell ref="H237:L237"/>
-    <mergeCell ref="M237:P237"/>
+    <mergeCell ref="N237:P237"/>
     <mergeCell ref="Q237:R237"/>
     <mergeCell ref="S237:V237"/>
     <mergeCell ref="X237:Y237"/>
     <mergeCell ref="Z237:AB237"/>
     <mergeCell ref="AC237:AD237"/>
     <mergeCell ref="AE237:AI237"/>
-    <mergeCell ref="N238:P238"/>
+    <mergeCell ref="F238:K238"/>
+    <mergeCell ref="L238:P238"/>
     <mergeCell ref="Q238:R238"/>
     <mergeCell ref="S238:V238"/>
     <mergeCell ref="X238:Y238"/>
@@ -19056,7 +19339,8 @@
     <mergeCell ref="Z241:AB241"/>
     <mergeCell ref="AC241:AD241"/>
     <mergeCell ref="AE241:AI241"/>
-    <mergeCell ref="N242:P242"/>
+    <mergeCell ref="H242:L242"/>
+    <mergeCell ref="M242:P242"/>
     <mergeCell ref="Q242:R242"/>
     <mergeCell ref="S242:V242"/>
     <mergeCell ref="X242:Y242"/>
@@ -19070,7 +19354,8 @@
     <mergeCell ref="Z243:AB243"/>
     <mergeCell ref="AC243:AD243"/>
     <mergeCell ref="AE243:AI243"/>
-    <mergeCell ref="N244:P244"/>
+    <mergeCell ref="H244:L244"/>
+    <mergeCell ref="M244:P244"/>
     <mergeCell ref="Q244:R244"/>
     <mergeCell ref="S244:V244"/>
     <mergeCell ref="X244:Y244"/>
@@ -19133,8 +19418,7 @@
     <mergeCell ref="Z252:AB252"/>
     <mergeCell ref="AC252:AD252"/>
     <mergeCell ref="AE252:AI252"/>
-    <mergeCell ref="H253:L253"/>
-    <mergeCell ref="M253:P253"/>
+    <mergeCell ref="N253:P253"/>
     <mergeCell ref="Q253:R253"/>
     <mergeCell ref="S253:V253"/>
     <mergeCell ref="X253:Y253"/>
@@ -19170,7 +19454,8 @@
     <mergeCell ref="Z258:AB258"/>
     <mergeCell ref="AC258:AD258"/>
     <mergeCell ref="AE258:AI258"/>
-    <mergeCell ref="N259:P259"/>
+    <mergeCell ref="H259:L259"/>
+    <mergeCell ref="M259:P259"/>
     <mergeCell ref="Q259:R259"/>
     <mergeCell ref="S259:V259"/>
     <mergeCell ref="X259:Y259"/>
@@ -19226,8 +19511,7 @@
     <mergeCell ref="Z266:AB266"/>
     <mergeCell ref="AC266:AD266"/>
     <mergeCell ref="AE266:AI266"/>
-    <mergeCell ref="H267:L267"/>
-    <mergeCell ref="M267:P267"/>
+    <mergeCell ref="N267:P267"/>
     <mergeCell ref="Q267:R267"/>
     <mergeCell ref="S267:V267"/>
     <mergeCell ref="X267:Y267"/>
@@ -19255,8 +19539,7 @@
     <mergeCell ref="Z270:AB270"/>
     <mergeCell ref="AC270:AD270"/>
     <mergeCell ref="AE270:AI270"/>
-    <mergeCell ref="F271:K271"/>
-    <mergeCell ref="L271:P271"/>
+    <mergeCell ref="N271:P271"/>
     <mergeCell ref="Q271:R271"/>
     <mergeCell ref="S271:V271"/>
     <mergeCell ref="X271:Y271"/>
@@ -19292,14 +19575,16 @@
     <mergeCell ref="Z275:AB275"/>
     <mergeCell ref="AC275:AD275"/>
     <mergeCell ref="AE275:AI275"/>
-    <mergeCell ref="N276:P276"/>
+    <mergeCell ref="F276:K276"/>
+    <mergeCell ref="L276:P276"/>
     <mergeCell ref="Q276:R276"/>
     <mergeCell ref="S276:V276"/>
     <mergeCell ref="X276:Y276"/>
     <mergeCell ref="Z276:AB276"/>
     <mergeCell ref="AC276:AD276"/>
     <mergeCell ref="AE276:AI276"/>
-    <mergeCell ref="N277:P277"/>
+    <mergeCell ref="H277:L277"/>
+    <mergeCell ref="M277:P277"/>
     <mergeCell ref="Q277:R277"/>
     <mergeCell ref="S277:V277"/>
     <mergeCell ref="X277:Y277"/>
@@ -19320,8 +19605,7 @@
     <mergeCell ref="Z279:AB279"/>
     <mergeCell ref="AC279:AD279"/>
     <mergeCell ref="AE279:AI279"/>
-    <mergeCell ref="H280:L280"/>
-    <mergeCell ref="M280:P280"/>
+    <mergeCell ref="N280:P280"/>
     <mergeCell ref="Q280:R280"/>
     <mergeCell ref="S280:V280"/>
     <mergeCell ref="X280:Y280"/>
@@ -19336,54 +19620,90 @@
     <mergeCell ref="AC281:AD281"/>
     <mergeCell ref="AE281:AI281"/>
     <mergeCell ref="B282:AF282"/>
-    <mergeCell ref="C283:F283"/>
-    <mergeCell ref="G283:P283"/>
+    <mergeCell ref="N283:P283"/>
     <mergeCell ref="Q283:R283"/>
     <mergeCell ref="S283:V283"/>
     <mergeCell ref="X283:Y283"/>
     <mergeCell ref="Z283:AB283"/>
     <mergeCell ref="AC283:AD283"/>
     <mergeCell ref="AE283:AI283"/>
-    <mergeCell ref="C284:J284"/>
-    <mergeCell ref="K284:P284"/>
+    <mergeCell ref="N284:P284"/>
     <mergeCell ref="Q284:R284"/>
     <mergeCell ref="S284:V284"/>
     <mergeCell ref="X284:Y284"/>
     <mergeCell ref="Z284:AB284"/>
     <mergeCell ref="AC284:AD284"/>
     <mergeCell ref="AE284:AI284"/>
-    <mergeCell ref="E285:I285"/>
-    <mergeCell ref="J285:P285"/>
+    <mergeCell ref="N285:P285"/>
     <mergeCell ref="Q285:R285"/>
     <mergeCell ref="S285:V285"/>
     <mergeCell ref="X285:Y285"/>
     <mergeCell ref="Z285:AB285"/>
     <mergeCell ref="AC285:AD285"/>
     <mergeCell ref="AE285:AI285"/>
-    <mergeCell ref="F286:K286"/>
-    <mergeCell ref="L286:P286"/>
+    <mergeCell ref="H286:L286"/>
+    <mergeCell ref="M286:P286"/>
     <mergeCell ref="Q286:R286"/>
     <mergeCell ref="S286:V286"/>
     <mergeCell ref="X286:Y286"/>
     <mergeCell ref="Z286:AB286"/>
     <mergeCell ref="AC286:AD286"/>
     <mergeCell ref="AE286:AI286"/>
-    <mergeCell ref="H287:L287"/>
-    <mergeCell ref="M287:P287"/>
+    <mergeCell ref="N287:P287"/>
     <mergeCell ref="Q287:R287"/>
     <mergeCell ref="S287:V287"/>
     <mergeCell ref="X287:Y287"/>
     <mergeCell ref="Z287:AB287"/>
     <mergeCell ref="AC287:AD287"/>
     <mergeCell ref="AE287:AI287"/>
-    <mergeCell ref="N288:P288"/>
+    <mergeCell ref="C288:F288"/>
+    <mergeCell ref="G288:P288"/>
     <mergeCell ref="Q288:R288"/>
     <mergeCell ref="S288:V288"/>
     <mergeCell ref="X288:Y288"/>
     <mergeCell ref="Z288:AB288"/>
     <mergeCell ref="AC288:AD288"/>
     <mergeCell ref="AE288:AI288"/>
-    <mergeCell ref="B289:AF289"/>
+    <mergeCell ref="C289:J289"/>
+    <mergeCell ref="K289:P289"/>
+    <mergeCell ref="Q289:R289"/>
+    <mergeCell ref="S289:V289"/>
+    <mergeCell ref="X289:Y289"/>
+    <mergeCell ref="Z289:AB289"/>
+    <mergeCell ref="AC289:AD289"/>
+    <mergeCell ref="AE289:AI289"/>
+    <mergeCell ref="E290:I290"/>
+    <mergeCell ref="J290:P290"/>
+    <mergeCell ref="Q290:R290"/>
+    <mergeCell ref="S290:V290"/>
+    <mergeCell ref="X290:Y290"/>
+    <mergeCell ref="Z290:AB290"/>
+    <mergeCell ref="AC290:AD290"/>
+    <mergeCell ref="AE290:AI290"/>
+    <mergeCell ref="F291:K291"/>
+    <mergeCell ref="L291:P291"/>
+    <mergeCell ref="Q291:R291"/>
+    <mergeCell ref="S291:V291"/>
+    <mergeCell ref="X291:Y291"/>
+    <mergeCell ref="Z291:AB291"/>
+    <mergeCell ref="AC291:AD291"/>
+    <mergeCell ref="AE291:AI291"/>
+    <mergeCell ref="H292:L292"/>
+    <mergeCell ref="M292:P292"/>
+    <mergeCell ref="Q292:R292"/>
+    <mergeCell ref="S292:V292"/>
+    <mergeCell ref="X292:Y292"/>
+    <mergeCell ref="Z292:AB292"/>
+    <mergeCell ref="AC292:AD292"/>
+    <mergeCell ref="AE292:AI292"/>
+    <mergeCell ref="N293:P293"/>
+    <mergeCell ref="Q293:R293"/>
+    <mergeCell ref="S293:V293"/>
+    <mergeCell ref="X293:Y293"/>
+    <mergeCell ref="Z293:AB293"/>
+    <mergeCell ref="AC293:AD293"/>
+    <mergeCell ref="AE293:AI293"/>
+    <mergeCell ref="B294:AF294"/>
   </mergeCells>
   <pageMargins left="0.0" right="0.0" top="0.0" bottom="0.00" header="0.0" footer="0.0"/>
   <pageSetup orientation="landscape" paperSize="9"/>

--- a/Database/Akrual.xlsx
+++ b/Database/Akrual.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E641CD86-4225-48BE-AEB5-582BCEAA2324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB7EA93A-EAC6-4995-96BE-75B0C8D3B4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Database/Akrual.xlsx
+++ b/Database/Akrual.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB7EA93A-EAC6-4995-96BE-75B0C8D3B4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D0373B4-E131-4C64-B601-FC1934E016AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2155,19 +2155,19 @@
         <v>80919905375</v>
       </c>
       <c r="X9" s="4">
-        <v>0</v>
+        <v>1938614197</v>
       </c>
       <c r="Y9" s="18">
-        <v>80919905375</v>
+        <v>82858519572</v>
       </c>
       <c r="Z9" s="18"/>
       <c r="AA9" s="18"/>
       <c r="AB9" s="18"/>
       <c r="AC9" s="5">
-        <v>0.95187794227321709</v>
+        <v>0.97468227062914359</v>
       </c>
       <c r="AD9" s="18">
-        <v>4090894625</v>
+        <v>2152280428</v>
       </c>
       <c r="AE9" s="18"/>
       <c r="AF9" s="18"/>
@@ -2807,20 +2807,20 @@
         <v>76886537335</v>
       </c>
       <c r="X21" s="20">
-        <v>0</v>
+        <v>1938614197</v>
       </c>
       <c r="Y21" s="20"/>
       <c r="Z21" s="20">
-        <v>76886537335</v>
+        <v>78825151532</v>
       </c>
       <c r="AA21" s="20"/>
       <c r="AB21" s="20"/>
       <c r="AC21" s="21">
-        <v>0.9494814273488652</v>
+        <v>0.97342161556187279</v>
       </c>
       <c r="AD21" s="21"/>
       <c r="AE21" s="20">
-        <v>4090862665</v>
+        <v>2152248468</v>
       </c>
       <c r="AF21" s="20"/>
       <c r="AG21" s="20"/>
@@ -2862,20 +2862,20 @@
         <v>76886537335</v>
       </c>
       <c r="X22" s="20">
-        <v>0</v>
+        <v>1938614197</v>
       </c>
       <c r="Y22" s="20"/>
       <c r="Z22" s="20">
-        <v>76886537335</v>
+        <v>78825151532</v>
       </c>
       <c r="AA22" s="20"/>
       <c r="AB22" s="20"/>
       <c r="AC22" s="21">
-        <v>0.9494814273488652</v>
+        <v>0.97342161556187279</v>
       </c>
       <c r="AD22" s="21"/>
       <c r="AE22" s="20">
-        <v>4090862665</v>
+        <v>2152248468</v>
       </c>
       <c r="AF22" s="20"/>
       <c r="AG22" s="20"/>
@@ -2917,20 +2917,20 @@
         <v>76885937335</v>
       </c>
       <c r="X23" s="23">
-        <v>0</v>
+        <v>1938614197</v>
       </c>
       <c r="Y23" s="23"/>
       <c r="Z23" s="23">
-        <v>76885937335</v>
+        <v>78824551532</v>
       </c>
       <c r="AA23" s="23"/>
       <c r="AB23" s="23"/>
       <c r="AC23" s="24">
-        <v>0.94948105303000363</v>
+        <v>0.97342141862854548</v>
       </c>
       <c r="AD23" s="24"/>
       <c r="AE23" s="23">
-        <v>4090862665</v>
+        <v>2152248468</v>
       </c>
       <c r="AF23" s="23"/>
       <c r="AG23" s="23"/>
@@ -4154,20 +4154,20 @@
         <v>76870226283</v>
       </c>
       <c r="X46" s="28">
-        <v>0</v>
+        <v>1938614197</v>
       </c>
       <c r="Y46" s="28"/>
       <c r="Z46" s="27">
-        <v>76870226283</v>
+        <v>78808840480</v>
       </c>
       <c r="AA46" s="27"/>
       <c r="AB46" s="27"/>
       <c r="AC46" s="29">
-        <v>0.94950430985000045</v>
+        <v>0.97345015499960663</v>
       </c>
       <c r="AD46" s="29"/>
       <c r="AE46" s="27">
-        <v>4088043717</v>
+        <v>2149429520</v>
       </c>
       <c r="AF46" s="27"/>
       <c r="AG46" s="27"/>
@@ -4209,20 +4209,20 @@
         <v>70952227437</v>
       </c>
       <c r="X47" s="31">
-        <v>0</v>
+        <v>1929165877</v>
       </c>
       <c r="Y47" s="31"/>
       <c r="Z47" s="31">
-        <v>70952227437</v>
+        <v>72881393314</v>
       </c>
       <c r="AA47" s="31"/>
       <c r="AB47" s="31"/>
       <c r="AC47" s="32">
-        <v>0.95507148828243493</v>
+        <v>0.98103954301230323</v>
       </c>
       <c r="AD47" s="32"/>
       <c r="AE47" s="31">
-        <v>3337737563</v>
+        <v>1408571686</v>
       </c>
       <c r="AF47" s="31"/>
       <c r="AG47" s="31"/>
@@ -4264,20 +4264,20 @@
         <v>5428525892</v>
       </c>
       <c r="X48" s="20">
-        <v>0</v>
+        <v>202138903</v>
       </c>
       <c r="Y48" s="20"/>
       <c r="Z48" s="20">
-        <v>5428525892</v>
+        <v>5630664795</v>
       </c>
       <c r="AA48" s="20"/>
       <c r="AB48" s="20"/>
       <c r="AC48" s="21">
-        <v>0.84729791405098409</v>
+        <v>0.87884826017954487</v>
       </c>
       <c r="AD48" s="21"/>
       <c r="AE48" s="20">
-        <v>978342108</v>
+        <v>776203205</v>
       </c>
       <c r="AF48" s="20"/>
       <c r="AG48" s="20"/>
@@ -4319,20 +4319,20 @@
         <v>2140015700</v>
       </c>
       <c r="X49" s="20">
-        <v>0</v>
+        <v>161230800</v>
       </c>
       <c r="Y49" s="20"/>
       <c r="Z49" s="20">
-        <v>2140015700</v>
+        <v>2301246500</v>
       </c>
       <c r="AA49" s="20"/>
       <c r="AB49" s="20"/>
       <c r="AC49" s="21">
-        <v>0.76363459567628977</v>
+        <v>0.82116754591051699</v>
       </c>
       <c r="AD49" s="21"/>
       <c r="AE49" s="20">
-        <v>662392300</v>
+        <v>501161500</v>
       </c>
       <c r="AF49" s="20"/>
       <c r="AG49" s="20"/>
@@ -4372,20 +4372,20 @@
         <v>1809835300</v>
       </c>
       <c r="X50" s="20">
-        <v>0</v>
+        <v>161230800</v>
       </c>
       <c r="Y50" s="20"/>
       <c r="Z50" s="20">
-        <v>1809835300</v>
+        <v>1971066100</v>
       </c>
       <c r="AA50" s="20"/>
       <c r="AB50" s="20"/>
       <c r="AC50" s="21">
-        <v>0.73207005374934875</v>
+        <v>0.79728717070029476</v>
       </c>
       <c r="AD50" s="21"/>
       <c r="AE50" s="20">
-        <v>662380700</v>
+        <v>501149900</v>
       </c>
       <c r="AF50" s="20"/>
       <c r="AG50" s="20"/>
@@ -4533,20 +4533,20 @@
         <v>25093</v>
       </c>
       <c r="X53" s="20">
-        <v>0</v>
+        <v>1803</v>
       </c>
       <c r="Y53" s="20"/>
       <c r="Z53" s="20">
-        <v>25093</v>
+        <v>26896</v>
       </c>
       <c r="AA53" s="20"/>
       <c r="AB53" s="20"/>
       <c r="AC53" s="21">
-        <v>0.83643333333333336</v>
+        <v>0.89653333333333329</v>
       </c>
       <c r="AD53" s="21"/>
       <c r="AE53" s="20">
-        <v>4907</v>
+        <v>3104</v>
       </c>
       <c r="AF53" s="20"/>
       <c r="AG53" s="20"/>
@@ -4586,20 +4586,20 @@
         <v>20511</v>
       </c>
       <c r="X54" s="20">
-        <v>0</v>
+        <v>1803</v>
       </c>
       <c r="Y54" s="20"/>
       <c r="Z54" s="20">
-        <v>20511</v>
+        <v>22314</v>
       </c>
       <c r="AA54" s="20"/>
       <c r="AB54" s="20"/>
       <c r="AC54" s="21">
-        <v>0.85462499999999997</v>
+        <v>0.92974999999999997</v>
       </c>
       <c r="AD54" s="21"/>
       <c r="AE54" s="20">
-        <v>3489</v>
+        <v>1686</v>
       </c>
       <c r="AF54" s="20"/>
       <c r="AG54" s="20"/>
@@ -4747,20 +4747,20 @@
         <v>163021160</v>
       </c>
       <c r="X57" s="20">
-        <v>0</v>
+        <v>12175610</v>
       </c>
       <c r="Y57" s="20"/>
       <c r="Z57" s="20">
-        <v>163021160</v>
+        <v>175196770</v>
       </c>
       <c r="AA57" s="20"/>
       <c r="AB57" s="20"/>
       <c r="AC57" s="21">
-        <v>0.89572065934065936</v>
+        <v>0.96261961538461538</v>
       </c>
       <c r="AD57" s="21"/>
       <c r="AE57" s="20">
-        <v>18978840</v>
+        <v>6803230</v>
       </c>
       <c r="AF57" s="20"/>
       <c r="AG57" s="20"/>
@@ -4800,20 +4800,20 @@
         <v>137822840</v>
       </c>
       <c r="X58" s="20">
-        <v>0</v>
+        <v>12175610</v>
       </c>
       <c r="Y58" s="20"/>
       <c r="Z58" s="20">
-        <v>137822840</v>
+        <v>149998450</v>
       </c>
       <c r="AA58" s="20"/>
       <c r="AB58" s="20"/>
       <c r="AC58" s="21">
-        <v>0.8790170416858003</v>
+        <v>0.95667157763151178</v>
       </c>
       <c r="AD58" s="21"/>
       <c r="AE58" s="20">
-        <v>18969160</v>
+        <v>6793550</v>
       </c>
       <c r="AF58" s="20"/>
       <c r="AG58" s="20"/>
@@ -5000,20 +5000,20 @@
         <v>49459528</v>
       </c>
       <c r="X62" s="20">
-        <v>0</v>
+        <v>3650984</v>
       </c>
       <c r="Y62" s="20"/>
       <c r="Z62" s="20">
-        <v>49459528</v>
+        <v>53110512</v>
       </c>
       <c r="AA62" s="20"/>
       <c r="AB62" s="20"/>
       <c r="AC62" s="21">
-        <v>0.88320585714285715</v>
+        <v>0.94840199999999997</v>
       </c>
       <c r="AD62" s="21"/>
       <c r="AE62" s="20">
-        <v>6540472</v>
+        <v>2889488</v>
       </c>
       <c r="AF62" s="20"/>
       <c r="AG62" s="20"/>
@@ -5053,20 +5053,20 @@
         <v>41783470</v>
       </c>
       <c r="X63" s="20">
-        <v>0</v>
+        <v>3650984</v>
       </c>
       <c r="Y63" s="20"/>
       <c r="Z63" s="20">
-        <v>41783470</v>
+        <v>45434454</v>
       </c>
       <c r="AA63" s="20"/>
       <c r="AB63" s="20"/>
       <c r="AC63" s="21">
-        <v>0.86486732074846828</v>
+        <v>0.94043827620466969</v>
       </c>
       <c r="AD63" s="21"/>
       <c r="AE63" s="20">
-        <v>6528530</v>
+        <v>2877546</v>
       </c>
       <c r="AF63" s="20"/>
       <c r="AG63" s="20"/>
@@ -5214,20 +5214,20 @@
         <v>23400000</v>
       </c>
       <c r="X66" s="20">
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="Y66" s="20"/>
       <c r="Z66" s="20">
-        <v>23400000</v>
+        <v>25200000</v>
       </c>
       <c r="AA66" s="20"/>
       <c r="AB66" s="20"/>
       <c r="AC66" s="21">
-        <v>0.9285714285714286</v>
+        <v>1</v>
       </c>
       <c r="AD66" s="21"/>
       <c r="AE66" s="20">
-        <v>1800000</v>
+        <v>0</v>
       </c>
       <c r="AF66" s="20"/>
       <c r="AG66" s="20"/>
@@ -5267,20 +5267,20 @@
         <v>19800000</v>
       </c>
       <c r="X67" s="20">
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="Y67" s="20"/>
       <c r="Z67" s="20">
-        <v>19800000</v>
+        <v>21600000</v>
       </c>
       <c r="AA67" s="20"/>
       <c r="AB67" s="20"/>
       <c r="AC67" s="21">
-        <v>0.91666666666666663</v>
+        <v>1</v>
       </c>
       <c r="AD67" s="21"/>
       <c r="AE67" s="20">
-        <v>1800000</v>
+        <v>0</v>
       </c>
       <c r="AF67" s="20"/>
       <c r="AG67" s="20"/>
@@ -5428,20 +5428,20 @@
         <v>149682000</v>
       </c>
       <c r="X70" s="20">
-        <v>0</v>
+        <v>10394000</v>
       </c>
       <c r="Y70" s="20"/>
       <c r="Z70" s="20">
-        <v>149682000</v>
+        <v>160076000</v>
       </c>
       <c r="AA70" s="20"/>
       <c r="AB70" s="20"/>
       <c r="AC70" s="21">
-        <v>1.0321899954487153</v>
+        <v>1.1038658336436482</v>
       </c>
       <c r="AD70" s="21"/>
       <c r="AE70" s="20">
-        <v>-4668000</v>
+        <v>-15062000</v>
       </c>
       <c r="AF70" s="20"/>
       <c r="AG70" s="20"/>
@@ -5481,20 +5481,20 @@
         <v>125654000</v>
       </c>
       <c r="X71" s="20">
-        <v>0</v>
+        <v>10394000</v>
       </c>
       <c r="Y71" s="20"/>
       <c r="Z71" s="20">
-        <v>125654000</v>
+        <v>136048000</v>
       </c>
       <c r="AA71" s="20"/>
       <c r="AB71" s="20"/>
       <c r="AC71" s="21">
-        <v>1.0386001454737817</v>
+        <v>1.1245123322092176</v>
       </c>
       <c r="AD71" s="21"/>
       <c r="AE71" s="20">
-        <v>-4670000</v>
+        <v>-15064000</v>
       </c>
       <c r="AF71" s="20"/>
       <c r="AG71" s="20"/>
@@ -5642,20 +5642,20 @@
         <v>19962339</v>
       </c>
       <c r="X74" s="20">
-        <v>0</v>
+        <v>307406</v>
       </c>
       <c r="Y74" s="20"/>
       <c r="Z74" s="20">
-        <v>19962339</v>
+        <v>20269745</v>
       </c>
       <c r="AA74" s="20"/>
       <c r="AB74" s="20"/>
       <c r="AC74" s="21">
-        <v>1.0081989393939395</v>
+        <v>1.023724494949495</v>
       </c>
       <c r="AD74" s="21"/>
       <c r="AE74" s="20">
-        <v>-162339</v>
+        <v>-469745</v>
       </c>
       <c r="AF74" s="20"/>
       <c r="AG74" s="20"/>
@@ -5695,20 +5695,20 @@
         <v>2431323</v>
       </c>
       <c r="X75" s="20">
-        <v>0</v>
+        <v>307406</v>
       </c>
       <c r="Y75" s="20"/>
       <c r="Z75" s="20">
-        <v>2431323</v>
+        <v>2738729</v>
       </c>
       <c r="AA75" s="20"/>
       <c r="AB75" s="20"/>
       <c r="AC75" s="21">
-        <v>1.0777140957446809</v>
+        <v>1.213975620567376</v>
       </c>
       <c r="AD75" s="21"/>
       <c r="AE75" s="20">
-        <v>-175323</v>
+        <v>-482729</v>
       </c>
       <c r="AF75" s="20"/>
       <c r="AG75" s="20"/>
@@ -5856,20 +5856,20 @@
         <v>112830360</v>
       </c>
       <c r="X78" s="20">
-        <v>0</v>
+        <v>8328300</v>
       </c>
       <c r="Y78" s="20"/>
       <c r="Z78" s="20">
-        <v>112830360</v>
+        <v>121158660</v>
       </c>
       <c r="AA78" s="20"/>
       <c r="AB78" s="20"/>
       <c r="AC78" s="21">
-        <v>0.89547904761904762</v>
+        <v>0.96157666666666664</v>
       </c>
       <c r="AD78" s="21"/>
       <c r="AE78" s="20">
-        <v>13169640</v>
+        <v>4841340</v>
       </c>
       <c r="AF78" s="20"/>
       <c r="AG78" s="20"/>
@@ -5909,20 +5909,20 @@
         <v>95304720</v>
       </c>
       <c r="X79" s="20">
-        <v>0</v>
+        <v>8328300</v>
       </c>
       <c r="Y79" s="20"/>
       <c r="Z79" s="20">
-        <v>95304720</v>
+        <v>103633020</v>
       </c>
       <c r="AA79" s="20"/>
       <c r="AB79" s="20"/>
       <c r="AC79" s="21">
-        <v>0.87864365527160082</v>
+        <v>0.95542482575506138</v>
       </c>
       <c r="AD79" s="21"/>
       <c r="AE79" s="20">
-        <v>13163280</v>
+        <v>4834980</v>
       </c>
       <c r="AF79" s="20"/>
       <c r="AG79" s="20"/>
@@ -6284,20 +6284,20 @@
         <v>53385000</v>
       </c>
       <c r="X86" s="20">
-        <v>0</v>
+        <v>4250000</v>
       </c>
       <c r="Y86" s="20"/>
       <c r="Z86" s="20">
-        <v>53385000</v>
+        <v>57635000</v>
       </c>
       <c r="AA86" s="20"/>
       <c r="AB86" s="20"/>
       <c r="AC86" s="21">
-        <v>0.84738095238095235</v>
+        <v>0.91484126984126979</v>
       </c>
       <c r="AD86" s="21"/>
       <c r="AE86" s="20">
-        <v>9615000</v>
+        <v>5365000</v>
       </c>
       <c r="AF86" s="20"/>
       <c r="AG86" s="20"/>
@@ -6337,20 +6337,20 @@
         <v>45455000</v>
       </c>
       <c r="X87" s="20">
-        <v>0</v>
+        <v>4250000</v>
       </c>
       <c r="Y87" s="20"/>
       <c r="Z87" s="20">
-        <v>45455000</v>
+        <v>49705000</v>
       </c>
       <c r="AA87" s="20"/>
       <c r="AB87" s="20"/>
       <c r="AC87" s="21">
-        <v>0.8261541257724464</v>
+        <v>0.90339876408578701</v>
       </c>
       <c r="AD87" s="21"/>
       <c r="AE87" s="20">
-        <v>9565000</v>
+        <v>5315000</v>
       </c>
       <c r="AF87" s="20"/>
       <c r="AG87" s="20"/>
@@ -6751,20 +6751,20 @@
         <v>136865920</v>
       </c>
       <c r="X95" s="20">
-        <v>0</v>
+        <v>136865920</v>
       </c>
       <c r="Y95" s="20"/>
       <c r="Z95" s="20">
-        <v>136865920</v>
+        <v>273731840</v>
       </c>
       <c r="AA95" s="20"/>
       <c r="AB95" s="20"/>
       <c r="AC95" s="21">
-        <v>1013.8216296296297</v>
+        <v>2027.6432592592594</v>
       </c>
       <c r="AD95" s="21"/>
       <c r="AE95" s="20">
-        <v>-136730920</v>
+        <v>-273596840</v>
       </c>
       <c r="AF95" s="20"/>
       <c r="AG95" s="20"/>
@@ -6806,20 +6806,20 @@
         <v>112205200</v>
       </c>
       <c r="X96" s="20">
-        <v>0</v>
+        <v>112205200</v>
       </c>
       <c r="Y96" s="20"/>
       <c r="Z96" s="20">
-        <v>112205200</v>
+        <v>224410400</v>
       </c>
       <c r="AA96" s="20"/>
       <c r="AB96" s="20"/>
       <c r="AC96" s="21">
-        <v>8014.6571428571433</v>
+        <v>16029.314285714287</v>
       </c>
       <c r="AD96" s="21"/>
       <c r="AE96" s="20">
-        <v>-112191200</v>
+        <v>-224396400</v>
       </c>
       <c r="AF96" s="20"/>
       <c r="AG96" s="20"/>
@@ -6859,20 +6859,20 @@
         <v>112205200</v>
       </c>
       <c r="X97" s="20">
-        <v>0</v>
+        <v>112205200</v>
       </c>
       <c r="Y97" s="20"/>
       <c r="Z97" s="20">
-        <v>112205200</v>
+        <v>224410400</v>
       </c>
       <c r="AA97" s="20"/>
       <c r="AB97" s="20"/>
       <c r="AC97" s="21">
-        <v>9350.4333333333325</v>
+        <v>18700.866666666665</v>
       </c>
       <c r="AD97" s="21"/>
       <c r="AE97" s="20">
-        <v>-112193200</v>
+        <v>-224398400</v>
       </c>
       <c r="AF97" s="20"/>
       <c r="AG97" s="20"/>
@@ -7020,20 +7020,20 @@
         <v>2086</v>
       </c>
       <c r="X100" s="20">
-        <v>0</v>
+        <v>2086</v>
       </c>
       <c r="Y100" s="20"/>
       <c r="Z100" s="20">
-        <v>2086</v>
+        <v>4172</v>
       </c>
       <c r="AA100" s="20"/>
       <c r="AB100" s="20"/>
       <c r="AC100" s="21">
-        <v>0.14899999999999999</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="AD100" s="21"/>
       <c r="AE100" s="20">
-        <v>11914</v>
+        <v>9828</v>
       </c>
       <c r="AF100" s="20"/>
       <c r="AG100" s="20"/>
@@ -7073,20 +7073,20 @@
         <v>2086</v>
       </c>
       <c r="X101" s="20">
-        <v>0</v>
+        <v>2086</v>
       </c>
       <c r="Y101" s="20"/>
       <c r="Z101" s="20">
-        <v>2086</v>
+        <v>4172</v>
       </c>
       <c r="AA101" s="20"/>
       <c r="AB101" s="20"/>
       <c r="AC101" s="21">
-        <v>0.17383333333333334</v>
+        <v>0.34766666666666668</v>
       </c>
       <c r="AD101" s="21"/>
       <c r="AE101" s="20">
-        <v>9914</v>
+        <v>7828</v>
       </c>
       <c r="AF101" s="20"/>
       <c r="AG101" s="20"/>
@@ -7234,20 +7234,20 @@
         <v>7571670</v>
       </c>
       <c r="X104" s="20">
-        <v>0</v>
+        <v>7571670</v>
       </c>
       <c r="Y104" s="20"/>
       <c r="Z104" s="20">
-        <v>7571670</v>
+        <v>15143340</v>
       </c>
       <c r="AA104" s="20"/>
       <c r="AB104" s="20"/>
       <c r="AC104" s="21">
-        <v>540.83357142857142</v>
+        <v>1081.6671428571428</v>
       </c>
       <c r="AD104" s="21"/>
       <c r="AE104" s="20">
-        <v>-7557670</v>
+        <v>-15129340</v>
       </c>
       <c r="AF104" s="20"/>
       <c r="AG104" s="20"/>
@@ -7287,20 +7287,20 @@
         <v>7571670</v>
       </c>
       <c r="X105" s="20">
-        <v>0</v>
+        <v>7571670</v>
       </c>
       <c r="Y105" s="20"/>
       <c r="Z105" s="20">
-        <v>7571670</v>
+        <v>15143340</v>
       </c>
       <c r="AA105" s="20"/>
       <c r="AB105" s="20"/>
       <c r="AC105" s="21">
-        <v>630.97249999999997</v>
+        <v>1261.9449999999999</v>
       </c>
       <c r="AD105" s="21"/>
       <c r="AE105" s="20">
-        <v>-7559670</v>
+        <v>-15131340</v>
       </c>
       <c r="AF105" s="20"/>
       <c r="AG105" s="20"/>
@@ -7448,20 +7448,20 @@
         <v>2630444</v>
       </c>
       <c r="X108" s="20">
-        <v>0</v>
+        <v>2630444</v>
       </c>
       <c r="Y108" s="20"/>
       <c r="Z108" s="20">
-        <v>2630444</v>
+        <v>5260888</v>
       </c>
       <c r="AA108" s="20"/>
       <c r="AB108" s="20"/>
       <c r="AC108" s="21">
-        <v>187.88885714285715</v>
+        <v>375.7777142857143</v>
       </c>
       <c r="AD108" s="21"/>
       <c r="AE108" s="20">
-        <v>-2616444</v>
+        <v>-5246888</v>
       </c>
       <c r="AF108" s="20"/>
       <c r="AG108" s="20"/>
@@ -7501,20 +7501,20 @@
         <v>2630444</v>
       </c>
       <c r="X109" s="20">
-        <v>0</v>
+        <v>2630444</v>
       </c>
       <c r="Y109" s="20"/>
       <c r="Z109" s="20">
-        <v>2630444</v>
+        <v>5260888</v>
       </c>
       <c r="AA109" s="20"/>
       <c r="AB109" s="20"/>
       <c r="AC109" s="21">
-        <v>219.20366666666666</v>
+        <v>438.40733333333333</v>
       </c>
       <c r="AD109" s="21"/>
       <c r="AE109" s="20">
-        <v>-2618444</v>
+        <v>-5248888</v>
       </c>
       <c r="AF109" s="20"/>
       <c r="AG109" s="20"/>
@@ -7662,20 +7662,20 @@
         <v>7676520</v>
       </c>
       <c r="X112" s="20">
-        <v>0</v>
+        <v>7676520</v>
       </c>
       <c r="Y112" s="20"/>
       <c r="Z112" s="20">
-        <v>7676520</v>
+        <v>15353040</v>
       </c>
       <c r="AA112" s="20"/>
       <c r="AB112" s="20"/>
       <c r="AC112" s="21">
-        <v>548.32285714285717</v>
+        <v>1096.6457142857143</v>
       </c>
       <c r="AD112" s="21"/>
       <c r="AE112" s="20">
-        <v>-7662520</v>
+        <v>-15339040</v>
       </c>
       <c r="AF112" s="20"/>
       <c r="AG112" s="20"/>
@@ -7715,20 +7715,20 @@
         <v>7676520</v>
       </c>
       <c r="X113" s="20">
-        <v>0</v>
+        <v>7676520</v>
       </c>
       <c r="Y113" s="20"/>
       <c r="Z113" s="20">
-        <v>7676520</v>
+        <v>15353040</v>
       </c>
       <c r="AA113" s="20"/>
       <c r="AB113" s="20"/>
       <c r="AC113" s="21">
-        <v>639.71</v>
+        <v>1279.42</v>
       </c>
       <c r="AD113" s="21"/>
       <c r="AE113" s="20">
-        <v>-7664520</v>
+        <v>-15341040</v>
       </c>
       <c r="AF113" s="20"/>
       <c r="AG113" s="20"/>
@@ -8023,20 +8023,20 @@
         <v>6780000</v>
       </c>
       <c r="X119" s="20">
-        <v>0</v>
+        <v>6780000</v>
       </c>
       <c r="Y119" s="20"/>
       <c r="Z119" s="20">
-        <v>6780000</v>
+        <v>13560000</v>
       </c>
       <c r="AA119" s="20"/>
       <c r="AB119" s="20"/>
       <c r="AC119" s="21">
-        <v>484.28571428571428</v>
+        <v>968.57142857142856</v>
       </c>
       <c r="AD119" s="21"/>
       <c r="AE119" s="20">
-        <v>-6766000</v>
+        <v>-13546000</v>
       </c>
       <c r="AF119" s="20"/>
       <c r="AG119" s="20"/>
@@ -8076,20 +8076,20 @@
         <v>6780000</v>
       </c>
       <c r="X120" s="20">
-        <v>0</v>
+        <v>6780000</v>
       </c>
       <c r="Y120" s="20"/>
       <c r="Z120" s="20">
-        <v>6780000</v>
+        <v>13560000</v>
       </c>
       <c r="AA120" s="20"/>
       <c r="AB120" s="20"/>
       <c r="AC120" s="21">
-        <v>565</v>
+        <v>1130</v>
       </c>
       <c r="AD120" s="21"/>
       <c r="AE120" s="20">
-        <v>-6768000</v>
+        <v>-13548000</v>
       </c>
       <c r="AF120" s="20"/>
       <c r="AG120" s="20"/>
@@ -8451,20 +8451,20 @@
         <v>46945779107</v>
       </c>
       <c r="X127" s="20">
-        <v>0</v>
+        <v>1590161054</v>
       </c>
       <c r="Y127" s="20"/>
       <c r="Z127" s="20">
-        <v>46945779107</v>
+        <v>48535940161</v>
       </c>
       <c r="AA127" s="20"/>
       <c r="AB127" s="20"/>
       <c r="AC127" s="21">
-        <v>0.89664757938202799</v>
+        <v>0.92701908640605513</v>
       </c>
       <c r="AD127" s="21"/>
       <c r="AE127" s="20">
-        <v>5411222893</v>
+        <v>3821061839</v>
       </c>
       <c r="AF127" s="20"/>
       <c r="AG127" s="20"/>
@@ -8506,20 +8506,20 @@
         <v>15933147500</v>
       </c>
       <c r="X128" s="20">
-        <v>0</v>
+        <v>1154795300</v>
       </c>
       <c r="Y128" s="20"/>
       <c r="Z128" s="20">
-        <v>15933147500</v>
+        <v>17087942800</v>
       </c>
       <c r="AA128" s="20"/>
       <c r="AB128" s="20"/>
       <c r="AC128" s="21">
-        <v>1.2115804130482952</v>
+        <v>1.2993927782172132</v>
       </c>
       <c r="AD128" s="21"/>
       <c r="AE128" s="20">
-        <v>-2782433500</v>
+        <v>-3937228800</v>
       </c>
       <c r="AF128" s="20"/>
       <c r="AG128" s="20"/>
@@ -8559,20 +8559,20 @@
         <v>13442394100</v>
       </c>
       <c r="X129" s="20">
-        <v>0</v>
+        <v>1154795300</v>
       </c>
       <c r="Y129" s="20"/>
       <c r="Z129" s="20">
-        <v>13442394100</v>
+        <v>14597189400</v>
       </c>
       <c r="AA129" s="20"/>
       <c r="AB129" s="20"/>
       <c r="AC129" s="21">
-        <v>1.2610173115096117</v>
+        <v>1.3693474834802382</v>
       </c>
       <c r="AD129" s="21"/>
       <c r="AE129" s="20">
-        <v>-2782434100</v>
+        <v>-3937229400</v>
       </c>
       <c r="AF129" s="20"/>
       <c r="AG129" s="20"/>
@@ -8720,20 +8720,20 @@
         <v>215018</v>
       </c>
       <c r="X132" s="20">
-        <v>0</v>
+        <v>15003</v>
       </c>
       <c r="Y132" s="20"/>
       <c r="Z132" s="20">
-        <v>215018</v>
+        <v>230021</v>
       </c>
       <c r="AA132" s="20"/>
       <c r="AB132" s="20"/>
       <c r="AC132" s="21">
-        <v>0.89965690376569041</v>
+        <v>0.96243096234309622</v>
       </c>
       <c r="AD132" s="21"/>
       <c r="AE132" s="20">
-        <v>23982</v>
+        <v>8979</v>
       </c>
       <c r="AF132" s="20"/>
       <c r="AG132" s="20"/>
@@ -8773,20 +8773,20 @@
         <v>181244</v>
       </c>
       <c r="X133" s="20">
-        <v>0</v>
+        <v>15003</v>
       </c>
       <c r="Y133" s="20"/>
       <c r="Z133" s="20">
-        <v>181244</v>
+        <v>196247</v>
       </c>
       <c r="AA133" s="20"/>
       <c r="AB133" s="20"/>
       <c r="AC133" s="21">
-        <v>0.88845098039215686</v>
+        <v>0.96199509803921568</v>
       </c>
       <c r="AD133" s="21"/>
       <c r="AE133" s="20">
-        <v>22756</v>
+        <v>7753</v>
       </c>
       <c r="AF133" s="20"/>
       <c r="AG133" s="20"/>
@@ -8934,20 +8934,20 @@
         <v>1253308570</v>
       </c>
       <c r="X136" s="20">
-        <v>0</v>
+        <v>91064390</v>
       </c>
       <c r="Y136" s="20"/>
       <c r="Z136" s="20">
-        <v>1253308570</v>
+        <v>1344372960</v>
       </c>
       <c r="AA136" s="20"/>
       <c r="AB136" s="20"/>
       <c r="AC136" s="21">
-        <v>0.9137899238088294</v>
+        <v>0.98018516277204626</v>
       </c>
       <c r="AD136" s="21"/>
       <c r="AE136" s="20">
-        <v>118241430</v>
+        <v>27177040</v>
       </c>
       <c r="AF136" s="20"/>
       <c r="AG136" s="20"/>
@@ -8987,20 +8987,20 @@
         <v>1058323510</v>
       </c>
       <c r="X137" s="20">
-        <v>0</v>
+        <v>91064390</v>
       </c>
       <c r="Y137" s="20"/>
       <c r="Z137" s="20">
-        <v>1058323510</v>
+        <v>1149387900</v>
       </c>
       <c r="AA137" s="20"/>
       <c r="AB137" s="20"/>
       <c r="AC137" s="21">
-        <v>0.89950356291710443</v>
+        <v>0.97690214896937189</v>
       </c>
       <c r="AD137" s="21"/>
       <c r="AE137" s="20">
-        <v>118240490</v>
+        <v>27176100</v>
       </c>
       <c r="AF137" s="20"/>
       <c r="AG137" s="20"/>
@@ -9148,20 +9148,20 @@
         <v>391175896</v>
       </c>
       <c r="X140" s="20">
-        <v>0</v>
+        <v>29286128</v>
       </c>
       <c r="Y140" s="20"/>
       <c r="Z140" s="20">
-        <v>391175896</v>
+        <v>420462024</v>
       </c>
       <c r="AA140" s="20"/>
       <c r="AB140" s="20"/>
       <c r="AC140" s="21">
-        <v>0.90287265064384414</v>
+        <v>0.9704679301199981</v>
       </c>
       <c r="AD140" s="21"/>
       <c r="AE140" s="20">
-        <v>42081104</v>
+        <v>12794976</v>
       </c>
       <c r="AF140" s="20"/>
       <c r="AG140" s="20"/>
@@ -9201,20 +9201,20 @@
         <v>330785040</v>
       </c>
       <c r="X141" s="20">
-        <v>0</v>
+        <v>29286128</v>
       </c>
       <c r="Y141" s="20"/>
       <c r="Z141" s="20">
-        <v>330785040</v>
+        <v>360071168</v>
       </c>
       <c r="AA141" s="20"/>
       <c r="AB141" s="20"/>
       <c r="AC141" s="21">
-        <v>0.88714662718846549</v>
+        <v>0.96569035358736699</v>
       </c>
       <c r="AD141" s="21"/>
       <c r="AE141" s="20">
-        <v>42078960</v>
+        <v>12792832</v>
       </c>
       <c r="AF141" s="20"/>
       <c r="AG141" s="20"/>
@@ -9362,20 +9362,20 @@
         <v>3435770000</v>
       </c>
       <c r="X144" s="20">
-        <v>0</v>
+        <v>247680000</v>
       </c>
       <c r="Y144" s="20"/>
       <c r="Z144" s="20">
-        <v>3435770000</v>
+        <v>3683450000</v>
       </c>
       <c r="AA144" s="20"/>
       <c r="AB144" s="20"/>
       <c r="AC144" s="21">
-        <v>0.89240779220779221</v>
+        <v>0.95674025974025978</v>
       </c>
       <c r="AD144" s="21"/>
       <c r="AE144" s="20">
-        <v>414230000</v>
+        <v>166550000</v>
       </c>
       <c r="AF144" s="20"/>
       <c r="AG144" s="20"/>
@@ -9454,20 +9454,20 @@
         <v>2897510000</v>
       </c>
       <c r="X146" s="20">
-        <v>0</v>
+        <v>247680000</v>
       </c>
       <c r="Y146" s="20"/>
       <c r="Z146" s="20">
-        <v>2897510000</v>
+        <v>3145190000</v>
       </c>
       <c r="AA146" s="20"/>
       <c r="AB146" s="20"/>
       <c r="AC146" s="21">
-        <v>0.87492179328303943</v>
+        <v>0.94971036338645354</v>
       </c>
       <c r="AD146" s="21"/>
       <c r="AE146" s="20">
-        <v>414226000</v>
+        <v>166546000</v>
       </c>
       <c r="AF146" s="20"/>
       <c r="AG146" s="20"/>
@@ -9615,20 +9615,20 @@
         <v>227374624</v>
       </c>
       <c r="X149" s="20">
-        <v>0</v>
+        <v>2029653</v>
       </c>
       <c r="Y149" s="20"/>
       <c r="Z149" s="20">
-        <v>227374624</v>
+        <v>229404277</v>
       </c>
       <c r="AA149" s="20"/>
       <c r="AB149" s="20"/>
       <c r="AC149" s="21">
-        <v>0.92530266552720464</v>
+        <v>0.93356235298905299</v>
       </c>
       <c r="AD149" s="21"/>
       <c r="AE149" s="20">
-        <v>18355376</v>
+        <v>16325723</v>
       </c>
       <c r="AF149" s="20"/>
       <c r="AG149" s="20"/>
@@ -9668,20 +9668,20 @@
         <v>41918493</v>
       </c>
       <c r="X150" s="20">
-        <v>0</v>
+        <v>2029653</v>
       </c>
       <c r="Y150" s="20"/>
       <c r="Z150" s="20">
-        <v>41918493</v>
+        <v>43948146</v>
       </c>
       <c r="AA150" s="20"/>
       <c r="AB150" s="20"/>
       <c r="AC150" s="21">
-        <v>0.6955809936280366</v>
+        <v>0.729260354440462</v>
       </c>
       <c r="AD150" s="21"/>
       <c r="AE150" s="20">
-        <v>18345507</v>
+        <v>16315854</v>
       </c>
       <c r="AF150" s="20"/>
       <c r="AG150" s="20"/>
@@ -9829,20 +9829,20 @@
         <v>877947660</v>
       </c>
       <c r="X153" s="20">
-        <v>0</v>
+        <v>65105580</v>
       </c>
       <c r="Y153" s="20"/>
       <c r="Z153" s="20">
-        <v>877947660</v>
+        <v>943053240</v>
       </c>
       <c r="AA153" s="20"/>
       <c r="AB153" s="20"/>
       <c r="AC153" s="21">
-        <v>0.89586495918367348</v>
+        <v>0.96229922448979588</v>
       </c>
       <c r="AD153" s="21"/>
       <c r="AE153" s="20">
-        <v>102052340</v>
+        <v>36946760</v>
       </c>
       <c r="AF153" s="20"/>
       <c r="AG153" s="20"/>
@@ -9882,20 +9882,20 @@
         <v>741218700</v>
       </c>
       <c r="X154" s="20">
-        <v>0</v>
+        <v>65105580</v>
       </c>
       <c r="Y154" s="20"/>
       <c r="Z154" s="20">
-        <v>741218700</v>
+        <v>806324280</v>
       </c>
       <c r="AA154" s="20"/>
       <c r="AB154" s="20"/>
       <c r="AC154" s="21">
-        <v>0.87898771914845175</v>
+        <v>0.95619435906193073</v>
       </c>
       <c r="AD154" s="21"/>
       <c r="AE154" s="20">
-        <v>102045300</v>
+        <v>36939720</v>
       </c>
       <c r="AF154" s="20"/>
       <c r="AG154" s="20"/>
@@ -10257,20 +10257,20 @@
         <v>2775000</v>
       </c>
       <c r="X161" s="20">
-        <v>0</v>
+        <v>185000</v>
       </c>
       <c r="Y161" s="20"/>
       <c r="Z161" s="20">
-        <v>2775000</v>
+        <v>2960000</v>
       </c>
       <c r="AA161" s="20"/>
       <c r="AB161" s="20"/>
       <c r="AC161" s="21">
-        <v>0.5357142857142857</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AD161" s="21"/>
       <c r="AE161" s="20">
-        <v>2405000</v>
+        <v>2220000</v>
       </c>
       <c r="AF161" s="20"/>
       <c r="AG161" s="20"/>
@@ -10310,20 +10310,20 @@
         <v>2220000</v>
       </c>
       <c r="X162" s="20">
-        <v>0</v>
+        <v>185000</v>
       </c>
       <c r="Y162" s="20"/>
       <c r="Z162" s="20">
-        <v>2220000</v>
+        <v>2405000</v>
       </c>
       <c r="AA162" s="20"/>
       <c r="AB162" s="20"/>
       <c r="AC162" s="21">
-        <v>0.48051948051948051</v>
+        <v>0.52056277056277056</v>
       </c>
       <c r="AD162" s="21"/>
       <c r="AE162" s="20">
-        <v>2400000</v>
+        <v>2215000</v>
       </c>
       <c r="AF162" s="20"/>
       <c r="AG162" s="20"/>
@@ -12477,20 +12477,20 @@
         <v>5917998846</v>
       </c>
       <c r="X203" s="31">
-        <v>0</v>
+        <v>9448320</v>
       </c>
       <c r="Y203" s="31"/>
       <c r="Z203" s="31">
-        <v>5917998846</v>
+        <v>5927447166</v>
       </c>
       <c r="AA203" s="31"/>
       <c r="AB203" s="31"/>
       <c r="AC203" s="32">
-        <v>0.88748172826527882</v>
+        <v>0.8888986280621537</v>
       </c>
       <c r="AD203" s="32"/>
       <c r="AE203" s="31">
-        <v>750306154</v>
+        <v>740857834</v>
       </c>
       <c r="AF203" s="31"/>
       <c r="AG203" s="31"/>
@@ -14554,20 +14554,20 @@
         <v>560645387</v>
       </c>
       <c r="X242" s="20">
-        <v>0</v>
+        <v>9448320</v>
       </c>
       <c r="Y242" s="20"/>
       <c r="Z242" s="20">
-        <v>560645387</v>
+        <v>570093707</v>
       </c>
       <c r="AA242" s="20"/>
       <c r="AB242" s="20"/>
       <c r="AC242" s="21">
-        <v>0.73765732762307001</v>
+        <v>0.75008875512311934</v>
       </c>
       <c r="AD242" s="21"/>
       <c r="AE242" s="20">
-        <v>199389613</v>
+        <v>189941293</v>
       </c>
       <c r="AF242" s="20"/>
       <c r="AG242" s="20"/>
@@ -15714,20 +15714,20 @@
         <v>158031069</v>
       </c>
       <c r="X264" s="20">
-        <v>0</v>
+        <v>9448320</v>
       </c>
       <c r="Y264" s="20"/>
       <c r="Z264" s="20">
-        <v>158031069</v>
+        <v>167479389</v>
       </c>
       <c r="AA264" s="20"/>
       <c r="AB264" s="20"/>
       <c r="AC264" s="21">
-        <v>0.68721111932510004</v>
+        <v>0.72829791702904856</v>
       </c>
       <c r="AD264" s="21"/>
       <c r="AE264" s="20">
-        <v>71928931</v>
+        <v>62480611</v>
       </c>
       <c r="AF264" s="20"/>
       <c r="AG264" s="20"/>
@@ -16032,20 +16032,20 @@
         <v>4737535</v>
       </c>
       <c r="X270" s="20">
-        <v>0</v>
+        <v>9448320</v>
       </c>
       <c r="Y270" s="20"/>
       <c r="Z270" s="20">
-        <v>4737535</v>
+        <v>14185855</v>
       </c>
       <c r="AA270" s="20"/>
       <c r="AB270" s="20"/>
       <c r="AC270" s="21">
-        <v>0.32672655172413795</v>
+        <v>0.97833482758620693</v>
       </c>
       <c r="AD270" s="21"/>
       <c r="AE270" s="20">
-        <v>9762465</v>
+        <v>314145</v>
       </c>
       <c r="AF270" s="20"/>
       <c r="AG270" s="20"/>

--- a/Database/Akrual.xlsx
+++ b/Database/Akrual.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D0373B4-E131-4C64-B601-FC1934E016AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{876B2871-EC8D-49A7-9027-8C23F5BD8716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="45" windowWidth="14925" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GLP039_LAPORAN REALISASI SUPER " sheetId="1" r:id="rId1"/>
@@ -2155,19 +2155,19 @@
         <v>80919905375</v>
       </c>
       <c r="X9" s="4">
-        <v>1938614197</v>
+        <v>3695933614</v>
       </c>
       <c r="Y9" s="18">
-        <v>82858519572</v>
+        <v>84615838989</v>
       </c>
       <c r="Z9" s="18"/>
       <c r="AA9" s="18"/>
       <c r="AB9" s="18"/>
       <c r="AC9" s="5">
-        <v>0.97468227062914359</v>
+        <v>0.99535399018712911</v>
       </c>
       <c r="AD9" s="18">
-        <v>2152280428</v>
+        <v>394961011</v>
       </c>
       <c r="AE9" s="18"/>
       <c r="AF9" s="18"/>
@@ -2807,20 +2807,20 @@
         <v>76886537335</v>
       </c>
       <c r="X21" s="20">
-        <v>1938614197</v>
+        <v>3695933614</v>
       </c>
       <c r="Y21" s="20"/>
       <c r="Z21" s="20">
-        <v>78825151532</v>
+        <v>80582470949</v>
       </c>
       <c r="AA21" s="20"/>
       <c r="AB21" s="20"/>
       <c r="AC21" s="21">
-        <v>0.97342161556187279</v>
+        <v>0.9951229719526683</v>
       </c>
       <c r="AD21" s="21"/>
       <c r="AE21" s="20">
-        <v>2152248468</v>
+        <v>394929051</v>
       </c>
       <c r="AF21" s="20"/>
       <c r="AG21" s="20"/>
@@ -2862,20 +2862,20 @@
         <v>76886537335</v>
       </c>
       <c r="X22" s="20">
-        <v>1938614197</v>
+        <v>3695933614</v>
       </c>
       <c r="Y22" s="20"/>
       <c r="Z22" s="20">
-        <v>78825151532</v>
+        <v>80582470949</v>
       </c>
       <c r="AA22" s="20"/>
       <c r="AB22" s="20"/>
       <c r="AC22" s="21">
-        <v>0.97342161556187279</v>
+        <v>0.9951229719526683</v>
       </c>
       <c r="AD22" s="21"/>
       <c r="AE22" s="20">
-        <v>2152248468</v>
+        <v>394929051</v>
       </c>
       <c r="AF22" s="20"/>
       <c r="AG22" s="20"/>
@@ -2917,20 +2917,20 @@
         <v>76885937335</v>
       </c>
       <c r="X23" s="23">
-        <v>1938614197</v>
+        <v>3695933614</v>
       </c>
       <c r="Y23" s="23"/>
       <c r="Z23" s="23">
-        <v>78824551532</v>
+        <v>80581870949</v>
       </c>
       <c r="AA23" s="23"/>
       <c r="AB23" s="23"/>
       <c r="AC23" s="24">
-        <v>0.97342141862854548</v>
+        <v>0.99512293581618438</v>
       </c>
       <c r="AD23" s="24"/>
       <c r="AE23" s="23">
-        <v>2152248468</v>
+        <v>394929051</v>
       </c>
       <c r="AF23" s="23"/>
       <c r="AG23" s="23"/>
@@ -3557,20 +3557,20 @@
         <v>14661052</v>
       </c>
       <c r="X35" s="28">
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="Y35" s="28"/>
       <c r="Z35" s="27">
-        <v>14661052</v>
+        <v>16461052</v>
       </c>
       <c r="AA35" s="27"/>
       <c r="AB35" s="27"/>
       <c r="AC35" s="29">
-        <v>0.83873295194508013</v>
+        <v>0.94170778032036617</v>
       </c>
       <c r="AD35" s="29"/>
       <c r="AE35" s="27">
-        <v>2818948</v>
+        <v>1018948</v>
       </c>
       <c r="AF35" s="27"/>
       <c r="AG35" s="27"/>
@@ -3612,20 +3612,20 @@
         <v>14661052</v>
       </c>
       <c r="X36" s="31">
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="Y36" s="31"/>
       <c r="Z36" s="31">
-        <v>14661052</v>
+        <v>16461052</v>
       </c>
       <c r="AA36" s="31"/>
       <c r="AB36" s="31"/>
       <c r="AC36" s="32">
-        <v>0.83873295194508013</v>
+        <v>0.94170778032036617</v>
       </c>
       <c r="AD36" s="32"/>
       <c r="AE36" s="31">
-        <v>2818948</v>
+        <v>1018948</v>
       </c>
       <c r="AF36" s="31"/>
       <c r="AG36" s="31"/>
@@ -3938,20 +3938,20 @@
         <v>12261052</v>
       </c>
       <c r="X42" s="20">
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="Y42" s="20"/>
       <c r="Z42" s="20">
-        <v>12261052</v>
+        <v>14061052</v>
       </c>
       <c r="AA42" s="20"/>
       <c r="AB42" s="20"/>
       <c r="AC42" s="21">
-        <v>0.81306710875331567</v>
+        <v>0.9324305039787798</v>
       </c>
       <c r="AD42" s="21"/>
       <c r="AE42" s="20">
-        <v>2818948</v>
+        <v>1018948</v>
       </c>
       <c r="AF42" s="20"/>
       <c r="AG42" s="20"/>
@@ -3993,20 +3993,20 @@
         <v>12261052</v>
       </c>
       <c r="X43" s="20">
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="Y43" s="20"/>
       <c r="Z43" s="20">
-        <v>12261052</v>
+        <v>14061052</v>
       </c>
       <c r="AA43" s="20"/>
       <c r="AB43" s="20"/>
       <c r="AC43" s="21">
-        <v>0.81306710875331567</v>
+        <v>0.9324305039787798</v>
       </c>
       <c r="AD43" s="21"/>
       <c r="AE43" s="20">
-        <v>2818948</v>
+        <v>1018948</v>
       </c>
       <c r="AF43" s="20"/>
       <c r="AG43" s="20"/>
@@ -4046,20 +4046,20 @@
         <v>11511952</v>
       </c>
       <c r="X44" s="20">
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="Y44" s="20"/>
       <c r="Z44" s="20">
-        <v>11511952</v>
+        <v>13311952</v>
       </c>
       <c r="AA44" s="20"/>
       <c r="AB44" s="20"/>
       <c r="AC44" s="21">
-        <v>0.8366244186046512</v>
+        <v>0.9674383720930233</v>
       </c>
       <c r="AD44" s="21"/>
       <c r="AE44" s="20">
-        <v>2248048</v>
+        <v>448048</v>
       </c>
       <c r="AF44" s="20"/>
       <c r="AG44" s="20"/>
@@ -4154,20 +4154,20 @@
         <v>76870226283</v>
       </c>
       <c r="X46" s="28">
-        <v>1938614197</v>
+        <v>3694133614</v>
       </c>
       <c r="Y46" s="28"/>
       <c r="Z46" s="27">
-        <v>78808840480</v>
+        <v>80564359897</v>
       </c>
       <c r="AA46" s="27"/>
       <c r="AB46" s="27"/>
       <c r="AC46" s="29">
-        <v>0.97345015499960663</v>
+        <v>0.99513440562650368</v>
       </c>
       <c r="AD46" s="29"/>
       <c r="AE46" s="27">
-        <v>2149429520</v>
+        <v>393910103</v>
       </c>
       <c r="AF46" s="27"/>
       <c r="AG46" s="27"/>
@@ -4209,20 +4209,20 @@
         <v>70952227437</v>
       </c>
       <c r="X47" s="31">
-        <v>1929165877</v>
+        <v>3610829713</v>
       </c>
       <c r="Y47" s="31"/>
       <c r="Z47" s="31">
-        <v>72881393314</v>
+        <v>74563057150</v>
       </c>
       <c r="AA47" s="31"/>
       <c r="AB47" s="31"/>
       <c r="AC47" s="32">
-        <v>0.98103954301230323</v>
+        <v>1.0036760301340835</v>
       </c>
       <c r="AD47" s="32"/>
       <c r="AE47" s="31">
-        <v>1408571686</v>
+        <v>-273092150</v>
       </c>
       <c r="AF47" s="31"/>
       <c r="AG47" s="31"/>
@@ -4264,20 +4264,20 @@
         <v>5428525892</v>
       </c>
       <c r="X48" s="20">
-        <v>202138903</v>
+        <v>233886903</v>
       </c>
       <c r="Y48" s="20"/>
       <c r="Z48" s="20">
-        <v>5630664795</v>
+        <v>5662412795</v>
       </c>
       <c r="AA48" s="20"/>
       <c r="AB48" s="20"/>
       <c r="AC48" s="21">
-        <v>0.87884826017954487</v>
+        <v>0.88380356751536004</v>
       </c>
       <c r="AD48" s="21"/>
       <c r="AE48" s="20">
-        <v>776203205</v>
+        <v>744455205</v>
       </c>
       <c r="AF48" s="20"/>
       <c r="AG48" s="20"/>
@@ -6070,20 +6070,20 @@
         <v>245993000</v>
       </c>
       <c r="X82" s="20">
-        <v>0</v>
+        <v>31748000</v>
       </c>
       <c r="Y82" s="20"/>
       <c r="Z82" s="20">
-        <v>245993000</v>
+        <v>277741000</v>
       </c>
       <c r="AA82" s="20"/>
       <c r="AB82" s="20"/>
       <c r="AC82" s="21">
-        <v>0.78487696862955303</v>
+        <v>0.88617364780355823</v>
       </c>
       <c r="AD82" s="21"/>
       <c r="AE82" s="20">
-        <v>67423000</v>
+        <v>35675000</v>
       </c>
       <c r="AF82" s="20"/>
       <c r="AG82" s="20"/>
@@ -6123,20 +6123,20 @@
         <v>13930000</v>
       </c>
       <c r="X83" s="20">
-        <v>0</v>
+        <v>1610000</v>
       </c>
       <c r="Y83" s="20"/>
       <c r="Z83" s="20">
-        <v>13930000</v>
+        <v>15540000</v>
       </c>
       <c r="AA83" s="20"/>
       <c r="AB83" s="20"/>
       <c r="AC83" s="21">
-        <v>0.46064814814814814</v>
+        <v>0.51388888888888884</v>
       </c>
       <c r="AD83" s="21"/>
       <c r="AE83" s="20">
-        <v>16310000</v>
+        <v>14700000</v>
       </c>
       <c r="AF83" s="20"/>
       <c r="AG83" s="20"/>
@@ -6176,20 +6176,20 @@
         <v>201354000</v>
       </c>
       <c r="X84" s="20">
-        <v>0</v>
+        <v>26899000</v>
       </c>
       <c r="Y84" s="20"/>
       <c r="Z84" s="20">
-        <v>201354000</v>
+        <v>228253000</v>
       </c>
       <c r="AA84" s="20"/>
       <c r="AB84" s="20"/>
       <c r="AC84" s="21">
-        <v>0.81272401433691754</v>
+        <v>0.92129629629629628</v>
       </c>
       <c r="AD84" s="21"/>
       <c r="AE84" s="20">
-        <v>46398000</v>
+        <v>19499000</v>
       </c>
       <c r="AF84" s="20"/>
       <c r="AG84" s="20"/>
@@ -6229,20 +6229,20 @@
         <v>30709000</v>
       </c>
       <c r="X85" s="20">
-        <v>0</v>
+        <v>3239000</v>
       </c>
       <c r="Y85" s="20"/>
       <c r="Z85" s="20">
-        <v>30709000</v>
+        <v>33948000</v>
       </c>
       <c r="AA85" s="20"/>
       <c r="AB85" s="20"/>
       <c r="AC85" s="21">
-        <v>0.86689814814814814</v>
+        <v>0.95833333333333337</v>
       </c>
       <c r="AD85" s="21"/>
       <c r="AE85" s="20">
-        <v>4715000</v>
+        <v>1476000</v>
       </c>
       <c r="AF85" s="20"/>
       <c r="AG85" s="20"/>
@@ -6751,20 +6751,20 @@
         <v>136865920</v>
       </c>
       <c r="X95" s="20">
-        <v>136865920</v>
+        <v>143788036</v>
       </c>
       <c r="Y95" s="20"/>
       <c r="Z95" s="20">
-        <v>273731840</v>
+        <v>280653956</v>
       </c>
       <c r="AA95" s="20"/>
       <c r="AB95" s="20"/>
       <c r="AC95" s="21">
-        <v>2027.6432592592594</v>
+        <v>2078.9181925925927</v>
       </c>
       <c r="AD95" s="21"/>
       <c r="AE95" s="20">
-        <v>-273596840</v>
+        <v>-280518956</v>
       </c>
       <c r="AF95" s="20"/>
       <c r="AG95" s="20"/>
@@ -6806,20 +6806,20 @@
         <v>112205200</v>
       </c>
       <c r="X96" s="20">
-        <v>112205200</v>
+        <v>118612400</v>
       </c>
       <c r="Y96" s="20"/>
       <c r="Z96" s="20">
-        <v>224410400</v>
+        <v>230817600</v>
       </c>
       <c r="AA96" s="20"/>
       <c r="AB96" s="20"/>
       <c r="AC96" s="21">
-        <v>16029.314285714287</v>
+        <v>16486.971428571429</v>
       </c>
       <c r="AD96" s="21"/>
       <c r="AE96" s="20">
-        <v>-224396400</v>
+        <v>-230803600</v>
       </c>
       <c r="AF96" s="20"/>
       <c r="AG96" s="20"/>
@@ -6859,20 +6859,20 @@
         <v>112205200</v>
       </c>
       <c r="X97" s="20">
-        <v>112205200</v>
+        <v>118612400</v>
       </c>
       <c r="Y97" s="20"/>
       <c r="Z97" s="20">
-        <v>224410400</v>
+        <v>230817600</v>
       </c>
       <c r="AA97" s="20"/>
       <c r="AB97" s="20"/>
       <c r="AC97" s="21">
-        <v>18700.866666666665</v>
+        <v>19234.8</v>
       </c>
       <c r="AD97" s="21"/>
       <c r="AE97" s="20">
-        <v>-224398400</v>
+        <v>-230805600</v>
       </c>
       <c r="AF97" s="20"/>
       <c r="AG97" s="20"/>
@@ -7020,20 +7020,20 @@
         <v>2086</v>
       </c>
       <c r="X100" s="20">
-        <v>2086</v>
+        <v>2162</v>
       </c>
       <c r="Y100" s="20"/>
       <c r="Z100" s="20">
-        <v>4172</v>
+        <v>4248</v>
       </c>
       <c r="AA100" s="20"/>
       <c r="AB100" s="20"/>
       <c r="AC100" s="21">
-        <v>0.29799999999999999</v>
+        <v>0.30342857142857144</v>
       </c>
       <c r="AD100" s="21"/>
       <c r="AE100" s="20">
-        <v>9828</v>
+        <v>9752</v>
       </c>
       <c r="AF100" s="20"/>
       <c r="AG100" s="20"/>
@@ -7073,20 +7073,20 @@
         <v>2086</v>
       </c>
       <c r="X101" s="20">
-        <v>2086</v>
+        <v>2162</v>
       </c>
       <c r="Y101" s="20"/>
       <c r="Z101" s="20">
-        <v>4172</v>
+        <v>4248</v>
       </c>
       <c r="AA101" s="20"/>
       <c r="AB101" s="20"/>
       <c r="AC101" s="21">
-        <v>0.34766666666666668</v>
+        <v>0.35399999999999998</v>
       </c>
       <c r="AD101" s="21"/>
       <c r="AE101" s="20">
-        <v>7828</v>
+        <v>7752</v>
       </c>
       <c r="AF101" s="20"/>
       <c r="AG101" s="20"/>
@@ -7662,20 +7662,20 @@
         <v>7676520</v>
       </c>
       <c r="X112" s="20">
-        <v>7676520</v>
+        <v>7821360</v>
       </c>
       <c r="Y112" s="20"/>
       <c r="Z112" s="20">
-        <v>15353040</v>
+        <v>15497880</v>
       </c>
       <c r="AA112" s="20"/>
       <c r="AB112" s="20"/>
       <c r="AC112" s="21">
-        <v>1096.6457142857143</v>
+        <v>1106.9914285714285</v>
       </c>
       <c r="AD112" s="21"/>
       <c r="AE112" s="20">
-        <v>-15339040</v>
+        <v>-15483880</v>
       </c>
       <c r="AF112" s="20"/>
       <c r="AG112" s="20"/>
@@ -7715,20 +7715,20 @@
         <v>7676520</v>
       </c>
       <c r="X113" s="20">
-        <v>7676520</v>
+        <v>7821360</v>
       </c>
       <c r="Y113" s="20"/>
       <c r="Z113" s="20">
-        <v>15353040</v>
+        <v>15497880</v>
       </c>
       <c r="AA113" s="20"/>
       <c r="AB113" s="20"/>
       <c r="AC113" s="21">
-        <v>1279.42</v>
+        <v>1291.49</v>
       </c>
       <c r="AD113" s="21"/>
       <c r="AE113" s="20">
-        <v>-15341040</v>
+        <v>-15485880</v>
       </c>
       <c r="AF113" s="20"/>
       <c r="AG113" s="20"/>
@@ -8023,20 +8023,20 @@
         <v>6780000</v>
       </c>
       <c r="X119" s="20">
-        <v>6780000</v>
+        <v>7150000</v>
       </c>
       <c r="Y119" s="20"/>
       <c r="Z119" s="20">
-        <v>13560000</v>
+        <v>13930000</v>
       </c>
       <c r="AA119" s="20"/>
       <c r="AB119" s="20"/>
       <c r="AC119" s="21">
-        <v>968.57142857142856</v>
+        <v>995</v>
       </c>
       <c r="AD119" s="21"/>
       <c r="AE119" s="20">
-        <v>-13546000</v>
+        <v>-13916000</v>
       </c>
       <c r="AF119" s="20"/>
       <c r="AG119" s="20"/>
@@ -8076,20 +8076,20 @@
         <v>6780000</v>
       </c>
       <c r="X120" s="20">
-        <v>6780000</v>
+        <v>7150000</v>
       </c>
       <c r="Y120" s="20"/>
       <c r="Z120" s="20">
-        <v>13560000</v>
+        <v>13930000</v>
       </c>
       <c r="AA120" s="20"/>
       <c r="AB120" s="20"/>
       <c r="AC120" s="21">
-        <v>1130</v>
+        <v>1160.8333333333333</v>
       </c>
       <c r="AD120" s="21"/>
       <c r="AE120" s="20">
-        <v>-13548000</v>
+        <v>-13918000</v>
       </c>
       <c r="AF120" s="20"/>
       <c r="AG120" s="20"/>
@@ -8451,20 +8451,20 @@
         <v>46945779107</v>
       </c>
       <c r="X127" s="20">
-        <v>1590161054</v>
+        <v>1842950054</v>
       </c>
       <c r="Y127" s="20"/>
       <c r="Z127" s="20">
-        <v>48535940161</v>
+        <v>48788729161</v>
       </c>
       <c r="AA127" s="20"/>
       <c r="AB127" s="20"/>
       <c r="AC127" s="21">
-        <v>0.92701908640605513</v>
+        <v>0.93184726583466337</v>
       </c>
       <c r="AD127" s="21"/>
       <c r="AE127" s="20">
-        <v>3821061839</v>
+        <v>3568272839</v>
       </c>
       <c r="AF127" s="20"/>
       <c r="AG127" s="20"/>
@@ -10043,20 +10043,20 @@
         <v>1960479000</v>
       </c>
       <c r="X157" s="20">
-        <v>0</v>
+        <v>252789000</v>
       </c>
       <c r="Y157" s="20"/>
       <c r="Z157" s="20">
-        <v>1960479000</v>
+        <v>2213268000</v>
       </c>
       <c r="AA157" s="20"/>
       <c r="AB157" s="20"/>
       <c r="AC157" s="21">
-        <v>0.75977663374072213</v>
+        <v>0.8577441077441077</v>
       </c>
       <c r="AD157" s="21"/>
       <c r="AE157" s="20">
-        <v>619857000</v>
+        <v>367068000</v>
       </c>
       <c r="AF157" s="20"/>
       <c r="AG157" s="20"/>
@@ -10096,20 +10096,20 @@
         <v>174930000</v>
       </c>
       <c r="X158" s="20">
-        <v>0</v>
+        <v>24010000</v>
       </c>
       <c r="Y158" s="20"/>
       <c r="Z158" s="20">
-        <v>174930000</v>
+        <v>198940000</v>
       </c>
       <c r="AA158" s="20"/>
       <c r="AB158" s="20"/>
       <c r="AC158" s="21">
-        <v>0.68055555555555558</v>
+        <v>0.77396514161220042</v>
       </c>
       <c r="AD158" s="21"/>
       <c r="AE158" s="20">
-        <v>82110000</v>
+        <v>58100000</v>
       </c>
       <c r="AF158" s="20"/>
       <c r="AG158" s="20"/>
@@ -10149,20 +10149,20 @@
         <v>1398304000</v>
       </c>
       <c r="X159" s="20">
-        <v>0</v>
+        <v>183187000</v>
       </c>
       <c r="Y159" s="20"/>
       <c r="Z159" s="20">
-        <v>1398304000</v>
+        <v>1581491000</v>
       </c>
       <c r="AA159" s="20"/>
       <c r="AB159" s="20"/>
       <c r="AC159" s="21">
-        <v>0.78812145478812146</v>
+        <v>0.89137053720387049</v>
       </c>
       <c r="AD159" s="21"/>
       <c r="AE159" s="20">
-        <v>375920000</v>
+        <v>192733000</v>
       </c>
       <c r="AF159" s="20"/>
       <c r="AG159" s="20"/>
@@ -10202,20 +10202,20 @@
         <v>387245000</v>
       </c>
       <c r="X160" s="20">
-        <v>0</v>
+        <v>45592000</v>
       </c>
       <c r="Y160" s="20"/>
       <c r="Z160" s="20">
-        <v>387245000</v>
+        <v>432837000</v>
       </c>
       <c r="AA160" s="20"/>
       <c r="AB160" s="20"/>
       <c r="AC160" s="21">
-        <v>0.70527180406212664</v>
+        <v>0.78830645161290325</v>
       </c>
       <c r="AD160" s="21"/>
       <c r="AE160" s="20">
-        <v>161827000</v>
+        <v>116235000</v>
       </c>
       <c r="AF160" s="20"/>
       <c r="AG160" s="20"/>
@@ -10685,20 +10685,20 @@
         <v>18441056518</v>
       </c>
       <c r="X169" s="20">
-        <v>0</v>
+        <v>1390204720</v>
       </c>
       <c r="Y169" s="20"/>
       <c r="Z169" s="20">
-        <v>18441056518</v>
+        <v>19831261238</v>
       </c>
       <c r="AA169" s="20"/>
       <c r="AB169" s="20"/>
       <c r="AC169" s="21">
-        <v>1.1877562816083513</v>
+        <v>1.2772969425401071</v>
       </c>
       <c r="AD169" s="21"/>
       <c r="AE169" s="20">
-        <v>-2915096518</v>
+        <v>-4305301238</v>
       </c>
       <c r="AF169" s="20"/>
       <c r="AG169" s="20"/>
@@ -10740,20 +10740,20 @@
         <v>6960502066</v>
       </c>
       <c r="X170" s="20">
-        <v>0</v>
+        <v>1060348000</v>
       </c>
       <c r="Y170" s="20"/>
       <c r="Z170" s="20">
-        <v>6960502066</v>
+        <v>8020850066</v>
       </c>
       <c r="AA170" s="20"/>
       <c r="AB170" s="20"/>
       <c r="AC170" s="21">
-        <v>1.5592850893365586</v>
+        <v>1.7968232453819593</v>
       </c>
       <c r="AD170" s="21"/>
       <c r="AE170" s="20">
-        <v>-2496596066</v>
+        <v>-3556944066</v>
       </c>
       <c r="AF170" s="20"/>
       <c r="AG170" s="20"/>
@@ -10793,20 +10793,20 @@
         <v>5871388400</v>
       </c>
       <c r="X171" s="20">
-        <v>0</v>
+        <v>1060348000</v>
       </c>
       <c r="Y171" s="20"/>
       <c r="Z171" s="20">
-        <v>5871388400</v>
+        <v>6931736400</v>
       </c>
       <c r="AA171" s="20"/>
       <c r="AB171" s="20"/>
       <c r="AC171" s="21">
-        <v>1.7397819830839545</v>
+        <v>2.0539792768959435</v>
       </c>
       <c r="AD171" s="21"/>
       <c r="AE171" s="20">
-        <v>-2496604400</v>
+        <v>-3556952400</v>
       </c>
       <c r="AF171" s="20"/>
       <c r="AG171" s="20"/>
@@ -10993,20 +10993,20 @@
         <v>131546</v>
       </c>
       <c r="X175" s="20">
-        <v>0</v>
+        <v>5920</v>
       </c>
       <c r="Y175" s="20"/>
       <c r="Z175" s="20">
-        <v>131546</v>
+        <v>137466</v>
       </c>
       <c r="AA175" s="20"/>
       <c r="AB175" s="20"/>
       <c r="AC175" s="21">
-        <v>0.83256962025316461</v>
+        <v>0.87003797468354427</v>
       </c>
       <c r="AD175" s="21"/>
       <c r="AE175" s="20">
-        <v>26454</v>
+        <v>20534</v>
       </c>
       <c r="AF175" s="20"/>
       <c r="AG175" s="20"/>
@@ -11046,20 +11046,20 @@
         <v>118426</v>
       </c>
       <c r="X176" s="20">
-        <v>0</v>
+        <v>5920</v>
       </c>
       <c r="Y176" s="20"/>
       <c r="Z176" s="20">
-        <v>118426</v>
+        <v>124346</v>
       </c>
       <c r="AA176" s="20"/>
       <c r="AB176" s="20"/>
       <c r="AC176" s="21">
-        <v>0.82240277777777782</v>
+        <v>0.86351388888888891</v>
       </c>
       <c r="AD176" s="21"/>
       <c r="AE176" s="20">
-        <v>25574</v>
+        <v>19654</v>
       </c>
       <c r="AF176" s="20"/>
       <c r="AG176" s="20"/>
@@ -11207,20 +11207,20 @@
         <v>473036570</v>
       </c>
       <c r="X179" s="20">
-        <v>0</v>
+        <v>70065440</v>
       </c>
       <c r="Y179" s="20"/>
       <c r="Z179" s="20">
-        <v>473036570</v>
+        <v>543102010</v>
       </c>
       <c r="AA179" s="20"/>
       <c r="AB179" s="20"/>
       <c r="AC179" s="21">
-        <v>1.310111087723574</v>
+        <v>1.5041627015559482</v>
       </c>
       <c r="AD179" s="21"/>
       <c r="AE179" s="20">
-        <v>-111970570</v>
+        <v>-182036010</v>
       </c>
       <c r="AF179" s="20"/>
       <c r="AG179" s="20"/>
@@ -11260,20 +11260,20 @@
         <v>399311800</v>
       </c>
       <c r="X180" s="20">
-        <v>0</v>
+        <v>70065440</v>
       </c>
       <c r="Y180" s="20"/>
       <c r="Z180" s="20">
-        <v>399311800</v>
+        <v>469377240</v>
       </c>
       <c r="AA180" s="20"/>
       <c r="AB180" s="20"/>
       <c r="AC180" s="21">
-        <v>1.3896839980510893</v>
+        <v>1.6335255794529129</v>
       </c>
       <c r="AD180" s="21"/>
       <c r="AE180" s="20">
-        <v>-111971800</v>
+        <v>-182037240</v>
       </c>
       <c r="AF180" s="20"/>
       <c r="AG180" s="20"/>
@@ -11421,20 +11421,20 @@
         <v>141009928</v>
       </c>
       <c r="X183" s="20">
-        <v>0</v>
+        <v>20735760</v>
       </c>
       <c r="Y183" s="20"/>
       <c r="Z183" s="20">
-        <v>141009928</v>
+        <v>161745688</v>
       </c>
       <c r="AA183" s="20"/>
       <c r="AB183" s="20"/>
       <c r="AC183" s="21">
-        <v>1.2582532747974444</v>
+        <v>1.4432816504265267</v>
       </c>
       <c r="AD183" s="21"/>
       <c r="AE183" s="20">
-        <v>-28941928</v>
+        <v>-49677688</v>
       </c>
       <c r="AF183" s="20"/>
       <c r="AG183" s="20"/>
@@ -11474,20 +11474,20 @@
         <v>119127344</v>
       </c>
       <c r="X184" s="20">
-        <v>0</v>
+        <v>20735760</v>
       </c>
       <c r="Y184" s="20"/>
       <c r="Z184" s="20">
-        <v>119127344</v>
+        <v>139863104</v>
       </c>
       <c r="AA184" s="20"/>
       <c r="AB184" s="20"/>
       <c r="AC184" s="21">
-        <v>1.3209951652251053</v>
+        <v>1.5509326236416057</v>
       </c>
       <c r="AD184" s="21"/>
       <c r="AE184" s="20">
-        <v>-28947344</v>
+        <v>-49683104</v>
       </c>
       <c r="AF184" s="20"/>
       <c r="AG184" s="20"/>
@@ -11635,20 +11635,20 @@
         <v>1133130000</v>
       </c>
       <c r="X187" s="20">
-        <v>0</v>
+        <v>175320000</v>
       </c>
       <c r="Y187" s="20"/>
       <c r="Z187" s="20">
-        <v>1133130000</v>
+        <v>1308450000</v>
       </c>
       <c r="AA187" s="20"/>
       <c r="AB187" s="20"/>
       <c r="AC187" s="21">
-        <v>1.2616407241632708</v>
+        <v>1.4568441445654352</v>
       </c>
       <c r="AD187" s="21"/>
       <c r="AE187" s="20">
-        <v>-234990000</v>
+        <v>-410310000</v>
       </c>
       <c r="AF187" s="20"/>
       <c r="AG187" s="20"/>
@@ -11688,20 +11688,20 @@
         <v>955320000</v>
       </c>
       <c r="X188" s="20">
-        <v>0</v>
+        <v>175320000</v>
       </c>
       <c r="Y188" s="20"/>
       <c r="Z188" s="20">
-        <v>955320000</v>
+        <v>1130640000</v>
       </c>
       <c r="AA188" s="20"/>
       <c r="AB188" s="20"/>
       <c r="AC188" s="21">
-        <v>1.32623652689623</v>
+        <v>1.5696270011828011</v>
       </c>
       <c r="AD188" s="21"/>
       <c r="AE188" s="20">
-        <v>-234996000</v>
+        <v>-410316000</v>
       </c>
       <c r="AF188" s="20"/>
       <c r="AG188" s="20"/>
@@ -11849,20 +11849,20 @@
         <v>425745110</v>
       </c>
       <c r="X191" s="20">
-        <v>0</v>
+        <v>63729600</v>
       </c>
       <c r="Y191" s="20"/>
       <c r="Z191" s="20">
-        <v>425745110</v>
+        <v>489474710</v>
       </c>
       <c r="AA191" s="20"/>
       <c r="AB191" s="20"/>
       <c r="AC191" s="21">
-        <v>1.2872190005684085</v>
+        <v>1.4799022518654685</v>
       </c>
       <c r="AD191" s="21"/>
       <c r="AE191" s="20">
-        <v>-94997110</v>
+        <v>-158726710</v>
       </c>
       <c r="AF191" s="20"/>
       <c r="AG191" s="20"/>
@@ -11902,20 +11902,20 @@
         <v>359203200</v>
       </c>
       <c r="X192" s="20">
-        <v>0</v>
+        <v>63729600</v>
       </c>
       <c r="Y192" s="20"/>
       <c r="Z192" s="20">
-        <v>359203200</v>
+        <v>422932800</v>
       </c>
       <c r="AA192" s="20"/>
       <c r="AB192" s="20"/>
       <c r="AC192" s="21">
-        <v>1.3595676068492528</v>
+        <v>1.6007812145160558</v>
       </c>
       <c r="AD192" s="21"/>
       <c r="AE192" s="20">
-        <v>-94999200</v>
+        <v>-158728800</v>
       </c>
       <c r="AF192" s="20"/>
       <c r="AG192" s="20"/>
@@ -12477,20 +12477,20 @@
         <v>5917998846</v>
       </c>
       <c r="X203" s="31">
-        <v>9448320</v>
+        <v>83303901</v>
       </c>
       <c r="Y203" s="31"/>
       <c r="Z203" s="31">
-        <v>5927447166</v>
+        <v>6001302747</v>
       </c>
       <c r="AA203" s="31"/>
       <c r="AB203" s="31"/>
       <c r="AC203" s="32">
-        <v>0.8888986280621537</v>
+        <v>0.89997424337968945</v>
       </c>
       <c r="AD203" s="32"/>
       <c r="AE203" s="31">
-        <v>740857834</v>
+        <v>667002253</v>
       </c>
       <c r="AF203" s="31"/>
       <c r="AG203" s="31"/>
@@ -12532,20 +12532,20 @@
         <v>4659213091</v>
       </c>
       <c r="X204" s="20">
-        <v>0</v>
+        <v>23400000</v>
       </c>
       <c r="Y204" s="20"/>
       <c r="Z204" s="20">
-        <v>4659213091</v>
+        <v>4682613091</v>
       </c>
       <c r="AA204" s="20"/>
       <c r="AB204" s="20"/>
       <c r="AC204" s="21">
-        <v>0.94518676494752918</v>
+        <v>0.94993378335338308</v>
       </c>
       <c r="AD204" s="21"/>
       <c r="AE204" s="20">
-        <v>270196909</v>
+        <v>246796909</v>
       </c>
       <c r="AF204" s="20"/>
       <c r="AG204" s="20"/>
@@ -12587,20 +12587,20 @@
         <v>1700954357</v>
       </c>
       <c r="X205" s="20">
-        <v>0</v>
+        <v>23400000</v>
       </c>
       <c r="Y205" s="20"/>
       <c r="Z205" s="20">
-        <v>1700954357</v>
+        <v>1724354357</v>
       </c>
       <c r="AA205" s="20"/>
       <c r="AB205" s="20"/>
       <c r="AC205" s="21">
-        <v>0.92320896562541899</v>
+        <v>0.93590953557706447</v>
       </c>
       <c r="AD205" s="21"/>
       <c r="AE205" s="20">
-        <v>141482643</v>
+        <v>118082643</v>
       </c>
       <c r="AF205" s="20"/>
       <c r="AG205" s="20"/>
@@ -13011,20 +13011,20 @@
         <v>0</v>
       </c>
       <c r="X213" s="20">
-        <v>0</v>
+        <v>23400000</v>
       </c>
       <c r="Y213" s="20"/>
       <c r="Z213" s="20">
-        <v>0</v>
+        <v>23400000</v>
       </c>
       <c r="AA213" s="20"/>
       <c r="AB213" s="20"/>
       <c r="AC213" s="21">
-        <v>0</v>
+        <v>0.2988505747126437</v>
       </c>
       <c r="AD213" s="21"/>
       <c r="AE213" s="20">
-        <v>78300000</v>
+        <v>54900000</v>
       </c>
       <c r="AF213" s="20"/>
       <c r="AG213" s="20"/>
@@ -14014,20 +14014,20 @@
         <v>587220368</v>
       </c>
       <c r="X232" s="20">
-        <v>0</v>
+        <v>50455581</v>
       </c>
       <c r="Y232" s="20"/>
       <c r="Z232" s="20">
-        <v>587220368</v>
+        <v>637675949</v>
       </c>
       <c r="AA232" s="20"/>
       <c r="AB232" s="20"/>
       <c r="AC232" s="21">
-        <v>0.69355644163084051</v>
+        <v>0.75314870907544762</v>
       </c>
       <c r="AD232" s="21"/>
       <c r="AE232" s="20">
-        <v>259459632</v>
+        <v>209004051</v>
       </c>
       <c r="AF232" s="20"/>
       <c r="AG232" s="20"/>
@@ -14069,20 +14069,20 @@
         <v>430266392</v>
       </c>
       <c r="X233" s="20">
-        <v>0</v>
+        <v>40247519</v>
       </c>
       <c r="Y233" s="20"/>
       <c r="Z233" s="20">
-        <v>430266392</v>
+        <v>470513911</v>
       </c>
       <c r="AA233" s="20"/>
       <c r="AB233" s="20"/>
       <c r="AC233" s="21">
-        <v>0.66658361529404475</v>
+        <v>0.72893646743508711</v>
       </c>
       <c r="AD233" s="21"/>
       <c r="AE233" s="20">
-        <v>215213608</v>
+        <v>174966089</v>
       </c>
       <c r="AF233" s="20"/>
       <c r="AG233" s="20"/>
@@ -14122,20 +14122,20 @@
         <v>430266392</v>
       </c>
       <c r="X234" s="20">
-        <v>0</v>
+        <v>40247519</v>
       </c>
       <c r="Y234" s="20"/>
       <c r="Z234" s="20">
-        <v>430266392</v>
+        <v>470513911</v>
       </c>
       <c r="AA234" s="20"/>
       <c r="AB234" s="20"/>
       <c r="AC234" s="21">
-        <v>0.66658361529404475</v>
+        <v>0.72893646743508711</v>
       </c>
       <c r="AD234" s="21"/>
       <c r="AE234" s="20">
-        <v>215213608</v>
+        <v>174966089</v>
       </c>
       <c r="AF234" s="20"/>
       <c r="AG234" s="20"/>
@@ -14177,20 +14177,20 @@
         <v>5219220</v>
       </c>
       <c r="X235" s="20">
-        <v>0</v>
+        <v>266012</v>
       </c>
       <c r="Y235" s="20"/>
       <c r="Z235" s="20">
-        <v>5219220</v>
+        <v>5485232</v>
       </c>
       <c r="AA235" s="20"/>
       <c r="AB235" s="20"/>
       <c r="AC235" s="21">
-        <v>0.86987000000000003</v>
+        <v>0.91420533333333331</v>
       </c>
       <c r="AD235" s="21"/>
       <c r="AE235" s="20">
-        <v>780780</v>
+        <v>514768</v>
       </c>
       <c r="AF235" s="20"/>
       <c r="AG235" s="20"/>
@@ -14230,20 +14230,20 @@
         <v>5219220</v>
       </c>
       <c r="X236" s="20">
-        <v>0</v>
+        <v>266012</v>
       </c>
       <c r="Y236" s="20"/>
       <c r="Z236" s="20">
-        <v>5219220</v>
+        <v>5485232</v>
       </c>
       <c r="AA236" s="20"/>
       <c r="AB236" s="20"/>
       <c r="AC236" s="21">
-        <v>0.86987000000000003</v>
+        <v>0.91420533333333331</v>
       </c>
       <c r="AD236" s="21"/>
       <c r="AE236" s="20">
-        <v>780780</v>
+        <v>514768</v>
       </c>
       <c r="AF236" s="20"/>
       <c r="AG236" s="20"/>
@@ -14285,20 +14285,20 @@
         <v>29408400</v>
       </c>
       <c r="X237" s="20">
-        <v>0</v>
+        <v>691300</v>
       </c>
       <c r="Y237" s="20"/>
       <c r="Z237" s="20">
-        <v>29408400</v>
+        <v>30099700</v>
       </c>
       <c r="AA237" s="20"/>
       <c r="AB237" s="20"/>
       <c r="AC237" s="21">
-        <v>0.74263636363636365</v>
+        <v>0.76009343434343435</v>
       </c>
       <c r="AD237" s="21"/>
       <c r="AE237" s="20">
-        <v>10191600</v>
+        <v>9500300</v>
       </c>
       <c r="AF237" s="20"/>
       <c r="AG237" s="20"/>
@@ -14338,20 +14338,20 @@
         <v>29408400</v>
       </c>
       <c r="X238" s="20">
-        <v>0</v>
+        <v>691300</v>
       </c>
       <c r="Y238" s="20"/>
       <c r="Z238" s="20">
-        <v>29408400</v>
+        <v>30099700</v>
       </c>
       <c r="AA238" s="20"/>
       <c r="AB238" s="20"/>
       <c r="AC238" s="21">
-        <v>0.74263636363636365</v>
+        <v>0.76009343434343435</v>
       </c>
       <c r="AD238" s="21"/>
       <c r="AE238" s="20">
-        <v>10191600</v>
+        <v>9500300</v>
       </c>
       <c r="AF238" s="20"/>
       <c r="AG238" s="20"/>
@@ -14393,20 +14393,20 @@
         <v>122326356</v>
       </c>
       <c r="X239" s="20">
-        <v>0</v>
+        <v>9250750</v>
       </c>
       <c r="Y239" s="20"/>
       <c r="Z239" s="20">
-        <v>122326356</v>
+        <v>131577106</v>
       </c>
       <c r="AA239" s="20"/>
       <c r="AB239" s="20"/>
       <c r="AC239" s="21">
-        <v>0.78615910025706937</v>
+        <v>0.84561122107969156</v>
       </c>
       <c r="AD239" s="21"/>
       <c r="AE239" s="20">
-        <v>33273644</v>
+        <v>24022894</v>
       </c>
       <c r="AF239" s="20"/>
       <c r="AG239" s="20"/>
@@ -14446,20 +14446,20 @@
         <v>95184750</v>
       </c>
       <c r="X240" s="20">
-        <v>0</v>
+        <v>9250750</v>
       </c>
       <c r="Y240" s="20"/>
       <c r="Z240" s="20">
-        <v>95184750</v>
+        <v>104435500</v>
       </c>
       <c r="AA240" s="20"/>
       <c r="AB240" s="20"/>
       <c r="AC240" s="21">
-        <v>0.75007683215130028</v>
+        <v>0.82297478329393225</v>
       </c>
       <c r="AD240" s="21"/>
       <c r="AE240" s="20">
-        <v>31715250</v>
+        <v>22464500</v>
       </c>
       <c r="AF240" s="20"/>
       <c r="AG240" s="20"/>

--- a/Database/Akrual.xlsx
+++ b/Database/Akrual.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B8BD4D9-BA9A-4AD3-9B9F-B8C4D70ADE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B726F07-E42D-4E5A-81B2-FC7DCC3C45A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="600" windowWidth="14925" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="135" yWindow="165" windowWidth="14925" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GLP039_LAPORAN REALISASI SUPER " sheetId="1" r:id="rId1"/>

--- a/Database/Akrual.xlsx
+++ b/Database/Akrual.xlsx
@@ -601,7 +601,7 @@
       <c r="A3" s="4" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Periode November 2025</t>
+            <t xml:space="preserve">Periode Desember 2025</t>
           </r>
         </is>
       </c>
@@ -979,22 +979,22 @@
       <c r="U9" s="10" t="inlineStr"/>
       <c r="V9" s="10" t="inlineStr"/>
       <c r="W9" s="11" t="n">
-        <v>8.0919905375E10</v>
+        <v>9.0559784495E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>9.387303917E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>9.0307209292E10</v>
+        <v>9.0559784495E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.90310787405397</v>
+        <v>0.9056337261582303</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>9.688828708E9</v>
+        <v>9.436253505E9</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1711,23 +1711,23 @@
       <c r="U21" s="14" t="inlineStr"/>
       <c r="V21" s="14" t="inlineStr"/>
       <c r="W21" s="14" t="n">
-        <v>7.6886537335E10</v>
+        <v>8.6526416455E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>9.387303917E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>8.6273841252E10</v>
+        <v>8.6526416455E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.8990357398470017</v>
+        <v>0.9016677558926631</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>9.688796748E9</v>
+        <v>9.436221545E9</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1774,23 +1774,23 @@
       <c r="U22" s="14" t="inlineStr"/>
       <c r="V22" s="14" t="inlineStr"/>
       <c r="W22" s="14" t="n">
-        <v>7.6886537335E10</v>
+        <v>8.6526416455E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>9.387303917E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>8.6273841252E10</v>
+        <v>8.6526416455E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.8990357398470017</v>
+        <v>0.9016677558926631</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>9.688796748E9</v>
+        <v>9.436221545E9</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1837,23 +1837,23 @@
       <c r="U23" s="17" t="inlineStr"/>
       <c r="V23" s="17" t="inlineStr"/>
       <c r="W23" s="17" t="n">
-        <v>7.6885937335E10</v>
+        <v>8.6525816455E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>9.387303917E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>8.6273241252E10</v>
+        <v>8.6525816455E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.8990351085707454</v>
+        <v>0.9016671410730147</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>9.688796748E9</v>
+        <v>9.436221545E9</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -2561,10 +2561,10 @@
       <c r="U35" s="21" t="inlineStr"/>
       <c r="V35" s="21" t="inlineStr"/>
       <c r="W35" s="22" t="n">
-        <v>1.4661052E7</v>
+        <v>1.6461052E7</v>
       </c>
       <c r="X35" s="22" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y35" s="22" t="inlineStr"/>
       <c r="Z35" s="21" t="n">
@@ -2624,10 +2624,10 @@
       <c r="U36" s="25" t="inlineStr"/>
       <c r="V36" s="25" t="inlineStr"/>
       <c r="W36" s="25" t="n">
-        <v>1.4661052E7</v>
+        <v>1.6461052E7</v>
       </c>
       <c r="X36" s="25" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y36" s="25" t="inlineStr"/>
       <c r="Z36" s="25" t="n">
@@ -2990,10 +2990,10 @@
       <c r="U42" s="14" t="inlineStr"/>
       <c r="V42" s="14" t="inlineStr"/>
       <c r="W42" s="14" t="n">
-        <v>1.2261052E7</v>
+        <v>1.4061052E7</v>
       </c>
       <c r="X42" s="14" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y42" s="14" t="inlineStr"/>
       <c r="Z42" s="14" t="n">
@@ -3053,10 +3053,10 @@
       <c r="U43" s="14" t="inlineStr"/>
       <c r="V43" s="14" t="inlineStr"/>
       <c r="W43" s="14" t="n">
-        <v>1.2261052E7</v>
+        <v>1.4061052E7</v>
       </c>
       <c r="X43" s="14" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y43" s="14" t="inlineStr"/>
       <c r="Z43" s="14" t="n">
@@ -3100,7 +3100,7 @@
       <c r="O44" s="13" t="inlineStr"/>
       <c r="P44" s="13" t="inlineStr"/>
       <c r="Q44" s="14" t="n">
-        <v>1.376E7</v>
+        <v>1.431E7</v>
       </c>
       <c r="R44" s="14" t="inlineStr"/>
       <c r="S44" s="14" t="n">
@@ -3110,10 +3110,10 @@
       <c r="U44" s="14" t="inlineStr"/>
       <c r="V44" s="14" t="inlineStr"/>
       <c r="W44" s="14" t="n">
-        <v>1.1511952E7</v>
+        <v>1.3311952E7</v>
       </c>
       <c r="X44" s="14" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y44" s="14" t="inlineStr"/>
       <c r="Z44" s="14" t="n">
@@ -3122,11 +3122,11 @@
       <c r="AA44" s="14" t="inlineStr"/>
       <c r="AB44" s="14" t="inlineStr"/>
       <c r="AC44" s="15" t="n">
-        <v>0.9674383720930233</v>
+        <v>0.9302552061495458</v>
       </c>
       <c r="AD44" s="15" t="inlineStr"/>
       <c r="AE44" s="14" t="n">
-        <v>448048.0</v>
+        <v>998048.0</v>
       </c>
       <c r="AF44" s="14" t="inlineStr"/>
       <c r="AG44" s="14" t="inlineStr"/>
@@ -3157,7 +3157,7 @@
       <c r="O45" s="13" t="inlineStr"/>
       <c r="P45" s="13" t="inlineStr"/>
       <c r="Q45" s="14" t="n">
-        <v>1320000.0</v>
+        <v>770000.0</v>
       </c>
       <c r="R45" s="14" t="inlineStr"/>
       <c r="S45" s="14" t="n">
@@ -3179,11 +3179,11 @@
       <c r="AA45" s="14" t="inlineStr"/>
       <c r="AB45" s="14" t="inlineStr"/>
       <c r="AC45" s="15" t="n">
-        <v>0.5675</v>
+        <v>0.9728571428571429</v>
       </c>
       <c r="AD45" s="15" t="inlineStr"/>
       <c r="AE45" s="14" t="n">
-        <v>570900.0</v>
+        <v>20900.0</v>
       </c>
       <c r="AF45" s="14" t="inlineStr"/>
       <c r="AG45" s="14" t="inlineStr"/>
@@ -3230,23 +3230,23 @@
       <c r="U46" s="21" t="inlineStr"/>
       <c r="V46" s="21" t="inlineStr"/>
       <c r="W46" s="22" t="n">
-        <v>7.6870226283E10</v>
+        <v>8.6508305403E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>9.385503917E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>8.62557302E10</v>
+        <v>8.6508305403E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.8990262290597087</v>
+        <v>0.9016587698982197</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>9.6877778E9</v>
+        <v>9.435202597E9</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -3293,23 +3293,23 @@
       <c r="U47" s="25" t="inlineStr"/>
       <c r="V47" s="25" t="inlineStr"/>
       <c r="W47" s="25" t="n">
-        <v>7.0952227437E10</v>
+        <v>8.0279551347E10</v>
       </c>
       <c r="X47" s="25" t="n">
-        <v>9.158498601E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y47" s="25" t="inlineStr"/>
       <c r="Z47" s="25" t="n">
-        <v>8.0110726038E10</v>
+        <v>8.0279551347E10</v>
       </c>
       <c r="AA47" s="25" t="inlineStr"/>
       <c r="AB47" s="25" t="inlineStr"/>
       <c r="AC47" s="26" t="n">
-        <v>0.9001536611409838</v>
+        <v>0.9020506445726097</v>
       </c>
       <c r="AD47" s="26" t="inlineStr"/>
       <c r="AE47" s="25" t="n">
-        <v>8.885996962E9</v>
+        <v>8.717171653E9</v>
       </c>
       <c r="AF47" s="25" t="inlineStr"/>
       <c r="AG47" s="25" t="inlineStr"/>
@@ -3356,23 +3356,23 @@
       <c r="U48" s="14" t="inlineStr"/>
       <c r="V48" s="14" t="inlineStr"/>
       <c r="W48" s="14" t="n">
-        <v>5.428525892E9</v>
+        <v>5.831238104E9</v>
       </c>
       <c r="X48" s="14" t="n">
-        <v>2.33886903E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y48" s="14" t="inlineStr"/>
       <c r="Z48" s="14" t="n">
-        <v>5.662412795E9</v>
+        <v>5.831238104E9</v>
       </c>
       <c r="AA48" s="14" t="inlineStr"/>
       <c r="AB48" s="14" t="inlineStr"/>
       <c r="AC48" s="15" t="n">
-        <v>0.9528023328325681</v>
+        <v>0.981210213727161</v>
       </c>
       <c r="AD48" s="15" t="inlineStr"/>
       <c r="AE48" s="14" t="n">
-        <v>2.80491205E8</v>
+        <v>1.11665896E8</v>
       </c>
       <c r="AF48" s="14" t="inlineStr"/>
       <c r="AG48" s="14" t="inlineStr"/>
@@ -3419,10 +3419,10 @@
       <c r="U49" s="14" t="inlineStr"/>
       <c r="V49" s="14" t="inlineStr"/>
       <c r="W49" s="14" t="n">
-        <v>2.1400157E9</v>
+        <v>2.3012465E9</v>
       </c>
       <c r="X49" s="14" t="n">
-        <v>1.612308E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y49" s="14" t="inlineStr"/>
       <c r="Z49" s="14" t="n">
@@ -3476,10 +3476,10 @@
       <c r="U50" s="14" t="inlineStr"/>
       <c r="V50" s="14" t="inlineStr"/>
       <c r="W50" s="14" t="n">
-        <v>1.8098353E9</v>
+        <v>1.9710661E9</v>
       </c>
       <c r="X50" s="14" t="n">
-        <v>1.612308E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y50" s="14" t="inlineStr"/>
       <c r="Z50" s="14" t="n">
@@ -3653,10 +3653,10 @@
       <c r="U53" s="14" t="inlineStr"/>
       <c r="V53" s="14" t="inlineStr"/>
       <c r="W53" s="14" t="n">
-        <v>25093.0</v>
+        <v>26896.0</v>
       </c>
       <c r="X53" s="14" t="n">
-        <v>1803.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y53" s="14" t="inlineStr"/>
       <c r="Z53" s="14" t="n">
@@ -3710,10 +3710,10 @@
       <c r="U54" s="14" t="inlineStr"/>
       <c r="V54" s="14" t="inlineStr"/>
       <c r="W54" s="14" t="n">
-        <v>20511.0</v>
+        <v>22314.0</v>
       </c>
       <c r="X54" s="14" t="n">
-        <v>1803.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y54" s="14" t="inlineStr"/>
       <c r="Z54" s="14" t="n">
@@ -3887,10 +3887,10 @@
       <c r="U57" s="14" t="inlineStr"/>
       <c r="V57" s="14" t="inlineStr"/>
       <c r="W57" s="14" t="n">
-        <v>1.6302116E8</v>
+        <v>1.7519677E8</v>
       </c>
       <c r="X57" s="14" t="n">
-        <v>1.217561E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y57" s="14" t="inlineStr"/>
       <c r="Z57" s="14" t="n">
@@ -3944,10 +3944,10 @@
       <c r="U58" s="14" t="inlineStr"/>
       <c r="V58" s="14" t="inlineStr"/>
       <c r="W58" s="14" t="n">
-        <v>1.3782284E8</v>
+        <v>1.4999845E8</v>
       </c>
       <c r="X58" s="14" t="n">
-        <v>1.217561E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y58" s="14" t="inlineStr"/>
       <c r="Z58" s="14" t="n">
@@ -4164,10 +4164,10 @@
       <c r="U62" s="14" t="inlineStr"/>
       <c r="V62" s="14" t="inlineStr"/>
       <c r="W62" s="14" t="n">
-        <v>4.9459528E7</v>
+        <v>5.3110512E7</v>
       </c>
       <c r="X62" s="14" t="n">
-        <v>3650984.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y62" s="14" t="inlineStr"/>
       <c r="Z62" s="14" t="n">
@@ -4221,10 +4221,10 @@
       <c r="U63" s="14" t="inlineStr"/>
       <c r="V63" s="14" t="inlineStr"/>
       <c r="W63" s="14" t="n">
-        <v>4.178347E7</v>
+        <v>4.5434454E7</v>
       </c>
       <c r="X63" s="14" t="n">
-        <v>3650984.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y63" s="14" t="inlineStr"/>
       <c r="Z63" s="14" t="n">
@@ -4398,10 +4398,10 @@
       <c r="U66" s="14" t="inlineStr"/>
       <c r="V66" s="14" t="inlineStr"/>
       <c r="W66" s="14" t="n">
-        <v>2.34E7</v>
+        <v>2.52E7</v>
       </c>
       <c r="X66" s="14" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y66" s="14" t="inlineStr"/>
       <c r="Z66" s="14" t="n">
@@ -4455,10 +4455,10 @@
       <c r="U67" s="14" t="inlineStr"/>
       <c r="V67" s="14" t="inlineStr"/>
       <c r="W67" s="14" t="n">
-        <v>1.98E7</v>
+        <v>2.16E7</v>
       </c>
       <c r="X67" s="14" t="n">
-        <v>1800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y67" s="14" t="inlineStr"/>
       <c r="Z67" s="14" t="n">
@@ -4632,10 +4632,10 @@
       <c r="U70" s="14" t="inlineStr"/>
       <c r="V70" s="14" t="inlineStr"/>
       <c r="W70" s="14" t="n">
-        <v>1.49682E8</v>
+        <v>1.60076E8</v>
       </c>
       <c r="X70" s="14" t="n">
-        <v>1.0394E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y70" s="14" t="inlineStr"/>
       <c r="Z70" s="14" t="n">
@@ -4689,10 +4689,10 @@
       <c r="U71" s="14" t="inlineStr"/>
       <c r="V71" s="14" t="inlineStr"/>
       <c r="W71" s="14" t="n">
-        <v>1.25654E8</v>
+        <v>1.36048E8</v>
       </c>
       <c r="X71" s="14" t="n">
-        <v>1.0394E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y71" s="14" t="inlineStr"/>
       <c r="Z71" s="14" t="n">
@@ -4866,10 +4866,10 @@
       <c r="U74" s="14" t="inlineStr"/>
       <c r="V74" s="14" t="inlineStr"/>
       <c r="W74" s="14" t="n">
-        <v>1.9962339E7</v>
+        <v>2.0269745E7</v>
       </c>
       <c r="X74" s="14" t="n">
-        <v>307406.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y74" s="14" t="inlineStr"/>
       <c r="Z74" s="14" t="n">
@@ -4923,10 +4923,10 @@
       <c r="U75" s="14" t="inlineStr"/>
       <c r="V75" s="14" t="inlineStr"/>
       <c r="W75" s="14" t="n">
-        <v>2431323.0</v>
+        <v>2738729.0</v>
       </c>
       <c r="X75" s="14" t="n">
-        <v>307406.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y75" s="14" t="inlineStr"/>
       <c r="Z75" s="14" t="n">
@@ -5100,10 +5100,10 @@
       <c r="U78" s="14" t="inlineStr"/>
       <c r="V78" s="14" t="inlineStr"/>
       <c r="W78" s="14" t="n">
-        <v>1.1283036E8</v>
+        <v>1.2115866E8</v>
       </c>
       <c r="X78" s="14" t="n">
-        <v>8328300.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y78" s="14" t="inlineStr"/>
       <c r="Z78" s="14" t="n">
@@ -5157,10 +5157,10 @@
       <c r="U79" s="14" t="inlineStr"/>
       <c r="V79" s="14" t="inlineStr"/>
       <c r="W79" s="14" t="n">
-        <v>9.530472E7</v>
+        <v>1.0363302E8</v>
       </c>
       <c r="X79" s="14" t="n">
-        <v>8328300.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y79" s="14" t="inlineStr"/>
       <c r="Z79" s="14" t="n">
@@ -5334,10 +5334,10 @@
       <c r="U82" s="14" t="inlineStr"/>
       <c r="V82" s="14" t="inlineStr"/>
       <c r="W82" s="14" t="n">
-        <v>2.45993E8</v>
+        <v>2.77741E8</v>
       </c>
       <c r="X82" s="14" t="n">
-        <v>3.1748E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y82" s="14" t="inlineStr"/>
       <c r="Z82" s="14" t="n">
@@ -5391,10 +5391,10 @@
       <c r="U83" s="14" t="inlineStr"/>
       <c r="V83" s="14" t="inlineStr"/>
       <c r="W83" s="14" t="n">
-        <v>1.393E7</v>
+        <v>1.554E7</v>
       </c>
       <c r="X83" s="14" t="n">
-        <v>1610000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y83" s="14" t="inlineStr"/>
       <c r="Z83" s="14" t="n">
@@ -5448,10 +5448,10 @@
       <c r="U84" s="14" t="inlineStr"/>
       <c r="V84" s="14" t="inlineStr"/>
       <c r="W84" s="14" t="n">
-        <v>2.01354E8</v>
+        <v>2.28253E8</v>
       </c>
       <c r="X84" s="14" t="n">
-        <v>2.6899E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y84" s="14" t="inlineStr"/>
       <c r="Z84" s="14" t="n">
@@ -5505,10 +5505,10 @@
       <c r="U85" s="14" t="inlineStr"/>
       <c r="V85" s="14" t="inlineStr"/>
       <c r="W85" s="14" t="n">
-        <v>3.0709E7</v>
+        <v>3.3948E7</v>
       </c>
       <c r="X85" s="14" t="n">
-        <v>3239000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y85" s="14" t="inlineStr"/>
       <c r="Z85" s="14" t="n">
@@ -5568,10 +5568,10 @@
       <c r="U86" s="14" t="inlineStr"/>
       <c r="V86" s="14" t="inlineStr"/>
       <c r="W86" s="14" t="n">
-        <v>5.3385E7</v>
+        <v>5.7635E7</v>
       </c>
       <c r="X86" s="14" t="n">
-        <v>4250000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y86" s="14" t="inlineStr"/>
       <c r="Z86" s="14" t="n">
@@ -5625,10 +5625,10 @@
       <c r="U87" s="14" t="inlineStr"/>
       <c r="V87" s="14" t="inlineStr"/>
       <c r="W87" s="14" t="n">
-        <v>4.5455E7</v>
+        <v>4.9705E7</v>
       </c>
       <c r="X87" s="14" t="n">
-        <v>4250000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y87" s="14" t="inlineStr"/>
       <c r="Z87" s="14" t="n">
@@ -5845,23 +5845,23 @@
       <c r="U91" s="14" t="inlineStr"/>
       <c r="V91" s="14" t="inlineStr"/>
       <c r="W91" s="14" t="n">
-        <v>2.470751712E9</v>
+        <v>2.639577021E9</v>
       </c>
       <c r="X91" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y91" s="14" t="inlineStr"/>
       <c r="Z91" s="14" t="n">
-        <v>2.470751712E9</v>
+        <v>2.639577021E9</v>
       </c>
       <c r="AA91" s="14" t="inlineStr"/>
       <c r="AB91" s="14" t="inlineStr"/>
       <c r="AC91" s="15" t="n">
-        <v>0.9321396440988989</v>
+        <v>0.9958323100522745</v>
       </c>
       <c r="AD91" s="15" t="inlineStr"/>
       <c r="AE91" s="14" t="n">
-        <v>1.79872288E8</v>
+        <v>1.1046979E7</v>
       </c>
       <c r="AF91" s="14" t="inlineStr"/>
       <c r="AG91" s="14" t="inlineStr"/>
@@ -5902,23 +5902,23 @@
       <c r="U92" s="14" t="inlineStr"/>
       <c r="V92" s="14" t="inlineStr"/>
       <c r="W92" s="14" t="n">
-        <v>2.02813692E9</v>
+        <v>2.196962229E9</v>
       </c>
       <c r="X92" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y92" s="14" t="inlineStr"/>
       <c r="Z92" s="14" t="n">
-        <v>2.02813692E9</v>
+        <v>2.196962229E9</v>
       </c>
       <c r="AA92" s="14" t="inlineStr"/>
       <c r="AB92" s="14" t="inlineStr"/>
       <c r="AC92" s="15" t="n">
-        <v>0.9185402717391304</v>
+        <v>0.9950010095108696</v>
       </c>
       <c r="AD92" s="15" t="inlineStr"/>
       <c r="AE92" s="14" t="n">
-        <v>1.7986308E8</v>
+        <v>1.1037771E7</v>
       </c>
       <c r="AF92" s="14" t="inlineStr"/>
       <c r="AG92" s="14" t="inlineStr"/>
@@ -6079,10 +6079,10 @@
       <c r="U95" s="14" t="inlineStr"/>
       <c r="V95" s="14" t="inlineStr"/>
       <c r="W95" s="14" t="n">
-        <v>1.3686592E8</v>
+        <v>5.93914035E8</v>
       </c>
       <c r="X95" s="14" t="n">
-        <v>4.57048115E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y95" s="14" t="inlineStr"/>
       <c r="Z95" s="14" t="n">
@@ -6142,10 +6142,10 @@
       <c r="U96" s="14" t="inlineStr"/>
       <c r="V96" s="14" t="inlineStr"/>
       <c r="W96" s="14" t="n">
-        <v>1.122052E8</v>
+        <v>3.462264E8</v>
       </c>
       <c r="X96" s="14" t="n">
-        <v>2.340212E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y96" s="14" t="inlineStr"/>
       <c r="Z96" s="14" t="n">
@@ -6199,10 +6199,10 @@
       <c r="U97" s="14" t="inlineStr"/>
       <c r="V97" s="14" t="inlineStr"/>
       <c r="W97" s="14" t="n">
-        <v>1.122052E8</v>
+        <v>3.462264E8</v>
       </c>
       <c r="X97" s="14" t="n">
-        <v>2.340212E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y97" s="14" t="inlineStr"/>
       <c r="Z97" s="14" t="n">
@@ -6262,10 +6262,10 @@
       <c r="U98" s="14" t="inlineStr"/>
       <c r="V98" s="14" t="inlineStr"/>
       <c r="W98" s="14" t="n">
-        <v>2086.0</v>
+        <v>6359.0</v>
       </c>
       <c r="X98" s="14" t="n">
-        <v>4273.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y98" s="14" t="inlineStr"/>
       <c r="Z98" s="14" t="n">
@@ -6319,10 +6319,10 @@
       <c r="U99" s="14" t="inlineStr"/>
       <c r="V99" s="14" t="inlineStr"/>
       <c r="W99" s="14" t="n">
-        <v>2086.0</v>
+        <v>6359.0</v>
       </c>
       <c r="X99" s="14" t="n">
-        <v>4273.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y99" s="14" t="inlineStr"/>
       <c r="Z99" s="14" t="n">
@@ -6382,10 +6382,10 @@
       <c r="U100" s="14" t="inlineStr"/>
       <c r="V100" s="14" t="inlineStr"/>
       <c r="W100" s="14" t="n">
-        <v>7571670.0</v>
+        <v>2.271501E7</v>
       </c>
       <c r="X100" s="14" t="n">
-        <v>1.514334E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y100" s="14" t="inlineStr"/>
       <c r="Z100" s="14" t="n">
@@ -6439,10 +6439,10 @@
       <c r="U101" s="14" t="inlineStr"/>
       <c r="V101" s="14" t="inlineStr"/>
       <c r="W101" s="14" t="n">
-        <v>7571670.0</v>
+        <v>2.271501E7</v>
       </c>
       <c r="X101" s="14" t="n">
-        <v>1.514334E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y101" s="14" t="inlineStr"/>
       <c r="Z101" s="14" t="n">
@@ -6502,10 +6502,10 @@
       <c r="U102" s="14" t="inlineStr"/>
       <c r="V102" s="14" t="inlineStr"/>
       <c r="W102" s="14" t="n">
-        <v>2630444.0</v>
+        <v>7891332.0</v>
       </c>
       <c r="X102" s="14" t="n">
-        <v>5260888.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y102" s="14" t="inlineStr"/>
       <c r="Z102" s="14" t="n">
@@ -6559,10 +6559,10 @@
       <c r="U103" s="14" t="inlineStr"/>
       <c r="V103" s="14" t="inlineStr"/>
       <c r="W103" s="14" t="n">
-        <v>2630444.0</v>
+        <v>7891332.0</v>
       </c>
       <c r="X103" s="14" t="n">
-        <v>5260888.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y103" s="14" t="inlineStr"/>
       <c r="Z103" s="14" t="n">
@@ -6622,10 +6622,10 @@
       <c r="U104" s="14" t="inlineStr"/>
       <c r="V104" s="14" t="inlineStr"/>
       <c r="W104" s="14" t="n">
-        <v>7676520.0</v>
+        <v>2.324682E7</v>
       </c>
       <c r="X104" s="14" t="n">
-        <v>1.55703E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y104" s="14" t="inlineStr"/>
       <c r="Z104" s="14" t="n">
@@ -6679,10 +6679,10 @@
       <c r="U105" s="14" t="inlineStr"/>
       <c r="V105" s="14" t="inlineStr"/>
       <c r="W105" s="14" t="n">
-        <v>7676520.0</v>
+        <v>2.324682E7</v>
       </c>
       <c r="X105" s="14" t="n">
-        <v>1.55703E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y105" s="14" t="inlineStr"/>
       <c r="Z105" s="14" t="n">
@@ -6742,10 +6742,10 @@
       <c r="U106" s="14" t="inlineStr"/>
       <c r="V106" s="14" t="inlineStr"/>
       <c r="W106" s="14" t="n">
-        <v>0.0</v>
+        <v>3.0833E7</v>
       </c>
       <c r="X106" s="14" t="n">
-        <v>3.0833E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y106" s="14" t="inlineStr"/>
       <c r="Z106" s="14" t="n">
@@ -6799,10 +6799,10 @@
       <c r="U107" s="14" t="inlineStr"/>
       <c r="V107" s="14" t="inlineStr"/>
       <c r="W107" s="14" t="n">
-        <v>0.0</v>
+        <v>8855000.0</v>
       </c>
       <c r="X107" s="14" t="n">
-        <v>8855000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y107" s="14" t="inlineStr"/>
       <c r="Z107" s="14" t="n">
@@ -6856,10 +6856,10 @@
       <c r="U108" s="14" t="inlineStr"/>
       <c r="V108" s="14" t="inlineStr"/>
       <c r="W108" s="14" t="n">
-        <v>0.0</v>
+        <v>2.1978E7</v>
       </c>
       <c r="X108" s="14" t="n">
-        <v>2.1978E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y108" s="14" t="inlineStr"/>
       <c r="Z108" s="14" t="n">
@@ -6919,10 +6919,10 @@
       <c r="U109" s="14" t="inlineStr"/>
       <c r="V109" s="14" t="inlineStr"/>
       <c r="W109" s="14" t="n">
-        <v>6780000.0</v>
+        <v>2.0895E7</v>
       </c>
       <c r="X109" s="14" t="n">
-        <v>1.4115E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y109" s="14" t="inlineStr"/>
       <c r="Z109" s="14" t="n">
@@ -6976,10 +6976,10 @@
       <c r="U110" s="14" t="inlineStr"/>
       <c r="V110" s="14" t="inlineStr"/>
       <c r="W110" s="14" t="n">
-        <v>6780000.0</v>
+        <v>2.0895E7</v>
       </c>
       <c r="X110" s="14" t="n">
-        <v>1.4115E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y110" s="14" t="inlineStr"/>
       <c r="Z110" s="14" t="n">
@@ -7039,10 +7039,10 @@
       <c r="U111" s="14" t="inlineStr"/>
       <c r="V111" s="14" t="inlineStr"/>
       <c r="W111" s="14" t="n">
-        <v>0.0</v>
+        <v>1.42100114E8</v>
       </c>
       <c r="X111" s="14" t="n">
-        <v>1.42100114E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y111" s="14" t="inlineStr"/>
       <c r="Z111" s="14" t="n">
@@ -7096,10 +7096,10 @@
       <c r="U112" s="14" t="inlineStr"/>
       <c r="V112" s="14" t="inlineStr"/>
       <c r="W112" s="14" t="n">
-        <v>0.0</v>
+        <v>1.42100114E8</v>
       </c>
       <c r="X112" s="14" t="n">
-        <v>1.42100114E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y112" s="14" t="inlineStr"/>
       <c r="Z112" s="14" t="n">
@@ -7159,10 +7159,10 @@
       <c r="U113" s="14" t="inlineStr"/>
       <c r="V113" s="14" t="inlineStr"/>
       <c r="W113" s="14" t="n">
-        <v>4.6945779107E10</v>
+        <v>5.0689888E10</v>
       </c>
       <c r="X113" s="14" t="n">
-        <v>3.744108893E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y113" s="14" t="inlineStr"/>
       <c r="Z113" s="14" t="n">
@@ -7222,10 +7222,10 @@
       <c r="U114" s="14" t="inlineStr"/>
       <c r="V114" s="14" t="inlineStr"/>
       <c r="W114" s="14" t="n">
-        <v>1.59331475E10</v>
+        <v>1.70891536E10</v>
       </c>
       <c r="X114" s="14" t="n">
-        <v>1.1560061E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y114" s="14" t="inlineStr"/>
       <c r="Z114" s="14" t="n">
@@ -7279,10 +7279,10 @@
       <c r="U115" s="14" t="inlineStr"/>
       <c r="V115" s="14" t="inlineStr"/>
       <c r="W115" s="14" t="n">
-        <v>1.34423941E10</v>
+        <v>1.45984002E10</v>
       </c>
       <c r="X115" s="14" t="n">
-        <v>1.1560061E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y115" s="14" t="inlineStr"/>
       <c r="Z115" s="14" t="n">
@@ -7499,10 +7499,10 @@
       <c r="U119" s="14" t="inlineStr"/>
       <c r="V119" s="14" t="inlineStr"/>
       <c r="W119" s="14" t="n">
-        <v>215018.0</v>
+        <v>230145.0</v>
       </c>
       <c r="X119" s="14" t="n">
-        <v>15127.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y119" s="14" t="inlineStr"/>
       <c r="Z119" s="14" t="n">
@@ -7556,10 +7556,10 @@
       <c r="U120" s="14" t="inlineStr"/>
       <c r="V120" s="14" t="inlineStr"/>
       <c r="W120" s="14" t="n">
-        <v>181244.0</v>
+        <v>196371.0</v>
       </c>
       <c r="X120" s="14" t="n">
-        <v>15127.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y120" s="14" t="inlineStr"/>
       <c r="Z120" s="14" t="n">
@@ -7733,10 +7733,10 @@
       <c r="U123" s="14" t="inlineStr"/>
       <c r="V123" s="14" t="inlineStr"/>
       <c r="W123" s="14" t="n">
-        <v>1.25330857E9</v>
+        <v>1.34446923E9</v>
       </c>
       <c r="X123" s="14" t="n">
-        <v>9.116066E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y123" s="14" t="inlineStr"/>
       <c r="Z123" s="14" t="n">
@@ -7790,10 +7790,10 @@
       <c r="U124" s="14" t="inlineStr"/>
       <c r="V124" s="14" t="inlineStr"/>
       <c r="W124" s="14" t="n">
-        <v>1.05832351E9</v>
+        <v>1.14948417E9</v>
       </c>
       <c r="X124" s="14" t="n">
-        <v>9.116066E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y124" s="14" t="inlineStr"/>
       <c r="Z124" s="14" t="n">
@@ -7967,10 +7967,10 @@
       <c r="U127" s="14" t="inlineStr"/>
       <c r="V127" s="14" t="inlineStr"/>
       <c r="W127" s="14" t="n">
-        <v>3.91175896E8</v>
+        <v>4.20471554E8</v>
       </c>
       <c r="X127" s="14" t="n">
-        <v>2.9295658E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y127" s="14" t="inlineStr"/>
       <c r="Z127" s="14" t="n">
@@ -8024,10 +8024,10 @@
       <c r="U128" s="14" t="inlineStr"/>
       <c r="V128" s="14" t="inlineStr"/>
       <c r="W128" s="14" t="n">
-        <v>3.3078504E8</v>
+        <v>3.60080698E8</v>
       </c>
       <c r="X128" s="14" t="n">
-        <v>2.9295658E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y128" s="14" t="inlineStr"/>
       <c r="Z128" s="14" t="n">
@@ -8201,10 +8201,10 @@
       <c r="U131" s="14" t="inlineStr"/>
       <c r="V131" s="14" t="inlineStr"/>
       <c r="W131" s="14" t="n">
-        <v>3.43577E9</v>
+        <v>3.68345E9</v>
       </c>
       <c r="X131" s="14" t="n">
-        <v>2.4768E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y131" s="14" t="inlineStr"/>
       <c r="Z131" s="14" t="n">
@@ -8258,10 +8258,10 @@
       <c r="U132" s="14" t="inlineStr"/>
       <c r="V132" s="14" t="inlineStr"/>
       <c r="W132" s="14" t="n">
-        <v>2.89751E9</v>
+        <v>3.14519E9</v>
       </c>
       <c r="X132" s="14" t="n">
-        <v>2.4768E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y132" s="14" t="inlineStr"/>
       <c r="Z132" s="14" t="n">
@@ -8435,10 +8435,10 @@
       <c r="U135" s="14" t="inlineStr"/>
       <c r="V135" s="14" t="inlineStr"/>
       <c r="W135" s="14" t="n">
-        <v>2.27374624E8</v>
+        <v>2.37273951E8</v>
       </c>
       <c r="X135" s="14" t="n">
-        <v>9899327.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y135" s="14" t="inlineStr"/>
       <c r="Z135" s="14" t="n">
@@ -8492,10 +8492,10 @@
       <c r="U136" s="14" t="inlineStr"/>
       <c r="V136" s="14" t="inlineStr"/>
       <c r="W136" s="14" t="n">
-        <v>4.1918493E7</v>
+        <v>5.181782E7</v>
       </c>
       <c r="X136" s="14" t="n">
-        <v>9899327.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y136" s="14" t="inlineStr"/>
       <c r="Z136" s="14" t="n">
@@ -8669,10 +8669,10 @@
       <c r="U139" s="14" t="inlineStr"/>
       <c r="V139" s="14" t="inlineStr"/>
       <c r="W139" s="14" t="n">
-        <v>8.7794766E8</v>
+        <v>9.4305324E8</v>
       </c>
       <c r="X139" s="14" t="n">
-        <v>6.510558E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y139" s="14" t="inlineStr"/>
       <c r="Z139" s="14" t="n">
@@ -8726,10 +8726,10 @@
       <c r="U140" s="14" t="inlineStr"/>
       <c r="V140" s="14" t="inlineStr"/>
       <c r="W140" s="14" t="n">
-        <v>7.412187E8</v>
+        <v>8.0632428E8</v>
       </c>
       <c r="X140" s="14" t="n">
-        <v>6.510558E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y140" s="14" t="inlineStr"/>
       <c r="Z140" s="14" t="n">
@@ -8903,10 +8903,10 @@
       <c r="U143" s="14" t="inlineStr"/>
       <c r="V143" s="14" t="inlineStr"/>
       <c r="W143" s="14" t="n">
-        <v>1.960479E9</v>
+        <v>2.213268E9</v>
       </c>
       <c r="X143" s="14" t="n">
-        <v>2.52789E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y143" s="14" t="inlineStr"/>
       <c r="Z143" s="14" t="n">
@@ -8960,10 +8960,10 @@
       <c r="U144" s="14" t="inlineStr"/>
       <c r="V144" s="14" t="inlineStr"/>
       <c r="W144" s="14" t="n">
-        <v>1.7493E8</v>
+        <v>1.9894E8</v>
       </c>
       <c r="X144" s="14" t="n">
-        <v>2.401E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y144" s="14" t="inlineStr"/>
       <c r="Z144" s="14" t="n">
@@ -9060,10 +9060,10 @@
       <c r="U146" s="14" t="inlineStr"/>
       <c r="V146" s="14" t="inlineStr"/>
       <c r="W146" s="14" t="n">
-        <v>1.398304E9</v>
+        <v>1.581491E9</v>
       </c>
       <c r="X146" s="14" t="n">
-        <v>1.83187E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y146" s="14" t="inlineStr"/>
       <c r="Z146" s="14" t="n">
@@ -9117,10 +9117,10 @@
       <c r="U147" s="14" t="inlineStr"/>
       <c r="V147" s="14" t="inlineStr"/>
       <c r="W147" s="14" t="n">
-        <v>3.87245E8</v>
+        <v>4.32837E8</v>
       </c>
       <c r="X147" s="14" t="n">
-        <v>4.5592E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y147" s="14" t="inlineStr"/>
       <c r="Z147" s="14" t="n">
@@ -9180,10 +9180,10 @@
       <c r="U148" s="14" t="inlineStr"/>
       <c r="V148" s="14" t="inlineStr"/>
       <c r="W148" s="14" t="n">
-        <v>2775000.0</v>
+        <v>2960000.0</v>
       </c>
       <c r="X148" s="14" t="n">
-        <v>185000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y148" s="14" t="inlineStr"/>
       <c r="Z148" s="14" t="n">
@@ -9237,10 +9237,10 @@
       <c r="U149" s="14" t="inlineStr"/>
       <c r="V149" s="14" t="inlineStr"/>
       <c r="W149" s="14" t="n">
-        <v>2220000.0</v>
+        <v>2405000.0</v>
       </c>
       <c r="X149" s="14" t="n">
-        <v>185000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y149" s="14" t="inlineStr"/>
       <c r="Z149" s="14" t="n">
@@ -9414,10 +9414,10 @@
       <c r="U152" s="14" t="inlineStr"/>
       <c r="V152" s="14" t="inlineStr"/>
       <c r="W152" s="14" t="n">
-        <v>2.2863585839E10</v>
+        <v>2.475555828E10</v>
       </c>
       <c r="X152" s="14" t="n">
-        <v>1.891972441E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y152" s="14" t="inlineStr"/>
       <c r="Z152" s="14" t="n">
@@ -9471,10 +9471,10 @@
       <c r="U153" s="14" t="inlineStr"/>
       <c r="V153" s="14" t="inlineStr"/>
       <c r="W153" s="14" t="n">
-        <v>1.8086300639E10</v>
+        <v>1.997827308E10</v>
       </c>
       <c r="X153" s="14" t="n">
-        <v>1.891972441E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y153" s="14" t="inlineStr"/>
       <c r="Z153" s="14" t="n">
@@ -9648,10 +9648,10 @@
       <c r="U156" s="14" t="inlineStr"/>
       <c r="V156" s="14" t="inlineStr"/>
       <c r="W156" s="14" t="n">
-        <v>1.8441056518E10</v>
+        <v>2.3164511208E10</v>
       </c>
       <c r="X156" s="14" t="n">
-        <v>4.72345469E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y156" s="14" t="inlineStr"/>
       <c r="Z156" s="14" t="n">
@@ -9711,10 +9711,10 @@
       <c r="U157" s="14" t="inlineStr"/>
       <c r="V157" s="14" t="inlineStr"/>
       <c r="W157" s="14" t="n">
-        <v>6.960502066E9</v>
+        <v>9.208780066E9</v>
       </c>
       <c r="X157" s="14" t="n">
-        <v>2.248278E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y157" s="14" t="inlineStr"/>
       <c r="Z157" s="14" t="n">
@@ -9768,10 +9768,10 @@
       <c r="U158" s="14" t="inlineStr"/>
       <c r="V158" s="14" t="inlineStr"/>
       <c r="W158" s="14" t="n">
-        <v>5.8713884E9</v>
+        <v>8.1196664E9</v>
       </c>
       <c r="X158" s="14" t="n">
-        <v>2.248278E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y158" s="14" t="inlineStr"/>
       <c r="Z158" s="14" t="n">
@@ -9945,10 +9945,10 @@
       <c r="U161" s="14" t="inlineStr"/>
       <c r="V161" s="14" t="inlineStr"/>
       <c r="W161" s="14" t="n">
-        <v>131546.0</v>
+        <v>193969.0</v>
       </c>
       <c r="X161" s="14" t="n">
-        <v>62423.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y161" s="14" t="inlineStr"/>
       <c r="Z161" s="14" t="n">
@@ -10002,10 +10002,10 @@
       <c r="U162" s="14" t="inlineStr"/>
       <c r="V162" s="14" t="inlineStr"/>
       <c r="W162" s="14" t="n">
-        <v>118426.0</v>
+        <v>180849.0</v>
       </c>
       <c r="X162" s="14" t="n">
-        <v>62423.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y162" s="14" t="inlineStr"/>
       <c r="Z162" s="14" t="n">
@@ -10179,10 +10179,10 @@
       <c r="U165" s="14" t="inlineStr"/>
       <c r="V165" s="14" t="inlineStr"/>
       <c r="W165" s="14" t="n">
-        <v>4.7303657E8</v>
+        <v>6.2467749E8</v>
       </c>
       <c r="X165" s="14" t="n">
-        <v>1.5164092E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y165" s="14" t="inlineStr"/>
       <c r="Z165" s="14" t="n">
@@ -10236,10 +10236,10 @@
       <c r="U166" s="14" t="inlineStr"/>
       <c r="V166" s="14" t="inlineStr"/>
       <c r="W166" s="14" t="n">
-        <v>3.993118E8</v>
+        <v>5.5095272E8</v>
       </c>
       <c r="X166" s="14" t="n">
-        <v>1.5164092E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y166" s="14" t="inlineStr"/>
       <c r="Z166" s="14" t="n">
@@ -10413,10 +10413,10 @@
       <c r="U169" s="14" t="inlineStr"/>
       <c r="V169" s="14" t="inlineStr"/>
       <c r="W169" s="14" t="n">
-        <v>1.41009928E8</v>
+        <v>1.85815464E8</v>
       </c>
       <c r="X169" s="14" t="n">
-        <v>4.4805536E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y169" s="14" t="inlineStr"/>
       <c r="Z169" s="14" t="n">
@@ -10470,10 +10470,10 @@
       <c r="U170" s="14" t="inlineStr"/>
       <c r="V170" s="14" t="inlineStr"/>
       <c r="W170" s="14" t="n">
-        <v>1.19127344E8</v>
+        <v>1.6393288E8</v>
       </c>
       <c r="X170" s="14" t="n">
-        <v>4.4805536E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y170" s="14" t="inlineStr"/>
       <c r="Z170" s="14" t="n">
@@ -10690,10 +10690,10 @@
       <c r="U174" s="14" t="inlineStr"/>
       <c r="V174" s="14" t="inlineStr"/>
       <c r="W174" s="14" t="n">
-        <v>1.13313E9</v>
+        <v>1.48485E9</v>
       </c>
       <c r="X174" s="14" t="n">
-        <v>3.5172E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y174" s="14" t="inlineStr"/>
       <c r="Z174" s="14" t="n">
@@ -10747,10 +10747,10 @@
       <c r="U175" s="14" t="inlineStr"/>
       <c r="V175" s="14" t="inlineStr"/>
       <c r="W175" s="14" t="n">
-        <v>9.5532E8</v>
+        <v>1.30704E9</v>
       </c>
       <c r="X175" s="14" t="n">
-        <v>3.5172E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y175" s="14" t="inlineStr"/>
       <c r="Z175" s="14" t="n">
@@ -10924,10 +10924,10 @@
       <c r="U178" s="14" t="inlineStr"/>
       <c r="V178" s="14" t="inlineStr"/>
       <c r="W178" s="14" t="n">
-        <v>4.2574511E8</v>
+        <v>5.5508723E8</v>
       </c>
       <c r="X178" s="14" t="n">
-        <v>1.2934212E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y178" s="14" t="inlineStr"/>
       <c r="Z178" s="14" t="n">
@@ -10981,10 +10981,10 @@
       <c r="U179" s="14" t="inlineStr"/>
       <c r="V179" s="14" t="inlineStr"/>
       <c r="W179" s="14" t="n">
-        <v>3.592032E8</v>
+        <v>4.8854532E8</v>
       </c>
       <c r="X179" s="14" t="n">
-        <v>1.2934212E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y179" s="14" t="inlineStr"/>
       <c r="Z179" s="14" t="n">
@@ -11158,10 +11158,10 @@
       <c r="U182" s="14" t="inlineStr"/>
       <c r="V182" s="14" t="inlineStr"/>
       <c r="W182" s="14" t="n">
-        <v>1.030637E9</v>
+        <v>1.310426E9</v>
       </c>
       <c r="X182" s="14" t="n">
-        <v>2.79789E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y182" s="14" t="inlineStr"/>
       <c r="Z182" s="14" t="n">
@@ -11215,10 +11215,10 @@
       <c r="U183" s="14" t="inlineStr"/>
       <c r="V183" s="14" t="inlineStr"/>
       <c r="W183" s="14" t="n">
-        <v>9.968E7</v>
+        <v>1.2502E8</v>
       </c>
       <c r="X183" s="14" t="n">
-        <v>2.534E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y183" s="14" t="inlineStr"/>
       <c r="Z183" s="14" t="n">
@@ -11272,10 +11272,10 @@
       <c r="U184" s="14" t="inlineStr"/>
       <c r="V184" s="14" t="inlineStr"/>
       <c r="W184" s="14" t="n">
-        <v>9.30957E8</v>
+        <v>1.185406E9</v>
       </c>
       <c r="X184" s="14" t="n">
-        <v>2.54449E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y184" s="14" t="inlineStr"/>
       <c r="Z184" s="14" t="n">
@@ -11335,10 +11335,10 @@
       <c r="U185" s="14" t="inlineStr"/>
       <c r="V185" s="14" t="inlineStr"/>
       <c r="W185" s="14" t="n">
-        <v>8.276864298E9</v>
+        <v>9.794680989E9</v>
       </c>
       <c r="X185" s="14" t="n">
-        <v>1.517816691E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y185" s="14" t="inlineStr"/>
       <c r="Z185" s="14" t="n">
@@ -11392,10 +11392,10 @@
       <c r="U186" s="14" t="inlineStr"/>
       <c r="V186" s="14" t="inlineStr"/>
       <c r="W186" s="14" t="n">
-        <v>6.702420922E9</v>
+        <v>8.220237613E9</v>
       </c>
       <c r="X186" s="14" t="n">
-        <v>1.517816691E9</v>
+        <v>0.0</v>
       </c>
       <c r="Y186" s="14" t="inlineStr"/>
       <c r="Z186" s="14" t="n">
@@ -11569,23 +11569,23 @@
       <c r="U189" s="25" t="inlineStr"/>
       <c r="V189" s="25" t="inlineStr"/>
       <c r="W189" s="25" t="n">
-        <v>5.917998846E9</v>
+        <v>6.228754056E9</v>
       </c>
       <c r="X189" s="25" t="n">
-        <v>2.27005316E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y189" s="25" t="inlineStr"/>
       <c r="Z189" s="25" t="n">
-        <v>6.145004162E9</v>
+        <v>6.228754056E9</v>
       </c>
       <c r="AA189" s="25" t="inlineStr"/>
       <c r="AB189" s="25" t="inlineStr"/>
       <c r="AC189" s="26" t="n">
-        <v>0.8845824596557976</v>
+        <v>0.8966383810640461</v>
       </c>
       <c r="AD189" s="26" t="inlineStr"/>
       <c r="AE189" s="25" t="n">
-        <v>8.01780838E8</v>
+        <v>7.18030944E8</v>
       </c>
       <c r="AF189" s="25" t="inlineStr"/>
       <c r="AG189" s="25" t="inlineStr"/>
@@ -11622,7 +11622,7 @@
       <c r="O190" s="13" t="inlineStr"/>
       <c r="P190" s="13" t="inlineStr"/>
       <c r="Q190" s="14" t="n">
-        <v>5.00789E9</v>
+        <v>5.000041E9</v>
       </c>
       <c r="R190" s="14" t="inlineStr"/>
       <c r="S190" s="14" t="n">
@@ -11632,23 +11632,23 @@
       <c r="U190" s="14" t="inlineStr"/>
       <c r="V190" s="14" t="inlineStr"/>
       <c r="W190" s="14" t="n">
-        <v>4.659213091E9</v>
+        <v>4.783558496E9</v>
       </c>
       <c r="X190" s="14" t="n">
-        <v>1.16004265E8</v>
+        <v>0.0</v>
       </c>
       <c r="Y190" s="14" t="inlineStr"/>
       <c r="Z190" s="14" t="n">
-        <v>4.775217356E9</v>
+        <v>4.783558496E9</v>
       </c>
       <c r="AA190" s="14" t="inlineStr"/>
       <c r="AB190" s="14" t="inlineStr"/>
       <c r="AC190" s="15" t="n">
-        <v>0.9535387869941233</v>
+        <v>0.9567038542283953</v>
       </c>
       <c r="AD190" s="15" t="inlineStr"/>
       <c r="AE190" s="14" t="n">
-        <v>2.32672644E8</v>
+        <v>2.16482504E8</v>
       </c>
       <c r="AF190" s="14" t="inlineStr"/>
       <c r="AG190" s="14" t="inlineStr"/>
@@ -11685,7 +11685,7 @@
       <c r="O191" s="13" t="inlineStr"/>
       <c r="P191" s="13" t="inlineStr"/>
       <c r="Q191" s="14" t="n">
-        <v>1.920917E9</v>
+        <v>1.890817E9</v>
       </c>
       <c r="R191" s="14" t="inlineStr"/>
       <c r="S191" s="14" t="n">
@@ -11695,23 +11695,23 @@
       <c r="U191" s="14" t="inlineStr"/>
       <c r="V191" s="14" t="inlineStr"/>
       <c r="W191" s="14" t="n">
-        <v>1.700954357E9</v>
+        <v>1.777909494E9</v>
       </c>
       <c r="X191" s="14" t="n">
-        <v>7.4808997E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y191" s="14" t="inlineStr"/>
       <c r="Z191" s="14" t="n">
-        <v>1.775763354E9</v>
+        <v>1.777909494E9</v>
       </c>
       <c r="AA191" s="14" t="inlineStr"/>
       <c r="AB191" s="14" t="inlineStr"/>
       <c r="AC191" s="15" t="n">
-        <v>0.9244352327560222</v>
+        <v>0.9402863915439728</v>
       </c>
       <c r="AD191" s="15" t="inlineStr"/>
       <c r="AE191" s="14" t="n">
-        <v>1.45153646E8</v>
+        <v>1.12907506E8</v>
       </c>
       <c r="AF191" s="14" t="inlineStr"/>
       <c r="AG191" s="14" t="inlineStr"/>
@@ -11742,7 +11742,7 @@
       <c r="O192" s="13" t="inlineStr"/>
       <c r="P192" s="13" t="inlineStr"/>
       <c r="Q192" s="14" t="n">
-        <v>6.8E8</v>
+        <v>6.385E8</v>
       </c>
       <c r="R192" s="14" t="inlineStr"/>
       <c r="S192" s="14" t="n">
@@ -11764,11 +11764,11 @@
       <c r="AA192" s="14" t="inlineStr"/>
       <c r="AB192" s="14" t="inlineStr"/>
       <c r="AC192" s="15" t="n">
-        <v>0.9389705882352941</v>
+        <v>1.0</v>
       </c>
       <c r="AD192" s="15" t="inlineStr"/>
       <c r="AE192" s="14" t="n">
-        <v>4.15E7</v>
+        <v>0.0</v>
       </c>
       <c r="AF192" s="14" t="inlineStr"/>
       <c r="AG192" s="14" t="inlineStr"/>
@@ -11856,7 +11856,7 @@
       <c r="O194" s="13" t="inlineStr"/>
       <c r="P194" s="13" t="inlineStr"/>
       <c r="Q194" s="14" t="n">
-        <v>6.3714E7</v>
+        <v>9.393E7</v>
       </c>
       <c r="R194" s="14" t="inlineStr"/>
       <c r="S194" s="14" t="n">
@@ -11866,23 +11866,23 @@
       <c r="U194" s="14" t="inlineStr"/>
       <c r="V194" s="14" t="inlineStr"/>
       <c r="W194" s="14" t="n">
-        <v>5.0329917E7</v>
+        <v>5.5184254E7</v>
       </c>
       <c r="X194" s="14" t="n">
-        <v>2708197.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y194" s="14" t="inlineStr"/>
       <c r="Z194" s="14" t="n">
-        <v>5.3038114E7</v>
+        <v>5.5184254E7</v>
       </c>
       <c r="AA194" s="14" t="inlineStr"/>
       <c r="AB194" s="14" t="inlineStr"/>
       <c r="AC194" s="15" t="n">
-        <v>0.8324404997331827</v>
+        <v>0.587504034919621</v>
       </c>
       <c r="AD194" s="15" t="inlineStr"/>
       <c r="AE194" s="14" t="n">
-        <v>1.0675886E7</v>
+        <v>3.8745746E7</v>
       </c>
       <c r="AF194" s="14" t="inlineStr"/>
       <c r="AG194" s="14" t="inlineStr"/>
@@ -12084,7 +12084,7 @@
       <c r="O198" s="13" t="inlineStr"/>
       <c r="P198" s="13" t="inlineStr"/>
       <c r="Q198" s="14" t="n">
-        <v>8936000.0</v>
+        <v>5420000.0</v>
       </c>
       <c r="R198" s="14" t="inlineStr"/>
       <c r="S198" s="14" t="n">
@@ -12106,11 +12106,11 @@
       <c r="AA198" s="14" t="inlineStr"/>
       <c r="AB198" s="14" t="inlineStr"/>
       <c r="AC198" s="15" t="n">
-        <v>0.6064726947179946</v>
+        <v>0.9998966789667897</v>
       </c>
       <c r="AD198" s="15" t="inlineStr"/>
       <c r="AE198" s="14" t="n">
-        <v>3516560.0</v>
+        <v>560.0</v>
       </c>
       <c r="AF198" s="14" t="inlineStr"/>
       <c r="AG198" s="14" t="inlineStr"/>
@@ -12141,7 +12141,7 @@
       <c r="O199" s="13" t="inlineStr"/>
       <c r="P199" s="13" t="inlineStr"/>
       <c r="Q199" s="14" t="n">
-        <v>7.83E7</v>
+        <v>9.945E7</v>
       </c>
       <c r="R199" s="14" t="inlineStr"/>
       <c r="S199" s="14" t="n">
@@ -12151,10 +12151,10 @@
       <c r="U199" s="14" t="inlineStr"/>
       <c r="V199" s="14" t="inlineStr"/>
       <c r="W199" s="14" t="n">
-        <v>0.0</v>
+        <v>4.87008E7</v>
       </c>
       <c r="X199" s="14" t="n">
-        <v>4.87008E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y199" s="14" t="inlineStr"/>
       <c r="Z199" s="14" t="n">
@@ -12163,11 +12163,11 @@
       <c r="AA199" s="14" t="inlineStr"/>
       <c r="AB199" s="14" t="inlineStr"/>
       <c r="AC199" s="15" t="n">
-        <v>0.6219770114942529</v>
+        <v>0.48970135746606336</v>
       </c>
       <c r="AD199" s="15" t="inlineStr"/>
       <c r="AE199" s="14" t="n">
-        <v>2.95992E7</v>
+        <v>5.07492E7</v>
       </c>
       <c r="AF199" s="14" t="inlineStr"/>
       <c r="AG199" s="14" t="inlineStr"/>
@@ -12234,14 +12234,14 @@
       <c r="N201" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000295. BPJS Ketenagakerjaan</t>
+            <t xml:space="preserve">000301. Gaji PPPK Paruh Waktu (PPB)</t>
           </r>
         </is>
       </c>
       <c r="O201" s="13" t="inlineStr"/>
       <c r="P201" s="13" t="inlineStr"/>
       <c r="Q201" s="14" t="n">
-        <v>5250000.0</v>
+        <v>4.68E7</v>
       </c>
       <c r="R201" s="14" t="inlineStr"/>
       <c r="S201" s="14" t="n">
@@ -12251,23 +12251,23 @@
       <c r="U201" s="14" t="inlineStr"/>
       <c r="V201" s="14" t="inlineStr"/>
       <c r="W201" s="14" t="n">
-        <v>0.0</v>
+        <v>2.34E7</v>
       </c>
       <c r="X201" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y201" s="14" t="inlineStr"/>
       <c r="Z201" s="14" t="n">
-        <v>0.0</v>
+        <v>2.34E7</v>
       </c>
       <c r="AA201" s="14" t="inlineStr"/>
       <c r="AB201" s="14" t="inlineStr"/>
       <c r="AC201" s="15" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="AD201" s="15" t="inlineStr"/>
       <c r="AE201" s="14" t="n">
-        <v>5250000.0</v>
+        <v>2.34E7</v>
       </c>
       <c r="AF201" s="14" t="inlineStr"/>
       <c r="AG201" s="14" t="inlineStr"/>
@@ -12282,23 +12282,29 @@
       <c r="E202" s="2" t="inlineStr"/>
       <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr"/>
-      <c r="I202" s="2" t="inlineStr"/>
-      <c r="J202" s="2" t="inlineStr"/>
-      <c r="K202" s="2" t="inlineStr"/>
-      <c r="L202" s="2" t="inlineStr"/>
-      <c r="M202" s="2" t="inlineStr"/>
-      <c r="N202" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000301. Gaji PPPK Paruh Waktu (PPB)</t>
-          </r>
-        </is>
-      </c>
+      <c r="H202" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521119</t>
+          </r>
+        </is>
+      </c>
+      <c r="I202" s="13" t="inlineStr"/>
+      <c r="J202" s="13" t="inlineStr"/>
+      <c r="K202" s="13" t="inlineStr"/>
+      <c r="L202" s="13" t="inlineStr"/>
+      <c r="M202" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N202" s="13" t="inlineStr"/>
       <c r="O202" s="13" t="inlineStr"/>
       <c r="P202" s="13" t="inlineStr"/>
       <c r="Q202" s="14" t="n">
-        <v>7.8E7</v>
+        <v>1.23E7</v>
       </c>
       <c r="R202" s="14" t="inlineStr"/>
       <c r="S202" s="14" t="n">
@@ -12308,23 +12314,23 @@
       <c r="U202" s="14" t="inlineStr"/>
       <c r="V202" s="14" t="inlineStr"/>
       <c r="W202" s="14" t="n">
-        <v>0.0</v>
+        <v>9417000.0</v>
       </c>
       <c r="X202" s="14" t="n">
-        <v>2.34E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y202" s="14" t="inlineStr"/>
       <c r="Z202" s="14" t="n">
-        <v>2.34E7</v>
+        <v>9417000.0</v>
       </c>
       <c r="AA202" s="14" t="inlineStr"/>
       <c r="AB202" s="14" t="inlineStr"/>
       <c r="AC202" s="15" t="n">
-        <v>0.3</v>
+        <v>0.765609756097561</v>
       </c>
       <c r="AD202" s="15" t="inlineStr"/>
       <c r="AE202" s="14" t="n">
-        <v>5.46E7</v>
+        <v>2883000.0</v>
       </c>
       <c r="AF202" s="14" t="inlineStr"/>
       <c r="AG202" s="14" t="inlineStr"/>
@@ -12339,29 +12345,23 @@
       <c r="E203" s="2" t="inlineStr"/>
       <c r="F203" s="2" t="inlineStr"/>
       <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521119</t>
-          </r>
-        </is>
-      </c>
-      <c r="I203" s="13" t="inlineStr"/>
-      <c r="J203" s="13" t="inlineStr"/>
-      <c r="K203" s="13" t="inlineStr"/>
-      <c r="L203" s="13" t="inlineStr"/>
-      <c r="M203" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N203" s="13" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr"/>
+      <c r="I203" s="2" t="inlineStr"/>
+      <c r="J203" s="2" t="inlineStr"/>
+      <c r="K203" s="2" t="inlineStr"/>
+      <c r="L203" s="2" t="inlineStr"/>
+      <c r="M203" s="2" t="inlineStr"/>
+      <c r="N203" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000133. Biaya Tol</t>
+          </r>
+        </is>
+      </c>
       <c r="O203" s="13" t="inlineStr"/>
       <c r="P203" s="13" t="inlineStr"/>
       <c r="Q203" s="14" t="n">
-        <v>1.0E7</v>
+        <v>7800000.0</v>
       </c>
       <c r="R203" s="14" t="inlineStr"/>
       <c r="S203" s="14" t="n">
@@ -12371,23 +12371,23 @@
       <c r="U203" s="14" t="inlineStr"/>
       <c r="V203" s="14" t="inlineStr"/>
       <c r="W203" s="14" t="n">
-        <v>9013000.0</v>
+        <v>5781000.0</v>
       </c>
       <c r="X203" s="14" t="n">
-        <v>404000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y203" s="14" t="inlineStr"/>
       <c r="Z203" s="14" t="n">
-        <v>9417000.0</v>
+        <v>5781000.0</v>
       </c>
       <c r="AA203" s="14" t="inlineStr"/>
       <c r="AB203" s="14" t="inlineStr"/>
       <c r="AC203" s="15" t="n">
-        <v>0.9417</v>
+        <v>0.7411538461538462</v>
       </c>
       <c r="AD203" s="15" t="inlineStr"/>
       <c r="AE203" s="14" t="n">
-        <v>583000.0</v>
+        <v>2019000.0</v>
       </c>
       <c r="AF203" s="14" t="inlineStr"/>
       <c r="AG203" s="14" t="inlineStr"/>
@@ -12411,14 +12411,14 @@
       <c r="N204" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000133. Biaya Tol</t>
+            <t xml:space="preserve">000134. Biaya Angkut Sampah</t>
           </r>
         </is>
       </c>
       <c r="O204" s="13" t="inlineStr"/>
       <c r="P204" s="13" t="inlineStr"/>
       <c r="Q204" s="14" t="n">
-        <v>5800000.0</v>
+        <v>4500000.0</v>
       </c>
       <c r="R204" s="14" t="inlineStr"/>
       <c r="S204" s="14" t="n">
@@ -12428,23 +12428,23 @@
       <c r="U204" s="14" t="inlineStr"/>
       <c r="V204" s="14" t="inlineStr"/>
       <c r="W204" s="14" t="n">
-        <v>5781000.0</v>
+        <v>3636000.0</v>
       </c>
       <c r="X204" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y204" s="14" t="inlineStr"/>
       <c r="Z204" s="14" t="n">
-        <v>5781000.0</v>
+        <v>3636000.0</v>
       </c>
       <c r="AA204" s="14" t="inlineStr"/>
       <c r="AB204" s="14" t="inlineStr"/>
       <c r="AC204" s="15" t="n">
-        <v>0.9967241379310345</v>
+        <v>0.808</v>
       </c>
       <c r="AD204" s="15" t="inlineStr"/>
       <c r="AE204" s="14" t="n">
-        <v>19000.0</v>
+        <v>864000.0</v>
       </c>
       <c r="AF204" s="14" t="inlineStr"/>
       <c r="AG204" s="14" t="inlineStr"/>
@@ -12459,23 +12459,29 @@
       <c r="E205" s="2" t="inlineStr"/>
       <c r="F205" s="2" t="inlineStr"/>
       <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr"/>
-      <c r="I205" s="2" t="inlineStr"/>
-      <c r="J205" s="2" t="inlineStr"/>
-      <c r="K205" s="2" t="inlineStr"/>
-      <c r="L205" s="2" t="inlineStr"/>
-      <c r="M205" s="2" t="inlineStr"/>
-      <c r="N205" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000134. Biaya Angkut Sampah</t>
-          </r>
-        </is>
-      </c>
+      <c r="H205" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521211</t>
+          </r>
+        </is>
+      </c>
+      <c r="I205" s="13" t="inlineStr"/>
+      <c r="J205" s="13" t="inlineStr"/>
+      <c r="K205" s="13" t="inlineStr"/>
+      <c r="L205" s="13" t="inlineStr"/>
+      <c r="M205" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Bahan</t>
+          </r>
+        </is>
+      </c>
+      <c r="N205" s="13" t="inlineStr"/>
       <c r="O205" s="13" t="inlineStr"/>
       <c r="P205" s="13" t="inlineStr"/>
       <c r="Q205" s="14" t="n">
-        <v>4200000.0</v>
+        <v>7.4556E7</v>
       </c>
       <c r="R205" s="14" t="inlineStr"/>
       <c r="S205" s="14" t="n">
@@ -12485,23 +12491,23 @@
       <c r="U205" s="14" t="inlineStr"/>
       <c r="V205" s="14" t="inlineStr"/>
       <c r="W205" s="14" t="n">
-        <v>3232000.0</v>
+        <v>5.526601E7</v>
       </c>
       <c r="X205" s="14" t="n">
-        <v>404000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y205" s="14" t="inlineStr"/>
       <c r="Z205" s="14" t="n">
-        <v>3636000.0</v>
+        <v>5.526601E7</v>
       </c>
       <c r="AA205" s="14" t="inlineStr"/>
       <c r="AB205" s="14" t="inlineStr"/>
       <c r="AC205" s="15" t="n">
-        <v>0.8657142857142858</v>
+        <v>0.7412684425130104</v>
       </c>
       <c r="AD205" s="15" t="inlineStr"/>
       <c r="AE205" s="14" t="n">
-        <v>564000.0</v>
+        <v>1.928999E7</v>
       </c>
       <c r="AF205" s="14" t="inlineStr"/>
       <c r="AG205" s="14" t="inlineStr"/>
@@ -12516,29 +12522,23 @@
       <c r="E206" s="2" t="inlineStr"/>
       <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521211</t>
-          </r>
-        </is>
-      </c>
-      <c r="I206" s="13" t="inlineStr"/>
-      <c r="J206" s="13" t="inlineStr"/>
-      <c r="K206" s="13" t="inlineStr"/>
-      <c r="L206" s="13" t="inlineStr"/>
-      <c r="M206" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Bahan</t>
-          </r>
-        </is>
-      </c>
-      <c r="N206" s="13" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr"/>
+      <c r="I206" s="2" t="inlineStr"/>
+      <c r="J206" s="2" t="inlineStr"/>
+      <c r="K206" s="2" t="inlineStr"/>
+      <c r="L206" s="2" t="inlineStr"/>
+      <c r="M206" s="2" t="inlineStr"/>
+      <c r="N206" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000135. Jamuan Tamu/Delegasi</t>
+          </r>
+        </is>
+      </c>
       <c r="O206" s="13" t="inlineStr"/>
       <c r="P206" s="13" t="inlineStr"/>
       <c r="Q206" s="14" t="n">
-        <v>5.9605E7</v>
+        <v>7.4556E7</v>
       </c>
       <c r="R206" s="14" t="inlineStr"/>
       <c r="S206" s="14" t="n">
@@ -12548,23 +12548,23 @@
       <c r="U206" s="14" t="inlineStr"/>
       <c r="V206" s="14" t="inlineStr"/>
       <c r="W206" s="14" t="n">
-        <v>4.634851E7</v>
+        <v>5.526601E7</v>
       </c>
       <c r="X206" s="14" t="n">
-        <v>2722500.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y206" s="14" t="inlineStr"/>
       <c r="Z206" s="14" t="n">
-        <v>4.907101E7</v>
+        <v>5.526601E7</v>
       </c>
       <c r="AA206" s="14" t="inlineStr"/>
       <c r="AB206" s="14" t="inlineStr"/>
       <c r="AC206" s="15" t="n">
-        <v>0.8232700276822414</v>
+        <v>0.7412684425130104</v>
       </c>
       <c r="AD206" s="15" t="inlineStr"/>
       <c r="AE206" s="14" t="n">
-        <v>1.053399E7</v>
+        <v>1.928999E7</v>
       </c>
       <c r="AF206" s="14" t="inlineStr"/>
       <c r="AG206" s="14" t="inlineStr"/>
@@ -12579,23 +12579,29 @@
       <c r="E207" s="2" t="inlineStr"/>
       <c r="F207" s="2" t="inlineStr"/>
       <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="2" t="inlineStr"/>
-      <c r="I207" s="2" t="inlineStr"/>
-      <c r="J207" s="2" t="inlineStr"/>
-      <c r="K207" s="2" t="inlineStr"/>
-      <c r="L207" s="2" t="inlineStr"/>
-      <c r="M207" s="2" t="inlineStr"/>
-      <c r="N207" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000135. Jamuan Tamu/Delegasi</t>
-          </r>
-        </is>
-      </c>
+      <c r="H207" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521811</t>
+          </r>
+        </is>
+      </c>
+      <c r="I207" s="13" t="inlineStr"/>
+      <c r="J207" s="13" t="inlineStr"/>
+      <c r="K207" s="13" t="inlineStr"/>
+      <c r="L207" s="13" t="inlineStr"/>
+      <c r="M207" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
+          </r>
+        </is>
+      </c>
+      <c r="N207" s="13" t="inlineStr"/>
       <c r="O207" s="13" t="inlineStr"/>
       <c r="P207" s="13" t="inlineStr"/>
       <c r="Q207" s="14" t="n">
-        <v>5.9605E7</v>
+        <v>1.1E7</v>
       </c>
       <c r="R207" s="14" t="inlineStr"/>
       <c r="S207" s="14" t="n">
@@ -12605,23 +12611,23 @@
       <c r="U207" s="14" t="inlineStr"/>
       <c r="V207" s="14" t="inlineStr"/>
       <c r="W207" s="14" t="n">
-        <v>4.634851E7</v>
+        <v>4274800.0</v>
       </c>
       <c r="X207" s="14" t="n">
-        <v>2722500.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y207" s="14" t="inlineStr"/>
       <c r="Z207" s="14" t="n">
-        <v>4.907101E7</v>
+        <v>4274800.0</v>
       </c>
       <c r="AA207" s="14" t="inlineStr"/>
       <c r="AB207" s="14" t="inlineStr"/>
       <c r="AC207" s="15" t="n">
-        <v>0.8232700276822414</v>
+        <v>0.3886181818181818</v>
       </c>
       <c r="AD207" s="15" t="inlineStr"/>
       <c r="AE207" s="14" t="n">
-        <v>1.053399E7</v>
+        <v>6725200.0</v>
       </c>
       <c r="AF207" s="14" t="inlineStr"/>
       <c r="AG207" s="14" t="inlineStr"/>
@@ -12636,29 +12642,23 @@
       <c r="E208" s="2" t="inlineStr"/>
       <c r="F208" s="2" t="inlineStr"/>
       <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521811</t>
-          </r>
-        </is>
-      </c>
-      <c r="I208" s="13" t="inlineStr"/>
-      <c r="J208" s="13" t="inlineStr"/>
-      <c r="K208" s="13" t="inlineStr"/>
-      <c r="L208" s="13" t="inlineStr"/>
-      <c r="M208" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
-          </r>
-        </is>
-      </c>
-      <c r="N208" s="13" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr"/>
+      <c r="I208" s="2" t="inlineStr"/>
+      <c r="J208" s="2" t="inlineStr"/>
+      <c r="K208" s="2" t="inlineStr"/>
+      <c r="L208" s="2" t="inlineStr"/>
+      <c r="M208" s="2" t="inlineStr"/>
+      <c r="N208" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000137. Bahan Komputer</t>
+          </r>
+        </is>
+      </c>
       <c r="O208" s="13" t="inlineStr"/>
       <c r="P208" s="13" t="inlineStr"/>
       <c r="Q208" s="14" t="n">
-        <v>6000000.0</v>
+        <v>9000000.0</v>
       </c>
       <c r="R208" s="14" t="inlineStr"/>
       <c r="S208" s="14" t="n">
@@ -12668,23 +12668,23 @@
       <c r="U208" s="14" t="inlineStr"/>
       <c r="V208" s="14" t="inlineStr"/>
       <c r="W208" s="14" t="n">
-        <v>3257800.0</v>
+        <v>3964800.0</v>
       </c>
       <c r="X208" s="14" t="n">
-        <v>1017000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y208" s="14" t="inlineStr"/>
       <c r="Z208" s="14" t="n">
-        <v>4274800.0</v>
+        <v>3964800.0</v>
       </c>
       <c r="AA208" s="14" t="inlineStr"/>
       <c r="AB208" s="14" t="inlineStr"/>
       <c r="AC208" s="15" t="n">
-        <v>0.7124666666666667</v>
+        <v>0.44053333333333333</v>
       </c>
       <c r="AD208" s="15" t="inlineStr"/>
       <c r="AE208" s="14" t="n">
-        <v>1725200.0</v>
+        <v>5035200.0</v>
       </c>
       <c r="AF208" s="14" t="inlineStr"/>
       <c r="AG208" s="14" t="inlineStr"/>
@@ -12708,14 +12708,14 @@
       <c r="N209" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000137. Bahan Komputer</t>
+            <t xml:space="preserve">000292. ATK</t>
           </r>
         </is>
       </c>
       <c r="O209" s="13" t="inlineStr"/>
       <c r="P209" s="13" t="inlineStr"/>
       <c r="Q209" s="14" t="n">
-        <v>4000000.0</v>
+        <v>2000000.0</v>
       </c>
       <c r="R209" s="14" t="inlineStr"/>
       <c r="S209" s="14" t="n">
@@ -12725,23 +12725,23 @@
       <c r="U209" s="14" t="inlineStr"/>
       <c r="V209" s="14" t="inlineStr"/>
       <c r="W209" s="14" t="n">
-        <v>2947800.0</v>
+        <v>310000.0</v>
       </c>
       <c r="X209" s="14" t="n">
-        <v>1017000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y209" s="14" t="inlineStr"/>
       <c r="Z209" s="14" t="n">
-        <v>3964800.0</v>
+        <v>310000.0</v>
       </c>
       <c r="AA209" s="14" t="inlineStr"/>
       <c r="AB209" s="14" t="inlineStr"/>
       <c r="AC209" s="15" t="n">
-        <v>0.9912</v>
+        <v>0.155</v>
       </c>
       <c r="AD209" s="15" t="inlineStr"/>
       <c r="AE209" s="14" t="n">
-        <v>35200.0</v>
+        <v>1690000.0</v>
       </c>
       <c r="AF209" s="14" t="inlineStr"/>
       <c r="AG209" s="14" t="inlineStr"/>
@@ -12756,23 +12756,29 @@
       <c r="E210" s="2" t="inlineStr"/>
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr"/>
-      <c r="I210" s="2" t="inlineStr"/>
-      <c r="J210" s="2" t="inlineStr"/>
-      <c r="K210" s="2" t="inlineStr"/>
-      <c r="L210" s="2" t="inlineStr"/>
-      <c r="M210" s="2" t="inlineStr"/>
-      <c r="N210" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000292. ATK</t>
-          </r>
-        </is>
-      </c>
+      <c r="H210" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522191</t>
+          </r>
+        </is>
+      </c>
+      <c r="I210" s="13" t="inlineStr"/>
+      <c r="J210" s="13" t="inlineStr"/>
+      <c r="K210" s="13" t="inlineStr"/>
+      <c r="L210" s="13" t="inlineStr"/>
+      <c r="M210" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Jasa Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N210" s="13" t="inlineStr"/>
       <c r="O210" s="13" t="inlineStr"/>
       <c r="P210" s="13" t="inlineStr"/>
       <c r="Q210" s="14" t="n">
-        <v>2000000.0</v>
+        <v>3.011368E9</v>
       </c>
       <c r="R210" s="14" t="inlineStr"/>
       <c r="S210" s="14" t="n">
@@ -12782,30 +12788,30 @@
       <c r="U210" s="14" t="inlineStr"/>
       <c r="V210" s="14" t="inlineStr"/>
       <c r="W210" s="14" t="n">
-        <v>310000.0</v>
+        <v>2.936691192E9</v>
       </c>
       <c r="X210" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y210" s="14" t="inlineStr"/>
       <c r="Z210" s="14" t="n">
-        <v>310000.0</v>
+        <v>2.936691192E9</v>
       </c>
       <c r="AA210" s="14" t="inlineStr"/>
       <c r="AB210" s="14" t="inlineStr"/>
       <c r="AC210" s="15" t="n">
-        <v>0.155</v>
+        <v>0.9752016996926314</v>
       </c>
       <c r="AD210" s="15" t="inlineStr"/>
       <c r="AE210" s="14" t="n">
-        <v>1690000.0</v>
+        <v>7.4676808E7</v>
       </c>
       <c r="AF210" s="14" t="inlineStr"/>
       <c r="AG210" s="14" t="inlineStr"/>
       <c r="AH210" s="14" t="inlineStr"/>
       <c r="AI210" s="14" t="inlineStr"/>
     </row>
-    <row r="211" customHeight="1" ht="15">
+    <row r="211" customHeight="1" ht="18">
       <c r="A211" s="2" t="inlineStr"/>
       <c r="B211" s="2" t="inlineStr"/>
       <c r="C211" s="2" t="inlineStr"/>
@@ -12813,29 +12819,23 @@
       <c r="E211" s="2" t="inlineStr"/>
       <c r="F211" s="2" t="inlineStr"/>
       <c r="G211" s="2" t="inlineStr"/>
-      <c r="H211" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522191</t>
-          </r>
-        </is>
-      </c>
-      <c r="I211" s="13" t="inlineStr"/>
-      <c r="J211" s="13" t="inlineStr"/>
-      <c r="K211" s="13" t="inlineStr"/>
-      <c r="L211" s="13" t="inlineStr"/>
-      <c r="M211" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Jasa Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N211" s="13" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr"/>
+      <c r="I211" s="2" t="inlineStr"/>
+      <c r="J211" s="2" t="inlineStr"/>
+      <c r="K211" s="2" t="inlineStr"/>
+      <c r="L211" s="2" t="inlineStr"/>
+      <c r="M211" s="2" t="inlineStr"/>
+      <c r="N211" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000139. Biaya Outsourcing Perorangan Tenaga Kebersihan (Januari s.d September) (9 ORG)</t>
+          </r>
+        </is>
+      </c>
       <c r="O211" s="13" t="inlineStr"/>
       <c r="P211" s="13" t="inlineStr"/>
       <c r="Q211" s="14" t="n">
-        <v>3.011368E9</v>
+        <v>4.0995E8</v>
       </c>
       <c r="R211" s="14" t="inlineStr"/>
       <c r="S211" s="14" t="n">
@@ -12845,30 +12845,30 @@
       <c r="U211" s="14" t="inlineStr"/>
       <c r="V211" s="14" t="inlineStr"/>
       <c r="W211" s="14" t="n">
-        <v>2.899639424E9</v>
+        <v>4.09846464E8</v>
       </c>
       <c r="X211" s="14" t="n">
-        <v>3.7051768E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y211" s="14" t="inlineStr"/>
       <c r="Z211" s="14" t="n">
-        <v>2.936691192E9</v>
+        <v>4.09846464E8</v>
       </c>
       <c r="AA211" s="14" t="inlineStr"/>
       <c r="AB211" s="14" t="inlineStr"/>
       <c r="AC211" s="15" t="n">
-        <v>0.9752016996926314</v>
+        <v>0.9997474423710209</v>
       </c>
       <c r="AD211" s="15" t="inlineStr"/>
       <c r="AE211" s="14" t="n">
-        <v>7.4676808E7</v>
+        <v>103536.0</v>
       </c>
       <c r="AF211" s="14" t="inlineStr"/>
       <c r="AG211" s="14" t="inlineStr"/>
       <c r="AH211" s="14" t="inlineStr"/>
       <c r="AI211" s="14" t="inlineStr"/>
     </row>
-    <row r="212" customHeight="1" ht="18">
+    <row r="212" customHeight="1" ht="15">
       <c r="A212" s="2" t="inlineStr"/>
       <c r="B212" s="2" t="inlineStr"/>
       <c r="C212" s="2" t="inlineStr"/>
@@ -12885,14 +12885,14 @@
       <c r="N212" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000139. Biaya Outsourcing Perorangan Tenaga Kebersihan (Januari s.d September) (9 ORG)</t>
+            <t xml:space="preserve">000140. Biaya Outsourcing Perorangan Pengemudi (2 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O212" s="13" t="inlineStr"/>
       <c r="P212" s="13" t="inlineStr"/>
       <c r="Q212" s="14" t="n">
-        <v>4.0995E8</v>
+        <v>1.226E8</v>
       </c>
       <c r="R212" s="14" t="inlineStr"/>
       <c r="S212" s="14" t="n">
@@ -12902,30 +12902,30 @@
       <c r="U212" s="14" t="inlineStr"/>
       <c r="V212" s="14" t="inlineStr"/>
       <c r="W212" s="14" t="n">
-        <v>4.09846464E8</v>
+        <v>1.0331888E8</v>
       </c>
       <c r="X212" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y212" s="14" t="inlineStr"/>
       <c r="Z212" s="14" t="n">
-        <v>4.09846464E8</v>
+        <v>1.0331888E8</v>
       </c>
       <c r="AA212" s="14" t="inlineStr"/>
       <c r="AB212" s="14" t="inlineStr"/>
       <c r="AC212" s="15" t="n">
-        <v>0.9997474423710209</v>
+        <v>0.842731484502447</v>
       </c>
       <c r="AD212" s="15" t="inlineStr"/>
       <c r="AE212" s="14" t="n">
-        <v>103536.0</v>
+        <v>1.928112E7</v>
       </c>
       <c r="AF212" s="14" t="inlineStr"/>
       <c r="AG212" s="14" t="inlineStr"/>
       <c r="AH212" s="14" t="inlineStr"/>
       <c r="AI212" s="14" t="inlineStr"/>
     </row>
-    <row r="213" customHeight="1" ht="15">
+    <row r="213" customHeight="1" ht="18">
       <c r="A213" s="2" t="inlineStr"/>
       <c r="B213" s="2" t="inlineStr"/>
       <c r="C213" s="2" t="inlineStr"/>
@@ -12942,14 +12942,14 @@
       <c r="N213" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000140. Biaya Outsourcing Perorangan Pengemudi (2 ORG)</t>
+            <t xml:space="preserve">000141. Biaya Outsourcing Perorangan Petugas Kolam (Januari s.d September) (3 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O213" s="13" t="inlineStr"/>
       <c r="P213" s="13" t="inlineStr"/>
       <c r="Q213" s="14" t="n">
-        <v>1.226E8</v>
+        <v>1.3629E8</v>
       </c>
       <c r="R213" s="14" t="inlineStr"/>
       <c r="S213" s="14" t="n">
@@ -12959,23 +12959,23 @@
       <c r="U213" s="14" t="inlineStr"/>
       <c r="V213" s="14" t="inlineStr"/>
       <c r="W213" s="14" t="n">
-        <v>9.3850352E7</v>
+        <v>1.36218456E8</v>
       </c>
       <c r="X213" s="14" t="n">
-        <v>9468528.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y213" s="14" t="inlineStr"/>
       <c r="Z213" s="14" t="n">
-        <v>1.0331888E8</v>
+        <v>1.36218456E8</v>
       </c>
       <c r="AA213" s="14" t="inlineStr"/>
       <c r="AB213" s="14" t="inlineStr"/>
       <c r="AC213" s="15" t="n">
-        <v>0.842731484502447</v>
+        <v>0.9994750605326876</v>
       </c>
       <c r="AD213" s="15" t="inlineStr"/>
       <c r="AE213" s="14" t="n">
-        <v>1.928112E7</v>
+        <v>71544.0</v>
       </c>
       <c r="AF213" s="14" t="inlineStr"/>
       <c r="AG213" s="14" t="inlineStr"/>
@@ -12999,14 +12999,14 @@
       <c r="N214" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000141. Biaya Outsourcing Perorangan Petugas Kolam (Januari s.d September) (3 ORG)</t>
+            <t xml:space="preserve">000142. Biaya Outsourcing Perorangan Petugas Layanan Informasi (1 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O214" s="13" t="inlineStr"/>
       <c r="P214" s="13" t="inlineStr"/>
       <c r="Q214" s="14" t="n">
-        <v>1.3629E8</v>
+        <v>4.59E7</v>
       </c>
       <c r="R214" s="14" t="inlineStr"/>
       <c r="S214" s="14" t="n">
@@ -13016,30 +13016,30 @@
       <c r="U214" s="14" t="inlineStr"/>
       <c r="V214" s="14" t="inlineStr"/>
       <c r="W214" s="14" t="n">
-        <v>1.36218456E8</v>
+        <v>4.5886152E7</v>
       </c>
       <c r="X214" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y214" s="14" t="inlineStr"/>
       <c r="Z214" s="14" t="n">
-        <v>1.36218456E8</v>
+        <v>4.5886152E7</v>
       </c>
       <c r="AA214" s="14" t="inlineStr"/>
       <c r="AB214" s="14" t="inlineStr"/>
       <c r="AC214" s="15" t="n">
-        <v>0.9994750605326876</v>
+        <v>0.9996983006535948</v>
       </c>
       <c r="AD214" s="15" t="inlineStr"/>
       <c r="AE214" s="14" t="n">
-        <v>71544.0</v>
+        <v>13848.0</v>
       </c>
       <c r="AF214" s="14" t="inlineStr"/>
       <c r="AG214" s="14" t="inlineStr"/>
       <c r="AH214" s="14" t="inlineStr"/>
       <c r="AI214" s="14" t="inlineStr"/>
     </row>
-    <row r="215" customHeight="1" ht="18">
+    <row r="215" customHeight="1" ht="15">
       <c r="A215" s="2" t="inlineStr"/>
       <c r="B215" s="2" t="inlineStr"/>
       <c r="C215" s="2" t="inlineStr"/>
@@ -13056,14 +13056,14 @@
       <c r="N215" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000142. Biaya Outsourcing Perorangan Petugas Layanan Informasi (1 ORG)</t>
+            <t xml:space="preserve">000144. Biaya Outsourcing Satpam (24 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O215" s="13" t="inlineStr"/>
       <c r="P215" s="13" t="inlineStr"/>
       <c r="Q215" s="14" t="n">
-        <v>4.59E7</v>
+        <v>2.213838E9</v>
       </c>
       <c r="R215" s="14" t="inlineStr"/>
       <c r="S215" s="14" t="n">
@@ -13073,30 +13073,30 @@
       <c r="U215" s="14" t="inlineStr"/>
       <c r="V215" s="14" t="inlineStr"/>
       <c r="W215" s="14" t="n">
-        <v>4.5886152E7</v>
+        <v>2.213838E9</v>
       </c>
       <c r="X215" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y215" s="14" t="inlineStr"/>
       <c r="Z215" s="14" t="n">
-        <v>4.5886152E7</v>
+        <v>2.213838E9</v>
       </c>
       <c r="AA215" s="14" t="inlineStr"/>
       <c r="AB215" s="14" t="inlineStr"/>
       <c r="AC215" s="15" t="n">
-        <v>0.9996983006535948</v>
+        <v>1.0</v>
       </c>
       <c r="AD215" s="15" t="inlineStr"/>
       <c r="AE215" s="14" t="n">
-        <v>13848.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF215" s="14" t="inlineStr"/>
       <c r="AG215" s="14" t="inlineStr"/>
       <c r="AH215" s="14" t="inlineStr"/>
       <c r="AI215" s="14" t="inlineStr"/>
     </row>
-    <row r="216" customHeight="1" ht="15">
+    <row r="216" customHeight="1" ht="18">
       <c r="A216" s="2" t="inlineStr"/>
       <c r="B216" s="2" t="inlineStr"/>
       <c r="C216" s="2" t="inlineStr"/>
@@ -13113,14 +13113,14 @@
       <c r="N216" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000144. Biaya Outsourcing Satpam (24 ORG)</t>
+            <t xml:space="preserve">000296. Biaya Outsourcing Perorangan Tenaga Kebersihan (Oktober s.d Desember) (5 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O216" s="13" t="inlineStr"/>
       <c r="P216" s="13" t="inlineStr"/>
       <c r="Q216" s="14" t="n">
-        <v>2.213838E9</v>
+        <v>6.89E7</v>
       </c>
       <c r="R216" s="14" t="inlineStr"/>
       <c r="S216" s="14" t="n">
@@ -13130,23 +13130,23 @@
       <c r="U216" s="14" t="inlineStr"/>
       <c r="V216" s="14" t="inlineStr"/>
       <c r="W216" s="14" t="n">
-        <v>2.213838E9</v>
+        <v>2.2953312E7</v>
       </c>
       <c r="X216" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y216" s="14" t="inlineStr"/>
       <c r="Z216" s="14" t="n">
-        <v>2.213838E9</v>
+        <v>2.2953312E7</v>
       </c>
       <c r="AA216" s="14" t="inlineStr"/>
       <c r="AB216" s="14" t="inlineStr"/>
       <c r="AC216" s="15" t="n">
-        <v>1.0</v>
+        <v>0.33313950653120467</v>
       </c>
       <c r="AD216" s="15" t="inlineStr"/>
       <c r="AE216" s="14" t="n">
-        <v>0.0</v>
+        <v>4.5946688E7</v>
       </c>
       <c r="AF216" s="14" t="inlineStr"/>
       <c r="AG216" s="14" t="inlineStr"/>
@@ -13170,14 +13170,14 @@
       <c r="N217" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000296. Biaya Outsourcing Perorangan Tenaga Kebersihan (Oktober s.d Desember) (5 ORG)</t>
+            <t xml:space="preserve">000297. Biaya Outsourcing Perorangan Petugas Kolam (Oktober s.d Desember) (1 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O217" s="13" t="inlineStr"/>
       <c r="P217" s="13" t="inlineStr"/>
       <c r="Q217" s="14" t="n">
-        <v>6.89E7</v>
+        <v>1.389E7</v>
       </c>
       <c r="R217" s="14" t="inlineStr"/>
       <c r="S217" s="14" t="n">
@@ -13187,54 +13187,60 @@
       <c r="U217" s="14" t="inlineStr"/>
       <c r="V217" s="14" t="inlineStr"/>
       <c r="W217" s="14" t="n">
-        <v>0.0</v>
+        <v>4629928.0</v>
       </c>
       <c r="X217" s="14" t="n">
-        <v>2.2953312E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y217" s="14" t="inlineStr"/>
       <c r="Z217" s="14" t="n">
-        <v>2.2953312E7</v>
+        <v>4629928.0</v>
       </c>
       <c r="AA217" s="14" t="inlineStr"/>
       <c r="AB217" s="14" t="inlineStr"/>
       <c r="AC217" s="15" t="n">
-        <v>0.33313950653120467</v>
+        <v>0.33332814974802016</v>
       </c>
       <c r="AD217" s="15" t="inlineStr"/>
       <c r="AE217" s="14" t="n">
-        <v>4.5946688E7</v>
+        <v>9260072.0</v>
       </c>
       <c r="AF217" s="14" t="inlineStr"/>
       <c r="AG217" s="14" t="inlineStr"/>
       <c r="AH217" s="14" t="inlineStr"/>
       <c r="AI217" s="14" t="inlineStr"/>
     </row>
-    <row r="218" customHeight="1" ht="18">
+    <row r="218" customHeight="1" ht="15">
       <c r="A218" s="2" t="inlineStr"/>
       <c r="B218" s="2" t="inlineStr"/>
       <c r="C218" s="2" t="inlineStr"/>
       <c r="D218" s="2" t="inlineStr"/>
       <c r="E218" s="2" t="inlineStr"/>
-      <c r="F218" s="2" t="inlineStr"/>
-      <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="2" t="inlineStr"/>
-      <c r="I218" s="2" t="inlineStr"/>
-      <c r="J218" s="2" t="inlineStr"/>
-      <c r="K218" s="2" t="inlineStr"/>
-      <c r="L218" s="2" t="inlineStr"/>
-      <c r="M218" s="2" t="inlineStr"/>
-      <c r="N218" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000297. Biaya Outsourcing Perorangan Petugas Kolam (Oktober s.d Desember) (1 ORG)</t>
-          </r>
-        </is>
-      </c>
+      <c r="F218" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">002.DB</t>
+          </r>
+        </is>
+      </c>
+      <c r="G218" s="13" t="inlineStr"/>
+      <c r="H218" s="13" t="inlineStr"/>
+      <c r="I218" s="13" t="inlineStr"/>
+      <c r="J218" s="13" t="inlineStr"/>
+      <c r="K218" s="13" t="inlineStr"/>
+      <c r="L218" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Langganan Daya dan Jasa</t>
+          </r>
+        </is>
+      </c>
+      <c r="M218" s="13" t="inlineStr"/>
+      <c r="N218" s="13" t="inlineStr"/>
       <c r="O218" s="13" t="inlineStr"/>
       <c r="P218" s="13" t="inlineStr"/>
       <c r="Q218" s="14" t="n">
-        <v>1.389E7</v>
+        <v>7.00144E8</v>
       </c>
       <c r="R218" s="14" t="inlineStr"/>
       <c r="S218" s="14" t="n">
@@ -13244,23 +13250,23 @@
       <c r="U218" s="14" t="inlineStr"/>
       <c r="V218" s="14" t="inlineStr"/>
       <c r="W218" s="14" t="n">
-        <v>0.0</v>
+        <v>6.39842407E8</v>
       </c>
       <c r="X218" s="14" t="n">
-        <v>4629928.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y218" s="14" t="inlineStr"/>
       <c r="Z218" s="14" t="n">
-        <v>4629928.0</v>
+        <v>6.39842407E8</v>
       </c>
       <c r="AA218" s="14" t="inlineStr"/>
       <c r="AB218" s="14" t="inlineStr"/>
       <c r="AC218" s="15" t="n">
-        <v>0.33332814974802016</v>
+        <v>0.9138725847825591</v>
       </c>
       <c r="AD218" s="15" t="inlineStr"/>
       <c r="AE218" s="14" t="n">
-        <v>9260072.0</v>
+        <v>6.0301593E7</v>
       </c>
       <c r="AF218" s="14" t="inlineStr"/>
       <c r="AG218" s="14" t="inlineStr"/>
@@ -13273,31 +13279,31 @@
       <c r="C219" s="2" t="inlineStr"/>
       <c r="D219" s="2" t="inlineStr"/>
       <c r="E219" s="2" t="inlineStr"/>
-      <c r="F219" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">002.DB</t>
-          </r>
-        </is>
-      </c>
-      <c r="G219" s="13" t="inlineStr"/>
-      <c r="H219" s="13" t="inlineStr"/>
+      <c r="F219" s="2" t="inlineStr"/>
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522111</t>
+          </r>
+        </is>
+      </c>
       <c r="I219" s="13" t="inlineStr"/>
       <c r="J219" s="13" t="inlineStr"/>
       <c r="K219" s="13" t="inlineStr"/>
-      <c r="L219" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Langganan Daya dan Jasa</t>
-          </r>
-        </is>
-      </c>
-      <c r="M219" s="13" t="inlineStr"/>
+      <c r="L219" s="13" t="inlineStr"/>
+      <c r="M219" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Listrik</t>
+          </r>
+        </is>
+      </c>
       <c r="N219" s="13" t="inlineStr"/>
       <c r="O219" s="13" t="inlineStr"/>
       <c r="P219" s="13" t="inlineStr"/>
       <c r="Q219" s="14" t="n">
-        <v>8.4668E8</v>
+        <v>5.16E8</v>
       </c>
       <c r="R219" s="14" t="inlineStr"/>
       <c r="S219" s="14" t="n">
@@ -13307,23 +13313,23 @@
       <c r="U219" s="14" t="inlineStr"/>
       <c r="V219" s="14" t="inlineStr"/>
       <c r="W219" s="14" t="n">
-        <v>5.87220368E8</v>
+        <v>4.70513911E8</v>
       </c>
       <c r="X219" s="14" t="n">
-        <v>5.2010239E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y219" s="14" t="inlineStr"/>
       <c r="Z219" s="14" t="n">
-        <v>6.39230607E8</v>
+        <v>4.70513911E8</v>
       </c>
       <c r="AA219" s="14" t="inlineStr"/>
       <c r="AB219" s="14" t="inlineStr"/>
       <c r="AC219" s="15" t="n">
-        <v>0.7549848903954268</v>
+        <v>0.9118486647286822</v>
       </c>
       <c r="AD219" s="15" t="inlineStr"/>
       <c r="AE219" s="14" t="n">
-        <v>2.07449393E8</v>
+        <v>4.5486089E7</v>
       </c>
       <c r="AF219" s="14" t="inlineStr"/>
       <c r="AG219" s="14" t="inlineStr"/>
@@ -13338,29 +13344,23 @@
       <c r="E220" s="2" t="inlineStr"/>
       <c r="F220" s="2" t="inlineStr"/>
       <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522111</t>
-          </r>
-        </is>
-      </c>
-      <c r="I220" s="13" t="inlineStr"/>
-      <c r="J220" s="13" t="inlineStr"/>
-      <c r="K220" s="13" t="inlineStr"/>
-      <c r="L220" s="13" t="inlineStr"/>
-      <c r="M220" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Listrik</t>
-          </r>
-        </is>
-      </c>
-      <c r="N220" s="13" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr"/>
+      <c r="I220" s="2" t="inlineStr"/>
+      <c r="J220" s="2" t="inlineStr"/>
+      <c r="K220" s="2" t="inlineStr"/>
+      <c r="L220" s="2" t="inlineStr"/>
+      <c r="M220" s="2" t="inlineStr"/>
+      <c r="N220" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000145. Langganan Listrik</t>
+          </r>
+        </is>
+      </c>
       <c r="O220" s="13" t="inlineStr"/>
       <c r="P220" s="13" t="inlineStr"/>
       <c r="Q220" s="14" t="n">
-        <v>6.4548E8</v>
+        <v>5.16E8</v>
       </c>
       <c r="R220" s="14" t="inlineStr"/>
       <c r="S220" s="14" t="n">
@@ -13370,10 +13370,10 @@
       <c r="U220" s="14" t="inlineStr"/>
       <c r="V220" s="14" t="inlineStr"/>
       <c r="W220" s="14" t="n">
-        <v>4.30266392E8</v>
+        <v>4.70513911E8</v>
       </c>
       <c r="X220" s="14" t="n">
-        <v>4.0247519E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y220" s="14" t="inlineStr"/>
       <c r="Z220" s="14" t="n">
@@ -13382,11 +13382,11 @@
       <c r="AA220" s="14" t="inlineStr"/>
       <c r="AB220" s="14" t="inlineStr"/>
       <c r="AC220" s="15" t="n">
-        <v>0.7289364674350871</v>
+        <v>0.9118486647286822</v>
       </c>
       <c r="AD220" s="15" t="inlineStr"/>
       <c r="AE220" s="14" t="n">
-        <v>1.74966089E8</v>
+        <v>4.5486089E7</v>
       </c>
       <c r="AF220" s="14" t="inlineStr"/>
       <c r="AG220" s="14" t="inlineStr"/>
@@ -13401,23 +13401,29 @@
       <c r="E221" s="2" t="inlineStr"/>
       <c r="F221" s="2" t="inlineStr"/>
       <c r="G221" s="2" t="inlineStr"/>
-      <c r="H221" s="2" t="inlineStr"/>
-      <c r="I221" s="2" t="inlineStr"/>
-      <c r="J221" s="2" t="inlineStr"/>
-      <c r="K221" s="2" t="inlineStr"/>
-      <c r="L221" s="2" t="inlineStr"/>
-      <c r="M221" s="2" t="inlineStr"/>
-      <c r="N221" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000145. Langganan Listrik</t>
-          </r>
-        </is>
-      </c>
+      <c r="H221" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522112</t>
+          </r>
+        </is>
+      </c>
+      <c r="I221" s="13" t="inlineStr"/>
+      <c r="J221" s="13" t="inlineStr"/>
+      <c r="K221" s="13" t="inlineStr"/>
+      <c r="L221" s="13" t="inlineStr"/>
+      <c r="M221" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Telepon</t>
+          </r>
+        </is>
+      </c>
+      <c r="N221" s="13" t="inlineStr"/>
       <c r="O221" s="13" t="inlineStr"/>
       <c r="P221" s="13" t="inlineStr"/>
       <c r="Q221" s="14" t="n">
-        <v>6.4548E8</v>
+        <v>6000000.0</v>
       </c>
       <c r="R221" s="14" t="inlineStr"/>
       <c r="S221" s="14" t="n">
@@ -13427,23 +13433,23 @@
       <c r="U221" s="14" t="inlineStr"/>
       <c r="V221" s="14" t="inlineStr"/>
       <c r="W221" s="14" t="n">
-        <v>4.30266392E8</v>
+        <v>5485232.0</v>
       </c>
       <c r="X221" s="14" t="n">
-        <v>4.0247519E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y221" s="14" t="inlineStr"/>
       <c r="Z221" s="14" t="n">
-        <v>4.70513911E8</v>
+        <v>5485232.0</v>
       </c>
       <c r="AA221" s="14" t="inlineStr"/>
       <c r="AB221" s="14" t="inlineStr"/>
       <c r="AC221" s="15" t="n">
-        <v>0.7289364674350871</v>
+        <v>0.9142053333333333</v>
       </c>
       <c r="AD221" s="15" t="inlineStr"/>
       <c r="AE221" s="14" t="n">
-        <v>1.74966089E8</v>
+        <v>514768.0</v>
       </c>
       <c r="AF221" s="14" t="inlineStr"/>
       <c r="AG221" s="14" t="inlineStr"/>
@@ -13458,25 +13464,19 @@
       <c r="E222" s="2" t="inlineStr"/>
       <c r="F222" s="2" t="inlineStr"/>
       <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522112</t>
-          </r>
-        </is>
-      </c>
-      <c r="I222" s="13" t="inlineStr"/>
-      <c r="J222" s="13" t="inlineStr"/>
-      <c r="K222" s="13" t="inlineStr"/>
-      <c r="L222" s="13" t="inlineStr"/>
-      <c r="M222" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Telepon</t>
-          </r>
-        </is>
-      </c>
-      <c r="N222" s="13" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr"/>
+      <c r="I222" s="2" t="inlineStr"/>
+      <c r="J222" s="2" t="inlineStr"/>
+      <c r="K222" s="2" t="inlineStr"/>
+      <c r="L222" s="2" t="inlineStr"/>
+      <c r="M222" s="2" t="inlineStr"/>
+      <c r="N222" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000146. Langganan Telepon</t>
+          </r>
+        </is>
+      </c>
       <c r="O222" s="13" t="inlineStr"/>
       <c r="P222" s="13" t="inlineStr"/>
       <c r="Q222" s="14" t="n">
@@ -13490,10 +13490,10 @@
       <c r="U222" s="14" t="inlineStr"/>
       <c r="V222" s="14" t="inlineStr"/>
       <c r="W222" s="14" t="n">
-        <v>5219220.0</v>
+        <v>5485232.0</v>
       </c>
       <c r="X222" s="14" t="n">
-        <v>266012.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y222" s="14" t="inlineStr"/>
       <c r="Z222" s="14" t="n">
@@ -13521,23 +13521,29 @@
       <c r="E223" s="2" t="inlineStr"/>
       <c r="F223" s="2" t="inlineStr"/>
       <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="2" t="inlineStr"/>
-      <c r="I223" s="2" t="inlineStr"/>
-      <c r="J223" s="2" t="inlineStr"/>
-      <c r="K223" s="2" t="inlineStr"/>
-      <c r="L223" s="2" t="inlineStr"/>
-      <c r="M223" s="2" t="inlineStr"/>
-      <c r="N223" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000146. Langganan Telepon</t>
-          </r>
-        </is>
-      </c>
+      <c r="H223" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522113</t>
+          </r>
+        </is>
+      </c>
+      <c r="I223" s="13" t="inlineStr"/>
+      <c r="J223" s="13" t="inlineStr"/>
+      <c r="K223" s="13" t="inlineStr"/>
+      <c r="L223" s="13" t="inlineStr"/>
+      <c r="M223" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Air</t>
+          </r>
+        </is>
+      </c>
+      <c r="N223" s="13" t="inlineStr"/>
       <c r="O223" s="13" t="inlineStr"/>
       <c r="P223" s="13" t="inlineStr"/>
       <c r="Q223" s="14" t="n">
-        <v>6000000.0</v>
+        <v>3.3444E7</v>
       </c>
       <c r="R223" s="14" t="inlineStr"/>
       <c r="S223" s="14" t="n">
@@ -13547,23 +13553,23 @@
       <c r="U223" s="14" t="inlineStr"/>
       <c r="V223" s="14" t="inlineStr"/>
       <c r="W223" s="14" t="n">
-        <v>5219220.0</v>
+        <v>3.08218E7</v>
       </c>
       <c r="X223" s="14" t="n">
-        <v>266012.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y223" s="14" t="inlineStr"/>
       <c r="Z223" s="14" t="n">
-        <v>5485232.0</v>
+        <v>3.08218E7</v>
       </c>
       <c r="AA223" s="14" t="inlineStr"/>
       <c r="AB223" s="14" t="inlineStr"/>
       <c r="AC223" s="15" t="n">
-        <v>0.9142053333333333</v>
+        <v>0.9215943069010883</v>
       </c>
       <c r="AD223" s="15" t="inlineStr"/>
       <c r="AE223" s="14" t="n">
-        <v>514768.0</v>
+        <v>2622200.0</v>
       </c>
       <c r="AF223" s="14" t="inlineStr"/>
       <c r="AG223" s="14" t="inlineStr"/>
@@ -13578,29 +13584,23 @@
       <c r="E224" s="2" t="inlineStr"/>
       <c r="F224" s="2" t="inlineStr"/>
       <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522113</t>
-          </r>
-        </is>
-      </c>
-      <c r="I224" s="13" t="inlineStr"/>
-      <c r="J224" s="13" t="inlineStr"/>
-      <c r="K224" s="13" t="inlineStr"/>
-      <c r="L224" s="13" t="inlineStr"/>
-      <c r="M224" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Air</t>
-          </r>
-        </is>
-      </c>
-      <c r="N224" s="13" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr"/>
+      <c r="I224" s="2" t="inlineStr"/>
+      <c r="J224" s="2" t="inlineStr"/>
+      <c r="K224" s="2" t="inlineStr"/>
+      <c r="L224" s="2" t="inlineStr"/>
+      <c r="M224" s="2" t="inlineStr"/>
+      <c r="N224" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000147. Langganan Air (PAM)</t>
+          </r>
+        </is>
+      </c>
       <c r="O224" s="13" t="inlineStr"/>
       <c r="P224" s="13" t="inlineStr"/>
       <c r="Q224" s="14" t="n">
-        <v>3.96E7</v>
+        <v>3.3444E7</v>
       </c>
       <c r="R224" s="14" t="inlineStr"/>
       <c r="S224" s="14" t="n">
@@ -13610,23 +13610,23 @@
       <c r="U224" s="14" t="inlineStr"/>
       <c r="V224" s="14" t="inlineStr"/>
       <c r="W224" s="14" t="n">
-        <v>2.94084E7</v>
+        <v>3.08218E7</v>
       </c>
       <c r="X224" s="14" t="n">
-        <v>801600.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y224" s="14" t="inlineStr"/>
       <c r="Z224" s="14" t="n">
-        <v>3.021E7</v>
+        <v>3.08218E7</v>
       </c>
       <c r="AA224" s="14" t="inlineStr"/>
       <c r="AB224" s="14" t="inlineStr"/>
       <c r="AC224" s="15" t="n">
-        <v>0.7628787878787879</v>
+        <v>0.9215943069010883</v>
       </c>
       <c r="AD224" s="15" t="inlineStr"/>
       <c r="AE224" s="14" t="n">
-        <v>9390000.0</v>
+        <v>2622200.0</v>
       </c>
       <c r="AF224" s="14" t="inlineStr"/>
       <c r="AG224" s="14" t="inlineStr"/>
@@ -13641,23 +13641,29 @@
       <c r="E225" s="2" t="inlineStr"/>
       <c r="F225" s="2" t="inlineStr"/>
       <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="2" t="inlineStr"/>
-      <c r="I225" s="2" t="inlineStr"/>
-      <c r="J225" s="2" t="inlineStr"/>
-      <c r="K225" s="2" t="inlineStr"/>
-      <c r="L225" s="2" t="inlineStr"/>
-      <c r="M225" s="2" t="inlineStr"/>
-      <c r="N225" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000147. Langganan Air (PAM)</t>
-          </r>
-        </is>
-      </c>
+      <c r="H225" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522119</t>
+          </r>
+        </is>
+      </c>
+      <c r="I225" s="13" t="inlineStr"/>
+      <c r="J225" s="13" t="inlineStr"/>
+      <c r="K225" s="13" t="inlineStr"/>
+      <c r="L225" s="13" t="inlineStr"/>
+      <c r="M225" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Daya dan Jasa Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N225" s="13" t="inlineStr"/>
       <c r="O225" s="13" t="inlineStr"/>
       <c r="P225" s="13" t="inlineStr"/>
       <c r="Q225" s="14" t="n">
-        <v>3.96E7</v>
+        <v>1.447E8</v>
       </c>
       <c r="R225" s="14" t="inlineStr"/>
       <c r="S225" s="14" t="n">
@@ -13667,23 +13673,23 @@
       <c r="U225" s="14" t="inlineStr"/>
       <c r="V225" s="14" t="inlineStr"/>
       <c r="W225" s="14" t="n">
-        <v>2.94084E7</v>
+        <v>1.33021464E8</v>
       </c>
       <c r="X225" s="14" t="n">
-        <v>801600.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y225" s="14" t="inlineStr"/>
       <c r="Z225" s="14" t="n">
-        <v>3.021E7</v>
+        <v>1.33021464E8</v>
       </c>
       <c r="AA225" s="14" t="inlineStr"/>
       <c r="AB225" s="14" t="inlineStr"/>
       <c r="AC225" s="15" t="n">
-        <v>0.7628787878787879</v>
+        <v>0.919291389080857</v>
       </c>
       <c r="AD225" s="15" t="inlineStr"/>
       <c r="AE225" s="14" t="n">
-        <v>9390000.0</v>
+        <v>1.1678536E7</v>
       </c>
       <c r="AF225" s="14" t="inlineStr"/>
       <c r="AG225" s="14" t="inlineStr"/>
@@ -13698,29 +13704,23 @@
       <c r="E226" s="2" t="inlineStr"/>
       <c r="F226" s="2" t="inlineStr"/>
       <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522119</t>
-          </r>
-        </is>
-      </c>
-      <c r="I226" s="13" t="inlineStr"/>
-      <c r="J226" s="13" t="inlineStr"/>
-      <c r="K226" s="13" t="inlineStr"/>
-      <c r="L226" s="13" t="inlineStr"/>
-      <c r="M226" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Daya dan Jasa Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N226" s="13" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr"/>
+      <c r="I226" s="2" t="inlineStr"/>
+      <c r="J226" s="2" t="inlineStr"/>
+      <c r="K226" s="2" t="inlineStr"/>
+      <c r="L226" s="2" t="inlineStr"/>
+      <c r="M226" s="2" t="inlineStr"/>
+      <c r="N226" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000148. Langganan Internet</t>
+          </r>
+        </is>
+      </c>
       <c r="O226" s="13" t="inlineStr"/>
       <c r="P226" s="13" t="inlineStr"/>
       <c r="Q226" s="14" t="n">
-        <v>1.556E8</v>
+        <v>1.146E8</v>
       </c>
       <c r="R226" s="14" t="inlineStr"/>
       <c r="S226" s="14" t="n">
@@ -13730,23 +13730,23 @@
       <c r="U226" s="14" t="inlineStr"/>
       <c r="V226" s="14" t="inlineStr"/>
       <c r="W226" s="14" t="n">
-        <v>1.22326356E8</v>
+        <v>1.044355E8</v>
       </c>
       <c r="X226" s="14" t="n">
-        <v>1.0695108E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y226" s="14" t="inlineStr"/>
       <c r="Z226" s="14" t="n">
-        <v>1.33021464E8</v>
+        <v>1.044355E8</v>
       </c>
       <c r="AA226" s="14" t="inlineStr"/>
       <c r="AB226" s="14" t="inlineStr"/>
       <c r="AC226" s="15" t="n">
-        <v>0.8548937275064268</v>
+        <v>0.9113045375218151</v>
       </c>
       <c r="AD226" s="15" t="inlineStr"/>
       <c r="AE226" s="14" t="n">
-        <v>2.2578536E7</v>
+        <v>1.01645E7</v>
       </c>
       <c r="AF226" s="14" t="inlineStr"/>
       <c r="AG226" s="14" t="inlineStr"/>
@@ -13813,14 +13813,14 @@
       <c r="N228" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000148. Langganan Internet</t>
+            <t xml:space="preserve">000240. Langganan aplikasi perkantoran</t>
           </r>
         </is>
       </c>
       <c r="O228" s="13" t="inlineStr"/>
       <c r="P228" s="13" t="inlineStr"/>
       <c r="Q228" s="14" t="n">
-        <v>1.269E8</v>
+        <v>3.01E7</v>
       </c>
       <c r="R228" s="14" t="inlineStr"/>
       <c r="S228" s="14" t="n">
@@ -13830,23 +13830,23 @@
       <c r="U228" s="14" t="inlineStr"/>
       <c r="V228" s="14" t="inlineStr"/>
       <c r="W228" s="14" t="n">
-        <v>9.518475E7</v>
+        <v>2.8585964E7</v>
       </c>
       <c r="X228" s="14" t="n">
-        <v>9250750.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y228" s="14" t="inlineStr"/>
       <c r="Z228" s="14" t="n">
-        <v>1.044355E8</v>
+        <v>2.8585964E7</v>
       </c>
       <c r="AA228" s="14" t="inlineStr"/>
       <c r="AB228" s="14" t="inlineStr"/>
       <c r="AC228" s="15" t="n">
-        <v>0.8229747832939323</v>
+        <v>0.9496998006644518</v>
       </c>
       <c r="AD228" s="15" t="inlineStr"/>
       <c r="AE228" s="14" t="n">
-        <v>2.24645E7</v>
+        <v>1514036.0</v>
       </c>
       <c r="AF228" s="14" t="inlineStr"/>
       <c r="AG228" s="14" t="inlineStr"/>
@@ -13859,25 +13859,31 @@
       <c r="C229" s="2" t="inlineStr"/>
       <c r="D229" s="2" t="inlineStr"/>
       <c r="E229" s="2" t="inlineStr"/>
-      <c r="F229" s="2" t="inlineStr"/>
-      <c r="G229" s="2" t="inlineStr"/>
-      <c r="H229" s="2" t="inlineStr"/>
-      <c r="I229" s="2" t="inlineStr"/>
-      <c r="J229" s="2" t="inlineStr"/>
-      <c r="K229" s="2" t="inlineStr"/>
-      <c r="L229" s="2" t="inlineStr"/>
-      <c r="M229" s="2" t="inlineStr"/>
-      <c r="N229" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000240. Langganan aplikasi perkantoran</t>
-          </r>
-        </is>
-      </c>
+      <c r="F229" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">002.DC</t>
+          </r>
+        </is>
+      </c>
+      <c r="G229" s="13" t="inlineStr"/>
+      <c r="H229" s="13" t="inlineStr"/>
+      <c r="I229" s="13" t="inlineStr"/>
+      <c r="J229" s="13" t="inlineStr"/>
+      <c r="K229" s="13" t="inlineStr"/>
+      <c r="L229" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pemeliharaan Kantor</t>
+          </r>
+        </is>
+      </c>
+      <c r="M229" s="13" t="inlineStr"/>
+      <c r="N229" s="13" t="inlineStr"/>
       <c r="O229" s="13" t="inlineStr"/>
       <c r="P229" s="13" t="inlineStr"/>
       <c r="Q229" s="14" t="n">
-        <v>2.87E7</v>
+        <v>1.11442E9</v>
       </c>
       <c r="R229" s="14" t="inlineStr"/>
       <c r="S229" s="14" t="n">
@@ -13887,23 +13893,23 @@
       <c r="U229" s="14" t="inlineStr"/>
       <c r="V229" s="14" t="inlineStr"/>
       <c r="W229" s="14" t="n">
-        <v>2.7141606E7</v>
+        <v>6.74613153E8</v>
       </c>
       <c r="X229" s="14" t="n">
-        <v>1444358.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y229" s="14" t="inlineStr"/>
       <c r="Z229" s="14" t="n">
-        <v>2.8585964E7</v>
+        <v>6.74613153E8</v>
       </c>
       <c r="AA229" s="14" t="inlineStr"/>
       <c r="AB229" s="14" t="inlineStr"/>
       <c r="AC229" s="15" t="n">
-        <v>0.9960266202090592</v>
+        <v>0.6053491080562086</v>
       </c>
       <c r="AD229" s="15" t="inlineStr"/>
       <c r="AE229" s="14" t="n">
-        <v>114036.0</v>
+        <v>4.39806847E8</v>
       </c>
       <c r="AF229" s="14" t="inlineStr"/>
       <c r="AG229" s="14" t="inlineStr"/>
@@ -13916,31 +13922,31 @@
       <c r="C230" s="2" t="inlineStr"/>
       <c r="D230" s="2" t="inlineStr"/>
       <c r="E230" s="2" t="inlineStr"/>
-      <c r="F230" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">002.DC</t>
-          </r>
-        </is>
-      </c>
-      <c r="G230" s="13" t="inlineStr"/>
-      <c r="H230" s="13" t="inlineStr"/>
+      <c r="F230" s="2" t="inlineStr"/>
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521811</t>
+          </r>
+        </is>
+      </c>
       <c r="I230" s="13" t="inlineStr"/>
       <c r="J230" s="13" t="inlineStr"/>
       <c r="K230" s="13" t="inlineStr"/>
-      <c r="L230" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pemeliharaan Kantor</t>
-          </r>
-        </is>
-      </c>
-      <c r="M230" s="13" t="inlineStr"/>
+      <c r="L230" s="13" t="inlineStr"/>
+      <c r="M230" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
+          </r>
+        </is>
+      </c>
       <c r="N230" s="13" t="inlineStr"/>
       <c r="O230" s="13" t="inlineStr"/>
       <c r="P230" s="13" t="inlineStr"/>
       <c r="Q230" s="14" t="n">
-        <v>9.60035E8</v>
+        <v>2.3E8</v>
       </c>
       <c r="R230" s="14" t="inlineStr"/>
       <c r="S230" s="14" t="n">
@@ -13950,23 +13956,23 @@
       <c r="U230" s="14" t="inlineStr"/>
       <c r="V230" s="14" t="inlineStr"/>
       <c r="W230" s="14" t="n">
-        <v>5.60645387E8</v>
+        <v>2.179125E8</v>
       </c>
       <c r="X230" s="14" t="n">
-        <v>5.8990812E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y230" s="14" t="inlineStr"/>
       <c r="Z230" s="14" t="n">
-        <v>6.19636199E8</v>
+        <v>2.179125E8</v>
       </c>
       <c r="AA230" s="14" t="inlineStr"/>
       <c r="AB230" s="14" t="inlineStr"/>
       <c r="AC230" s="15" t="n">
-        <v>0.6454308426255293</v>
+        <v>0.9474456521739131</v>
       </c>
       <c r="AD230" s="15" t="inlineStr"/>
       <c r="AE230" s="14" t="n">
-        <v>3.40398801E8</v>
+        <v>1.20875E7</v>
       </c>
       <c r="AF230" s="14" t="inlineStr"/>
       <c r="AG230" s="14" t="inlineStr"/>
@@ -13981,29 +13987,23 @@
       <c r="E231" s="2" t="inlineStr"/>
       <c r="F231" s="2" t="inlineStr"/>
       <c r="G231" s="2" t="inlineStr"/>
-      <c r="H231" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521811</t>
-          </r>
-        </is>
-      </c>
-      <c r="I231" s="13" t="inlineStr"/>
-      <c r="J231" s="13" t="inlineStr"/>
-      <c r="K231" s="13" t="inlineStr"/>
-      <c r="L231" s="13" t="inlineStr"/>
-      <c r="M231" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
-          </r>
-        </is>
-      </c>
-      <c r="N231" s="13" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr"/>
+      <c r="I231" s="2" t="inlineStr"/>
+      <c r="J231" s="2" t="inlineStr"/>
+      <c r="K231" s="2" t="inlineStr"/>
+      <c r="L231" s="2" t="inlineStr"/>
+      <c r="M231" s="2" t="inlineStr"/>
+      <c r="N231" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000149. Pakan Induk Ikan Koleksi</t>
+          </r>
+        </is>
+      </c>
       <c r="O231" s="13" t="inlineStr"/>
       <c r="P231" s="13" t="inlineStr"/>
       <c r="Q231" s="14" t="n">
-        <v>2.2E8</v>
+        <v>1.8E8</v>
       </c>
       <c r="R231" s="14" t="inlineStr"/>
       <c r="S231" s="14" t="n">
@@ -14013,23 +14013,23 @@
       <c r="U231" s="14" t="inlineStr"/>
       <c r="V231" s="14" t="inlineStr"/>
       <c r="W231" s="14" t="n">
-        <v>1.9288E8</v>
+        <v>1.67915E8</v>
       </c>
       <c r="X231" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y231" s="14" t="inlineStr"/>
       <c r="Z231" s="14" t="n">
-        <v>1.9288E8</v>
+        <v>1.67915E8</v>
       </c>
       <c r="AA231" s="14" t="inlineStr"/>
       <c r="AB231" s="14" t="inlineStr"/>
       <c r="AC231" s="15" t="n">
-        <v>0.8767272727272727</v>
+        <v>0.9328611111111111</v>
       </c>
       <c r="AD231" s="15" t="inlineStr"/>
       <c r="AE231" s="14" t="n">
-        <v>2.712E7</v>
+        <v>1.2085E7</v>
       </c>
       <c r="AF231" s="14" t="inlineStr"/>
       <c r="AG231" s="14" t="inlineStr"/>
@@ -14053,14 +14053,14 @@
       <c r="N232" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000149. Pakan Induk Ikan Koleksi</t>
+            <t xml:space="preserve">000286. Bahan Baku Pakan Ikan</t>
           </r>
         </is>
       </c>
       <c r="O232" s="13" t="inlineStr"/>
       <c r="P232" s="13" t="inlineStr"/>
       <c r="Q232" s="14" t="n">
-        <v>1.7E8</v>
+        <v>5.0E7</v>
       </c>
       <c r="R232" s="14" t="inlineStr"/>
       <c r="S232" s="14" t="n">
@@ -14070,23 +14070,23 @@
       <c r="U232" s="14" t="inlineStr"/>
       <c r="V232" s="14" t="inlineStr"/>
       <c r="W232" s="14" t="n">
-        <v>1.5279E8</v>
+        <v>4.99975E7</v>
       </c>
       <c r="X232" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y232" s="14" t="inlineStr"/>
       <c r="Z232" s="14" t="n">
-        <v>1.5279E8</v>
+        <v>4.99975E7</v>
       </c>
       <c r="AA232" s="14" t="inlineStr"/>
       <c r="AB232" s="14" t="inlineStr"/>
       <c r="AC232" s="15" t="n">
-        <v>0.8987647058823529</v>
+        <v>0.99995</v>
       </c>
       <c r="AD232" s="15" t="inlineStr"/>
       <c r="AE232" s="14" t="n">
-        <v>1.721E7</v>
+        <v>2500.0</v>
       </c>
       <c r="AF232" s="14" t="inlineStr"/>
       <c r="AG232" s="14" t="inlineStr"/>
@@ -14101,23 +14101,29 @@
       <c r="E233" s="2" t="inlineStr"/>
       <c r="F233" s="2" t="inlineStr"/>
       <c r="G233" s="2" t="inlineStr"/>
-      <c r="H233" s="2" t="inlineStr"/>
-      <c r="I233" s="2" t="inlineStr"/>
-      <c r="J233" s="2" t="inlineStr"/>
-      <c r="K233" s="2" t="inlineStr"/>
-      <c r="L233" s="2" t="inlineStr"/>
-      <c r="M233" s="2" t="inlineStr"/>
-      <c r="N233" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000286. Bahan Baku Pakan Ikan</t>
-          </r>
-        </is>
-      </c>
+      <c r="H233" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522191</t>
+          </r>
+        </is>
+      </c>
+      <c r="I233" s="13" t="inlineStr"/>
+      <c r="J233" s="13" t="inlineStr"/>
+      <c r="K233" s="13" t="inlineStr"/>
+      <c r="L233" s="13" t="inlineStr"/>
+      <c r="M233" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Jasa Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N233" s="13" t="inlineStr"/>
       <c r="O233" s="13" t="inlineStr"/>
       <c r="P233" s="13" t="inlineStr"/>
       <c r="Q233" s="14" t="n">
-        <v>5.0E7</v>
+        <v>3.041E7</v>
       </c>
       <c r="R233" s="14" t="inlineStr"/>
       <c r="S233" s="14" t="n">
@@ -14127,23 +14133,23 @@
       <c r="U233" s="14" t="inlineStr"/>
       <c r="V233" s="14" t="inlineStr"/>
       <c r="W233" s="14" t="n">
-        <v>4.009E7</v>
+        <v>3.0406785E7</v>
       </c>
       <c r="X233" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y233" s="14" t="inlineStr"/>
       <c r="Z233" s="14" t="n">
-        <v>4.009E7</v>
+        <v>3.0406785E7</v>
       </c>
       <c r="AA233" s="14" t="inlineStr"/>
       <c r="AB233" s="14" t="inlineStr"/>
       <c r="AC233" s="15" t="n">
-        <v>0.8018</v>
+        <v>0.9998942781979612</v>
       </c>
       <c r="AD233" s="15" t="inlineStr"/>
       <c r="AE233" s="14" t="n">
-        <v>9910000.0</v>
+        <v>3215.0</v>
       </c>
       <c r="AF233" s="14" t="inlineStr"/>
       <c r="AG233" s="14" t="inlineStr"/>
@@ -14158,29 +14164,23 @@
       <c r="E234" s="2" t="inlineStr"/>
       <c r="F234" s="2" t="inlineStr"/>
       <c r="G234" s="2" t="inlineStr"/>
-      <c r="H234" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522191</t>
-          </r>
-        </is>
-      </c>
-      <c r="I234" s="13" t="inlineStr"/>
-      <c r="J234" s="13" t="inlineStr"/>
-      <c r="K234" s="13" t="inlineStr"/>
-      <c r="L234" s="13" t="inlineStr"/>
-      <c r="M234" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Jasa Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N234" s="13" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr"/>
+      <c r="I234" s="2" t="inlineStr"/>
+      <c r="J234" s="2" t="inlineStr"/>
+      <c r="K234" s="2" t="inlineStr"/>
+      <c r="L234" s="2" t="inlineStr"/>
+      <c r="M234" s="2" t="inlineStr"/>
+      <c r="N234" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000242. Jasa Penanganan Rayap</t>
+          </r>
+        </is>
+      </c>
       <c r="O234" s="13" t="inlineStr"/>
       <c r="P234" s="13" t="inlineStr"/>
       <c r="Q234" s="14" t="n">
-        <v>3.526E7</v>
+        <v>3.041E7</v>
       </c>
       <c r="R234" s="14" t="inlineStr"/>
       <c r="S234" s="14" t="n">
@@ -14202,11 +14202,11 @@
       <c r="AA234" s="14" t="inlineStr"/>
       <c r="AB234" s="14" t="inlineStr"/>
       <c r="AC234" s="15" t="n">
-        <v>0.8623591888825864</v>
+        <v>0.9998942781979612</v>
       </c>
       <c r="AD234" s="15" t="inlineStr"/>
       <c r="AE234" s="14" t="n">
-        <v>4853215.0</v>
+        <v>3215.0</v>
       </c>
       <c r="AF234" s="14" t="inlineStr"/>
       <c r="AG234" s="14" t="inlineStr"/>
@@ -14221,23 +14221,29 @@
       <c r="E235" s="2" t="inlineStr"/>
       <c r="F235" s="2" t="inlineStr"/>
       <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="2" t="inlineStr"/>
-      <c r="I235" s="2" t="inlineStr"/>
-      <c r="J235" s="2" t="inlineStr"/>
-      <c r="K235" s="2" t="inlineStr"/>
-      <c r="L235" s="2" t="inlineStr"/>
-      <c r="M235" s="2" t="inlineStr"/>
-      <c r="N235" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000242. Jasa Penanganan Rayap</t>
-          </r>
-        </is>
-      </c>
+      <c r="H235" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">523111</t>
+          </r>
+        </is>
+      </c>
+      <c r="I235" s="13" t="inlineStr"/>
+      <c r="J235" s="13" t="inlineStr"/>
+      <c r="K235" s="13" t="inlineStr"/>
+      <c r="L235" s="13" t="inlineStr"/>
+      <c r="M235" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Pemeliharaan Gedung dan Bangunan</t>
+          </r>
+        </is>
+      </c>
+      <c r="N235" s="13" t="inlineStr"/>
       <c r="O235" s="13" t="inlineStr"/>
       <c r="P235" s="13" t="inlineStr"/>
       <c r="Q235" s="14" t="n">
-        <v>3.526E7</v>
+        <v>3.7109E8</v>
       </c>
       <c r="R235" s="14" t="inlineStr"/>
       <c r="S235" s="14" t="n">
@@ -14247,23 +14253,23 @@
       <c r="U235" s="14" t="inlineStr"/>
       <c r="V235" s="14" t="inlineStr"/>
       <c r="W235" s="14" t="n">
-        <v>3.0406785E7</v>
+        <v>1.34221533E8</v>
       </c>
       <c r="X235" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y235" s="14" t="inlineStr"/>
       <c r="Z235" s="14" t="n">
-        <v>3.0406785E7</v>
+        <v>1.34221533E8</v>
       </c>
       <c r="AA235" s="14" t="inlineStr"/>
       <c r="AB235" s="14" t="inlineStr"/>
       <c r="AC235" s="15" t="n">
-        <v>0.8623591888825864</v>
+        <v>0.36169536500579375</v>
       </c>
       <c r="AD235" s="15" t="inlineStr"/>
       <c r="AE235" s="14" t="n">
-        <v>4853215.0</v>
+        <v>2.36868467E8</v>
       </c>
       <c r="AF235" s="14" t="inlineStr"/>
       <c r="AG235" s="14" t="inlineStr"/>
@@ -14278,29 +14284,23 @@
       <c r="E236" s="2" t="inlineStr"/>
       <c r="F236" s="2" t="inlineStr"/>
       <c r="G236" s="2" t="inlineStr"/>
-      <c r="H236" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">523111</t>
-          </r>
-        </is>
-      </c>
-      <c r="I236" s="13" t="inlineStr"/>
-      <c r="J236" s="13" t="inlineStr"/>
-      <c r="K236" s="13" t="inlineStr"/>
-      <c r="L236" s="13" t="inlineStr"/>
-      <c r="M236" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Pemeliharaan Gedung dan Bangunan</t>
-          </r>
-        </is>
-      </c>
-      <c r="N236" s="13" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr"/>
+      <c r="I236" s="2" t="inlineStr"/>
+      <c r="J236" s="2" t="inlineStr"/>
+      <c r="K236" s="2" t="inlineStr"/>
+      <c r="L236" s="2" t="inlineStr"/>
+      <c r="M236" s="2" t="inlineStr"/>
+      <c r="N236" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000157. Pemeliharaan Kantor Cibalagung</t>
+          </r>
+        </is>
+      </c>
       <c r="O236" s="13" t="inlineStr"/>
       <c r="P236" s="13" t="inlineStr"/>
       <c r="Q236" s="14" t="n">
-        <v>3.93715E8</v>
+        <v>1.7E7</v>
       </c>
       <c r="R236" s="14" t="inlineStr"/>
       <c r="S236" s="14" t="n">
@@ -14310,30 +14310,30 @@
       <c r="U236" s="14" t="inlineStr"/>
       <c r="V236" s="14" t="inlineStr"/>
       <c r="W236" s="14" t="n">
-        <v>1.17911533E8</v>
+        <v>1.6931622E7</v>
       </c>
       <c r="X236" s="14" t="n">
-        <v>1.0897E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y236" s="14" t="inlineStr"/>
       <c r="Z236" s="14" t="n">
-        <v>1.28808533E8</v>
+        <v>1.6931622E7</v>
       </c>
       <c r="AA236" s="14" t="inlineStr"/>
       <c r="AB236" s="14" t="inlineStr"/>
       <c r="AC236" s="15" t="n">
-        <v>0.3271618632767357</v>
+        <v>0.9959777647058824</v>
       </c>
       <c r="AD236" s="15" t="inlineStr"/>
       <c r="AE236" s="14" t="n">
-        <v>2.64906467E8</v>
+        <v>68378.0</v>
       </c>
       <c r="AF236" s="14" t="inlineStr"/>
       <c r="AG236" s="14" t="inlineStr"/>
       <c r="AH236" s="14" t="inlineStr"/>
       <c r="AI236" s="14" t="inlineStr"/>
     </row>
-    <row r="237" customHeight="1" ht="15">
+    <row r="237" customHeight="1" ht="18">
       <c r="A237" s="2" t="inlineStr"/>
       <c r="B237" s="2" t="inlineStr"/>
       <c r="C237" s="2" t="inlineStr"/>
@@ -14350,14 +14350,14 @@
       <c r="N237" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000157. Pemeliharaan Kantor Cibalagung</t>
+            <t xml:space="preserve">000158. Pemeliharaan Hatchery dan Laboratorium Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O237" s="13" t="inlineStr"/>
       <c r="P237" s="13" t="inlineStr"/>
       <c r="Q237" s="14" t="n">
-        <v>1.7E7</v>
+        <v>3.73E7</v>
       </c>
       <c r="R237" s="14" t="inlineStr"/>
       <c r="S237" s="14" t="n">
@@ -14367,30 +14367,30 @@
       <c r="U237" s="14" t="inlineStr"/>
       <c r="V237" s="14" t="inlineStr"/>
       <c r="W237" s="14" t="n">
-        <v>1.6931622E7</v>
+        <v>2.1347299E7</v>
       </c>
       <c r="X237" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y237" s="14" t="inlineStr"/>
       <c r="Z237" s="14" t="n">
-        <v>1.6931622E7</v>
+        <v>2.1347299E7</v>
       </c>
       <c r="AA237" s="14" t="inlineStr"/>
       <c r="AB237" s="14" t="inlineStr"/>
       <c r="AC237" s="15" t="n">
-        <v>0.9959777647058824</v>
+        <v>0.5723136461126005</v>
       </c>
       <c r="AD237" s="15" t="inlineStr"/>
       <c r="AE237" s="14" t="n">
-        <v>68378.0</v>
+        <v>1.5952701E7</v>
       </c>
       <c r="AF237" s="14" t="inlineStr"/>
       <c r="AG237" s="14" t="inlineStr"/>
       <c r="AH237" s="14" t="inlineStr"/>
       <c r="AI237" s="14" t="inlineStr"/>
     </row>
-    <row r="238" customHeight="1" ht="18">
+    <row r="238" customHeight="1" ht="15">
       <c r="A238" s="2" t="inlineStr"/>
       <c r="B238" s="2" t="inlineStr"/>
       <c r="C238" s="2" t="inlineStr"/>
@@ -14407,14 +14407,14 @@
       <c r="N238" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000158. Pemeliharaan Hatchery dan Laboratorium Cibalagung</t>
+            <t xml:space="preserve">000159. Pemeliharaan Kolam Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O238" s="13" t="inlineStr"/>
       <c r="P238" s="13" t="inlineStr"/>
       <c r="Q238" s="14" t="n">
-        <v>2.695E7</v>
+        <v>2.595E7</v>
       </c>
       <c r="R238" s="14" t="inlineStr"/>
       <c r="S238" s="14" t="n">
@@ -14424,23 +14424,23 @@
       <c r="U238" s="14" t="inlineStr"/>
       <c r="V238" s="14" t="inlineStr"/>
       <c r="W238" s="14" t="n">
-        <v>1.2396299E7</v>
+        <v>2.5327E7</v>
       </c>
       <c r="X238" s="14" t="n">
-        <v>8951000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y238" s="14" t="inlineStr"/>
       <c r="Z238" s="14" t="n">
-        <v>2.1347299E7</v>
+        <v>2.5327E7</v>
       </c>
       <c r="AA238" s="14" t="inlineStr"/>
       <c r="AB238" s="14" t="inlineStr"/>
       <c r="AC238" s="15" t="n">
-        <v>0.7921075695732839</v>
+        <v>0.9759922928709056</v>
       </c>
       <c r="AD238" s="15" t="inlineStr"/>
       <c r="AE238" s="14" t="n">
-        <v>5602701.0</v>
+        <v>623000.0</v>
       </c>
       <c r="AF238" s="14" t="inlineStr"/>
       <c r="AG238" s="14" t="inlineStr"/>
@@ -14464,14 +14464,14 @@
       <c r="N239" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000159. Pemeliharaan Kolam Cibalagung</t>
+            <t xml:space="preserve">000160. Pemeliharaan Pagar Keliling Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O239" s="13" t="inlineStr"/>
       <c r="P239" s="13" t="inlineStr"/>
       <c r="Q239" s="14" t="n">
-        <v>2.595E7</v>
+        <v>2170000.0</v>
       </c>
       <c r="R239" s="14" t="inlineStr"/>
       <c r="S239" s="14" t="n">
@@ -14481,23 +14481,23 @@
       <c r="U239" s="14" t="inlineStr"/>
       <c r="V239" s="14" t="inlineStr"/>
       <c r="W239" s="14" t="n">
-        <v>2.5327E7</v>
+        <v>2167000.0</v>
       </c>
       <c r="X239" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y239" s="14" t="inlineStr"/>
       <c r="Z239" s="14" t="n">
-        <v>2.5327E7</v>
+        <v>2167000.0</v>
       </c>
       <c r="AA239" s="14" t="inlineStr"/>
       <c r="AB239" s="14" t="inlineStr"/>
       <c r="AC239" s="15" t="n">
-        <v>0.9759922928709056</v>
+        <v>0.9986175115207373</v>
       </c>
       <c r="AD239" s="15" t="inlineStr"/>
       <c r="AE239" s="14" t="n">
-        <v>623000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="AF239" s="14" t="inlineStr"/>
       <c r="AG239" s="14" t="inlineStr"/>
@@ -14521,14 +14521,14 @@
       <c r="N240" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000160. Pemeliharaan Pagar Keliling Cibalagung</t>
+            <t xml:space="preserve">000161. Pemeliharaan Kantor Sempur</t>
           </r>
         </is>
       </c>
       <c r="O240" s="13" t="inlineStr"/>
       <c r="P240" s="13" t="inlineStr"/>
       <c r="Q240" s="14" t="n">
-        <v>2170000.0</v>
+        <v>1.341E8</v>
       </c>
       <c r="R240" s="14" t="inlineStr"/>
       <c r="S240" s="14" t="n">
@@ -14538,23 +14538,23 @@
       <c r="U240" s="14" t="inlineStr"/>
       <c r="V240" s="14" t="inlineStr"/>
       <c r="W240" s="14" t="n">
-        <v>2167000.0</v>
+        <v>4421000.0</v>
       </c>
       <c r="X240" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y240" s="14" t="inlineStr"/>
       <c r="Z240" s="14" t="n">
-        <v>2167000.0</v>
+        <v>4421000.0</v>
       </c>
       <c r="AA240" s="14" t="inlineStr"/>
       <c r="AB240" s="14" t="inlineStr"/>
       <c r="AC240" s="15" t="n">
-        <v>0.9986175115207373</v>
+        <v>0.03296793437733035</v>
       </c>
       <c r="AD240" s="15" t="inlineStr"/>
       <c r="AE240" s="14" t="n">
-        <v>3000.0</v>
+        <v>1.29679E8</v>
       </c>
       <c r="AF240" s="14" t="inlineStr"/>
       <c r="AG240" s="14" t="inlineStr"/>
@@ -14578,14 +14578,14 @@
       <c r="N241" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000161. Pemeliharaan Kantor Sempur</t>
+            <t xml:space="preserve">000164. Pemeliharaan Kantor Depok</t>
           </r>
         </is>
       </c>
       <c r="O241" s="13" t="inlineStr"/>
       <c r="P241" s="13" t="inlineStr"/>
       <c r="Q241" s="14" t="n">
-        <v>2.05735E8</v>
+        <v>2800000.0</v>
       </c>
       <c r="R241" s="14" t="inlineStr"/>
       <c r="S241" s="14" t="n">
@@ -14595,23 +14595,23 @@
       <c r="U241" s="14" t="inlineStr"/>
       <c r="V241" s="14" t="inlineStr"/>
       <c r="W241" s="14" t="n">
-        <v>2475000.0</v>
+        <v>1360000.0</v>
       </c>
       <c r="X241" s="14" t="n">
-        <v>1946000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y241" s="14" t="inlineStr"/>
       <c r="Z241" s="14" t="n">
-        <v>4421000.0</v>
+        <v>1360000.0</v>
       </c>
       <c r="AA241" s="14" t="inlineStr"/>
       <c r="AB241" s="14" t="inlineStr"/>
       <c r="AC241" s="15" t="n">
-        <v>0.02148880841859674</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="AD241" s="15" t="inlineStr"/>
       <c r="AE241" s="14" t="n">
-        <v>2.01314E8</v>
+        <v>1440000.0</v>
       </c>
       <c r="AF241" s="14" t="inlineStr"/>
       <c r="AG241" s="14" t="inlineStr"/>
@@ -14635,14 +14635,14 @@
       <c r="N242" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000164. Pemeliharaan Kantor Depok</t>
+            <t xml:space="preserve">000165. Pemeliharaan Gedung Laboratorium Depok</t>
           </r>
         </is>
       </c>
       <c r="O242" s="13" t="inlineStr"/>
       <c r="P242" s="13" t="inlineStr"/>
       <c r="Q242" s="14" t="n">
-        <v>2800000.0</v>
+        <v>2.66E7</v>
       </c>
       <c r="R242" s="14" t="inlineStr"/>
       <c r="S242" s="14" t="n">
@@ -14652,23 +14652,23 @@
       <c r="U242" s="14" t="inlineStr"/>
       <c r="V242" s="14" t="inlineStr"/>
       <c r="W242" s="14" t="n">
-        <v>1360000.0</v>
+        <v>1.2143622E7</v>
       </c>
       <c r="X242" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y242" s="14" t="inlineStr"/>
       <c r="Z242" s="14" t="n">
-        <v>1360000.0</v>
+        <v>1.2143622E7</v>
       </c>
       <c r="AA242" s="14" t="inlineStr"/>
       <c r="AB242" s="14" t="inlineStr"/>
       <c r="AC242" s="15" t="n">
-        <v>0.4857142857142857</v>
+        <v>0.45652714285714285</v>
       </c>
       <c r="AD242" s="15" t="inlineStr"/>
       <c r="AE242" s="14" t="n">
-        <v>1440000.0</v>
+        <v>1.4456378E7</v>
       </c>
       <c r="AF242" s="14" t="inlineStr"/>
       <c r="AG242" s="14" t="inlineStr"/>
@@ -14692,14 +14692,14 @@
       <c r="N243" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000165. Pemeliharaan Gedung Laboratorium Depok</t>
+            <t xml:space="preserve">000167. Pemeliharaan Halaman Kantor Depok</t>
           </r>
         </is>
       </c>
       <c r="O243" s="13" t="inlineStr"/>
       <c r="P243" s="13" t="inlineStr"/>
       <c r="Q243" s="14" t="n">
-        <v>2.66E7</v>
+        <v>1.443E7</v>
       </c>
       <c r="R243" s="14" t="inlineStr"/>
       <c r="S243" s="14" t="n">
@@ -14709,23 +14709,23 @@
       <c r="U243" s="14" t="inlineStr"/>
       <c r="V243" s="14" t="inlineStr"/>
       <c r="W243" s="14" t="n">
-        <v>1.2143622E7</v>
+        <v>1.443E7</v>
       </c>
       <c r="X243" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y243" s="14" t="inlineStr"/>
       <c r="Z243" s="14" t="n">
-        <v>1.2143622E7</v>
+        <v>1.443E7</v>
       </c>
       <c r="AA243" s="14" t="inlineStr"/>
       <c r="AB243" s="14" t="inlineStr"/>
       <c r="AC243" s="15" t="n">
-        <v>0.45652714285714285</v>
+        <v>1.0</v>
       </c>
       <c r="AD243" s="15" t="inlineStr"/>
       <c r="AE243" s="14" t="n">
-        <v>1.4456378E7</v>
+        <v>0.0</v>
       </c>
       <c r="AF243" s="14" t="inlineStr"/>
       <c r="AG243" s="14" t="inlineStr"/>
@@ -14749,14 +14749,14 @@
       <c r="N244" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000167. Pemeliharaan Halaman Kantor Depok</t>
+            <t xml:space="preserve">000170. Pemeliharaan Halaman Kantor Sempur</t>
           </r>
         </is>
       </c>
       <c r="O244" s="13" t="inlineStr"/>
       <c r="P244" s="13" t="inlineStr"/>
       <c r="Q244" s="14" t="n">
-        <v>1.443E7</v>
+        <v>4150000.0</v>
       </c>
       <c r="R244" s="14" t="inlineStr"/>
       <c r="S244" s="14" t="n">
@@ -14766,23 +14766,23 @@
       <c r="U244" s="14" t="inlineStr"/>
       <c r="V244" s="14" t="inlineStr"/>
       <c r="W244" s="14" t="n">
-        <v>1.443E7</v>
+        <v>1576500.0</v>
       </c>
       <c r="X244" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y244" s="14" t="inlineStr"/>
       <c r="Z244" s="14" t="n">
-        <v>1.443E7</v>
+        <v>1576500.0</v>
       </c>
       <c r="AA244" s="14" t="inlineStr"/>
       <c r="AB244" s="14" t="inlineStr"/>
       <c r="AC244" s="15" t="n">
-        <v>1.0</v>
+        <v>0.37987951807228915</v>
       </c>
       <c r="AD244" s="15" t="inlineStr"/>
       <c r="AE244" s="14" t="n">
-        <v>0.0</v>
+        <v>2573500.0</v>
       </c>
       <c r="AF244" s="14" t="inlineStr"/>
       <c r="AG244" s="14" t="inlineStr"/>
@@ -14806,14 +14806,14 @@
       <c r="N245" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000170. Pemeliharaan Halaman Kantor Sempur</t>
+            <t xml:space="preserve">000241. Pemeliharaan Rumah Dinas Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O245" s="13" t="inlineStr"/>
       <c r="P245" s="13" t="inlineStr"/>
       <c r="Q245" s="14" t="n">
-        <v>4150000.0</v>
+        <v>4400000.0</v>
       </c>
       <c r="R245" s="14" t="inlineStr"/>
       <c r="S245" s="14" t="n">
@@ -14823,23 +14823,23 @@
       <c r="U245" s="14" t="inlineStr"/>
       <c r="V245" s="14" t="inlineStr"/>
       <c r="W245" s="14" t="n">
-        <v>1576500.0</v>
+        <v>4180000.0</v>
       </c>
       <c r="X245" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y245" s="14" t="inlineStr"/>
       <c r="Z245" s="14" t="n">
-        <v>1576500.0</v>
+        <v>4180000.0</v>
       </c>
       <c r="AA245" s="14" t="inlineStr"/>
       <c r="AB245" s="14" t="inlineStr"/>
       <c r="AC245" s="15" t="n">
-        <v>0.37987951807228915</v>
+        <v>0.95</v>
       </c>
       <c r="AD245" s="15" t="inlineStr"/>
       <c r="AE245" s="14" t="n">
-        <v>2573500.0</v>
+        <v>220000.0</v>
       </c>
       <c r="AF245" s="14" t="inlineStr"/>
       <c r="AG245" s="14" t="inlineStr"/>
@@ -14863,14 +14863,14 @@
       <c r="N246" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000241. Pemeliharaan Rumah Dinas Cibalagung</t>
+            <t xml:space="preserve">000264. Pemeliharaan Kolam Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O246" s="13" t="inlineStr"/>
       <c r="P246" s="13" t="inlineStr"/>
       <c r="Q246" s="14" t="n">
-        <v>4400000.0</v>
+        <v>4.21E7</v>
       </c>
       <c r="R246" s="14" t="inlineStr"/>
       <c r="S246" s="14" t="n">
@@ -14880,23 +14880,23 @@
       <c r="U246" s="14" t="inlineStr"/>
       <c r="V246" s="14" t="inlineStr"/>
       <c r="W246" s="14" t="n">
-        <v>4180000.0</v>
+        <v>1.5284E7</v>
       </c>
       <c r="X246" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y246" s="14" t="inlineStr"/>
       <c r="Z246" s="14" t="n">
-        <v>4180000.0</v>
+        <v>1.5284E7</v>
       </c>
       <c r="AA246" s="14" t="inlineStr"/>
       <c r="AB246" s="14" t="inlineStr"/>
       <c r="AC246" s="15" t="n">
-        <v>0.95</v>
+        <v>0.36304038004750594</v>
       </c>
       <c r="AD246" s="15" t="inlineStr"/>
       <c r="AE246" s="14" t="n">
-        <v>220000.0</v>
+        <v>2.6816E7</v>
       </c>
       <c r="AF246" s="14" t="inlineStr"/>
       <c r="AG246" s="14" t="inlineStr"/>
@@ -14920,14 +14920,14 @@
       <c r="N247" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000264. Pemeliharaan Kolam Cijeruk</t>
+            <t xml:space="preserve">000280. Pemeliharaan Kantor Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O247" s="13" t="inlineStr"/>
       <c r="P247" s="13" t="inlineStr"/>
       <c r="Q247" s="14" t="n">
-        <v>2.71E7</v>
+        <v>3.059E7</v>
       </c>
       <c r="R247" s="14" t="inlineStr"/>
       <c r="S247" s="14" t="n">
@@ -14937,23 +14937,23 @@
       <c r="U247" s="14" t="inlineStr"/>
       <c r="V247" s="14" t="inlineStr"/>
       <c r="W247" s="14" t="n">
-        <v>1.5284E7</v>
+        <v>0.0</v>
       </c>
       <c r="X247" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y247" s="14" t="inlineStr"/>
       <c r="Z247" s="14" t="n">
-        <v>1.5284E7</v>
+        <v>0.0</v>
       </c>
       <c r="AA247" s="14" t="inlineStr"/>
       <c r="AB247" s="14" t="inlineStr"/>
       <c r="AC247" s="15" t="n">
-        <v>0.5639852398523986</v>
+        <v>0.0</v>
       </c>
       <c r="AD247" s="15" t="inlineStr"/>
       <c r="AE247" s="14" t="n">
-        <v>1.1816E7</v>
+        <v>3.059E7</v>
       </c>
       <c r="AF247" s="14" t="inlineStr"/>
       <c r="AG247" s="14" t="inlineStr"/>
@@ -14977,14 +14977,14 @@
       <c r="N248" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000280. Pemeliharaan Kantor Cijeruk</t>
+            <t xml:space="preserve">000281. Pemeliharaan Pagar Keliling Depok</t>
           </r>
         </is>
       </c>
       <c r="O248" s="13" t="inlineStr"/>
       <c r="P248" s="13" t="inlineStr"/>
       <c r="Q248" s="14" t="n">
-        <v>6930000.0</v>
+        <v>1.0E7</v>
       </c>
       <c r="R248" s="14" t="inlineStr"/>
       <c r="S248" s="14" t="n">
@@ -14994,23 +14994,23 @@
       <c r="U248" s="14" t="inlineStr"/>
       <c r="V248" s="14" t="inlineStr"/>
       <c r="W248" s="14" t="n">
-        <v>0.0</v>
+        <v>9640490.0</v>
       </c>
       <c r="X248" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y248" s="14" t="inlineStr"/>
       <c r="Z248" s="14" t="n">
-        <v>0.0</v>
+        <v>9640490.0</v>
       </c>
       <c r="AA248" s="14" t="inlineStr"/>
       <c r="AB248" s="14" t="inlineStr"/>
       <c r="AC248" s="15" t="n">
-        <v>0.0</v>
+        <v>0.964049</v>
       </c>
       <c r="AD248" s="15" t="inlineStr"/>
       <c r="AE248" s="14" t="n">
-        <v>6930000.0</v>
+        <v>359510.0</v>
       </c>
       <c r="AF248" s="14" t="inlineStr"/>
       <c r="AG248" s="14" t="inlineStr"/>
@@ -15034,14 +15034,14 @@
       <c r="N249" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000281. Pemeliharaan Pagar Keliling Depok</t>
+            <t xml:space="preserve">000298. Pemeliharaan Halaman Kantor Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O249" s="13" t="inlineStr"/>
       <c r="P249" s="13" t="inlineStr"/>
       <c r="Q249" s="14" t="n">
-        <v>1.0E7</v>
+        <v>4300000.0</v>
       </c>
       <c r="R249" s="14" t="inlineStr"/>
       <c r="S249" s="14" t="n">
@@ -15051,23 +15051,23 @@
       <c r="U249" s="14" t="inlineStr"/>
       <c r="V249" s="14" t="inlineStr"/>
       <c r="W249" s="14" t="n">
-        <v>9640490.0</v>
+        <v>0.0</v>
       </c>
       <c r="X249" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y249" s="14" t="inlineStr"/>
       <c r="Z249" s="14" t="n">
-        <v>9640490.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA249" s="14" t="inlineStr"/>
       <c r="AB249" s="14" t="inlineStr"/>
       <c r="AC249" s="15" t="n">
-        <v>0.964049</v>
+        <v>0.0</v>
       </c>
       <c r="AD249" s="15" t="inlineStr"/>
       <c r="AE249" s="14" t="n">
-        <v>359510.0</v>
+        <v>4300000.0</v>
       </c>
       <c r="AF249" s="14" t="inlineStr"/>
       <c r="AG249" s="14" t="inlineStr"/>
@@ -15091,14 +15091,14 @@
       <c r="N250" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000298. Pemeliharaan Halaman Kantor Cijeruk</t>
+            <t xml:space="preserve">000302. Pemeliharaan Gedung Laboratorium Permanen</t>
           </r>
         </is>
       </c>
       <c r="O250" s="13" t="inlineStr"/>
       <c r="P250" s="13" t="inlineStr"/>
       <c r="Q250" s="14" t="n">
-        <v>4300000.0</v>
+        <v>5700000.0</v>
       </c>
       <c r="R250" s="14" t="inlineStr"/>
       <c r="S250" s="14" t="n">
@@ -15124,7 +15124,7 @@
       </c>
       <c r="AD250" s="15" t="inlineStr"/>
       <c r="AE250" s="14" t="n">
-        <v>4300000.0</v>
+        <v>5700000.0</v>
       </c>
       <c r="AF250" s="14" t="inlineStr"/>
       <c r="AG250" s="14" t="inlineStr"/>
@@ -15148,14 +15148,14 @@
       <c r="N251" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000302. Pemeliharaan Gedung Laboratorium Permanen</t>
+            <t xml:space="preserve">000303. Pemeliharaan Mushola</t>
           </r>
         </is>
       </c>
       <c r="O251" s="13" t="inlineStr"/>
       <c r="P251" s="13" t="inlineStr"/>
       <c r="Q251" s="14" t="n">
-        <v>5700000.0</v>
+        <v>9500000.0</v>
       </c>
       <c r="R251" s="14" t="inlineStr"/>
       <c r="S251" s="14" t="n">
@@ -15165,23 +15165,23 @@
       <c r="U251" s="14" t="inlineStr"/>
       <c r="V251" s="14" t="inlineStr"/>
       <c r="W251" s="14" t="n">
-        <v>0.0</v>
+        <v>5413000.0</v>
       </c>
       <c r="X251" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y251" s="14" t="inlineStr"/>
       <c r="Z251" s="14" t="n">
-        <v>0.0</v>
+        <v>5413000.0</v>
       </c>
       <c r="AA251" s="14" t="inlineStr"/>
       <c r="AB251" s="14" t="inlineStr"/>
       <c r="AC251" s="15" t="n">
-        <v>0.0</v>
+        <v>0.5697894736842105</v>
       </c>
       <c r="AD251" s="15" t="inlineStr"/>
       <c r="AE251" s="14" t="n">
-        <v>5700000.0</v>
+        <v>4087000.0</v>
       </c>
       <c r="AF251" s="14" t="inlineStr"/>
       <c r="AG251" s="14" t="inlineStr"/>
@@ -15196,23 +15196,29 @@
       <c r="E252" s="2" t="inlineStr"/>
       <c r="F252" s="2" t="inlineStr"/>
       <c r="G252" s="2" t="inlineStr"/>
-      <c r="H252" s="2" t="inlineStr"/>
-      <c r="I252" s="2" t="inlineStr"/>
-      <c r="J252" s="2" t="inlineStr"/>
-      <c r="K252" s="2" t="inlineStr"/>
-      <c r="L252" s="2" t="inlineStr"/>
-      <c r="M252" s="2" t="inlineStr"/>
-      <c r="N252" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000303. Pemeliharaan Mushola</t>
-          </r>
-        </is>
-      </c>
+      <c r="H252" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">523121</t>
+          </r>
+        </is>
+      </c>
+      <c r="I252" s="13" t="inlineStr"/>
+      <c r="J252" s="13" t="inlineStr"/>
+      <c r="K252" s="13" t="inlineStr"/>
+      <c r="L252" s="13" t="inlineStr"/>
+      <c r="M252" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Pemeliharaan Peralatan dan Mesin</t>
+          </r>
+        </is>
+      </c>
+      <c r="N252" s="13" t="inlineStr"/>
       <c r="O252" s="13" t="inlineStr"/>
       <c r="P252" s="13" t="inlineStr"/>
       <c r="Q252" s="14" t="n">
-        <v>9500000.0</v>
+        <v>3.3E8</v>
       </c>
       <c r="R252" s="14" t="inlineStr"/>
       <c r="S252" s="14" t="n">
@@ -15222,23 +15228,23 @@
       <c r="U252" s="14" t="inlineStr"/>
       <c r="V252" s="14" t="inlineStr"/>
       <c r="W252" s="14" t="n">
-        <v>0.0</v>
+        <v>2.11521335E8</v>
       </c>
       <c r="X252" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y252" s="14" t="inlineStr"/>
       <c r="Z252" s="14" t="n">
-        <v>0.0</v>
+        <v>2.11521335E8</v>
       </c>
       <c r="AA252" s="14" t="inlineStr"/>
       <c r="AB252" s="14" t="inlineStr"/>
       <c r="AC252" s="15" t="n">
-        <v>0.0</v>
+        <v>0.6409737424242424</v>
       </c>
       <c r="AD252" s="15" t="inlineStr"/>
       <c r="AE252" s="14" t="n">
-        <v>9500000.0</v>
+        <v>1.18478665E8</v>
       </c>
       <c r="AF252" s="14" t="inlineStr"/>
       <c r="AG252" s="14" t="inlineStr"/>
@@ -15253,29 +15259,23 @@
       <c r="E253" s="2" t="inlineStr"/>
       <c r="F253" s="2" t="inlineStr"/>
       <c r="G253" s="2" t="inlineStr"/>
-      <c r="H253" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">523121</t>
-          </r>
-        </is>
-      </c>
-      <c r="I253" s="13" t="inlineStr"/>
-      <c r="J253" s="13" t="inlineStr"/>
-      <c r="K253" s="13" t="inlineStr"/>
-      <c r="L253" s="13" t="inlineStr"/>
-      <c r="M253" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Pemeliharaan Peralatan dan Mesin</t>
-          </r>
-        </is>
-      </c>
-      <c r="N253" s="13" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr"/>
+      <c r="I253" s="2" t="inlineStr"/>
+      <c r="J253" s="2" t="inlineStr"/>
+      <c r="K253" s="2" t="inlineStr"/>
+      <c r="L253" s="2" t="inlineStr"/>
+      <c r="M253" s="2" t="inlineStr"/>
+      <c r="N253" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000175. Pemeliharaan AC Split</t>
+          </r>
+        </is>
+      </c>
       <c r="O253" s="13" t="inlineStr"/>
       <c r="P253" s="13" t="inlineStr"/>
       <c r="Q253" s="14" t="n">
-        <v>2.2996E8</v>
+        <v>2.257E7</v>
       </c>
       <c r="R253" s="14" t="inlineStr"/>
       <c r="S253" s="14" t="n">
@@ -15285,23 +15285,23 @@
       <c r="U253" s="14" t="inlineStr"/>
       <c r="V253" s="14" t="inlineStr"/>
       <c r="W253" s="14" t="n">
-        <v>1.58031069E8</v>
+        <v>1.396E7</v>
       </c>
       <c r="X253" s="14" t="n">
-        <v>4.8093812E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y253" s="14" t="inlineStr"/>
       <c r="Z253" s="14" t="n">
-        <v>2.06124881E8</v>
+        <v>1.396E7</v>
       </c>
       <c r="AA253" s="14" t="inlineStr"/>
       <c r="AB253" s="14" t="inlineStr"/>
       <c r="AC253" s="15" t="n">
-        <v>0.8963510219168551</v>
+        <v>0.618520159503766</v>
       </c>
       <c r="AD253" s="15" t="inlineStr"/>
       <c r="AE253" s="14" t="n">
-        <v>2.3835119E7</v>
+        <v>8610000.0</v>
       </c>
       <c r="AF253" s="14" t="inlineStr"/>
       <c r="AG253" s="14" t="inlineStr"/>
@@ -15368,14 +15368,14 @@
       <c r="N255" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000175. Pemeliharaan AC Split</t>
+            <t xml:space="preserve">000176. Pemeliharaan Laptop</t>
           </r>
         </is>
       </c>
       <c r="O255" s="13" t="inlineStr"/>
       <c r="P255" s="13" t="inlineStr"/>
       <c r="Q255" s="14" t="n">
-        <v>1.43E7</v>
+        <v>5000000.0</v>
       </c>
       <c r="R255" s="14" t="inlineStr"/>
       <c r="S255" s="14" t="n">
@@ -15385,23 +15385,23 @@
       <c r="U255" s="14" t="inlineStr"/>
       <c r="V255" s="14" t="inlineStr"/>
       <c r="W255" s="14" t="n">
-        <v>1.396E7</v>
+        <v>2487928.0</v>
       </c>
       <c r="X255" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y255" s="14" t="inlineStr"/>
       <c r="Z255" s="14" t="n">
-        <v>1.396E7</v>
+        <v>2487928.0</v>
       </c>
       <c r="AA255" s="14" t="inlineStr"/>
       <c r="AB255" s="14" t="inlineStr"/>
       <c r="AC255" s="15" t="n">
-        <v>0.9762237762237762</v>
+        <v>0.4975856</v>
       </c>
       <c r="AD255" s="15" t="inlineStr"/>
       <c r="AE255" s="14" t="n">
-        <v>340000.0</v>
+        <v>2512072.0</v>
       </c>
       <c r="AF255" s="14" t="inlineStr"/>
       <c r="AG255" s="14" t="inlineStr"/>
@@ -15425,14 +15425,14 @@
       <c r="N256" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000176. Pemeliharaan Laptop</t>
+            <t xml:space="preserve">000182. Pemeliharaan Instalasi Listrik</t>
           </r>
         </is>
       </c>
       <c r="O256" s="13" t="inlineStr"/>
       <c r="P256" s="13" t="inlineStr"/>
       <c r="Q256" s="14" t="n">
-        <v>5000000.0</v>
+        <v>4.5E7</v>
       </c>
       <c r="R256" s="14" t="inlineStr"/>
       <c r="S256" s="14" t="n">
@@ -15442,23 +15442,23 @@
       <c r="U256" s="14" t="inlineStr"/>
       <c r="V256" s="14" t="inlineStr"/>
       <c r="W256" s="14" t="n">
-        <v>350000.0</v>
+        <v>2.9845218E7</v>
       </c>
       <c r="X256" s="14" t="n">
-        <v>937928.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y256" s="14" t="inlineStr"/>
       <c r="Z256" s="14" t="n">
-        <v>1287928.0</v>
+        <v>2.9845218E7</v>
       </c>
       <c r="AA256" s="14" t="inlineStr"/>
       <c r="AB256" s="14" t="inlineStr"/>
       <c r="AC256" s="15" t="n">
-        <v>0.2575856</v>
+        <v>0.6632270666666666</v>
       </c>
       <c r="AD256" s="15" t="inlineStr"/>
       <c r="AE256" s="14" t="n">
-        <v>3712072.0</v>
+        <v>1.5154782E7</v>
       </c>
       <c r="AF256" s="14" t="inlineStr"/>
       <c r="AG256" s="14" t="inlineStr"/>
@@ -15482,14 +15482,14 @@
       <c r="N257" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000182. Pemeliharaan Instalasi Listrik</t>
+            <t xml:space="preserve">000183. Pemeliharaan Kendaraan Roda 4</t>
           </r>
         </is>
       </c>
       <c r="O257" s="13" t="inlineStr"/>
       <c r="P257" s="13" t="inlineStr"/>
       <c r="Q257" s="14" t="n">
-        <v>3.0E7</v>
+        <v>1.6975E8</v>
       </c>
       <c r="R257" s="14" t="inlineStr"/>
       <c r="S257" s="14" t="n">
@@ -15499,23 +15499,23 @@
       <c r="U257" s="14" t="inlineStr"/>
       <c r="V257" s="14" t="inlineStr"/>
       <c r="W257" s="14" t="n">
-        <v>2.7531718E7</v>
+        <v>1.22043496E8</v>
       </c>
       <c r="X257" s="14" t="n">
-        <v>509000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y257" s="14" t="inlineStr"/>
       <c r="Z257" s="14" t="n">
-        <v>2.8040718E7</v>
+        <v>1.22043496E8</v>
       </c>
       <c r="AA257" s="14" t="inlineStr"/>
       <c r="AB257" s="14" t="inlineStr"/>
       <c r="AC257" s="15" t="n">
-        <v>0.9346906</v>
+        <v>0.7189602120765832</v>
       </c>
       <c r="AD257" s="15" t="inlineStr"/>
       <c r="AE257" s="14" t="n">
-        <v>1959282.0</v>
+        <v>4.7706504E7</v>
       </c>
       <c r="AF257" s="14" t="inlineStr"/>
       <c r="AG257" s="14" t="inlineStr"/>
@@ -15539,14 +15539,14 @@
       <c r="N258" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000183. Pemeliharaan Kendaraan Roda 4</t>
+            <t xml:space="preserve">000184. Pemeliharaan Kendaraan Roda 2</t>
           </r>
         </is>
       </c>
       <c r="O258" s="13" t="inlineStr"/>
       <c r="P258" s="13" t="inlineStr"/>
       <c r="Q258" s="14" t="n">
-        <v>1.246E8</v>
+        <v>4500000.0</v>
       </c>
       <c r="R258" s="14" t="inlineStr"/>
       <c r="S258" s="14" t="n">
@@ -15556,23 +15556,23 @@
       <c r="U258" s="14" t="inlineStr"/>
       <c r="V258" s="14" t="inlineStr"/>
       <c r="W258" s="14" t="n">
-        <v>9.4757877E7</v>
+        <v>4147992.0</v>
       </c>
       <c r="X258" s="14" t="n">
-        <v>2.6080619E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y258" s="14" t="inlineStr"/>
       <c r="Z258" s="14" t="n">
-        <v>1.20838496E8</v>
+        <v>4147992.0</v>
       </c>
       <c r="AA258" s="14" t="inlineStr"/>
       <c r="AB258" s="14" t="inlineStr"/>
       <c r="AC258" s="15" t="n">
-        <v>0.9698113643659712</v>
+        <v>0.921776</v>
       </c>
       <c r="AD258" s="15" t="inlineStr"/>
       <c r="AE258" s="14" t="n">
-        <v>3761504.0</v>
+        <v>352008.0</v>
       </c>
       <c r="AF258" s="14" t="inlineStr"/>
       <c r="AG258" s="14" t="inlineStr"/>
@@ -15596,14 +15596,14 @@
       <c r="N259" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000184. Pemeliharaan Kendaraan Roda 2</t>
+            <t xml:space="preserve">000185. Pemeliharaan CCTV</t>
           </r>
         </is>
       </c>
       <c r="O259" s="13" t="inlineStr"/>
       <c r="P259" s="13" t="inlineStr"/>
       <c r="Q259" s="14" t="n">
-        <v>4500000.0</v>
+        <v>2.1E7</v>
       </c>
       <c r="R259" s="14" t="inlineStr"/>
       <c r="S259" s="14" t="n">
@@ -15613,23 +15613,23 @@
       <c r="U259" s="14" t="inlineStr"/>
       <c r="V259" s="14" t="inlineStr"/>
       <c r="W259" s="14" t="n">
-        <v>3229902.0</v>
+        <v>1.4290555E7</v>
       </c>
       <c r="X259" s="14" t="n">
-        <v>182090.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y259" s="14" t="inlineStr"/>
       <c r="Z259" s="14" t="n">
-        <v>3411992.0</v>
+        <v>1.4290555E7</v>
       </c>
       <c r="AA259" s="14" t="inlineStr"/>
       <c r="AB259" s="14" t="inlineStr"/>
       <c r="AC259" s="15" t="n">
-        <v>0.7582204444444445</v>
+        <v>0.680502619047619</v>
       </c>
       <c r="AD259" s="15" t="inlineStr"/>
       <c r="AE259" s="14" t="n">
-        <v>1088008.0</v>
+        <v>6709445.0</v>
       </c>
       <c r="AF259" s="14" t="inlineStr"/>
       <c r="AG259" s="14" t="inlineStr"/>
@@ -15653,14 +15653,14 @@
       <c r="N260" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000185. Pemeliharaan CCTV</t>
+            <t xml:space="preserve">000186. Pemeliharaan Genset 250 KVA</t>
           </r>
         </is>
       </c>
       <c r="O260" s="13" t="inlineStr"/>
       <c r="P260" s="13" t="inlineStr"/>
       <c r="Q260" s="14" t="n">
-        <v>1.45E7</v>
+        <v>9010000.0</v>
       </c>
       <c r="R260" s="14" t="inlineStr"/>
       <c r="S260" s="14" t="n">
@@ -15670,23 +15670,23 @@
       <c r="U260" s="14" t="inlineStr"/>
       <c r="V260" s="14" t="inlineStr"/>
       <c r="W260" s="14" t="n">
-        <v>4737535.0</v>
+        <v>1000052.0</v>
       </c>
       <c r="X260" s="14" t="n">
-        <v>9553020.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y260" s="14" t="inlineStr"/>
       <c r="Z260" s="14" t="n">
-        <v>1.4290555E7</v>
+        <v>1000052.0</v>
       </c>
       <c r="AA260" s="14" t="inlineStr"/>
       <c r="AB260" s="14" t="inlineStr"/>
       <c r="AC260" s="15" t="n">
-        <v>0.9855555172413794</v>
+        <v>0.11099356270810211</v>
       </c>
       <c r="AD260" s="15" t="inlineStr"/>
       <c r="AE260" s="14" t="n">
-        <v>209445.0</v>
+        <v>8009948.0</v>
       </c>
       <c r="AF260" s="14" t="inlineStr"/>
       <c r="AG260" s="14" t="inlineStr"/>
@@ -15710,14 +15710,14 @@
       <c r="N261" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000186. Pemeliharaan Genset 250 KVA</t>
+            <t xml:space="preserve">000187. Pemeliharaan Genset 40 KVA</t>
           </r>
         </is>
       </c>
       <c r="O261" s="13" t="inlineStr"/>
       <c r="P261" s="13" t="inlineStr"/>
       <c r="Q261" s="14" t="n">
-        <v>6010000.0</v>
+        <v>4050000.0</v>
       </c>
       <c r="R261" s="14" t="inlineStr"/>
       <c r="S261" s="14" t="n">
@@ -15727,23 +15727,23 @@
       <c r="U261" s="14" t="inlineStr"/>
       <c r="V261" s="14" t="inlineStr"/>
       <c r="W261" s="14" t="n">
-        <v>1000052.0</v>
+        <v>1978406.0</v>
       </c>
       <c r="X261" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y261" s="14" t="inlineStr"/>
       <c r="Z261" s="14" t="n">
-        <v>1000052.0</v>
+        <v>1978406.0</v>
       </c>
       <c r="AA261" s="14" t="inlineStr"/>
       <c r="AB261" s="14" t="inlineStr"/>
       <c r="AC261" s="15" t="n">
-        <v>0.166398003327787</v>
+        <v>0.4884953086419753</v>
       </c>
       <c r="AD261" s="15" t="inlineStr"/>
       <c r="AE261" s="14" t="n">
-        <v>5009948.0</v>
+        <v>2071594.0</v>
       </c>
       <c r="AF261" s="14" t="inlineStr"/>
       <c r="AG261" s="14" t="inlineStr"/>
@@ -15767,14 +15767,14 @@
       <c r="N262" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000187. Pemeliharaan Genset 40 KVA</t>
+            <t xml:space="preserve">000190. Pemeliharaan Mesin Potong Rumput</t>
           </r>
         </is>
       </c>
       <c r="O262" s="13" t="inlineStr"/>
       <c r="P262" s="13" t="inlineStr"/>
       <c r="Q262" s="14" t="n">
-        <v>4050000.0</v>
+        <v>1.2E7</v>
       </c>
       <c r="R262" s="14" t="inlineStr"/>
       <c r="S262" s="14" t="n">
@@ -15784,23 +15784,23 @@
       <c r="U262" s="14" t="inlineStr"/>
       <c r="V262" s="14" t="inlineStr"/>
       <c r="W262" s="14" t="n">
-        <v>1358480.0</v>
+        <v>8450284.0</v>
       </c>
       <c r="X262" s="14" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y262" s="14" t="inlineStr"/>
       <c r="Z262" s="14" t="n">
-        <v>1658480.0</v>
+        <v>8450284.0</v>
       </c>
       <c r="AA262" s="14" t="inlineStr"/>
       <c r="AB262" s="14" t="inlineStr"/>
       <c r="AC262" s="15" t="n">
-        <v>0.4095012345679012</v>
+        <v>0.7041903333333334</v>
       </c>
       <c r="AD262" s="15" t="inlineStr"/>
       <c r="AE262" s="14" t="n">
-        <v>2391520.0</v>
+        <v>3549716.0</v>
       </c>
       <c r="AF262" s="14" t="inlineStr"/>
       <c r="AG262" s="14" t="inlineStr"/>
@@ -15824,14 +15824,14 @@
       <c r="N263" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000190. Pemeliharaan Mesin Potong Rumput</t>
+            <t xml:space="preserve">000191. Pemeliharaan Printer</t>
           </r>
         </is>
       </c>
       <c r="O263" s="13" t="inlineStr"/>
       <c r="P263" s="13" t="inlineStr"/>
       <c r="Q263" s="14" t="n">
-        <v>1.0E7</v>
+        <v>1500000.0</v>
       </c>
       <c r="R263" s="14" t="inlineStr"/>
       <c r="S263" s="14" t="n">
@@ -15841,23 +15841,23 @@
       <c r="U263" s="14" t="inlineStr"/>
       <c r="V263" s="14" t="inlineStr"/>
       <c r="W263" s="14" t="n">
-        <v>8224613.0</v>
+        <v>1167558.0</v>
       </c>
       <c r="X263" s="14" t="n">
-        <v>94643.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y263" s="14" t="inlineStr"/>
       <c r="Z263" s="14" t="n">
-        <v>8319256.0</v>
+        <v>1167558.0</v>
       </c>
       <c r="AA263" s="14" t="inlineStr"/>
       <c r="AB263" s="14" t="inlineStr"/>
       <c r="AC263" s="15" t="n">
-        <v>0.8319256</v>
+        <v>0.778372</v>
       </c>
       <c r="AD263" s="15" t="inlineStr"/>
       <c r="AE263" s="14" t="n">
-        <v>1680744.0</v>
+        <v>332442.0</v>
       </c>
       <c r="AF263" s="14" t="inlineStr"/>
       <c r="AG263" s="14" t="inlineStr"/>
@@ -15881,14 +15881,14 @@
       <c r="N264" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000191. Pemeliharaan Printer</t>
+            <t xml:space="preserve">000192. Pemeliharaan Komputer/PC</t>
           </r>
         </is>
       </c>
       <c r="O264" s="13" t="inlineStr"/>
       <c r="P264" s="13" t="inlineStr"/>
       <c r="Q264" s="14" t="n">
-        <v>1500000.0</v>
+        <v>1.562E7</v>
       </c>
       <c r="R264" s="14" t="inlineStr"/>
       <c r="S264" s="14" t="n">
@@ -15898,23 +15898,23 @@
       <c r="U264" s="14" t="inlineStr"/>
       <c r="V264" s="14" t="inlineStr"/>
       <c r="W264" s="14" t="n">
-        <v>1167558.0</v>
+        <v>3760846.0</v>
       </c>
       <c r="X264" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y264" s="14" t="inlineStr"/>
       <c r="Z264" s="14" t="n">
-        <v>1167558.0</v>
+        <v>3760846.0</v>
       </c>
       <c r="AA264" s="14" t="inlineStr"/>
       <c r="AB264" s="14" t="inlineStr"/>
       <c r="AC264" s="15" t="n">
-        <v>0.778372</v>
+        <v>0.24077119078104994</v>
       </c>
       <c r="AD264" s="15" t="inlineStr"/>
       <c r="AE264" s="14" t="n">
-        <v>332442.0</v>
+        <v>1.1859154E7</v>
       </c>
       <c r="AF264" s="14" t="inlineStr"/>
       <c r="AG264" s="14" t="inlineStr"/>
@@ -15938,14 +15938,14 @@
       <c r="N265" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000192. Pemeliharaan Komputer/PC</t>
+            <t xml:space="preserve">000283. Pemeliharaan Kulkas</t>
           </r>
         </is>
       </c>
       <c r="O265" s="13" t="inlineStr"/>
       <c r="P265" s="13" t="inlineStr"/>
       <c r="Q265" s="14" t="n">
-        <v>5000000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="R265" s="14" t="inlineStr"/>
       <c r="S265" s="14" t="n">
@@ -15955,23 +15955,23 @@
       <c r="U265" s="14" t="inlineStr"/>
       <c r="V265" s="14" t="inlineStr"/>
       <c r="W265" s="14" t="n">
-        <v>1213334.0</v>
+        <v>500000.0</v>
       </c>
       <c r="X265" s="14" t="n">
-        <v>2547512.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y265" s="14" t="inlineStr"/>
       <c r="Z265" s="14" t="n">
-        <v>3760846.0</v>
+        <v>500000.0</v>
       </c>
       <c r="AA265" s="14" t="inlineStr"/>
       <c r="AB265" s="14" t="inlineStr"/>
       <c r="AC265" s="15" t="n">
-        <v>0.7521692</v>
+        <v>1.0</v>
       </c>
       <c r="AD265" s="15" t="inlineStr"/>
       <c r="AE265" s="14" t="n">
-        <v>1239154.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF265" s="14" t="inlineStr"/>
       <c r="AG265" s="14" t="inlineStr"/>
@@ -15995,14 +15995,14 @@
       <c r="N266" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000283. Pemeliharaan Kulkas</t>
+            <t xml:space="preserve">000299. Pemeliharaan Instalasi Air</t>
           </r>
         </is>
       </c>
       <c r="O266" s="13" t="inlineStr"/>
       <c r="P266" s="13" t="inlineStr"/>
       <c r="Q266" s="14" t="n">
-        <v>500000.0</v>
+        <v>1.3E7</v>
       </c>
       <c r="R266" s="14" t="inlineStr"/>
       <c r="S266" s="14" t="n">
@@ -16012,23 +16012,23 @@
       <c r="U266" s="14" t="inlineStr"/>
       <c r="V266" s="14" t="inlineStr"/>
       <c r="W266" s="14" t="n">
-        <v>500000.0</v>
+        <v>7889000.0</v>
       </c>
       <c r="X266" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y266" s="14" t="inlineStr"/>
       <c r="Z266" s="14" t="n">
-        <v>500000.0</v>
+        <v>7889000.0</v>
       </c>
       <c r="AA266" s="14" t="inlineStr"/>
       <c r="AB266" s="14" t="inlineStr"/>
       <c r="AC266" s="15" t="n">
-        <v>1.0</v>
+        <v>0.6068461538461538</v>
       </c>
       <c r="AD266" s="15" t="inlineStr"/>
       <c r="AE266" s="14" t="n">
-        <v>0.0</v>
+        <v>5111000.0</v>
       </c>
       <c r="AF266" s="14" t="inlineStr"/>
       <c r="AG266" s="14" t="inlineStr"/>
@@ -16052,14 +16052,14 @@
       <c r="N267" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000299. Pemeliharaan Instalasi Air</t>
+            <t xml:space="preserve">000304. Pemeliharaan Alat Laboratorium</t>
           </r>
         </is>
       </c>
       <c r="O267" s="13" t="inlineStr"/>
       <c r="P267" s="13" t="inlineStr"/>
       <c r="Q267" s="14" t="n">
-        <v>1.0E7</v>
+        <v>5000000.0</v>
       </c>
       <c r="R267" s="14" t="inlineStr"/>
       <c r="S267" s="14" t="n">
@@ -16072,20 +16072,20 @@
         <v>0.0</v>
       </c>
       <c r="X267" s="14" t="n">
-        <v>7889000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y267" s="14" t="inlineStr"/>
       <c r="Z267" s="14" t="n">
-        <v>7889000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA267" s="14" t="inlineStr"/>
       <c r="AB267" s="14" t="inlineStr"/>
       <c r="AC267" s="15" t="n">
-        <v>0.7889</v>
+        <v>0.0</v>
       </c>
       <c r="AD267" s="15" t="inlineStr"/>
       <c r="AE267" s="14" t="n">
-        <v>2111000.0</v>
+        <v>5000000.0</v>
       </c>
       <c r="AF267" s="14" t="inlineStr"/>
       <c r="AG267" s="14" t="inlineStr"/>
@@ -16100,29 +16100,23 @@
       <c r="E268" s="2" t="inlineStr"/>
       <c r="F268" s="2" t="inlineStr"/>
       <c r="G268" s="2" t="inlineStr"/>
-      <c r="H268" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">523132</t>
-          </r>
-        </is>
-      </c>
-      <c r="I268" s="13" t="inlineStr"/>
-      <c r="J268" s="13" t="inlineStr"/>
-      <c r="K268" s="13" t="inlineStr"/>
-      <c r="L268" s="13" t="inlineStr"/>
-      <c r="M268" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Pemeliharaan Irigasi</t>
-          </r>
-        </is>
-      </c>
-      <c r="N268" s="13" t="inlineStr"/>
+      <c r="H268" s="2" t="inlineStr"/>
+      <c r="I268" s="2" t="inlineStr"/>
+      <c r="J268" s="2" t="inlineStr"/>
+      <c r="K268" s="2" t="inlineStr"/>
+      <c r="L268" s="2" t="inlineStr"/>
+      <c r="M268" s="2" t="inlineStr"/>
+      <c r="N268" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000305. Pemeliharaan TV</t>
+          </r>
+        </is>
+      </c>
       <c r="O268" s="13" t="inlineStr"/>
       <c r="P268" s="13" t="inlineStr"/>
       <c r="Q268" s="14" t="n">
-        <v>8.11E7</v>
+        <v>1500000.0</v>
       </c>
       <c r="R268" s="14" t="inlineStr"/>
       <c r="S268" s="14" t="n">
@@ -16132,23 +16126,23 @@
       <c r="U268" s="14" t="inlineStr"/>
       <c r="V268" s="14" t="inlineStr"/>
       <c r="W268" s="14" t="n">
-        <v>6.1416E7</v>
+        <v>0.0</v>
       </c>
       <c r="X268" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y268" s="14" t="inlineStr"/>
       <c r="Z268" s="14" t="n">
-        <v>6.1416E7</v>
+        <v>0.0</v>
       </c>
       <c r="AA268" s="14" t="inlineStr"/>
       <c r="AB268" s="14" t="inlineStr"/>
       <c r="AC268" s="15" t="n">
-        <v>0.7572872996300863</v>
+        <v>0.0</v>
       </c>
       <c r="AD268" s="15" t="inlineStr"/>
       <c r="AE268" s="14" t="n">
-        <v>1.9684E7</v>
+        <v>1500000.0</v>
       </c>
       <c r="AF268" s="14" t="inlineStr"/>
       <c r="AG268" s="14" t="inlineStr"/>
@@ -16163,23 +16157,29 @@
       <c r="E269" s="2" t="inlineStr"/>
       <c r="F269" s="2" t="inlineStr"/>
       <c r="G269" s="2" t="inlineStr"/>
-      <c r="H269" s="2" t="inlineStr"/>
-      <c r="I269" s="2" t="inlineStr"/>
-      <c r="J269" s="2" t="inlineStr"/>
-      <c r="K269" s="2" t="inlineStr"/>
-      <c r="L269" s="2" t="inlineStr"/>
-      <c r="M269" s="2" t="inlineStr"/>
-      <c r="N269" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000195. Pemeliharaan Talud Cijeruk</t>
-          </r>
-        </is>
-      </c>
+      <c r="H269" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">523132</t>
+          </r>
+        </is>
+      </c>
+      <c r="I269" s="13" t="inlineStr"/>
+      <c r="J269" s="13" t="inlineStr"/>
+      <c r="K269" s="13" t="inlineStr"/>
+      <c r="L269" s="13" t="inlineStr"/>
+      <c r="M269" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Pemeliharaan Irigasi</t>
+          </r>
+        </is>
+      </c>
+      <c r="N269" s="13" t="inlineStr"/>
       <c r="O269" s="13" t="inlineStr"/>
       <c r="P269" s="13" t="inlineStr"/>
       <c r="Q269" s="14" t="n">
-        <v>3.91E7</v>
+        <v>1.5292E8</v>
       </c>
       <c r="R269" s="14" t="inlineStr"/>
       <c r="S269" s="14" t="n">
@@ -16189,23 +16189,23 @@
       <c r="U269" s="14" t="inlineStr"/>
       <c r="V269" s="14" t="inlineStr"/>
       <c r="W269" s="14" t="n">
-        <v>3.909E7</v>
+        <v>8.0551E7</v>
       </c>
       <c r="X269" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y269" s="14" t="inlineStr"/>
       <c r="Z269" s="14" t="n">
-        <v>3.909E7</v>
+        <v>8.0551E7</v>
       </c>
       <c r="AA269" s="14" t="inlineStr"/>
       <c r="AB269" s="14" t="inlineStr"/>
       <c r="AC269" s="15" t="n">
-        <v>0.9997442455242966</v>
+        <v>0.5267525503531258</v>
       </c>
       <c r="AD269" s="15" t="inlineStr"/>
       <c r="AE269" s="14" t="n">
-        <v>10000.0</v>
+        <v>7.2369E7</v>
       </c>
       <c r="AF269" s="14" t="inlineStr"/>
       <c r="AG269" s="14" t="inlineStr"/>
@@ -16229,14 +16229,14 @@
       <c r="N270" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000284. Pemeliharaan Talud Cibalagung</t>
+            <t xml:space="preserve">000195. Pemeliharaan Talud Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O270" s="13" t="inlineStr"/>
       <c r="P270" s="13" t="inlineStr"/>
       <c r="Q270" s="14" t="n">
-        <v>3.0E7</v>
+        <v>6.216E7</v>
       </c>
       <c r="R270" s="14" t="inlineStr"/>
       <c r="S270" s="14" t="n">
@@ -16246,23 +16246,23 @@
       <c r="U270" s="14" t="inlineStr"/>
       <c r="V270" s="14" t="inlineStr"/>
       <c r="W270" s="14" t="n">
-        <v>1.155E7</v>
+        <v>3.909E7</v>
       </c>
       <c r="X270" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y270" s="14" t="inlineStr"/>
       <c r="Z270" s="14" t="n">
-        <v>1.155E7</v>
+        <v>3.909E7</v>
       </c>
       <c r="AA270" s="14" t="inlineStr"/>
       <c r="AB270" s="14" t="inlineStr"/>
       <c r="AC270" s="15" t="n">
-        <v>0.385</v>
+        <v>0.6288610038610039</v>
       </c>
       <c r="AD270" s="15" t="inlineStr"/>
       <c r="AE270" s="14" t="n">
-        <v>1.845E7</v>
+        <v>2.307E7</v>
       </c>
       <c r="AF270" s="14" t="inlineStr"/>
       <c r="AG270" s="14" t="inlineStr"/>
@@ -16286,14 +16286,14 @@
       <c r="N271" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000285. Pemeliharaan Saluran Air Cijeruk</t>
+            <t xml:space="preserve">000284. Pemeliharaan Talud Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O271" s="13" t="inlineStr"/>
       <c r="P271" s="13" t="inlineStr"/>
       <c r="Q271" s="14" t="n">
-        <v>1.2E7</v>
+        <v>3.07E7</v>
       </c>
       <c r="R271" s="14" t="inlineStr"/>
       <c r="S271" s="14" t="n">
@@ -16303,23 +16303,23 @@
       <c r="U271" s="14" t="inlineStr"/>
       <c r="V271" s="14" t="inlineStr"/>
       <c r="W271" s="14" t="n">
-        <v>1.0776E7</v>
+        <v>3.0685E7</v>
       </c>
       <c r="X271" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y271" s="14" t="inlineStr"/>
       <c r="Z271" s="14" t="n">
-        <v>1.0776E7</v>
+        <v>3.0685E7</v>
       </c>
       <c r="AA271" s="14" t="inlineStr"/>
       <c r="AB271" s="14" t="inlineStr"/>
       <c r="AC271" s="15" t="n">
-        <v>0.898</v>
+        <v>0.9995114006514658</v>
       </c>
       <c r="AD271" s="15" t="inlineStr"/>
       <c r="AE271" s="14" t="n">
-        <v>1224000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="AF271" s="14" t="inlineStr"/>
       <c r="AG271" s="14" t="inlineStr"/>
@@ -16332,31 +16332,25 @@
       <c r="C272" s="2" t="inlineStr"/>
       <c r="D272" s="2" t="inlineStr"/>
       <c r="E272" s="2" t="inlineStr"/>
-      <c r="F272" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">002.DD</t>
-          </r>
-        </is>
-      </c>
-      <c r="G272" s="13" t="inlineStr"/>
-      <c r="H272" s="13" t="inlineStr"/>
-      <c r="I272" s="13" t="inlineStr"/>
-      <c r="J272" s="13" t="inlineStr"/>
-      <c r="K272" s="13" t="inlineStr"/>
-      <c r="L272" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pembayaran Terkait Pelaksanaan Operasional Kantor</t>
-          </r>
-        </is>
-      </c>
-      <c r="M272" s="13" t="inlineStr"/>
-      <c r="N272" s="13" t="inlineStr"/>
+      <c r="F272" s="2" t="inlineStr"/>
+      <c r="G272" s="2" t="inlineStr"/>
+      <c r="H272" s="2" t="inlineStr"/>
+      <c r="I272" s="2" t="inlineStr"/>
+      <c r="J272" s="2" t="inlineStr"/>
+      <c r="K272" s="2" t="inlineStr"/>
+      <c r="L272" s="2" t="inlineStr"/>
+      <c r="M272" s="2" t="inlineStr"/>
+      <c r="N272" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000285. Pemeliharaan Saluran Air Cijeruk</t>
+          </r>
+        </is>
+      </c>
       <c r="O272" s="13" t="inlineStr"/>
       <c r="P272" s="13" t="inlineStr"/>
       <c r="Q272" s="14" t="n">
-        <v>1.3218E8</v>
+        <v>6.006E7</v>
       </c>
       <c r="R272" s="14" t="inlineStr"/>
       <c r="S272" s="14" t="n">
@@ -16366,23 +16360,23 @@
       <c r="U272" s="14" t="inlineStr"/>
       <c r="V272" s="14" t="inlineStr"/>
       <c r="W272" s="14" t="n">
-        <v>1.1092E8</v>
+        <v>1.0776E7</v>
       </c>
       <c r="X272" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y272" s="14" t="inlineStr"/>
       <c r="Z272" s="14" t="n">
-        <v>1.1092E8</v>
+        <v>1.0776E7</v>
       </c>
       <c r="AA272" s="14" t="inlineStr"/>
       <c r="AB272" s="14" t="inlineStr"/>
       <c r="AC272" s="15" t="n">
-        <v>0.8391587229535482</v>
+        <v>0.17942057942057943</v>
       </c>
       <c r="AD272" s="15" t="inlineStr"/>
       <c r="AE272" s="14" t="n">
-        <v>2.126E7</v>
+        <v>4.9284E7</v>
       </c>
       <c r="AF272" s="14" t="inlineStr"/>
       <c r="AG272" s="14" t="inlineStr"/>
@@ -16395,31 +16389,31 @@
       <c r="C273" s="2" t="inlineStr"/>
       <c r="D273" s="2" t="inlineStr"/>
       <c r="E273" s="2" t="inlineStr"/>
-      <c r="F273" s="2" t="inlineStr"/>
-      <c r="G273" s="2" t="inlineStr"/>
-      <c r="H273" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521115</t>
-          </r>
-        </is>
-      </c>
+      <c r="F273" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">002.DD</t>
+          </r>
+        </is>
+      </c>
+      <c r="G273" s="13" t="inlineStr"/>
+      <c r="H273" s="13" t="inlineStr"/>
       <c r="I273" s="13" t="inlineStr"/>
       <c r="J273" s="13" t="inlineStr"/>
       <c r="K273" s="13" t="inlineStr"/>
-      <c r="L273" s="13" t="inlineStr"/>
-      <c r="M273" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Honor Operasional Satuan Kerja</t>
-          </r>
-        </is>
-      </c>
+      <c r="L273" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pembayaran Terkait Pelaksanaan Operasional Kantor</t>
+          </r>
+        </is>
+      </c>
+      <c r="M273" s="13" t="inlineStr"/>
       <c r="N273" s="13" t="inlineStr"/>
       <c r="O273" s="13" t="inlineStr"/>
       <c r="P273" s="13" t="inlineStr"/>
       <c r="Q273" s="14" t="n">
-        <v>1.2468E8</v>
+        <v>1.3218E8</v>
       </c>
       <c r="R273" s="14" t="inlineStr"/>
       <c r="S273" s="14" t="n">
@@ -16429,23 +16423,23 @@
       <c r="U273" s="14" t="inlineStr"/>
       <c r="V273" s="14" t="inlineStr"/>
       <c r="W273" s="14" t="n">
-        <v>1.0342E8</v>
+        <v>1.3074E8</v>
       </c>
       <c r="X273" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y273" s="14" t="inlineStr"/>
       <c r="Z273" s="14" t="n">
-        <v>1.0342E8</v>
+        <v>1.3074E8</v>
       </c>
       <c r="AA273" s="14" t="inlineStr"/>
       <c r="AB273" s="14" t="inlineStr"/>
       <c r="AC273" s="15" t="n">
-        <v>0.8294834777029195</v>
+        <v>0.9891057648660917</v>
       </c>
       <c r="AD273" s="15" t="inlineStr"/>
       <c r="AE273" s="14" t="n">
-        <v>2.126E7</v>
+        <v>1440000.0</v>
       </c>
       <c r="AF273" s="14" t="inlineStr"/>
       <c r="AG273" s="14" t="inlineStr"/>
@@ -16460,23 +16454,29 @@
       <c r="E274" s="2" t="inlineStr"/>
       <c r="F274" s="2" t="inlineStr"/>
       <c r="G274" s="2" t="inlineStr"/>
-      <c r="H274" s="2" t="inlineStr"/>
-      <c r="I274" s="2" t="inlineStr"/>
-      <c r="J274" s="2" t="inlineStr"/>
-      <c r="K274" s="2" t="inlineStr"/>
-      <c r="L274" s="2" t="inlineStr"/>
-      <c r="M274" s="2" t="inlineStr"/>
-      <c r="N274" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000197. Honorarium Pejabat Kuasa Pengguna Anggaran</t>
-          </r>
-        </is>
-      </c>
+      <c r="H274" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521115</t>
+          </r>
+        </is>
+      </c>
+      <c r="I274" s="13" t="inlineStr"/>
+      <c r="J274" s="13" t="inlineStr"/>
+      <c r="K274" s="13" t="inlineStr"/>
+      <c r="L274" s="13" t="inlineStr"/>
+      <c r="M274" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Honor Operasional Satuan Kerja</t>
+          </r>
+        </is>
+      </c>
+      <c r="N274" s="13" t="inlineStr"/>
       <c r="O274" s="13" t="inlineStr"/>
       <c r="P274" s="13" t="inlineStr"/>
       <c r="Q274" s="14" t="n">
-        <v>3.06E7</v>
+        <v>1.2468E8</v>
       </c>
       <c r="R274" s="14" t="inlineStr"/>
       <c r="S274" s="14" t="n">
@@ -16486,23 +16486,23 @@
       <c r="U274" s="14" t="inlineStr"/>
       <c r="V274" s="14" t="inlineStr"/>
       <c r="W274" s="14" t="n">
-        <v>2.55E7</v>
+        <v>1.2324E8</v>
       </c>
       <c r="X274" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y274" s="14" t="inlineStr"/>
       <c r="Z274" s="14" t="n">
-        <v>2.55E7</v>
+        <v>1.2324E8</v>
       </c>
       <c r="AA274" s="14" t="inlineStr"/>
       <c r="AB274" s="14" t="inlineStr"/>
       <c r="AC274" s="15" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9884504331087585</v>
       </c>
       <c r="AD274" s="15" t="inlineStr"/>
       <c r="AE274" s="14" t="n">
-        <v>5100000.0</v>
+        <v>1440000.0</v>
       </c>
       <c r="AF274" s="14" t="inlineStr"/>
       <c r="AG274" s="14" t="inlineStr"/>
@@ -16526,14 +16526,14 @@
       <c r="N275" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000198. Honorarium Pejabat Pembuat Komitmen</t>
+            <t xml:space="preserve">000197. Honorarium Pejabat Kuasa Pengguna Anggaran</t>
           </r>
         </is>
       </c>
       <c r="O275" s="13" t="inlineStr"/>
       <c r="P275" s="13" t="inlineStr"/>
       <c r="Q275" s="14" t="n">
-        <v>2.976E7</v>
+        <v>3.06E7</v>
       </c>
       <c r="R275" s="14" t="inlineStr"/>
       <c r="S275" s="14" t="n">
@@ -16543,30 +16543,30 @@
       <c r="U275" s="14" t="inlineStr"/>
       <c r="V275" s="14" t="inlineStr"/>
       <c r="W275" s="14" t="n">
-        <v>2.48E7</v>
+        <v>3.06E7</v>
       </c>
       <c r="X275" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y275" s="14" t="inlineStr"/>
       <c r="Z275" s="14" t="n">
-        <v>2.48E7</v>
+        <v>3.06E7</v>
       </c>
       <c r="AA275" s="14" t="inlineStr"/>
       <c r="AB275" s="14" t="inlineStr"/>
       <c r="AC275" s="15" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.0</v>
       </c>
       <c r="AD275" s="15" t="inlineStr"/>
       <c r="AE275" s="14" t="n">
-        <v>4960000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF275" s="14" t="inlineStr"/>
       <c r="AG275" s="14" t="inlineStr"/>
       <c r="AH275" s="14" t="inlineStr"/>
       <c r="AI275" s="14" t="inlineStr"/>
     </row>
-    <row r="276" customHeight="1" ht="18">
+    <row r="276" customHeight="1" ht="15">
       <c r="A276" s="2" t="inlineStr"/>
       <c r="B276" s="2" t="inlineStr"/>
       <c r="C276" s="2" t="inlineStr"/>
@@ -16583,14 +16583,14 @@
       <c r="N276" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000199. Honorarium Pejabat  Penguji Tagihan   Penandatangan  Spm</t>
+            <t xml:space="preserve">000198. Honorarium Pejabat Pembuat Komitmen</t>
           </r>
         </is>
       </c>
       <c r="O276" s="13" t="inlineStr"/>
       <c r="P276" s="13" t="inlineStr"/>
       <c r="Q276" s="14" t="n">
-        <v>1.476E7</v>
+        <v>2.976E7</v>
       </c>
       <c r="R276" s="14" t="inlineStr"/>
       <c r="S276" s="14" t="n">
@@ -16600,30 +16600,30 @@
       <c r="U276" s="14" t="inlineStr"/>
       <c r="V276" s="14" t="inlineStr"/>
       <c r="W276" s="14" t="n">
-        <v>1.23E7</v>
+        <v>2.976E7</v>
       </c>
       <c r="X276" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y276" s="14" t="inlineStr"/>
       <c r="Z276" s="14" t="n">
-        <v>1.23E7</v>
+        <v>2.976E7</v>
       </c>
       <c r="AA276" s="14" t="inlineStr"/>
       <c r="AB276" s="14" t="inlineStr"/>
       <c r="AC276" s="15" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.0</v>
       </c>
       <c r="AD276" s="15" t="inlineStr"/>
       <c r="AE276" s="14" t="n">
-        <v>2460000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF276" s="14" t="inlineStr"/>
       <c r="AG276" s="14" t="inlineStr"/>
       <c r="AH276" s="14" t="inlineStr"/>
       <c r="AI276" s="14" t="inlineStr"/>
     </row>
-    <row r="277" customHeight="1" ht="15">
+    <row r="277" customHeight="1" ht="18">
       <c r="A277" s="2" t="inlineStr"/>
       <c r="B277" s="2" t="inlineStr"/>
       <c r="C277" s="2" t="inlineStr"/>
@@ -16640,14 +16640,14 @@
       <c r="N277" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000200. Honorarium Bendahara  Pengeluaran</t>
+            <t xml:space="preserve">000199. Honorarium Pejabat  Penguji Tagihan   Penandatangan  Spm</t>
           </r>
         </is>
       </c>
       <c r="O277" s="13" t="inlineStr"/>
       <c r="P277" s="13" t="inlineStr"/>
       <c r="Q277" s="14" t="n">
-        <v>1.284E7</v>
+        <v>1.476E7</v>
       </c>
       <c r="R277" s="14" t="inlineStr"/>
       <c r="S277" s="14" t="n">
@@ -16657,23 +16657,23 @@
       <c r="U277" s="14" t="inlineStr"/>
       <c r="V277" s="14" t="inlineStr"/>
       <c r="W277" s="14" t="n">
-        <v>1.07E7</v>
+        <v>1.476E7</v>
       </c>
       <c r="X277" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y277" s="14" t="inlineStr"/>
       <c r="Z277" s="14" t="n">
-        <v>1.07E7</v>
+        <v>1.476E7</v>
       </c>
       <c r="AA277" s="14" t="inlineStr"/>
       <c r="AB277" s="14" t="inlineStr"/>
       <c r="AC277" s="15" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.0</v>
       </c>
       <c r="AD277" s="15" t="inlineStr"/>
       <c r="AE277" s="14" t="n">
-        <v>2140000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF277" s="14" t="inlineStr"/>
       <c r="AG277" s="14" t="inlineStr"/>
@@ -16697,14 +16697,14 @@
       <c r="N278" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000201. Honorarium Staf  Pengelola</t>
+            <t xml:space="preserve">000200. Honorarium Bendahara  Pengeluaran</t>
           </r>
         </is>
       </c>
       <c r="O278" s="13" t="inlineStr"/>
       <c r="P278" s="13" t="inlineStr"/>
       <c r="Q278" s="14" t="n">
-        <v>2.88E7</v>
+        <v>1.284E7</v>
       </c>
       <c r="R278" s="14" t="inlineStr"/>
       <c r="S278" s="14" t="n">
@@ -16714,23 +16714,23 @@
       <c r="U278" s="14" t="inlineStr"/>
       <c r="V278" s="14" t="inlineStr"/>
       <c r="W278" s="14" t="n">
-        <v>2.4E7</v>
+        <v>1.284E7</v>
       </c>
       <c r="X278" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y278" s="14" t="inlineStr"/>
       <c r="Z278" s="14" t="n">
-        <v>2.4E7</v>
+        <v>1.284E7</v>
       </c>
       <c r="AA278" s="14" t="inlineStr"/>
       <c r="AB278" s="14" t="inlineStr"/>
       <c r="AC278" s="15" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.0</v>
       </c>
       <c r="AD278" s="15" t="inlineStr"/>
       <c r="AE278" s="14" t="n">
-        <v>4800000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF278" s="14" t="inlineStr"/>
       <c r="AG278" s="14" t="inlineStr"/>
@@ -16754,14 +16754,14 @@
       <c r="N279" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000202. Honorarium Anggota/Petugas (UAKPA/Barang)</t>
+            <t xml:space="preserve">000201. Honorarium Staf  Pengelola</t>
           </r>
         </is>
       </c>
       <c r="O279" s="13" t="inlineStr"/>
       <c r="P279" s="13" t="inlineStr"/>
       <c r="Q279" s="14" t="n">
-        <v>3600000.0</v>
+        <v>2.88E7</v>
       </c>
       <c r="R279" s="14" t="inlineStr"/>
       <c r="S279" s="14" t="n">
@@ -16771,30 +16771,30 @@
       <c r="U279" s="14" t="inlineStr"/>
       <c r="V279" s="14" t="inlineStr"/>
       <c r="W279" s="14" t="n">
-        <v>2700000.0</v>
+        <v>2.88E7</v>
       </c>
       <c r="X279" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y279" s="14" t="inlineStr"/>
       <c r="Z279" s="14" t="n">
-        <v>2700000.0</v>
+        <v>2.88E7</v>
       </c>
       <c r="AA279" s="14" t="inlineStr"/>
       <c r="AB279" s="14" t="inlineStr"/>
       <c r="AC279" s="15" t="n">
-        <v>0.75</v>
+        <v>1.0</v>
       </c>
       <c r="AD279" s="15" t="inlineStr"/>
       <c r="AE279" s="14" t="n">
-        <v>900000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF279" s="14" t="inlineStr"/>
       <c r="AG279" s="14" t="inlineStr"/>
       <c r="AH279" s="14" t="inlineStr"/>
       <c r="AI279" s="14" t="inlineStr"/>
     </row>
-    <row r="280" customHeight="1" ht="18">
+    <row r="280" customHeight="1" ht="15">
       <c r="A280" s="2" t="inlineStr"/>
       <c r="B280" s="2" t="inlineStr"/>
       <c r="C280" s="2" t="inlineStr"/>
@@ -16811,14 +16811,14 @@
       <c r="N280" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000203. Honorarium Pengurus/Penyimpan Bmn Tingkat Kuasa Pengguna Barang</t>
+            <t xml:space="preserve">000202. Honorarium Anggota/Petugas (UAKPA/Barang)</t>
           </r>
         </is>
       </c>
       <c r="O280" s="13" t="inlineStr"/>
       <c r="P280" s="13" t="inlineStr"/>
       <c r="Q280" s="14" t="n">
-        <v>4320000.0</v>
+        <v>3600000.0</v>
       </c>
       <c r="R280" s="14" t="inlineStr"/>
       <c r="S280" s="14" t="n">
@@ -16828,19 +16828,19 @@
       <c r="U280" s="14" t="inlineStr"/>
       <c r="V280" s="14" t="inlineStr"/>
       <c r="W280" s="14" t="n">
-        <v>3420000.0</v>
+        <v>2700000.0</v>
       </c>
       <c r="X280" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y280" s="14" t="inlineStr"/>
       <c r="Z280" s="14" t="n">
-        <v>3420000.0</v>
+        <v>2700000.0</v>
       </c>
       <c r="AA280" s="14" t="inlineStr"/>
       <c r="AB280" s="14" t="inlineStr"/>
       <c r="AC280" s="15" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="AD280" s="15" t="inlineStr"/>
       <c r="AE280" s="14" t="n">
@@ -16894,7 +16894,7 @@
       <c r="AH281" s="2" t="inlineStr"/>
       <c r="AI281" s="2" t="inlineStr"/>
     </row>
-    <row r="282" customHeight="1" ht="15">
+    <row r="282" customHeight="1" ht="18">
       <c r="A282" s="2" t="inlineStr"/>
       <c r="B282" s="2" t="inlineStr"/>
       <c r="C282" s="2" t="inlineStr"/>
@@ -16902,29 +16902,23 @@
       <c r="E282" s="2" t="inlineStr"/>
       <c r="F282" s="2" t="inlineStr"/>
       <c r="G282" s="2" t="inlineStr"/>
-      <c r="H282" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521119</t>
-          </r>
-        </is>
-      </c>
-      <c r="I282" s="13" t="inlineStr"/>
-      <c r="J282" s="13" t="inlineStr"/>
-      <c r="K282" s="13" t="inlineStr"/>
-      <c r="L282" s="13" t="inlineStr"/>
-      <c r="M282" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N282" s="13" t="inlineStr"/>
+      <c r="H282" s="2" t="inlineStr"/>
+      <c r="I282" s="2" t="inlineStr"/>
+      <c r="J282" s="2" t="inlineStr"/>
+      <c r="K282" s="2" t="inlineStr"/>
+      <c r="L282" s="2" t="inlineStr"/>
+      <c r="M282" s="2" t="inlineStr"/>
+      <c r="N282" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000203. Honorarium Pengurus/Penyimpan Bmn Tingkat Kuasa Pengguna Barang</t>
+          </r>
+        </is>
+      </c>
       <c r="O282" s="13" t="inlineStr"/>
       <c r="P282" s="13" t="inlineStr"/>
       <c r="Q282" s="14" t="n">
-        <v>7500000.0</v>
+        <v>4320000.0</v>
       </c>
       <c r="R282" s="14" t="inlineStr"/>
       <c r="S282" s="14" t="n">
@@ -16934,23 +16928,23 @@
       <c r="U282" s="14" t="inlineStr"/>
       <c r="V282" s="14" t="inlineStr"/>
       <c r="W282" s="14" t="n">
-        <v>7500000.0</v>
+        <v>3780000.0</v>
       </c>
       <c r="X282" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y282" s="14" t="inlineStr"/>
       <c r="Z282" s="14" t="n">
-        <v>7500000.0</v>
+        <v>3780000.0</v>
       </c>
       <c r="AA282" s="14" t="inlineStr"/>
       <c r="AB282" s="14" t="inlineStr"/>
       <c r="AC282" s="15" t="n">
-        <v>1.0</v>
+        <v>0.875</v>
       </c>
       <c r="AD282" s="15" t="inlineStr"/>
       <c r="AE282" s="14" t="n">
-        <v>0.0</v>
+        <v>540000.0</v>
       </c>
       <c r="AF282" s="14" t="inlineStr"/>
       <c r="AG282" s="14" t="inlineStr"/>
@@ -16965,19 +16959,25 @@
       <c r="E283" s="2" t="inlineStr"/>
       <c r="F283" s="2" t="inlineStr"/>
       <c r="G283" s="2" t="inlineStr"/>
-      <c r="H283" s="2" t="inlineStr"/>
-      <c r="I283" s="2" t="inlineStr"/>
-      <c r="J283" s="2" t="inlineStr"/>
-      <c r="K283" s="2" t="inlineStr"/>
-      <c r="L283" s="2" t="inlineStr"/>
-      <c r="M283" s="2" t="inlineStr"/>
-      <c r="N283" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000243. Pakaian Kerja PJLP</t>
-          </r>
-        </is>
-      </c>
+      <c r="H283" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521119</t>
+          </r>
+        </is>
+      </c>
+      <c r="I283" s="13" t="inlineStr"/>
+      <c r="J283" s="13" t="inlineStr"/>
+      <c r="K283" s="13" t="inlineStr"/>
+      <c r="L283" s="13" t="inlineStr"/>
+      <c r="M283" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N283" s="13" t="inlineStr"/>
       <c r="O283" s="13" t="inlineStr"/>
       <c r="P283" s="13" t="inlineStr"/>
       <c r="Q283" s="14" t="n">
@@ -17017,254 +17017,248 @@
     <row r="284" customHeight="1" ht="15">
       <c r="A284" s="2" t="inlineStr"/>
       <c r="B284" s="2" t="inlineStr"/>
-      <c r="C284" s="16" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">EBD</t>
-          </r>
-        </is>
-      </c>
-      <c r="D284" s="16" t="inlineStr"/>
-      <c r="E284" s="16" t="inlineStr"/>
-      <c r="F284" s="16" t="inlineStr"/>
-      <c r="G284" s="16" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Manajemen Kinerja Internal</t>
-          </r>
-        </is>
-      </c>
-      <c r="H284" s="16" t="inlineStr"/>
-      <c r="I284" s="16" t="inlineStr"/>
-      <c r="J284" s="16" t="inlineStr"/>
-      <c r="K284" s="16" t="inlineStr"/>
-      <c r="L284" s="16" t="inlineStr"/>
-      <c r="M284" s="16" t="inlineStr"/>
-      <c r="N284" s="16" t="inlineStr"/>
-      <c r="O284" s="16" t="inlineStr"/>
-      <c r="P284" s="16" t="inlineStr"/>
-      <c r="Q284" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="R284" s="17" t="inlineStr"/>
-      <c r="S284" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T284" s="17" t="inlineStr"/>
-      <c r="U284" s="17" t="inlineStr"/>
-      <c r="V284" s="17" t="inlineStr"/>
-      <c r="W284" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="X284" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y284" s="17" t="inlineStr"/>
-      <c r="Z284" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="AA284" s="17" t="inlineStr"/>
-      <c r="AB284" s="17" t="inlineStr"/>
-      <c r="AC284" s="18" t="n">
+      <c r="C284" s="2" t="inlineStr"/>
+      <c r="D284" s="2" t="inlineStr"/>
+      <c r="E284" s="2" t="inlineStr"/>
+      <c r="F284" s="2" t="inlineStr"/>
+      <c r="G284" s="2" t="inlineStr"/>
+      <c r="H284" s="2" t="inlineStr"/>
+      <c r="I284" s="2" t="inlineStr"/>
+      <c r="J284" s="2" t="inlineStr"/>
+      <c r="K284" s="2" t="inlineStr"/>
+      <c r="L284" s="2" t="inlineStr"/>
+      <c r="M284" s="2" t="inlineStr"/>
+      <c r="N284" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000243. Pakaian Kerja PJLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="O284" s="13" t="inlineStr"/>
+      <c r="P284" s="13" t="inlineStr"/>
+      <c r="Q284" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="R284" s="14" t="inlineStr"/>
+      <c r="S284" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T284" s="14" t="inlineStr"/>
+      <c r="U284" s="14" t="inlineStr"/>
+      <c r="V284" s="14" t="inlineStr"/>
+      <c r="W284" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="X284" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y284" s="14" t="inlineStr"/>
+      <c r="Z284" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="AA284" s="14" t="inlineStr"/>
+      <c r="AB284" s="14" t="inlineStr"/>
+      <c r="AC284" s="15" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD284" s="18" t="inlineStr"/>
-      <c r="AE284" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF284" s="17" t="inlineStr"/>
-      <c r="AG284" s="17" t="inlineStr"/>
-      <c r="AH284" s="17" t="inlineStr"/>
-      <c r="AI284" s="17" t="inlineStr"/>
+      <c r="AD284" s="15" t="inlineStr"/>
+      <c r="AE284" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF284" s="14" t="inlineStr"/>
+      <c r="AG284" s="14" t="inlineStr"/>
+      <c r="AH284" s="14" t="inlineStr"/>
+      <c r="AI284" s="14" t="inlineStr"/>
     </row>
     <row r="285" customHeight="1" ht="15">
       <c r="A285" s="2" t="inlineStr"/>
       <c r="B285" s="2" t="inlineStr"/>
-      <c r="C285" s="28" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">EBD.955</t>
-          </r>
-        </is>
-      </c>
-      <c r="D285" s="28" t="inlineStr"/>
-      <c r="E285" s="28" t="inlineStr"/>
-      <c r="F285" s="28" t="inlineStr"/>
-      <c r="G285" s="28" t="inlineStr"/>
-      <c r="H285" s="28" t="inlineStr"/>
-      <c r="I285" s="28" t="inlineStr"/>
-      <c r="J285" s="28" t="inlineStr"/>
-      <c r="K285" s="20" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Manajemen Keuangan</t>
-          </r>
-        </is>
-      </c>
-      <c r="L285" s="20" t="inlineStr"/>
-      <c r="M285" s="20" t="inlineStr"/>
-      <c r="N285" s="20" t="inlineStr"/>
-      <c r="O285" s="20" t="inlineStr"/>
-      <c r="P285" s="20" t="inlineStr"/>
-      <c r="Q285" s="21" t="n">
+      <c r="C285" s="16" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">EBD</t>
+          </r>
+        </is>
+      </c>
+      <c r="D285" s="16" t="inlineStr"/>
+      <c r="E285" s="16" t="inlineStr"/>
+      <c r="F285" s="16" t="inlineStr"/>
+      <c r="G285" s="16" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Manajemen Kinerja Internal</t>
+          </r>
+        </is>
+      </c>
+      <c r="H285" s="16" t="inlineStr"/>
+      <c r="I285" s="16" t="inlineStr"/>
+      <c r="J285" s="16" t="inlineStr"/>
+      <c r="K285" s="16" t="inlineStr"/>
+      <c r="L285" s="16" t="inlineStr"/>
+      <c r="M285" s="16" t="inlineStr"/>
+      <c r="N285" s="16" t="inlineStr"/>
+      <c r="O285" s="16" t="inlineStr"/>
+      <c r="P285" s="16" t="inlineStr"/>
+      <c r="Q285" s="17" t="n">
         <v>600000.0</v>
       </c>
-      <c r="R285" s="21" t="inlineStr"/>
-      <c r="S285" s="21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T285" s="21" t="inlineStr"/>
-      <c r="U285" s="21" t="inlineStr"/>
-      <c r="V285" s="21" t="inlineStr"/>
-      <c r="W285" s="22" t="n">
+      <c r="R285" s="17" t="inlineStr"/>
+      <c r="S285" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T285" s="17" t="inlineStr"/>
+      <c r="U285" s="17" t="inlineStr"/>
+      <c r="V285" s="17" t="inlineStr"/>
+      <c r="W285" s="17" t="n">
         <v>600000.0</v>
       </c>
-      <c r="X285" s="22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y285" s="22" t="inlineStr"/>
-      <c r="Z285" s="21" t="n">
+      <c r="X285" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y285" s="17" t="inlineStr"/>
+      <c r="Z285" s="17" t="n">
         <v>600000.0</v>
       </c>
-      <c r="AA285" s="21" t="inlineStr"/>
-      <c r="AB285" s="21" t="inlineStr"/>
-      <c r="AC285" s="23" t="n">
+      <c r="AA285" s="17" t="inlineStr"/>
+      <c r="AB285" s="17" t="inlineStr"/>
+      <c r="AC285" s="18" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD285" s="23" t="inlineStr"/>
-      <c r="AE285" s="21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF285" s="21" t="inlineStr"/>
-      <c r="AG285" s="21" t="inlineStr"/>
-      <c r="AH285" s="21" t="inlineStr"/>
-      <c r="AI285" s="21" t="inlineStr"/>
+      <c r="AD285" s="18" t="inlineStr"/>
+      <c r="AE285" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF285" s="17" t="inlineStr"/>
+      <c r="AG285" s="17" t="inlineStr"/>
+      <c r="AH285" s="17" t="inlineStr"/>
+      <c r="AI285" s="17" t="inlineStr"/>
     </row>
     <row r="286" customHeight="1" ht="15">
       <c r="A286" s="2" t="inlineStr"/>
       <c r="B286" s="2" t="inlineStr"/>
-      <c r="C286" s="2" t="inlineStr"/>
-      <c r="D286" s="2" t="inlineStr"/>
-      <c r="E286" s="24" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">201</t>
-          </r>
-        </is>
-      </c>
-      <c r="F286" s="24" t="inlineStr"/>
-      <c r="G286" s="24" t="inlineStr"/>
-      <c r="H286" s="24" t="inlineStr"/>
-      <c r="I286" s="24" t="inlineStr"/>
-      <c r="J286" s="24" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pelayanan Keuangan Penyuluhan Kelautan dan Perikanan</t>
-          </r>
-        </is>
-      </c>
-      <c r="K286" s="24" t="inlineStr"/>
-      <c r="L286" s="24" t="inlineStr"/>
-      <c r="M286" s="24" t="inlineStr"/>
-      <c r="N286" s="24" t="inlineStr"/>
-      <c r="O286" s="24" t="inlineStr"/>
-      <c r="P286" s="24" t="inlineStr"/>
-      <c r="Q286" s="25" t="n">
+      <c r="C286" s="28" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">EBD.955</t>
+          </r>
+        </is>
+      </c>
+      <c r="D286" s="28" t="inlineStr"/>
+      <c r="E286" s="28" t="inlineStr"/>
+      <c r="F286" s="28" t="inlineStr"/>
+      <c r="G286" s="28" t="inlineStr"/>
+      <c r="H286" s="28" t="inlineStr"/>
+      <c r="I286" s="28" t="inlineStr"/>
+      <c r="J286" s="28" t="inlineStr"/>
+      <c r="K286" s="20" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Manajemen Keuangan</t>
+          </r>
+        </is>
+      </c>
+      <c r="L286" s="20" t="inlineStr"/>
+      <c r="M286" s="20" t="inlineStr"/>
+      <c r="N286" s="20" t="inlineStr"/>
+      <c r="O286" s="20" t="inlineStr"/>
+      <c r="P286" s="20" t="inlineStr"/>
+      <c r="Q286" s="21" t="n">
         <v>600000.0</v>
       </c>
-      <c r="R286" s="25" t="inlineStr"/>
-      <c r="S286" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T286" s="25" t="inlineStr"/>
-      <c r="U286" s="25" t="inlineStr"/>
-      <c r="V286" s="25" t="inlineStr"/>
-      <c r="W286" s="25" t="n">
+      <c r="R286" s="21" t="inlineStr"/>
+      <c r="S286" s="21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T286" s="21" t="inlineStr"/>
+      <c r="U286" s="21" t="inlineStr"/>
+      <c r="V286" s="21" t="inlineStr"/>
+      <c r="W286" s="22" t="n">
         <v>600000.0</v>
       </c>
-      <c r="X286" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y286" s="25" t="inlineStr"/>
-      <c r="Z286" s="25" t="n">
+      <c r="X286" s="22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y286" s="22" t="inlineStr"/>
+      <c r="Z286" s="21" t="n">
         <v>600000.0</v>
       </c>
-      <c r="AA286" s="25" t="inlineStr"/>
-      <c r="AB286" s="25" t="inlineStr"/>
-      <c r="AC286" s="26" t="n">
+      <c r="AA286" s="21" t="inlineStr"/>
+      <c r="AB286" s="21" t="inlineStr"/>
+      <c r="AC286" s="23" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD286" s="26" t="inlineStr"/>
-      <c r="AE286" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF286" s="25" t="inlineStr"/>
-      <c r="AG286" s="25" t="inlineStr"/>
-      <c r="AH286" s="25" t="inlineStr"/>
-      <c r="AI286" s="25" t="inlineStr"/>
+      <c r="AD286" s="23" t="inlineStr"/>
+      <c r="AE286" s="21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF286" s="21" t="inlineStr"/>
+      <c r="AG286" s="21" t="inlineStr"/>
+      <c r="AH286" s="21" t="inlineStr"/>
+      <c r="AI286" s="21" t="inlineStr"/>
     </row>
     <row r="287" customHeight="1" ht="15">
       <c r="A287" s="2" t="inlineStr"/>
       <c r="B287" s="2" t="inlineStr"/>
       <c r="C287" s="2" t="inlineStr"/>
       <c r="D287" s="2" t="inlineStr"/>
-      <c r="E287" s="2" t="inlineStr"/>
-      <c r="F287" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">201.DA</t>
-          </r>
-        </is>
-      </c>
-      <c r="G287" s="13" t="inlineStr"/>
-      <c r="H287" s="13" t="inlineStr"/>
-      <c r="I287" s="13" t="inlineStr"/>
-      <c r="J287" s="13" t="inlineStr"/>
-      <c r="K287" s="13" t="inlineStr"/>
-      <c r="L287" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Keuangan</t>
-          </r>
-        </is>
-      </c>
-      <c r="M287" s="13" t="inlineStr"/>
-      <c r="N287" s="13" t="inlineStr"/>
-      <c r="O287" s="13" t="inlineStr"/>
-      <c r="P287" s="13" t="inlineStr"/>
-      <c r="Q287" s="14" t="n">
+      <c r="E287" s="24" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">201</t>
+          </r>
+        </is>
+      </c>
+      <c r="F287" s="24" t="inlineStr"/>
+      <c r="G287" s="24" t="inlineStr"/>
+      <c r="H287" s="24" t="inlineStr"/>
+      <c r="I287" s="24" t="inlineStr"/>
+      <c r="J287" s="24" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pelayanan Keuangan Penyuluhan Kelautan dan Perikanan</t>
+          </r>
+        </is>
+      </c>
+      <c r="K287" s="24" t="inlineStr"/>
+      <c r="L287" s="24" t="inlineStr"/>
+      <c r="M287" s="24" t="inlineStr"/>
+      <c r="N287" s="24" t="inlineStr"/>
+      <c r="O287" s="24" t="inlineStr"/>
+      <c r="P287" s="24" t="inlineStr"/>
+      <c r="Q287" s="25" t="n">
         <v>600000.0</v>
       </c>
-      <c r="R287" s="14" t="inlineStr"/>
-      <c r="S287" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T287" s="14" t="inlineStr"/>
-      <c r="U287" s="14" t="inlineStr"/>
-      <c r="V287" s="14" t="inlineStr"/>
-      <c r="W287" s="14" t="n">
+      <c r="R287" s="25" t="inlineStr"/>
+      <c r="S287" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T287" s="25" t="inlineStr"/>
+      <c r="U287" s="25" t="inlineStr"/>
+      <c r="V287" s="25" t="inlineStr"/>
+      <c r="W287" s="25" t="n">
         <v>600000.0</v>
       </c>
-      <c r="X287" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y287" s="14" t="inlineStr"/>
-      <c r="Z287" s="14" t="n">
+      <c r="X287" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y287" s="25" t="inlineStr"/>
+      <c r="Z287" s="25" t="n">
         <v>600000.0</v>
       </c>
-      <c r="AA287" s="14" t="inlineStr"/>
-      <c r="AB287" s="14" t="inlineStr"/>
-      <c r="AC287" s="15" t="n">
+      <c r="AA287" s="25" t="inlineStr"/>
+      <c r="AB287" s="25" t="inlineStr"/>
+      <c r="AC287" s="26" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD287" s="15" t="inlineStr"/>
-      <c r="AE287" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF287" s="14" t="inlineStr"/>
-      <c r="AG287" s="14" t="inlineStr"/>
-      <c r="AH287" s="14" t="inlineStr"/>
-      <c r="AI287" s="14" t="inlineStr"/>
+      <c r="AD287" s="26" t="inlineStr"/>
+      <c r="AE287" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF287" s="25" t="inlineStr"/>
+      <c r="AG287" s="25" t="inlineStr"/>
+      <c r="AH287" s="25" t="inlineStr"/>
+      <c r="AI287" s="25" t="inlineStr"/>
     </row>
     <row r="288" customHeight="1" ht="15">
       <c r="A288" s="2" t="inlineStr"/>
@@ -17272,26 +17266,26 @@
       <c r="C288" s="2" t="inlineStr"/>
       <c r="D288" s="2" t="inlineStr"/>
       <c r="E288" s="2" t="inlineStr"/>
-      <c r="F288" s="2" t="inlineStr"/>
-      <c r="G288" s="2" t="inlineStr"/>
-      <c r="H288" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">524111</t>
-          </r>
-        </is>
-      </c>
+      <c r="F288" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">201.DA</t>
+          </r>
+        </is>
+      </c>
+      <c r="G288" s="13" t="inlineStr"/>
+      <c r="H288" s="13" t="inlineStr"/>
       <c r="I288" s="13" t="inlineStr"/>
       <c r="J288" s="13" t="inlineStr"/>
       <c r="K288" s="13" t="inlineStr"/>
-      <c r="L288" s="13" t="inlineStr"/>
-      <c r="M288" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Perjalanan Dinas Biasa</t>
-          </r>
-        </is>
-      </c>
+      <c r="L288" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Keuangan</t>
+          </r>
+        </is>
+      </c>
+      <c r="M288" s="13" t="inlineStr"/>
       <c r="N288" s="13" t="inlineStr"/>
       <c r="O288" s="13" t="inlineStr"/>
       <c r="P288" s="13" t="inlineStr"/>
@@ -17337,19 +17331,25 @@
       <c r="E289" s="2" t="inlineStr"/>
       <c r="F289" s="2" t="inlineStr"/>
       <c r="G289" s="2" t="inlineStr"/>
-      <c r="H289" s="2" t="inlineStr"/>
-      <c r="I289" s="2" t="inlineStr"/>
-      <c r="J289" s="2" t="inlineStr"/>
-      <c r="K289" s="2" t="inlineStr"/>
-      <c r="L289" s="2" t="inlineStr"/>
-      <c r="M289" s="2" t="inlineStr"/>
-      <c r="N289" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000231. Uang Harian</t>
-          </r>
-        </is>
-      </c>
+      <c r="H289" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">524111</t>
+          </r>
+        </is>
+      </c>
+      <c r="I289" s="13" t="inlineStr"/>
+      <c r="J289" s="13" t="inlineStr"/>
+      <c r="K289" s="13" t="inlineStr"/>
+      <c r="L289" s="13" t="inlineStr"/>
+      <c r="M289" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Perjalanan Dinas Biasa</t>
+          </r>
+        </is>
+      </c>
+      <c r="N289" s="13" t="inlineStr"/>
       <c r="O289" s="13" t="inlineStr"/>
       <c r="P289" s="13" t="inlineStr"/>
       <c r="Q289" s="14" t="n">
@@ -17386,48 +17386,105 @@
       <c r="AH289" s="14" t="inlineStr"/>
       <c r="AI289" s="14" t="inlineStr"/>
     </row>
-    <row r="290" customHeight="1" ht="12">
+    <row r="290" customHeight="1" ht="15">
       <c r="A290" s="2" t="inlineStr"/>
-      <c r="B290" s="27" t="inlineStr">
+      <c r="B290" s="2" t="inlineStr"/>
+      <c r="C290" s="2" t="inlineStr"/>
+      <c r="D290" s="2" t="inlineStr"/>
+      <c r="E290" s="2" t="inlineStr"/>
+      <c r="F290" s="2" t="inlineStr"/>
+      <c r="G290" s="2" t="inlineStr"/>
+      <c r="H290" s="2" t="inlineStr"/>
+      <c r="I290" s="2" t="inlineStr"/>
+      <c r="J290" s="2" t="inlineStr"/>
+      <c r="K290" s="2" t="inlineStr"/>
+      <c r="L290" s="2" t="inlineStr"/>
+      <c r="M290" s="2" t="inlineStr"/>
+      <c r="N290" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000231. Uang Harian</t>
+          </r>
+        </is>
+      </c>
+      <c r="O290" s="13" t="inlineStr"/>
+      <c r="P290" s="13" t="inlineStr"/>
+      <c r="Q290" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R290" s="14" t="inlineStr"/>
+      <c r="S290" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T290" s="14" t="inlineStr"/>
+      <c r="U290" s="14" t="inlineStr"/>
+      <c r="V290" s="14" t="inlineStr"/>
+      <c r="W290" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X290" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y290" s="14" t="inlineStr"/>
+      <c r="Z290" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA290" s="14" t="inlineStr"/>
+      <c r="AB290" s="14" t="inlineStr"/>
+      <c r="AC290" s="15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD290" s="15" t="inlineStr"/>
+      <c r="AE290" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF290" s="14" t="inlineStr"/>
+      <c r="AG290" s="14" t="inlineStr"/>
+      <c r="AH290" s="14" t="inlineStr"/>
+      <c r="AI290" s="14" t="inlineStr"/>
+    </row>
+    <row r="291" customHeight="1" ht="12">
+      <c r="A291" s="2" t="inlineStr"/>
+      <c r="B291" s="27" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">*Lock Pagu adalah jumlah pagu yang sedang dalam proses usulan revisi DIPA atau POK. Lock pagu akan hilang setelah usulan revisi DIPA/POK selesai menjadi DIPA.</t>
           </r>
         </is>
       </c>
-      <c r="C290" s="27" t="inlineStr"/>
-      <c r="D290" s="27" t="inlineStr"/>
-      <c r="E290" s="27" t="inlineStr"/>
-      <c r="F290" s="27" t="inlineStr"/>
-      <c r="G290" s="27" t="inlineStr"/>
-      <c r="H290" s="27" t="inlineStr"/>
-      <c r="I290" s="27" t="inlineStr"/>
-      <c r="J290" s="27" t="inlineStr"/>
-      <c r="K290" s="27" t="inlineStr"/>
-      <c r="L290" s="27" t="inlineStr"/>
-      <c r="M290" s="27" t="inlineStr"/>
-      <c r="N290" s="27" t="inlineStr"/>
-      <c r="O290" s="27" t="inlineStr"/>
-      <c r="P290" s="27" t="inlineStr"/>
-      <c r="Q290" s="27" t="inlineStr"/>
-      <c r="R290" s="27" t="inlineStr"/>
-      <c r="S290" s="27" t="inlineStr"/>
-      <c r="T290" s="27" t="inlineStr"/>
-      <c r="U290" s="27" t="inlineStr"/>
-      <c r="V290" s="27" t="inlineStr"/>
-      <c r="W290" s="27" t="inlineStr"/>
-      <c r="X290" s="27" t="inlineStr"/>
-      <c r="Y290" s="27" t="inlineStr"/>
-      <c r="Z290" s="27" t="inlineStr"/>
-      <c r="AA290" s="27" t="inlineStr"/>
-      <c r="AB290" s="27" t="inlineStr"/>
-      <c r="AC290" s="27" t="inlineStr"/>
-      <c r="AD290" s="27" t="inlineStr"/>
-      <c r="AE290" s="27" t="inlineStr"/>
-      <c r="AF290" s="27" t="inlineStr"/>
-      <c r="AG290" s="2" t="inlineStr"/>
-      <c r="AH290" s="2" t="inlineStr"/>
-      <c r="AI290" s="2" t="inlineStr"/>
+      <c r="C291" s="27" t="inlineStr"/>
+      <c r="D291" s="27" t="inlineStr"/>
+      <c r="E291" s="27" t="inlineStr"/>
+      <c r="F291" s="27" t="inlineStr"/>
+      <c r="G291" s="27" t="inlineStr"/>
+      <c r="H291" s="27" t="inlineStr"/>
+      <c r="I291" s="27" t="inlineStr"/>
+      <c r="J291" s="27" t="inlineStr"/>
+      <c r="K291" s="27" t="inlineStr"/>
+      <c r="L291" s="27" t="inlineStr"/>
+      <c r="M291" s="27" t="inlineStr"/>
+      <c r="N291" s="27" t="inlineStr"/>
+      <c r="O291" s="27" t="inlineStr"/>
+      <c r="P291" s="27" t="inlineStr"/>
+      <c r="Q291" s="27" t="inlineStr"/>
+      <c r="R291" s="27" t="inlineStr"/>
+      <c r="S291" s="27" t="inlineStr"/>
+      <c r="T291" s="27" t="inlineStr"/>
+      <c r="U291" s="27" t="inlineStr"/>
+      <c r="V291" s="27" t="inlineStr"/>
+      <c r="W291" s="27" t="inlineStr"/>
+      <c r="X291" s="27" t="inlineStr"/>
+      <c r="Y291" s="27" t="inlineStr"/>
+      <c r="Z291" s="27" t="inlineStr"/>
+      <c r="AA291" s="27" t="inlineStr"/>
+      <c r="AB291" s="27" t="inlineStr"/>
+      <c r="AC291" s="27" t="inlineStr"/>
+      <c r="AD291" s="27" t="inlineStr"/>
+      <c r="AE291" s="27" t="inlineStr"/>
+      <c r="AF291" s="27" t="inlineStr"/>
+      <c r="AG291" s="2" t="inlineStr"/>
+      <c r="AH291" s="2" t="inlineStr"/>
+      <c r="AI291" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -18826,15 +18883,15 @@
     <mergeCell ref="Z201:AB201"/>
     <mergeCell ref="AC201:AD201"/>
     <mergeCell ref="AE201:AI201"/>
-    <mergeCell ref="N202:P202"/>
+    <mergeCell ref="H202:L202"/>
+    <mergeCell ref="M202:P202"/>
     <mergeCell ref="Q202:R202"/>
     <mergeCell ref="S202:V202"/>
     <mergeCell ref="X202:Y202"/>
     <mergeCell ref="Z202:AB202"/>
     <mergeCell ref="AC202:AD202"/>
     <mergeCell ref="AE202:AI202"/>
-    <mergeCell ref="H203:L203"/>
-    <mergeCell ref="M203:P203"/>
+    <mergeCell ref="N203:P203"/>
     <mergeCell ref="Q203:R203"/>
     <mergeCell ref="S203:V203"/>
     <mergeCell ref="X203:Y203"/>
@@ -18848,30 +18905,30 @@
     <mergeCell ref="Z204:AB204"/>
     <mergeCell ref="AC204:AD204"/>
     <mergeCell ref="AE204:AI204"/>
-    <mergeCell ref="N205:P205"/>
+    <mergeCell ref="H205:L205"/>
+    <mergeCell ref="M205:P205"/>
     <mergeCell ref="Q205:R205"/>
     <mergeCell ref="S205:V205"/>
     <mergeCell ref="X205:Y205"/>
     <mergeCell ref="Z205:AB205"/>
     <mergeCell ref="AC205:AD205"/>
     <mergeCell ref="AE205:AI205"/>
-    <mergeCell ref="H206:L206"/>
-    <mergeCell ref="M206:P206"/>
+    <mergeCell ref="N206:P206"/>
     <mergeCell ref="Q206:R206"/>
     <mergeCell ref="S206:V206"/>
     <mergeCell ref="X206:Y206"/>
     <mergeCell ref="Z206:AB206"/>
     <mergeCell ref="AC206:AD206"/>
     <mergeCell ref="AE206:AI206"/>
-    <mergeCell ref="N207:P207"/>
+    <mergeCell ref="H207:L207"/>
+    <mergeCell ref="M207:P207"/>
     <mergeCell ref="Q207:R207"/>
     <mergeCell ref="S207:V207"/>
     <mergeCell ref="X207:Y207"/>
     <mergeCell ref="Z207:AB207"/>
     <mergeCell ref="AC207:AD207"/>
     <mergeCell ref="AE207:AI207"/>
-    <mergeCell ref="H208:L208"/>
-    <mergeCell ref="M208:P208"/>
+    <mergeCell ref="N208:P208"/>
     <mergeCell ref="Q208:R208"/>
     <mergeCell ref="S208:V208"/>
     <mergeCell ref="X208:Y208"/>
@@ -18885,15 +18942,15 @@
     <mergeCell ref="Z209:AB209"/>
     <mergeCell ref="AC209:AD209"/>
     <mergeCell ref="AE209:AI209"/>
-    <mergeCell ref="N210:P210"/>
+    <mergeCell ref="H210:L210"/>
+    <mergeCell ref="M210:P210"/>
     <mergeCell ref="Q210:R210"/>
     <mergeCell ref="S210:V210"/>
     <mergeCell ref="X210:Y210"/>
     <mergeCell ref="Z210:AB210"/>
     <mergeCell ref="AC210:AD210"/>
     <mergeCell ref="AE210:AI210"/>
-    <mergeCell ref="H211:L211"/>
-    <mergeCell ref="M211:P211"/>
+    <mergeCell ref="N211:P211"/>
     <mergeCell ref="Q211:R211"/>
     <mergeCell ref="S211:V211"/>
     <mergeCell ref="X211:Y211"/>
@@ -18942,68 +18999,68 @@
     <mergeCell ref="Z217:AB217"/>
     <mergeCell ref="AC217:AD217"/>
     <mergeCell ref="AE217:AI217"/>
-    <mergeCell ref="N218:P218"/>
+    <mergeCell ref="F218:K218"/>
+    <mergeCell ref="L218:P218"/>
     <mergeCell ref="Q218:R218"/>
     <mergeCell ref="S218:V218"/>
     <mergeCell ref="X218:Y218"/>
     <mergeCell ref="Z218:AB218"/>
     <mergeCell ref="AC218:AD218"/>
     <mergeCell ref="AE218:AI218"/>
-    <mergeCell ref="F219:K219"/>
-    <mergeCell ref="L219:P219"/>
+    <mergeCell ref="H219:L219"/>
+    <mergeCell ref="M219:P219"/>
     <mergeCell ref="Q219:R219"/>
     <mergeCell ref="S219:V219"/>
     <mergeCell ref="X219:Y219"/>
     <mergeCell ref="Z219:AB219"/>
     <mergeCell ref="AC219:AD219"/>
     <mergeCell ref="AE219:AI219"/>
-    <mergeCell ref="H220:L220"/>
-    <mergeCell ref="M220:P220"/>
+    <mergeCell ref="N220:P220"/>
     <mergeCell ref="Q220:R220"/>
     <mergeCell ref="S220:V220"/>
     <mergeCell ref="X220:Y220"/>
     <mergeCell ref="Z220:AB220"/>
     <mergeCell ref="AC220:AD220"/>
     <mergeCell ref="AE220:AI220"/>
-    <mergeCell ref="N221:P221"/>
+    <mergeCell ref="H221:L221"/>
+    <mergeCell ref="M221:P221"/>
     <mergeCell ref="Q221:R221"/>
     <mergeCell ref="S221:V221"/>
     <mergeCell ref="X221:Y221"/>
     <mergeCell ref="Z221:AB221"/>
     <mergeCell ref="AC221:AD221"/>
     <mergeCell ref="AE221:AI221"/>
-    <mergeCell ref="H222:L222"/>
-    <mergeCell ref="M222:P222"/>
+    <mergeCell ref="N222:P222"/>
     <mergeCell ref="Q222:R222"/>
     <mergeCell ref="S222:V222"/>
     <mergeCell ref="X222:Y222"/>
     <mergeCell ref="Z222:AB222"/>
     <mergeCell ref="AC222:AD222"/>
     <mergeCell ref="AE222:AI222"/>
-    <mergeCell ref="N223:P223"/>
+    <mergeCell ref="H223:L223"/>
+    <mergeCell ref="M223:P223"/>
     <mergeCell ref="Q223:R223"/>
     <mergeCell ref="S223:V223"/>
     <mergeCell ref="X223:Y223"/>
     <mergeCell ref="Z223:AB223"/>
     <mergeCell ref="AC223:AD223"/>
     <mergeCell ref="AE223:AI223"/>
-    <mergeCell ref="H224:L224"/>
-    <mergeCell ref="M224:P224"/>
+    <mergeCell ref="N224:P224"/>
     <mergeCell ref="Q224:R224"/>
     <mergeCell ref="S224:V224"/>
     <mergeCell ref="X224:Y224"/>
     <mergeCell ref="Z224:AB224"/>
     <mergeCell ref="AC224:AD224"/>
     <mergeCell ref="AE224:AI224"/>
-    <mergeCell ref="N225:P225"/>
+    <mergeCell ref="H225:L225"/>
+    <mergeCell ref="M225:P225"/>
     <mergeCell ref="Q225:R225"/>
     <mergeCell ref="S225:V225"/>
     <mergeCell ref="X225:Y225"/>
     <mergeCell ref="Z225:AB225"/>
     <mergeCell ref="AC225:AD225"/>
     <mergeCell ref="AE225:AI225"/>
-    <mergeCell ref="H226:L226"/>
-    <mergeCell ref="M226:P226"/>
+    <mergeCell ref="N226:P226"/>
     <mergeCell ref="Q226:R226"/>
     <mergeCell ref="S226:V226"/>
     <mergeCell ref="X226:Y226"/>
@@ -19018,23 +19075,23 @@
     <mergeCell ref="Z228:AB228"/>
     <mergeCell ref="AC228:AD228"/>
     <mergeCell ref="AE228:AI228"/>
-    <mergeCell ref="N229:P229"/>
+    <mergeCell ref="F229:K229"/>
+    <mergeCell ref="L229:P229"/>
     <mergeCell ref="Q229:R229"/>
     <mergeCell ref="S229:V229"/>
     <mergeCell ref="X229:Y229"/>
     <mergeCell ref="Z229:AB229"/>
     <mergeCell ref="AC229:AD229"/>
     <mergeCell ref="AE229:AI229"/>
-    <mergeCell ref="F230:K230"/>
-    <mergeCell ref="L230:P230"/>
+    <mergeCell ref="H230:L230"/>
+    <mergeCell ref="M230:P230"/>
     <mergeCell ref="Q230:R230"/>
     <mergeCell ref="S230:V230"/>
     <mergeCell ref="X230:Y230"/>
     <mergeCell ref="Z230:AB230"/>
     <mergeCell ref="AC230:AD230"/>
     <mergeCell ref="AE230:AI230"/>
-    <mergeCell ref="H231:L231"/>
-    <mergeCell ref="M231:P231"/>
+    <mergeCell ref="N231:P231"/>
     <mergeCell ref="Q231:R231"/>
     <mergeCell ref="S231:V231"/>
     <mergeCell ref="X231:Y231"/>
@@ -19048,30 +19105,30 @@
     <mergeCell ref="Z232:AB232"/>
     <mergeCell ref="AC232:AD232"/>
     <mergeCell ref="AE232:AI232"/>
-    <mergeCell ref="N233:P233"/>
+    <mergeCell ref="H233:L233"/>
+    <mergeCell ref="M233:P233"/>
     <mergeCell ref="Q233:R233"/>
     <mergeCell ref="S233:V233"/>
     <mergeCell ref="X233:Y233"/>
     <mergeCell ref="Z233:AB233"/>
     <mergeCell ref="AC233:AD233"/>
     <mergeCell ref="AE233:AI233"/>
-    <mergeCell ref="H234:L234"/>
-    <mergeCell ref="M234:P234"/>
+    <mergeCell ref="N234:P234"/>
     <mergeCell ref="Q234:R234"/>
     <mergeCell ref="S234:V234"/>
     <mergeCell ref="X234:Y234"/>
     <mergeCell ref="Z234:AB234"/>
     <mergeCell ref="AC234:AD234"/>
     <mergeCell ref="AE234:AI234"/>
-    <mergeCell ref="N235:P235"/>
+    <mergeCell ref="H235:L235"/>
+    <mergeCell ref="M235:P235"/>
     <mergeCell ref="Q235:R235"/>
     <mergeCell ref="S235:V235"/>
     <mergeCell ref="X235:Y235"/>
     <mergeCell ref="Z235:AB235"/>
     <mergeCell ref="AC235:AD235"/>
     <mergeCell ref="AE235:AI235"/>
-    <mergeCell ref="H236:L236"/>
-    <mergeCell ref="M236:P236"/>
+    <mergeCell ref="N236:P236"/>
     <mergeCell ref="Q236:R236"/>
     <mergeCell ref="S236:V236"/>
     <mergeCell ref="X236:Y236"/>
@@ -19183,15 +19240,15 @@
     <mergeCell ref="Z251:AB251"/>
     <mergeCell ref="AC251:AD251"/>
     <mergeCell ref="AE251:AI251"/>
-    <mergeCell ref="N252:P252"/>
+    <mergeCell ref="H252:L252"/>
+    <mergeCell ref="M252:P252"/>
     <mergeCell ref="Q252:R252"/>
     <mergeCell ref="S252:V252"/>
     <mergeCell ref="X252:Y252"/>
     <mergeCell ref="Z252:AB252"/>
     <mergeCell ref="AC252:AD252"/>
     <mergeCell ref="AE252:AI252"/>
-    <mergeCell ref="H253:L253"/>
-    <mergeCell ref="M253:P253"/>
+    <mergeCell ref="N253:P253"/>
     <mergeCell ref="Q253:R253"/>
     <mergeCell ref="S253:V253"/>
     <mergeCell ref="X253:Y253"/>
@@ -19290,15 +19347,15 @@
     <mergeCell ref="Z267:AB267"/>
     <mergeCell ref="AC267:AD267"/>
     <mergeCell ref="AE267:AI267"/>
-    <mergeCell ref="H268:L268"/>
-    <mergeCell ref="M268:P268"/>
+    <mergeCell ref="N268:P268"/>
     <mergeCell ref="Q268:R268"/>
     <mergeCell ref="S268:V268"/>
     <mergeCell ref="X268:Y268"/>
     <mergeCell ref="Z268:AB268"/>
     <mergeCell ref="AC268:AD268"/>
     <mergeCell ref="AE268:AI268"/>
-    <mergeCell ref="N269:P269"/>
+    <mergeCell ref="H269:L269"/>
+    <mergeCell ref="M269:P269"/>
     <mergeCell ref="Q269:R269"/>
     <mergeCell ref="S269:V269"/>
     <mergeCell ref="X269:Y269"/>
@@ -19319,23 +19376,23 @@
     <mergeCell ref="Z271:AB271"/>
     <mergeCell ref="AC271:AD271"/>
     <mergeCell ref="AE271:AI271"/>
-    <mergeCell ref="F272:K272"/>
-    <mergeCell ref="L272:P272"/>
+    <mergeCell ref="N272:P272"/>
     <mergeCell ref="Q272:R272"/>
     <mergeCell ref="S272:V272"/>
     <mergeCell ref="X272:Y272"/>
     <mergeCell ref="Z272:AB272"/>
     <mergeCell ref="AC272:AD272"/>
     <mergeCell ref="AE272:AI272"/>
-    <mergeCell ref="H273:L273"/>
-    <mergeCell ref="M273:P273"/>
+    <mergeCell ref="F273:K273"/>
+    <mergeCell ref="L273:P273"/>
     <mergeCell ref="Q273:R273"/>
     <mergeCell ref="S273:V273"/>
     <mergeCell ref="X273:Y273"/>
     <mergeCell ref="Z273:AB273"/>
     <mergeCell ref="AC273:AD273"/>
     <mergeCell ref="AE273:AI273"/>
-    <mergeCell ref="N274:P274"/>
+    <mergeCell ref="H274:L274"/>
+    <mergeCell ref="M274:P274"/>
     <mergeCell ref="Q274:R274"/>
     <mergeCell ref="S274:V274"/>
     <mergeCell ref="X274:Y274"/>
@@ -19385,69 +19442,76 @@
     <mergeCell ref="AC280:AD280"/>
     <mergeCell ref="AE280:AI280"/>
     <mergeCell ref="B281:AF281"/>
-    <mergeCell ref="H282:L282"/>
-    <mergeCell ref="M282:P282"/>
+    <mergeCell ref="N282:P282"/>
     <mergeCell ref="Q282:R282"/>
     <mergeCell ref="S282:V282"/>
     <mergeCell ref="X282:Y282"/>
     <mergeCell ref="Z282:AB282"/>
     <mergeCell ref="AC282:AD282"/>
     <mergeCell ref="AE282:AI282"/>
-    <mergeCell ref="N283:P283"/>
+    <mergeCell ref="H283:L283"/>
+    <mergeCell ref="M283:P283"/>
     <mergeCell ref="Q283:R283"/>
     <mergeCell ref="S283:V283"/>
     <mergeCell ref="X283:Y283"/>
     <mergeCell ref="Z283:AB283"/>
     <mergeCell ref="AC283:AD283"/>
     <mergeCell ref="AE283:AI283"/>
-    <mergeCell ref="C284:F284"/>
-    <mergeCell ref="G284:P284"/>
+    <mergeCell ref="N284:P284"/>
     <mergeCell ref="Q284:R284"/>
     <mergeCell ref="S284:V284"/>
     <mergeCell ref="X284:Y284"/>
     <mergeCell ref="Z284:AB284"/>
     <mergeCell ref="AC284:AD284"/>
     <mergeCell ref="AE284:AI284"/>
-    <mergeCell ref="C285:J285"/>
-    <mergeCell ref="K285:P285"/>
+    <mergeCell ref="C285:F285"/>
+    <mergeCell ref="G285:P285"/>
     <mergeCell ref="Q285:R285"/>
     <mergeCell ref="S285:V285"/>
     <mergeCell ref="X285:Y285"/>
     <mergeCell ref="Z285:AB285"/>
     <mergeCell ref="AC285:AD285"/>
     <mergeCell ref="AE285:AI285"/>
-    <mergeCell ref="E286:I286"/>
-    <mergeCell ref="J286:P286"/>
+    <mergeCell ref="C286:J286"/>
+    <mergeCell ref="K286:P286"/>
     <mergeCell ref="Q286:R286"/>
     <mergeCell ref="S286:V286"/>
     <mergeCell ref="X286:Y286"/>
     <mergeCell ref="Z286:AB286"/>
     <mergeCell ref="AC286:AD286"/>
     <mergeCell ref="AE286:AI286"/>
-    <mergeCell ref="F287:K287"/>
-    <mergeCell ref="L287:P287"/>
+    <mergeCell ref="E287:I287"/>
+    <mergeCell ref="J287:P287"/>
     <mergeCell ref="Q287:R287"/>
     <mergeCell ref="S287:V287"/>
     <mergeCell ref="X287:Y287"/>
     <mergeCell ref="Z287:AB287"/>
     <mergeCell ref="AC287:AD287"/>
     <mergeCell ref="AE287:AI287"/>
-    <mergeCell ref="H288:L288"/>
-    <mergeCell ref="M288:P288"/>
+    <mergeCell ref="F288:K288"/>
+    <mergeCell ref="L288:P288"/>
     <mergeCell ref="Q288:R288"/>
     <mergeCell ref="S288:V288"/>
     <mergeCell ref="X288:Y288"/>
     <mergeCell ref="Z288:AB288"/>
     <mergeCell ref="AC288:AD288"/>
     <mergeCell ref="AE288:AI288"/>
-    <mergeCell ref="N289:P289"/>
+    <mergeCell ref="H289:L289"/>
+    <mergeCell ref="M289:P289"/>
     <mergeCell ref="Q289:R289"/>
     <mergeCell ref="S289:V289"/>
     <mergeCell ref="X289:Y289"/>
     <mergeCell ref="Z289:AB289"/>
     <mergeCell ref="AC289:AD289"/>
     <mergeCell ref="AE289:AI289"/>
-    <mergeCell ref="B290:AF290"/>
+    <mergeCell ref="N290:P290"/>
+    <mergeCell ref="Q290:R290"/>
+    <mergeCell ref="S290:V290"/>
+    <mergeCell ref="X290:Y290"/>
+    <mergeCell ref="Z290:AB290"/>
+    <mergeCell ref="AC290:AD290"/>
+    <mergeCell ref="AE290:AI290"/>
+    <mergeCell ref="B291:AF291"/>
   </mergeCells>
   <pageMargins left="0.0" right="0.0" top="0.0" bottom="0.00" header="0.0" footer="0.0"/>
   <pageSetup orientation="landscape" paperSize="9"/>

--- a/Database/Akrual.xlsx
+++ b/Database/Akrual.xlsx
@@ -982,19 +982,19 @@
         <v>9.0559784495E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>0.0</v>
+        <v>6.42836618E8</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>9.0559784495E10</v>
+        <v>9.1202621113E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.9056337261582303</v>
+        <v>0.9120623470401897</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>9.436253505E9</v>
+        <v>8.793416887E9</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1714,20 +1714,20 @@
         <v>8.6526416455E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>0.0</v>
+        <v>6.42836618E8</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>8.6526416455E10</v>
+        <v>8.7169253073E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.9016677558926631</v>
+        <v>0.9083665777612324</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>9.436221545E9</v>
+        <v>8.793384927E9</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1777,20 +1777,20 @@
         <v>8.6526416455E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>0.0</v>
+        <v>6.42836618E8</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>8.6526416455E10</v>
+        <v>8.7169253073E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.9016677558926631</v>
+        <v>0.9083665777612324</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>9.436221545E9</v>
+        <v>8.793384927E9</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1840,20 +1840,20 @@
         <v>8.6525816455E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>0.0</v>
+        <v>6.42836618E8</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>8.6525816455E10</v>
+        <v>8.7168653073E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.9016671410730147</v>
+        <v>0.9083660048257833</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>9.436221545E9</v>
+        <v>8.793384927E9</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -3233,20 +3233,20 @@
         <v>8.6508305403E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>0.0</v>
+        <v>6.42836618E8</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>8.6508305403E10</v>
+        <v>8.7151142021E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.9016587698982197</v>
+        <v>0.9083589274325887</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>9.435202597E9</v>
+        <v>8.792365979E9</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -3296,20 +3296,20 @@
         <v>8.0279551347E10</v>
       </c>
       <c r="X47" s="25" t="n">
-        <v>0.0</v>
+        <v>5.189E8</v>
       </c>
       <c r="Y47" s="25" t="inlineStr"/>
       <c r="Z47" s="25" t="n">
-        <v>8.0279551347E10</v>
+        <v>8.0798451347E10</v>
       </c>
       <c r="AA47" s="25" t="inlineStr"/>
       <c r="AB47" s="25" t="inlineStr"/>
       <c r="AC47" s="26" t="n">
-        <v>0.9020506445726097</v>
+        <v>0.9078811963334875</v>
       </c>
       <c r="AD47" s="26" t="inlineStr"/>
       <c r="AE47" s="25" t="n">
-        <v>8.717171653E9</v>
+        <v>8.198271653E9</v>
       </c>
       <c r="AF47" s="25" t="inlineStr"/>
       <c r="AG47" s="25" t="inlineStr"/>
@@ -3359,20 +3359,20 @@
         <v>5.831238104E9</v>
       </c>
       <c r="X48" s="14" t="n">
-        <v>0.0</v>
+        <v>2.8323E7</v>
       </c>
       <c r="Y48" s="14" t="inlineStr"/>
       <c r="Z48" s="14" t="n">
-        <v>5.831238104E9</v>
+        <v>5.859561104E9</v>
       </c>
       <c r="AA48" s="14" t="inlineStr"/>
       <c r="AB48" s="14" t="inlineStr"/>
       <c r="AC48" s="15" t="n">
-        <v>0.981210213727161</v>
+        <v>0.9859760655733292</v>
       </c>
       <c r="AD48" s="15" t="inlineStr"/>
       <c r="AE48" s="14" t="n">
-        <v>1.11665896E8</v>
+        <v>8.3342896E7</v>
       </c>
       <c r="AF48" s="14" t="inlineStr"/>
       <c r="AG48" s="14" t="inlineStr"/>
@@ -5337,20 +5337,20 @@
         <v>2.77741E8</v>
       </c>
       <c r="X82" s="14" t="n">
-        <v>0.0</v>
+        <v>2.8323E7</v>
       </c>
       <c r="Y82" s="14" t="inlineStr"/>
       <c r="Z82" s="14" t="n">
-        <v>2.77741E8</v>
+        <v>3.06064E8</v>
       </c>
       <c r="AA82" s="14" t="inlineStr"/>
       <c r="AB82" s="14" t="inlineStr"/>
       <c r="AC82" s="15" t="n">
-        <v>0.7699628520736305</v>
+        <v>0.8484808161454868</v>
       </c>
       <c r="AD82" s="15" t="inlineStr"/>
       <c r="AE82" s="14" t="n">
-        <v>8.2979E7</v>
+        <v>5.4656E7</v>
       </c>
       <c r="AF82" s="14" t="inlineStr"/>
       <c r="AG82" s="14" t="inlineStr"/>
@@ -5394,20 +5394,20 @@
         <v>1.554E7</v>
       </c>
       <c r="X83" s="14" t="n">
-        <v>0.0</v>
+        <v>1400000.0</v>
       </c>
       <c r="Y83" s="14" t="inlineStr"/>
       <c r="Z83" s="14" t="n">
-        <v>1.554E7</v>
+        <v>1.694E7</v>
       </c>
       <c r="AA83" s="14" t="inlineStr"/>
       <c r="AB83" s="14" t="inlineStr"/>
       <c r="AC83" s="15" t="n">
-        <v>0.8409090909090909</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="AD83" s="15" t="inlineStr"/>
       <c r="AE83" s="14" t="n">
-        <v>2940000.0</v>
+        <v>1540000.0</v>
       </c>
       <c r="AF83" s="14" t="inlineStr"/>
       <c r="AG83" s="14" t="inlineStr"/>
@@ -5451,20 +5451,20 @@
         <v>2.28253E8</v>
       </c>
       <c r="X84" s="14" t="n">
-        <v>0.0</v>
+        <v>2.3643E7</v>
       </c>
       <c r="Y84" s="14" t="inlineStr"/>
       <c r="Z84" s="14" t="n">
-        <v>2.28253E8</v>
+        <v>2.51896E8</v>
       </c>
       <c r="AA84" s="14" t="inlineStr"/>
       <c r="AB84" s="14" t="inlineStr"/>
       <c r="AC84" s="15" t="n">
-        <v>0.7789141414141414</v>
+        <v>0.8595959595959596</v>
       </c>
       <c r="AD84" s="15" t="inlineStr"/>
       <c r="AE84" s="14" t="n">
-        <v>6.4787E7</v>
+        <v>4.1144E7</v>
       </c>
       <c r="AF84" s="14" t="inlineStr"/>
       <c r="AG84" s="14" t="inlineStr"/>
@@ -5508,20 +5508,20 @@
         <v>3.3948E7</v>
       </c>
       <c r="X85" s="14" t="n">
-        <v>0.0</v>
+        <v>3280000.0</v>
       </c>
       <c r="Y85" s="14" t="inlineStr"/>
       <c r="Z85" s="14" t="n">
-        <v>3.3948E7</v>
+        <v>3.7228E7</v>
       </c>
       <c r="AA85" s="14" t="inlineStr"/>
       <c r="AB85" s="14" t="inlineStr"/>
       <c r="AC85" s="15" t="n">
-        <v>0.69</v>
+        <v>0.7566666666666667</v>
       </c>
       <c r="AD85" s="15" t="inlineStr"/>
       <c r="AE85" s="14" t="n">
-        <v>1.5252E7</v>
+        <v>1.1972E7</v>
       </c>
       <c r="AF85" s="14" t="inlineStr"/>
       <c r="AG85" s="14" t="inlineStr"/>
@@ -6082,20 +6082,20 @@
         <v>5.93914035E8</v>
       </c>
       <c r="X95" s="14" t="n">
-        <v>0.0</v>
+        <v>2.694E7</v>
       </c>
       <c r="Y95" s="14" t="inlineStr"/>
       <c r="Z95" s="14" t="n">
-        <v>5.93914035E8</v>
+        <v>6.20854035E8</v>
       </c>
       <c r="AA95" s="14" t="inlineStr"/>
       <c r="AB95" s="14" t="inlineStr"/>
       <c r="AC95" s="15" t="n">
-        <v>0.6139331677334524</v>
+        <v>0.6417812375955145</v>
       </c>
       <c r="AD95" s="15" t="inlineStr"/>
       <c r="AE95" s="14" t="n">
-        <v>3.73477965E8</v>
+        <v>3.46537965E8</v>
       </c>
       <c r="AF95" s="14" t="inlineStr"/>
       <c r="AG95" s="14" t="inlineStr"/>
@@ -6745,20 +6745,20 @@
         <v>3.0833E7</v>
       </c>
       <c r="X106" s="14" t="n">
-        <v>0.0</v>
+        <v>2.694E7</v>
       </c>
       <c r="Y106" s="14" t="inlineStr"/>
       <c r="Z106" s="14" t="n">
-        <v>3.0833E7</v>
+        <v>5.7773E7</v>
       </c>
       <c r="AA106" s="14" t="inlineStr"/>
       <c r="AB106" s="14" t="inlineStr"/>
       <c r="AC106" s="15" t="n">
-        <v>0.3713029865125241</v>
+        <v>0.6957249518304431</v>
       </c>
       <c r="AD106" s="15" t="inlineStr"/>
       <c r="AE106" s="14" t="n">
-        <v>5.2207E7</v>
+        <v>2.5267E7</v>
       </c>
       <c r="AF106" s="14" t="inlineStr"/>
       <c r="AG106" s="14" t="inlineStr"/>
@@ -6802,20 +6802,20 @@
         <v>8855000.0</v>
       </c>
       <c r="X107" s="14" t="n">
-        <v>0.0</v>
+        <v>7700000.0</v>
       </c>
       <c r="Y107" s="14" t="inlineStr"/>
       <c r="Z107" s="14" t="n">
-        <v>8855000.0</v>
+        <v>1.6555E7</v>
       </c>
       <c r="AA107" s="14" t="inlineStr"/>
       <c r="AB107" s="14" t="inlineStr"/>
       <c r="AC107" s="15" t="n">
-        <v>0.38333333333333336</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="AD107" s="15" t="inlineStr"/>
       <c r="AE107" s="14" t="n">
-        <v>1.4245E7</v>
+        <v>6545000.0</v>
       </c>
       <c r="AF107" s="14" t="inlineStr"/>
       <c r="AG107" s="14" t="inlineStr"/>
@@ -6859,20 +6859,20 @@
         <v>2.1978E7</v>
       </c>
       <c r="X108" s="14" t="n">
-        <v>0.0</v>
+        <v>1.924E7</v>
       </c>
       <c r="Y108" s="14" t="inlineStr"/>
       <c r="Z108" s="14" t="n">
-        <v>2.1978E7</v>
+        <v>4.1218E7</v>
       </c>
       <c r="AA108" s="14" t="inlineStr"/>
       <c r="AB108" s="14" t="inlineStr"/>
       <c r="AC108" s="15" t="n">
-        <v>0.36666666666666664</v>
+        <v>0.6876543209876543</v>
       </c>
       <c r="AD108" s="15" t="inlineStr"/>
       <c r="AE108" s="14" t="n">
-        <v>3.7962E7</v>
+        <v>1.8722E7</v>
       </c>
       <c r="AF108" s="14" t="inlineStr"/>
       <c r="AG108" s="14" t="inlineStr"/>
@@ -7162,20 +7162,20 @@
         <v>5.0689888E10</v>
       </c>
       <c r="X113" s="14" t="n">
-        <v>0.0</v>
+        <v>2.18452E8</v>
       </c>
       <c r="Y113" s="14" t="inlineStr"/>
       <c r="Z113" s="14" t="n">
-        <v>5.0689888E10</v>
+        <v>5.090834E10</v>
       </c>
       <c r="AA113" s="14" t="inlineStr"/>
       <c r="AB113" s="14" t="inlineStr"/>
       <c r="AC113" s="15" t="n">
-        <v>0.9193436738595991</v>
+        <v>0.9233056566566804</v>
       </c>
       <c r="AD113" s="15" t="inlineStr"/>
       <c r="AE113" s="14" t="n">
-        <v>4.447151E9</v>
+        <v>4.228699E9</v>
       </c>
       <c r="AF113" s="14" t="inlineStr"/>
       <c r="AG113" s="14" t="inlineStr"/>
@@ -8906,20 +8906,20 @@
         <v>2.213268E9</v>
       </c>
       <c r="X143" s="14" t="n">
-        <v>0.0</v>
+        <v>2.18452E8</v>
       </c>
       <c r="Y143" s="14" t="inlineStr"/>
       <c r="Z143" s="14" t="n">
-        <v>2.213268E9</v>
+        <v>2.43172E9</v>
       </c>
       <c r="AA143" s="14" t="inlineStr"/>
       <c r="AB143" s="14" t="inlineStr"/>
       <c r="AC143" s="15" t="n">
-        <v>0.8282097567985056</v>
+        <v>0.9099549759911868</v>
       </c>
       <c r="AD143" s="15" t="inlineStr"/>
       <c r="AE143" s="14" t="n">
-        <v>4.59084E8</v>
+        <v>2.40632E8</v>
       </c>
       <c r="AF143" s="14" t="inlineStr"/>
       <c r="AG143" s="14" t="inlineStr"/>
@@ -8963,20 +8963,20 @@
         <v>1.9894E8</v>
       </c>
       <c r="X144" s="14" t="n">
-        <v>0.0</v>
+        <v>3.0567E7</v>
       </c>
       <c r="Y144" s="14" t="inlineStr"/>
       <c r="Z144" s="14" t="n">
-        <v>1.9894E8</v>
+        <v>2.29507E8</v>
       </c>
       <c r="AA144" s="14" t="inlineStr"/>
       <c r="AB144" s="14" t="inlineStr"/>
       <c r="AC144" s="15" t="n">
-        <v>0.8166666666666667</v>
+        <v>0.9421469622331692</v>
       </c>
       <c r="AD144" s="15" t="inlineStr"/>
       <c r="AE144" s="14" t="n">
-        <v>4.466E7</v>
+        <v>1.4093E7</v>
       </c>
       <c r="AF144" s="14" t="inlineStr"/>
       <c r="AG144" s="14" t="inlineStr"/>
@@ -9063,20 +9063,20 @@
         <v>1.581491E9</v>
       </c>
       <c r="X146" s="14" t="n">
-        <v>0.0</v>
+        <v>1.59359E8</v>
       </c>
       <c r="Y146" s="14" t="inlineStr"/>
       <c r="Z146" s="14" t="n">
-        <v>1.581491E9</v>
+        <v>1.74085E9</v>
       </c>
       <c r="AA146" s="14" t="inlineStr"/>
       <c r="AB146" s="14" t="inlineStr"/>
       <c r="AC146" s="15" t="n">
-        <v>0.8283527131782946</v>
+        <v>0.9118217054263565</v>
       </c>
       <c r="AD146" s="15" t="inlineStr"/>
       <c r="AE146" s="14" t="n">
-        <v>3.27709E8</v>
+        <v>1.6835E8</v>
       </c>
       <c r="AF146" s="14" t="inlineStr"/>
       <c r="AG146" s="14" t="inlineStr"/>
@@ -9120,20 +9120,20 @@
         <v>4.32837E8</v>
       </c>
       <c r="X147" s="14" t="n">
-        <v>0.0</v>
+        <v>2.8526E7</v>
       </c>
       <c r="Y147" s="14" t="inlineStr"/>
       <c r="Z147" s="14" t="n">
-        <v>4.32837E8</v>
+        <v>4.61363E8</v>
       </c>
       <c r="AA147" s="14" t="inlineStr"/>
       <c r="AB147" s="14" t="inlineStr"/>
       <c r="AC147" s="15" t="n">
-        <v>0.8330965909090909</v>
+        <v>0.8880015859817689</v>
       </c>
       <c r="AD147" s="15" t="inlineStr"/>
       <c r="AE147" s="14" t="n">
-        <v>8.6715E7</v>
+        <v>5.8189E7</v>
       </c>
       <c r="AF147" s="14" t="inlineStr"/>
       <c r="AG147" s="14" t="inlineStr"/>
@@ -9651,20 +9651,20 @@
         <v>2.3164511208E10</v>
       </c>
       <c r="X156" s="14" t="n">
-        <v>0.0</v>
+        <v>2.45185E8</v>
       </c>
       <c r="Y156" s="14" t="inlineStr"/>
       <c r="Z156" s="14" t="n">
-        <v>2.3164511208E10</v>
+        <v>2.3409696208E10</v>
       </c>
       <c r="AA156" s="14" t="inlineStr"/>
       <c r="AB156" s="14" t="inlineStr"/>
       <c r="AC156" s="15" t="n">
-        <v>0.8595561134078443</v>
+        <v>0.8686540936662458</v>
       </c>
       <c r="AD156" s="15" t="inlineStr"/>
       <c r="AE156" s="14" t="n">
-        <v>3.784876792E9</v>
+        <v>3.539691792E9</v>
       </c>
       <c r="AF156" s="14" t="inlineStr"/>
       <c r="AG156" s="14" t="inlineStr"/>
@@ -11161,20 +11161,20 @@
         <v>1.310426E9</v>
       </c>
       <c r="X182" s="14" t="n">
-        <v>0.0</v>
+        <v>2.45185E8</v>
       </c>
       <c r="Y182" s="14" t="inlineStr"/>
       <c r="Z182" s="14" t="n">
-        <v>1.310426E9</v>
+        <v>1.555611E9</v>
       </c>
       <c r="AA182" s="14" t="inlineStr"/>
       <c r="AB182" s="14" t="inlineStr"/>
       <c r="AC182" s="15" t="n">
-        <v>0.7344778495202224</v>
+        <v>0.871901062684961</v>
       </c>
       <c r="AD182" s="15" t="inlineStr"/>
       <c r="AE182" s="14" t="n">
-        <v>4.73734E8</v>
+        <v>2.28549E8</v>
       </c>
       <c r="AF182" s="14" t="inlineStr"/>
       <c r="AG182" s="14" t="inlineStr"/>
@@ -11218,20 +11218,20 @@
         <v>1.2502E8</v>
       </c>
       <c r="X183" s="14" t="n">
-        <v>0.0</v>
+        <v>2.226E7</v>
       </c>
       <c r="Y183" s="14" t="inlineStr"/>
       <c r="Z183" s="14" t="n">
-        <v>1.2502E8</v>
+        <v>1.4728E8</v>
       </c>
       <c r="AA183" s="14" t="inlineStr"/>
       <c r="AB183" s="14" t="inlineStr"/>
       <c r="AC183" s="15" t="n">
-        <v>0.7441666666666666</v>
+        <v>0.8766666666666667</v>
       </c>
       <c r="AD183" s="15" t="inlineStr"/>
       <c r="AE183" s="14" t="n">
-        <v>4.298E7</v>
+        <v>2.072E7</v>
       </c>
       <c r="AF183" s="14" t="inlineStr"/>
       <c r="AG183" s="14" t="inlineStr"/>
@@ -11275,20 +11275,20 @@
         <v>1.185406E9</v>
       </c>
       <c r="X184" s="14" t="n">
-        <v>0.0</v>
+        <v>2.22925E8</v>
       </c>
       <c r="Y184" s="14" t="inlineStr"/>
       <c r="Z184" s="14" t="n">
-        <v>1.185406E9</v>
+        <v>1.408331E9</v>
       </c>
       <c r="AA184" s="14" t="inlineStr"/>
       <c r="AB184" s="14" t="inlineStr"/>
       <c r="AC184" s="15" t="n">
-        <v>0.7334706959706959</v>
+        <v>0.8714056776556777</v>
       </c>
       <c r="AD184" s="15" t="inlineStr"/>
       <c r="AE184" s="14" t="n">
-        <v>4.30754E8</v>
+        <v>2.07829E8</v>
       </c>
       <c r="AF184" s="14" t="inlineStr"/>
       <c r="AG184" s="14" t="inlineStr"/>
@@ -11572,20 +11572,20 @@
         <v>6.228754056E9</v>
       </c>
       <c r="X189" s="25" t="n">
-        <v>0.0</v>
+        <v>1.23936618E8</v>
       </c>
       <c r="Y189" s="25" t="inlineStr"/>
       <c r="Z189" s="25" t="n">
-        <v>6.228754056E9</v>
+        <v>6.352690674E9</v>
       </c>
       <c r="AA189" s="25" t="inlineStr"/>
       <c r="AB189" s="25" t="inlineStr"/>
       <c r="AC189" s="26" t="n">
-        <v>0.8966383810640461</v>
+        <v>0.9144792409726226</v>
       </c>
       <c r="AD189" s="26" t="inlineStr"/>
       <c r="AE189" s="25" t="n">
-        <v>7.18030944E8</v>
+        <v>5.94094326E8</v>
       </c>
       <c r="AF189" s="25" t="inlineStr"/>
       <c r="AG189" s="25" t="inlineStr"/>
@@ -11635,20 +11635,20 @@
         <v>4.783558496E9</v>
       </c>
       <c r="X190" s="14" t="n">
-        <v>0.0</v>
+        <v>9.108618E7</v>
       </c>
       <c r="Y190" s="14" t="inlineStr"/>
       <c r="Z190" s="14" t="n">
-        <v>4.783558496E9</v>
+        <v>4.874644676E9</v>
       </c>
       <c r="AA190" s="14" t="inlineStr"/>
       <c r="AB190" s="14" t="inlineStr"/>
       <c r="AC190" s="15" t="n">
-        <v>0.9567038542283953</v>
+        <v>0.9749209408482851</v>
       </c>
       <c r="AD190" s="15" t="inlineStr"/>
       <c r="AE190" s="14" t="n">
-        <v>2.16482504E8</v>
+        <v>1.25396324E8</v>
       </c>
       <c r="AF190" s="14" t="inlineStr"/>
       <c r="AG190" s="14" t="inlineStr"/>
@@ -11698,20 +11698,20 @@
         <v>1.777909494E9</v>
       </c>
       <c r="X191" s="14" t="n">
-        <v>0.0</v>
+        <v>5.2653912E7</v>
       </c>
       <c r="Y191" s="14" t="inlineStr"/>
       <c r="Z191" s="14" t="n">
-        <v>1.777909494E9</v>
+        <v>1.830563406E9</v>
       </c>
       <c r="AA191" s="14" t="inlineStr"/>
       <c r="AB191" s="14" t="inlineStr"/>
       <c r="AC191" s="15" t="n">
-        <v>0.9402863915439728</v>
+        <v>0.9681335666011042</v>
       </c>
       <c r="AD191" s="15" t="inlineStr"/>
       <c r="AE191" s="14" t="n">
-        <v>1.12907506E8</v>
+        <v>6.0253594E7</v>
       </c>
       <c r="AF191" s="14" t="inlineStr"/>
       <c r="AG191" s="14" t="inlineStr"/>
@@ -11869,20 +11869,20 @@
         <v>5.5184254E7</v>
       </c>
       <c r="X194" s="14" t="n">
-        <v>0.0</v>
+        <v>3953112.0</v>
       </c>
       <c r="Y194" s="14" t="inlineStr"/>
       <c r="Z194" s="14" t="n">
-        <v>5.5184254E7</v>
+        <v>5.9137366E7</v>
       </c>
       <c r="AA194" s="14" t="inlineStr"/>
       <c r="AB194" s="14" t="inlineStr"/>
       <c r="AC194" s="15" t="n">
-        <v>0.587504034919621</v>
+        <v>0.6295897583306718</v>
       </c>
       <c r="AD194" s="15" t="inlineStr"/>
       <c r="AE194" s="14" t="n">
-        <v>3.8745746E7</v>
+        <v>3.4792634E7</v>
       </c>
       <c r="AF194" s="14" t="inlineStr"/>
       <c r="AG194" s="14" t="inlineStr"/>
@@ -12154,20 +12154,20 @@
         <v>4.87008E7</v>
       </c>
       <c r="X199" s="14" t="n">
-        <v>0.0</v>
+        <v>4.87008E7</v>
       </c>
       <c r="Y199" s="14" t="inlineStr"/>
       <c r="Z199" s="14" t="n">
-        <v>4.87008E7</v>
+        <v>9.74016E7</v>
       </c>
       <c r="AA199" s="14" t="inlineStr"/>
       <c r="AB199" s="14" t="inlineStr"/>
       <c r="AC199" s="15" t="n">
-        <v>0.48970135746606336</v>
+        <v>0.9794027149321267</v>
       </c>
       <c r="AD199" s="15" t="inlineStr"/>
       <c r="AE199" s="14" t="n">
-        <v>5.07492E7</v>
+        <v>2048400.0</v>
       </c>
       <c r="AF199" s="14" t="inlineStr"/>
       <c r="AG199" s="14" t="inlineStr"/>
@@ -12317,20 +12317,20 @@
         <v>9417000.0</v>
       </c>
       <c r="X202" s="14" t="n">
-        <v>0.0</v>
+        <v>1380500.0</v>
       </c>
       <c r="Y202" s="14" t="inlineStr"/>
       <c r="Z202" s="14" t="n">
-        <v>9417000.0</v>
+        <v>1.07975E7</v>
       </c>
       <c r="AA202" s="14" t="inlineStr"/>
       <c r="AB202" s="14" t="inlineStr"/>
       <c r="AC202" s="15" t="n">
-        <v>0.765609756097561</v>
+        <v>0.8778455284552845</v>
       </c>
       <c r="AD202" s="15" t="inlineStr"/>
       <c r="AE202" s="14" t="n">
-        <v>2883000.0</v>
+        <v>1502500.0</v>
       </c>
       <c r="AF202" s="14" t="inlineStr"/>
       <c r="AG202" s="14" t="inlineStr"/>
@@ -12374,20 +12374,20 @@
         <v>5781000.0</v>
       </c>
       <c r="X203" s="14" t="n">
-        <v>0.0</v>
+        <v>1380500.0</v>
       </c>
       <c r="Y203" s="14" t="inlineStr"/>
       <c r="Z203" s="14" t="n">
-        <v>5781000.0</v>
+        <v>7161500.0</v>
       </c>
       <c r="AA203" s="14" t="inlineStr"/>
       <c r="AB203" s="14" t="inlineStr"/>
       <c r="AC203" s="15" t="n">
-        <v>0.7411538461538462</v>
+        <v>0.9181410256410256</v>
       </c>
       <c r="AD203" s="15" t="inlineStr"/>
       <c r="AE203" s="14" t="n">
-        <v>2019000.0</v>
+        <v>638500.0</v>
       </c>
       <c r="AF203" s="14" t="inlineStr"/>
       <c r="AG203" s="14" t="inlineStr"/>
@@ -12791,20 +12791,20 @@
         <v>2.936691192E9</v>
       </c>
       <c r="X210" s="14" t="n">
-        <v>0.0</v>
+        <v>3.7051768E7</v>
       </c>
       <c r="Y210" s="14" t="inlineStr"/>
       <c r="Z210" s="14" t="n">
-        <v>2.936691192E9</v>
+        <v>2.97374296E9</v>
       </c>
       <c r="AA210" s="14" t="inlineStr"/>
       <c r="AB210" s="14" t="inlineStr"/>
       <c r="AC210" s="15" t="n">
-        <v>0.9752016996926314</v>
+        <v>0.987505665199338</v>
       </c>
       <c r="AD210" s="15" t="inlineStr"/>
       <c r="AE210" s="14" t="n">
-        <v>7.4676808E7</v>
+        <v>3.762504E7</v>
       </c>
       <c r="AF210" s="14" t="inlineStr"/>
       <c r="AG210" s="14" t="inlineStr"/>
@@ -12905,20 +12905,20 @@
         <v>1.0331888E8</v>
       </c>
       <c r="X212" s="14" t="n">
-        <v>0.0</v>
+        <v>9468528.0</v>
       </c>
       <c r="Y212" s="14" t="inlineStr"/>
       <c r="Z212" s="14" t="n">
-        <v>1.0331888E8</v>
+        <v>1.12787408E8</v>
       </c>
       <c r="AA212" s="14" t="inlineStr"/>
       <c r="AB212" s="14" t="inlineStr"/>
       <c r="AC212" s="15" t="n">
-        <v>0.842731484502447</v>
+        <v>0.9199625448613377</v>
       </c>
       <c r="AD212" s="15" t="inlineStr"/>
       <c r="AE212" s="14" t="n">
-        <v>1.928112E7</v>
+        <v>9812592.0</v>
       </c>
       <c r="AF212" s="14" t="inlineStr"/>
       <c r="AG212" s="14" t="inlineStr"/>
@@ -13133,20 +13133,20 @@
         <v>2.2953312E7</v>
       </c>
       <c r="X216" s="14" t="n">
-        <v>0.0</v>
+        <v>2.2953312E7</v>
       </c>
       <c r="Y216" s="14" t="inlineStr"/>
       <c r="Z216" s="14" t="n">
-        <v>2.2953312E7</v>
+        <v>4.5906624E7</v>
       </c>
       <c r="AA216" s="14" t="inlineStr"/>
       <c r="AB216" s="14" t="inlineStr"/>
       <c r="AC216" s="15" t="n">
-        <v>0.33313950653120467</v>
+        <v>0.6662790130624093</v>
       </c>
       <c r="AD216" s="15" t="inlineStr"/>
       <c r="AE216" s="14" t="n">
-        <v>4.5946688E7</v>
+        <v>2.2993376E7</v>
       </c>
       <c r="AF216" s="14" t="inlineStr"/>
       <c r="AG216" s="14" t="inlineStr"/>
@@ -13190,20 +13190,20 @@
         <v>4629928.0</v>
       </c>
       <c r="X217" s="14" t="n">
-        <v>0.0</v>
+        <v>4629928.0</v>
       </c>
       <c r="Y217" s="14" t="inlineStr"/>
       <c r="Z217" s="14" t="n">
-        <v>4629928.0</v>
+        <v>9259856.0</v>
       </c>
       <c r="AA217" s="14" t="inlineStr"/>
       <c r="AB217" s="14" t="inlineStr"/>
       <c r="AC217" s="15" t="n">
-        <v>0.33332814974802016</v>
+        <v>0.6666562994960403</v>
       </c>
       <c r="AD217" s="15" t="inlineStr"/>
       <c r="AE217" s="14" t="n">
-        <v>9260072.0</v>
+        <v>4630144.0</v>
       </c>
       <c r="AF217" s="14" t="inlineStr"/>
       <c r="AG217" s="14" t="inlineStr"/>
@@ -13253,20 +13253,20 @@
         <v>6.39842407E8</v>
       </c>
       <c r="X218" s="14" t="n">
-        <v>0.0</v>
+        <v>604300.0</v>
       </c>
       <c r="Y218" s="14" t="inlineStr"/>
       <c r="Z218" s="14" t="n">
-        <v>6.39842407E8</v>
+        <v>6.40446707E8</v>
       </c>
       <c r="AA218" s="14" t="inlineStr"/>
       <c r="AB218" s="14" t="inlineStr"/>
       <c r="AC218" s="15" t="n">
-        <v>0.9138725847825591</v>
+        <v>0.9147356929431659</v>
       </c>
       <c r="AD218" s="15" t="inlineStr"/>
       <c r="AE218" s="14" t="n">
-        <v>6.0301593E7</v>
+        <v>5.9697293E7</v>
       </c>
       <c r="AF218" s="14" t="inlineStr"/>
       <c r="AG218" s="14" t="inlineStr"/>
@@ -13556,20 +13556,20 @@
         <v>3.08218E7</v>
       </c>
       <c r="X223" s="14" t="n">
-        <v>0.0</v>
+        <v>604300.0</v>
       </c>
       <c r="Y223" s="14" t="inlineStr"/>
       <c r="Z223" s="14" t="n">
-        <v>3.08218E7</v>
+        <v>3.14261E7</v>
       </c>
       <c r="AA223" s="14" t="inlineStr"/>
       <c r="AB223" s="14" t="inlineStr"/>
       <c r="AC223" s="15" t="n">
-        <v>0.9215943069010883</v>
+        <v>0.9396633177849539</v>
       </c>
       <c r="AD223" s="15" t="inlineStr"/>
       <c r="AE223" s="14" t="n">
-        <v>2622200.0</v>
+        <v>2017900.0</v>
       </c>
       <c r="AF223" s="14" t="inlineStr"/>
       <c r="AG223" s="14" t="inlineStr"/>
@@ -13613,20 +13613,20 @@
         <v>3.08218E7</v>
       </c>
       <c r="X224" s="14" t="n">
-        <v>0.0</v>
+        <v>604300.0</v>
       </c>
       <c r="Y224" s="14" t="inlineStr"/>
       <c r="Z224" s="14" t="n">
-        <v>3.08218E7</v>
+        <v>3.14261E7</v>
       </c>
       <c r="AA224" s="14" t="inlineStr"/>
       <c r="AB224" s="14" t="inlineStr"/>
       <c r="AC224" s="15" t="n">
-        <v>0.9215943069010883</v>
+        <v>0.9396633177849539</v>
       </c>
       <c r="AD224" s="15" t="inlineStr"/>
       <c r="AE224" s="14" t="n">
-        <v>2622200.0</v>
+        <v>2017900.0</v>
       </c>
       <c r="AF224" s="14" t="inlineStr"/>
       <c r="AG224" s="14" t="inlineStr"/>
@@ -13896,20 +13896,20 @@
         <v>6.74613153E8</v>
       </c>
       <c r="X229" s="14" t="n">
-        <v>0.0</v>
+        <v>3.1766138E7</v>
       </c>
       <c r="Y229" s="14" t="inlineStr"/>
       <c r="Z229" s="14" t="n">
-        <v>6.74613153E8</v>
+        <v>7.06379291E8</v>
       </c>
       <c r="AA229" s="14" t="inlineStr"/>
       <c r="AB229" s="14" t="inlineStr"/>
       <c r="AC229" s="15" t="n">
-        <v>0.6053491080562086</v>
+        <v>0.6338537454460617</v>
       </c>
       <c r="AD229" s="15" t="inlineStr"/>
       <c r="AE229" s="14" t="n">
-        <v>4.39806847E8</v>
+        <v>4.08040709E8</v>
       </c>
       <c r="AF229" s="14" t="inlineStr"/>
       <c r="AG229" s="14" t="inlineStr"/>
@@ -14256,20 +14256,20 @@
         <v>1.34221533E8</v>
       </c>
       <c r="X235" s="14" t="n">
-        <v>0.0</v>
+        <v>2.5076E7</v>
       </c>
       <c r="Y235" s="14" t="inlineStr"/>
       <c r="Z235" s="14" t="n">
-        <v>1.34221533E8</v>
+        <v>1.59297533E8</v>
       </c>
       <c r="AA235" s="14" t="inlineStr"/>
       <c r="AB235" s="14" t="inlineStr"/>
       <c r="AC235" s="15" t="n">
-        <v>0.36169536500579375</v>
+        <v>0.4292692689105069</v>
       </c>
       <c r="AD235" s="15" t="inlineStr"/>
       <c r="AE235" s="14" t="n">
-        <v>2.36868467E8</v>
+        <v>2.11792467E8</v>
       </c>
       <c r="AF235" s="14" t="inlineStr"/>
       <c r="AG235" s="14" t="inlineStr"/>
@@ -14541,20 +14541,20 @@
         <v>4421000.0</v>
       </c>
       <c r="X240" s="14" t="n">
-        <v>0.0</v>
+        <v>2.5076E7</v>
       </c>
       <c r="Y240" s="14" t="inlineStr"/>
       <c r="Z240" s="14" t="n">
-        <v>4421000.0</v>
+        <v>2.9497E7</v>
       </c>
       <c r="AA240" s="14" t="inlineStr"/>
       <c r="AB240" s="14" t="inlineStr"/>
       <c r="AC240" s="15" t="n">
-        <v>0.03296793437733035</v>
+        <v>0.2199627143922446</v>
       </c>
       <c r="AD240" s="15" t="inlineStr"/>
       <c r="AE240" s="14" t="n">
-        <v>1.29679E8</v>
+        <v>1.04603E8</v>
       </c>
       <c r="AF240" s="14" t="inlineStr"/>
       <c r="AG240" s="14" t="inlineStr"/>
@@ -15231,20 +15231,20 @@
         <v>2.11521335E8</v>
       </c>
       <c r="X252" s="14" t="n">
-        <v>0.0</v>
+        <v>6690138.0</v>
       </c>
       <c r="Y252" s="14" t="inlineStr"/>
       <c r="Z252" s="14" t="n">
-        <v>2.11521335E8</v>
+        <v>2.18211473E8</v>
       </c>
       <c r="AA252" s="14" t="inlineStr"/>
       <c r="AB252" s="14" t="inlineStr"/>
       <c r="AC252" s="15" t="n">
-        <v>0.6409737424242424</v>
+        <v>0.6612468878787878</v>
       </c>
       <c r="AD252" s="15" t="inlineStr"/>
       <c r="AE252" s="14" t="n">
-        <v>1.18478665E8</v>
+        <v>1.11788527E8</v>
       </c>
       <c r="AF252" s="14" t="inlineStr"/>
       <c r="AG252" s="14" t="inlineStr"/>
@@ -15288,20 +15288,20 @@
         <v>1.396E7</v>
       </c>
       <c r="X253" s="14" t="n">
-        <v>0.0</v>
+        <v>2890000.0</v>
       </c>
       <c r="Y253" s="14" t="inlineStr"/>
       <c r="Z253" s="14" t="n">
-        <v>1.396E7</v>
+        <v>1.685E7</v>
       </c>
       <c r="AA253" s="14" t="inlineStr"/>
       <c r="AB253" s="14" t="inlineStr"/>
       <c r="AC253" s="15" t="n">
-        <v>0.618520159503766</v>
+        <v>0.7465662383695171</v>
       </c>
       <c r="AD253" s="15" t="inlineStr"/>
       <c r="AE253" s="14" t="n">
-        <v>8610000.0</v>
+        <v>5720000.0</v>
       </c>
       <c r="AF253" s="14" t="inlineStr"/>
       <c r="AG253" s="14" t="inlineStr"/>
@@ -15502,20 +15502,20 @@
         <v>1.22043496E8</v>
       </c>
       <c r="X257" s="14" t="n">
-        <v>0.0</v>
+        <v>1490000.0</v>
       </c>
       <c r="Y257" s="14" t="inlineStr"/>
       <c r="Z257" s="14" t="n">
-        <v>1.22043496E8</v>
+        <v>1.23533496E8</v>
       </c>
       <c r="AA257" s="14" t="inlineStr"/>
       <c r="AB257" s="14" t="inlineStr"/>
       <c r="AC257" s="15" t="n">
-        <v>0.7189602120765832</v>
+        <v>0.7277378262150221</v>
       </c>
       <c r="AD257" s="15" t="inlineStr"/>
       <c r="AE257" s="14" t="n">
-        <v>4.7706504E7</v>
+        <v>4.6216504E7</v>
       </c>
       <c r="AF257" s="14" t="inlineStr"/>
       <c r="AG257" s="14" t="inlineStr"/>
@@ -15901,20 +15901,20 @@
         <v>3760846.0</v>
       </c>
       <c r="X264" s="14" t="n">
-        <v>0.0</v>
+        <v>1560138.0</v>
       </c>
       <c r="Y264" s="14" t="inlineStr"/>
       <c r="Z264" s="14" t="n">
-        <v>3760846.0</v>
+        <v>5320984.0</v>
       </c>
       <c r="AA264" s="14" t="inlineStr"/>
       <c r="AB264" s="14" t="inlineStr"/>
       <c r="AC264" s="15" t="n">
-        <v>0.24077119078104994</v>
+        <v>0.3406519846350832</v>
       </c>
       <c r="AD264" s="15" t="inlineStr"/>
       <c r="AE264" s="14" t="n">
-        <v>1.1859154E7</v>
+        <v>1.0299016E7</v>
       </c>
       <c r="AF264" s="14" t="inlineStr"/>
       <c r="AG264" s="14" t="inlineStr"/>
@@ -16129,20 +16129,20 @@
         <v>0.0</v>
       </c>
       <c r="X268" s="14" t="n">
-        <v>0.0</v>
+        <v>750000.0</v>
       </c>
       <c r="Y268" s="14" t="inlineStr"/>
       <c r="Z268" s="14" t="n">
-        <v>0.0</v>
+        <v>750000.0</v>
       </c>
       <c r="AA268" s="14" t="inlineStr"/>
       <c r="AB268" s="14" t="inlineStr"/>
       <c r="AC268" s="15" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="AD268" s="15" t="inlineStr"/>
       <c r="AE268" s="14" t="n">
-        <v>1500000.0</v>
+        <v>750000.0</v>
       </c>
       <c r="AF268" s="14" t="inlineStr"/>
       <c r="AG268" s="14" t="inlineStr"/>
@@ -16426,20 +16426,20 @@
         <v>1.3074E8</v>
       </c>
       <c r="X273" s="14" t="n">
-        <v>0.0</v>
+        <v>480000.0</v>
       </c>
       <c r="Y273" s="14" t="inlineStr"/>
       <c r="Z273" s="14" t="n">
-        <v>1.3074E8</v>
+        <v>1.3122E8</v>
       </c>
       <c r="AA273" s="14" t="inlineStr"/>
       <c r="AB273" s="14" t="inlineStr"/>
       <c r="AC273" s="15" t="n">
-        <v>0.9891057648660917</v>
+        <v>0.9927371765773945</v>
       </c>
       <c r="AD273" s="15" t="inlineStr"/>
       <c r="AE273" s="14" t="n">
-        <v>1440000.0</v>
+        <v>960000.0</v>
       </c>
       <c r="AF273" s="14" t="inlineStr"/>
       <c r="AG273" s="14" t="inlineStr"/>
@@ -16489,20 +16489,20 @@
         <v>1.2324E8</v>
       </c>
       <c r="X274" s="14" t="n">
-        <v>0.0</v>
+        <v>480000.0</v>
       </c>
       <c r="Y274" s="14" t="inlineStr"/>
       <c r="Z274" s="14" t="n">
-        <v>1.2324E8</v>
+        <v>1.2372E8</v>
       </c>
       <c r="AA274" s="14" t="inlineStr"/>
       <c r="AB274" s="14" t="inlineStr"/>
       <c r="AC274" s="15" t="n">
-        <v>0.9884504331087585</v>
+        <v>0.9923002887391723</v>
       </c>
       <c r="AD274" s="15" t="inlineStr"/>
       <c r="AE274" s="14" t="n">
-        <v>1440000.0</v>
+        <v>960000.0</v>
       </c>
       <c r="AF274" s="14" t="inlineStr"/>
       <c r="AG274" s="14" t="inlineStr"/>
@@ -16831,20 +16831,20 @@
         <v>2700000.0</v>
       </c>
       <c r="X280" s="14" t="n">
-        <v>0.0</v>
+        <v>300000.0</v>
       </c>
       <c r="Y280" s="14" t="inlineStr"/>
       <c r="Z280" s="14" t="n">
-        <v>2700000.0</v>
+        <v>3000000.0</v>
       </c>
       <c r="AA280" s="14" t="inlineStr"/>
       <c r="AB280" s="14" t="inlineStr"/>
       <c r="AC280" s="15" t="n">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AD280" s="15" t="inlineStr"/>
       <c r="AE280" s="14" t="n">
-        <v>900000.0</v>
+        <v>600000.0</v>
       </c>
       <c r="AF280" s="14" t="inlineStr"/>
       <c r="AG280" s="14" t="inlineStr"/>
@@ -16931,20 +16931,20 @@
         <v>3780000.0</v>
       </c>
       <c r="X282" s="14" t="n">
-        <v>0.0</v>
+        <v>180000.0</v>
       </c>
       <c r="Y282" s="14" t="inlineStr"/>
       <c r="Z282" s="14" t="n">
-        <v>3780000.0</v>
+        <v>3960000.0</v>
       </c>
       <c r="AA282" s="14" t="inlineStr"/>
       <c r="AB282" s="14" t="inlineStr"/>
       <c r="AC282" s="15" t="n">
-        <v>0.875</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="AD282" s="15" t="inlineStr"/>
       <c r="AE282" s="14" t="n">
-        <v>540000.0</v>
+        <v>360000.0</v>
       </c>
       <c r="AF282" s="14" t="inlineStr"/>
       <c r="AG282" s="14" t="inlineStr"/>

--- a/Database/Akrual.xlsx
+++ b/Database/Akrual.xlsx
@@ -982,19 +982,19 @@
         <v>9.0559784495E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>6.42836618E8</v>
+        <v>6.68137418E8</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>9.1202621113E10</v>
+        <v>9.1227921913E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.9120623470401897</v>
+        <v>0.9123153650647639</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>8.793416887E9</v>
+        <v>8.768116087E9</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1714,20 +1714,20 @@
         <v>8.6526416455E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>6.42836618E8</v>
+        <v>6.68137418E8</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>8.7169253073E10</v>
+        <v>8.7194553873E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.9083665777612324</v>
+        <v>0.9086302303715327</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>8.793384927E9</v>
+        <v>8.768084127E9</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1777,20 +1777,20 @@
         <v>8.6526416455E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>6.42836618E8</v>
+        <v>6.68137418E8</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>8.7169253073E10</v>
+        <v>8.7194553873E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.9083665777612324</v>
+        <v>0.9086302303715327</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>8.793384927E9</v>
+        <v>8.768084127E9</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1840,20 +1840,20 @@
         <v>8.6525816455E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>6.42836618E8</v>
+        <v>6.68137418E8</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>8.7168653073E10</v>
+        <v>8.7193953873E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.9083660048257833</v>
+        <v>0.9086296590845643</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>8.793384927E9</v>
+        <v>8.768084127E9</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -3233,20 +3233,20 @@
         <v>8.6508305403E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>6.42836618E8</v>
+        <v>6.68137418E8</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>8.7151142021E10</v>
+        <v>8.7176442821E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.9083589274325887</v>
+        <v>0.9086226326120992</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>8.792365979E9</v>
+        <v>8.767065179E9</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -4154,7 +4154,7 @@
       <c r="O62" s="13" t="inlineStr"/>
       <c r="P62" s="13" t="inlineStr"/>
       <c r="Q62" s="14" t="n">
-        <v>5.3276E7</v>
+        <v>5.3132E7</v>
       </c>
       <c r="R62" s="14" t="inlineStr"/>
       <c r="S62" s="14" t="n">
@@ -4176,11 +4176,11 @@
       <c r="AA62" s="14" t="inlineStr"/>
       <c r="AB62" s="14" t="inlineStr"/>
       <c r="AC62" s="15" t="n">
-        <v>0.9968937607928523</v>
+        <v>0.9995955732891666</v>
       </c>
       <c r="AD62" s="15" t="inlineStr"/>
       <c r="AE62" s="14" t="n">
-        <v>165488.0</v>
+        <v>21488.0</v>
       </c>
       <c r="AF62" s="14" t="inlineStr"/>
       <c r="AG62" s="14" t="inlineStr"/>
@@ -4211,7 +4211,7 @@
       <c r="O63" s="13" t="inlineStr"/>
       <c r="P63" s="13" t="inlineStr"/>
       <c r="Q63" s="14" t="n">
-        <v>4.5588E7</v>
+        <v>4.5444E7</v>
       </c>
       <c r="R63" s="14" t="inlineStr"/>
       <c r="S63" s="14" t="n">
@@ -4233,11 +4233,11 @@
       <c r="AA63" s="14" t="inlineStr"/>
       <c r="AB63" s="14" t="inlineStr"/>
       <c r="AC63" s="15" t="n">
-        <v>0.9966318768096868</v>
+        <v>0.9997899392659096</v>
       </c>
       <c r="AD63" s="15" t="inlineStr"/>
       <c r="AE63" s="14" t="n">
-        <v>153546.0</v>
+        <v>9546.0</v>
       </c>
       <c r="AF63" s="14" t="inlineStr"/>
       <c r="AG63" s="14" t="inlineStr"/>
@@ -4856,7 +4856,7 @@
       <c r="O74" s="13" t="inlineStr"/>
       <c r="P74" s="13" t="inlineStr"/>
       <c r="Q74" s="14" t="n">
-        <v>2.016E7</v>
+        <v>2.0304E7</v>
       </c>
       <c r="R74" s="14" t="inlineStr"/>
       <c r="S74" s="14" t="n">
@@ -4878,11 +4878,11 @@
       <c r="AA74" s="14" t="inlineStr"/>
       <c r="AB74" s="14" t="inlineStr"/>
       <c r="AC74" s="15" t="n">
-        <v>1.0054437003968253</v>
+        <v>0.9983128940110323</v>
       </c>
       <c r="AD74" s="15" t="inlineStr"/>
       <c r="AE74" s="14" t="n">
-        <v>-109745.0</v>
+        <v>34255.0</v>
       </c>
       <c r="AF74" s="14" t="inlineStr"/>
       <c r="AG74" s="14" t="inlineStr"/>
@@ -4913,7 +4913,7 @@
       <c r="O75" s="13" t="inlineStr"/>
       <c r="P75" s="13" t="inlineStr"/>
       <c r="Q75" s="14" t="n">
-        <v>2616000.0</v>
+        <v>2760000.0</v>
       </c>
       <c r="R75" s="14" t="inlineStr"/>
       <c r="S75" s="14" t="n">
@@ -4935,11 +4935,11 @@
       <c r="AA75" s="14" t="inlineStr"/>
       <c r="AB75" s="14" t="inlineStr"/>
       <c r="AC75" s="15" t="n">
-        <v>1.046914755351682</v>
+        <v>0.992293115942029</v>
       </c>
       <c r="AD75" s="15" t="inlineStr"/>
       <c r="AE75" s="14" t="n">
-        <v>-122729.0</v>
+        <v>21271.0</v>
       </c>
       <c r="AF75" s="14" t="inlineStr"/>
       <c r="AG75" s="14" t="inlineStr"/>
@@ -6132,7 +6132,7 @@
       <c r="O96" s="13" t="inlineStr"/>
       <c r="P96" s="13" t="inlineStr"/>
       <c r="Q96" s="14" t="n">
-        <v>3.47283E8</v>
+        <v>3.4728E8</v>
       </c>
       <c r="R96" s="14" t="inlineStr"/>
       <c r="S96" s="14" t="n">
@@ -6154,11 +6154,11 @@
       <c r="AA96" s="14" t="inlineStr"/>
       <c r="AB96" s="14" t="inlineStr"/>
       <c r="AC96" s="15" t="n">
-        <v>0.9969575245549019</v>
+        <v>0.9969661368348307</v>
       </c>
       <c r="AD96" s="15" t="inlineStr"/>
       <c r="AE96" s="14" t="n">
-        <v>1056600.0</v>
+        <v>1053600.0</v>
       </c>
       <c r="AF96" s="14" t="inlineStr"/>
       <c r="AG96" s="14" t="inlineStr"/>
@@ -6189,7 +6189,7 @@
       <c r="O97" s="13" t="inlineStr"/>
       <c r="P97" s="13" t="inlineStr"/>
       <c r="Q97" s="14" t="n">
-        <v>3.47283E8</v>
+        <v>3.4728E8</v>
       </c>
       <c r="R97" s="14" t="inlineStr"/>
       <c r="S97" s="14" t="n">
@@ -6211,11 +6211,11 @@
       <c r="AA97" s="14" t="inlineStr"/>
       <c r="AB97" s="14" t="inlineStr"/>
       <c r="AC97" s="15" t="n">
-        <v>0.9969575245549019</v>
+        <v>0.9969661368348307</v>
       </c>
       <c r="AD97" s="15" t="inlineStr"/>
       <c r="AE97" s="14" t="n">
-        <v>1056600.0</v>
+        <v>1053600.0</v>
       </c>
       <c r="AF97" s="14" t="inlineStr"/>
       <c r="AG97" s="14" t="inlineStr"/>
@@ -6252,7 +6252,7 @@
       <c r="O98" s="13" t="inlineStr"/>
       <c r="P98" s="13" t="inlineStr"/>
       <c r="Q98" s="14" t="n">
-        <v>6000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="R98" s="14" t="inlineStr"/>
       <c r="S98" s="14" t="n">
@@ -6274,11 +6274,11 @@
       <c r="AA98" s="14" t="inlineStr"/>
       <c r="AB98" s="14" t="inlineStr"/>
       <c r="AC98" s="15" t="n">
-        <v>1.0598333333333334</v>
+        <v>0.7065555555555556</v>
       </c>
       <c r="AD98" s="15" t="inlineStr"/>
       <c r="AE98" s="14" t="n">
-        <v>-359.0</v>
+        <v>2641.0</v>
       </c>
       <c r="AF98" s="14" t="inlineStr"/>
       <c r="AG98" s="14" t="inlineStr"/>
@@ -6309,7 +6309,7 @@
       <c r="O99" s="13" t="inlineStr"/>
       <c r="P99" s="13" t="inlineStr"/>
       <c r="Q99" s="14" t="n">
-        <v>6000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="R99" s="14" t="inlineStr"/>
       <c r="S99" s="14" t="n">
@@ -6331,11 +6331,11 @@
       <c r="AA99" s="14" t="inlineStr"/>
       <c r="AB99" s="14" t="inlineStr"/>
       <c r="AC99" s="15" t="n">
-        <v>1.0598333333333334</v>
+        <v>0.7065555555555556</v>
       </c>
       <c r="AD99" s="15" t="inlineStr"/>
       <c r="AE99" s="14" t="n">
-        <v>-359.0</v>
+        <v>2641.0</v>
       </c>
       <c r="AF99" s="14" t="inlineStr"/>
       <c r="AG99" s="14" t="inlineStr"/>
@@ -7212,7 +7212,7 @@
       <c r="O114" s="13" t="inlineStr"/>
       <c r="P114" s="13" t="inlineStr"/>
       <c r="Q114" s="14" t="n">
-        <v>1.7108339E10</v>
+        <v>1.7101139E10</v>
       </c>
       <c r="R114" s="14" t="inlineStr"/>
       <c r="S114" s="14" t="n">
@@ -7234,11 +7234,11 @@
       <c r="AA114" s="14" t="inlineStr"/>
       <c r="AB114" s="14" t="inlineStr"/>
       <c r="AC114" s="15" t="n">
-        <v>0.9988785936495647</v>
+        <v>0.9992991460978126</v>
       </c>
       <c r="AD114" s="15" t="inlineStr"/>
       <c r="AE114" s="14" t="n">
-        <v>1.91854E7</v>
+        <v>1.19854E7</v>
       </c>
       <c r="AF114" s="14" t="inlineStr"/>
       <c r="AG114" s="14" t="inlineStr"/>
@@ -7269,7 +7269,7 @@
       <c r="O115" s="13" t="inlineStr"/>
       <c r="P115" s="13" t="inlineStr"/>
       <c r="Q115" s="14" t="n">
-        <v>1.463616E10</v>
+        <v>1.460406E10</v>
       </c>
       <c r="R115" s="14" t="inlineStr"/>
       <c r="S115" s="14" t="n">
@@ -7291,11 +7291,11 @@
       <c r="AA115" s="14" t="inlineStr"/>
       <c r="AB115" s="14" t="inlineStr"/>
       <c r="AC115" s="15" t="n">
-        <v>0.9974201019939656</v>
+        <v>0.9996124502364411</v>
       </c>
       <c r="AD115" s="15" t="inlineStr"/>
       <c r="AE115" s="14" t="n">
-        <v>3.77598E7</v>
+        <v>5659800.0</v>
       </c>
       <c r="AF115" s="14" t="inlineStr"/>
       <c r="AG115" s="14" t="inlineStr"/>
@@ -7326,7 +7326,7 @@
       <c r="O116" s="13" t="inlineStr"/>
       <c r="P116" s="13" t="inlineStr"/>
       <c r="Q116" s="14" t="n">
-        <v>1.250844E9</v>
+        <v>1.243644E9</v>
       </c>
       <c r="R116" s="14" t="inlineStr"/>
       <c r="S116" s="14" t="n">
@@ -7348,11 +7348,11 @@
       <c r="AA116" s="14" t="inlineStr"/>
       <c r="AB116" s="14" t="inlineStr"/>
       <c r="AC116" s="15" t="n">
-        <v>0.9891997723137338</v>
+        <v>0.9949266831987289</v>
       </c>
       <c r="AD116" s="15" t="inlineStr"/>
       <c r="AE116" s="14" t="n">
-        <v>1.35094E7</v>
+        <v>6309400.0</v>
       </c>
       <c r="AF116" s="14" t="inlineStr"/>
       <c r="AG116" s="14" t="inlineStr"/>
@@ -7426,7 +7426,7 @@
       <c r="O118" s="13" t="inlineStr"/>
       <c r="P118" s="13" t="inlineStr"/>
       <c r="Q118" s="14" t="n">
-        <v>1.221335E9</v>
+        <v>1.253435E9</v>
       </c>
       <c r="R118" s="14" t="inlineStr"/>
       <c r="S118" s="14" t="n">
@@ -7448,11 +7448,11 @@
       <c r="AA118" s="14" t="inlineStr"/>
       <c r="AB118" s="14" t="inlineStr"/>
       <c r="AC118" s="15" t="n">
-        <v>1.0262694510515133</v>
+        <v>0.9999870755164807</v>
       </c>
       <c r="AD118" s="15" t="inlineStr"/>
       <c r="AE118" s="14" t="n">
-        <v>-3.20838E7</v>
+        <v>16200.0</v>
       </c>
       <c r="AF118" s="14" t="inlineStr"/>
       <c r="AG118" s="14" t="inlineStr"/>
@@ -8425,7 +8425,7 @@
       <c r="O135" s="13" t="inlineStr"/>
       <c r="P135" s="13" t="inlineStr"/>
       <c r="Q135" s="14" t="n">
-        <v>2.3055E8</v>
+        <v>2.3775E8</v>
       </c>
       <c r="R135" s="14" t="inlineStr"/>
       <c r="S135" s="14" t="n">
@@ -8447,11 +8447,11 @@
       <c r="AA135" s="14" t="inlineStr"/>
       <c r="AB135" s="14" t="inlineStr"/>
       <c r="AC135" s="15" t="n">
-        <v>1.0291648275862069</v>
+        <v>0.9979976908517351</v>
       </c>
       <c r="AD135" s="15" t="inlineStr"/>
       <c r="AE135" s="14" t="n">
-        <v>-6723951.0</v>
+        <v>476049.0</v>
       </c>
       <c r="AF135" s="14" t="inlineStr"/>
       <c r="AG135" s="14" t="inlineStr"/>
@@ -8482,7 +8482,7 @@
       <c r="O136" s="13" t="inlineStr"/>
       <c r="P136" s="13" t="inlineStr"/>
       <c r="Q136" s="14" t="n">
-        <v>4.5084E7</v>
+        <v>5.2284E7</v>
       </c>
       <c r="R136" s="14" t="inlineStr"/>
       <c r="S136" s="14" t="n">
@@ -8504,11 +8504,11 @@
       <c r="AA136" s="14" t="inlineStr"/>
       <c r="AB136" s="14" t="inlineStr"/>
       <c r="AC136" s="15" t="n">
-        <v>1.1493616360571377</v>
+        <v>0.9910836967332263</v>
       </c>
       <c r="AD136" s="15" t="inlineStr"/>
       <c r="AE136" s="14" t="n">
-        <v>-6733820.0</v>
+        <v>466180.0</v>
       </c>
       <c r="AF136" s="14" t="inlineStr"/>
       <c r="AG136" s="14" t="inlineStr"/>
@@ -9935,7 +9935,7 @@
       <c r="O161" s="13" t="inlineStr"/>
       <c r="P161" s="13" t="inlineStr"/>
       <c r="Q161" s="14" t="n">
-        <v>182000.0</v>
+        <v>206000.0</v>
       </c>
       <c r="R161" s="14" t="inlineStr"/>
       <c r="S161" s="14" t="n">
@@ -9957,11 +9957,11 @@
       <c r="AA161" s="14" t="inlineStr"/>
       <c r="AB161" s="14" t="inlineStr"/>
       <c r="AC161" s="15" t="n">
-        <v>1.0657637362637362</v>
+        <v>0.9415970873786408</v>
       </c>
       <c r="AD161" s="15" t="inlineStr"/>
       <c r="AE161" s="14" t="n">
-        <v>-11969.0</v>
+        <v>12031.0</v>
       </c>
       <c r="AF161" s="14" t="inlineStr"/>
       <c r="AG161" s="14" t="inlineStr"/>
@@ -9992,7 +9992,7 @@
       <c r="O162" s="13" t="inlineStr"/>
       <c r="P162" s="13" t="inlineStr"/>
       <c r="Q162" s="14" t="n">
-        <v>168000.0</v>
+        <v>192000.0</v>
       </c>
       <c r="R162" s="14" t="inlineStr"/>
       <c r="S162" s="14" t="n">
@@ -10014,11 +10014,11 @@
       <c r="AA162" s="14" t="inlineStr"/>
       <c r="AB162" s="14" t="inlineStr"/>
       <c r="AC162" s="15" t="n">
-        <v>1.076482142857143</v>
+        <v>0.941921875</v>
       </c>
       <c r="AD162" s="15" t="inlineStr"/>
       <c r="AE162" s="14" t="n">
-        <v>-12849.0</v>
+        <v>11151.0</v>
       </c>
       <c r="AF162" s="14" t="inlineStr"/>
       <c r="AG162" s="14" t="inlineStr"/>
@@ -10169,7 +10169,7 @@
       <c r="O165" s="13" t="inlineStr"/>
       <c r="P165" s="13" t="inlineStr"/>
       <c r="Q165" s="14" t="n">
-        <v>6.40678E8</v>
+        <v>6.40654E8</v>
       </c>
       <c r="R165" s="14" t="inlineStr"/>
       <c r="S165" s="14" t="n">
@@ -10191,11 +10191,11 @@
       <c r="AA165" s="14" t="inlineStr"/>
       <c r="AB165" s="14" t="inlineStr"/>
       <c r="AC165" s="15" t="n">
-        <v>0.9750256603161026</v>
+        <v>0.9750621864532181</v>
       </c>
       <c r="AD165" s="15" t="inlineStr"/>
       <c r="AE165" s="14" t="n">
-        <v>1.600051E7</v>
+        <v>1.597651E7</v>
       </c>
       <c r="AF165" s="14" t="inlineStr"/>
       <c r="AG165" s="14" t="inlineStr"/>
@@ -10226,7 +10226,7 @@
       <c r="O166" s="13" t="inlineStr"/>
       <c r="P166" s="13" t="inlineStr"/>
       <c r="Q166" s="14" t="n">
-        <v>5.66952E8</v>
+        <v>5.66928E8</v>
       </c>
       <c r="R166" s="14" t="inlineStr"/>
       <c r="S166" s="14" t="n">
@@ -10248,11 +10248,11 @@
       <c r="AA166" s="14" t="inlineStr"/>
       <c r="AB166" s="14" t="inlineStr"/>
       <c r="AC166" s="15" t="n">
-        <v>0.9717801859769434</v>
+        <v>0.9718213247537606</v>
       </c>
       <c r="AD166" s="15" t="inlineStr"/>
       <c r="AE166" s="14" t="n">
-        <v>1.599928E7</v>
+        <v>1.597528E7</v>
       </c>
       <c r="AF166" s="14" t="inlineStr"/>
       <c r="AG166" s="14" t="inlineStr"/>
@@ -11572,20 +11572,20 @@
         <v>6.228754056E9</v>
       </c>
       <c r="X189" s="25" t="n">
-        <v>1.23936618E8</v>
+        <v>1.49237418E8</v>
       </c>
       <c r="Y189" s="25" t="inlineStr"/>
       <c r="Z189" s="25" t="n">
-        <v>6.352690674E9</v>
+        <v>6.377991474E9</v>
       </c>
       <c r="AA189" s="25" t="inlineStr"/>
       <c r="AB189" s="25" t="inlineStr"/>
       <c r="AC189" s="26" t="n">
-        <v>0.9144792409726226</v>
+        <v>0.918121328643394</v>
       </c>
       <c r="AD189" s="26" t="inlineStr"/>
       <c r="AE189" s="25" t="n">
-        <v>5.94094326E8</v>
+        <v>5.68793526E8</v>
       </c>
       <c r="AF189" s="25" t="inlineStr"/>
       <c r="AG189" s="25" t="inlineStr"/>
@@ -11622,7 +11622,7 @@
       <c r="O190" s="13" t="inlineStr"/>
       <c r="P190" s="13" t="inlineStr"/>
       <c r="Q190" s="14" t="n">
-        <v>5.000041E9</v>
+        <v>5.006041E9</v>
       </c>
       <c r="R190" s="14" t="inlineStr"/>
       <c r="S190" s="14" t="n">
@@ -11635,20 +11635,20 @@
         <v>4.783558496E9</v>
       </c>
       <c r="X190" s="14" t="n">
-        <v>9.108618E7</v>
+        <v>1.1638698E8</v>
       </c>
       <c r="Y190" s="14" t="inlineStr"/>
       <c r="Z190" s="14" t="n">
-        <v>4.874644676E9</v>
+        <v>4.899945476E9</v>
       </c>
       <c r="AA190" s="14" t="inlineStr"/>
       <c r="AB190" s="14" t="inlineStr"/>
       <c r="AC190" s="15" t="n">
-        <v>0.9749209408482851</v>
+        <v>0.9788065011852679</v>
       </c>
       <c r="AD190" s="15" t="inlineStr"/>
       <c r="AE190" s="14" t="n">
-        <v>1.25396324E8</v>
+        <v>1.06095524E8</v>
       </c>
       <c r="AF190" s="14" t="inlineStr"/>
       <c r="AG190" s="14" t="inlineStr"/>
@@ -11698,20 +11698,20 @@
         <v>1.777909494E9</v>
       </c>
       <c r="X191" s="14" t="n">
-        <v>5.2653912E7</v>
+        <v>7.7954712E7</v>
       </c>
       <c r="Y191" s="14" t="inlineStr"/>
       <c r="Z191" s="14" t="n">
-        <v>1.830563406E9</v>
+        <v>1.855864206E9</v>
       </c>
       <c r="AA191" s="14" t="inlineStr"/>
       <c r="AB191" s="14" t="inlineStr"/>
       <c r="AC191" s="15" t="n">
-        <v>0.9681335666011042</v>
+        <v>0.9815144490450425</v>
       </c>
       <c r="AD191" s="15" t="inlineStr"/>
       <c r="AE191" s="14" t="n">
-        <v>6.0253594E7</v>
+        <v>3.4952794E7</v>
       </c>
       <c r="AF191" s="14" t="inlineStr"/>
       <c r="AG191" s="14" t="inlineStr"/>
@@ -12141,7 +12141,7 @@
       <c r="O199" s="13" t="inlineStr"/>
       <c r="P199" s="13" t="inlineStr"/>
       <c r="Q199" s="14" t="n">
-        <v>9.945E7</v>
+        <v>1.2285E8</v>
       </c>
       <c r="R199" s="14" t="inlineStr"/>
       <c r="S199" s="14" t="n">
@@ -12154,20 +12154,20 @@
         <v>4.87008E7</v>
       </c>
       <c r="X199" s="14" t="n">
-        <v>4.87008E7</v>
+        <v>7.40016E7</v>
       </c>
       <c r="Y199" s="14" t="inlineStr"/>
       <c r="Z199" s="14" t="n">
-        <v>9.74016E7</v>
+        <v>1.227024E8</v>
       </c>
       <c r="AA199" s="14" t="inlineStr"/>
       <c r="AB199" s="14" t="inlineStr"/>
       <c r="AC199" s="15" t="n">
-        <v>0.9794027149321267</v>
+        <v>0.9987985347985348</v>
       </c>
       <c r="AD199" s="15" t="inlineStr"/>
       <c r="AE199" s="14" t="n">
-        <v>2048400.0</v>
+        <v>147600.0</v>
       </c>
       <c r="AF199" s="14" t="inlineStr"/>
       <c r="AG199" s="14" t="inlineStr"/>
@@ -12241,7 +12241,7 @@
       <c r="O201" s="13" t="inlineStr"/>
       <c r="P201" s="13" t="inlineStr"/>
       <c r="Q201" s="14" t="n">
-        <v>4.68E7</v>
+        <v>2.34E7</v>
       </c>
       <c r="R201" s="14" t="inlineStr"/>
       <c r="S201" s="14" t="n">
@@ -12263,11 +12263,11 @@
       <c r="AA201" s="14" t="inlineStr"/>
       <c r="AB201" s="14" t="inlineStr"/>
       <c r="AC201" s="15" t="n">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="AD201" s="15" t="inlineStr"/>
       <c r="AE201" s="14" t="n">
-        <v>2.34E7</v>
+        <v>0.0</v>
       </c>
       <c r="AF201" s="14" t="inlineStr"/>
       <c r="AG201" s="14" t="inlineStr"/>
@@ -12481,7 +12481,7 @@
       <c r="O205" s="13" t="inlineStr"/>
       <c r="P205" s="13" t="inlineStr"/>
       <c r="Q205" s="14" t="n">
-        <v>7.4556E7</v>
+        <v>8.0556E7</v>
       </c>
       <c r="R205" s="14" t="inlineStr"/>
       <c r="S205" s="14" t="n">
@@ -12503,11 +12503,11 @@
       <c r="AA205" s="14" t="inlineStr"/>
       <c r="AB205" s="14" t="inlineStr"/>
       <c r="AC205" s="15" t="n">
-        <v>0.7412684425130104</v>
+        <v>0.6860570286508764</v>
       </c>
       <c r="AD205" s="15" t="inlineStr"/>
       <c r="AE205" s="14" t="n">
-        <v>1.928999E7</v>
+        <v>2.528999E7</v>
       </c>
       <c r="AF205" s="14" t="inlineStr"/>
       <c r="AG205" s="14" t="inlineStr"/>
@@ -12538,7 +12538,7 @@
       <c r="O206" s="13" t="inlineStr"/>
       <c r="P206" s="13" t="inlineStr"/>
       <c r="Q206" s="14" t="n">
-        <v>7.4556E7</v>
+        <v>7.4476E7</v>
       </c>
       <c r="R206" s="14" t="inlineStr"/>
       <c r="S206" s="14" t="n">
@@ -12560,11 +12560,11 @@
       <c r="AA206" s="14" t="inlineStr"/>
       <c r="AB206" s="14" t="inlineStr"/>
       <c r="AC206" s="15" t="n">
-        <v>0.7412684425130104</v>
+        <v>0.7420646919813094</v>
       </c>
       <c r="AD206" s="15" t="inlineStr"/>
       <c r="AE206" s="14" t="n">
-        <v>1.928999E7</v>
+        <v>1.920999E7</v>
       </c>
       <c r="AF206" s="14" t="inlineStr"/>
       <c r="AG206" s="14" t="inlineStr"/>
@@ -12579,29 +12579,23 @@
       <c r="E207" s="2" t="inlineStr"/>
       <c r="F207" s="2" t="inlineStr"/>
       <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521811</t>
-          </r>
-        </is>
-      </c>
-      <c r="I207" s="13" t="inlineStr"/>
-      <c r="J207" s="13" t="inlineStr"/>
-      <c r="K207" s="13" t="inlineStr"/>
-      <c r="L207" s="13" t="inlineStr"/>
-      <c r="M207" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
-          </r>
-        </is>
-      </c>
-      <c r="N207" s="13" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr"/>
+      <c r="I207" s="2" t="inlineStr"/>
+      <c r="J207" s="2" t="inlineStr"/>
+      <c r="K207" s="2" t="inlineStr"/>
+      <c r="L207" s="2" t="inlineStr"/>
+      <c r="M207" s="2" t="inlineStr"/>
+      <c r="N207" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000306. Konsumsi Rapat</t>
+          </r>
+        </is>
+      </c>
       <c r="O207" s="13" t="inlineStr"/>
       <c r="P207" s="13" t="inlineStr"/>
       <c r="Q207" s="14" t="n">
-        <v>1.1E7</v>
+        <v>6080000.0</v>
       </c>
       <c r="R207" s="14" t="inlineStr"/>
       <c r="S207" s="14" t="n">
@@ -12611,23 +12605,23 @@
       <c r="U207" s="14" t="inlineStr"/>
       <c r="V207" s="14" t="inlineStr"/>
       <c r="W207" s="14" t="n">
-        <v>4274800.0</v>
+        <v>0.0</v>
       </c>
       <c r="X207" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y207" s="14" t="inlineStr"/>
       <c r="Z207" s="14" t="n">
-        <v>4274800.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA207" s="14" t="inlineStr"/>
       <c r="AB207" s="14" t="inlineStr"/>
       <c r="AC207" s="15" t="n">
-        <v>0.3886181818181818</v>
+        <v>0.0</v>
       </c>
       <c r="AD207" s="15" t="inlineStr"/>
       <c r="AE207" s="14" t="n">
-        <v>6725200.0</v>
+        <v>6080000.0</v>
       </c>
       <c r="AF207" s="14" t="inlineStr"/>
       <c r="AG207" s="14" t="inlineStr"/>
@@ -12642,23 +12636,29 @@
       <c r="E208" s="2" t="inlineStr"/>
       <c r="F208" s="2" t="inlineStr"/>
       <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr"/>
-      <c r="I208" s="2" t="inlineStr"/>
-      <c r="J208" s="2" t="inlineStr"/>
-      <c r="K208" s="2" t="inlineStr"/>
-      <c r="L208" s="2" t="inlineStr"/>
-      <c r="M208" s="2" t="inlineStr"/>
-      <c r="N208" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000137. Bahan Komputer</t>
-          </r>
-        </is>
-      </c>
+      <c r="H208" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521811</t>
+          </r>
+        </is>
+      </c>
+      <c r="I208" s="13" t="inlineStr"/>
+      <c r="J208" s="13" t="inlineStr"/>
+      <c r="K208" s="13" t="inlineStr"/>
+      <c r="L208" s="13" t="inlineStr"/>
+      <c r="M208" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
+          </r>
+        </is>
+      </c>
+      <c r="N208" s="13" t="inlineStr"/>
       <c r="O208" s="13" t="inlineStr"/>
       <c r="P208" s="13" t="inlineStr"/>
       <c r="Q208" s="14" t="n">
-        <v>9000000.0</v>
+        <v>1.1E7</v>
       </c>
       <c r="R208" s="14" t="inlineStr"/>
       <c r="S208" s="14" t="n">
@@ -12668,23 +12668,23 @@
       <c r="U208" s="14" t="inlineStr"/>
       <c r="V208" s="14" t="inlineStr"/>
       <c r="W208" s="14" t="n">
-        <v>3964800.0</v>
+        <v>4274800.0</v>
       </c>
       <c r="X208" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y208" s="14" t="inlineStr"/>
       <c r="Z208" s="14" t="n">
-        <v>3964800.0</v>
+        <v>4274800.0</v>
       </c>
       <c r="AA208" s="14" t="inlineStr"/>
       <c r="AB208" s="14" t="inlineStr"/>
       <c r="AC208" s="15" t="n">
-        <v>0.44053333333333333</v>
+        <v>0.3886181818181818</v>
       </c>
       <c r="AD208" s="15" t="inlineStr"/>
       <c r="AE208" s="14" t="n">
-        <v>5035200.0</v>
+        <v>6725200.0</v>
       </c>
       <c r="AF208" s="14" t="inlineStr"/>
       <c r="AG208" s="14" t="inlineStr"/>
@@ -12708,14 +12708,14 @@
       <c r="N209" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000292. ATK</t>
+            <t xml:space="preserve">000137. Bahan Komputer</t>
           </r>
         </is>
       </c>
       <c r="O209" s="13" t="inlineStr"/>
       <c r="P209" s="13" t="inlineStr"/>
       <c r="Q209" s="14" t="n">
-        <v>2000000.0</v>
+        <v>9000000.0</v>
       </c>
       <c r="R209" s="14" t="inlineStr"/>
       <c r="S209" s="14" t="n">
@@ -12725,23 +12725,23 @@
       <c r="U209" s="14" t="inlineStr"/>
       <c r="V209" s="14" t="inlineStr"/>
       <c r="W209" s="14" t="n">
-        <v>310000.0</v>
+        <v>3964800.0</v>
       </c>
       <c r="X209" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y209" s="14" t="inlineStr"/>
       <c r="Z209" s="14" t="n">
-        <v>310000.0</v>
+        <v>3964800.0</v>
       </c>
       <c r="AA209" s="14" t="inlineStr"/>
       <c r="AB209" s="14" t="inlineStr"/>
       <c r="AC209" s="15" t="n">
-        <v>0.155</v>
+        <v>0.44053333333333333</v>
       </c>
       <c r="AD209" s="15" t="inlineStr"/>
       <c r="AE209" s="14" t="n">
-        <v>1690000.0</v>
+        <v>5035200.0</v>
       </c>
       <c r="AF209" s="14" t="inlineStr"/>
       <c r="AG209" s="14" t="inlineStr"/>
@@ -12756,29 +12756,23 @@
       <c r="E210" s="2" t="inlineStr"/>
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522191</t>
-          </r>
-        </is>
-      </c>
-      <c r="I210" s="13" t="inlineStr"/>
-      <c r="J210" s="13" t="inlineStr"/>
-      <c r="K210" s="13" t="inlineStr"/>
-      <c r="L210" s="13" t="inlineStr"/>
-      <c r="M210" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Jasa Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N210" s="13" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr"/>
+      <c r="I210" s="2" t="inlineStr"/>
+      <c r="J210" s="2" t="inlineStr"/>
+      <c r="K210" s="2" t="inlineStr"/>
+      <c r="L210" s="2" t="inlineStr"/>
+      <c r="M210" s="2" t="inlineStr"/>
+      <c r="N210" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000292. ATK</t>
+          </r>
+        </is>
+      </c>
       <c r="O210" s="13" t="inlineStr"/>
       <c r="P210" s="13" t="inlineStr"/>
       <c r="Q210" s="14" t="n">
-        <v>3.011368E9</v>
+        <v>2000000.0</v>
       </c>
       <c r="R210" s="14" t="inlineStr"/>
       <c r="S210" s="14" t="n">
@@ -12788,30 +12782,30 @@
       <c r="U210" s="14" t="inlineStr"/>
       <c r="V210" s="14" t="inlineStr"/>
       <c r="W210" s="14" t="n">
-        <v>2.936691192E9</v>
+        <v>310000.0</v>
       </c>
       <c r="X210" s="14" t="n">
-        <v>3.7051768E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y210" s="14" t="inlineStr"/>
       <c r="Z210" s="14" t="n">
-        <v>2.97374296E9</v>
+        <v>310000.0</v>
       </c>
       <c r="AA210" s="14" t="inlineStr"/>
       <c r="AB210" s="14" t="inlineStr"/>
       <c r="AC210" s="15" t="n">
-        <v>0.987505665199338</v>
+        <v>0.155</v>
       </c>
       <c r="AD210" s="15" t="inlineStr"/>
       <c r="AE210" s="14" t="n">
-        <v>3.762504E7</v>
+        <v>1690000.0</v>
       </c>
       <c r="AF210" s="14" t="inlineStr"/>
       <c r="AG210" s="14" t="inlineStr"/>
       <c r="AH210" s="14" t="inlineStr"/>
       <c r="AI210" s="14" t="inlineStr"/>
     </row>
-    <row r="211" customHeight="1" ht="18">
+    <row r="211" customHeight="1" ht="15">
       <c r="A211" s="2" t="inlineStr"/>
       <c r="B211" s="2" t="inlineStr"/>
       <c r="C211" s="2" t="inlineStr"/>
@@ -12819,23 +12813,29 @@
       <c r="E211" s="2" t="inlineStr"/>
       <c r="F211" s="2" t="inlineStr"/>
       <c r="G211" s="2" t="inlineStr"/>
-      <c r="H211" s="2" t="inlineStr"/>
-      <c r="I211" s="2" t="inlineStr"/>
-      <c r="J211" s="2" t="inlineStr"/>
-      <c r="K211" s="2" t="inlineStr"/>
-      <c r="L211" s="2" t="inlineStr"/>
-      <c r="M211" s="2" t="inlineStr"/>
-      <c r="N211" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000139. Biaya Outsourcing Perorangan Tenaga Kebersihan (Januari s.d September) (9 ORG)</t>
-          </r>
-        </is>
-      </c>
+      <c r="H211" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522191</t>
+          </r>
+        </is>
+      </c>
+      <c r="I211" s="13" t="inlineStr"/>
+      <c r="J211" s="13" t="inlineStr"/>
+      <c r="K211" s="13" t="inlineStr"/>
+      <c r="L211" s="13" t="inlineStr"/>
+      <c r="M211" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Jasa Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N211" s="13" t="inlineStr"/>
       <c r="O211" s="13" t="inlineStr"/>
       <c r="P211" s="13" t="inlineStr"/>
       <c r="Q211" s="14" t="n">
-        <v>4.0995E8</v>
+        <v>3.011368E9</v>
       </c>
       <c r="R211" s="14" t="inlineStr"/>
       <c r="S211" s="14" t="n">
@@ -12845,30 +12845,30 @@
       <c r="U211" s="14" t="inlineStr"/>
       <c r="V211" s="14" t="inlineStr"/>
       <c r="W211" s="14" t="n">
-        <v>4.09846464E8</v>
+        <v>2.936691192E9</v>
       </c>
       <c r="X211" s="14" t="n">
-        <v>0.0</v>
+        <v>3.7051768E7</v>
       </c>
       <c r="Y211" s="14" t="inlineStr"/>
       <c r="Z211" s="14" t="n">
-        <v>4.09846464E8</v>
+        <v>2.97374296E9</v>
       </c>
       <c r="AA211" s="14" t="inlineStr"/>
       <c r="AB211" s="14" t="inlineStr"/>
       <c r="AC211" s="15" t="n">
-        <v>0.9997474423710209</v>
+        <v>0.987505665199338</v>
       </c>
       <c r="AD211" s="15" t="inlineStr"/>
       <c r="AE211" s="14" t="n">
-        <v>103536.0</v>
+        <v>3.762504E7</v>
       </c>
       <c r="AF211" s="14" t="inlineStr"/>
       <c r="AG211" s="14" t="inlineStr"/>
       <c r="AH211" s="14" t="inlineStr"/>
       <c r="AI211" s="14" t="inlineStr"/>
     </row>
-    <row r="212" customHeight="1" ht="15">
+    <row r="212" customHeight="1" ht="18">
       <c r="A212" s="2" t="inlineStr"/>
       <c r="B212" s="2" t="inlineStr"/>
       <c r="C212" s="2" t="inlineStr"/>
@@ -12885,14 +12885,14 @@
       <c r="N212" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000140. Biaya Outsourcing Perorangan Pengemudi (2 ORG)</t>
+            <t xml:space="preserve">000139. Biaya Outsourcing Perorangan Tenaga Kebersihan (Januari s.d September) (9 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O212" s="13" t="inlineStr"/>
       <c r="P212" s="13" t="inlineStr"/>
       <c r="Q212" s="14" t="n">
-        <v>1.226E8</v>
+        <v>4.0995E8</v>
       </c>
       <c r="R212" s="14" t="inlineStr"/>
       <c r="S212" s="14" t="n">
@@ -12902,30 +12902,30 @@
       <c r="U212" s="14" t="inlineStr"/>
       <c r="V212" s="14" t="inlineStr"/>
       <c r="W212" s="14" t="n">
-        <v>1.0331888E8</v>
+        <v>4.09846464E8</v>
       </c>
       <c r="X212" s="14" t="n">
-        <v>9468528.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y212" s="14" t="inlineStr"/>
       <c r="Z212" s="14" t="n">
-        <v>1.12787408E8</v>
+        <v>4.09846464E8</v>
       </c>
       <c r="AA212" s="14" t="inlineStr"/>
       <c r="AB212" s="14" t="inlineStr"/>
       <c r="AC212" s="15" t="n">
-        <v>0.9199625448613377</v>
+        <v>0.9997474423710209</v>
       </c>
       <c r="AD212" s="15" t="inlineStr"/>
       <c r="AE212" s="14" t="n">
-        <v>9812592.0</v>
+        <v>103536.0</v>
       </c>
       <c r="AF212" s="14" t="inlineStr"/>
       <c r="AG212" s="14" t="inlineStr"/>
       <c r="AH212" s="14" t="inlineStr"/>
       <c r="AI212" s="14" t="inlineStr"/>
     </row>
-    <row r="213" customHeight="1" ht="18">
+    <row r="213" customHeight="1" ht="15">
       <c r="A213" s="2" t="inlineStr"/>
       <c r="B213" s="2" t="inlineStr"/>
       <c r="C213" s="2" t="inlineStr"/>
@@ -12942,14 +12942,14 @@
       <c r="N213" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000141. Biaya Outsourcing Perorangan Petugas Kolam (Januari s.d September) (3 ORG)</t>
+            <t xml:space="preserve">000140. Biaya Outsourcing Perorangan Pengemudi (2 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O213" s="13" t="inlineStr"/>
       <c r="P213" s="13" t="inlineStr"/>
       <c r="Q213" s="14" t="n">
-        <v>1.3629E8</v>
+        <v>1.226E8</v>
       </c>
       <c r="R213" s="14" t="inlineStr"/>
       <c r="S213" s="14" t="n">
@@ -12959,23 +12959,23 @@
       <c r="U213" s="14" t="inlineStr"/>
       <c r="V213" s="14" t="inlineStr"/>
       <c r="W213" s="14" t="n">
-        <v>1.36218456E8</v>
+        <v>1.0331888E8</v>
       </c>
       <c r="X213" s="14" t="n">
-        <v>0.0</v>
+        <v>9468528.0</v>
       </c>
       <c r="Y213" s="14" t="inlineStr"/>
       <c r="Z213" s="14" t="n">
-        <v>1.36218456E8</v>
+        <v>1.12787408E8</v>
       </c>
       <c r="AA213" s="14" t="inlineStr"/>
       <c r="AB213" s="14" t="inlineStr"/>
       <c r="AC213" s="15" t="n">
-        <v>0.9994750605326876</v>
+        <v>0.9199625448613377</v>
       </c>
       <c r="AD213" s="15" t="inlineStr"/>
       <c r="AE213" s="14" t="n">
-        <v>71544.0</v>
+        <v>9812592.0</v>
       </c>
       <c r="AF213" s="14" t="inlineStr"/>
       <c r="AG213" s="14" t="inlineStr"/>
@@ -12999,14 +12999,14 @@
       <c r="N214" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000142. Biaya Outsourcing Perorangan Petugas Layanan Informasi (1 ORG)</t>
+            <t xml:space="preserve">000141. Biaya Outsourcing Perorangan Petugas Kolam (Januari s.d September) (3 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O214" s="13" t="inlineStr"/>
       <c r="P214" s="13" t="inlineStr"/>
       <c r="Q214" s="14" t="n">
-        <v>4.59E7</v>
+        <v>1.3629E8</v>
       </c>
       <c r="R214" s="14" t="inlineStr"/>
       <c r="S214" s="14" t="n">
@@ -13016,30 +13016,30 @@
       <c r="U214" s="14" t="inlineStr"/>
       <c r="V214" s="14" t="inlineStr"/>
       <c r="W214" s="14" t="n">
-        <v>4.5886152E7</v>
+        <v>1.36218456E8</v>
       </c>
       <c r="X214" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y214" s="14" t="inlineStr"/>
       <c r="Z214" s="14" t="n">
-        <v>4.5886152E7</v>
+        <v>1.36218456E8</v>
       </c>
       <c r="AA214" s="14" t="inlineStr"/>
       <c r="AB214" s="14" t="inlineStr"/>
       <c r="AC214" s="15" t="n">
-        <v>0.9996983006535948</v>
+        <v>0.9994750605326876</v>
       </c>
       <c r="AD214" s="15" t="inlineStr"/>
       <c r="AE214" s="14" t="n">
-        <v>13848.0</v>
+        <v>71544.0</v>
       </c>
       <c r="AF214" s="14" t="inlineStr"/>
       <c r="AG214" s="14" t="inlineStr"/>
       <c r="AH214" s="14" t="inlineStr"/>
       <c r="AI214" s="14" t="inlineStr"/>
     </row>
-    <row r="215" customHeight="1" ht="15">
+    <row r="215" customHeight="1" ht="18">
       <c r="A215" s="2" t="inlineStr"/>
       <c r="B215" s="2" t="inlineStr"/>
       <c r="C215" s="2" t="inlineStr"/>
@@ -13056,14 +13056,14 @@
       <c r="N215" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000144. Biaya Outsourcing Satpam (24 ORG)</t>
+            <t xml:space="preserve">000142. Biaya Outsourcing Perorangan Petugas Layanan Informasi (1 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O215" s="13" t="inlineStr"/>
       <c r="P215" s="13" t="inlineStr"/>
       <c r="Q215" s="14" t="n">
-        <v>2.213838E9</v>
+        <v>4.59E7</v>
       </c>
       <c r="R215" s="14" t="inlineStr"/>
       <c r="S215" s="14" t="n">
@@ -13073,30 +13073,30 @@
       <c r="U215" s="14" t="inlineStr"/>
       <c r="V215" s="14" t="inlineStr"/>
       <c r="W215" s="14" t="n">
-        <v>2.213838E9</v>
+        <v>4.5886152E7</v>
       </c>
       <c r="X215" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y215" s="14" t="inlineStr"/>
       <c r="Z215" s="14" t="n">
-        <v>2.213838E9</v>
+        <v>4.5886152E7</v>
       </c>
       <c r="AA215" s="14" t="inlineStr"/>
       <c r="AB215" s="14" t="inlineStr"/>
       <c r="AC215" s="15" t="n">
-        <v>1.0</v>
+        <v>0.9996983006535948</v>
       </c>
       <c r="AD215" s="15" t="inlineStr"/>
       <c r="AE215" s="14" t="n">
-        <v>0.0</v>
+        <v>13848.0</v>
       </c>
       <c r="AF215" s="14" t="inlineStr"/>
       <c r="AG215" s="14" t="inlineStr"/>
       <c r="AH215" s="14" t="inlineStr"/>
       <c r="AI215" s="14" t="inlineStr"/>
     </row>
-    <row r="216" customHeight="1" ht="18">
+    <row r="216" customHeight="1" ht="15">
       <c r="A216" s="2" t="inlineStr"/>
       <c r="B216" s="2" t="inlineStr"/>
       <c r="C216" s="2" t="inlineStr"/>
@@ -13113,14 +13113,14 @@
       <c r="N216" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000296. Biaya Outsourcing Perorangan Tenaga Kebersihan (Oktober s.d Desember) (5 ORG)</t>
+            <t xml:space="preserve">000144. Biaya Outsourcing Satpam (24 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O216" s="13" t="inlineStr"/>
       <c r="P216" s="13" t="inlineStr"/>
       <c r="Q216" s="14" t="n">
-        <v>6.89E7</v>
+        <v>2.213838E9</v>
       </c>
       <c r="R216" s="14" t="inlineStr"/>
       <c r="S216" s="14" t="n">
@@ -13130,23 +13130,23 @@
       <c r="U216" s="14" t="inlineStr"/>
       <c r="V216" s="14" t="inlineStr"/>
       <c r="W216" s="14" t="n">
-        <v>2.2953312E7</v>
+        <v>2.213838E9</v>
       </c>
       <c r="X216" s="14" t="n">
-        <v>2.2953312E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y216" s="14" t="inlineStr"/>
       <c r="Z216" s="14" t="n">
-        <v>4.5906624E7</v>
+        <v>2.213838E9</v>
       </c>
       <c r="AA216" s="14" t="inlineStr"/>
       <c r="AB216" s="14" t="inlineStr"/>
       <c r="AC216" s="15" t="n">
-        <v>0.6662790130624093</v>
+        <v>1.0</v>
       </c>
       <c r="AD216" s="15" t="inlineStr"/>
       <c r="AE216" s="14" t="n">
-        <v>2.2993376E7</v>
+        <v>0.0</v>
       </c>
       <c r="AF216" s="14" t="inlineStr"/>
       <c r="AG216" s="14" t="inlineStr"/>
@@ -13170,14 +13170,14 @@
       <c r="N217" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000297. Biaya Outsourcing Perorangan Petugas Kolam (Oktober s.d Desember) (1 ORG)</t>
+            <t xml:space="preserve">000296. Biaya Outsourcing Perorangan Tenaga Kebersihan (Oktober s.d Desember) (5 ORG)</t>
           </r>
         </is>
       </c>
       <c r="O217" s="13" t="inlineStr"/>
       <c r="P217" s="13" t="inlineStr"/>
       <c r="Q217" s="14" t="n">
-        <v>1.389E7</v>
+        <v>6.89E7</v>
       </c>
       <c r="R217" s="14" t="inlineStr"/>
       <c r="S217" s="14" t="n">
@@ -13187,60 +13187,54 @@
       <c r="U217" s="14" t="inlineStr"/>
       <c r="V217" s="14" t="inlineStr"/>
       <c r="W217" s="14" t="n">
-        <v>4629928.0</v>
+        <v>2.2953312E7</v>
       </c>
       <c r="X217" s="14" t="n">
-        <v>4629928.0</v>
+        <v>2.2953312E7</v>
       </c>
       <c r="Y217" s="14" t="inlineStr"/>
       <c r="Z217" s="14" t="n">
-        <v>9259856.0</v>
+        <v>4.5906624E7</v>
       </c>
       <c r="AA217" s="14" t="inlineStr"/>
       <c r="AB217" s="14" t="inlineStr"/>
       <c r="AC217" s="15" t="n">
-        <v>0.6666562994960403</v>
+        <v>0.6662790130624093</v>
       </c>
       <c r="AD217" s="15" t="inlineStr"/>
       <c r="AE217" s="14" t="n">
-        <v>4630144.0</v>
+        <v>2.2993376E7</v>
       </c>
       <c r="AF217" s="14" t="inlineStr"/>
       <c r="AG217" s="14" t="inlineStr"/>
       <c r="AH217" s="14" t="inlineStr"/>
       <c r="AI217" s="14" t="inlineStr"/>
     </row>
-    <row r="218" customHeight="1" ht="15">
+    <row r="218" customHeight="1" ht="18">
       <c r="A218" s="2" t="inlineStr"/>
       <c r="B218" s="2" t="inlineStr"/>
       <c r="C218" s="2" t="inlineStr"/>
       <c r="D218" s="2" t="inlineStr"/>
       <c r="E218" s="2" t="inlineStr"/>
-      <c r="F218" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">002.DB</t>
-          </r>
-        </is>
-      </c>
-      <c r="G218" s="13" t="inlineStr"/>
-      <c r="H218" s="13" t="inlineStr"/>
-      <c r="I218" s="13" t="inlineStr"/>
-      <c r="J218" s="13" t="inlineStr"/>
-      <c r="K218" s="13" t="inlineStr"/>
-      <c r="L218" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Langganan Daya dan Jasa</t>
-          </r>
-        </is>
-      </c>
-      <c r="M218" s="13" t="inlineStr"/>
-      <c r="N218" s="13" t="inlineStr"/>
+      <c r="F218" s="2" t="inlineStr"/>
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr"/>
+      <c r="I218" s="2" t="inlineStr"/>
+      <c r="J218" s="2" t="inlineStr"/>
+      <c r="K218" s="2" t="inlineStr"/>
+      <c r="L218" s="2" t="inlineStr"/>
+      <c r="M218" s="2" t="inlineStr"/>
+      <c r="N218" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000297. Biaya Outsourcing Perorangan Petugas Kolam (Oktober s.d Desember) (1 ORG)</t>
+          </r>
+        </is>
+      </c>
       <c r="O218" s="13" t="inlineStr"/>
       <c r="P218" s="13" t="inlineStr"/>
       <c r="Q218" s="14" t="n">
-        <v>7.00144E8</v>
+        <v>1.389E7</v>
       </c>
       <c r="R218" s="14" t="inlineStr"/>
       <c r="S218" s="14" t="n">
@@ -13250,23 +13244,23 @@
       <c r="U218" s="14" t="inlineStr"/>
       <c r="V218" s="14" t="inlineStr"/>
       <c r="W218" s="14" t="n">
-        <v>6.39842407E8</v>
+        <v>4629928.0</v>
       </c>
       <c r="X218" s="14" t="n">
-        <v>604300.0</v>
+        <v>4629928.0</v>
       </c>
       <c r="Y218" s="14" t="inlineStr"/>
       <c r="Z218" s="14" t="n">
-        <v>6.40446707E8</v>
+        <v>9259856.0</v>
       </c>
       <c r="AA218" s="14" t="inlineStr"/>
       <c r="AB218" s="14" t="inlineStr"/>
       <c r="AC218" s="15" t="n">
-        <v>0.9147356929431659</v>
+        <v>0.6666562994960403</v>
       </c>
       <c r="AD218" s="15" t="inlineStr"/>
       <c r="AE218" s="14" t="n">
-        <v>5.9697293E7</v>
+        <v>4630144.0</v>
       </c>
       <c r="AF218" s="14" t="inlineStr"/>
       <c r="AG218" s="14" t="inlineStr"/>
@@ -13279,31 +13273,31 @@
       <c r="C219" s="2" t="inlineStr"/>
       <c r="D219" s="2" t="inlineStr"/>
       <c r="E219" s="2" t="inlineStr"/>
-      <c r="F219" s="2" t="inlineStr"/>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522111</t>
-          </r>
-        </is>
-      </c>
+      <c r="F219" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">002.DB</t>
+          </r>
+        </is>
+      </c>
+      <c r="G219" s="13" t="inlineStr"/>
+      <c r="H219" s="13" t="inlineStr"/>
       <c r="I219" s="13" t="inlineStr"/>
       <c r="J219" s="13" t="inlineStr"/>
       <c r="K219" s="13" t="inlineStr"/>
-      <c r="L219" s="13" t="inlineStr"/>
-      <c r="M219" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Listrik</t>
-          </r>
-        </is>
-      </c>
+      <c r="L219" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Langganan Daya dan Jasa</t>
+          </r>
+        </is>
+      </c>
+      <c r="M219" s="13" t="inlineStr"/>
       <c r="N219" s="13" t="inlineStr"/>
       <c r="O219" s="13" t="inlineStr"/>
       <c r="P219" s="13" t="inlineStr"/>
       <c r="Q219" s="14" t="n">
-        <v>5.16E8</v>
+        <v>7.00144E8</v>
       </c>
       <c r="R219" s="14" t="inlineStr"/>
       <c r="S219" s="14" t="n">
@@ -13313,23 +13307,23 @@
       <c r="U219" s="14" t="inlineStr"/>
       <c r="V219" s="14" t="inlineStr"/>
       <c r="W219" s="14" t="n">
-        <v>4.70513911E8</v>
+        <v>6.39842407E8</v>
       </c>
       <c r="X219" s="14" t="n">
-        <v>0.0</v>
+        <v>604300.0</v>
       </c>
       <c r="Y219" s="14" t="inlineStr"/>
       <c r="Z219" s="14" t="n">
-        <v>4.70513911E8</v>
+        <v>6.40446707E8</v>
       </c>
       <c r="AA219" s="14" t="inlineStr"/>
       <c r="AB219" s="14" t="inlineStr"/>
       <c r="AC219" s="15" t="n">
-        <v>0.9118486647286822</v>
+        <v>0.9147356929431659</v>
       </c>
       <c r="AD219" s="15" t="inlineStr"/>
       <c r="AE219" s="14" t="n">
-        <v>4.5486089E7</v>
+        <v>5.9697293E7</v>
       </c>
       <c r="AF219" s="14" t="inlineStr"/>
       <c r="AG219" s="14" t="inlineStr"/>
@@ -13344,19 +13338,25 @@
       <c r="E220" s="2" t="inlineStr"/>
       <c r="F220" s="2" t="inlineStr"/>
       <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="inlineStr"/>
-      <c r="I220" s="2" t="inlineStr"/>
-      <c r="J220" s="2" t="inlineStr"/>
-      <c r="K220" s="2" t="inlineStr"/>
-      <c r="L220" s="2" t="inlineStr"/>
-      <c r="M220" s="2" t="inlineStr"/>
-      <c r="N220" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000145. Langganan Listrik</t>
-          </r>
-        </is>
-      </c>
+      <c r="H220" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522111</t>
+          </r>
+        </is>
+      </c>
+      <c r="I220" s="13" t="inlineStr"/>
+      <c r="J220" s="13" t="inlineStr"/>
+      <c r="K220" s="13" t="inlineStr"/>
+      <c r="L220" s="13" t="inlineStr"/>
+      <c r="M220" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Listrik</t>
+          </r>
+        </is>
+      </c>
+      <c r="N220" s="13" t="inlineStr"/>
       <c r="O220" s="13" t="inlineStr"/>
       <c r="P220" s="13" t="inlineStr"/>
       <c r="Q220" s="14" t="n">
@@ -13401,29 +13401,23 @@
       <c r="E221" s="2" t="inlineStr"/>
       <c r="F221" s="2" t="inlineStr"/>
       <c r="G221" s="2" t="inlineStr"/>
-      <c r="H221" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522112</t>
-          </r>
-        </is>
-      </c>
-      <c r="I221" s="13" t="inlineStr"/>
-      <c r="J221" s="13" t="inlineStr"/>
-      <c r="K221" s="13" t="inlineStr"/>
-      <c r="L221" s="13" t="inlineStr"/>
-      <c r="M221" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Telepon</t>
-          </r>
-        </is>
-      </c>
-      <c r="N221" s="13" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr"/>
+      <c r="I221" s="2" t="inlineStr"/>
+      <c r="J221" s="2" t="inlineStr"/>
+      <c r="K221" s="2" t="inlineStr"/>
+      <c r="L221" s="2" t="inlineStr"/>
+      <c r="M221" s="2" t="inlineStr"/>
+      <c r="N221" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000145. Langganan Listrik</t>
+          </r>
+        </is>
+      </c>
       <c r="O221" s="13" t="inlineStr"/>
       <c r="P221" s="13" t="inlineStr"/>
       <c r="Q221" s="14" t="n">
-        <v>6000000.0</v>
+        <v>5.16E8</v>
       </c>
       <c r="R221" s="14" t="inlineStr"/>
       <c r="S221" s="14" t="n">
@@ -13433,23 +13427,23 @@
       <c r="U221" s="14" t="inlineStr"/>
       <c r="V221" s="14" t="inlineStr"/>
       <c r="W221" s="14" t="n">
-        <v>5485232.0</v>
+        <v>4.70513911E8</v>
       </c>
       <c r="X221" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y221" s="14" t="inlineStr"/>
       <c r="Z221" s="14" t="n">
-        <v>5485232.0</v>
+        <v>4.70513911E8</v>
       </c>
       <c r="AA221" s="14" t="inlineStr"/>
       <c r="AB221" s="14" t="inlineStr"/>
       <c r="AC221" s="15" t="n">
-        <v>0.9142053333333333</v>
+        <v>0.9118486647286822</v>
       </c>
       <c r="AD221" s="15" t="inlineStr"/>
       <c r="AE221" s="14" t="n">
-        <v>514768.0</v>
+        <v>4.5486089E7</v>
       </c>
       <c r="AF221" s="14" t="inlineStr"/>
       <c r="AG221" s="14" t="inlineStr"/>
@@ -13464,19 +13458,25 @@
       <c r="E222" s="2" t="inlineStr"/>
       <c r="F222" s="2" t="inlineStr"/>
       <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="2" t="inlineStr"/>
-      <c r="I222" s="2" t="inlineStr"/>
-      <c r="J222" s="2" t="inlineStr"/>
-      <c r="K222" s="2" t="inlineStr"/>
-      <c r="L222" s="2" t="inlineStr"/>
-      <c r="M222" s="2" t="inlineStr"/>
-      <c r="N222" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000146. Langganan Telepon</t>
-          </r>
-        </is>
-      </c>
+      <c r="H222" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522112</t>
+          </r>
+        </is>
+      </c>
+      <c r="I222" s="13" t="inlineStr"/>
+      <c r="J222" s="13" t="inlineStr"/>
+      <c r="K222" s="13" t="inlineStr"/>
+      <c r="L222" s="13" t="inlineStr"/>
+      <c r="M222" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Telepon</t>
+          </r>
+        </is>
+      </c>
+      <c r="N222" s="13" t="inlineStr"/>
       <c r="O222" s="13" t="inlineStr"/>
       <c r="P222" s="13" t="inlineStr"/>
       <c r="Q222" s="14" t="n">
@@ -13521,29 +13521,23 @@
       <c r="E223" s="2" t="inlineStr"/>
       <c r="F223" s="2" t="inlineStr"/>
       <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522113</t>
-          </r>
-        </is>
-      </c>
-      <c r="I223" s="13" t="inlineStr"/>
-      <c r="J223" s="13" t="inlineStr"/>
-      <c r="K223" s="13" t="inlineStr"/>
-      <c r="L223" s="13" t="inlineStr"/>
-      <c r="M223" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Air</t>
-          </r>
-        </is>
-      </c>
-      <c r="N223" s="13" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr"/>
+      <c r="I223" s="2" t="inlineStr"/>
+      <c r="J223" s="2" t="inlineStr"/>
+      <c r="K223" s="2" t="inlineStr"/>
+      <c r="L223" s="2" t="inlineStr"/>
+      <c r="M223" s="2" t="inlineStr"/>
+      <c r="N223" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000146. Langganan Telepon</t>
+          </r>
+        </is>
+      </c>
       <c r="O223" s="13" t="inlineStr"/>
       <c r="P223" s="13" t="inlineStr"/>
       <c r="Q223" s="14" t="n">
-        <v>3.3444E7</v>
+        <v>6000000.0</v>
       </c>
       <c r="R223" s="14" t="inlineStr"/>
       <c r="S223" s="14" t="n">
@@ -13553,23 +13547,23 @@
       <c r="U223" s="14" t="inlineStr"/>
       <c r="V223" s="14" t="inlineStr"/>
       <c r="W223" s="14" t="n">
-        <v>3.08218E7</v>
+        <v>5485232.0</v>
       </c>
       <c r="X223" s="14" t="n">
-        <v>604300.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y223" s="14" t="inlineStr"/>
       <c r="Z223" s="14" t="n">
-        <v>3.14261E7</v>
+        <v>5485232.0</v>
       </c>
       <c r="AA223" s="14" t="inlineStr"/>
       <c r="AB223" s="14" t="inlineStr"/>
       <c r="AC223" s="15" t="n">
-        <v>0.9396633177849539</v>
+        <v>0.9142053333333333</v>
       </c>
       <c r="AD223" s="15" t="inlineStr"/>
       <c r="AE223" s="14" t="n">
-        <v>2017900.0</v>
+        <v>514768.0</v>
       </c>
       <c r="AF223" s="14" t="inlineStr"/>
       <c r="AG223" s="14" t="inlineStr"/>
@@ -13584,19 +13578,25 @@
       <c r="E224" s="2" t="inlineStr"/>
       <c r="F224" s="2" t="inlineStr"/>
       <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="2" t="inlineStr"/>
-      <c r="I224" s="2" t="inlineStr"/>
-      <c r="J224" s="2" t="inlineStr"/>
-      <c r="K224" s="2" t="inlineStr"/>
-      <c r="L224" s="2" t="inlineStr"/>
-      <c r="M224" s="2" t="inlineStr"/>
-      <c r="N224" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000147. Langganan Air (PAM)</t>
-          </r>
-        </is>
-      </c>
+      <c r="H224" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522113</t>
+          </r>
+        </is>
+      </c>
+      <c r="I224" s="13" t="inlineStr"/>
+      <c r="J224" s="13" t="inlineStr"/>
+      <c r="K224" s="13" t="inlineStr"/>
+      <c r="L224" s="13" t="inlineStr"/>
+      <c r="M224" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Air</t>
+          </r>
+        </is>
+      </c>
+      <c r="N224" s="13" t="inlineStr"/>
       <c r="O224" s="13" t="inlineStr"/>
       <c r="P224" s="13" t="inlineStr"/>
       <c r="Q224" s="14" t="n">
@@ -13641,29 +13641,23 @@
       <c r="E225" s="2" t="inlineStr"/>
       <c r="F225" s="2" t="inlineStr"/>
       <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522119</t>
-          </r>
-        </is>
-      </c>
-      <c r="I225" s="13" t="inlineStr"/>
-      <c r="J225" s="13" t="inlineStr"/>
-      <c r="K225" s="13" t="inlineStr"/>
-      <c r="L225" s="13" t="inlineStr"/>
-      <c r="M225" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Langganan Daya dan Jasa Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N225" s="13" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr"/>
+      <c r="I225" s="2" t="inlineStr"/>
+      <c r="J225" s="2" t="inlineStr"/>
+      <c r="K225" s="2" t="inlineStr"/>
+      <c r="L225" s="2" t="inlineStr"/>
+      <c r="M225" s="2" t="inlineStr"/>
+      <c r="N225" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000147. Langganan Air (PAM)</t>
+          </r>
+        </is>
+      </c>
       <c r="O225" s="13" t="inlineStr"/>
       <c r="P225" s="13" t="inlineStr"/>
       <c r="Q225" s="14" t="n">
-        <v>1.447E8</v>
+        <v>3.3444E7</v>
       </c>
       <c r="R225" s="14" t="inlineStr"/>
       <c r="S225" s="14" t="n">
@@ -13673,23 +13667,23 @@
       <c r="U225" s="14" t="inlineStr"/>
       <c r="V225" s="14" t="inlineStr"/>
       <c r="W225" s="14" t="n">
-        <v>1.33021464E8</v>
+        <v>3.08218E7</v>
       </c>
       <c r="X225" s="14" t="n">
-        <v>0.0</v>
+        <v>604300.0</v>
       </c>
       <c r="Y225" s="14" t="inlineStr"/>
       <c r="Z225" s="14" t="n">
-        <v>1.33021464E8</v>
+        <v>3.14261E7</v>
       </c>
       <c r="AA225" s="14" t="inlineStr"/>
       <c r="AB225" s="14" t="inlineStr"/>
       <c r="AC225" s="15" t="n">
-        <v>0.919291389080857</v>
+        <v>0.9396633177849539</v>
       </c>
       <c r="AD225" s="15" t="inlineStr"/>
       <c r="AE225" s="14" t="n">
-        <v>1.1678536E7</v>
+        <v>2017900.0</v>
       </c>
       <c r="AF225" s="14" t="inlineStr"/>
       <c r="AG225" s="14" t="inlineStr"/>
@@ -13704,23 +13698,29 @@
       <c r="E226" s="2" t="inlineStr"/>
       <c r="F226" s="2" t="inlineStr"/>
       <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="2" t="inlineStr"/>
-      <c r="I226" s="2" t="inlineStr"/>
-      <c r="J226" s="2" t="inlineStr"/>
-      <c r="K226" s="2" t="inlineStr"/>
-      <c r="L226" s="2" t="inlineStr"/>
-      <c r="M226" s="2" t="inlineStr"/>
-      <c r="N226" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000148. Langganan Internet</t>
-          </r>
-        </is>
-      </c>
+      <c r="H226" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522119</t>
+          </r>
+        </is>
+      </c>
+      <c r="I226" s="13" t="inlineStr"/>
+      <c r="J226" s="13" t="inlineStr"/>
+      <c r="K226" s="13" t="inlineStr"/>
+      <c r="L226" s="13" t="inlineStr"/>
+      <c r="M226" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Langganan Daya dan Jasa Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N226" s="13" t="inlineStr"/>
       <c r="O226" s="13" t="inlineStr"/>
       <c r="P226" s="13" t="inlineStr"/>
       <c r="Q226" s="14" t="n">
-        <v>1.146E8</v>
+        <v>1.447E8</v>
       </c>
       <c r="R226" s="14" t="inlineStr"/>
       <c r="S226" s="14" t="n">
@@ -13730,23 +13730,23 @@
       <c r="U226" s="14" t="inlineStr"/>
       <c r="V226" s="14" t="inlineStr"/>
       <c r="W226" s="14" t="n">
-        <v>1.044355E8</v>
+        <v>1.33021464E8</v>
       </c>
       <c r="X226" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y226" s="14" t="inlineStr"/>
       <c r="Z226" s="14" t="n">
-        <v>1.044355E8</v>
+        <v>1.33021464E8</v>
       </c>
       <c r="AA226" s="14" t="inlineStr"/>
       <c r="AB226" s="14" t="inlineStr"/>
       <c r="AC226" s="15" t="n">
-        <v>0.9113045375218151</v>
+        <v>0.919291389080857</v>
       </c>
       <c r="AD226" s="15" t="inlineStr"/>
       <c r="AE226" s="14" t="n">
-        <v>1.01645E7</v>
+        <v>1.1678536E7</v>
       </c>
       <c r="AF226" s="14" t="inlineStr"/>
       <c r="AG226" s="14" t="inlineStr"/>
@@ -13813,14 +13813,14 @@
       <c r="N228" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000240. Langganan aplikasi perkantoran</t>
+            <t xml:space="preserve">000148. Langganan Internet</t>
           </r>
         </is>
       </c>
       <c r="O228" s="13" t="inlineStr"/>
       <c r="P228" s="13" t="inlineStr"/>
       <c r="Q228" s="14" t="n">
-        <v>3.01E7</v>
+        <v>1.146E8</v>
       </c>
       <c r="R228" s="14" t="inlineStr"/>
       <c r="S228" s="14" t="n">
@@ -13830,23 +13830,23 @@
       <c r="U228" s="14" t="inlineStr"/>
       <c r="V228" s="14" t="inlineStr"/>
       <c r="W228" s="14" t="n">
-        <v>2.8585964E7</v>
+        <v>1.044355E8</v>
       </c>
       <c r="X228" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y228" s="14" t="inlineStr"/>
       <c r="Z228" s="14" t="n">
-        <v>2.8585964E7</v>
+        <v>1.044355E8</v>
       </c>
       <c r="AA228" s="14" t="inlineStr"/>
       <c r="AB228" s="14" t="inlineStr"/>
       <c r="AC228" s="15" t="n">
-        <v>0.9496998006644518</v>
+        <v>0.9113045375218151</v>
       </c>
       <c r="AD228" s="15" t="inlineStr"/>
       <c r="AE228" s="14" t="n">
-        <v>1514036.0</v>
+        <v>1.01645E7</v>
       </c>
       <c r="AF228" s="14" t="inlineStr"/>
       <c r="AG228" s="14" t="inlineStr"/>
@@ -13859,31 +13859,25 @@
       <c r="C229" s="2" t="inlineStr"/>
       <c r="D229" s="2" t="inlineStr"/>
       <c r="E229" s="2" t="inlineStr"/>
-      <c r="F229" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">002.DC</t>
-          </r>
-        </is>
-      </c>
-      <c r="G229" s="13" t="inlineStr"/>
-      <c r="H229" s="13" t="inlineStr"/>
-      <c r="I229" s="13" t="inlineStr"/>
-      <c r="J229" s="13" t="inlineStr"/>
-      <c r="K229" s="13" t="inlineStr"/>
-      <c r="L229" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pemeliharaan Kantor</t>
-          </r>
-        </is>
-      </c>
-      <c r="M229" s="13" t="inlineStr"/>
-      <c r="N229" s="13" t="inlineStr"/>
+      <c r="F229" s="2" t="inlineStr"/>
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr"/>
+      <c r="I229" s="2" t="inlineStr"/>
+      <c r="J229" s="2" t="inlineStr"/>
+      <c r="K229" s="2" t="inlineStr"/>
+      <c r="L229" s="2" t="inlineStr"/>
+      <c r="M229" s="2" t="inlineStr"/>
+      <c r="N229" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000240. Langganan aplikasi perkantoran</t>
+          </r>
+        </is>
+      </c>
       <c r="O229" s="13" t="inlineStr"/>
       <c r="P229" s="13" t="inlineStr"/>
       <c r="Q229" s="14" t="n">
-        <v>1.11442E9</v>
+        <v>3.01E7</v>
       </c>
       <c r="R229" s="14" t="inlineStr"/>
       <c r="S229" s="14" t="n">
@@ -13893,23 +13887,23 @@
       <c r="U229" s="14" t="inlineStr"/>
       <c r="V229" s="14" t="inlineStr"/>
       <c r="W229" s="14" t="n">
-        <v>6.74613153E8</v>
+        <v>2.8585964E7</v>
       </c>
       <c r="X229" s="14" t="n">
-        <v>3.1766138E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y229" s="14" t="inlineStr"/>
       <c r="Z229" s="14" t="n">
-        <v>7.06379291E8</v>
+        <v>2.8585964E7</v>
       </c>
       <c r="AA229" s="14" t="inlineStr"/>
       <c r="AB229" s="14" t="inlineStr"/>
       <c r="AC229" s="15" t="n">
-        <v>0.6338537454460617</v>
+        <v>0.9496998006644518</v>
       </c>
       <c r="AD229" s="15" t="inlineStr"/>
       <c r="AE229" s="14" t="n">
-        <v>4.08040709E8</v>
+        <v>1514036.0</v>
       </c>
       <c r="AF229" s="14" t="inlineStr"/>
       <c r="AG229" s="14" t="inlineStr"/>
@@ -13922,31 +13916,31 @@
       <c r="C230" s="2" t="inlineStr"/>
       <c r="D230" s="2" t="inlineStr"/>
       <c r="E230" s="2" t="inlineStr"/>
-      <c r="F230" s="2" t="inlineStr"/>
-      <c r="G230" s="2" t="inlineStr"/>
-      <c r="H230" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521811</t>
-          </r>
-        </is>
-      </c>
+      <c r="F230" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">002.DC</t>
+          </r>
+        </is>
+      </c>
+      <c r="G230" s="13" t="inlineStr"/>
+      <c r="H230" s="13" t="inlineStr"/>
       <c r="I230" s="13" t="inlineStr"/>
       <c r="J230" s="13" t="inlineStr"/>
       <c r="K230" s="13" t="inlineStr"/>
-      <c r="L230" s="13" t="inlineStr"/>
-      <c r="M230" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
-          </r>
-        </is>
-      </c>
+      <c r="L230" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pemeliharaan Kantor</t>
+          </r>
+        </is>
+      </c>
+      <c r="M230" s="13" t="inlineStr"/>
       <c r="N230" s="13" t="inlineStr"/>
       <c r="O230" s="13" t="inlineStr"/>
       <c r="P230" s="13" t="inlineStr"/>
       <c r="Q230" s="14" t="n">
-        <v>2.3E8</v>
+        <v>1.10842E9</v>
       </c>
       <c r="R230" s="14" t="inlineStr"/>
       <c r="S230" s="14" t="n">
@@ -13956,23 +13950,23 @@
       <c r="U230" s="14" t="inlineStr"/>
       <c r="V230" s="14" t="inlineStr"/>
       <c r="W230" s="14" t="n">
-        <v>2.179125E8</v>
+        <v>6.74613153E8</v>
       </c>
       <c r="X230" s="14" t="n">
-        <v>0.0</v>
+        <v>3.1766138E7</v>
       </c>
       <c r="Y230" s="14" t="inlineStr"/>
       <c r="Z230" s="14" t="n">
-        <v>2.179125E8</v>
+        <v>7.06379291E8</v>
       </c>
       <c r="AA230" s="14" t="inlineStr"/>
       <c r="AB230" s="14" t="inlineStr"/>
       <c r="AC230" s="15" t="n">
-        <v>0.9474456521739131</v>
+        <v>0.6372848658450768</v>
       </c>
       <c r="AD230" s="15" t="inlineStr"/>
       <c r="AE230" s="14" t="n">
-        <v>1.20875E7</v>
+        <v>4.02040709E8</v>
       </c>
       <c r="AF230" s="14" t="inlineStr"/>
       <c r="AG230" s="14" t="inlineStr"/>
@@ -13987,23 +13981,29 @@
       <c r="E231" s="2" t="inlineStr"/>
       <c r="F231" s="2" t="inlineStr"/>
       <c r="G231" s="2" t="inlineStr"/>
-      <c r="H231" s="2" t="inlineStr"/>
-      <c r="I231" s="2" t="inlineStr"/>
-      <c r="J231" s="2" t="inlineStr"/>
-      <c r="K231" s="2" t="inlineStr"/>
-      <c r="L231" s="2" t="inlineStr"/>
-      <c r="M231" s="2" t="inlineStr"/>
-      <c r="N231" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000149. Pakan Induk Ikan Koleksi</t>
-          </r>
-        </is>
-      </c>
+      <c r="H231" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521811</t>
+          </r>
+        </is>
+      </c>
+      <c r="I231" s="13" t="inlineStr"/>
+      <c r="J231" s="13" t="inlineStr"/>
+      <c r="K231" s="13" t="inlineStr"/>
+      <c r="L231" s="13" t="inlineStr"/>
+      <c r="M231" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Persediaan Barang Konsumsi</t>
+          </r>
+        </is>
+      </c>
+      <c r="N231" s="13" t="inlineStr"/>
       <c r="O231" s="13" t="inlineStr"/>
       <c r="P231" s="13" t="inlineStr"/>
       <c r="Q231" s="14" t="n">
-        <v>1.8E8</v>
+        <v>2.4E8</v>
       </c>
       <c r="R231" s="14" t="inlineStr"/>
       <c r="S231" s="14" t="n">
@@ -14013,23 +14013,23 @@
       <c r="U231" s="14" t="inlineStr"/>
       <c r="V231" s="14" t="inlineStr"/>
       <c r="W231" s="14" t="n">
-        <v>1.67915E8</v>
+        <v>2.179125E8</v>
       </c>
       <c r="X231" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y231" s="14" t="inlineStr"/>
       <c r="Z231" s="14" t="n">
-        <v>1.67915E8</v>
+        <v>2.179125E8</v>
       </c>
       <c r="AA231" s="14" t="inlineStr"/>
       <c r="AB231" s="14" t="inlineStr"/>
       <c r="AC231" s="15" t="n">
-        <v>0.9328611111111111</v>
+        <v>0.90796875</v>
       </c>
       <c r="AD231" s="15" t="inlineStr"/>
       <c r="AE231" s="14" t="n">
-        <v>1.2085E7</v>
+        <v>2.20875E7</v>
       </c>
       <c r="AF231" s="14" t="inlineStr"/>
       <c r="AG231" s="14" t="inlineStr"/>
@@ -14053,14 +14053,14 @@
       <c r="N232" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000286. Bahan Baku Pakan Ikan</t>
+            <t xml:space="preserve">000149. Pakan Induk Ikan Koleksi</t>
           </r>
         </is>
       </c>
       <c r="O232" s="13" t="inlineStr"/>
       <c r="P232" s="13" t="inlineStr"/>
       <c r="Q232" s="14" t="n">
-        <v>5.0E7</v>
+        <v>1.8E8</v>
       </c>
       <c r="R232" s="14" t="inlineStr"/>
       <c r="S232" s="14" t="n">
@@ -14070,23 +14070,23 @@
       <c r="U232" s="14" t="inlineStr"/>
       <c r="V232" s="14" t="inlineStr"/>
       <c r="W232" s="14" t="n">
-        <v>4.99975E7</v>
+        <v>1.67915E8</v>
       </c>
       <c r="X232" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y232" s="14" t="inlineStr"/>
       <c r="Z232" s="14" t="n">
-        <v>4.99975E7</v>
+        <v>1.67915E8</v>
       </c>
       <c r="AA232" s="14" t="inlineStr"/>
       <c r="AB232" s="14" t="inlineStr"/>
       <c r="AC232" s="15" t="n">
-        <v>0.99995</v>
+        <v>0.9328611111111111</v>
       </c>
       <c r="AD232" s="15" t="inlineStr"/>
       <c r="AE232" s="14" t="n">
-        <v>2500.0</v>
+        <v>1.2085E7</v>
       </c>
       <c r="AF232" s="14" t="inlineStr"/>
       <c r="AG232" s="14" t="inlineStr"/>
@@ -14101,29 +14101,23 @@
       <c r="E233" s="2" t="inlineStr"/>
       <c r="F233" s="2" t="inlineStr"/>
       <c r="G233" s="2" t="inlineStr"/>
-      <c r="H233" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">522191</t>
-          </r>
-        </is>
-      </c>
-      <c r="I233" s="13" t="inlineStr"/>
-      <c r="J233" s="13" t="inlineStr"/>
-      <c r="K233" s="13" t="inlineStr"/>
-      <c r="L233" s="13" t="inlineStr"/>
-      <c r="M233" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Jasa Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N233" s="13" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr"/>
+      <c r="I233" s="2" t="inlineStr"/>
+      <c r="J233" s="2" t="inlineStr"/>
+      <c r="K233" s="2" t="inlineStr"/>
+      <c r="L233" s="2" t="inlineStr"/>
+      <c r="M233" s="2" t="inlineStr"/>
+      <c r="N233" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000286. Bahan Baku Pakan Ikan</t>
+          </r>
+        </is>
+      </c>
       <c r="O233" s="13" t="inlineStr"/>
       <c r="P233" s="13" t="inlineStr"/>
       <c r="Q233" s="14" t="n">
-        <v>3.041E7</v>
+        <v>6.0E7</v>
       </c>
       <c r="R233" s="14" t="inlineStr"/>
       <c r="S233" s="14" t="n">
@@ -14133,23 +14127,23 @@
       <c r="U233" s="14" t="inlineStr"/>
       <c r="V233" s="14" t="inlineStr"/>
       <c r="W233" s="14" t="n">
-        <v>3.0406785E7</v>
+        <v>4.99975E7</v>
       </c>
       <c r="X233" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y233" s="14" t="inlineStr"/>
       <c r="Z233" s="14" t="n">
-        <v>3.0406785E7</v>
+        <v>4.99975E7</v>
       </c>
       <c r="AA233" s="14" t="inlineStr"/>
       <c r="AB233" s="14" t="inlineStr"/>
       <c r="AC233" s="15" t="n">
-        <v>0.9998942781979612</v>
+        <v>0.8332916666666667</v>
       </c>
       <c r="AD233" s="15" t="inlineStr"/>
       <c r="AE233" s="14" t="n">
-        <v>3215.0</v>
+        <v>1.00025E7</v>
       </c>
       <c r="AF233" s="14" t="inlineStr"/>
       <c r="AG233" s="14" t="inlineStr"/>
@@ -14164,19 +14158,25 @@
       <c r="E234" s="2" t="inlineStr"/>
       <c r="F234" s="2" t="inlineStr"/>
       <c r="G234" s="2" t="inlineStr"/>
-      <c r="H234" s="2" t="inlineStr"/>
-      <c r="I234" s="2" t="inlineStr"/>
-      <c r="J234" s="2" t="inlineStr"/>
-      <c r="K234" s="2" t="inlineStr"/>
-      <c r="L234" s="2" t="inlineStr"/>
-      <c r="M234" s="2" t="inlineStr"/>
-      <c r="N234" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000242. Jasa Penanganan Rayap</t>
-          </r>
-        </is>
-      </c>
+      <c r="H234" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">522191</t>
+          </r>
+        </is>
+      </c>
+      <c r="I234" s="13" t="inlineStr"/>
+      <c r="J234" s="13" t="inlineStr"/>
+      <c r="K234" s="13" t="inlineStr"/>
+      <c r="L234" s="13" t="inlineStr"/>
+      <c r="M234" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Jasa Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N234" s="13" t="inlineStr"/>
       <c r="O234" s="13" t="inlineStr"/>
       <c r="P234" s="13" t="inlineStr"/>
       <c r="Q234" s="14" t="n">
@@ -14221,29 +14221,23 @@
       <c r="E235" s="2" t="inlineStr"/>
       <c r="F235" s="2" t="inlineStr"/>
       <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">523111</t>
-          </r>
-        </is>
-      </c>
-      <c r="I235" s="13" t="inlineStr"/>
-      <c r="J235" s="13" t="inlineStr"/>
-      <c r="K235" s="13" t="inlineStr"/>
-      <c r="L235" s="13" t="inlineStr"/>
-      <c r="M235" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Pemeliharaan Gedung dan Bangunan</t>
-          </r>
-        </is>
-      </c>
-      <c r="N235" s="13" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr"/>
+      <c r="I235" s="2" t="inlineStr"/>
+      <c r="J235" s="2" t="inlineStr"/>
+      <c r="K235" s="2" t="inlineStr"/>
+      <c r="L235" s="2" t="inlineStr"/>
+      <c r="M235" s="2" t="inlineStr"/>
+      <c r="N235" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000242. Jasa Penanganan Rayap</t>
+          </r>
+        </is>
+      </c>
       <c r="O235" s="13" t="inlineStr"/>
       <c r="P235" s="13" t="inlineStr"/>
       <c r="Q235" s="14" t="n">
-        <v>3.7109E8</v>
+        <v>3.041E7</v>
       </c>
       <c r="R235" s="14" t="inlineStr"/>
       <c r="S235" s="14" t="n">
@@ -14253,23 +14247,23 @@
       <c r="U235" s="14" t="inlineStr"/>
       <c r="V235" s="14" t="inlineStr"/>
       <c r="W235" s="14" t="n">
-        <v>1.34221533E8</v>
+        <v>3.0406785E7</v>
       </c>
       <c r="X235" s="14" t="n">
-        <v>2.5076E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y235" s="14" t="inlineStr"/>
       <c r="Z235" s="14" t="n">
-        <v>1.59297533E8</v>
+        <v>3.0406785E7</v>
       </c>
       <c r="AA235" s="14" t="inlineStr"/>
       <c r="AB235" s="14" t="inlineStr"/>
       <c r="AC235" s="15" t="n">
-        <v>0.4292692689105069</v>
+        <v>0.9998942781979612</v>
       </c>
       <c r="AD235" s="15" t="inlineStr"/>
       <c r="AE235" s="14" t="n">
-        <v>2.11792467E8</v>
+        <v>3215.0</v>
       </c>
       <c r="AF235" s="14" t="inlineStr"/>
       <c r="AG235" s="14" t="inlineStr"/>
@@ -14284,23 +14278,29 @@
       <c r="E236" s="2" t="inlineStr"/>
       <c r="F236" s="2" t="inlineStr"/>
       <c r="G236" s="2" t="inlineStr"/>
-      <c r="H236" s="2" t="inlineStr"/>
-      <c r="I236" s="2" t="inlineStr"/>
-      <c r="J236" s="2" t="inlineStr"/>
-      <c r="K236" s="2" t="inlineStr"/>
-      <c r="L236" s="2" t="inlineStr"/>
-      <c r="M236" s="2" t="inlineStr"/>
-      <c r="N236" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000157. Pemeliharaan Kantor Cibalagung</t>
-          </r>
-        </is>
-      </c>
+      <c r="H236" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">523111</t>
+          </r>
+        </is>
+      </c>
+      <c r="I236" s="13" t="inlineStr"/>
+      <c r="J236" s="13" t="inlineStr"/>
+      <c r="K236" s="13" t="inlineStr"/>
+      <c r="L236" s="13" t="inlineStr"/>
+      <c r="M236" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Pemeliharaan Gedung dan Bangunan</t>
+          </r>
+        </is>
+      </c>
+      <c r="N236" s="13" t="inlineStr"/>
       <c r="O236" s="13" t="inlineStr"/>
       <c r="P236" s="13" t="inlineStr"/>
       <c r="Q236" s="14" t="n">
-        <v>1.7E7</v>
+        <v>3.5259E8</v>
       </c>
       <c r="R236" s="14" t="inlineStr"/>
       <c r="S236" s="14" t="n">
@@ -14310,30 +14310,30 @@
       <c r="U236" s="14" t="inlineStr"/>
       <c r="V236" s="14" t="inlineStr"/>
       <c r="W236" s="14" t="n">
-        <v>1.6931622E7</v>
+        <v>1.34221533E8</v>
       </c>
       <c r="X236" s="14" t="n">
-        <v>0.0</v>
+        <v>2.5076E7</v>
       </c>
       <c r="Y236" s="14" t="inlineStr"/>
       <c r="Z236" s="14" t="n">
-        <v>1.6931622E7</v>
+        <v>1.59297533E8</v>
       </c>
       <c r="AA236" s="14" t="inlineStr"/>
       <c r="AB236" s="14" t="inlineStr"/>
       <c r="AC236" s="15" t="n">
-        <v>0.9959777647058824</v>
+        <v>0.4517925437476956</v>
       </c>
       <c r="AD236" s="15" t="inlineStr"/>
       <c r="AE236" s="14" t="n">
-        <v>68378.0</v>
+        <v>1.93292467E8</v>
       </c>
       <c r="AF236" s="14" t="inlineStr"/>
       <c r="AG236" s="14" t="inlineStr"/>
       <c r="AH236" s="14" t="inlineStr"/>
       <c r="AI236" s="14" t="inlineStr"/>
     </row>
-    <row r="237" customHeight="1" ht="18">
+    <row r="237" customHeight="1" ht="15">
       <c r="A237" s="2" t="inlineStr"/>
       <c r="B237" s="2" t="inlineStr"/>
       <c r="C237" s="2" t="inlineStr"/>
@@ -14350,14 +14350,14 @@
       <c r="N237" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000158. Pemeliharaan Hatchery dan Laboratorium Cibalagung</t>
+            <t xml:space="preserve">000157. Pemeliharaan Kantor Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O237" s="13" t="inlineStr"/>
       <c r="P237" s="13" t="inlineStr"/>
       <c r="Q237" s="14" t="n">
-        <v>3.73E7</v>
+        <v>1.7E7</v>
       </c>
       <c r="R237" s="14" t="inlineStr"/>
       <c r="S237" s="14" t="n">
@@ -14367,30 +14367,30 @@
       <c r="U237" s="14" t="inlineStr"/>
       <c r="V237" s="14" t="inlineStr"/>
       <c r="W237" s="14" t="n">
-        <v>2.1347299E7</v>
+        <v>1.6931622E7</v>
       </c>
       <c r="X237" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y237" s="14" t="inlineStr"/>
       <c r="Z237" s="14" t="n">
-        <v>2.1347299E7</v>
+        <v>1.6931622E7</v>
       </c>
       <c r="AA237" s="14" t="inlineStr"/>
       <c r="AB237" s="14" t="inlineStr"/>
       <c r="AC237" s="15" t="n">
-        <v>0.5723136461126005</v>
+        <v>0.9959777647058824</v>
       </c>
       <c r="AD237" s="15" t="inlineStr"/>
       <c r="AE237" s="14" t="n">
-        <v>1.5952701E7</v>
+        <v>68378.0</v>
       </c>
       <c r="AF237" s="14" t="inlineStr"/>
       <c r="AG237" s="14" t="inlineStr"/>
       <c r="AH237" s="14" t="inlineStr"/>
       <c r="AI237" s="14" t="inlineStr"/>
     </row>
-    <row r="238" customHeight="1" ht="15">
+    <row r="238" customHeight="1" ht="18">
       <c r="A238" s="2" t="inlineStr"/>
       <c r="B238" s="2" t="inlineStr"/>
       <c r="C238" s="2" t="inlineStr"/>
@@ -14407,14 +14407,14 @@
       <c r="N238" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000159. Pemeliharaan Kolam Cibalagung</t>
+            <t xml:space="preserve">000158. Pemeliharaan Hatchery dan Laboratorium Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O238" s="13" t="inlineStr"/>
       <c r="P238" s="13" t="inlineStr"/>
       <c r="Q238" s="14" t="n">
-        <v>2.595E7</v>
+        <v>3.73E7</v>
       </c>
       <c r="R238" s="14" t="inlineStr"/>
       <c r="S238" s="14" t="n">
@@ -14424,23 +14424,23 @@
       <c r="U238" s="14" t="inlineStr"/>
       <c r="V238" s="14" t="inlineStr"/>
       <c r="W238" s="14" t="n">
-        <v>2.5327E7</v>
+        <v>2.1347299E7</v>
       </c>
       <c r="X238" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y238" s="14" t="inlineStr"/>
       <c r="Z238" s="14" t="n">
-        <v>2.5327E7</v>
+        <v>2.1347299E7</v>
       </c>
       <c r="AA238" s="14" t="inlineStr"/>
       <c r="AB238" s="14" t="inlineStr"/>
       <c r="AC238" s="15" t="n">
-        <v>0.9759922928709056</v>
+        <v>0.5723136461126005</v>
       </c>
       <c r="AD238" s="15" t="inlineStr"/>
       <c r="AE238" s="14" t="n">
-        <v>623000.0</v>
+        <v>1.5952701E7</v>
       </c>
       <c r="AF238" s="14" t="inlineStr"/>
       <c r="AG238" s="14" t="inlineStr"/>
@@ -14464,14 +14464,14 @@
       <c r="N239" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000160. Pemeliharaan Pagar Keliling Cibalagung</t>
+            <t xml:space="preserve">000159. Pemeliharaan Kolam Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O239" s="13" t="inlineStr"/>
       <c r="P239" s="13" t="inlineStr"/>
       <c r="Q239" s="14" t="n">
-        <v>2170000.0</v>
+        <v>2.595E7</v>
       </c>
       <c r="R239" s="14" t="inlineStr"/>
       <c r="S239" s="14" t="n">
@@ -14481,23 +14481,23 @@
       <c r="U239" s="14" t="inlineStr"/>
       <c r="V239" s="14" t="inlineStr"/>
       <c r="W239" s="14" t="n">
-        <v>2167000.0</v>
+        <v>2.5327E7</v>
       </c>
       <c r="X239" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y239" s="14" t="inlineStr"/>
       <c r="Z239" s="14" t="n">
-        <v>2167000.0</v>
+        <v>2.5327E7</v>
       </c>
       <c r="AA239" s="14" t="inlineStr"/>
       <c r="AB239" s="14" t="inlineStr"/>
       <c r="AC239" s="15" t="n">
-        <v>0.9986175115207373</v>
+        <v>0.9759922928709056</v>
       </c>
       <c r="AD239" s="15" t="inlineStr"/>
       <c r="AE239" s="14" t="n">
-        <v>3000.0</v>
+        <v>623000.0</v>
       </c>
       <c r="AF239" s="14" t="inlineStr"/>
       <c r="AG239" s="14" t="inlineStr"/>
@@ -14521,14 +14521,14 @@
       <c r="N240" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000161. Pemeliharaan Kantor Sempur</t>
+            <t xml:space="preserve">000160. Pemeliharaan Pagar Keliling Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O240" s="13" t="inlineStr"/>
       <c r="P240" s="13" t="inlineStr"/>
       <c r="Q240" s="14" t="n">
-        <v>1.341E8</v>
+        <v>2170000.0</v>
       </c>
       <c r="R240" s="14" t="inlineStr"/>
       <c r="S240" s="14" t="n">
@@ -14538,23 +14538,23 @@
       <c r="U240" s="14" t="inlineStr"/>
       <c r="V240" s="14" t="inlineStr"/>
       <c r="W240" s="14" t="n">
-        <v>4421000.0</v>
+        <v>2167000.0</v>
       </c>
       <c r="X240" s="14" t="n">
-        <v>2.5076E7</v>
+        <v>0.0</v>
       </c>
       <c r="Y240" s="14" t="inlineStr"/>
       <c r="Z240" s="14" t="n">
-        <v>2.9497E7</v>
+        <v>2167000.0</v>
       </c>
       <c r="AA240" s="14" t="inlineStr"/>
       <c r="AB240" s="14" t="inlineStr"/>
       <c r="AC240" s="15" t="n">
-        <v>0.2199627143922446</v>
+        <v>0.9986175115207373</v>
       </c>
       <c r="AD240" s="15" t="inlineStr"/>
       <c r="AE240" s="14" t="n">
-        <v>1.04603E8</v>
+        <v>3000.0</v>
       </c>
       <c r="AF240" s="14" t="inlineStr"/>
       <c r="AG240" s="14" t="inlineStr"/>
@@ -14578,14 +14578,14 @@
       <c r="N241" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000164. Pemeliharaan Kantor Depok</t>
+            <t xml:space="preserve">000161. Pemeliharaan Kantor Sempur</t>
           </r>
         </is>
       </c>
       <c r="O241" s="13" t="inlineStr"/>
       <c r="P241" s="13" t="inlineStr"/>
       <c r="Q241" s="14" t="n">
-        <v>2800000.0</v>
+        <v>1.156E8</v>
       </c>
       <c r="R241" s="14" t="inlineStr"/>
       <c r="S241" s="14" t="n">
@@ -14595,23 +14595,23 @@
       <c r="U241" s="14" t="inlineStr"/>
       <c r="V241" s="14" t="inlineStr"/>
       <c r="W241" s="14" t="n">
-        <v>1360000.0</v>
+        <v>4421000.0</v>
       </c>
       <c r="X241" s="14" t="n">
-        <v>0.0</v>
+        <v>2.5076E7</v>
       </c>
       <c r="Y241" s="14" t="inlineStr"/>
       <c r="Z241" s="14" t="n">
-        <v>1360000.0</v>
+        <v>2.9497E7</v>
       </c>
       <c r="AA241" s="14" t="inlineStr"/>
       <c r="AB241" s="14" t="inlineStr"/>
       <c r="AC241" s="15" t="n">
-        <v>0.4857142857142857</v>
+        <v>0.2551643598615917</v>
       </c>
       <c r="AD241" s="15" t="inlineStr"/>
       <c r="AE241" s="14" t="n">
-        <v>1440000.0</v>
+        <v>8.6103E7</v>
       </c>
       <c r="AF241" s="14" t="inlineStr"/>
       <c r="AG241" s="14" t="inlineStr"/>
@@ -14635,14 +14635,14 @@
       <c r="N242" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000165. Pemeliharaan Gedung Laboratorium Depok</t>
+            <t xml:space="preserve">000164. Pemeliharaan Kantor Depok</t>
           </r>
         </is>
       </c>
       <c r="O242" s="13" t="inlineStr"/>
       <c r="P242" s="13" t="inlineStr"/>
       <c r="Q242" s="14" t="n">
-        <v>2.66E7</v>
+        <v>2800000.0</v>
       </c>
       <c r="R242" s="14" t="inlineStr"/>
       <c r="S242" s="14" t="n">
@@ -14652,23 +14652,23 @@
       <c r="U242" s="14" t="inlineStr"/>
       <c r="V242" s="14" t="inlineStr"/>
       <c r="W242" s="14" t="n">
-        <v>1.2143622E7</v>
+        <v>1360000.0</v>
       </c>
       <c r="X242" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y242" s="14" t="inlineStr"/>
       <c r="Z242" s="14" t="n">
-        <v>1.2143622E7</v>
+        <v>1360000.0</v>
       </c>
       <c r="AA242" s="14" t="inlineStr"/>
       <c r="AB242" s="14" t="inlineStr"/>
       <c r="AC242" s="15" t="n">
-        <v>0.45652714285714285</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="AD242" s="15" t="inlineStr"/>
       <c r="AE242" s="14" t="n">
-        <v>1.4456378E7</v>
+        <v>1440000.0</v>
       </c>
       <c r="AF242" s="14" t="inlineStr"/>
       <c r="AG242" s="14" t="inlineStr"/>
@@ -14692,14 +14692,14 @@
       <c r="N243" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000167. Pemeliharaan Halaman Kantor Depok</t>
+            <t xml:space="preserve">000165. Pemeliharaan Gedung Laboratorium Depok</t>
           </r>
         </is>
       </c>
       <c r="O243" s="13" t="inlineStr"/>
       <c r="P243" s="13" t="inlineStr"/>
       <c r="Q243" s="14" t="n">
-        <v>1.443E7</v>
+        <v>2.66E7</v>
       </c>
       <c r="R243" s="14" t="inlineStr"/>
       <c r="S243" s="14" t="n">
@@ -14709,23 +14709,23 @@
       <c r="U243" s="14" t="inlineStr"/>
       <c r="V243" s="14" t="inlineStr"/>
       <c r="W243" s="14" t="n">
-        <v>1.443E7</v>
+        <v>1.2143622E7</v>
       </c>
       <c r="X243" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y243" s="14" t="inlineStr"/>
       <c r="Z243" s="14" t="n">
-        <v>1.443E7</v>
+        <v>1.2143622E7</v>
       </c>
       <c r="AA243" s="14" t="inlineStr"/>
       <c r="AB243" s="14" t="inlineStr"/>
       <c r="AC243" s="15" t="n">
-        <v>1.0</v>
+        <v>0.45652714285714285</v>
       </c>
       <c r="AD243" s="15" t="inlineStr"/>
       <c r="AE243" s="14" t="n">
-        <v>0.0</v>
+        <v>1.4456378E7</v>
       </c>
       <c r="AF243" s="14" t="inlineStr"/>
       <c r="AG243" s="14" t="inlineStr"/>
@@ -14749,14 +14749,14 @@
       <c r="N244" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000170. Pemeliharaan Halaman Kantor Sempur</t>
+            <t xml:space="preserve">000167. Pemeliharaan Halaman Kantor Depok</t>
           </r>
         </is>
       </c>
       <c r="O244" s="13" t="inlineStr"/>
       <c r="P244" s="13" t="inlineStr"/>
       <c r="Q244" s="14" t="n">
-        <v>4150000.0</v>
+        <v>1.443E7</v>
       </c>
       <c r="R244" s="14" t="inlineStr"/>
       <c r="S244" s="14" t="n">
@@ -14766,23 +14766,23 @@
       <c r="U244" s="14" t="inlineStr"/>
       <c r="V244" s="14" t="inlineStr"/>
       <c r="W244" s="14" t="n">
-        <v>1576500.0</v>
+        <v>1.443E7</v>
       </c>
       <c r="X244" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y244" s="14" t="inlineStr"/>
       <c r="Z244" s="14" t="n">
-        <v>1576500.0</v>
+        <v>1.443E7</v>
       </c>
       <c r="AA244" s="14" t="inlineStr"/>
       <c r="AB244" s="14" t="inlineStr"/>
       <c r="AC244" s="15" t="n">
-        <v>0.37987951807228915</v>
+        <v>1.0</v>
       </c>
       <c r="AD244" s="15" t="inlineStr"/>
       <c r="AE244" s="14" t="n">
-        <v>2573500.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF244" s="14" t="inlineStr"/>
       <c r="AG244" s="14" t="inlineStr"/>
@@ -14806,14 +14806,14 @@
       <c r="N245" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000241. Pemeliharaan Rumah Dinas Cibalagung</t>
+            <t xml:space="preserve">000170. Pemeliharaan Halaman Kantor Sempur</t>
           </r>
         </is>
       </c>
       <c r="O245" s="13" t="inlineStr"/>
       <c r="P245" s="13" t="inlineStr"/>
       <c r="Q245" s="14" t="n">
-        <v>4400000.0</v>
+        <v>4150000.0</v>
       </c>
       <c r="R245" s="14" t="inlineStr"/>
       <c r="S245" s="14" t="n">
@@ -14823,23 +14823,23 @@
       <c r="U245" s="14" t="inlineStr"/>
       <c r="V245" s="14" t="inlineStr"/>
       <c r="W245" s="14" t="n">
-        <v>4180000.0</v>
+        <v>1576500.0</v>
       </c>
       <c r="X245" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y245" s="14" t="inlineStr"/>
       <c r="Z245" s="14" t="n">
-        <v>4180000.0</v>
+        <v>1576500.0</v>
       </c>
       <c r="AA245" s="14" t="inlineStr"/>
       <c r="AB245" s="14" t="inlineStr"/>
       <c r="AC245" s="15" t="n">
-        <v>0.95</v>
+        <v>0.37987951807228915</v>
       </c>
       <c r="AD245" s="15" t="inlineStr"/>
       <c r="AE245" s="14" t="n">
-        <v>220000.0</v>
+        <v>2573500.0</v>
       </c>
       <c r="AF245" s="14" t="inlineStr"/>
       <c r="AG245" s="14" t="inlineStr"/>
@@ -14863,14 +14863,14 @@
       <c r="N246" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000264. Pemeliharaan Kolam Cijeruk</t>
+            <t xml:space="preserve">000241. Pemeliharaan Rumah Dinas Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O246" s="13" t="inlineStr"/>
       <c r="P246" s="13" t="inlineStr"/>
       <c r="Q246" s="14" t="n">
-        <v>4.21E7</v>
+        <v>4400000.0</v>
       </c>
       <c r="R246" s="14" t="inlineStr"/>
       <c r="S246" s="14" t="n">
@@ -14880,23 +14880,23 @@
       <c r="U246" s="14" t="inlineStr"/>
       <c r="V246" s="14" t="inlineStr"/>
       <c r="W246" s="14" t="n">
-        <v>1.5284E7</v>
+        <v>4180000.0</v>
       </c>
       <c r="X246" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y246" s="14" t="inlineStr"/>
       <c r="Z246" s="14" t="n">
-        <v>1.5284E7</v>
+        <v>4180000.0</v>
       </c>
       <c r="AA246" s="14" t="inlineStr"/>
       <c r="AB246" s="14" t="inlineStr"/>
       <c r="AC246" s="15" t="n">
-        <v>0.36304038004750594</v>
+        <v>0.95</v>
       </c>
       <c r="AD246" s="15" t="inlineStr"/>
       <c r="AE246" s="14" t="n">
-        <v>2.6816E7</v>
+        <v>220000.0</v>
       </c>
       <c r="AF246" s="14" t="inlineStr"/>
       <c r="AG246" s="14" t="inlineStr"/>
@@ -14920,14 +14920,14 @@
       <c r="N247" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000280. Pemeliharaan Kantor Cijeruk</t>
+            <t xml:space="preserve">000264. Pemeliharaan Kolam Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O247" s="13" t="inlineStr"/>
       <c r="P247" s="13" t="inlineStr"/>
       <c r="Q247" s="14" t="n">
-        <v>3.059E7</v>
+        <v>4.21E7</v>
       </c>
       <c r="R247" s="14" t="inlineStr"/>
       <c r="S247" s="14" t="n">
@@ -14937,23 +14937,23 @@
       <c r="U247" s="14" t="inlineStr"/>
       <c r="V247" s="14" t="inlineStr"/>
       <c r="W247" s="14" t="n">
-        <v>0.0</v>
+        <v>1.5284E7</v>
       </c>
       <c r="X247" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y247" s="14" t="inlineStr"/>
       <c r="Z247" s="14" t="n">
-        <v>0.0</v>
+        <v>1.5284E7</v>
       </c>
       <c r="AA247" s="14" t="inlineStr"/>
       <c r="AB247" s="14" t="inlineStr"/>
       <c r="AC247" s="15" t="n">
-        <v>0.0</v>
+        <v>0.36304038004750594</v>
       </c>
       <c r="AD247" s="15" t="inlineStr"/>
       <c r="AE247" s="14" t="n">
-        <v>3.059E7</v>
+        <v>2.6816E7</v>
       </c>
       <c r="AF247" s="14" t="inlineStr"/>
       <c r="AG247" s="14" t="inlineStr"/>
@@ -14977,14 +14977,14 @@
       <c r="N248" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000281. Pemeliharaan Pagar Keliling Depok</t>
+            <t xml:space="preserve">000280. Pemeliharaan Kantor Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O248" s="13" t="inlineStr"/>
       <c r="P248" s="13" t="inlineStr"/>
       <c r="Q248" s="14" t="n">
-        <v>1.0E7</v>
+        <v>3.059E7</v>
       </c>
       <c r="R248" s="14" t="inlineStr"/>
       <c r="S248" s="14" t="n">
@@ -14994,23 +14994,23 @@
       <c r="U248" s="14" t="inlineStr"/>
       <c r="V248" s="14" t="inlineStr"/>
       <c r="W248" s="14" t="n">
-        <v>9640490.0</v>
+        <v>0.0</v>
       </c>
       <c r="X248" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y248" s="14" t="inlineStr"/>
       <c r="Z248" s="14" t="n">
-        <v>9640490.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA248" s="14" t="inlineStr"/>
       <c r="AB248" s="14" t="inlineStr"/>
       <c r="AC248" s="15" t="n">
-        <v>0.964049</v>
+        <v>0.0</v>
       </c>
       <c r="AD248" s="15" t="inlineStr"/>
       <c r="AE248" s="14" t="n">
-        <v>359510.0</v>
+        <v>3.059E7</v>
       </c>
       <c r="AF248" s="14" t="inlineStr"/>
       <c r="AG248" s="14" t="inlineStr"/>
@@ -15034,14 +15034,14 @@
       <c r="N249" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000298. Pemeliharaan Halaman Kantor Cijeruk</t>
+            <t xml:space="preserve">000281. Pemeliharaan Pagar Keliling Depok</t>
           </r>
         </is>
       </c>
       <c r="O249" s="13" t="inlineStr"/>
       <c r="P249" s="13" t="inlineStr"/>
       <c r="Q249" s="14" t="n">
-        <v>4300000.0</v>
+        <v>1.0E7</v>
       </c>
       <c r="R249" s="14" t="inlineStr"/>
       <c r="S249" s="14" t="n">
@@ -15051,23 +15051,23 @@
       <c r="U249" s="14" t="inlineStr"/>
       <c r="V249" s="14" t="inlineStr"/>
       <c r="W249" s="14" t="n">
-        <v>0.0</v>
+        <v>9640490.0</v>
       </c>
       <c r="X249" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y249" s="14" t="inlineStr"/>
       <c r="Z249" s="14" t="n">
-        <v>0.0</v>
+        <v>9640490.0</v>
       </c>
       <c r="AA249" s="14" t="inlineStr"/>
       <c r="AB249" s="14" t="inlineStr"/>
       <c r="AC249" s="15" t="n">
-        <v>0.0</v>
+        <v>0.964049</v>
       </c>
       <c r="AD249" s="15" t="inlineStr"/>
       <c r="AE249" s="14" t="n">
-        <v>4300000.0</v>
+        <v>359510.0</v>
       </c>
       <c r="AF249" s="14" t="inlineStr"/>
       <c r="AG249" s="14" t="inlineStr"/>
@@ -15091,14 +15091,14 @@
       <c r="N250" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000302. Pemeliharaan Gedung Laboratorium Permanen</t>
+            <t xml:space="preserve">000298. Pemeliharaan Halaman Kantor Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O250" s="13" t="inlineStr"/>
       <c r="P250" s="13" t="inlineStr"/>
       <c r="Q250" s="14" t="n">
-        <v>5700000.0</v>
+        <v>4300000.0</v>
       </c>
       <c r="R250" s="14" t="inlineStr"/>
       <c r="S250" s="14" t="n">
@@ -15124,7 +15124,7 @@
       </c>
       <c r="AD250" s="15" t="inlineStr"/>
       <c r="AE250" s="14" t="n">
-        <v>5700000.0</v>
+        <v>4300000.0</v>
       </c>
       <c r="AF250" s="14" t="inlineStr"/>
       <c r="AG250" s="14" t="inlineStr"/>
@@ -15148,14 +15148,14 @@
       <c r="N251" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000303. Pemeliharaan Mushola</t>
+            <t xml:space="preserve">000302. Pemeliharaan Gedung Laboratorium Permanen</t>
           </r>
         </is>
       </c>
       <c r="O251" s="13" t="inlineStr"/>
       <c r="P251" s="13" t="inlineStr"/>
       <c r="Q251" s="14" t="n">
-        <v>9500000.0</v>
+        <v>5700000.0</v>
       </c>
       <c r="R251" s="14" t="inlineStr"/>
       <c r="S251" s="14" t="n">
@@ -15165,23 +15165,23 @@
       <c r="U251" s="14" t="inlineStr"/>
       <c r="V251" s="14" t="inlineStr"/>
       <c r="W251" s="14" t="n">
-        <v>5413000.0</v>
+        <v>0.0</v>
       </c>
       <c r="X251" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y251" s="14" t="inlineStr"/>
       <c r="Z251" s="14" t="n">
-        <v>5413000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA251" s="14" t="inlineStr"/>
       <c r="AB251" s="14" t="inlineStr"/>
       <c r="AC251" s="15" t="n">
-        <v>0.5697894736842105</v>
+        <v>0.0</v>
       </c>
       <c r="AD251" s="15" t="inlineStr"/>
       <c r="AE251" s="14" t="n">
-        <v>4087000.0</v>
+        <v>5700000.0</v>
       </c>
       <c r="AF251" s="14" t="inlineStr"/>
       <c r="AG251" s="14" t="inlineStr"/>
@@ -15196,29 +15196,23 @@
       <c r="E252" s="2" t="inlineStr"/>
       <c r="F252" s="2" t="inlineStr"/>
       <c r="G252" s="2" t="inlineStr"/>
-      <c r="H252" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">523121</t>
-          </r>
-        </is>
-      </c>
-      <c r="I252" s="13" t="inlineStr"/>
-      <c r="J252" s="13" t="inlineStr"/>
-      <c r="K252" s="13" t="inlineStr"/>
-      <c r="L252" s="13" t="inlineStr"/>
-      <c r="M252" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Pemeliharaan Peralatan dan Mesin</t>
-          </r>
-        </is>
-      </c>
-      <c r="N252" s="13" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr"/>
+      <c r="I252" s="2" t="inlineStr"/>
+      <c r="J252" s="2" t="inlineStr"/>
+      <c r="K252" s="2" t="inlineStr"/>
+      <c r="L252" s="2" t="inlineStr"/>
+      <c r="M252" s="2" t="inlineStr"/>
+      <c r="N252" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000303. Pemeliharaan Mushola</t>
+          </r>
+        </is>
+      </c>
       <c r="O252" s="13" t="inlineStr"/>
       <c r="P252" s="13" t="inlineStr"/>
       <c r="Q252" s="14" t="n">
-        <v>3.3E8</v>
+        <v>9500000.0</v>
       </c>
       <c r="R252" s="14" t="inlineStr"/>
       <c r="S252" s="14" t="n">
@@ -15228,23 +15222,23 @@
       <c r="U252" s="14" t="inlineStr"/>
       <c r="V252" s="14" t="inlineStr"/>
       <c r="W252" s="14" t="n">
-        <v>2.11521335E8</v>
+        <v>5413000.0</v>
       </c>
       <c r="X252" s="14" t="n">
-        <v>6690138.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y252" s="14" t="inlineStr"/>
       <c r="Z252" s="14" t="n">
-        <v>2.18211473E8</v>
+        <v>5413000.0</v>
       </c>
       <c r="AA252" s="14" t="inlineStr"/>
       <c r="AB252" s="14" t="inlineStr"/>
       <c r="AC252" s="15" t="n">
-        <v>0.6612468878787878</v>
+        <v>0.5697894736842105</v>
       </c>
       <c r="AD252" s="15" t="inlineStr"/>
       <c r="AE252" s="14" t="n">
-        <v>1.11788527E8</v>
+        <v>4087000.0</v>
       </c>
       <c r="AF252" s="14" t="inlineStr"/>
       <c r="AG252" s="14" t="inlineStr"/>
@@ -15259,23 +15253,29 @@
       <c r="E253" s="2" t="inlineStr"/>
       <c r="F253" s="2" t="inlineStr"/>
       <c r="G253" s="2" t="inlineStr"/>
-      <c r="H253" s="2" t="inlineStr"/>
-      <c r="I253" s="2" t="inlineStr"/>
-      <c r="J253" s="2" t="inlineStr"/>
-      <c r="K253" s="2" t="inlineStr"/>
-      <c r="L253" s="2" t="inlineStr"/>
-      <c r="M253" s="2" t="inlineStr"/>
-      <c r="N253" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000175. Pemeliharaan AC Split</t>
-          </r>
-        </is>
-      </c>
+      <c r="H253" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">523121</t>
+          </r>
+        </is>
+      </c>
+      <c r="I253" s="13" t="inlineStr"/>
+      <c r="J253" s="13" t="inlineStr"/>
+      <c r="K253" s="13" t="inlineStr"/>
+      <c r="L253" s="13" t="inlineStr"/>
+      <c r="M253" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Pemeliharaan Peralatan dan Mesin</t>
+          </r>
+        </is>
+      </c>
+      <c r="N253" s="13" t="inlineStr"/>
       <c r="O253" s="13" t="inlineStr"/>
       <c r="P253" s="13" t="inlineStr"/>
       <c r="Q253" s="14" t="n">
-        <v>2.257E7</v>
+        <v>3.325E8</v>
       </c>
       <c r="R253" s="14" t="inlineStr"/>
       <c r="S253" s="14" t="n">
@@ -15285,23 +15285,23 @@
       <c r="U253" s="14" t="inlineStr"/>
       <c r="V253" s="14" t="inlineStr"/>
       <c r="W253" s="14" t="n">
-        <v>1.396E7</v>
+        <v>2.11521335E8</v>
       </c>
       <c r="X253" s="14" t="n">
-        <v>2890000.0</v>
+        <v>6690138.0</v>
       </c>
       <c r="Y253" s="14" t="inlineStr"/>
       <c r="Z253" s="14" t="n">
-        <v>1.685E7</v>
+        <v>2.18211473E8</v>
       </c>
       <c r="AA253" s="14" t="inlineStr"/>
       <c r="AB253" s="14" t="inlineStr"/>
       <c r="AC253" s="15" t="n">
-        <v>0.7465662383695171</v>
+        <v>0.6562751067669172</v>
       </c>
       <c r="AD253" s="15" t="inlineStr"/>
       <c r="AE253" s="14" t="n">
-        <v>5720000.0</v>
+        <v>1.14288527E8</v>
       </c>
       <c r="AF253" s="14" t="inlineStr"/>
       <c r="AG253" s="14" t="inlineStr"/>
@@ -15368,14 +15368,14 @@
       <c r="N255" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000176. Pemeliharaan Laptop</t>
+            <t xml:space="preserve">000175. Pemeliharaan AC Split</t>
           </r>
         </is>
       </c>
       <c r="O255" s="13" t="inlineStr"/>
       <c r="P255" s="13" t="inlineStr"/>
       <c r="Q255" s="14" t="n">
-        <v>5000000.0</v>
+        <v>2.257E7</v>
       </c>
       <c r="R255" s="14" t="inlineStr"/>
       <c r="S255" s="14" t="n">
@@ -15385,23 +15385,23 @@
       <c r="U255" s="14" t="inlineStr"/>
       <c r="V255" s="14" t="inlineStr"/>
       <c r="W255" s="14" t="n">
-        <v>2487928.0</v>
+        <v>1.396E7</v>
       </c>
       <c r="X255" s="14" t="n">
-        <v>0.0</v>
+        <v>2890000.0</v>
       </c>
       <c r="Y255" s="14" t="inlineStr"/>
       <c r="Z255" s="14" t="n">
-        <v>2487928.0</v>
+        <v>1.685E7</v>
       </c>
       <c r="AA255" s="14" t="inlineStr"/>
       <c r="AB255" s="14" t="inlineStr"/>
       <c r="AC255" s="15" t="n">
-        <v>0.4975856</v>
+        <v>0.7465662383695171</v>
       </c>
       <c r="AD255" s="15" t="inlineStr"/>
       <c r="AE255" s="14" t="n">
-        <v>2512072.0</v>
+        <v>5720000.0</v>
       </c>
       <c r="AF255" s="14" t="inlineStr"/>
       <c r="AG255" s="14" t="inlineStr"/>
@@ -15425,14 +15425,14 @@
       <c r="N256" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000182. Pemeliharaan Instalasi Listrik</t>
+            <t xml:space="preserve">000176. Pemeliharaan Laptop</t>
           </r>
         </is>
       </c>
       <c r="O256" s="13" t="inlineStr"/>
       <c r="P256" s="13" t="inlineStr"/>
       <c r="Q256" s="14" t="n">
-        <v>4.5E7</v>
+        <v>5000000.0</v>
       </c>
       <c r="R256" s="14" t="inlineStr"/>
       <c r="S256" s="14" t="n">
@@ -15442,23 +15442,23 @@
       <c r="U256" s="14" t="inlineStr"/>
       <c r="V256" s="14" t="inlineStr"/>
       <c r="W256" s="14" t="n">
-        <v>2.9845218E7</v>
+        <v>2487928.0</v>
       </c>
       <c r="X256" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y256" s="14" t="inlineStr"/>
       <c r="Z256" s="14" t="n">
-        <v>2.9845218E7</v>
+        <v>2487928.0</v>
       </c>
       <c r="AA256" s="14" t="inlineStr"/>
       <c r="AB256" s="14" t="inlineStr"/>
       <c r="AC256" s="15" t="n">
-        <v>0.6632270666666666</v>
+        <v>0.4975856</v>
       </c>
       <c r="AD256" s="15" t="inlineStr"/>
       <c r="AE256" s="14" t="n">
-        <v>1.5154782E7</v>
+        <v>2512072.0</v>
       </c>
       <c r="AF256" s="14" t="inlineStr"/>
       <c r="AG256" s="14" t="inlineStr"/>
@@ -15482,14 +15482,14 @@
       <c r="N257" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000183. Pemeliharaan Kendaraan Roda 4</t>
+            <t xml:space="preserve">000182. Pemeliharaan Instalasi Listrik</t>
           </r>
         </is>
       </c>
       <c r="O257" s="13" t="inlineStr"/>
       <c r="P257" s="13" t="inlineStr"/>
       <c r="Q257" s="14" t="n">
-        <v>1.6975E8</v>
+        <v>4.5E7</v>
       </c>
       <c r="R257" s="14" t="inlineStr"/>
       <c r="S257" s="14" t="n">
@@ -15499,23 +15499,23 @@
       <c r="U257" s="14" t="inlineStr"/>
       <c r="V257" s="14" t="inlineStr"/>
       <c r="W257" s="14" t="n">
-        <v>1.22043496E8</v>
+        <v>2.9845218E7</v>
       </c>
       <c r="X257" s="14" t="n">
-        <v>1490000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y257" s="14" t="inlineStr"/>
       <c r="Z257" s="14" t="n">
-        <v>1.23533496E8</v>
+        <v>2.9845218E7</v>
       </c>
       <c r="AA257" s="14" t="inlineStr"/>
       <c r="AB257" s="14" t="inlineStr"/>
       <c r="AC257" s="15" t="n">
-        <v>0.7277378262150221</v>
+        <v>0.6632270666666666</v>
       </c>
       <c r="AD257" s="15" t="inlineStr"/>
       <c r="AE257" s="14" t="n">
-        <v>4.6216504E7</v>
+        <v>1.5154782E7</v>
       </c>
       <c r="AF257" s="14" t="inlineStr"/>
       <c r="AG257" s="14" t="inlineStr"/>
@@ -15539,14 +15539,14 @@
       <c r="N258" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000184. Pemeliharaan Kendaraan Roda 2</t>
+            <t xml:space="preserve">000183. Pemeliharaan Kendaraan Roda 4</t>
           </r>
         </is>
       </c>
       <c r="O258" s="13" t="inlineStr"/>
       <c r="P258" s="13" t="inlineStr"/>
       <c r="Q258" s="14" t="n">
-        <v>4500000.0</v>
+        <v>1.6975E8</v>
       </c>
       <c r="R258" s="14" t="inlineStr"/>
       <c r="S258" s="14" t="n">
@@ -15556,23 +15556,23 @@
       <c r="U258" s="14" t="inlineStr"/>
       <c r="V258" s="14" t="inlineStr"/>
       <c r="W258" s="14" t="n">
-        <v>4147992.0</v>
+        <v>1.22043496E8</v>
       </c>
       <c r="X258" s="14" t="n">
-        <v>0.0</v>
+        <v>1490000.0</v>
       </c>
       <c r="Y258" s="14" t="inlineStr"/>
       <c r="Z258" s="14" t="n">
-        <v>4147992.0</v>
+        <v>1.23533496E8</v>
       </c>
       <c r="AA258" s="14" t="inlineStr"/>
       <c r="AB258" s="14" t="inlineStr"/>
       <c r="AC258" s="15" t="n">
-        <v>0.921776</v>
+        <v>0.7277378262150221</v>
       </c>
       <c r="AD258" s="15" t="inlineStr"/>
       <c r="AE258" s="14" t="n">
-        <v>352008.0</v>
+        <v>4.6216504E7</v>
       </c>
       <c r="AF258" s="14" t="inlineStr"/>
       <c r="AG258" s="14" t="inlineStr"/>
@@ -15596,14 +15596,14 @@
       <c r="N259" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000185. Pemeliharaan CCTV</t>
+            <t xml:space="preserve">000184. Pemeliharaan Kendaraan Roda 2</t>
           </r>
         </is>
       </c>
       <c r="O259" s="13" t="inlineStr"/>
       <c r="P259" s="13" t="inlineStr"/>
       <c r="Q259" s="14" t="n">
-        <v>2.1E7</v>
+        <v>4500000.0</v>
       </c>
       <c r="R259" s="14" t="inlineStr"/>
       <c r="S259" s="14" t="n">
@@ -15613,23 +15613,23 @@
       <c r="U259" s="14" t="inlineStr"/>
       <c r="V259" s="14" t="inlineStr"/>
       <c r="W259" s="14" t="n">
-        <v>1.4290555E7</v>
+        <v>4147992.0</v>
       </c>
       <c r="X259" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y259" s="14" t="inlineStr"/>
       <c r="Z259" s="14" t="n">
-        <v>1.4290555E7</v>
+        <v>4147992.0</v>
       </c>
       <c r="AA259" s="14" t="inlineStr"/>
       <c r="AB259" s="14" t="inlineStr"/>
       <c r="AC259" s="15" t="n">
-        <v>0.680502619047619</v>
+        <v>0.921776</v>
       </c>
       <c r="AD259" s="15" t="inlineStr"/>
       <c r="AE259" s="14" t="n">
-        <v>6709445.0</v>
+        <v>352008.0</v>
       </c>
       <c r="AF259" s="14" t="inlineStr"/>
       <c r="AG259" s="14" t="inlineStr"/>
@@ -15653,14 +15653,14 @@
       <c r="N260" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000186. Pemeliharaan Genset 250 KVA</t>
+            <t xml:space="preserve">000185. Pemeliharaan CCTV</t>
           </r>
         </is>
       </c>
       <c r="O260" s="13" t="inlineStr"/>
       <c r="P260" s="13" t="inlineStr"/>
       <c r="Q260" s="14" t="n">
-        <v>9010000.0</v>
+        <v>2.1E7</v>
       </c>
       <c r="R260" s="14" t="inlineStr"/>
       <c r="S260" s="14" t="n">
@@ -15670,23 +15670,23 @@
       <c r="U260" s="14" t="inlineStr"/>
       <c r="V260" s="14" t="inlineStr"/>
       <c r="W260" s="14" t="n">
-        <v>1000052.0</v>
+        <v>1.4290555E7</v>
       </c>
       <c r="X260" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y260" s="14" t="inlineStr"/>
       <c r="Z260" s="14" t="n">
-        <v>1000052.0</v>
+        <v>1.4290555E7</v>
       </c>
       <c r="AA260" s="14" t="inlineStr"/>
       <c r="AB260" s="14" t="inlineStr"/>
       <c r="AC260" s="15" t="n">
-        <v>0.11099356270810211</v>
+        <v>0.680502619047619</v>
       </c>
       <c r="AD260" s="15" t="inlineStr"/>
       <c r="AE260" s="14" t="n">
-        <v>8009948.0</v>
+        <v>6709445.0</v>
       </c>
       <c r="AF260" s="14" t="inlineStr"/>
       <c r="AG260" s="14" t="inlineStr"/>
@@ -15710,14 +15710,14 @@
       <c r="N261" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000187. Pemeliharaan Genset 40 KVA</t>
+            <t xml:space="preserve">000186. Pemeliharaan Genset 250 KVA</t>
           </r>
         </is>
       </c>
       <c r="O261" s="13" t="inlineStr"/>
       <c r="P261" s="13" t="inlineStr"/>
       <c r="Q261" s="14" t="n">
-        <v>4050000.0</v>
+        <v>9010000.0</v>
       </c>
       <c r="R261" s="14" t="inlineStr"/>
       <c r="S261" s="14" t="n">
@@ -15727,23 +15727,23 @@
       <c r="U261" s="14" t="inlineStr"/>
       <c r="V261" s="14" t="inlineStr"/>
       <c r="W261" s="14" t="n">
-        <v>1978406.0</v>
+        <v>1000052.0</v>
       </c>
       <c r="X261" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y261" s="14" t="inlineStr"/>
       <c r="Z261" s="14" t="n">
-        <v>1978406.0</v>
+        <v>1000052.0</v>
       </c>
       <c r="AA261" s="14" t="inlineStr"/>
       <c r="AB261" s="14" t="inlineStr"/>
       <c r="AC261" s="15" t="n">
-        <v>0.4884953086419753</v>
+        <v>0.11099356270810211</v>
       </c>
       <c r="AD261" s="15" t="inlineStr"/>
       <c r="AE261" s="14" t="n">
-        <v>2071594.0</v>
+        <v>8009948.0</v>
       </c>
       <c r="AF261" s="14" t="inlineStr"/>
       <c r="AG261" s="14" t="inlineStr"/>
@@ -15767,14 +15767,14 @@
       <c r="N262" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000190. Pemeliharaan Mesin Potong Rumput</t>
+            <t xml:space="preserve">000187. Pemeliharaan Genset 40 KVA</t>
           </r>
         </is>
       </c>
       <c r="O262" s="13" t="inlineStr"/>
       <c r="P262" s="13" t="inlineStr"/>
       <c r="Q262" s="14" t="n">
-        <v>1.2E7</v>
+        <v>4050000.0</v>
       </c>
       <c r="R262" s="14" t="inlineStr"/>
       <c r="S262" s="14" t="n">
@@ -15784,23 +15784,23 @@
       <c r="U262" s="14" t="inlineStr"/>
       <c r="V262" s="14" t="inlineStr"/>
       <c r="W262" s="14" t="n">
-        <v>8450284.0</v>
+        <v>1978406.0</v>
       </c>
       <c r="X262" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y262" s="14" t="inlineStr"/>
       <c r="Z262" s="14" t="n">
-        <v>8450284.0</v>
+        <v>1978406.0</v>
       </c>
       <c r="AA262" s="14" t="inlineStr"/>
       <c r="AB262" s="14" t="inlineStr"/>
       <c r="AC262" s="15" t="n">
-        <v>0.7041903333333334</v>
+        <v>0.4884953086419753</v>
       </c>
       <c r="AD262" s="15" t="inlineStr"/>
       <c r="AE262" s="14" t="n">
-        <v>3549716.0</v>
+        <v>2071594.0</v>
       </c>
       <c r="AF262" s="14" t="inlineStr"/>
       <c r="AG262" s="14" t="inlineStr"/>
@@ -15824,14 +15824,14 @@
       <c r="N263" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000191. Pemeliharaan Printer</t>
+            <t xml:space="preserve">000190. Pemeliharaan Mesin Potong Rumput</t>
           </r>
         </is>
       </c>
       <c r="O263" s="13" t="inlineStr"/>
       <c r="P263" s="13" t="inlineStr"/>
       <c r="Q263" s="14" t="n">
-        <v>1500000.0</v>
+        <v>1.2E7</v>
       </c>
       <c r="R263" s="14" t="inlineStr"/>
       <c r="S263" s="14" t="n">
@@ -15841,23 +15841,23 @@
       <c r="U263" s="14" t="inlineStr"/>
       <c r="V263" s="14" t="inlineStr"/>
       <c r="W263" s="14" t="n">
-        <v>1167558.0</v>
+        <v>8450284.0</v>
       </c>
       <c r="X263" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y263" s="14" t="inlineStr"/>
       <c r="Z263" s="14" t="n">
-        <v>1167558.0</v>
+        <v>8450284.0</v>
       </c>
       <c r="AA263" s="14" t="inlineStr"/>
       <c r="AB263" s="14" t="inlineStr"/>
       <c r="AC263" s="15" t="n">
-        <v>0.778372</v>
+        <v>0.7041903333333334</v>
       </c>
       <c r="AD263" s="15" t="inlineStr"/>
       <c r="AE263" s="14" t="n">
-        <v>332442.0</v>
+        <v>3549716.0</v>
       </c>
       <c r="AF263" s="14" t="inlineStr"/>
       <c r="AG263" s="14" t="inlineStr"/>
@@ -15881,14 +15881,14 @@
       <c r="N264" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000192. Pemeliharaan Komputer/PC</t>
+            <t xml:space="preserve">000191. Pemeliharaan Printer</t>
           </r>
         </is>
       </c>
       <c r="O264" s="13" t="inlineStr"/>
       <c r="P264" s="13" t="inlineStr"/>
       <c r="Q264" s="14" t="n">
-        <v>1.562E7</v>
+        <v>1500000.0</v>
       </c>
       <c r="R264" s="14" t="inlineStr"/>
       <c r="S264" s="14" t="n">
@@ -15898,23 +15898,23 @@
       <c r="U264" s="14" t="inlineStr"/>
       <c r="V264" s="14" t="inlineStr"/>
       <c r="W264" s="14" t="n">
-        <v>3760846.0</v>
+        <v>1167558.0</v>
       </c>
       <c r="X264" s="14" t="n">
-        <v>1560138.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y264" s="14" t="inlineStr"/>
       <c r="Z264" s="14" t="n">
-        <v>5320984.0</v>
+        <v>1167558.0</v>
       </c>
       <c r="AA264" s="14" t="inlineStr"/>
       <c r="AB264" s="14" t="inlineStr"/>
       <c r="AC264" s="15" t="n">
-        <v>0.3406519846350832</v>
+        <v>0.778372</v>
       </c>
       <c r="AD264" s="15" t="inlineStr"/>
       <c r="AE264" s="14" t="n">
-        <v>1.0299016E7</v>
+        <v>332442.0</v>
       </c>
       <c r="AF264" s="14" t="inlineStr"/>
       <c r="AG264" s="14" t="inlineStr"/>
@@ -15938,14 +15938,14 @@
       <c r="N265" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000283. Pemeliharaan Kulkas</t>
+            <t xml:space="preserve">000192. Pemeliharaan Komputer/PC</t>
           </r>
         </is>
       </c>
       <c r="O265" s="13" t="inlineStr"/>
       <c r="P265" s="13" t="inlineStr"/>
       <c r="Q265" s="14" t="n">
-        <v>500000.0</v>
+        <v>1.562E7</v>
       </c>
       <c r="R265" s="14" t="inlineStr"/>
       <c r="S265" s="14" t="n">
@@ -15955,23 +15955,23 @@
       <c r="U265" s="14" t="inlineStr"/>
       <c r="V265" s="14" t="inlineStr"/>
       <c r="W265" s="14" t="n">
-        <v>500000.0</v>
+        <v>3760846.0</v>
       </c>
       <c r="X265" s="14" t="n">
-        <v>0.0</v>
+        <v>1560138.0</v>
       </c>
       <c r="Y265" s="14" t="inlineStr"/>
       <c r="Z265" s="14" t="n">
-        <v>500000.0</v>
+        <v>5320984.0</v>
       </c>
       <c r="AA265" s="14" t="inlineStr"/>
       <c r="AB265" s="14" t="inlineStr"/>
       <c r="AC265" s="15" t="n">
-        <v>1.0</v>
+        <v>0.3406519846350832</v>
       </c>
       <c r="AD265" s="15" t="inlineStr"/>
       <c r="AE265" s="14" t="n">
-        <v>0.0</v>
+        <v>1.0299016E7</v>
       </c>
       <c r="AF265" s="14" t="inlineStr"/>
       <c r="AG265" s="14" t="inlineStr"/>
@@ -15995,14 +15995,14 @@
       <c r="N266" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000299. Pemeliharaan Instalasi Air</t>
+            <t xml:space="preserve">000283. Pemeliharaan Kulkas</t>
           </r>
         </is>
       </c>
       <c r="O266" s="13" t="inlineStr"/>
       <c r="P266" s="13" t="inlineStr"/>
       <c r="Q266" s="14" t="n">
-        <v>1.3E7</v>
+        <v>500000.0</v>
       </c>
       <c r="R266" s="14" t="inlineStr"/>
       <c r="S266" s="14" t="n">
@@ -16012,23 +16012,23 @@
       <c r="U266" s="14" t="inlineStr"/>
       <c r="V266" s="14" t="inlineStr"/>
       <c r="W266" s="14" t="n">
-        <v>7889000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="X266" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y266" s="14" t="inlineStr"/>
       <c r="Z266" s="14" t="n">
-        <v>7889000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="AA266" s="14" t="inlineStr"/>
       <c r="AB266" s="14" t="inlineStr"/>
       <c r="AC266" s="15" t="n">
-        <v>0.6068461538461538</v>
+        <v>1.0</v>
       </c>
       <c r="AD266" s="15" t="inlineStr"/>
       <c r="AE266" s="14" t="n">
-        <v>5111000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF266" s="14" t="inlineStr"/>
       <c r="AG266" s="14" t="inlineStr"/>
@@ -16052,14 +16052,14 @@
       <c r="N267" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000304. Pemeliharaan Alat Laboratorium</t>
+            <t xml:space="preserve">000299. Pemeliharaan Instalasi Air</t>
           </r>
         </is>
       </c>
       <c r="O267" s="13" t="inlineStr"/>
       <c r="P267" s="13" t="inlineStr"/>
       <c r="Q267" s="14" t="n">
-        <v>5000000.0</v>
+        <v>1.3E7</v>
       </c>
       <c r="R267" s="14" t="inlineStr"/>
       <c r="S267" s="14" t="n">
@@ -16069,23 +16069,23 @@
       <c r="U267" s="14" t="inlineStr"/>
       <c r="V267" s="14" t="inlineStr"/>
       <c r="W267" s="14" t="n">
-        <v>0.0</v>
+        <v>7889000.0</v>
       </c>
       <c r="X267" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y267" s="14" t="inlineStr"/>
       <c r="Z267" s="14" t="n">
-        <v>0.0</v>
+        <v>7889000.0</v>
       </c>
       <c r="AA267" s="14" t="inlineStr"/>
       <c r="AB267" s="14" t="inlineStr"/>
       <c r="AC267" s="15" t="n">
-        <v>0.0</v>
+        <v>0.6068461538461538</v>
       </c>
       <c r="AD267" s="15" t="inlineStr"/>
       <c r="AE267" s="14" t="n">
-        <v>5000000.0</v>
+        <v>5111000.0</v>
       </c>
       <c r="AF267" s="14" t="inlineStr"/>
       <c r="AG267" s="14" t="inlineStr"/>
@@ -16109,14 +16109,14 @@
       <c r="N268" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000305. Pemeliharaan TV</t>
+            <t xml:space="preserve">000304. Pemeliharaan Alat Laboratorium</t>
           </r>
         </is>
       </c>
       <c r="O268" s="13" t="inlineStr"/>
       <c r="P268" s="13" t="inlineStr"/>
       <c r="Q268" s="14" t="n">
-        <v>1500000.0</v>
+        <v>2500000.0</v>
       </c>
       <c r="R268" s="14" t="inlineStr"/>
       <c r="S268" s="14" t="n">
@@ -16129,20 +16129,20 @@
         <v>0.0</v>
       </c>
       <c r="X268" s="14" t="n">
-        <v>750000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y268" s="14" t="inlineStr"/>
       <c r="Z268" s="14" t="n">
-        <v>750000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA268" s="14" t="inlineStr"/>
       <c r="AB268" s="14" t="inlineStr"/>
       <c r="AC268" s="15" t="n">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="AD268" s="15" t="inlineStr"/>
       <c r="AE268" s="14" t="n">
-        <v>750000.0</v>
+        <v>2500000.0</v>
       </c>
       <c r="AF268" s="14" t="inlineStr"/>
       <c r="AG268" s="14" t="inlineStr"/>
@@ -16157,29 +16157,23 @@
       <c r="E269" s="2" t="inlineStr"/>
       <c r="F269" s="2" t="inlineStr"/>
       <c r="G269" s="2" t="inlineStr"/>
-      <c r="H269" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">523132</t>
-          </r>
-        </is>
-      </c>
-      <c r="I269" s="13" t="inlineStr"/>
-      <c r="J269" s="13" t="inlineStr"/>
-      <c r="K269" s="13" t="inlineStr"/>
-      <c r="L269" s="13" t="inlineStr"/>
-      <c r="M269" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Pemeliharaan Irigasi</t>
-          </r>
-        </is>
-      </c>
-      <c r="N269" s="13" t="inlineStr"/>
+      <c r="H269" s="2" t="inlineStr"/>
+      <c r="I269" s="2" t="inlineStr"/>
+      <c r="J269" s="2" t="inlineStr"/>
+      <c r="K269" s="2" t="inlineStr"/>
+      <c r="L269" s="2" t="inlineStr"/>
+      <c r="M269" s="2" t="inlineStr"/>
+      <c r="N269" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000305. Pemeliharaan TV</t>
+          </r>
+        </is>
+      </c>
       <c r="O269" s="13" t="inlineStr"/>
       <c r="P269" s="13" t="inlineStr"/>
       <c r="Q269" s="14" t="n">
-        <v>1.5292E8</v>
+        <v>1500000.0</v>
       </c>
       <c r="R269" s="14" t="inlineStr"/>
       <c r="S269" s="14" t="n">
@@ -16189,23 +16183,23 @@
       <c r="U269" s="14" t="inlineStr"/>
       <c r="V269" s="14" t="inlineStr"/>
       <c r="W269" s="14" t="n">
-        <v>8.0551E7</v>
+        <v>0.0</v>
       </c>
       <c r="X269" s="14" t="n">
-        <v>0.0</v>
+        <v>750000.0</v>
       </c>
       <c r="Y269" s="14" t="inlineStr"/>
       <c r="Z269" s="14" t="n">
-        <v>8.0551E7</v>
+        <v>750000.0</v>
       </c>
       <c r="AA269" s="14" t="inlineStr"/>
       <c r="AB269" s="14" t="inlineStr"/>
       <c r="AC269" s="15" t="n">
-        <v>0.5267525503531258</v>
+        <v>0.5</v>
       </c>
       <c r="AD269" s="15" t="inlineStr"/>
       <c r="AE269" s="14" t="n">
-        <v>7.2369E7</v>
+        <v>750000.0</v>
       </c>
       <c r="AF269" s="14" t="inlineStr"/>
       <c r="AG269" s="14" t="inlineStr"/>
@@ -16229,14 +16223,14 @@
       <c r="N270" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000195. Pemeliharaan Talud Cijeruk</t>
+            <t xml:space="preserve">000307. Pemeliharaan Meubelair</t>
           </r>
         </is>
       </c>
       <c r="O270" s="13" t="inlineStr"/>
       <c r="P270" s="13" t="inlineStr"/>
       <c r="Q270" s="14" t="n">
-        <v>6.216E7</v>
+        <v>5000000.0</v>
       </c>
       <c r="R270" s="14" t="inlineStr"/>
       <c r="S270" s="14" t="n">
@@ -16246,23 +16240,23 @@
       <c r="U270" s="14" t="inlineStr"/>
       <c r="V270" s="14" t="inlineStr"/>
       <c r="W270" s="14" t="n">
-        <v>3.909E7</v>
+        <v>0.0</v>
       </c>
       <c r="X270" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y270" s="14" t="inlineStr"/>
       <c r="Z270" s="14" t="n">
-        <v>3.909E7</v>
+        <v>0.0</v>
       </c>
       <c r="AA270" s="14" t="inlineStr"/>
       <c r="AB270" s="14" t="inlineStr"/>
       <c r="AC270" s="15" t="n">
-        <v>0.6288610038610039</v>
+        <v>0.0</v>
       </c>
       <c r="AD270" s="15" t="inlineStr"/>
       <c r="AE270" s="14" t="n">
-        <v>2.307E7</v>
+        <v>5000000.0</v>
       </c>
       <c r="AF270" s="14" t="inlineStr"/>
       <c r="AG270" s="14" t="inlineStr"/>
@@ -16277,23 +16271,29 @@
       <c r="E271" s="2" t="inlineStr"/>
       <c r="F271" s="2" t="inlineStr"/>
       <c r="G271" s="2" t="inlineStr"/>
-      <c r="H271" s="2" t="inlineStr"/>
-      <c r="I271" s="2" t="inlineStr"/>
-      <c r="J271" s="2" t="inlineStr"/>
-      <c r="K271" s="2" t="inlineStr"/>
-      <c r="L271" s="2" t="inlineStr"/>
-      <c r="M271" s="2" t="inlineStr"/>
-      <c r="N271" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000284. Pemeliharaan Talud Cibalagung</t>
-          </r>
-        </is>
-      </c>
+      <c r="H271" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">523132</t>
+          </r>
+        </is>
+      </c>
+      <c r="I271" s="13" t="inlineStr"/>
+      <c r="J271" s="13" t="inlineStr"/>
+      <c r="K271" s="13" t="inlineStr"/>
+      <c r="L271" s="13" t="inlineStr"/>
+      <c r="M271" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Pemeliharaan Irigasi</t>
+          </r>
+        </is>
+      </c>
+      <c r="N271" s="13" t="inlineStr"/>
       <c r="O271" s="13" t="inlineStr"/>
       <c r="P271" s="13" t="inlineStr"/>
       <c r="Q271" s="14" t="n">
-        <v>3.07E7</v>
+        <v>1.5292E8</v>
       </c>
       <c r="R271" s="14" t="inlineStr"/>
       <c r="S271" s="14" t="n">
@@ -16303,23 +16303,23 @@
       <c r="U271" s="14" t="inlineStr"/>
       <c r="V271" s="14" t="inlineStr"/>
       <c r="W271" s="14" t="n">
-        <v>3.0685E7</v>
+        <v>8.0551E7</v>
       </c>
       <c r="X271" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y271" s="14" t="inlineStr"/>
       <c r="Z271" s="14" t="n">
-        <v>3.0685E7</v>
+        <v>8.0551E7</v>
       </c>
       <c r="AA271" s="14" t="inlineStr"/>
       <c r="AB271" s="14" t="inlineStr"/>
       <c r="AC271" s="15" t="n">
-        <v>0.9995114006514658</v>
+        <v>0.5267525503531258</v>
       </c>
       <c r="AD271" s="15" t="inlineStr"/>
       <c r="AE271" s="14" t="n">
-        <v>15000.0</v>
+        <v>7.2369E7</v>
       </c>
       <c r="AF271" s="14" t="inlineStr"/>
       <c r="AG271" s="14" t="inlineStr"/>
@@ -16343,14 +16343,14 @@
       <c r="N272" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000285. Pemeliharaan Saluran Air Cijeruk</t>
+            <t xml:space="preserve">000195. Pemeliharaan Talud Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O272" s="13" t="inlineStr"/>
       <c r="P272" s="13" t="inlineStr"/>
       <c r="Q272" s="14" t="n">
-        <v>6.006E7</v>
+        <v>6.216E7</v>
       </c>
       <c r="R272" s="14" t="inlineStr"/>
       <c r="S272" s="14" t="n">
@@ -16360,23 +16360,23 @@
       <c r="U272" s="14" t="inlineStr"/>
       <c r="V272" s="14" t="inlineStr"/>
       <c r="W272" s="14" t="n">
-        <v>1.0776E7</v>
+        <v>3.909E7</v>
       </c>
       <c r="X272" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y272" s="14" t="inlineStr"/>
       <c r="Z272" s="14" t="n">
-        <v>1.0776E7</v>
+        <v>3.909E7</v>
       </c>
       <c r="AA272" s="14" t="inlineStr"/>
       <c r="AB272" s="14" t="inlineStr"/>
       <c r="AC272" s="15" t="n">
-        <v>0.17942057942057943</v>
+        <v>0.6288610038610039</v>
       </c>
       <c r="AD272" s="15" t="inlineStr"/>
       <c r="AE272" s="14" t="n">
-        <v>4.9284E7</v>
+        <v>2.307E7</v>
       </c>
       <c r="AF272" s="14" t="inlineStr"/>
       <c r="AG272" s="14" t="inlineStr"/>
@@ -16389,31 +16389,25 @@
       <c r="C273" s="2" t="inlineStr"/>
       <c r="D273" s="2" t="inlineStr"/>
       <c r="E273" s="2" t="inlineStr"/>
-      <c r="F273" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">002.DD</t>
-          </r>
-        </is>
-      </c>
-      <c r="G273" s="13" t="inlineStr"/>
-      <c r="H273" s="13" t="inlineStr"/>
-      <c r="I273" s="13" t="inlineStr"/>
-      <c r="J273" s="13" t="inlineStr"/>
-      <c r="K273" s="13" t="inlineStr"/>
-      <c r="L273" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pembayaran Terkait Pelaksanaan Operasional Kantor</t>
-          </r>
-        </is>
-      </c>
-      <c r="M273" s="13" t="inlineStr"/>
-      <c r="N273" s="13" t="inlineStr"/>
+      <c r="F273" s="2" t="inlineStr"/>
+      <c r="G273" s="2" t="inlineStr"/>
+      <c r="H273" s="2" t="inlineStr"/>
+      <c r="I273" s="2" t="inlineStr"/>
+      <c r="J273" s="2" t="inlineStr"/>
+      <c r="K273" s="2" t="inlineStr"/>
+      <c r="L273" s="2" t="inlineStr"/>
+      <c r="M273" s="2" t="inlineStr"/>
+      <c r="N273" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000284. Pemeliharaan Talud Cibalagung</t>
+          </r>
+        </is>
+      </c>
       <c r="O273" s="13" t="inlineStr"/>
       <c r="P273" s="13" t="inlineStr"/>
       <c r="Q273" s="14" t="n">
-        <v>1.3218E8</v>
+        <v>3.07E7</v>
       </c>
       <c r="R273" s="14" t="inlineStr"/>
       <c r="S273" s="14" t="n">
@@ -16423,23 +16417,23 @@
       <c r="U273" s="14" t="inlineStr"/>
       <c r="V273" s="14" t="inlineStr"/>
       <c r="W273" s="14" t="n">
-        <v>1.3074E8</v>
+        <v>3.0685E7</v>
       </c>
       <c r="X273" s="14" t="n">
-        <v>480000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y273" s="14" t="inlineStr"/>
       <c r="Z273" s="14" t="n">
-        <v>1.3122E8</v>
+        <v>3.0685E7</v>
       </c>
       <c r="AA273" s="14" t="inlineStr"/>
       <c r="AB273" s="14" t="inlineStr"/>
       <c r="AC273" s="15" t="n">
-        <v>0.9927371765773945</v>
+        <v>0.9995114006514658</v>
       </c>
       <c r="AD273" s="15" t="inlineStr"/>
       <c r="AE273" s="14" t="n">
-        <v>960000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="AF273" s="14" t="inlineStr"/>
       <c r="AG273" s="14" t="inlineStr"/>
@@ -16454,29 +16448,23 @@
       <c r="E274" s="2" t="inlineStr"/>
       <c r="F274" s="2" t="inlineStr"/>
       <c r="G274" s="2" t="inlineStr"/>
-      <c r="H274" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521115</t>
-          </r>
-        </is>
-      </c>
-      <c r="I274" s="13" t="inlineStr"/>
-      <c r="J274" s="13" t="inlineStr"/>
-      <c r="K274" s="13" t="inlineStr"/>
-      <c r="L274" s="13" t="inlineStr"/>
-      <c r="M274" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Honor Operasional Satuan Kerja</t>
-          </r>
-        </is>
-      </c>
-      <c r="N274" s="13" t="inlineStr"/>
+      <c r="H274" s="2" t="inlineStr"/>
+      <c r="I274" s="2" t="inlineStr"/>
+      <c r="J274" s="2" t="inlineStr"/>
+      <c r="K274" s="2" t="inlineStr"/>
+      <c r="L274" s="2" t="inlineStr"/>
+      <c r="M274" s="2" t="inlineStr"/>
+      <c r="N274" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000285. Pemeliharaan Saluran Air Cijeruk</t>
+          </r>
+        </is>
+      </c>
       <c r="O274" s="13" t="inlineStr"/>
       <c r="P274" s="13" t="inlineStr"/>
       <c r="Q274" s="14" t="n">
-        <v>1.2468E8</v>
+        <v>6.006E7</v>
       </c>
       <c r="R274" s="14" t="inlineStr"/>
       <c r="S274" s="14" t="n">
@@ -16486,23 +16474,23 @@
       <c r="U274" s="14" t="inlineStr"/>
       <c r="V274" s="14" t="inlineStr"/>
       <c r="W274" s="14" t="n">
-        <v>1.2324E8</v>
+        <v>1.0776E7</v>
       </c>
       <c r="X274" s="14" t="n">
-        <v>480000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y274" s="14" t="inlineStr"/>
       <c r="Z274" s="14" t="n">
-        <v>1.2372E8</v>
+        <v>1.0776E7</v>
       </c>
       <c r="AA274" s="14" t="inlineStr"/>
       <c r="AB274" s="14" t="inlineStr"/>
       <c r="AC274" s="15" t="n">
-        <v>0.9923002887391723</v>
+        <v>0.17942057942057943</v>
       </c>
       <c r="AD274" s="15" t="inlineStr"/>
       <c r="AE274" s="14" t="n">
-        <v>960000.0</v>
+        <v>4.9284E7</v>
       </c>
       <c r="AF274" s="14" t="inlineStr"/>
       <c r="AG274" s="14" t="inlineStr"/>
@@ -16515,25 +16503,31 @@
       <c r="C275" s="2" t="inlineStr"/>
       <c r="D275" s="2" t="inlineStr"/>
       <c r="E275" s="2" t="inlineStr"/>
-      <c r="F275" s="2" t="inlineStr"/>
-      <c r="G275" s="2" t="inlineStr"/>
-      <c r="H275" s="2" t="inlineStr"/>
-      <c r="I275" s="2" t="inlineStr"/>
-      <c r="J275" s="2" t="inlineStr"/>
-      <c r="K275" s="2" t="inlineStr"/>
-      <c r="L275" s="2" t="inlineStr"/>
-      <c r="M275" s="2" t="inlineStr"/>
-      <c r="N275" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000197. Honorarium Pejabat Kuasa Pengguna Anggaran</t>
-          </r>
-        </is>
-      </c>
+      <c r="F275" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">002.DD</t>
+          </r>
+        </is>
+      </c>
+      <c r="G275" s="13" t="inlineStr"/>
+      <c r="H275" s="13" t="inlineStr"/>
+      <c r="I275" s="13" t="inlineStr"/>
+      <c r="J275" s="13" t="inlineStr"/>
+      <c r="K275" s="13" t="inlineStr"/>
+      <c r="L275" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pembayaran Terkait Pelaksanaan Operasional Kantor</t>
+          </r>
+        </is>
+      </c>
+      <c r="M275" s="13" t="inlineStr"/>
+      <c r="N275" s="13" t="inlineStr"/>
       <c r="O275" s="13" t="inlineStr"/>
       <c r="P275" s="13" t="inlineStr"/>
       <c r="Q275" s="14" t="n">
-        <v>3.06E7</v>
+        <v>1.3218E8</v>
       </c>
       <c r="R275" s="14" t="inlineStr"/>
       <c r="S275" s="14" t="n">
@@ -16543,23 +16537,23 @@
       <c r="U275" s="14" t="inlineStr"/>
       <c r="V275" s="14" t="inlineStr"/>
       <c r="W275" s="14" t="n">
-        <v>3.06E7</v>
+        <v>1.3074E8</v>
       </c>
       <c r="X275" s="14" t="n">
-        <v>0.0</v>
+        <v>480000.0</v>
       </c>
       <c r="Y275" s="14" t="inlineStr"/>
       <c r="Z275" s="14" t="n">
-        <v>3.06E7</v>
+        <v>1.3122E8</v>
       </c>
       <c r="AA275" s="14" t="inlineStr"/>
       <c r="AB275" s="14" t="inlineStr"/>
       <c r="AC275" s="15" t="n">
-        <v>1.0</v>
+        <v>0.9927371765773945</v>
       </c>
       <c r="AD275" s="15" t="inlineStr"/>
       <c r="AE275" s="14" t="n">
-        <v>0.0</v>
+        <v>960000.0</v>
       </c>
       <c r="AF275" s="14" t="inlineStr"/>
       <c r="AG275" s="14" t="inlineStr"/>
@@ -16574,23 +16568,29 @@
       <c r="E276" s="2" t="inlineStr"/>
       <c r="F276" s="2" t="inlineStr"/>
       <c r="G276" s="2" t="inlineStr"/>
-      <c r="H276" s="2" t="inlineStr"/>
-      <c r="I276" s="2" t="inlineStr"/>
-      <c r="J276" s="2" t="inlineStr"/>
-      <c r="K276" s="2" t="inlineStr"/>
-      <c r="L276" s="2" t="inlineStr"/>
-      <c r="M276" s="2" t="inlineStr"/>
-      <c r="N276" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000198. Honorarium Pejabat Pembuat Komitmen</t>
-          </r>
-        </is>
-      </c>
+      <c r="H276" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521115</t>
+          </r>
+        </is>
+      </c>
+      <c r="I276" s="13" t="inlineStr"/>
+      <c r="J276" s="13" t="inlineStr"/>
+      <c r="K276" s="13" t="inlineStr"/>
+      <c r="L276" s="13" t="inlineStr"/>
+      <c r="M276" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Honor Operasional Satuan Kerja</t>
+          </r>
+        </is>
+      </c>
+      <c r="N276" s="13" t="inlineStr"/>
       <c r="O276" s="13" t="inlineStr"/>
       <c r="P276" s="13" t="inlineStr"/>
       <c r="Q276" s="14" t="n">
-        <v>2.976E7</v>
+        <v>1.2468E8</v>
       </c>
       <c r="R276" s="14" t="inlineStr"/>
       <c r="S276" s="14" t="n">
@@ -16600,30 +16600,30 @@
       <c r="U276" s="14" t="inlineStr"/>
       <c r="V276" s="14" t="inlineStr"/>
       <c r="W276" s="14" t="n">
-        <v>2.976E7</v>
+        <v>1.2324E8</v>
       </c>
       <c r="X276" s="14" t="n">
-        <v>0.0</v>
+        <v>480000.0</v>
       </c>
       <c r="Y276" s="14" t="inlineStr"/>
       <c r="Z276" s="14" t="n">
-        <v>2.976E7</v>
+        <v>1.2372E8</v>
       </c>
       <c r="AA276" s="14" t="inlineStr"/>
       <c r="AB276" s="14" t="inlineStr"/>
       <c r="AC276" s="15" t="n">
-        <v>1.0</v>
+        <v>0.9923002887391723</v>
       </c>
       <c r="AD276" s="15" t="inlineStr"/>
       <c r="AE276" s="14" t="n">
-        <v>0.0</v>
+        <v>960000.0</v>
       </c>
       <c r="AF276" s="14" t="inlineStr"/>
       <c r="AG276" s="14" t="inlineStr"/>
       <c r="AH276" s="14" t="inlineStr"/>
       <c r="AI276" s="14" t="inlineStr"/>
     </row>
-    <row r="277" customHeight="1" ht="18">
+    <row r="277" customHeight="1" ht="15">
       <c r="A277" s="2" t="inlineStr"/>
       <c r="B277" s="2" t="inlineStr"/>
       <c r="C277" s="2" t="inlineStr"/>
@@ -16640,14 +16640,14 @@
       <c r="N277" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000199. Honorarium Pejabat  Penguji Tagihan   Penandatangan  Spm</t>
+            <t xml:space="preserve">000197. Honorarium Pejabat Kuasa Pengguna Anggaran</t>
           </r>
         </is>
       </c>
       <c r="O277" s="13" t="inlineStr"/>
       <c r="P277" s="13" t="inlineStr"/>
       <c r="Q277" s="14" t="n">
-        <v>1.476E7</v>
+        <v>3.06E7</v>
       </c>
       <c r="R277" s="14" t="inlineStr"/>
       <c r="S277" s="14" t="n">
@@ -16657,14 +16657,14 @@
       <c r="U277" s="14" t="inlineStr"/>
       <c r="V277" s="14" t="inlineStr"/>
       <c r="W277" s="14" t="n">
-        <v>1.476E7</v>
+        <v>3.06E7</v>
       </c>
       <c r="X277" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y277" s="14" t="inlineStr"/>
       <c r="Z277" s="14" t="n">
-        <v>1.476E7</v>
+        <v>3.06E7</v>
       </c>
       <c r="AA277" s="14" t="inlineStr"/>
       <c r="AB277" s="14" t="inlineStr"/>
@@ -16697,14 +16697,14 @@
       <c r="N278" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000200. Honorarium Bendahara  Pengeluaran</t>
+            <t xml:space="preserve">000198. Honorarium Pejabat Pembuat Komitmen</t>
           </r>
         </is>
       </c>
       <c r="O278" s="13" t="inlineStr"/>
       <c r="P278" s="13" t="inlineStr"/>
       <c r="Q278" s="14" t="n">
-        <v>1.284E7</v>
+        <v>2.976E7</v>
       </c>
       <c r="R278" s="14" t="inlineStr"/>
       <c r="S278" s="14" t="n">
@@ -16714,14 +16714,14 @@
       <c r="U278" s="14" t="inlineStr"/>
       <c r="V278" s="14" t="inlineStr"/>
       <c r="W278" s="14" t="n">
-        <v>1.284E7</v>
+        <v>2.976E7</v>
       </c>
       <c r="X278" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y278" s="14" t="inlineStr"/>
       <c r="Z278" s="14" t="n">
-        <v>1.284E7</v>
+        <v>2.976E7</v>
       </c>
       <c r="AA278" s="14" t="inlineStr"/>
       <c r="AB278" s="14" t="inlineStr"/>
@@ -16737,7 +16737,7 @@
       <c r="AH278" s="14" t="inlineStr"/>
       <c r="AI278" s="14" t="inlineStr"/>
     </row>
-    <row r="279" customHeight="1" ht="15">
+    <row r="279" customHeight="1" ht="18">
       <c r="A279" s="2" t="inlineStr"/>
       <c r="B279" s="2" t="inlineStr"/>
       <c r="C279" s="2" t="inlineStr"/>
@@ -16754,14 +16754,14 @@
       <c r="N279" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000201. Honorarium Staf  Pengelola</t>
+            <t xml:space="preserve">000199. Honorarium Pejabat  Penguji Tagihan   Penandatangan  Spm</t>
           </r>
         </is>
       </c>
       <c r="O279" s="13" t="inlineStr"/>
       <c r="P279" s="13" t="inlineStr"/>
       <c r="Q279" s="14" t="n">
-        <v>2.88E7</v>
+        <v>1.476E7</v>
       </c>
       <c r="R279" s="14" t="inlineStr"/>
       <c r="S279" s="14" t="n">
@@ -16771,14 +16771,14 @@
       <c r="U279" s="14" t="inlineStr"/>
       <c r="V279" s="14" t="inlineStr"/>
       <c r="W279" s="14" t="n">
-        <v>2.88E7</v>
+        <v>1.476E7</v>
       </c>
       <c r="X279" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y279" s="14" t="inlineStr"/>
       <c r="Z279" s="14" t="n">
-        <v>2.88E7</v>
+        <v>1.476E7</v>
       </c>
       <c r="AA279" s="14" t="inlineStr"/>
       <c r="AB279" s="14" t="inlineStr"/>
@@ -16811,14 +16811,14 @@
       <c r="N280" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000202. Honorarium Anggota/Petugas (UAKPA/Barang)</t>
+            <t xml:space="preserve">000200. Honorarium Bendahara  Pengeluaran</t>
           </r>
         </is>
       </c>
       <c r="O280" s="13" t="inlineStr"/>
       <c r="P280" s="13" t="inlineStr"/>
       <c r="Q280" s="14" t="n">
-        <v>3600000.0</v>
+        <v>1.284E7</v>
       </c>
       <c r="R280" s="14" t="inlineStr"/>
       <c r="S280" s="14" t="n">
@@ -16828,23 +16828,23 @@
       <c r="U280" s="14" t="inlineStr"/>
       <c r="V280" s="14" t="inlineStr"/>
       <c r="W280" s="14" t="n">
-        <v>2700000.0</v>
+        <v>1.284E7</v>
       </c>
       <c r="X280" s="14" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y280" s="14" t="inlineStr"/>
       <c r="Z280" s="14" t="n">
-        <v>3000000.0</v>
+        <v>1.284E7</v>
       </c>
       <c r="AA280" s="14" t="inlineStr"/>
       <c r="AB280" s="14" t="inlineStr"/>
       <c r="AC280" s="15" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.0</v>
       </c>
       <c r="AD280" s="15" t="inlineStr"/>
       <c r="AE280" s="14" t="n">
-        <v>600000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF280" s="14" t="inlineStr"/>
       <c r="AG280" s="14" t="inlineStr"/>
@@ -16894,7 +16894,7 @@
       <c r="AH281" s="2" t="inlineStr"/>
       <c r="AI281" s="2" t="inlineStr"/>
     </row>
-    <row r="282" customHeight="1" ht="18">
+    <row r="282" customHeight="1" ht="15">
       <c r="A282" s="2" t="inlineStr"/>
       <c r="B282" s="2" t="inlineStr"/>
       <c r="C282" s="2" t="inlineStr"/>
@@ -16911,14 +16911,14 @@
       <c r="N282" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000203. Honorarium Pengurus/Penyimpan Bmn Tingkat Kuasa Pengguna Barang</t>
+            <t xml:space="preserve">000201. Honorarium Staf  Pengelola</t>
           </r>
         </is>
       </c>
       <c r="O282" s="13" t="inlineStr"/>
       <c r="P282" s="13" t="inlineStr"/>
       <c r="Q282" s="14" t="n">
-        <v>4320000.0</v>
+        <v>2.88E7</v>
       </c>
       <c r="R282" s="14" t="inlineStr"/>
       <c r="S282" s="14" t="n">
@@ -16928,23 +16928,23 @@
       <c r="U282" s="14" t="inlineStr"/>
       <c r="V282" s="14" t="inlineStr"/>
       <c r="W282" s="14" t="n">
-        <v>3780000.0</v>
+        <v>2.88E7</v>
       </c>
       <c r="X282" s="14" t="n">
-        <v>180000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y282" s="14" t="inlineStr"/>
       <c r="Z282" s="14" t="n">
-        <v>3960000.0</v>
+        <v>2.88E7</v>
       </c>
       <c r="AA282" s="14" t="inlineStr"/>
       <c r="AB282" s="14" t="inlineStr"/>
       <c r="AC282" s="15" t="n">
-        <v>0.9166666666666666</v>
+        <v>1.0</v>
       </c>
       <c r="AD282" s="15" t="inlineStr"/>
       <c r="AE282" s="14" t="n">
-        <v>360000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF282" s="14" t="inlineStr"/>
       <c r="AG282" s="14" t="inlineStr"/>
@@ -16959,29 +16959,23 @@
       <c r="E283" s="2" t="inlineStr"/>
       <c r="F283" s="2" t="inlineStr"/>
       <c r="G283" s="2" t="inlineStr"/>
-      <c r="H283" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521119</t>
-          </r>
-        </is>
-      </c>
-      <c r="I283" s="13" t="inlineStr"/>
-      <c r="J283" s="13" t="inlineStr"/>
-      <c r="K283" s="13" t="inlineStr"/>
-      <c r="L283" s="13" t="inlineStr"/>
-      <c r="M283" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N283" s="13" t="inlineStr"/>
+      <c r="H283" s="2" t="inlineStr"/>
+      <c r="I283" s="2" t="inlineStr"/>
+      <c r="J283" s="2" t="inlineStr"/>
+      <c r="K283" s="2" t="inlineStr"/>
+      <c r="L283" s="2" t="inlineStr"/>
+      <c r="M283" s="2" t="inlineStr"/>
+      <c r="N283" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000202. Honorarium Anggota/Petugas (UAKPA/Barang)</t>
+          </r>
+        </is>
+      </c>
       <c r="O283" s="13" t="inlineStr"/>
       <c r="P283" s="13" t="inlineStr"/>
       <c r="Q283" s="14" t="n">
-        <v>7500000.0</v>
+        <v>3600000.0</v>
       </c>
       <c r="R283" s="14" t="inlineStr"/>
       <c r="S283" s="14" t="n">
@@ -16991,30 +16985,30 @@
       <c r="U283" s="14" t="inlineStr"/>
       <c r="V283" s="14" t="inlineStr"/>
       <c r="W283" s="14" t="n">
-        <v>7500000.0</v>
+        <v>2700000.0</v>
       </c>
       <c r="X283" s="14" t="n">
-        <v>0.0</v>
+        <v>300000.0</v>
       </c>
       <c r="Y283" s="14" t="inlineStr"/>
       <c r="Z283" s="14" t="n">
-        <v>7500000.0</v>
+        <v>3000000.0</v>
       </c>
       <c r="AA283" s="14" t="inlineStr"/>
       <c r="AB283" s="14" t="inlineStr"/>
       <c r="AC283" s="15" t="n">
-        <v>1.0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AD283" s="15" t="inlineStr"/>
       <c r="AE283" s="14" t="n">
-        <v>0.0</v>
+        <v>600000.0</v>
       </c>
       <c r="AF283" s="14" t="inlineStr"/>
       <c r="AG283" s="14" t="inlineStr"/>
       <c r="AH283" s="14" t="inlineStr"/>
       <c r="AI283" s="14" t="inlineStr"/>
     </row>
-    <row r="284" customHeight="1" ht="15">
+    <row r="284" customHeight="1" ht="18">
       <c r="A284" s="2" t="inlineStr"/>
       <c r="B284" s="2" t="inlineStr"/>
       <c r="C284" s="2" t="inlineStr"/>
@@ -17031,14 +17025,14 @@
       <c r="N284" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000243. Pakaian Kerja PJLP</t>
+            <t xml:space="preserve">000203. Honorarium Pengurus/Penyimpan Bmn Tingkat Kuasa Pengguna Barang</t>
           </r>
         </is>
       </c>
       <c r="O284" s="13" t="inlineStr"/>
       <c r="P284" s="13" t="inlineStr"/>
       <c r="Q284" s="14" t="n">
-        <v>7500000.0</v>
+        <v>4320000.0</v>
       </c>
       <c r="R284" s="14" t="inlineStr"/>
       <c r="S284" s="14" t="n">
@@ -17048,23 +17042,23 @@
       <c r="U284" s="14" t="inlineStr"/>
       <c r="V284" s="14" t="inlineStr"/>
       <c r="W284" s="14" t="n">
-        <v>7500000.0</v>
+        <v>3780000.0</v>
       </c>
       <c r="X284" s="14" t="n">
-        <v>0.0</v>
+        <v>180000.0</v>
       </c>
       <c r="Y284" s="14" t="inlineStr"/>
       <c r="Z284" s="14" t="n">
-        <v>7500000.0</v>
+        <v>3960000.0</v>
       </c>
       <c r="AA284" s="14" t="inlineStr"/>
       <c r="AB284" s="14" t="inlineStr"/>
       <c r="AC284" s="15" t="n">
-        <v>1.0</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="AD284" s="15" t="inlineStr"/>
       <c r="AE284" s="14" t="n">
-        <v>0.0</v>
+        <v>360000.0</v>
       </c>
       <c r="AF284" s="14" t="inlineStr"/>
       <c r="AG284" s="14" t="inlineStr"/>
@@ -17074,317 +17068,311 @@
     <row r="285" customHeight="1" ht="15">
       <c r="A285" s="2" t="inlineStr"/>
       <c r="B285" s="2" t="inlineStr"/>
-      <c r="C285" s="16" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">EBD</t>
-          </r>
-        </is>
-      </c>
-      <c r="D285" s="16" t="inlineStr"/>
-      <c r="E285" s="16" t="inlineStr"/>
-      <c r="F285" s="16" t="inlineStr"/>
-      <c r="G285" s="16" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Manajemen Kinerja Internal</t>
-          </r>
-        </is>
-      </c>
-      <c r="H285" s="16" t="inlineStr"/>
-      <c r="I285" s="16" t="inlineStr"/>
-      <c r="J285" s="16" t="inlineStr"/>
-      <c r="K285" s="16" t="inlineStr"/>
-      <c r="L285" s="16" t="inlineStr"/>
-      <c r="M285" s="16" t="inlineStr"/>
-      <c r="N285" s="16" t="inlineStr"/>
-      <c r="O285" s="16" t="inlineStr"/>
-      <c r="P285" s="16" t="inlineStr"/>
-      <c r="Q285" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="R285" s="17" t="inlineStr"/>
-      <c r="S285" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T285" s="17" t="inlineStr"/>
-      <c r="U285" s="17" t="inlineStr"/>
-      <c r="V285" s="17" t="inlineStr"/>
-      <c r="W285" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="X285" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y285" s="17" t="inlineStr"/>
-      <c r="Z285" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="AA285" s="17" t="inlineStr"/>
-      <c r="AB285" s="17" t="inlineStr"/>
-      <c r="AC285" s="18" t="n">
+      <c r="C285" s="2" t="inlineStr"/>
+      <c r="D285" s="2" t="inlineStr"/>
+      <c r="E285" s="2" t="inlineStr"/>
+      <c r="F285" s="2" t="inlineStr"/>
+      <c r="G285" s="2" t="inlineStr"/>
+      <c r="H285" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521119</t>
+          </r>
+        </is>
+      </c>
+      <c r="I285" s="13" t="inlineStr"/>
+      <c r="J285" s="13" t="inlineStr"/>
+      <c r="K285" s="13" t="inlineStr"/>
+      <c r="L285" s="13" t="inlineStr"/>
+      <c r="M285" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N285" s="13" t="inlineStr"/>
+      <c r="O285" s="13" t="inlineStr"/>
+      <c r="P285" s="13" t="inlineStr"/>
+      <c r="Q285" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="R285" s="14" t="inlineStr"/>
+      <c r="S285" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T285" s="14" t="inlineStr"/>
+      <c r="U285" s="14" t="inlineStr"/>
+      <c r="V285" s="14" t="inlineStr"/>
+      <c r="W285" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="X285" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y285" s="14" t="inlineStr"/>
+      <c r="Z285" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="AA285" s="14" t="inlineStr"/>
+      <c r="AB285" s="14" t="inlineStr"/>
+      <c r="AC285" s="15" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD285" s="18" t="inlineStr"/>
-      <c r="AE285" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF285" s="17" t="inlineStr"/>
-      <c r="AG285" s="17" t="inlineStr"/>
-      <c r="AH285" s="17" t="inlineStr"/>
-      <c r="AI285" s="17" t="inlineStr"/>
+      <c r="AD285" s="15" t="inlineStr"/>
+      <c r="AE285" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF285" s="14" t="inlineStr"/>
+      <c r="AG285" s="14" t="inlineStr"/>
+      <c r="AH285" s="14" t="inlineStr"/>
+      <c r="AI285" s="14" t="inlineStr"/>
     </row>
     <row r="286" customHeight="1" ht="15">
       <c r="A286" s="2" t="inlineStr"/>
       <c r="B286" s="2" t="inlineStr"/>
-      <c r="C286" s="28" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">EBD.955</t>
-          </r>
-        </is>
-      </c>
-      <c r="D286" s="28" t="inlineStr"/>
-      <c r="E286" s="28" t="inlineStr"/>
-      <c r="F286" s="28" t="inlineStr"/>
-      <c r="G286" s="28" t="inlineStr"/>
-      <c r="H286" s="28" t="inlineStr"/>
-      <c r="I286" s="28" t="inlineStr"/>
-      <c r="J286" s="28" t="inlineStr"/>
-      <c r="K286" s="20" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Manajemen Keuangan</t>
-          </r>
-        </is>
-      </c>
-      <c r="L286" s="20" t="inlineStr"/>
-      <c r="M286" s="20" t="inlineStr"/>
-      <c r="N286" s="20" t="inlineStr"/>
-      <c r="O286" s="20" t="inlineStr"/>
-      <c r="P286" s="20" t="inlineStr"/>
-      <c r="Q286" s="21" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="R286" s="21" t="inlineStr"/>
-      <c r="S286" s="21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T286" s="21" t="inlineStr"/>
-      <c r="U286" s="21" t="inlineStr"/>
-      <c r="V286" s="21" t="inlineStr"/>
-      <c r="W286" s="22" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="X286" s="22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y286" s="22" t="inlineStr"/>
-      <c r="Z286" s="21" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="AA286" s="21" t="inlineStr"/>
-      <c r="AB286" s="21" t="inlineStr"/>
-      <c r="AC286" s="23" t="n">
+      <c r="C286" s="2" t="inlineStr"/>
+      <c r="D286" s="2" t="inlineStr"/>
+      <c r="E286" s="2" t="inlineStr"/>
+      <c r="F286" s="2" t="inlineStr"/>
+      <c r="G286" s="2" t="inlineStr"/>
+      <c r="H286" s="2" t="inlineStr"/>
+      <c r="I286" s="2" t="inlineStr"/>
+      <c r="J286" s="2" t="inlineStr"/>
+      <c r="K286" s="2" t="inlineStr"/>
+      <c r="L286" s="2" t="inlineStr"/>
+      <c r="M286" s="2" t="inlineStr"/>
+      <c r="N286" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000243. Pakaian Kerja PJLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="O286" s="13" t="inlineStr"/>
+      <c r="P286" s="13" t="inlineStr"/>
+      <c r="Q286" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="R286" s="14" t="inlineStr"/>
+      <c r="S286" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T286" s="14" t="inlineStr"/>
+      <c r="U286" s="14" t="inlineStr"/>
+      <c r="V286" s="14" t="inlineStr"/>
+      <c r="W286" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="X286" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y286" s="14" t="inlineStr"/>
+      <c r="Z286" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="AA286" s="14" t="inlineStr"/>
+      <c r="AB286" s="14" t="inlineStr"/>
+      <c r="AC286" s="15" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD286" s="23" t="inlineStr"/>
-      <c r="AE286" s="21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF286" s="21" t="inlineStr"/>
-      <c r="AG286" s="21" t="inlineStr"/>
-      <c r="AH286" s="21" t="inlineStr"/>
-      <c r="AI286" s="21" t="inlineStr"/>
+      <c r="AD286" s="15" t="inlineStr"/>
+      <c r="AE286" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF286" s="14" t="inlineStr"/>
+      <c r="AG286" s="14" t="inlineStr"/>
+      <c r="AH286" s="14" t="inlineStr"/>
+      <c r="AI286" s="14" t="inlineStr"/>
     </row>
     <row r="287" customHeight="1" ht="15">
       <c r="A287" s="2" t="inlineStr"/>
       <c r="B287" s="2" t="inlineStr"/>
-      <c r="C287" s="2" t="inlineStr"/>
-      <c r="D287" s="2" t="inlineStr"/>
-      <c r="E287" s="24" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">201</t>
-          </r>
-        </is>
-      </c>
-      <c r="F287" s="24" t="inlineStr"/>
-      <c r="G287" s="24" t="inlineStr"/>
-      <c r="H287" s="24" t="inlineStr"/>
-      <c r="I287" s="24" t="inlineStr"/>
-      <c r="J287" s="24" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pelayanan Keuangan Penyuluhan Kelautan dan Perikanan</t>
-          </r>
-        </is>
-      </c>
-      <c r="K287" s="24" t="inlineStr"/>
-      <c r="L287" s="24" t="inlineStr"/>
-      <c r="M287" s="24" t="inlineStr"/>
-      <c r="N287" s="24" t="inlineStr"/>
-      <c r="O287" s="24" t="inlineStr"/>
-      <c r="P287" s="24" t="inlineStr"/>
-      <c r="Q287" s="25" t="n">
+      <c r="C287" s="16" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">EBD</t>
+          </r>
+        </is>
+      </c>
+      <c r="D287" s="16" t="inlineStr"/>
+      <c r="E287" s="16" t="inlineStr"/>
+      <c r="F287" s="16" t="inlineStr"/>
+      <c r="G287" s="16" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Manajemen Kinerja Internal</t>
+          </r>
+        </is>
+      </c>
+      <c r="H287" s="16" t="inlineStr"/>
+      <c r="I287" s="16" t="inlineStr"/>
+      <c r="J287" s="16" t="inlineStr"/>
+      <c r="K287" s="16" t="inlineStr"/>
+      <c r="L287" s="16" t="inlineStr"/>
+      <c r="M287" s="16" t="inlineStr"/>
+      <c r="N287" s="16" t="inlineStr"/>
+      <c r="O287" s="16" t="inlineStr"/>
+      <c r="P287" s="16" t="inlineStr"/>
+      <c r="Q287" s="17" t="n">
         <v>600000.0</v>
       </c>
-      <c r="R287" s="25" t="inlineStr"/>
-      <c r="S287" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T287" s="25" t="inlineStr"/>
-      <c r="U287" s="25" t="inlineStr"/>
-      <c r="V287" s="25" t="inlineStr"/>
-      <c r="W287" s="25" t="n">
+      <c r="R287" s="17" t="inlineStr"/>
+      <c r="S287" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T287" s="17" t="inlineStr"/>
+      <c r="U287" s="17" t="inlineStr"/>
+      <c r="V287" s="17" t="inlineStr"/>
+      <c r="W287" s="17" t="n">
         <v>600000.0</v>
       </c>
-      <c r="X287" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y287" s="25" t="inlineStr"/>
-      <c r="Z287" s="25" t="n">
+      <c r="X287" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y287" s="17" t="inlineStr"/>
+      <c r="Z287" s="17" t="n">
         <v>600000.0</v>
       </c>
-      <c r="AA287" s="25" t="inlineStr"/>
-      <c r="AB287" s="25" t="inlineStr"/>
-      <c r="AC287" s="26" t="n">
+      <c r="AA287" s="17" t="inlineStr"/>
+      <c r="AB287" s="17" t="inlineStr"/>
+      <c r="AC287" s="18" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD287" s="26" t="inlineStr"/>
-      <c r="AE287" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF287" s="25" t="inlineStr"/>
-      <c r="AG287" s="25" t="inlineStr"/>
-      <c r="AH287" s="25" t="inlineStr"/>
-      <c r="AI287" s="25" t="inlineStr"/>
+      <c r="AD287" s="18" t="inlineStr"/>
+      <c r="AE287" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF287" s="17" t="inlineStr"/>
+      <c r="AG287" s="17" t="inlineStr"/>
+      <c r="AH287" s="17" t="inlineStr"/>
+      <c r="AI287" s="17" t="inlineStr"/>
     </row>
     <row r="288" customHeight="1" ht="15">
       <c r="A288" s="2" t="inlineStr"/>
       <c r="B288" s="2" t="inlineStr"/>
-      <c r="C288" s="2" t="inlineStr"/>
-      <c r="D288" s="2" t="inlineStr"/>
-      <c r="E288" s="2" t="inlineStr"/>
-      <c r="F288" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">201.DA</t>
-          </r>
-        </is>
-      </c>
-      <c r="G288" s="13" t="inlineStr"/>
-      <c r="H288" s="13" t="inlineStr"/>
-      <c r="I288" s="13" t="inlineStr"/>
-      <c r="J288" s="13" t="inlineStr"/>
-      <c r="K288" s="13" t="inlineStr"/>
-      <c r="L288" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Keuangan</t>
-          </r>
-        </is>
-      </c>
-      <c r="M288" s="13" t="inlineStr"/>
-      <c r="N288" s="13" t="inlineStr"/>
-      <c r="O288" s="13" t="inlineStr"/>
-      <c r="P288" s="13" t="inlineStr"/>
-      <c r="Q288" s="14" t="n">
+      <c r="C288" s="28" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">EBD.955</t>
+          </r>
+        </is>
+      </c>
+      <c r="D288" s="28" t="inlineStr"/>
+      <c r="E288" s="28" t="inlineStr"/>
+      <c r="F288" s="28" t="inlineStr"/>
+      <c r="G288" s="28" t="inlineStr"/>
+      <c r="H288" s="28" t="inlineStr"/>
+      <c r="I288" s="28" t="inlineStr"/>
+      <c r="J288" s="28" t="inlineStr"/>
+      <c r="K288" s="20" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Manajemen Keuangan</t>
+          </r>
+        </is>
+      </c>
+      <c r="L288" s="20" t="inlineStr"/>
+      <c r="M288" s="20" t="inlineStr"/>
+      <c r="N288" s="20" t="inlineStr"/>
+      <c r="O288" s="20" t="inlineStr"/>
+      <c r="P288" s="20" t="inlineStr"/>
+      <c r="Q288" s="21" t="n">
         <v>600000.0</v>
       </c>
-      <c r="R288" s="14" t="inlineStr"/>
-      <c r="S288" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T288" s="14" t="inlineStr"/>
-      <c r="U288" s="14" t="inlineStr"/>
-      <c r="V288" s="14" t="inlineStr"/>
-      <c r="W288" s="14" t="n">
+      <c r="R288" s="21" t="inlineStr"/>
+      <c r="S288" s="21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T288" s="21" t="inlineStr"/>
+      <c r="U288" s="21" t="inlineStr"/>
+      <c r="V288" s="21" t="inlineStr"/>
+      <c r="W288" s="22" t="n">
         <v>600000.0</v>
       </c>
-      <c r="X288" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y288" s="14" t="inlineStr"/>
-      <c r="Z288" s="14" t="n">
+      <c r="X288" s="22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y288" s="22" t="inlineStr"/>
+      <c r="Z288" s="21" t="n">
         <v>600000.0</v>
       </c>
-      <c r="AA288" s="14" t="inlineStr"/>
-      <c r="AB288" s="14" t="inlineStr"/>
-      <c r="AC288" s="15" t="n">
+      <c r="AA288" s="21" t="inlineStr"/>
+      <c r="AB288" s="21" t="inlineStr"/>
+      <c r="AC288" s="23" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD288" s="15" t="inlineStr"/>
-      <c r="AE288" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF288" s="14" t="inlineStr"/>
-      <c r="AG288" s="14" t="inlineStr"/>
-      <c r="AH288" s="14" t="inlineStr"/>
-      <c r="AI288" s="14" t="inlineStr"/>
+      <c r="AD288" s="23" t="inlineStr"/>
+      <c r="AE288" s="21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF288" s="21" t="inlineStr"/>
+      <c r="AG288" s="21" t="inlineStr"/>
+      <c r="AH288" s="21" t="inlineStr"/>
+      <c r="AI288" s="21" t="inlineStr"/>
     </row>
     <row r="289" customHeight="1" ht="15">
       <c r="A289" s="2" t="inlineStr"/>
       <c r="B289" s="2" t="inlineStr"/>
       <c r="C289" s="2" t="inlineStr"/>
       <c r="D289" s="2" t="inlineStr"/>
-      <c r="E289" s="2" t="inlineStr"/>
-      <c r="F289" s="2" t="inlineStr"/>
-      <c r="G289" s="2" t="inlineStr"/>
-      <c r="H289" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">524111</t>
-          </r>
-        </is>
-      </c>
-      <c r="I289" s="13" t="inlineStr"/>
-      <c r="J289" s="13" t="inlineStr"/>
-      <c r="K289" s="13" t="inlineStr"/>
-      <c r="L289" s="13" t="inlineStr"/>
-      <c r="M289" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Perjalanan Dinas Biasa</t>
-          </r>
-        </is>
-      </c>
-      <c r="N289" s="13" t="inlineStr"/>
-      <c r="O289" s="13" t="inlineStr"/>
-      <c r="P289" s="13" t="inlineStr"/>
-      <c r="Q289" s="14" t="n">
+      <c r="E289" s="24" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">201</t>
+          </r>
+        </is>
+      </c>
+      <c r="F289" s="24" t="inlineStr"/>
+      <c r="G289" s="24" t="inlineStr"/>
+      <c r="H289" s="24" t="inlineStr"/>
+      <c r="I289" s="24" t="inlineStr"/>
+      <c r="J289" s="24" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pelayanan Keuangan Penyuluhan Kelautan dan Perikanan</t>
+          </r>
+        </is>
+      </c>
+      <c r="K289" s="24" t="inlineStr"/>
+      <c r="L289" s="24" t="inlineStr"/>
+      <c r="M289" s="24" t="inlineStr"/>
+      <c r="N289" s="24" t="inlineStr"/>
+      <c r="O289" s="24" t="inlineStr"/>
+      <c r="P289" s="24" t="inlineStr"/>
+      <c r="Q289" s="25" t="n">
         <v>600000.0</v>
       </c>
-      <c r="R289" s="14" t="inlineStr"/>
-      <c r="S289" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T289" s="14" t="inlineStr"/>
-      <c r="U289" s="14" t="inlineStr"/>
-      <c r="V289" s="14" t="inlineStr"/>
-      <c r="W289" s="14" t="n">
+      <c r="R289" s="25" t="inlineStr"/>
+      <c r="S289" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T289" s="25" t="inlineStr"/>
+      <c r="U289" s="25" t="inlineStr"/>
+      <c r="V289" s="25" t="inlineStr"/>
+      <c r="W289" s="25" t="n">
         <v>600000.0</v>
       </c>
-      <c r="X289" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y289" s="14" t="inlineStr"/>
-      <c r="Z289" s="14" t="n">
+      <c r="X289" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y289" s="25" t="inlineStr"/>
+      <c r="Z289" s="25" t="n">
         <v>600000.0</v>
       </c>
-      <c r="AA289" s="14" t="inlineStr"/>
-      <c r="AB289" s="14" t="inlineStr"/>
-      <c r="AC289" s="15" t="n">
+      <c r="AA289" s="25" t="inlineStr"/>
+      <c r="AB289" s="25" t="inlineStr"/>
+      <c r="AC289" s="26" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD289" s="15" t="inlineStr"/>
-      <c r="AE289" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF289" s="14" t="inlineStr"/>
-      <c r="AG289" s="14" t="inlineStr"/>
-      <c r="AH289" s="14" t="inlineStr"/>
-      <c r="AI289" s="14" t="inlineStr"/>
+      <c r="AD289" s="26" t="inlineStr"/>
+      <c r="AE289" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF289" s="25" t="inlineStr"/>
+      <c r="AG289" s="25" t="inlineStr"/>
+      <c r="AH289" s="25" t="inlineStr"/>
+      <c r="AI289" s="25" t="inlineStr"/>
     </row>
     <row r="290" customHeight="1" ht="15">
       <c r="A290" s="2" t="inlineStr"/>
@@ -17392,21 +17380,27 @@
       <c r="C290" s="2" t="inlineStr"/>
       <c r="D290" s="2" t="inlineStr"/>
       <c r="E290" s="2" t="inlineStr"/>
-      <c r="F290" s="2" t="inlineStr"/>
-      <c r="G290" s="2" t="inlineStr"/>
-      <c r="H290" s="2" t="inlineStr"/>
-      <c r="I290" s="2" t="inlineStr"/>
-      <c r="J290" s="2" t="inlineStr"/>
-      <c r="K290" s="2" t="inlineStr"/>
-      <c r="L290" s="2" t="inlineStr"/>
-      <c r="M290" s="2" t="inlineStr"/>
-      <c r="N290" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000231. Uang Harian</t>
-          </r>
-        </is>
-      </c>
+      <c r="F290" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">201.DA</t>
+          </r>
+        </is>
+      </c>
+      <c r="G290" s="13" t="inlineStr"/>
+      <c r="H290" s="13" t="inlineStr"/>
+      <c r="I290" s="13" t="inlineStr"/>
+      <c r="J290" s="13" t="inlineStr"/>
+      <c r="K290" s="13" t="inlineStr"/>
+      <c r="L290" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Keuangan</t>
+          </r>
+        </is>
+      </c>
+      <c r="M290" s="13" t="inlineStr"/>
+      <c r="N290" s="13" t="inlineStr"/>
       <c r="O290" s="13" t="inlineStr"/>
       <c r="P290" s="13" t="inlineStr"/>
       <c r="Q290" s="14" t="n">
@@ -17443,48 +17437,168 @@
       <c r="AH290" s="14" t="inlineStr"/>
       <c r="AI290" s="14" t="inlineStr"/>
     </row>
-    <row r="291" customHeight="1" ht="12">
+    <row r="291" customHeight="1" ht="15">
       <c r="A291" s="2" t="inlineStr"/>
-      <c r="B291" s="27" t="inlineStr">
+      <c r="B291" s="2" t="inlineStr"/>
+      <c r="C291" s="2" t="inlineStr"/>
+      <c r="D291" s="2" t="inlineStr"/>
+      <c r="E291" s="2" t="inlineStr"/>
+      <c r="F291" s="2" t="inlineStr"/>
+      <c r="G291" s="2" t="inlineStr"/>
+      <c r="H291" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">524111</t>
+          </r>
+        </is>
+      </c>
+      <c r="I291" s="13" t="inlineStr"/>
+      <c r="J291" s="13" t="inlineStr"/>
+      <c r="K291" s="13" t="inlineStr"/>
+      <c r="L291" s="13" t="inlineStr"/>
+      <c r="M291" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Perjalanan Dinas Biasa</t>
+          </r>
+        </is>
+      </c>
+      <c r="N291" s="13" t="inlineStr"/>
+      <c r="O291" s="13" t="inlineStr"/>
+      <c r="P291" s="13" t="inlineStr"/>
+      <c r="Q291" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R291" s="14" t="inlineStr"/>
+      <c r="S291" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T291" s="14" t="inlineStr"/>
+      <c r="U291" s="14" t="inlineStr"/>
+      <c r="V291" s="14" t="inlineStr"/>
+      <c r="W291" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X291" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y291" s="14" t="inlineStr"/>
+      <c r="Z291" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA291" s="14" t="inlineStr"/>
+      <c r="AB291" s="14" t="inlineStr"/>
+      <c r="AC291" s="15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD291" s="15" t="inlineStr"/>
+      <c r="AE291" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF291" s="14" t="inlineStr"/>
+      <c r="AG291" s="14" t="inlineStr"/>
+      <c r="AH291" s="14" t="inlineStr"/>
+      <c r="AI291" s="14" t="inlineStr"/>
+    </row>
+    <row r="292" customHeight="1" ht="15">
+      <c r="A292" s="2" t="inlineStr"/>
+      <c r="B292" s="2" t="inlineStr"/>
+      <c r="C292" s="2" t="inlineStr"/>
+      <c r="D292" s="2" t="inlineStr"/>
+      <c r="E292" s="2" t="inlineStr"/>
+      <c r="F292" s="2" t="inlineStr"/>
+      <c r="G292" s="2" t="inlineStr"/>
+      <c r="H292" s="2" t="inlineStr"/>
+      <c r="I292" s="2" t="inlineStr"/>
+      <c r="J292" s="2" t="inlineStr"/>
+      <c r="K292" s="2" t="inlineStr"/>
+      <c r="L292" s="2" t="inlineStr"/>
+      <c r="M292" s="2" t="inlineStr"/>
+      <c r="N292" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000231. Uang Harian</t>
+          </r>
+        </is>
+      </c>
+      <c r="O292" s="13" t="inlineStr"/>
+      <c r="P292" s="13" t="inlineStr"/>
+      <c r="Q292" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R292" s="14" t="inlineStr"/>
+      <c r="S292" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T292" s="14" t="inlineStr"/>
+      <c r="U292" s="14" t="inlineStr"/>
+      <c r="V292" s="14" t="inlineStr"/>
+      <c r="W292" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X292" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y292" s="14" t="inlineStr"/>
+      <c r="Z292" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA292" s="14" t="inlineStr"/>
+      <c r="AB292" s="14" t="inlineStr"/>
+      <c r="AC292" s="15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD292" s="15" t="inlineStr"/>
+      <c r="AE292" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF292" s="14" t="inlineStr"/>
+      <c r="AG292" s="14" t="inlineStr"/>
+      <c r="AH292" s="14" t="inlineStr"/>
+      <c r="AI292" s="14" t="inlineStr"/>
+    </row>
+    <row r="293" customHeight="1" ht="12">
+      <c r="A293" s="2" t="inlineStr"/>
+      <c r="B293" s="27" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">*Lock Pagu adalah jumlah pagu yang sedang dalam proses usulan revisi DIPA atau POK. Lock pagu akan hilang setelah usulan revisi DIPA/POK selesai menjadi DIPA.</t>
           </r>
         </is>
       </c>
-      <c r="C291" s="27" t="inlineStr"/>
-      <c r="D291" s="27" t="inlineStr"/>
-      <c r="E291" s="27" t="inlineStr"/>
-      <c r="F291" s="27" t="inlineStr"/>
-      <c r="G291" s="27" t="inlineStr"/>
-      <c r="H291" s="27" t="inlineStr"/>
-      <c r="I291" s="27" t="inlineStr"/>
-      <c r="J291" s="27" t="inlineStr"/>
-      <c r="K291" s="27" t="inlineStr"/>
-      <c r="L291" s="27" t="inlineStr"/>
-      <c r="M291" s="27" t="inlineStr"/>
-      <c r="N291" s="27" t="inlineStr"/>
-      <c r="O291" s="27" t="inlineStr"/>
-      <c r="P291" s="27" t="inlineStr"/>
-      <c r="Q291" s="27" t="inlineStr"/>
-      <c r="R291" s="27" t="inlineStr"/>
-      <c r="S291" s="27" t="inlineStr"/>
-      <c r="T291" s="27" t="inlineStr"/>
-      <c r="U291" s="27" t="inlineStr"/>
-      <c r="V291" s="27" t="inlineStr"/>
-      <c r="W291" s="27" t="inlineStr"/>
-      <c r="X291" s="27" t="inlineStr"/>
-      <c r="Y291" s="27" t="inlineStr"/>
-      <c r="Z291" s="27" t="inlineStr"/>
-      <c r="AA291" s="27" t="inlineStr"/>
-      <c r="AB291" s="27" t="inlineStr"/>
-      <c r="AC291" s="27" t="inlineStr"/>
-      <c r="AD291" s="27" t="inlineStr"/>
-      <c r="AE291" s="27" t="inlineStr"/>
-      <c r="AF291" s="27" t="inlineStr"/>
-      <c r="AG291" s="2" t="inlineStr"/>
-      <c r="AH291" s="2" t="inlineStr"/>
-      <c r="AI291" s="2" t="inlineStr"/>
+      <c r="C293" s="27" t="inlineStr"/>
+      <c r="D293" s="27" t="inlineStr"/>
+      <c r="E293" s="27" t="inlineStr"/>
+      <c r="F293" s="27" t="inlineStr"/>
+      <c r="G293" s="27" t="inlineStr"/>
+      <c r="H293" s="27" t="inlineStr"/>
+      <c r="I293" s="27" t="inlineStr"/>
+      <c r="J293" s="27" t="inlineStr"/>
+      <c r="K293" s="27" t="inlineStr"/>
+      <c r="L293" s="27" t="inlineStr"/>
+      <c r="M293" s="27" t="inlineStr"/>
+      <c r="N293" s="27" t="inlineStr"/>
+      <c r="O293" s="27" t="inlineStr"/>
+      <c r="P293" s="27" t="inlineStr"/>
+      <c r="Q293" s="27" t="inlineStr"/>
+      <c r="R293" s="27" t="inlineStr"/>
+      <c r="S293" s="27" t="inlineStr"/>
+      <c r="T293" s="27" t="inlineStr"/>
+      <c r="U293" s="27" t="inlineStr"/>
+      <c r="V293" s="27" t="inlineStr"/>
+      <c r="W293" s="27" t="inlineStr"/>
+      <c r="X293" s="27" t="inlineStr"/>
+      <c r="Y293" s="27" t="inlineStr"/>
+      <c r="Z293" s="27" t="inlineStr"/>
+      <c r="AA293" s="27" t="inlineStr"/>
+      <c r="AB293" s="27" t="inlineStr"/>
+      <c r="AC293" s="27" t="inlineStr"/>
+      <c r="AD293" s="27" t="inlineStr"/>
+      <c r="AE293" s="27" t="inlineStr"/>
+      <c r="AF293" s="27" t="inlineStr"/>
+      <c r="AG293" s="2" t="inlineStr"/>
+      <c r="AH293" s="2" t="inlineStr"/>
+      <c r="AI293" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -18920,15 +19034,15 @@
     <mergeCell ref="Z206:AB206"/>
     <mergeCell ref="AC206:AD206"/>
     <mergeCell ref="AE206:AI206"/>
-    <mergeCell ref="H207:L207"/>
-    <mergeCell ref="M207:P207"/>
+    <mergeCell ref="N207:P207"/>
     <mergeCell ref="Q207:R207"/>
     <mergeCell ref="S207:V207"/>
     <mergeCell ref="X207:Y207"/>
     <mergeCell ref="Z207:AB207"/>
     <mergeCell ref="AC207:AD207"/>
     <mergeCell ref="AE207:AI207"/>
-    <mergeCell ref="N208:P208"/>
+    <mergeCell ref="H208:L208"/>
+    <mergeCell ref="M208:P208"/>
     <mergeCell ref="Q208:R208"/>
     <mergeCell ref="S208:V208"/>
     <mergeCell ref="X208:Y208"/>
@@ -18942,15 +19056,15 @@
     <mergeCell ref="Z209:AB209"/>
     <mergeCell ref="AC209:AD209"/>
     <mergeCell ref="AE209:AI209"/>
-    <mergeCell ref="H210:L210"/>
-    <mergeCell ref="M210:P210"/>
+    <mergeCell ref="N210:P210"/>
     <mergeCell ref="Q210:R210"/>
     <mergeCell ref="S210:V210"/>
     <mergeCell ref="X210:Y210"/>
     <mergeCell ref="Z210:AB210"/>
     <mergeCell ref="AC210:AD210"/>
     <mergeCell ref="AE210:AI210"/>
-    <mergeCell ref="N211:P211"/>
+    <mergeCell ref="H211:L211"/>
+    <mergeCell ref="M211:P211"/>
     <mergeCell ref="Q211:R211"/>
     <mergeCell ref="S211:V211"/>
     <mergeCell ref="X211:Y211"/>
@@ -18999,68 +19113,68 @@
     <mergeCell ref="Z217:AB217"/>
     <mergeCell ref="AC217:AD217"/>
     <mergeCell ref="AE217:AI217"/>
-    <mergeCell ref="F218:K218"/>
-    <mergeCell ref="L218:P218"/>
+    <mergeCell ref="N218:P218"/>
     <mergeCell ref="Q218:R218"/>
     <mergeCell ref="S218:V218"/>
     <mergeCell ref="X218:Y218"/>
     <mergeCell ref="Z218:AB218"/>
     <mergeCell ref="AC218:AD218"/>
     <mergeCell ref="AE218:AI218"/>
-    <mergeCell ref="H219:L219"/>
-    <mergeCell ref="M219:P219"/>
+    <mergeCell ref="F219:K219"/>
+    <mergeCell ref="L219:P219"/>
     <mergeCell ref="Q219:R219"/>
     <mergeCell ref="S219:V219"/>
     <mergeCell ref="X219:Y219"/>
     <mergeCell ref="Z219:AB219"/>
     <mergeCell ref="AC219:AD219"/>
     <mergeCell ref="AE219:AI219"/>
-    <mergeCell ref="N220:P220"/>
+    <mergeCell ref="H220:L220"/>
+    <mergeCell ref="M220:P220"/>
     <mergeCell ref="Q220:R220"/>
     <mergeCell ref="S220:V220"/>
     <mergeCell ref="X220:Y220"/>
     <mergeCell ref="Z220:AB220"/>
     <mergeCell ref="AC220:AD220"/>
     <mergeCell ref="AE220:AI220"/>
-    <mergeCell ref="H221:L221"/>
-    <mergeCell ref="M221:P221"/>
+    <mergeCell ref="N221:P221"/>
     <mergeCell ref="Q221:R221"/>
     <mergeCell ref="S221:V221"/>
     <mergeCell ref="X221:Y221"/>
     <mergeCell ref="Z221:AB221"/>
     <mergeCell ref="AC221:AD221"/>
     <mergeCell ref="AE221:AI221"/>
-    <mergeCell ref="N222:P222"/>
+    <mergeCell ref="H222:L222"/>
+    <mergeCell ref="M222:P222"/>
     <mergeCell ref="Q222:R222"/>
     <mergeCell ref="S222:V222"/>
     <mergeCell ref="X222:Y222"/>
     <mergeCell ref="Z222:AB222"/>
     <mergeCell ref="AC222:AD222"/>
     <mergeCell ref="AE222:AI222"/>
-    <mergeCell ref="H223:L223"/>
-    <mergeCell ref="M223:P223"/>
+    <mergeCell ref="N223:P223"/>
     <mergeCell ref="Q223:R223"/>
     <mergeCell ref="S223:V223"/>
     <mergeCell ref="X223:Y223"/>
     <mergeCell ref="Z223:AB223"/>
     <mergeCell ref="AC223:AD223"/>
     <mergeCell ref="AE223:AI223"/>
-    <mergeCell ref="N224:P224"/>
+    <mergeCell ref="H224:L224"/>
+    <mergeCell ref="M224:P224"/>
     <mergeCell ref="Q224:R224"/>
     <mergeCell ref="S224:V224"/>
     <mergeCell ref="X224:Y224"/>
     <mergeCell ref="Z224:AB224"/>
     <mergeCell ref="AC224:AD224"/>
     <mergeCell ref="AE224:AI224"/>
-    <mergeCell ref="H225:L225"/>
-    <mergeCell ref="M225:P225"/>
+    <mergeCell ref="N225:P225"/>
     <mergeCell ref="Q225:R225"/>
     <mergeCell ref="S225:V225"/>
     <mergeCell ref="X225:Y225"/>
     <mergeCell ref="Z225:AB225"/>
     <mergeCell ref="AC225:AD225"/>
     <mergeCell ref="AE225:AI225"/>
-    <mergeCell ref="N226:P226"/>
+    <mergeCell ref="H226:L226"/>
+    <mergeCell ref="M226:P226"/>
     <mergeCell ref="Q226:R226"/>
     <mergeCell ref="S226:V226"/>
     <mergeCell ref="X226:Y226"/>
@@ -19075,23 +19189,23 @@
     <mergeCell ref="Z228:AB228"/>
     <mergeCell ref="AC228:AD228"/>
     <mergeCell ref="AE228:AI228"/>
-    <mergeCell ref="F229:K229"/>
-    <mergeCell ref="L229:P229"/>
+    <mergeCell ref="N229:P229"/>
     <mergeCell ref="Q229:R229"/>
     <mergeCell ref="S229:V229"/>
     <mergeCell ref="X229:Y229"/>
     <mergeCell ref="Z229:AB229"/>
     <mergeCell ref="AC229:AD229"/>
     <mergeCell ref="AE229:AI229"/>
-    <mergeCell ref="H230:L230"/>
-    <mergeCell ref="M230:P230"/>
+    <mergeCell ref="F230:K230"/>
+    <mergeCell ref="L230:P230"/>
     <mergeCell ref="Q230:R230"/>
     <mergeCell ref="S230:V230"/>
     <mergeCell ref="X230:Y230"/>
     <mergeCell ref="Z230:AB230"/>
     <mergeCell ref="AC230:AD230"/>
     <mergeCell ref="AE230:AI230"/>
-    <mergeCell ref="N231:P231"/>
+    <mergeCell ref="H231:L231"/>
+    <mergeCell ref="M231:P231"/>
     <mergeCell ref="Q231:R231"/>
     <mergeCell ref="S231:V231"/>
     <mergeCell ref="X231:Y231"/>
@@ -19105,30 +19219,30 @@
     <mergeCell ref="Z232:AB232"/>
     <mergeCell ref="AC232:AD232"/>
     <mergeCell ref="AE232:AI232"/>
-    <mergeCell ref="H233:L233"/>
-    <mergeCell ref="M233:P233"/>
+    <mergeCell ref="N233:P233"/>
     <mergeCell ref="Q233:R233"/>
     <mergeCell ref="S233:V233"/>
     <mergeCell ref="X233:Y233"/>
     <mergeCell ref="Z233:AB233"/>
     <mergeCell ref="AC233:AD233"/>
     <mergeCell ref="AE233:AI233"/>
-    <mergeCell ref="N234:P234"/>
+    <mergeCell ref="H234:L234"/>
+    <mergeCell ref="M234:P234"/>
     <mergeCell ref="Q234:R234"/>
     <mergeCell ref="S234:V234"/>
     <mergeCell ref="X234:Y234"/>
     <mergeCell ref="Z234:AB234"/>
     <mergeCell ref="AC234:AD234"/>
     <mergeCell ref="AE234:AI234"/>
-    <mergeCell ref="H235:L235"/>
-    <mergeCell ref="M235:P235"/>
+    <mergeCell ref="N235:P235"/>
     <mergeCell ref="Q235:R235"/>
     <mergeCell ref="S235:V235"/>
     <mergeCell ref="X235:Y235"/>
     <mergeCell ref="Z235:AB235"/>
     <mergeCell ref="AC235:AD235"/>
     <mergeCell ref="AE235:AI235"/>
-    <mergeCell ref="N236:P236"/>
+    <mergeCell ref="H236:L236"/>
+    <mergeCell ref="M236:P236"/>
     <mergeCell ref="Q236:R236"/>
     <mergeCell ref="S236:V236"/>
     <mergeCell ref="X236:Y236"/>
@@ -19240,15 +19354,15 @@
     <mergeCell ref="Z251:AB251"/>
     <mergeCell ref="AC251:AD251"/>
     <mergeCell ref="AE251:AI251"/>
-    <mergeCell ref="H252:L252"/>
-    <mergeCell ref="M252:P252"/>
+    <mergeCell ref="N252:P252"/>
     <mergeCell ref="Q252:R252"/>
     <mergeCell ref="S252:V252"/>
     <mergeCell ref="X252:Y252"/>
     <mergeCell ref="Z252:AB252"/>
     <mergeCell ref="AC252:AD252"/>
     <mergeCell ref="AE252:AI252"/>
-    <mergeCell ref="N253:P253"/>
+    <mergeCell ref="H253:L253"/>
+    <mergeCell ref="M253:P253"/>
     <mergeCell ref="Q253:R253"/>
     <mergeCell ref="S253:V253"/>
     <mergeCell ref="X253:Y253"/>
@@ -19354,8 +19468,7 @@
     <mergeCell ref="Z268:AB268"/>
     <mergeCell ref="AC268:AD268"/>
     <mergeCell ref="AE268:AI268"/>
-    <mergeCell ref="H269:L269"/>
-    <mergeCell ref="M269:P269"/>
+    <mergeCell ref="N269:P269"/>
     <mergeCell ref="Q269:R269"/>
     <mergeCell ref="S269:V269"/>
     <mergeCell ref="X269:Y269"/>
@@ -19369,7 +19482,8 @@
     <mergeCell ref="Z270:AB270"/>
     <mergeCell ref="AC270:AD270"/>
     <mergeCell ref="AE270:AI270"/>
-    <mergeCell ref="N271:P271"/>
+    <mergeCell ref="H271:L271"/>
+    <mergeCell ref="M271:P271"/>
     <mergeCell ref="Q271:R271"/>
     <mergeCell ref="S271:V271"/>
     <mergeCell ref="X271:Y271"/>
@@ -19383,30 +19497,30 @@
     <mergeCell ref="Z272:AB272"/>
     <mergeCell ref="AC272:AD272"/>
     <mergeCell ref="AE272:AI272"/>
-    <mergeCell ref="F273:K273"/>
-    <mergeCell ref="L273:P273"/>
+    <mergeCell ref="N273:P273"/>
     <mergeCell ref="Q273:R273"/>
     <mergeCell ref="S273:V273"/>
     <mergeCell ref="X273:Y273"/>
     <mergeCell ref="Z273:AB273"/>
     <mergeCell ref="AC273:AD273"/>
     <mergeCell ref="AE273:AI273"/>
-    <mergeCell ref="H274:L274"/>
-    <mergeCell ref="M274:P274"/>
+    <mergeCell ref="N274:P274"/>
     <mergeCell ref="Q274:R274"/>
     <mergeCell ref="S274:V274"/>
     <mergeCell ref="X274:Y274"/>
     <mergeCell ref="Z274:AB274"/>
     <mergeCell ref="AC274:AD274"/>
     <mergeCell ref="AE274:AI274"/>
-    <mergeCell ref="N275:P275"/>
+    <mergeCell ref="F275:K275"/>
+    <mergeCell ref="L275:P275"/>
     <mergeCell ref="Q275:R275"/>
     <mergeCell ref="S275:V275"/>
     <mergeCell ref="X275:Y275"/>
     <mergeCell ref="Z275:AB275"/>
     <mergeCell ref="AC275:AD275"/>
     <mergeCell ref="AE275:AI275"/>
-    <mergeCell ref="N276:P276"/>
+    <mergeCell ref="H276:L276"/>
+    <mergeCell ref="M276:P276"/>
     <mergeCell ref="Q276:R276"/>
     <mergeCell ref="S276:V276"/>
     <mergeCell ref="X276:Y276"/>
@@ -19449,8 +19563,7 @@
     <mergeCell ref="Z282:AB282"/>
     <mergeCell ref="AC282:AD282"/>
     <mergeCell ref="AE282:AI282"/>
-    <mergeCell ref="H283:L283"/>
-    <mergeCell ref="M283:P283"/>
+    <mergeCell ref="N283:P283"/>
     <mergeCell ref="Q283:R283"/>
     <mergeCell ref="S283:V283"/>
     <mergeCell ref="X283:Y283"/>
@@ -19464,54 +19577,69 @@
     <mergeCell ref="Z284:AB284"/>
     <mergeCell ref="AC284:AD284"/>
     <mergeCell ref="AE284:AI284"/>
-    <mergeCell ref="C285:F285"/>
-    <mergeCell ref="G285:P285"/>
+    <mergeCell ref="H285:L285"/>
+    <mergeCell ref="M285:P285"/>
     <mergeCell ref="Q285:R285"/>
     <mergeCell ref="S285:V285"/>
     <mergeCell ref="X285:Y285"/>
     <mergeCell ref="Z285:AB285"/>
     <mergeCell ref="AC285:AD285"/>
     <mergeCell ref="AE285:AI285"/>
-    <mergeCell ref="C286:J286"/>
-    <mergeCell ref="K286:P286"/>
+    <mergeCell ref="N286:P286"/>
     <mergeCell ref="Q286:R286"/>
     <mergeCell ref="S286:V286"/>
     <mergeCell ref="X286:Y286"/>
     <mergeCell ref="Z286:AB286"/>
     <mergeCell ref="AC286:AD286"/>
     <mergeCell ref="AE286:AI286"/>
-    <mergeCell ref="E287:I287"/>
-    <mergeCell ref="J287:P287"/>
+    <mergeCell ref="C287:F287"/>
+    <mergeCell ref="G287:P287"/>
     <mergeCell ref="Q287:R287"/>
     <mergeCell ref="S287:V287"/>
     <mergeCell ref="X287:Y287"/>
     <mergeCell ref="Z287:AB287"/>
     <mergeCell ref="AC287:AD287"/>
     <mergeCell ref="AE287:AI287"/>
-    <mergeCell ref="F288:K288"/>
-    <mergeCell ref="L288:P288"/>
+    <mergeCell ref="C288:J288"/>
+    <mergeCell ref="K288:P288"/>
     <mergeCell ref="Q288:R288"/>
     <mergeCell ref="S288:V288"/>
     <mergeCell ref="X288:Y288"/>
     <mergeCell ref="Z288:AB288"/>
     <mergeCell ref="AC288:AD288"/>
     <mergeCell ref="AE288:AI288"/>
-    <mergeCell ref="H289:L289"/>
-    <mergeCell ref="M289:P289"/>
+    <mergeCell ref="E289:I289"/>
+    <mergeCell ref="J289:P289"/>
     <mergeCell ref="Q289:R289"/>
     <mergeCell ref="S289:V289"/>
     <mergeCell ref="X289:Y289"/>
     <mergeCell ref="Z289:AB289"/>
     <mergeCell ref="AC289:AD289"/>
     <mergeCell ref="AE289:AI289"/>
-    <mergeCell ref="N290:P290"/>
+    <mergeCell ref="F290:K290"/>
+    <mergeCell ref="L290:P290"/>
     <mergeCell ref="Q290:R290"/>
     <mergeCell ref="S290:V290"/>
     <mergeCell ref="X290:Y290"/>
     <mergeCell ref="Z290:AB290"/>
     <mergeCell ref="AC290:AD290"/>
     <mergeCell ref="AE290:AI290"/>
-    <mergeCell ref="B291:AF291"/>
+    <mergeCell ref="H291:L291"/>
+    <mergeCell ref="M291:P291"/>
+    <mergeCell ref="Q291:R291"/>
+    <mergeCell ref="S291:V291"/>
+    <mergeCell ref="X291:Y291"/>
+    <mergeCell ref="Z291:AB291"/>
+    <mergeCell ref="AC291:AD291"/>
+    <mergeCell ref="AE291:AI291"/>
+    <mergeCell ref="N292:P292"/>
+    <mergeCell ref="Q292:R292"/>
+    <mergeCell ref="S292:V292"/>
+    <mergeCell ref="X292:Y292"/>
+    <mergeCell ref="Z292:AB292"/>
+    <mergeCell ref="AC292:AD292"/>
+    <mergeCell ref="AE292:AI292"/>
+    <mergeCell ref="B293:AF293"/>
   </mergeCells>
   <pageMargins left="0.0" right="0.0" top="0.0" bottom="0.00" header="0.0" footer="0.0"/>
   <pageSetup orientation="landscape" paperSize="9"/>

--- a/Database/Akrual.xlsx
+++ b/Database/Akrual.xlsx
@@ -982,19 +982,19 @@
         <v>9.0559784495E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>6.68137418E8</v>
+        <v>2.479274605E9</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>9.1227921913E10</v>
+        <v>9.30390591E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.9123153650647639</v>
+        <v>0.9304274545357487</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>8.768116087E9</v>
+        <v>6.9569789E9</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1714,20 +1714,20 @@
         <v>8.6526416455E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>6.68137418E8</v>
+        <v>2.479274605E9</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>8.7194553873E10</v>
+        <v>8.900569106E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.9086302303715327</v>
+        <v>0.9275035880109923</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>8.768084127E9</v>
+        <v>6.95694694E9</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1777,20 +1777,20 @@
         <v>8.6526416455E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>6.68137418E8</v>
+        <v>2.479274605E9</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>8.7194553873E10</v>
+        <v>8.900569106E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.9086302303715327</v>
+        <v>0.9275035880109923</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>8.768084127E9</v>
+        <v>6.95694694E9</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1840,20 +1840,20 @@
         <v>8.6525816455E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>6.68137418E8</v>
+        <v>2.479274605E9</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>8.7193953873E10</v>
+        <v>8.900509106E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.9086296590845643</v>
+        <v>0.9275031347291728</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>8.768084127E9</v>
+        <v>6.95694694E9</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -3233,20 +3233,20 @@
         <v>8.6508305403E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>6.68137418E8</v>
+        <v>2.479274605E9</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>8.7176442821E10</v>
+        <v>8.8987580008E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.9086226326120992</v>
+        <v>0.9274997533757052</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>8.767065179E9</v>
+        <v>6.955927992E9</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -3296,20 +3296,20 @@
         <v>8.0279551347E10</v>
       </c>
       <c r="X47" s="25" t="n">
-        <v>5.189E8</v>
+        <v>2.281636445E9</v>
       </c>
       <c r="Y47" s="25" t="inlineStr"/>
       <c r="Z47" s="25" t="n">
-        <v>8.0798451347E10</v>
+        <v>8.2561187792E10</v>
       </c>
       <c r="AA47" s="25" t="inlineStr"/>
       <c r="AB47" s="25" t="inlineStr"/>
       <c r="AC47" s="26" t="n">
-        <v>0.9078811963334875</v>
+        <v>0.9276879530946325</v>
       </c>
       <c r="AD47" s="26" t="inlineStr"/>
       <c r="AE47" s="25" t="n">
-        <v>8.198271653E9</v>
+        <v>6.435535208E9</v>
       </c>
       <c r="AF47" s="25" t="inlineStr"/>
       <c r="AG47" s="25" t="inlineStr"/>
@@ -7162,20 +7162,20 @@
         <v>5.0689888E10</v>
       </c>
       <c r="X113" s="14" t="n">
-        <v>2.18452E8</v>
+        <v>1.981188445E9</v>
       </c>
       <c r="Y113" s="14" t="inlineStr"/>
       <c r="Z113" s="14" t="n">
-        <v>5.090834E10</v>
+        <v>5.2671076445E10</v>
       </c>
       <c r="AA113" s="14" t="inlineStr"/>
       <c r="AB113" s="14" t="inlineStr"/>
       <c r="AC113" s="15" t="n">
-        <v>0.9233056566566804</v>
+        <v>0.9552757529289885</v>
       </c>
       <c r="AD113" s="15" t="inlineStr"/>
       <c r="AE113" s="14" t="n">
-        <v>4.228699E9</v>
+        <v>2.465962555E9</v>
       </c>
       <c r="AF113" s="14" t="inlineStr"/>
       <c r="AG113" s="14" t="inlineStr"/>
@@ -9417,20 +9417,20 @@
         <v>2.475555828E10</v>
       </c>
       <c r="X152" s="14" t="n">
-        <v>0.0</v>
+        <v>1.762736445E9</v>
       </c>
       <c r="Y152" s="14" t="inlineStr"/>
       <c r="Z152" s="14" t="n">
-        <v>2.475555828E10</v>
+        <v>2.6518294725E10</v>
       </c>
       <c r="AA152" s="14" t="inlineStr"/>
       <c r="AB152" s="14" t="inlineStr"/>
       <c r="AC152" s="15" t="n">
-        <v>0.8618034181440637</v>
+        <v>0.9231687194798619</v>
       </c>
       <c r="AD152" s="15" t="inlineStr"/>
       <c r="AE152" s="14" t="n">
-        <v>3.96973772E9</v>
+        <v>2.207001275E9</v>
       </c>
       <c r="AF152" s="14" t="inlineStr"/>
       <c r="AG152" s="14" t="inlineStr"/>
@@ -9474,20 +9474,20 @@
         <v>1.997827308E10</v>
       </c>
       <c r="X153" s="14" t="n">
-        <v>0.0</v>
+        <v>1.762736445E9</v>
       </c>
       <c r="Y153" s="14" t="inlineStr"/>
       <c r="Z153" s="14" t="n">
-        <v>1.997827308E10</v>
+        <v>2.1741009525E10</v>
       </c>
       <c r="AA153" s="14" t="inlineStr"/>
       <c r="AB153" s="14" t="inlineStr"/>
       <c r="AC153" s="15" t="n">
-        <v>0.8342358340523915</v>
+        <v>0.9078426919885392</v>
       </c>
       <c r="AD153" s="15" t="inlineStr"/>
       <c r="AE153" s="14" t="n">
-        <v>3.96971892E9</v>
+        <v>2.206982475E9</v>
       </c>
       <c r="AF153" s="14" t="inlineStr"/>
       <c r="AG153" s="14" t="inlineStr"/>
@@ -11572,20 +11572,20 @@
         <v>6.228754056E9</v>
       </c>
       <c r="X189" s="25" t="n">
-        <v>1.49237418E8</v>
+        <v>1.9763816E8</v>
       </c>
       <c r="Y189" s="25" t="inlineStr"/>
       <c r="Z189" s="25" t="n">
-        <v>6.377991474E9</v>
+        <v>6.426392216E9</v>
       </c>
       <c r="AA189" s="25" t="inlineStr"/>
       <c r="AB189" s="25" t="inlineStr"/>
       <c r="AC189" s="26" t="n">
-        <v>0.918121328643394</v>
+        <v>0.9250886872128617</v>
       </c>
       <c r="AD189" s="26" t="inlineStr"/>
       <c r="AE189" s="25" t="n">
-        <v>5.68793526E8</v>
+        <v>5.20392784E8</v>
       </c>
       <c r="AF189" s="25" t="inlineStr"/>
       <c r="AG189" s="25" t="inlineStr"/>
@@ -13310,20 +13310,20 @@
         <v>6.39842407E8</v>
       </c>
       <c r="X219" s="14" t="n">
-        <v>604300.0</v>
+        <v>4.9005042E7</v>
       </c>
       <c r="Y219" s="14" t="inlineStr"/>
       <c r="Z219" s="14" t="n">
-        <v>6.40446707E8</v>
+        <v>6.88847449E8</v>
       </c>
       <c r="AA219" s="14" t="inlineStr"/>
       <c r="AB219" s="14" t="inlineStr"/>
       <c r="AC219" s="15" t="n">
-        <v>0.9147356929431659</v>
+        <v>0.9838653891199525</v>
       </c>
       <c r="AD219" s="15" t="inlineStr"/>
       <c r="AE219" s="14" t="n">
-        <v>5.9697293E7</v>
+        <v>1.1296551E7</v>
       </c>
       <c r="AF219" s="14" t="inlineStr"/>
       <c r="AG219" s="14" t="inlineStr"/>
@@ -13373,20 +13373,20 @@
         <v>4.70513911E8</v>
       </c>
       <c r="X220" s="14" t="n">
-        <v>0.0</v>
+        <v>3.8886478E7</v>
       </c>
       <c r="Y220" s="14" t="inlineStr"/>
       <c r="Z220" s="14" t="n">
-        <v>4.70513911E8</v>
+        <v>5.09400389E8</v>
       </c>
       <c r="AA220" s="14" t="inlineStr"/>
       <c r="AB220" s="14" t="inlineStr"/>
       <c r="AC220" s="15" t="n">
-        <v>0.9118486647286822</v>
+        <v>0.9872100562015503</v>
       </c>
       <c r="AD220" s="15" t="inlineStr"/>
       <c r="AE220" s="14" t="n">
-        <v>4.5486089E7</v>
+        <v>6599611.0</v>
       </c>
       <c r="AF220" s="14" t="inlineStr"/>
       <c r="AG220" s="14" t="inlineStr"/>
@@ -13430,20 +13430,20 @@
         <v>4.70513911E8</v>
       </c>
       <c r="X221" s="14" t="n">
-        <v>0.0</v>
+        <v>3.8886478E7</v>
       </c>
       <c r="Y221" s="14" t="inlineStr"/>
       <c r="Z221" s="14" t="n">
-        <v>4.70513911E8</v>
+        <v>5.09400389E8</v>
       </c>
       <c r="AA221" s="14" t="inlineStr"/>
       <c r="AB221" s="14" t="inlineStr"/>
       <c r="AC221" s="15" t="n">
-        <v>0.9118486647286822</v>
+        <v>0.9872100562015503</v>
       </c>
       <c r="AD221" s="15" t="inlineStr"/>
       <c r="AE221" s="14" t="n">
-        <v>4.5486089E7</v>
+        <v>6599611.0</v>
       </c>
       <c r="AF221" s="14" t="inlineStr"/>
       <c r="AG221" s="14" t="inlineStr"/>
@@ -13493,20 +13493,20 @@
         <v>5485232.0</v>
       </c>
       <c r="X222" s="14" t="n">
-        <v>0.0</v>
+        <v>263514.0</v>
       </c>
       <c r="Y222" s="14" t="inlineStr"/>
       <c r="Z222" s="14" t="n">
-        <v>5485232.0</v>
+        <v>5748746.0</v>
       </c>
       <c r="AA222" s="14" t="inlineStr"/>
       <c r="AB222" s="14" t="inlineStr"/>
       <c r="AC222" s="15" t="n">
-        <v>0.9142053333333333</v>
+        <v>0.9581243333333334</v>
       </c>
       <c r="AD222" s="15" t="inlineStr"/>
       <c r="AE222" s="14" t="n">
-        <v>514768.0</v>
+        <v>251254.0</v>
       </c>
       <c r="AF222" s="14" t="inlineStr"/>
       <c r="AG222" s="14" t="inlineStr"/>
@@ -13550,20 +13550,20 @@
         <v>5485232.0</v>
       </c>
       <c r="X223" s="14" t="n">
-        <v>0.0</v>
+        <v>263514.0</v>
       </c>
       <c r="Y223" s="14" t="inlineStr"/>
       <c r="Z223" s="14" t="n">
-        <v>5485232.0</v>
+        <v>5748746.0</v>
       </c>
       <c r="AA223" s="14" t="inlineStr"/>
       <c r="AB223" s="14" t="inlineStr"/>
       <c r="AC223" s="15" t="n">
-        <v>0.9142053333333333</v>
+        <v>0.9581243333333334</v>
       </c>
       <c r="AD223" s="15" t="inlineStr"/>
       <c r="AE223" s="14" t="n">
-        <v>514768.0</v>
+        <v>251254.0</v>
       </c>
       <c r="AF223" s="14" t="inlineStr"/>
       <c r="AG223" s="14" t="inlineStr"/>
@@ -13733,20 +13733,20 @@
         <v>1.33021464E8</v>
       </c>
       <c r="X226" s="14" t="n">
-        <v>0.0</v>
+        <v>9250750.0</v>
       </c>
       <c r="Y226" s="14" t="inlineStr"/>
       <c r="Z226" s="14" t="n">
-        <v>1.33021464E8</v>
+        <v>1.42272214E8</v>
       </c>
       <c r="AA226" s="14" t="inlineStr"/>
       <c r="AB226" s="14" t="inlineStr"/>
       <c r="AC226" s="15" t="n">
-        <v>0.919291389080857</v>
+        <v>0.9832219350380097</v>
       </c>
       <c r="AD226" s="15" t="inlineStr"/>
       <c r="AE226" s="14" t="n">
-        <v>1.1678536E7</v>
+        <v>2427786.0</v>
       </c>
       <c r="AF226" s="14" t="inlineStr"/>
       <c r="AG226" s="14" t="inlineStr"/>
@@ -13833,20 +13833,20 @@
         <v>1.044355E8</v>
       </c>
       <c r="X228" s="14" t="n">
-        <v>0.0</v>
+        <v>9250750.0</v>
       </c>
       <c r="Y228" s="14" t="inlineStr"/>
       <c r="Z228" s="14" t="n">
-        <v>1.044355E8</v>
+        <v>1.1368625E8</v>
       </c>
       <c r="AA228" s="14" t="inlineStr"/>
       <c r="AB228" s="14" t="inlineStr"/>
       <c r="AC228" s="15" t="n">
-        <v>0.9113045375218151</v>
+        <v>0.9920266143106458</v>
       </c>
       <c r="AD228" s="15" t="inlineStr"/>
       <c r="AE228" s="14" t="n">
-        <v>1.01645E7</v>
+        <v>913750.0</v>
       </c>
       <c r="AF228" s="14" t="inlineStr"/>
       <c r="AG228" s="14" t="inlineStr"/>

--- a/Database/Akrual.xlsx
+++ b/Database/Akrual.xlsx
@@ -982,19 +982,19 @@
         <v>9.0559784495E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>2.479274605E9</v>
+        <v>7.709055227E9</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>9.30390591E10</v>
+        <v>9.8268839722E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.9304274545357487</v>
+        <v>0.9827273328769286</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>6.9569789E9</v>
+        <v>1.727198278E9</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1714,20 +1714,20 @@
         <v>8.6526416455E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>2.479274605E9</v>
+        <v>7.709055227E9</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>8.900569106E10</v>
+        <v>9.4235471682E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.9275035880109923</v>
+        <v>0.9820016794661273</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>6.95694694E9</v>
+        <v>1.727166318E9</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1777,20 +1777,20 @@
         <v>8.6526416455E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>2.479274605E9</v>
+        <v>7.709055227E9</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>8.900569106E10</v>
+        <v>9.4235471682E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.9275035880109923</v>
+        <v>0.9820016794661273</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>6.95694694E9</v>
+        <v>1.727166318E9</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1840,20 +1840,20 @@
         <v>8.6525816455E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>2.479274605E9</v>
+        <v>7.709055227E9</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>8.900509106E10</v>
+        <v>9.4234871682E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.9275031347291728</v>
+        <v>0.9820015669321237</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>6.95694694E9</v>
+        <v>1.727166318E9</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -3233,20 +3233,20 @@
         <v>8.6508305403E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>2.479274605E9</v>
+        <v>7.709055227E9</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>8.8987580008E10</v>
+        <v>9.421736063E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.9274997533757052</v>
+        <v>0.9820087111052892</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>6.955927992E9</v>
+        <v>1.72614737E9</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -3296,20 +3296,20 @@
         <v>8.0279551347E10</v>
       </c>
       <c r="X47" s="25" t="n">
-        <v>2.281636445E9</v>
+        <v>7.481889742E9</v>
       </c>
       <c r="Y47" s="25" t="inlineStr"/>
       <c r="Z47" s="25" t="n">
-        <v>8.2561187792E10</v>
+        <v>8.7761441089E10</v>
       </c>
       <c r="AA47" s="25" t="inlineStr"/>
       <c r="AB47" s="25" t="inlineStr"/>
       <c r="AC47" s="26" t="n">
-        <v>0.9276879530946325</v>
+        <v>0.9861199168985132</v>
       </c>
       <c r="AD47" s="26" t="inlineStr"/>
       <c r="AE47" s="25" t="n">
-        <v>6.435535208E9</v>
+        <v>1.235281911E9</v>
       </c>
       <c r="AF47" s="25" t="inlineStr"/>
       <c r="AG47" s="25" t="inlineStr"/>
@@ -6082,20 +6082,20 @@
         <v>5.93914035E8</v>
       </c>
       <c r="X95" s="14" t="n">
-        <v>2.694E7</v>
+        <v>3.10703762E8</v>
       </c>
       <c r="Y95" s="14" t="inlineStr"/>
       <c r="Z95" s="14" t="n">
-        <v>6.20854035E8</v>
+        <v>9.04617797E8</v>
       </c>
       <c r="AA95" s="14" t="inlineStr"/>
       <c r="AB95" s="14" t="inlineStr"/>
       <c r="AC95" s="15" t="n">
-        <v>0.6417812375955145</v>
+        <v>0.9351098592917866</v>
       </c>
       <c r="AD95" s="15" t="inlineStr"/>
       <c r="AE95" s="14" t="n">
-        <v>3.46537965E8</v>
+        <v>6.2774203E7</v>
       </c>
       <c r="AF95" s="14" t="inlineStr"/>
       <c r="AG95" s="14" t="inlineStr"/>
@@ -7042,20 +7042,20 @@
         <v>1.42100114E8</v>
       </c>
       <c r="X111" s="14" t="n">
-        <v>0.0</v>
+        <v>2.83763762E8</v>
       </c>
       <c r="Y111" s="14" t="inlineStr"/>
       <c r="Z111" s="14" t="n">
-        <v>1.42100114E8</v>
+        <v>4.25863876E8</v>
       </c>
       <c r="AA111" s="14" t="inlineStr"/>
       <c r="AB111" s="14" t="inlineStr"/>
       <c r="AC111" s="15" t="n">
-        <v>0.31577803111111113</v>
+        <v>0.9463641688888889</v>
       </c>
       <c r="AD111" s="15" t="inlineStr"/>
       <c r="AE111" s="14" t="n">
-        <v>3.07899886E8</v>
+        <v>2.4136124E7</v>
       </c>
       <c r="AF111" s="14" t="inlineStr"/>
       <c r="AG111" s="14" t="inlineStr"/>
@@ -7099,20 +7099,20 @@
         <v>1.42100114E8</v>
       </c>
       <c r="X112" s="14" t="n">
-        <v>0.0</v>
+        <v>2.83763762E8</v>
       </c>
       <c r="Y112" s="14" t="inlineStr"/>
       <c r="Z112" s="14" t="n">
-        <v>1.42100114E8</v>
+        <v>4.25863876E8</v>
       </c>
       <c r="AA112" s="14" t="inlineStr"/>
       <c r="AB112" s="14" t="inlineStr"/>
       <c r="AC112" s="15" t="n">
-        <v>0.31577803111111113</v>
+        <v>0.9463641688888889</v>
       </c>
       <c r="AD112" s="15" t="inlineStr"/>
       <c r="AE112" s="14" t="n">
-        <v>3.07899886E8</v>
+        <v>2.4136124E7</v>
       </c>
       <c r="AF112" s="14" t="inlineStr"/>
       <c r="AG112" s="14" t="inlineStr"/>
@@ -7162,20 +7162,20 @@
         <v>5.0689888E10</v>
       </c>
       <c r="X113" s="14" t="n">
-        <v>1.981188445E9</v>
+        <v>3.745299916E9</v>
       </c>
       <c r="Y113" s="14" t="inlineStr"/>
       <c r="Z113" s="14" t="n">
-        <v>5.2671076445E10</v>
+        <v>5.4435187916E10</v>
       </c>
       <c r="AA113" s="14" t="inlineStr"/>
       <c r="AB113" s="14" t="inlineStr"/>
       <c r="AC113" s="15" t="n">
-        <v>0.9552757529289885</v>
+        <v>0.9872707875372125</v>
       </c>
       <c r="AD113" s="15" t="inlineStr"/>
       <c r="AE113" s="14" t="n">
-        <v>2.465962555E9</v>
+        <v>7.01851084E8</v>
       </c>
       <c r="AF113" s="14" t="inlineStr"/>
       <c r="AG113" s="14" t="inlineStr"/>
@@ -9417,20 +9417,20 @@
         <v>2.475555828E10</v>
       </c>
       <c r="X152" s="14" t="n">
-        <v>1.762736445E9</v>
+        <v>3.526847916E9</v>
       </c>
       <c r="Y152" s="14" t="inlineStr"/>
       <c r="Z152" s="14" t="n">
-        <v>2.6518294725E10</v>
+        <v>2.8282406196E10</v>
       </c>
       <c r="AA152" s="14" t="inlineStr"/>
       <c r="AB152" s="14" t="inlineStr"/>
       <c r="AC152" s="15" t="n">
-        <v>0.9231687194798619</v>
+        <v>0.9845818889385857</v>
       </c>
       <c r="AD152" s="15" t="inlineStr"/>
       <c r="AE152" s="14" t="n">
-        <v>2.207001275E9</v>
+        <v>4.42889804E8</v>
       </c>
       <c r="AF152" s="14" t="inlineStr"/>
       <c r="AG152" s="14" t="inlineStr"/>
@@ -9474,20 +9474,20 @@
         <v>1.997827308E10</v>
       </c>
       <c r="X153" s="14" t="n">
-        <v>1.762736445E9</v>
+        <v>3.526847916E9</v>
       </c>
       <c r="Y153" s="14" t="inlineStr"/>
       <c r="Z153" s="14" t="n">
-        <v>2.1741009525E10</v>
+        <v>2.3505120996E10</v>
       </c>
       <c r="AA153" s="14" t="inlineStr"/>
       <c r="AB153" s="14" t="inlineStr"/>
       <c r="AC153" s="15" t="n">
-        <v>0.9078426919885392</v>
+        <v>0.9815069670977007</v>
       </c>
       <c r="AD153" s="15" t="inlineStr"/>
       <c r="AE153" s="14" t="n">
-        <v>2.206982475E9</v>
+        <v>4.42871004E8</v>
       </c>
       <c r="AF153" s="14" t="inlineStr"/>
       <c r="AG153" s="14" t="inlineStr"/>
@@ -9651,20 +9651,20 @@
         <v>2.3164511208E10</v>
       </c>
       <c r="X156" s="14" t="n">
-        <v>2.45185E8</v>
+        <v>3.397563064E9</v>
       </c>
       <c r="Y156" s="14" t="inlineStr"/>
       <c r="Z156" s="14" t="n">
-        <v>2.3409696208E10</v>
+        <v>2.6562074272E10</v>
       </c>
       <c r="AA156" s="14" t="inlineStr"/>
       <c r="AB156" s="14" t="inlineStr"/>
       <c r="AC156" s="15" t="n">
-        <v>0.8686540936662458</v>
+        <v>0.9856281067310323</v>
       </c>
       <c r="AD156" s="15" t="inlineStr"/>
       <c r="AE156" s="14" t="n">
-        <v>3.539691792E9</v>
+        <v>3.87313728E8</v>
       </c>
       <c r="AF156" s="14" t="inlineStr"/>
       <c r="AG156" s="14" t="inlineStr"/>
@@ -11338,20 +11338,20 @@
         <v>9.794680989E9</v>
       </c>
       <c r="X185" s="14" t="n">
-        <v>0.0</v>
+        <v>3.152378064E9</v>
       </c>
       <c r="Y185" s="14" t="inlineStr"/>
       <c r="Z185" s="14" t="n">
-        <v>9.794680989E9</v>
+        <v>1.2947059053E10</v>
       </c>
       <c r="AA185" s="14" t="inlineStr"/>
       <c r="AB185" s="14" t="inlineStr"/>
       <c r="AC185" s="15" t="n">
-        <v>0.7507542654118889</v>
+        <v>0.9923814588239839</v>
       </c>
       <c r="AD185" s="15" t="inlineStr"/>
       <c r="AE185" s="14" t="n">
-        <v>3.251773011E9</v>
+        <v>9.9394947E7</v>
       </c>
       <c r="AF185" s="14" t="inlineStr"/>
       <c r="AG185" s="14" t="inlineStr"/>
@@ -11395,20 +11395,20 @@
         <v>8.220237613E9</v>
       </c>
       <c r="X186" s="14" t="n">
-        <v>0.0</v>
+        <v>3.152378064E9</v>
       </c>
       <c r="Y186" s="14" t="inlineStr"/>
       <c r="Z186" s="14" t="n">
-        <v>8.220237613E9</v>
+        <v>1.1372615677E10</v>
       </c>
       <c r="AA186" s="14" t="inlineStr"/>
       <c r="AB186" s="14" t="inlineStr"/>
       <c r="AC186" s="15" t="n">
-        <v>0.7165479090829847</v>
+        <v>0.9913367919281729</v>
       </c>
       <c r="AD186" s="15" t="inlineStr"/>
       <c r="AE186" s="14" t="n">
-        <v>3.251762387E9</v>
+        <v>9.9384323E7</v>
       </c>
       <c r="AF186" s="14" t="inlineStr"/>
       <c r="AG186" s="14" t="inlineStr"/>
@@ -11572,20 +11572,20 @@
         <v>6.228754056E9</v>
       </c>
       <c r="X189" s="25" t="n">
-        <v>1.9763816E8</v>
+        <v>2.27165485E8</v>
       </c>
       <c r="Y189" s="25" t="inlineStr"/>
       <c r="Z189" s="25" t="n">
-        <v>6.426392216E9</v>
+        <v>6.455919541E9</v>
       </c>
       <c r="AA189" s="25" t="inlineStr"/>
       <c r="AB189" s="25" t="inlineStr"/>
       <c r="AC189" s="26" t="n">
-        <v>0.9250886872128617</v>
+        <v>0.9293391894235967</v>
       </c>
       <c r="AD189" s="26" t="inlineStr"/>
       <c r="AE189" s="25" t="n">
-        <v>5.20392784E8</v>
+        <v>4.90865459E8</v>
       </c>
       <c r="AF189" s="25" t="inlineStr"/>
       <c r="AG189" s="25" t="inlineStr"/>
@@ -11635,20 +11635,20 @@
         <v>4.783558496E9</v>
       </c>
       <c r="X190" s="14" t="n">
-        <v>1.1638698E8</v>
+        <v>1.31977006E8</v>
       </c>
       <c r="Y190" s="14" t="inlineStr"/>
       <c r="Z190" s="14" t="n">
-        <v>4.899945476E9</v>
+        <v>4.915535502E9</v>
       </c>
       <c r="AA190" s="14" t="inlineStr"/>
       <c r="AB190" s="14" t="inlineStr"/>
       <c r="AC190" s="15" t="n">
-        <v>0.9788065011852679</v>
+        <v>0.9819207437573924</v>
       </c>
       <c r="AD190" s="15" t="inlineStr"/>
       <c r="AE190" s="14" t="n">
-        <v>1.06095524E8</v>
+        <v>9.0505498E7</v>
       </c>
       <c r="AF190" s="14" t="inlineStr"/>
       <c r="AG190" s="14" t="inlineStr"/>
@@ -11698,20 +11698,20 @@
         <v>1.777909494E9</v>
       </c>
       <c r="X191" s="14" t="n">
-        <v>7.7954712E7</v>
+        <v>9.3544738E7</v>
       </c>
       <c r="Y191" s="14" t="inlineStr"/>
       <c r="Z191" s="14" t="n">
-        <v>1.855864206E9</v>
+        <v>1.871454232E9</v>
       </c>
       <c r="AA191" s="14" t="inlineStr"/>
       <c r="AB191" s="14" t="inlineStr"/>
       <c r="AC191" s="15" t="n">
-        <v>0.9815144490450425</v>
+        <v>0.9897595758870372</v>
       </c>
       <c r="AD191" s="15" t="inlineStr"/>
       <c r="AE191" s="14" t="n">
-        <v>3.4952794E7</v>
+        <v>1.9362768E7</v>
       </c>
       <c r="AF191" s="14" t="inlineStr"/>
       <c r="AG191" s="14" t="inlineStr"/>
@@ -11869,20 +11869,20 @@
         <v>5.5184254E7</v>
       </c>
       <c r="X194" s="14" t="n">
-        <v>3953112.0</v>
+        <v>1.9543138E7</v>
       </c>
       <c r="Y194" s="14" t="inlineStr"/>
       <c r="Z194" s="14" t="n">
-        <v>5.9137366E7</v>
+        <v>7.4727392E7</v>
       </c>
       <c r="AA194" s="14" t="inlineStr"/>
       <c r="AB194" s="14" t="inlineStr"/>
       <c r="AC194" s="15" t="n">
-        <v>0.6295897583306718</v>
+        <v>0.7955646971148728</v>
       </c>
       <c r="AD194" s="15" t="inlineStr"/>
       <c r="AE194" s="14" t="n">
-        <v>3.4792634E7</v>
+        <v>1.9202608E7</v>
       </c>
       <c r="AF194" s="14" t="inlineStr"/>
       <c r="AG194" s="14" t="inlineStr"/>
@@ -13953,20 +13953,20 @@
         <v>6.74613153E8</v>
       </c>
       <c r="X230" s="14" t="n">
-        <v>3.1766138E7</v>
+        <v>4.5703437E7</v>
       </c>
       <c r="Y230" s="14" t="inlineStr"/>
       <c r="Z230" s="14" t="n">
-        <v>7.06379291E8</v>
+        <v>7.2031659E8</v>
       </c>
       <c r="AA230" s="14" t="inlineStr"/>
       <c r="AB230" s="14" t="inlineStr"/>
       <c r="AC230" s="15" t="n">
-        <v>0.6372848658450768</v>
+        <v>0.6498588892297144</v>
       </c>
       <c r="AD230" s="15" t="inlineStr"/>
       <c r="AE230" s="14" t="n">
-        <v>4.02040709E8</v>
+        <v>3.8810341E8</v>
       </c>
       <c r="AF230" s="14" t="inlineStr"/>
       <c r="AG230" s="14" t="inlineStr"/>
@@ -15288,20 +15288,20 @@
         <v>2.11521335E8</v>
       </c>
       <c r="X253" s="14" t="n">
-        <v>6690138.0</v>
+        <v>2.0627437E7</v>
       </c>
       <c r="Y253" s="14" t="inlineStr"/>
       <c r="Z253" s="14" t="n">
-        <v>2.18211473E8</v>
+        <v>2.32148772E8</v>
       </c>
       <c r="AA253" s="14" t="inlineStr"/>
       <c r="AB253" s="14" t="inlineStr"/>
       <c r="AC253" s="15" t="n">
-        <v>0.6562751067669172</v>
+        <v>0.6981917954887218</v>
       </c>
       <c r="AD253" s="15" t="inlineStr"/>
       <c r="AE253" s="14" t="n">
-        <v>1.14288527E8</v>
+        <v>1.00351228E8</v>
       </c>
       <c r="AF253" s="14" t="inlineStr"/>
       <c r="AG253" s="14" t="inlineStr"/>
@@ -15559,20 +15559,20 @@
         <v>1.22043496E8</v>
       </c>
       <c r="X258" s="14" t="n">
-        <v>1490000.0</v>
+        <v>1.5139299E7</v>
       </c>
       <c r="Y258" s="14" t="inlineStr"/>
       <c r="Z258" s="14" t="n">
-        <v>1.23533496E8</v>
+        <v>1.37182795E8</v>
       </c>
       <c r="AA258" s="14" t="inlineStr"/>
       <c r="AB258" s="14" t="inlineStr"/>
       <c r="AC258" s="15" t="n">
-        <v>0.7277378262150221</v>
+        <v>0.8081460677466863</v>
       </c>
       <c r="AD258" s="15" t="inlineStr"/>
       <c r="AE258" s="14" t="n">
-        <v>4.6216504E7</v>
+        <v>3.2567205E7</v>
       </c>
       <c r="AF258" s="14" t="inlineStr"/>
       <c r="AG258" s="14" t="inlineStr"/>
@@ -15844,20 +15844,20 @@
         <v>8450284.0</v>
       </c>
       <c r="X263" s="14" t="n">
-        <v>0.0</v>
+        <v>288000.0</v>
       </c>
       <c r="Y263" s="14" t="inlineStr"/>
       <c r="Z263" s="14" t="n">
-        <v>8450284.0</v>
+        <v>8738284.0</v>
       </c>
       <c r="AA263" s="14" t="inlineStr"/>
       <c r="AB263" s="14" t="inlineStr"/>
       <c r="AC263" s="15" t="n">
-        <v>0.7041903333333334</v>
+        <v>0.7281903333333334</v>
       </c>
       <c r="AD263" s="15" t="inlineStr"/>
       <c r="AE263" s="14" t="n">
-        <v>3549716.0</v>
+        <v>3261716.0</v>
       </c>
       <c r="AF263" s="14" t="inlineStr"/>
       <c r="AG263" s="14" t="inlineStr"/>

--- a/Database/Akrual.xlsx
+++ b/Database/Akrual.xlsx
@@ -982,19 +982,19 @@
         <v>9.0559784495E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>7.709055227E9</v>
+        <v>8.096493585E9</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>9.8268839722E10</v>
+        <v>9.865627808E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.9827273328769286</v>
+        <v>0.986601869966088</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>1.727198278E9</v>
+        <v>1.33975992E9</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1714,20 +1714,20 @@
         <v>8.6526416455E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>7.709055227E9</v>
+        <v>8.096493585E9</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>9.4235471682E10</v>
+        <v>9.462291004E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.9820016794661273</v>
+        <v>0.9860390669960531</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>1.727166318E9</v>
+        <v>1.33972796E9</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1777,20 +1777,20 @@
         <v>8.6526416455E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>7.709055227E9</v>
+        <v>8.096493585E9</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>9.4235471682E10</v>
+        <v>9.462291004E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.9820016794661273</v>
+        <v>0.9860390669960531</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>1.727166318E9</v>
+        <v>1.33972796E9</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1840,20 +1840,20 @@
         <v>8.6525816455E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>7.709055227E9</v>
+        <v>8.096493585E9</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>9.4234871682E10</v>
+        <v>9.462231004E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.9820015669321237</v>
+        <v>0.9860389797057041</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>1.727166318E9</v>
+        <v>1.33972796E9</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -2564,20 +2564,20 @@
         <v>1.6461052E7</v>
       </c>
       <c r="X35" s="22" t="n">
-        <v>0.0</v>
+        <v>800000.0</v>
       </c>
       <c r="Y35" s="22" t="inlineStr"/>
       <c r="Z35" s="21" t="n">
-        <v>1.6461052E7</v>
+        <v>1.7261052E7</v>
       </c>
       <c r="AA35" s="21" t="inlineStr"/>
       <c r="AB35" s="21" t="inlineStr"/>
       <c r="AC35" s="23" t="n">
-        <v>0.9417077803203662</v>
+        <v>0.9874743707093822</v>
       </c>
       <c r="AD35" s="23" t="inlineStr"/>
       <c r="AE35" s="21" t="n">
-        <v>1018948.0</v>
+        <v>218948.0</v>
       </c>
       <c r="AF35" s="21" t="inlineStr"/>
       <c r="AG35" s="21" t="inlineStr"/>
@@ -2627,20 +2627,20 @@
         <v>1.6461052E7</v>
       </c>
       <c r="X36" s="25" t="n">
-        <v>0.0</v>
+        <v>800000.0</v>
       </c>
       <c r="Y36" s="25" t="inlineStr"/>
       <c r="Z36" s="25" t="n">
-        <v>1.6461052E7</v>
+        <v>1.7261052E7</v>
       </c>
       <c r="AA36" s="25" t="inlineStr"/>
       <c r="AB36" s="25" t="inlineStr"/>
       <c r="AC36" s="26" t="n">
-        <v>0.9417077803203662</v>
+        <v>0.9874743707093822</v>
       </c>
       <c r="AD36" s="26" t="inlineStr"/>
       <c r="AE36" s="25" t="n">
-        <v>1018948.0</v>
+        <v>218948.0</v>
       </c>
       <c r="AF36" s="25" t="inlineStr"/>
       <c r="AG36" s="25" t="inlineStr"/>
@@ -2993,20 +2993,20 @@
         <v>1.4061052E7</v>
       </c>
       <c r="X42" s="14" t="n">
-        <v>0.0</v>
+        <v>800000.0</v>
       </c>
       <c r="Y42" s="14" t="inlineStr"/>
       <c r="Z42" s="14" t="n">
-        <v>1.4061052E7</v>
+        <v>1.4861052E7</v>
       </c>
       <c r="AA42" s="14" t="inlineStr"/>
       <c r="AB42" s="14" t="inlineStr"/>
       <c r="AC42" s="15" t="n">
-        <v>0.9324305039787798</v>
+        <v>0.985480901856764</v>
       </c>
       <c r="AD42" s="15" t="inlineStr"/>
       <c r="AE42" s="14" t="n">
-        <v>1018948.0</v>
+        <v>218948.0</v>
       </c>
       <c r="AF42" s="14" t="inlineStr"/>
       <c r="AG42" s="14" t="inlineStr"/>
@@ -3056,20 +3056,20 @@
         <v>1.4061052E7</v>
       </c>
       <c r="X43" s="14" t="n">
-        <v>0.0</v>
+        <v>800000.0</v>
       </c>
       <c r="Y43" s="14" t="inlineStr"/>
       <c r="Z43" s="14" t="n">
-        <v>1.4061052E7</v>
+        <v>1.4861052E7</v>
       </c>
       <c r="AA43" s="14" t="inlineStr"/>
       <c r="AB43" s="14" t="inlineStr"/>
       <c r="AC43" s="15" t="n">
-        <v>0.9324305039787798</v>
+        <v>0.985480901856764</v>
       </c>
       <c r="AD43" s="15" t="inlineStr"/>
       <c r="AE43" s="14" t="n">
-        <v>1018948.0</v>
+        <v>218948.0</v>
       </c>
       <c r="AF43" s="14" t="inlineStr"/>
       <c r="AG43" s="14" t="inlineStr"/>
@@ -3113,20 +3113,20 @@
         <v>1.3311952E7</v>
       </c>
       <c r="X44" s="14" t="n">
-        <v>0.0</v>
+        <v>800000.0</v>
       </c>
       <c r="Y44" s="14" t="inlineStr"/>
       <c r="Z44" s="14" t="n">
-        <v>1.3311952E7</v>
+        <v>1.4111952E7</v>
       </c>
       <c r="AA44" s="14" t="inlineStr"/>
       <c r="AB44" s="14" t="inlineStr"/>
       <c r="AC44" s="15" t="n">
-        <v>0.9302552061495458</v>
+        <v>0.9861601677148847</v>
       </c>
       <c r="AD44" s="15" t="inlineStr"/>
       <c r="AE44" s="14" t="n">
-        <v>998048.0</v>
+        <v>198048.0</v>
       </c>
       <c r="AF44" s="14" t="inlineStr"/>
       <c r="AG44" s="14" t="inlineStr"/>
@@ -3233,20 +3233,20 @@
         <v>8.6508305403E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>7.709055227E9</v>
+        <v>8.095693585E9</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>9.421736063E10</v>
+        <v>9.4603998988E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.9820087111052892</v>
+        <v>0.9860385654024658</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>1.72614737E9</v>
+        <v>1.339509012E9</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -3296,20 +3296,20 @@
         <v>8.0279551347E10</v>
       </c>
       <c r="X47" s="25" t="n">
-        <v>7.481889742E9</v>
+        <v>7.495823038E9</v>
       </c>
       <c r="Y47" s="25" t="inlineStr"/>
       <c r="Z47" s="25" t="n">
-        <v>8.7761441089E10</v>
+        <v>8.7775374385E10</v>
       </c>
       <c r="AA47" s="25" t="inlineStr"/>
       <c r="AB47" s="25" t="inlineStr"/>
       <c r="AC47" s="26" t="n">
-        <v>0.9861199168985132</v>
+        <v>0.9862764765507153</v>
       </c>
       <c r="AD47" s="26" t="inlineStr"/>
       <c r="AE47" s="25" t="n">
-        <v>1.235281911E9</v>
+        <v>1.221348615E9</v>
       </c>
       <c r="AF47" s="25" t="inlineStr"/>
       <c r="AG47" s="25" t="inlineStr"/>
@@ -3346,7 +3346,7 @@
       <c r="O48" s="13" t="inlineStr"/>
       <c r="P48" s="13" t="inlineStr"/>
       <c r="Q48" s="14" t="n">
-        <v>5.942904E9</v>
+        <v>5.92038E9</v>
       </c>
       <c r="R48" s="14" t="inlineStr"/>
       <c r="S48" s="14" t="n">
@@ -3368,11 +3368,11 @@
       <c r="AA48" s="14" t="inlineStr"/>
       <c r="AB48" s="14" t="inlineStr"/>
       <c r="AC48" s="15" t="n">
-        <v>0.9859760655733292</v>
+        <v>0.9897271972407177</v>
       </c>
       <c r="AD48" s="15" t="inlineStr"/>
       <c r="AE48" s="14" t="n">
-        <v>8.3342896E7</v>
+        <v>6.0818896E7</v>
       </c>
       <c r="AF48" s="14" t="inlineStr"/>
       <c r="AG48" s="14" t="inlineStr"/>
@@ -5324,7 +5324,7 @@
       <c r="O82" s="13" t="inlineStr"/>
       <c r="P82" s="13" t="inlineStr"/>
       <c r="Q82" s="14" t="n">
-        <v>3.6072E8</v>
+        <v>3.38196E8</v>
       </c>
       <c r="R82" s="14" t="inlineStr"/>
       <c r="S82" s="14" t="n">
@@ -5346,11 +5346,11 @@
       <c r="AA82" s="14" t="inlineStr"/>
       <c r="AB82" s="14" t="inlineStr"/>
       <c r="AC82" s="15" t="n">
-        <v>0.8484808161454868</v>
+        <v>0.9049900057954559</v>
       </c>
       <c r="AD82" s="15" t="inlineStr"/>
       <c r="AE82" s="14" t="n">
-        <v>5.4656E7</v>
+        <v>3.2132E7</v>
       </c>
       <c r="AF82" s="14" t="inlineStr"/>
       <c r="AG82" s="14" t="inlineStr"/>
@@ -5438,7 +5438,7 @@
       <c r="O84" s="13" t="inlineStr"/>
       <c r="P84" s="13" t="inlineStr"/>
       <c r="Q84" s="14" t="n">
-        <v>2.9304E8</v>
+        <v>2.78388E8</v>
       </c>
       <c r="R84" s="14" t="inlineStr"/>
       <c r="S84" s="14" t="n">
@@ -5460,11 +5460,11 @@
       <c r="AA84" s="14" t="inlineStr"/>
       <c r="AB84" s="14" t="inlineStr"/>
       <c r="AC84" s="15" t="n">
-        <v>0.8595959595959596</v>
+        <v>0.9048378522062732</v>
       </c>
       <c r="AD84" s="15" t="inlineStr"/>
       <c r="AE84" s="14" t="n">
-        <v>4.1144E7</v>
+        <v>2.6492E7</v>
       </c>
       <c r="AF84" s="14" t="inlineStr"/>
       <c r="AG84" s="14" t="inlineStr"/>
@@ -5495,7 +5495,7 @@
       <c r="O85" s="13" t="inlineStr"/>
       <c r="P85" s="13" t="inlineStr"/>
       <c r="Q85" s="14" t="n">
-        <v>4.92E7</v>
+        <v>4.1328E7</v>
       </c>
       <c r="R85" s="14" t="inlineStr"/>
       <c r="S85" s="14" t="n">
@@ -5517,11 +5517,11 @@
       <c r="AA85" s="14" t="inlineStr"/>
       <c r="AB85" s="14" t="inlineStr"/>
       <c r="AC85" s="15" t="n">
-        <v>0.7566666666666667</v>
+        <v>0.9007936507936508</v>
       </c>
       <c r="AD85" s="15" t="inlineStr"/>
       <c r="AE85" s="14" t="n">
-        <v>1.1972E7</v>
+        <v>4100000.0</v>
       </c>
       <c r="AF85" s="14" t="inlineStr"/>
       <c r="AG85" s="14" t="inlineStr"/>
@@ -6069,7 +6069,7 @@
       <c r="O95" s="13" t="inlineStr"/>
       <c r="P95" s="13" t="inlineStr"/>
       <c r="Q95" s="14" t="n">
-        <v>9.67392E8</v>
+        <v>9.72489E8</v>
       </c>
       <c r="R95" s="14" t="inlineStr"/>
       <c r="S95" s="14" t="n">
@@ -6091,11 +6091,11 @@
       <c r="AA95" s="14" t="inlineStr"/>
       <c r="AB95" s="14" t="inlineStr"/>
       <c r="AC95" s="15" t="n">
-        <v>0.9351098592917866</v>
+        <v>0.9302087704848075</v>
       </c>
       <c r="AD95" s="15" t="inlineStr"/>
       <c r="AE95" s="14" t="n">
-        <v>6.2774203E7</v>
+        <v>6.7871203E7</v>
       </c>
       <c r="AF95" s="14" t="inlineStr"/>
       <c r="AG95" s="14" t="inlineStr"/>
@@ -6732,7 +6732,7 @@
       <c r="O106" s="13" t="inlineStr"/>
       <c r="P106" s="13" t="inlineStr"/>
       <c r="Q106" s="14" t="n">
-        <v>8.304E7</v>
+        <v>8.8137E7</v>
       </c>
       <c r="R106" s="14" t="inlineStr"/>
       <c r="S106" s="14" t="n">
@@ -6754,11 +6754,11 @@
       <c r="AA106" s="14" t="inlineStr"/>
       <c r="AB106" s="14" t="inlineStr"/>
       <c r="AC106" s="15" t="n">
-        <v>0.6957249518304431</v>
+        <v>0.6554908835108978</v>
       </c>
       <c r="AD106" s="15" t="inlineStr"/>
       <c r="AE106" s="14" t="n">
-        <v>2.5267E7</v>
+        <v>3.0364E7</v>
       </c>
       <c r="AF106" s="14" t="inlineStr"/>
       <c r="AG106" s="14" t="inlineStr"/>
@@ -6789,7 +6789,7 @@
       <c r="O107" s="13" t="inlineStr"/>
       <c r="P107" s="13" t="inlineStr"/>
       <c r="Q107" s="14" t="n">
-        <v>2.31E7</v>
+        <v>2.52E7</v>
       </c>
       <c r="R107" s="14" t="inlineStr"/>
       <c r="S107" s="14" t="n">
@@ -6811,11 +6811,11 @@
       <c r="AA107" s="14" t="inlineStr"/>
       <c r="AB107" s="14" t="inlineStr"/>
       <c r="AC107" s="15" t="n">
-        <v>0.7166666666666667</v>
+        <v>0.6569444444444444</v>
       </c>
       <c r="AD107" s="15" t="inlineStr"/>
       <c r="AE107" s="14" t="n">
-        <v>6545000.0</v>
+        <v>8645000.0</v>
       </c>
       <c r="AF107" s="14" t="inlineStr"/>
       <c r="AG107" s="14" t="inlineStr"/>
@@ -6846,7 +6846,7 @@
       <c r="O108" s="13" t="inlineStr"/>
       <c r="P108" s="13" t="inlineStr"/>
       <c r="Q108" s="14" t="n">
-        <v>5.994E7</v>
+        <v>6.2937E7</v>
       </c>
       <c r="R108" s="14" t="inlineStr"/>
       <c r="S108" s="14" t="n">
@@ -6868,11 +6868,11 @@
       <c r="AA108" s="14" t="inlineStr"/>
       <c r="AB108" s="14" t="inlineStr"/>
       <c r="AC108" s="15" t="n">
-        <v>0.6876543209876543</v>
+        <v>0.6549088771310994</v>
       </c>
       <c r="AD108" s="15" t="inlineStr"/>
       <c r="AE108" s="14" t="n">
-        <v>1.8722E7</v>
+        <v>2.1719E7</v>
       </c>
       <c r="AF108" s="14" t="inlineStr"/>
       <c r="AG108" s="14" t="inlineStr"/>
@@ -7149,7 +7149,7 @@
       <c r="O113" s="13" t="inlineStr"/>
       <c r="P113" s="13" t="inlineStr"/>
       <c r="Q113" s="14" t="n">
-        <v>5.5137039E10</v>
+        <v>5.5154319E10</v>
       </c>
       <c r="R113" s="14" t="inlineStr"/>
       <c r="S113" s="14" t="n">
@@ -7162,20 +7162,20 @@
         <v>5.0689888E10</v>
       </c>
       <c r="X113" s="14" t="n">
-        <v>3.745299916E9</v>
+        <v>3.759233212E9</v>
       </c>
       <c r="Y113" s="14" t="inlineStr"/>
       <c r="Z113" s="14" t="n">
-        <v>5.4435187916E10</v>
+        <v>5.4449121212E10</v>
       </c>
       <c r="AA113" s="14" t="inlineStr"/>
       <c r="AB113" s="14" t="inlineStr"/>
       <c r="AC113" s="15" t="n">
-        <v>0.9872707875372125</v>
+        <v>0.987214096723776</v>
       </c>
       <c r="AD113" s="15" t="inlineStr"/>
       <c r="AE113" s="14" t="n">
-        <v>7.01851084E8</v>
+        <v>7.05197788E8</v>
       </c>
       <c r="AF113" s="14" t="inlineStr"/>
       <c r="AG113" s="14" t="inlineStr"/>
@@ -7225,20 +7225,20 @@
         <v>1.70891536E10</v>
       </c>
       <c r="X114" s="14" t="n">
-        <v>0.0</v>
+        <v>3390500.0</v>
       </c>
       <c r="Y114" s="14" t="inlineStr"/>
       <c r="Z114" s="14" t="n">
-        <v>1.70891536E10</v>
+        <v>1.70925441E10</v>
       </c>
       <c r="AA114" s="14" t="inlineStr"/>
       <c r="AB114" s="14" t="inlineStr"/>
       <c r="AC114" s="15" t="n">
-        <v>0.9992991460978126</v>
+        <v>0.9994974077457648</v>
       </c>
       <c r="AD114" s="15" t="inlineStr"/>
       <c r="AE114" s="14" t="n">
-        <v>1.19854E7</v>
+        <v>8594900.0</v>
       </c>
       <c r="AF114" s="14" t="inlineStr"/>
       <c r="AG114" s="14" t="inlineStr"/>
@@ -7282,20 +7282,20 @@
         <v>1.45984002E10</v>
       </c>
       <c r="X115" s="14" t="n">
-        <v>0.0</v>
+        <v>3390500.0</v>
       </c>
       <c r="Y115" s="14" t="inlineStr"/>
       <c r="Z115" s="14" t="n">
-        <v>1.45984002E10</v>
+        <v>1.46017907E10</v>
       </c>
       <c r="AA115" s="14" t="inlineStr"/>
       <c r="AB115" s="14" t="inlineStr"/>
       <c r="AC115" s="15" t="n">
-        <v>0.9996124502364411</v>
+        <v>0.9998446117038686</v>
       </c>
       <c r="AD115" s="15" t="inlineStr"/>
       <c r="AE115" s="14" t="n">
-        <v>5659800.0</v>
+        <v>2269300.0</v>
       </c>
       <c r="AF115" s="14" t="inlineStr"/>
       <c r="AG115" s="14" t="inlineStr"/>
@@ -7502,20 +7502,20 @@
         <v>230145.0</v>
       </c>
       <c r="X119" s="14" t="n">
-        <v>0.0</v>
+        <v>76.0</v>
       </c>
       <c r="Y119" s="14" t="inlineStr"/>
       <c r="Z119" s="14" t="n">
-        <v>230145.0</v>
+        <v>230221.0</v>
       </c>
       <c r="AA119" s="14" t="inlineStr"/>
       <c r="AB119" s="14" t="inlineStr"/>
       <c r="AC119" s="15" t="n">
-        <v>0.9629497907949791</v>
+        <v>0.9632677824267782</v>
       </c>
       <c r="AD119" s="15" t="inlineStr"/>
       <c r="AE119" s="14" t="n">
-        <v>8855.0</v>
+        <v>8779.0</v>
       </c>
       <c r="AF119" s="14" t="inlineStr"/>
       <c r="AG119" s="14" t="inlineStr"/>
@@ -7559,20 +7559,20 @@
         <v>196371.0</v>
       </c>
       <c r="X120" s="14" t="n">
-        <v>0.0</v>
+        <v>76.0</v>
       </c>
       <c r="Y120" s="14" t="inlineStr"/>
       <c r="Z120" s="14" t="n">
-        <v>196371.0</v>
+        <v>196447.0</v>
       </c>
       <c r="AA120" s="14" t="inlineStr"/>
       <c r="AB120" s="14" t="inlineStr"/>
       <c r="AC120" s="15" t="n">
-        <v>0.9626029411764706</v>
+        <v>0.9629754901960784</v>
       </c>
       <c r="AD120" s="15" t="inlineStr"/>
       <c r="AE120" s="14" t="n">
-        <v>7629.0</v>
+        <v>7553.0</v>
       </c>
       <c r="AF120" s="14" t="inlineStr"/>
       <c r="AG120" s="14" t="inlineStr"/>
@@ -8204,20 +8204,20 @@
         <v>3.68345E9</v>
       </c>
       <c r="X131" s="14" t="n">
-        <v>0.0</v>
+        <v>540000.0</v>
       </c>
       <c r="Y131" s="14" t="inlineStr"/>
       <c r="Z131" s="14" t="n">
-        <v>3.68345E9</v>
+        <v>3.68399E9</v>
       </c>
       <c r="AA131" s="14" t="inlineStr"/>
       <c r="AB131" s="14" t="inlineStr"/>
       <c r="AC131" s="15" t="n">
-        <v>0.9989710472103284</v>
+        <v>0.9991174980554582</v>
       </c>
       <c r="AD131" s="15" t="inlineStr"/>
       <c r="AE131" s="14" t="n">
-        <v>3794000.0</v>
+        <v>3254000.0</v>
       </c>
       <c r="AF131" s="14" t="inlineStr"/>
       <c r="AG131" s="14" t="inlineStr"/>
@@ -8261,20 +8261,20 @@
         <v>3.14519E9</v>
       </c>
       <c r="X132" s="14" t="n">
-        <v>0.0</v>
+        <v>540000.0</v>
       </c>
       <c r="Y132" s="14" t="inlineStr"/>
       <c r="Z132" s="14" t="n">
-        <v>3.14519E9</v>
+        <v>3.14573E9</v>
       </c>
       <c r="AA132" s="14" t="inlineStr"/>
       <c r="AB132" s="14" t="inlineStr"/>
       <c r="AC132" s="15" t="n">
-        <v>0.9987964356712332</v>
+        <v>0.9989679197708464</v>
       </c>
       <c r="AD132" s="15" t="inlineStr"/>
       <c r="AE132" s="14" t="n">
-        <v>3790000.0</v>
+        <v>3250000.0</v>
       </c>
       <c r="AF132" s="14" t="inlineStr"/>
       <c r="AG132" s="14" t="inlineStr"/>
@@ -8672,20 +8672,20 @@
         <v>9.4305324E8</v>
       </c>
       <c r="X139" s="14" t="n">
-        <v>0.0</v>
+        <v>72420.0</v>
       </c>
       <c r="Y139" s="14" t="inlineStr"/>
       <c r="Z139" s="14" t="n">
-        <v>9.4305324E8</v>
+        <v>9.4312566E8</v>
       </c>
       <c r="AA139" s="14" t="inlineStr"/>
       <c r="AB139" s="14" t="inlineStr"/>
       <c r="AC139" s="15" t="n">
-        <v>0.9995307240306265</v>
+        <v>0.9996074811127975</v>
       </c>
       <c r="AD139" s="15" t="inlineStr"/>
       <c r="AE139" s="14" t="n">
-        <v>442760.0</v>
+        <v>370340.0</v>
       </c>
       <c r="AF139" s="14" t="inlineStr"/>
       <c r="AG139" s="14" t="inlineStr"/>
@@ -8729,20 +8729,20 @@
         <v>8.0632428E8</v>
       </c>
       <c r="X140" s="14" t="n">
-        <v>0.0</v>
+        <v>72420.0</v>
       </c>
       <c r="Y140" s="14" t="inlineStr"/>
       <c r="Z140" s="14" t="n">
-        <v>8.0632428E8</v>
+        <v>8.063967E8</v>
       </c>
       <c r="AA140" s="14" t="inlineStr"/>
       <c r="AB140" s="14" t="inlineStr"/>
       <c r="AC140" s="15" t="n">
-        <v>0.99945991372899</v>
+        <v>0.9995496802022906</v>
       </c>
       <c r="AD140" s="15" t="inlineStr"/>
       <c r="AE140" s="14" t="n">
-        <v>435720.0</v>
+        <v>363300.0</v>
       </c>
       <c r="AF140" s="14" t="inlineStr"/>
       <c r="AG140" s="14" t="inlineStr"/>
@@ -8893,7 +8893,7 @@
       <c r="O143" s="13" t="inlineStr"/>
       <c r="P143" s="13" t="inlineStr"/>
       <c r="Q143" s="14" t="n">
-        <v>2.672352E9</v>
+        <v>2.689632E9</v>
       </c>
       <c r="R143" s="14" t="inlineStr"/>
       <c r="S143" s="14" t="n">
@@ -8906,20 +8906,20 @@
         <v>2.213268E9</v>
       </c>
       <c r="X143" s="14" t="n">
-        <v>2.18452E8</v>
+        <v>2.19192E8</v>
       </c>
       <c r="Y143" s="14" t="inlineStr"/>
       <c r="Z143" s="14" t="n">
-        <v>2.43172E9</v>
+        <v>2.43246E9</v>
       </c>
       <c r="AA143" s="14" t="inlineStr"/>
       <c r="AB143" s="14" t="inlineStr"/>
       <c r="AC143" s="15" t="n">
-        <v>0.9099549759911868</v>
+        <v>0.904383945461684</v>
       </c>
       <c r="AD143" s="15" t="inlineStr"/>
       <c r="AE143" s="14" t="n">
-        <v>2.40632E8</v>
+        <v>2.57172E8</v>
       </c>
       <c r="AF143" s="14" t="inlineStr"/>
       <c r="AG143" s="14" t="inlineStr"/>
@@ -8950,7 +8950,7 @@
       <c r="O144" s="13" t="inlineStr"/>
       <c r="P144" s="13" t="inlineStr"/>
       <c r="Q144" s="14" t="n">
-        <v>2.436E8</v>
+        <v>2.52E8</v>
       </c>
       <c r="R144" s="14" t="inlineStr"/>
       <c r="S144" s="14" t="n">
@@ -8972,11 +8972,11 @@
       <c r="AA144" s="14" t="inlineStr"/>
       <c r="AB144" s="14" t="inlineStr"/>
       <c r="AC144" s="15" t="n">
-        <v>0.9421469622331692</v>
+        <v>0.9107420634920635</v>
       </c>
       <c r="AD144" s="15" t="inlineStr"/>
       <c r="AE144" s="14" t="n">
-        <v>1.4093E7</v>
+        <v>2.2493E7</v>
       </c>
       <c r="AF144" s="14" t="inlineStr"/>
       <c r="AG144" s="14" t="inlineStr"/>
@@ -9050,7 +9050,7 @@
       <c r="O146" s="13" t="inlineStr"/>
       <c r="P146" s="13" t="inlineStr"/>
       <c r="Q146" s="14" t="n">
-        <v>1.9092E9</v>
+        <v>1.91808E9</v>
       </c>
       <c r="R146" s="14" t="inlineStr"/>
       <c r="S146" s="14" t="n">
@@ -9063,20 +9063,20 @@
         <v>1.581491E9</v>
       </c>
       <c r="X146" s="14" t="n">
-        <v>1.59359E8</v>
+        <v>1.60099E8</v>
       </c>
       <c r="Y146" s="14" t="inlineStr"/>
       <c r="Z146" s="14" t="n">
-        <v>1.74085E9</v>
+        <v>1.74159E9</v>
       </c>
       <c r="AA146" s="14" t="inlineStr"/>
       <c r="AB146" s="14" t="inlineStr"/>
       <c r="AC146" s="15" t="n">
-        <v>0.9118217054263565</v>
+        <v>0.9079861111111112</v>
       </c>
       <c r="AD146" s="15" t="inlineStr"/>
       <c r="AE146" s="14" t="n">
-        <v>1.6835E8</v>
+        <v>1.7649E8</v>
       </c>
       <c r="AF146" s="14" t="inlineStr"/>
       <c r="AG146" s="14" t="inlineStr"/>
@@ -9417,20 +9417,20 @@
         <v>2.475555828E10</v>
       </c>
       <c r="X152" s="14" t="n">
-        <v>3.526847916E9</v>
+        <v>3.536038216E9</v>
       </c>
       <c r="Y152" s="14" t="inlineStr"/>
       <c r="Z152" s="14" t="n">
-        <v>2.8282406196E10</v>
+        <v>2.8291596496E10</v>
       </c>
       <c r="AA152" s="14" t="inlineStr"/>
       <c r="AB152" s="14" t="inlineStr"/>
       <c r="AC152" s="15" t="n">
-        <v>0.9845818889385857</v>
+        <v>0.9849018264598561</v>
       </c>
       <c r="AD152" s="15" t="inlineStr"/>
       <c r="AE152" s="14" t="n">
-        <v>4.42889804E8</v>
+        <v>4.33699504E8</v>
       </c>
       <c r="AF152" s="14" t="inlineStr"/>
       <c r="AG152" s="14" t="inlineStr"/>
@@ -9474,20 +9474,20 @@
         <v>1.997827308E10</v>
       </c>
       <c r="X153" s="14" t="n">
-        <v>3.526847916E9</v>
+        <v>3.536038216E9</v>
       </c>
       <c r="Y153" s="14" t="inlineStr"/>
       <c r="Z153" s="14" t="n">
-        <v>2.3505120996E10</v>
+        <v>2.3514311296E10</v>
       </c>
       <c r="AA153" s="14" t="inlineStr"/>
       <c r="AB153" s="14" t="inlineStr"/>
       <c r="AC153" s="15" t="n">
-        <v>0.9815069670977007</v>
+        <v>0.9818907278739696</v>
       </c>
       <c r="AD153" s="15" t="inlineStr"/>
       <c r="AE153" s="14" t="n">
-        <v>4.42871004E8</v>
+        <v>4.33680704E8</v>
       </c>
       <c r="AF153" s="14" t="inlineStr"/>
       <c r="AG153" s="14" t="inlineStr"/>
@@ -9638,7 +9638,7 @@
       <c r="O156" s="13" t="inlineStr"/>
       <c r="P156" s="13" t="inlineStr"/>
       <c r="Q156" s="14" t="n">
-        <v>2.6949388E10</v>
+        <v>2.6949535E10</v>
       </c>
       <c r="R156" s="14" t="inlineStr"/>
       <c r="S156" s="14" t="n">
@@ -9660,11 +9660,11 @@
       <c r="AA156" s="14" t="inlineStr"/>
       <c r="AB156" s="14" t="inlineStr"/>
       <c r="AC156" s="15" t="n">
-        <v>0.9856281067310323</v>
+        <v>0.9856227304849602</v>
       </c>
       <c r="AD156" s="15" t="inlineStr"/>
       <c r="AE156" s="14" t="n">
-        <v>3.87313728E8</v>
+        <v>3.87460728E8</v>
       </c>
       <c r="AF156" s="14" t="inlineStr"/>
       <c r="AG156" s="14" t="inlineStr"/>
@@ -11148,7 +11148,7 @@
       <c r="O182" s="13" t="inlineStr"/>
       <c r="P182" s="13" t="inlineStr"/>
       <c r="Q182" s="14" t="n">
-        <v>1.78416E9</v>
+        <v>1.82808E9</v>
       </c>
       <c r="R182" s="14" t="inlineStr"/>
       <c r="S182" s="14" t="n">
@@ -11170,11 +11170,11 @@
       <c r="AA182" s="14" t="inlineStr"/>
       <c r="AB182" s="14" t="inlineStr"/>
       <c r="AC182" s="15" t="n">
-        <v>0.871901062684961</v>
+        <v>0.8509534593672049</v>
       </c>
       <c r="AD182" s="15" t="inlineStr"/>
       <c r="AE182" s="14" t="n">
-        <v>2.28549E8</v>
+        <v>2.72469E8</v>
       </c>
       <c r="AF182" s="14" t="inlineStr"/>
       <c r="AG182" s="14" t="inlineStr"/>
@@ -11205,7 +11205,7 @@
       <c r="O183" s="13" t="inlineStr"/>
       <c r="P183" s="13" t="inlineStr"/>
       <c r="Q183" s="14" t="n">
-        <v>1.68E8</v>
+        <v>1.764E8</v>
       </c>
       <c r="R183" s="14" t="inlineStr"/>
       <c r="S183" s="14" t="n">
@@ -11227,11 +11227,11 @@
       <c r="AA183" s="14" t="inlineStr"/>
       <c r="AB183" s="14" t="inlineStr"/>
       <c r="AC183" s="15" t="n">
-        <v>0.8766666666666667</v>
+        <v>0.834920634920635</v>
       </c>
       <c r="AD183" s="15" t="inlineStr"/>
       <c r="AE183" s="14" t="n">
-        <v>2.072E7</v>
+        <v>2.912E7</v>
       </c>
       <c r="AF183" s="14" t="inlineStr"/>
       <c r="AG183" s="14" t="inlineStr"/>
@@ -11262,7 +11262,7 @@
       <c r="O184" s="13" t="inlineStr"/>
       <c r="P184" s="13" t="inlineStr"/>
       <c r="Q184" s="14" t="n">
-        <v>1.61616E9</v>
+        <v>1.65168E9</v>
       </c>
       <c r="R184" s="14" t="inlineStr"/>
       <c r="S184" s="14" t="n">
@@ -11284,11 +11284,11 @@
       <c r="AA184" s="14" t="inlineStr"/>
       <c r="AB184" s="14" t="inlineStr"/>
       <c r="AC184" s="15" t="n">
-        <v>0.8714056776556777</v>
+        <v>0.852665770609319</v>
       </c>
       <c r="AD184" s="15" t="inlineStr"/>
       <c r="AE184" s="14" t="n">
-        <v>2.07829E8</v>
+        <v>2.43349E8</v>
       </c>
       <c r="AF184" s="14" t="inlineStr"/>
       <c r="AG184" s="14" t="inlineStr"/>
@@ -11325,7 +11325,7 @@
       <c r="O185" s="13" t="inlineStr"/>
       <c r="P185" s="13" t="inlineStr"/>
       <c r="Q185" s="14" t="n">
-        <v>1.3046454E10</v>
+        <v>1.3002681E10</v>
       </c>
       <c r="R185" s="14" t="inlineStr"/>
       <c r="S185" s="14" t="n">
@@ -11347,11 +11347,11 @@
       <c r="AA185" s="14" t="inlineStr"/>
       <c r="AB185" s="14" t="inlineStr"/>
       <c r="AC185" s="15" t="n">
-        <v>0.9923814588239839</v>
+        <v>0.9957222708916723</v>
       </c>
       <c r="AD185" s="15" t="inlineStr"/>
       <c r="AE185" s="14" t="n">
-        <v>9.9394947E7</v>
+        <v>5.5621947E7</v>
       </c>
       <c r="AF185" s="14" t="inlineStr"/>
       <c r="AG185" s="14" t="inlineStr"/>
@@ -11382,7 +11382,7 @@
       <c r="O186" s="13" t="inlineStr"/>
       <c r="P186" s="13" t="inlineStr"/>
       <c r="Q186" s="14" t="n">
-        <v>1.1472E10</v>
+        <v>1.1428224E10</v>
       </c>
       <c r="R186" s="14" t="inlineStr"/>
       <c r="S186" s="14" t="n">
@@ -11404,11 +11404,11 @@
       <c r="AA186" s="14" t="inlineStr"/>
       <c r="AB186" s="14" t="inlineStr"/>
       <c r="AC186" s="15" t="n">
-        <v>0.9913367919281729</v>
+        <v>0.995134123814864</v>
       </c>
       <c r="AD186" s="15" t="inlineStr"/>
       <c r="AE186" s="14" t="n">
-        <v>9.9384323E7</v>
+        <v>5.5608323E7</v>
       </c>
       <c r="AF186" s="14" t="inlineStr"/>
       <c r="AG186" s="14" t="inlineStr"/>
@@ -11496,7 +11496,7 @@
       <c r="O188" s="13" t="inlineStr"/>
       <c r="P188" s="13" t="inlineStr"/>
       <c r="Q188" s="14" t="n">
-        <v>7.89135E8</v>
+        <v>7.89138E8</v>
       </c>
       <c r="R188" s="14" t="inlineStr"/>
       <c r="S188" s="14" t="n">
@@ -11518,11 +11518,11 @@
       <c r="AA188" s="14" t="inlineStr"/>
       <c r="AB188" s="14" t="inlineStr"/>
       <c r="AC188" s="15" t="n">
-        <v>0.9999994703060946</v>
+        <v>0.999995668691661</v>
       </c>
       <c r="AD188" s="15" t="inlineStr"/>
       <c r="AE188" s="14" t="n">
-        <v>418.0</v>
+        <v>3418.0</v>
       </c>
       <c r="AF188" s="14" t="inlineStr"/>
       <c r="AG188" s="14" t="inlineStr"/>
@@ -11572,20 +11572,20 @@
         <v>6.228754056E9</v>
       </c>
       <c r="X189" s="25" t="n">
-        <v>2.27165485E8</v>
+        <v>5.99870547E8</v>
       </c>
       <c r="Y189" s="25" t="inlineStr"/>
       <c r="Z189" s="25" t="n">
-        <v>6.455919541E9</v>
+        <v>6.828624603E9</v>
       </c>
       <c r="AA189" s="25" t="inlineStr"/>
       <c r="AB189" s="25" t="inlineStr"/>
       <c r="AC189" s="26" t="n">
-        <v>0.9293391894235967</v>
+        <v>0.9829906356681544</v>
       </c>
       <c r="AD189" s="26" t="inlineStr"/>
       <c r="AE189" s="25" t="n">
-        <v>4.90865459E8</v>
+        <v>1.18160397E8</v>
       </c>
       <c r="AF189" s="25" t="inlineStr"/>
       <c r="AG189" s="25" t="inlineStr"/>
@@ -11622,7 +11622,7 @@
       <c r="O190" s="13" t="inlineStr"/>
       <c r="P190" s="13" t="inlineStr"/>
       <c r="Q190" s="14" t="n">
-        <v>5.006041E9</v>
+        <v>5.008716E9</v>
       </c>
       <c r="R190" s="14" t="inlineStr"/>
       <c r="S190" s="14" t="n">
@@ -11635,20 +11635,20 @@
         <v>4.783558496E9</v>
       </c>
       <c r="X190" s="14" t="n">
-        <v>1.31977006E8</v>
+        <v>1.9710595E8</v>
       </c>
       <c r="Y190" s="14" t="inlineStr"/>
       <c r="Z190" s="14" t="n">
-        <v>4.915535502E9</v>
+        <v>4.980664446E9</v>
       </c>
       <c r="AA190" s="14" t="inlineStr"/>
       <c r="AB190" s="14" t="inlineStr"/>
       <c r="AC190" s="15" t="n">
-        <v>0.9819207437573924</v>
+        <v>0.9943994520751426</v>
       </c>
       <c r="AD190" s="15" t="inlineStr"/>
       <c r="AE190" s="14" t="n">
-        <v>9.0505498E7</v>
+        <v>2.8051554E7</v>
       </c>
       <c r="AF190" s="14" t="inlineStr"/>
       <c r="AG190" s="14" t="inlineStr"/>
@@ -11685,7 +11685,7 @@
       <c r="O191" s="13" t="inlineStr"/>
       <c r="P191" s="13" t="inlineStr"/>
       <c r="Q191" s="14" t="n">
-        <v>1.890817E9</v>
+        <v>1.892887E9</v>
       </c>
       <c r="R191" s="14" t="inlineStr"/>
       <c r="S191" s="14" t="n">
@@ -11698,20 +11698,20 @@
         <v>1.777909494E9</v>
       </c>
       <c r="X191" s="14" t="n">
-        <v>9.3544738E7</v>
+        <v>1.07421314E8</v>
       </c>
       <c r="Y191" s="14" t="inlineStr"/>
       <c r="Z191" s="14" t="n">
-        <v>1.871454232E9</v>
+        <v>1.885330808E9</v>
       </c>
       <c r="AA191" s="14" t="inlineStr"/>
       <c r="AB191" s="14" t="inlineStr"/>
       <c r="AC191" s="15" t="n">
-        <v>0.9897595758870372</v>
+        <v>0.9960081124758108</v>
       </c>
       <c r="AD191" s="15" t="inlineStr"/>
       <c r="AE191" s="14" t="n">
-        <v>1.9362768E7</v>
+        <v>7556192.0</v>
       </c>
       <c r="AF191" s="14" t="inlineStr"/>
       <c r="AG191" s="14" t="inlineStr"/>
@@ -11856,7 +11856,7 @@
       <c r="O194" s="13" t="inlineStr"/>
       <c r="P194" s="13" t="inlineStr"/>
       <c r="Q194" s="14" t="n">
-        <v>9.393E7</v>
+        <v>9.6E7</v>
       </c>
       <c r="R194" s="14" t="inlineStr"/>
       <c r="S194" s="14" t="n">
@@ -11869,20 +11869,20 @@
         <v>5.5184254E7</v>
       </c>
       <c r="X194" s="14" t="n">
-        <v>1.9543138E7</v>
+        <v>3.3419714E7</v>
       </c>
       <c r="Y194" s="14" t="inlineStr"/>
       <c r="Z194" s="14" t="n">
-        <v>7.4727392E7</v>
+        <v>8.8603968E7</v>
       </c>
       <c r="AA194" s="14" t="inlineStr"/>
       <c r="AB194" s="14" t="inlineStr"/>
       <c r="AC194" s="15" t="n">
-        <v>0.7955646971148728</v>
+        <v>0.922958</v>
       </c>
       <c r="AD194" s="15" t="inlineStr"/>
       <c r="AE194" s="14" t="n">
-        <v>1.9202608E7</v>
+        <v>7396032.0</v>
       </c>
       <c r="AF194" s="14" t="inlineStr"/>
       <c r="AG194" s="14" t="inlineStr"/>
@@ -12304,7 +12304,7 @@
       <c r="O202" s="13" t="inlineStr"/>
       <c r="P202" s="13" t="inlineStr"/>
       <c r="Q202" s="14" t="n">
-        <v>1.23E7</v>
+        <v>1.488E7</v>
       </c>
       <c r="R202" s="14" t="inlineStr"/>
       <c r="S202" s="14" t="n">
@@ -12317,20 +12317,20 @@
         <v>9417000.0</v>
       </c>
       <c r="X202" s="14" t="n">
-        <v>1380500.0</v>
+        <v>3215000.0</v>
       </c>
       <c r="Y202" s="14" t="inlineStr"/>
       <c r="Z202" s="14" t="n">
-        <v>1.07975E7</v>
+        <v>1.2632E7</v>
       </c>
       <c r="AA202" s="14" t="inlineStr"/>
       <c r="AB202" s="14" t="inlineStr"/>
       <c r="AC202" s="15" t="n">
-        <v>0.8778455284552845</v>
+        <v>0.8489247311827957</v>
       </c>
       <c r="AD202" s="15" t="inlineStr"/>
       <c r="AE202" s="14" t="n">
-        <v>1502500.0</v>
+        <v>2248000.0</v>
       </c>
       <c r="AF202" s="14" t="inlineStr"/>
       <c r="AG202" s="14" t="inlineStr"/>
@@ -12361,7 +12361,7 @@
       <c r="O203" s="13" t="inlineStr"/>
       <c r="P203" s="13" t="inlineStr"/>
       <c r="Q203" s="14" t="n">
-        <v>7800000.0</v>
+        <v>1.038E7</v>
       </c>
       <c r="R203" s="14" t="inlineStr"/>
       <c r="S203" s="14" t="n">
@@ -12374,20 +12374,20 @@
         <v>5781000.0</v>
       </c>
       <c r="X203" s="14" t="n">
-        <v>1380500.0</v>
+        <v>2407000.0</v>
       </c>
       <c r="Y203" s="14" t="inlineStr"/>
       <c r="Z203" s="14" t="n">
-        <v>7161500.0</v>
+        <v>8188000.0</v>
       </c>
       <c r="AA203" s="14" t="inlineStr"/>
       <c r="AB203" s="14" t="inlineStr"/>
       <c r="AC203" s="15" t="n">
-        <v>0.9181410256410256</v>
+        <v>0.7888246628131022</v>
       </c>
       <c r="AD203" s="15" t="inlineStr"/>
       <c r="AE203" s="14" t="n">
-        <v>638500.0</v>
+        <v>2192000.0</v>
       </c>
       <c r="AF203" s="14" t="inlineStr"/>
       <c r="AG203" s="14" t="inlineStr"/>
@@ -12431,20 +12431,20 @@
         <v>3636000.0</v>
       </c>
       <c r="X204" s="14" t="n">
-        <v>0.0</v>
+        <v>808000.0</v>
       </c>
       <c r="Y204" s="14" t="inlineStr"/>
       <c r="Z204" s="14" t="n">
-        <v>3636000.0</v>
+        <v>4444000.0</v>
       </c>
       <c r="AA204" s="14" t="inlineStr"/>
       <c r="AB204" s="14" t="inlineStr"/>
       <c r="AC204" s="15" t="n">
-        <v>0.808</v>
+        <v>0.9875555555555555</v>
       </c>
       <c r="AD204" s="15" t="inlineStr"/>
       <c r="AE204" s="14" t="n">
-        <v>864000.0</v>
+        <v>56000.0</v>
       </c>
       <c r="AF204" s="14" t="inlineStr"/>
       <c r="AG204" s="14" t="inlineStr"/>
@@ -12481,7 +12481,7 @@
       <c r="O205" s="13" t="inlineStr"/>
       <c r="P205" s="13" t="inlineStr"/>
       <c r="Q205" s="14" t="n">
-        <v>8.0556E7</v>
+        <v>7.8581E7</v>
       </c>
       <c r="R205" s="14" t="inlineStr"/>
       <c r="S205" s="14" t="n">
@@ -12494,20 +12494,20 @@
         <v>5.526601E7</v>
       </c>
       <c r="X205" s="14" t="n">
-        <v>0.0</v>
+        <v>1.23661E7</v>
       </c>
       <c r="Y205" s="14" t="inlineStr"/>
       <c r="Z205" s="14" t="n">
-        <v>5.526601E7</v>
+        <v>6.763211E7</v>
       </c>
       <c r="AA205" s="14" t="inlineStr"/>
       <c r="AB205" s="14" t="inlineStr"/>
       <c r="AC205" s="15" t="n">
-        <v>0.6860570286508764</v>
+        <v>0.8606674641452768</v>
       </c>
       <c r="AD205" s="15" t="inlineStr"/>
       <c r="AE205" s="14" t="n">
-        <v>2.528999E7</v>
+        <v>1.094889E7</v>
       </c>
       <c r="AF205" s="14" t="inlineStr"/>
       <c r="AG205" s="14" t="inlineStr"/>
@@ -12538,7 +12538,7 @@
       <c r="O206" s="13" t="inlineStr"/>
       <c r="P206" s="13" t="inlineStr"/>
       <c r="Q206" s="14" t="n">
-        <v>7.4476E7</v>
+        <v>7.2501E7</v>
       </c>
       <c r="R206" s="14" t="inlineStr"/>
       <c r="S206" s="14" t="n">
@@ -12551,20 +12551,20 @@
         <v>5.526601E7</v>
       </c>
       <c r="X206" s="14" t="n">
-        <v>0.0</v>
+        <v>9616100.0</v>
       </c>
       <c r="Y206" s="14" t="inlineStr"/>
       <c r="Z206" s="14" t="n">
-        <v>5.526601E7</v>
+        <v>6.488211E7</v>
       </c>
       <c r="AA206" s="14" t="inlineStr"/>
       <c r="AB206" s="14" t="inlineStr"/>
       <c r="AC206" s="15" t="n">
-        <v>0.7420646919813094</v>
+        <v>0.8949133115405304</v>
       </c>
       <c r="AD206" s="15" t="inlineStr"/>
       <c r="AE206" s="14" t="n">
-        <v>1.920999E7</v>
+        <v>7618890.0</v>
       </c>
       <c r="AF206" s="14" t="inlineStr"/>
       <c r="AG206" s="14" t="inlineStr"/>
@@ -12608,20 +12608,20 @@
         <v>0.0</v>
       </c>
       <c r="X207" s="14" t="n">
-        <v>0.0</v>
+        <v>2750000.0</v>
       </c>
       <c r="Y207" s="14" t="inlineStr"/>
       <c r="Z207" s="14" t="n">
-        <v>0.0</v>
+        <v>2750000.0</v>
       </c>
       <c r="AA207" s="14" t="inlineStr"/>
       <c r="AB207" s="14" t="inlineStr"/>
       <c r="AC207" s="15" t="n">
-        <v>0.0</v>
+        <v>0.45230263157894735</v>
       </c>
       <c r="AD207" s="15" t="inlineStr"/>
       <c r="AE207" s="14" t="n">
-        <v>6080000.0</v>
+        <v>3330000.0</v>
       </c>
       <c r="AF207" s="14" t="inlineStr"/>
       <c r="AG207" s="14" t="inlineStr"/>
@@ -12848,20 +12848,20 @@
         <v>2.936691192E9</v>
       </c>
       <c r="X211" s="14" t="n">
-        <v>3.7051768E7</v>
+        <v>7.4103536E7</v>
       </c>
       <c r="Y211" s="14" t="inlineStr"/>
       <c r="Z211" s="14" t="n">
-        <v>2.97374296E9</v>
+        <v>3.010794728E9</v>
       </c>
       <c r="AA211" s="14" t="inlineStr"/>
       <c r="AB211" s="14" t="inlineStr"/>
       <c r="AC211" s="15" t="n">
-        <v>0.987505665199338</v>
+        <v>0.9998096307060446</v>
       </c>
       <c r="AD211" s="15" t="inlineStr"/>
       <c r="AE211" s="14" t="n">
-        <v>3.762504E7</v>
+        <v>573272.0</v>
       </c>
       <c r="AF211" s="14" t="inlineStr"/>
       <c r="AG211" s="14" t="inlineStr"/>
@@ -12962,20 +12962,20 @@
         <v>1.0331888E8</v>
       </c>
       <c r="X213" s="14" t="n">
-        <v>9468528.0</v>
+        <v>1.8937056E7</v>
       </c>
       <c r="Y213" s="14" t="inlineStr"/>
       <c r="Z213" s="14" t="n">
-        <v>1.12787408E8</v>
+        <v>1.22255936E8</v>
       </c>
       <c r="AA213" s="14" t="inlineStr"/>
       <c r="AB213" s="14" t="inlineStr"/>
       <c r="AC213" s="15" t="n">
-        <v>0.9199625448613377</v>
+        <v>0.9971936052202284</v>
       </c>
       <c r="AD213" s="15" t="inlineStr"/>
       <c r="AE213" s="14" t="n">
-        <v>9812592.0</v>
+        <v>344064.0</v>
       </c>
       <c r="AF213" s="14" t="inlineStr"/>
       <c r="AG213" s="14" t="inlineStr"/>
@@ -13190,20 +13190,20 @@
         <v>2.2953312E7</v>
       </c>
       <c r="X217" s="14" t="n">
-        <v>2.2953312E7</v>
+        <v>4.5906624E7</v>
       </c>
       <c r="Y217" s="14" t="inlineStr"/>
       <c r="Z217" s="14" t="n">
-        <v>4.5906624E7</v>
+        <v>6.8859936E7</v>
       </c>
       <c r="AA217" s="14" t="inlineStr"/>
       <c r="AB217" s="14" t="inlineStr"/>
       <c r="AC217" s="15" t="n">
-        <v>0.6662790130624093</v>
+        <v>0.9994185195936139</v>
       </c>
       <c r="AD217" s="15" t="inlineStr"/>
       <c r="AE217" s="14" t="n">
-        <v>2.2993376E7</v>
+        <v>40064.0</v>
       </c>
       <c r="AF217" s="14" t="inlineStr"/>
       <c r="AG217" s="14" t="inlineStr"/>
@@ -13247,20 +13247,20 @@
         <v>4629928.0</v>
       </c>
       <c r="X218" s="14" t="n">
-        <v>4629928.0</v>
+        <v>9259856.0</v>
       </c>
       <c r="Y218" s="14" t="inlineStr"/>
       <c r="Z218" s="14" t="n">
-        <v>9259856.0</v>
+        <v>1.3889784E7</v>
       </c>
       <c r="AA218" s="14" t="inlineStr"/>
       <c r="AB218" s="14" t="inlineStr"/>
       <c r="AC218" s="15" t="n">
-        <v>0.6666562994960403</v>
+        <v>0.9999844492440605</v>
       </c>
       <c r="AD218" s="15" t="inlineStr"/>
       <c r="AE218" s="14" t="n">
-        <v>4630144.0</v>
+        <v>216.0</v>
       </c>
       <c r="AF218" s="14" t="inlineStr"/>
       <c r="AG218" s="14" t="inlineStr"/>
@@ -13297,7 +13297,7 @@
       <c r="O219" s="13" t="inlineStr"/>
       <c r="P219" s="13" t="inlineStr"/>
       <c r="Q219" s="14" t="n">
-        <v>7.00144E8</v>
+        <v>6.92704E8</v>
       </c>
       <c r="R219" s="14" t="inlineStr"/>
       <c r="S219" s="14" t="n">
@@ -13310,20 +13310,20 @@
         <v>6.39842407E8</v>
       </c>
       <c r="X219" s="14" t="n">
-        <v>4.9005042E7</v>
+        <v>5.2026307E7</v>
       </c>
       <c r="Y219" s="14" t="inlineStr"/>
       <c r="Z219" s="14" t="n">
-        <v>6.88847449E8</v>
+        <v>6.91868714E8</v>
       </c>
       <c r="AA219" s="14" t="inlineStr"/>
       <c r="AB219" s="14" t="inlineStr"/>
       <c r="AC219" s="15" t="n">
-        <v>0.9838653891199525</v>
+        <v>0.9987941660507229</v>
       </c>
       <c r="AD219" s="15" t="inlineStr"/>
       <c r="AE219" s="14" t="n">
-        <v>1.1296551E7</v>
+        <v>835286.0</v>
       </c>
       <c r="AF219" s="14" t="inlineStr"/>
       <c r="AG219" s="14" t="inlineStr"/>
@@ -13360,7 +13360,7 @@
       <c r="O220" s="13" t="inlineStr"/>
       <c r="P220" s="13" t="inlineStr"/>
       <c r="Q220" s="14" t="n">
-        <v>5.16E8</v>
+        <v>5.0946E8</v>
       </c>
       <c r="R220" s="14" t="inlineStr"/>
       <c r="S220" s="14" t="n">
@@ -13382,11 +13382,11 @@
       <c r="AA220" s="14" t="inlineStr"/>
       <c r="AB220" s="14" t="inlineStr"/>
       <c r="AC220" s="15" t="n">
-        <v>0.9872100562015503</v>
+        <v>0.9998829917952342</v>
       </c>
       <c r="AD220" s="15" t="inlineStr"/>
       <c r="AE220" s="14" t="n">
-        <v>6599611.0</v>
+        <v>59611.0</v>
       </c>
       <c r="AF220" s="14" t="inlineStr"/>
       <c r="AG220" s="14" t="inlineStr"/>
@@ -13417,7 +13417,7 @@
       <c r="O221" s="13" t="inlineStr"/>
       <c r="P221" s="13" t="inlineStr"/>
       <c r="Q221" s="14" t="n">
-        <v>5.16E8</v>
+        <v>5.0946E8</v>
       </c>
       <c r="R221" s="14" t="inlineStr"/>
       <c r="S221" s="14" t="n">
@@ -13439,11 +13439,11 @@
       <c r="AA221" s="14" t="inlineStr"/>
       <c r="AB221" s="14" t="inlineStr"/>
       <c r="AC221" s="15" t="n">
-        <v>0.9872100562015503</v>
+        <v>0.9998829917952342</v>
       </c>
       <c r="AD221" s="15" t="inlineStr"/>
       <c r="AE221" s="14" t="n">
-        <v>6599611.0</v>
+        <v>59611.0</v>
       </c>
       <c r="AF221" s="14" t="inlineStr"/>
       <c r="AG221" s="14" t="inlineStr"/>
@@ -13600,7 +13600,7 @@
       <c r="O224" s="13" t="inlineStr"/>
       <c r="P224" s="13" t="inlineStr"/>
       <c r="Q224" s="14" t="n">
-        <v>3.3444E7</v>
+        <v>3.2544E7</v>
       </c>
       <c r="R224" s="14" t="inlineStr"/>
       <c r="S224" s="14" t="n">
@@ -13613,20 +13613,20 @@
         <v>3.08218E7</v>
       </c>
       <c r="X224" s="14" t="n">
-        <v>604300.0</v>
+        <v>1639100.0</v>
       </c>
       <c r="Y224" s="14" t="inlineStr"/>
       <c r="Z224" s="14" t="n">
-        <v>3.14261E7</v>
+        <v>3.24609E7</v>
       </c>
       <c r="AA224" s="14" t="inlineStr"/>
       <c r="AB224" s="14" t="inlineStr"/>
       <c r="AC224" s="15" t="n">
-        <v>0.9396633177849539</v>
+        <v>0.9974465339233038</v>
       </c>
       <c r="AD224" s="15" t="inlineStr"/>
       <c r="AE224" s="14" t="n">
-        <v>2017900.0</v>
+        <v>83100.0</v>
       </c>
       <c r="AF224" s="14" t="inlineStr"/>
       <c r="AG224" s="14" t="inlineStr"/>
@@ -13657,7 +13657,7 @@
       <c r="O225" s="13" t="inlineStr"/>
       <c r="P225" s="13" t="inlineStr"/>
       <c r="Q225" s="14" t="n">
-        <v>3.3444E7</v>
+        <v>3.2544E7</v>
       </c>
       <c r="R225" s="14" t="inlineStr"/>
       <c r="S225" s="14" t="n">
@@ -13670,20 +13670,20 @@
         <v>3.08218E7</v>
       </c>
       <c r="X225" s="14" t="n">
-        <v>604300.0</v>
+        <v>1639100.0</v>
       </c>
       <c r="Y225" s="14" t="inlineStr"/>
       <c r="Z225" s="14" t="n">
-        <v>3.14261E7</v>
+        <v>3.24609E7</v>
       </c>
       <c r="AA225" s="14" t="inlineStr"/>
       <c r="AB225" s="14" t="inlineStr"/>
       <c r="AC225" s="15" t="n">
-        <v>0.9396633177849539</v>
+        <v>0.9974465339233038</v>
       </c>
       <c r="AD225" s="15" t="inlineStr"/>
       <c r="AE225" s="14" t="n">
-        <v>2017900.0</v>
+        <v>83100.0</v>
       </c>
       <c r="AF225" s="14" t="inlineStr"/>
       <c r="AG225" s="14" t="inlineStr"/>
@@ -13733,20 +13733,20 @@
         <v>1.33021464E8</v>
       </c>
       <c r="X226" s="14" t="n">
-        <v>9250750.0</v>
+        <v>1.1237215E7</v>
       </c>
       <c r="Y226" s="14" t="inlineStr"/>
       <c r="Z226" s="14" t="n">
-        <v>1.42272214E8</v>
+        <v>1.44258679E8</v>
       </c>
       <c r="AA226" s="14" t="inlineStr"/>
       <c r="AB226" s="14" t="inlineStr"/>
       <c r="AC226" s="15" t="n">
-        <v>0.9832219350380097</v>
+        <v>0.9969500967519005</v>
       </c>
       <c r="AD226" s="15" t="inlineStr"/>
       <c r="AE226" s="14" t="n">
-        <v>2427786.0</v>
+        <v>441321.0</v>
       </c>
       <c r="AF226" s="14" t="inlineStr"/>
       <c r="AG226" s="14" t="inlineStr"/>
@@ -13820,7 +13820,7 @@
       <c r="O228" s="13" t="inlineStr"/>
       <c r="P228" s="13" t="inlineStr"/>
       <c r="Q228" s="14" t="n">
-        <v>1.146E8</v>
+        <v>1.1508E8</v>
       </c>
       <c r="R228" s="14" t="inlineStr"/>
       <c r="S228" s="14" t="n">
@@ -13833,20 +13833,20 @@
         <v>1.044355E8</v>
       </c>
       <c r="X228" s="14" t="n">
-        <v>9250750.0</v>
+        <v>1.029815E7</v>
       </c>
       <c r="Y228" s="14" t="inlineStr"/>
       <c r="Z228" s="14" t="n">
-        <v>1.1368625E8</v>
+        <v>1.1473365E8</v>
       </c>
       <c r="AA228" s="14" t="inlineStr"/>
       <c r="AB228" s="14" t="inlineStr"/>
       <c r="AC228" s="15" t="n">
-        <v>0.9920266143106458</v>
+        <v>0.996990354535975</v>
       </c>
       <c r="AD228" s="15" t="inlineStr"/>
       <c r="AE228" s="14" t="n">
-        <v>913750.0</v>
+        <v>346350.0</v>
       </c>
       <c r="AF228" s="14" t="inlineStr"/>
       <c r="AG228" s="14" t="inlineStr"/>
@@ -13877,7 +13877,7 @@
       <c r="O229" s="13" t="inlineStr"/>
       <c r="P229" s="13" t="inlineStr"/>
       <c r="Q229" s="14" t="n">
-        <v>3.01E7</v>
+        <v>2.962E7</v>
       </c>
       <c r="R229" s="14" t="inlineStr"/>
       <c r="S229" s="14" t="n">
@@ -13890,20 +13890,20 @@
         <v>2.8585964E7</v>
       </c>
       <c r="X229" s="14" t="n">
-        <v>0.0</v>
+        <v>939065.0</v>
       </c>
       <c r="Y229" s="14" t="inlineStr"/>
       <c r="Z229" s="14" t="n">
-        <v>2.8585964E7</v>
+        <v>2.9525029E7</v>
       </c>
       <c r="AA229" s="14" t="inlineStr"/>
       <c r="AB229" s="14" t="inlineStr"/>
       <c r="AC229" s="15" t="n">
-        <v>0.9496998006644518</v>
+        <v>0.9967936866981769</v>
       </c>
       <c r="AD229" s="15" t="inlineStr"/>
       <c r="AE229" s="14" t="n">
-        <v>1514036.0</v>
+        <v>94971.0</v>
       </c>
       <c r="AF229" s="14" t="inlineStr"/>
       <c r="AG229" s="14" t="inlineStr"/>
@@ -13940,7 +13940,7 @@
       <c r="O230" s="13" t="inlineStr"/>
       <c r="P230" s="13" t="inlineStr"/>
       <c r="Q230" s="14" t="n">
-        <v>1.10842E9</v>
+        <v>1.093185E9</v>
       </c>
       <c r="R230" s="14" t="inlineStr"/>
       <c r="S230" s="14" t="n">
@@ -13953,20 +13953,20 @@
         <v>6.74613153E8</v>
       </c>
       <c r="X230" s="14" t="n">
-        <v>4.5703437E7</v>
+        <v>3.2949829E8</v>
       </c>
       <c r="Y230" s="14" t="inlineStr"/>
       <c r="Z230" s="14" t="n">
-        <v>7.2031659E8</v>
+        <v>1.004111443E9</v>
       </c>
       <c r="AA230" s="14" t="inlineStr"/>
       <c r="AB230" s="14" t="inlineStr"/>
       <c r="AC230" s="15" t="n">
-        <v>0.6498588892297144</v>
+        <v>0.9185192286758417</v>
       </c>
       <c r="AD230" s="15" t="inlineStr"/>
       <c r="AE230" s="14" t="n">
-        <v>3.8810341E8</v>
+        <v>8.9073557E7</v>
       </c>
       <c r="AF230" s="14" t="inlineStr"/>
       <c r="AG230" s="14" t="inlineStr"/>
@@ -14016,20 +14016,20 @@
         <v>2.179125E8</v>
       </c>
       <c r="X231" s="14" t="n">
-        <v>0.0</v>
+        <v>2.2065E7</v>
       </c>
       <c r="Y231" s="14" t="inlineStr"/>
       <c r="Z231" s="14" t="n">
-        <v>2.179125E8</v>
+        <v>2.399775E8</v>
       </c>
       <c r="AA231" s="14" t="inlineStr"/>
       <c r="AB231" s="14" t="inlineStr"/>
       <c r="AC231" s="15" t="n">
-        <v>0.90796875</v>
+        <v>0.99990625</v>
       </c>
       <c r="AD231" s="15" t="inlineStr"/>
       <c r="AE231" s="14" t="n">
-        <v>2.20875E7</v>
+        <v>22500.0</v>
       </c>
       <c r="AF231" s="14" t="inlineStr"/>
       <c r="AG231" s="14" t="inlineStr"/>
@@ -14073,20 +14073,20 @@
         <v>1.67915E8</v>
       </c>
       <c r="X232" s="14" t="n">
-        <v>0.0</v>
+        <v>1.2065E7</v>
       </c>
       <c r="Y232" s="14" t="inlineStr"/>
       <c r="Z232" s="14" t="n">
-        <v>1.67915E8</v>
+        <v>1.7998E8</v>
       </c>
       <c r="AA232" s="14" t="inlineStr"/>
       <c r="AB232" s="14" t="inlineStr"/>
       <c r="AC232" s="15" t="n">
-        <v>0.9328611111111111</v>
+        <v>0.9998888888888889</v>
       </c>
       <c r="AD232" s="15" t="inlineStr"/>
       <c r="AE232" s="14" t="n">
-        <v>1.2085E7</v>
+        <v>20000.0</v>
       </c>
       <c r="AF232" s="14" t="inlineStr"/>
       <c r="AG232" s="14" t="inlineStr"/>
@@ -14130,20 +14130,20 @@
         <v>4.99975E7</v>
       </c>
       <c r="X233" s="14" t="n">
-        <v>0.0</v>
+        <v>1.0E7</v>
       </c>
       <c r="Y233" s="14" t="inlineStr"/>
       <c r="Z233" s="14" t="n">
-        <v>4.99975E7</v>
+        <v>5.99975E7</v>
       </c>
       <c r="AA233" s="14" t="inlineStr"/>
       <c r="AB233" s="14" t="inlineStr"/>
       <c r="AC233" s="15" t="n">
-        <v>0.8332916666666667</v>
+        <v>0.9999583333333333</v>
       </c>
       <c r="AD233" s="15" t="inlineStr"/>
       <c r="AE233" s="14" t="n">
-        <v>1.00025E7</v>
+        <v>2500.0</v>
       </c>
       <c r="AF233" s="14" t="inlineStr"/>
       <c r="AG233" s="14" t="inlineStr"/>
@@ -14300,7 +14300,7 @@
       <c r="O236" s="13" t="inlineStr"/>
       <c r="P236" s="13" t="inlineStr"/>
       <c r="Q236" s="14" t="n">
-        <v>3.5259E8</v>
+        <v>3.47E8</v>
       </c>
       <c r="R236" s="14" t="inlineStr"/>
       <c r="S236" s="14" t="n">
@@ -14313,20 +14313,20 @@
         <v>1.34221533E8</v>
       </c>
       <c r="X236" s="14" t="n">
-        <v>2.5076E7</v>
+        <v>1.508445E8</v>
       </c>
       <c r="Y236" s="14" t="inlineStr"/>
       <c r="Z236" s="14" t="n">
-        <v>1.59297533E8</v>
+        <v>2.85066033E8</v>
       </c>
       <c r="AA236" s="14" t="inlineStr"/>
       <c r="AB236" s="14" t="inlineStr"/>
       <c r="AC236" s="15" t="n">
-        <v>0.4517925437476956</v>
+        <v>0.8215159452449567</v>
       </c>
       <c r="AD236" s="15" t="inlineStr"/>
       <c r="AE236" s="14" t="n">
-        <v>1.93292467E8</v>
+        <v>6.1933967E7</v>
       </c>
       <c r="AF236" s="14" t="inlineStr"/>
       <c r="AG236" s="14" t="inlineStr"/>
@@ -14427,20 +14427,20 @@
         <v>2.1347299E7</v>
       </c>
       <c r="X238" s="14" t="n">
-        <v>0.0</v>
+        <v>1.47355E7</v>
       </c>
       <c r="Y238" s="14" t="inlineStr"/>
       <c r="Z238" s="14" t="n">
-        <v>2.1347299E7</v>
+        <v>3.6082799E7</v>
       </c>
       <c r="AA238" s="14" t="inlineStr"/>
       <c r="AB238" s="14" t="inlineStr"/>
       <c r="AC238" s="15" t="n">
-        <v>0.5723136461126005</v>
+        <v>0.9673672654155496</v>
       </c>
       <c r="AD238" s="15" t="inlineStr"/>
       <c r="AE238" s="14" t="n">
-        <v>1.5952701E7</v>
+        <v>1217201.0</v>
       </c>
       <c r="AF238" s="14" t="inlineStr"/>
       <c r="AG238" s="14" t="inlineStr"/>
@@ -14484,20 +14484,20 @@
         <v>2.5327E7</v>
       </c>
       <c r="X239" s="14" t="n">
-        <v>0.0</v>
+        <v>375000.0</v>
       </c>
       <c r="Y239" s="14" t="inlineStr"/>
       <c r="Z239" s="14" t="n">
-        <v>2.5327E7</v>
+        <v>2.5702E7</v>
       </c>
       <c r="AA239" s="14" t="inlineStr"/>
       <c r="AB239" s="14" t="inlineStr"/>
       <c r="AC239" s="15" t="n">
-        <v>0.9759922928709056</v>
+        <v>0.9904431599229288</v>
       </c>
       <c r="AD239" s="15" t="inlineStr"/>
       <c r="AE239" s="14" t="n">
-        <v>623000.0</v>
+        <v>248000.0</v>
       </c>
       <c r="AF239" s="14" t="inlineStr"/>
       <c r="AG239" s="14" t="inlineStr"/>
@@ -14585,7 +14585,7 @@
       <c r="O241" s="13" t="inlineStr"/>
       <c r="P241" s="13" t="inlineStr"/>
       <c r="Q241" s="14" t="n">
-        <v>1.156E8</v>
+        <v>1.236E8</v>
       </c>
       <c r="R241" s="14" t="inlineStr"/>
       <c r="S241" s="14" t="n">
@@ -14598,20 +14598,20 @@
         <v>4421000.0</v>
       </c>
       <c r="X241" s="14" t="n">
-        <v>2.5076E7</v>
+        <v>7.4724E7</v>
       </c>
       <c r="Y241" s="14" t="inlineStr"/>
       <c r="Z241" s="14" t="n">
-        <v>2.9497E7</v>
+        <v>7.9145E7</v>
       </c>
       <c r="AA241" s="14" t="inlineStr"/>
       <c r="AB241" s="14" t="inlineStr"/>
       <c r="AC241" s="15" t="n">
-        <v>0.2551643598615917</v>
+        <v>0.640331715210356</v>
       </c>
       <c r="AD241" s="15" t="inlineStr"/>
       <c r="AE241" s="14" t="n">
-        <v>8.6103E7</v>
+        <v>4.4455E7</v>
       </c>
       <c r="AF241" s="14" t="inlineStr"/>
       <c r="AG241" s="14" t="inlineStr"/>
@@ -14642,7 +14642,7 @@
       <c r="O242" s="13" t="inlineStr"/>
       <c r="P242" s="13" t="inlineStr"/>
       <c r="Q242" s="14" t="n">
-        <v>2800000.0</v>
+        <v>1400000.0</v>
       </c>
       <c r="R242" s="14" t="inlineStr"/>
       <c r="S242" s="14" t="n">
@@ -14664,11 +14664,11 @@
       <c r="AA242" s="14" t="inlineStr"/>
       <c r="AB242" s="14" t="inlineStr"/>
       <c r="AC242" s="15" t="n">
-        <v>0.4857142857142857</v>
+        <v>0.9714285714285714</v>
       </c>
       <c r="AD242" s="15" t="inlineStr"/>
       <c r="AE242" s="14" t="n">
-        <v>1440000.0</v>
+        <v>40000.0</v>
       </c>
       <c r="AF242" s="14" t="inlineStr"/>
       <c r="AG242" s="14" t="inlineStr"/>
@@ -14699,7 +14699,7 @@
       <c r="O243" s="13" t="inlineStr"/>
       <c r="P243" s="13" t="inlineStr"/>
       <c r="Q243" s="14" t="n">
-        <v>2.66E7</v>
+        <v>1.66E7</v>
       </c>
       <c r="R243" s="14" t="inlineStr"/>
       <c r="S243" s="14" t="n">
@@ -14721,11 +14721,11 @@
       <c r="AA243" s="14" t="inlineStr"/>
       <c r="AB243" s="14" t="inlineStr"/>
       <c r="AC243" s="15" t="n">
-        <v>0.45652714285714285</v>
+        <v>0.7315434939759036</v>
       </c>
       <c r="AD243" s="15" t="inlineStr"/>
       <c r="AE243" s="14" t="n">
-        <v>1.4456378E7</v>
+        <v>4456378.0</v>
       </c>
       <c r="AF243" s="14" t="inlineStr"/>
       <c r="AG243" s="14" t="inlineStr"/>
@@ -14756,7 +14756,7 @@
       <c r="O244" s="13" t="inlineStr"/>
       <c r="P244" s="13" t="inlineStr"/>
       <c r="Q244" s="14" t="n">
-        <v>1.443E7</v>
+        <v>1.444E7</v>
       </c>
       <c r="R244" s="14" t="inlineStr"/>
       <c r="S244" s="14" t="n">
@@ -14778,11 +14778,11 @@
       <c r="AA244" s="14" t="inlineStr"/>
       <c r="AB244" s="14" t="inlineStr"/>
       <c r="AC244" s="15" t="n">
-        <v>1.0</v>
+        <v>0.9993074792243767</v>
       </c>
       <c r="AD244" s="15" t="inlineStr"/>
       <c r="AE244" s="14" t="n">
-        <v>0.0</v>
+        <v>10000.0</v>
       </c>
       <c r="AF244" s="14" t="inlineStr"/>
       <c r="AG244" s="14" t="inlineStr"/>
@@ -14826,20 +14826,20 @@
         <v>1576500.0</v>
       </c>
       <c r="X245" s="14" t="n">
-        <v>0.0</v>
+        <v>1800000.0</v>
       </c>
       <c r="Y245" s="14" t="inlineStr"/>
       <c r="Z245" s="14" t="n">
-        <v>1576500.0</v>
+        <v>3376500.0</v>
       </c>
       <c r="AA245" s="14" t="inlineStr"/>
       <c r="AB245" s="14" t="inlineStr"/>
       <c r="AC245" s="15" t="n">
-        <v>0.37987951807228915</v>
+        <v>0.8136144578313254</v>
       </c>
       <c r="AD245" s="15" t="inlineStr"/>
       <c r="AE245" s="14" t="n">
-        <v>2573500.0</v>
+        <v>773500.0</v>
       </c>
       <c r="AF245" s="14" t="inlineStr"/>
       <c r="AG245" s="14" t="inlineStr"/>
@@ -14927,7 +14927,7 @@
       <c r="O247" s="13" t="inlineStr"/>
       <c r="P247" s="13" t="inlineStr"/>
       <c r="Q247" s="14" t="n">
-        <v>4.21E7</v>
+        <v>3.65E7</v>
       </c>
       <c r="R247" s="14" t="inlineStr"/>
       <c r="S247" s="14" t="n">
@@ -14940,20 +14940,20 @@
         <v>1.5284E7</v>
       </c>
       <c r="X247" s="14" t="n">
-        <v>0.0</v>
+        <v>2.11705E7</v>
       </c>
       <c r="Y247" s="14" t="inlineStr"/>
       <c r="Z247" s="14" t="n">
-        <v>1.5284E7</v>
+        <v>3.64545E7</v>
       </c>
       <c r="AA247" s="14" t="inlineStr"/>
       <c r="AB247" s="14" t="inlineStr"/>
       <c r="AC247" s="15" t="n">
-        <v>0.36304038004750594</v>
+        <v>0.9987534246575343</v>
       </c>
       <c r="AD247" s="15" t="inlineStr"/>
       <c r="AE247" s="14" t="n">
-        <v>2.6816E7</v>
+        <v>45500.0</v>
       </c>
       <c r="AF247" s="14" t="inlineStr"/>
       <c r="AG247" s="14" t="inlineStr"/>
@@ -14997,20 +14997,20 @@
         <v>0.0</v>
       </c>
       <c r="X248" s="14" t="n">
-        <v>0.0</v>
+        <v>3.0407E7</v>
       </c>
       <c r="Y248" s="14" t="inlineStr"/>
       <c r="Z248" s="14" t="n">
-        <v>0.0</v>
+        <v>3.0407E7</v>
       </c>
       <c r="AA248" s="14" t="inlineStr"/>
       <c r="AB248" s="14" t="inlineStr"/>
       <c r="AC248" s="15" t="n">
-        <v>0.0</v>
+        <v>0.9940176528277215</v>
       </c>
       <c r="AD248" s="15" t="inlineStr"/>
       <c r="AE248" s="14" t="n">
-        <v>3.059E7</v>
+        <v>183000.0</v>
       </c>
       <c r="AF248" s="14" t="inlineStr"/>
       <c r="AG248" s="14" t="inlineStr"/>
@@ -15111,20 +15111,20 @@
         <v>0.0</v>
       </c>
       <c r="X250" s="14" t="n">
-        <v>0.0</v>
+        <v>4300000.0</v>
       </c>
       <c r="Y250" s="14" t="inlineStr"/>
       <c r="Z250" s="14" t="n">
-        <v>0.0</v>
+        <v>4300000.0</v>
       </c>
       <c r="AA250" s="14" t="inlineStr"/>
       <c r="AB250" s="14" t="inlineStr"/>
       <c r="AC250" s="15" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AD250" s="15" t="inlineStr"/>
       <c r="AE250" s="14" t="n">
-        <v>4300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF250" s="14" t="inlineStr"/>
       <c r="AG250" s="14" t="inlineStr"/>
@@ -15253,29 +15253,23 @@
       <c r="E253" s="2" t="inlineStr"/>
       <c r="F253" s="2" t="inlineStr"/>
       <c r="G253" s="2" t="inlineStr"/>
-      <c r="H253" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">523121</t>
-          </r>
-        </is>
-      </c>
-      <c r="I253" s="13" t="inlineStr"/>
-      <c r="J253" s="13" t="inlineStr"/>
-      <c r="K253" s="13" t="inlineStr"/>
-      <c r="L253" s="13" t="inlineStr"/>
-      <c r="M253" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Pemeliharaan Peralatan dan Mesin</t>
-          </r>
-        </is>
-      </c>
-      <c r="N253" s="13" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr"/>
+      <c r="I253" s="2" t="inlineStr"/>
+      <c r="J253" s="2" t="inlineStr"/>
+      <c r="K253" s="2" t="inlineStr"/>
+      <c r="L253" s="2" t="inlineStr"/>
+      <c r="M253" s="2" t="inlineStr"/>
+      <c r="N253" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000310. Pemeliharaan Gedung Lab Basah Depok</t>
+          </r>
+        </is>
+      </c>
       <c r="O253" s="13" t="inlineStr"/>
       <c r="P253" s="13" t="inlineStr"/>
       <c r="Q253" s="14" t="n">
-        <v>3.325E8</v>
+        <v>3400000.0</v>
       </c>
       <c r="R253" s="14" t="inlineStr"/>
       <c r="S253" s="14" t="n">
@@ -15285,23 +15279,23 @@
       <c r="U253" s="14" t="inlineStr"/>
       <c r="V253" s="14" t="inlineStr"/>
       <c r="W253" s="14" t="n">
-        <v>2.11521335E8</v>
+        <v>0.0</v>
       </c>
       <c r="X253" s="14" t="n">
-        <v>2.0627437E7</v>
+        <v>3332500.0</v>
       </c>
       <c r="Y253" s="14" t="inlineStr"/>
       <c r="Z253" s="14" t="n">
-        <v>2.32148772E8</v>
+        <v>3332500.0</v>
       </c>
       <c r="AA253" s="14" t="inlineStr"/>
       <c r="AB253" s="14" t="inlineStr"/>
       <c r="AC253" s="15" t="n">
-        <v>0.6981917954887218</v>
+        <v>0.9801470588235294</v>
       </c>
       <c r="AD253" s="15" t="inlineStr"/>
       <c r="AE253" s="14" t="n">
-        <v>1.00351228E8</v>
+        <v>67500.0</v>
       </c>
       <c r="AF253" s="14" t="inlineStr"/>
       <c r="AG253" s="14" t="inlineStr"/>
@@ -15359,23 +15353,29 @@
       <c r="E255" s="2" t="inlineStr"/>
       <c r="F255" s="2" t="inlineStr"/>
       <c r="G255" s="2" t="inlineStr"/>
-      <c r="H255" s="2" t="inlineStr"/>
-      <c r="I255" s="2" t="inlineStr"/>
-      <c r="J255" s="2" t="inlineStr"/>
-      <c r="K255" s="2" t="inlineStr"/>
-      <c r="L255" s="2" t="inlineStr"/>
-      <c r="M255" s="2" t="inlineStr"/>
-      <c r="N255" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000175. Pemeliharaan AC Split</t>
-          </r>
-        </is>
-      </c>
+      <c r="H255" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">523121</t>
+          </r>
+        </is>
+      </c>
+      <c r="I255" s="13" t="inlineStr"/>
+      <c r="J255" s="13" t="inlineStr"/>
+      <c r="K255" s="13" t="inlineStr"/>
+      <c r="L255" s="13" t="inlineStr"/>
+      <c r="M255" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Pemeliharaan Peralatan dan Mesin</t>
+          </r>
+        </is>
+      </c>
+      <c r="N255" s="13" t="inlineStr"/>
       <c r="O255" s="13" t="inlineStr"/>
       <c r="P255" s="13" t="inlineStr"/>
       <c r="Q255" s="14" t="n">
-        <v>2.257E7</v>
+        <v>3.24415E8</v>
       </c>
       <c r="R255" s="14" t="inlineStr"/>
       <c r="S255" s="14" t="n">
@@ -15385,23 +15385,23 @@
       <c r="U255" s="14" t="inlineStr"/>
       <c r="V255" s="14" t="inlineStr"/>
       <c r="W255" s="14" t="n">
-        <v>1.396E7</v>
+        <v>2.11521335E8</v>
       </c>
       <c r="X255" s="14" t="n">
-        <v>2890000.0</v>
+        <v>8.661379E7</v>
       </c>
       <c r="Y255" s="14" t="inlineStr"/>
       <c r="Z255" s="14" t="n">
-        <v>1.685E7</v>
+        <v>2.98135125E8</v>
       </c>
       <c r="AA255" s="14" t="inlineStr"/>
       <c r="AB255" s="14" t="inlineStr"/>
       <c r="AC255" s="15" t="n">
-        <v>0.7465662383695171</v>
+        <v>0.918993033614352</v>
       </c>
       <c r="AD255" s="15" t="inlineStr"/>
       <c r="AE255" s="14" t="n">
-        <v>5720000.0</v>
+        <v>2.6279875E7</v>
       </c>
       <c r="AF255" s="14" t="inlineStr"/>
       <c r="AG255" s="14" t="inlineStr"/>
@@ -15425,14 +15425,14 @@
       <c r="N256" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000176. Pemeliharaan Laptop</t>
+            <t xml:space="preserve">000175. Pemeliharaan AC Split</t>
           </r>
         </is>
       </c>
       <c r="O256" s="13" t="inlineStr"/>
       <c r="P256" s="13" t="inlineStr"/>
       <c r="Q256" s="14" t="n">
-        <v>5000000.0</v>
+        <v>2.257E7</v>
       </c>
       <c r="R256" s="14" t="inlineStr"/>
       <c r="S256" s="14" t="n">
@@ -15442,23 +15442,23 @@
       <c r="U256" s="14" t="inlineStr"/>
       <c r="V256" s="14" t="inlineStr"/>
       <c r="W256" s="14" t="n">
-        <v>2487928.0</v>
+        <v>1.396E7</v>
       </c>
       <c r="X256" s="14" t="n">
-        <v>0.0</v>
+        <v>5220000.0</v>
       </c>
       <c r="Y256" s="14" t="inlineStr"/>
       <c r="Z256" s="14" t="n">
-        <v>2487928.0</v>
+        <v>1.918E7</v>
       </c>
       <c r="AA256" s="14" t="inlineStr"/>
       <c r="AB256" s="14" t="inlineStr"/>
       <c r="AC256" s="15" t="n">
-        <v>0.4975856</v>
+        <v>0.8498006202924235</v>
       </c>
       <c r="AD256" s="15" t="inlineStr"/>
       <c r="AE256" s="14" t="n">
-        <v>2512072.0</v>
+        <v>3390000.0</v>
       </c>
       <c r="AF256" s="14" t="inlineStr"/>
       <c r="AG256" s="14" t="inlineStr"/>
@@ -15482,14 +15482,14 @@
       <c r="N257" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000182. Pemeliharaan Instalasi Listrik</t>
+            <t xml:space="preserve">000176. Pemeliharaan Laptop</t>
           </r>
         </is>
       </c>
       <c r="O257" s="13" t="inlineStr"/>
       <c r="P257" s="13" t="inlineStr"/>
       <c r="Q257" s="14" t="n">
-        <v>4.5E7</v>
+        <v>5000000.0</v>
       </c>
       <c r="R257" s="14" t="inlineStr"/>
       <c r="S257" s="14" t="n">
@@ -15499,23 +15499,23 @@
       <c r="U257" s="14" t="inlineStr"/>
       <c r="V257" s="14" t="inlineStr"/>
       <c r="W257" s="14" t="n">
-        <v>2.9845218E7</v>
+        <v>2487928.0</v>
       </c>
       <c r="X257" s="14" t="n">
-        <v>0.0</v>
+        <v>2500000.0</v>
       </c>
       <c r="Y257" s="14" t="inlineStr"/>
       <c r="Z257" s="14" t="n">
-        <v>2.9845218E7</v>
+        <v>4987928.0</v>
       </c>
       <c r="AA257" s="14" t="inlineStr"/>
       <c r="AB257" s="14" t="inlineStr"/>
       <c r="AC257" s="15" t="n">
-        <v>0.6632270666666666</v>
+        <v>0.9975856</v>
       </c>
       <c r="AD257" s="15" t="inlineStr"/>
       <c r="AE257" s="14" t="n">
-        <v>1.5154782E7</v>
+        <v>12072.0</v>
       </c>
       <c r="AF257" s="14" t="inlineStr"/>
       <c r="AG257" s="14" t="inlineStr"/>
@@ -15539,14 +15539,14 @@
       <c r="N258" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000183. Pemeliharaan Kendaraan Roda 4</t>
+            <t xml:space="preserve">000182. Pemeliharaan Instalasi Listrik</t>
           </r>
         </is>
       </c>
       <c r="O258" s="13" t="inlineStr"/>
       <c r="P258" s="13" t="inlineStr"/>
       <c r="Q258" s="14" t="n">
-        <v>1.6975E8</v>
+        <v>4.5E7</v>
       </c>
       <c r="R258" s="14" t="inlineStr"/>
       <c r="S258" s="14" t="n">
@@ -15556,23 +15556,23 @@
       <c r="U258" s="14" t="inlineStr"/>
       <c r="V258" s="14" t="inlineStr"/>
       <c r="W258" s="14" t="n">
-        <v>1.22043496E8</v>
+        <v>2.9845218E7</v>
       </c>
       <c r="X258" s="14" t="n">
-        <v>1.5139299E7</v>
+        <v>1.279805E7</v>
       </c>
       <c r="Y258" s="14" t="inlineStr"/>
       <c r="Z258" s="14" t="n">
-        <v>1.37182795E8</v>
+        <v>4.2643268E7</v>
       </c>
       <c r="AA258" s="14" t="inlineStr"/>
       <c r="AB258" s="14" t="inlineStr"/>
       <c r="AC258" s="15" t="n">
-        <v>0.8081460677466863</v>
+        <v>0.9476281777777777</v>
       </c>
       <c r="AD258" s="15" t="inlineStr"/>
       <c r="AE258" s="14" t="n">
-        <v>3.2567205E7</v>
+        <v>2356732.0</v>
       </c>
       <c r="AF258" s="14" t="inlineStr"/>
       <c r="AG258" s="14" t="inlineStr"/>
@@ -15596,14 +15596,14 @@
       <c r="N259" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000184. Pemeliharaan Kendaraan Roda 2</t>
+            <t xml:space="preserve">000183. Pemeliharaan Kendaraan Roda 4</t>
           </r>
         </is>
       </c>
       <c r="O259" s="13" t="inlineStr"/>
       <c r="P259" s="13" t="inlineStr"/>
       <c r="Q259" s="14" t="n">
-        <v>4500000.0</v>
+        <v>1.74265E8</v>
       </c>
       <c r="R259" s="14" t="inlineStr"/>
       <c r="S259" s="14" t="n">
@@ -15613,23 +15613,23 @@
       <c r="U259" s="14" t="inlineStr"/>
       <c r="V259" s="14" t="inlineStr"/>
       <c r="W259" s="14" t="n">
-        <v>4147992.0</v>
+        <v>1.22043496E8</v>
       </c>
       <c r="X259" s="14" t="n">
-        <v>0.0</v>
+        <v>4.7543521E7</v>
       </c>
       <c r="Y259" s="14" t="inlineStr"/>
       <c r="Z259" s="14" t="n">
-        <v>4147992.0</v>
+        <v>1.69587017E8</v>
       </c>
       <c r="AA259" s="14" t="inlineStr"/>
       <c r="AB259" s="14" t="inlineStr"/>
       <c r="AC259" s="15" t="n">
-        <v>0.921776</v>
+        <v>0.9731559234499182</v>
       </c>
       <c r="AD259" s="15" t="inlineStr"/>
       <c r="AE259" s="14" t="n">
-        <v>352008.0</v>
+        <v>4677983.0</v>
       </c>
       <c r="AF259" s="14" t="inlineStr"/>
       <c r="AG259" s="14" t="inlineStr"/>
@@ -15653,14 +15653,14 @@
       <c r="N260" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000185. Pemeliharaan CCTV</t>
+            <t xml:space="preserve">000184. Pemeliharaan Kendaraan Roda 2</t>
           </r>
         </is>
       </c>
       <c r="O260" s="13" t="inlineStr"/>
       <c r="P260" s="13" t="inlineStr"/>
       <c r="Q260" s="14" t="n">
-        <v>2.1E7</v>
+        <v>4500000.0</v>
       </c>
       <c r="R260" s="14" t="inlineStr"/>
       <c r="S260" s="14" t="n">
@@ -15670,23 +15670,23 @@
       <c r="U260" s="14" t="inlineStr"/>
       <c r="V260" s="14" t="inlineStr"/>
       <c r="W260" s="14" t="n">
-        <v>1.4290555E7</v>
+        <v>4147992.0</v>
       </c>
       <c r="X260" s="14" t="n">
-        <v>0.0</v>
+        <v>90000.0</v>
       </c>
       <c r="Y260" s="14" t="inlineStr"/>
       <c r="Z260" s="14" t="n">
-        <v>1.4290555E7</v>
+        <v>4237992.0</v>
       </c>
       <c r="AA260" s="14" t="inlineStr"/>
       <c r="AB260" s="14" t="inlineStr"/>
       <c r="AC260" s="15" t="n">
-        <v>0.680502619047619</v>
+        <v>0.941776</v>
       </c>
       <c r="AD260" s="15" t="inlineStr"/>
       <c r="AE260" s="14" t="n">
-        <v>6709445.0</v>
+        <v>262008.0</v>
       </c>
       <c r="AF260" s="14" t="inlineStr"/>
       <c r="AG260" s="14" t="inlineStr"/>
@@ -15710,14 +15710,14 @@
       <c r="N261" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000186. Pemeliharaan Genset 250 KVA</t>
+            <t xml:space="preserve">000185. Pemeliharaan CCTV</t>
           </r>
         </is>
       </c>
       <c r="O261" s="13" t="inlineStr"/>
       <c r="P261" s="13" t="inlineStr"/>
       <c r="Q261" s="14" t="n">
-        <v>9010000.0</v>
+        <v>1.5E7</v>
       </c>
       <c r="R261" s="14" t="inlineStr"/>
       <c r="S261" s="14" t="n">
@@ -15727,23 +15727,23 @@
       <c r="U261" s="14" t="inlineStr"/>
       <c r="V261" s="14" t="inlineStr"/>
       <c r="W261" s="14" t="n">
-        <v>1000052.0</v>
+        <v>1.4290555E7</v>
       </c>
       <c r="X261" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y261" s="14" t="inlineStr"/>
       <c r="Z261" s="14" t="n">
-        <v>1000052.0</v>
+        <v>1.4290555E7</v>
       </c>
       <c r="AA261" s="14" t="inlineStr"/>
       <c r="AB261" s="14" t="inlineStr"/>
       <c r="AC261" s="15" t="n">
-        <v>0.11099356270810211</v>
+        <v>0.9527036666666666</v>
       </c>
       <c r="AD261" s="15" t="inlineStr"/>
       <c r="AE261" s="14" t="n">
-        <v>8009948.0</v>
+        <v>709445.0</v>
       </c>
       <c r="AF261" s="14" t="inlineStr"/>
       <c r="AG261" s="14" t="inlineStr"/>
@@ -15767,14 +15767,14 @@
       <c r="N262" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000187. Pemeliharaan Genset 40 KVA</t>
+            <t xml:space="preserve">000186. Pemeliharaan Genset 250 KVA</t>
           </r>
         </is>
       </c>
       <c r="O262" s="13" t="inlineStr"/>
       <c r="P262" s="13" t="inlineStr"/>
       <c r="Q262" s="14" t="n">
-        <v>4050000.0</v>
+        <v>9010000.0</v>
       </c>
       <c r="R262" s="14" t="inlineStr"/>
       <c r="S262" s="14" t="n">
@@ -15784,23 +15784,23 @@
       <c r="U262" s="14" t="inlineStr"/>
       <c r="V262" s="14" t="inlineStr"/>
       <c r="W262" s="14" t="n">
-        <v>1978406.0</v>
+        <v>1000052.0</v>
       </c>
       <c r="X262" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y262" s="14" t="inlineStr"/>
       <c r="Z262" s="14" t="n">
-        <v>1978406.0</v>
+        <v>1000052.0</v>
       </c>
       <c r="AA262" s="14" t="inlineStr"/>
       <c r="AB262" s="14" t="inlineStr"/>
       <c r="AC262" s="15" t="n">
-        <v>0.4884953086419753</v>
+        <v>0.11099356270810211</v>
       </c>
       <c r="AD262" s="15" t="inlineStr"/>
       <c r="AE262" s="14" t="n">
-        <v>2071594.0</v>
+        <v>8009948.0</v>
       </c>
       <c r="AF262" s="14" t="inlineStr"/>
       <c r="AG262" s="14" t="inlineStr"/>
@@ -15824,14 +15824,14 @@
       <c r="N263" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000190. Pemeliharaan Mesin Potong Rumput</t>
+            <t xml:space="preserve">000187. Pemeliharaan Genset 40 KVA</t>
           </r>
         </is>
       </c>
       <c r="O263" s="13" t="inlineStr"/>
       <c r="P263" s="13" t="inlineStr"/>
       <c r="Q263" s="14" t="n">
-        <v>1.2E7</v>
+        <v>3050000.0</v>
       </c>
       <c r="R263" s="14" t="inlineStr"/>
       <c r="S263" s="14" t="n">
@@ -15841,23 +15841,23 @@
       <c r="U263" s="14" t="inlineStr"/>
       <c r="V263" s="14" t="inlineStr"/>
       <c r="W263" s="14" t="n">
-        <v>8450284.0</v>
+        <v>1978406.0</v>
       </c>
       <c r="X263" s="14" t="n">
-        <v>288000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y263" s="14" t="inlineStr"/>
       <c r="Z263" s="14" t="n">
-        <v>8738284.0</v>
+        <v>1978406.0</v>
       </c>
       <c r="AA263" s="14" t="inlineStr"/>
       <c r="AB263" s="14" t="inlineStr"/>
       <c r="AC263" s="15" t="n">
-        <v>0.7281903333333334</v>
+        <v>0.6486577049180328</v>
       </c>
       <c r="AD263" s="15" t="inlineStr"/>
       <c r="AE263" s="14" t="n">
-        <v>3261716.0</v>
+        <v>1071594.0</v>
       </c>
       <c r="AF263" s="14" t="inlineStr"/>
       <c r="AG263" s="14" t="inlineStr"/>
@@ -15881,14 +15881,14 @@
       <c r="N264" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000191. Pemeliharaan Printer</t>
+            <t xml:space="preserve">000190. Pemeliharaan Mesin Potong Rumput</t>
           </r>
         </is>
       </c>
       <c r="O264" s="13" t="inlineStr"/>
       <c r="P264" s="13" t="inlineStr"/>
       <c r="Q264" s="14" t="n">
-        <v>1500000.0</v>
+        <v>1.2E7</v>
       </c>
       <c r="R264" s="14" t="inlineStr"/>
       <c r="S264" s="14" t="n">
@@ -15898,23 +15898,23 @@
       <c r="U264" s="14" t="inlineStr"/>
       <c r="V264" s="14" t="inlineStr"/>
       <c r="W264" s="14" t="n">
-        <v>1167558.0</v>
+        <v>8450284.0</v>
       </c>
       <c r="X264" s="14" t="n">
-        <v>0.0</v>
+        <v>2385941.0</v>
       </c>
       <c r="Y264" s="14" t="inlineStr"/>
       <c r="Z264" s="14" t="n">
-        <v>1167558.0</v>
+        <v>1.0836225E7</v>
       </c>
       <c r="AA264" s="14" t="inlineStr"/>
       <c r="AB264" s="14" t="inlineStr"/>
       <c r="AC264" s="15" t="n">
-        <v>0.778372</v>
+        <v>0.90301875</v>
       </c>
       <c r="AD264" s="15" t="inlineStr"/>
       <c r="AE264" s="14" t="n">
-        <v>332442.0</v>
+        <v>1163775.0</v>
       </c>
       <c r="AF264" s="14" t="inlineStr"/>
       <c r="AG264" s="14" t="inlineStr"/>
@@ -15938,14 +15938,14 @@
       <c r="N265" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000192. Pemeliharaan Komputer/PC</t>
+            <t xml:space="preserve">000191. Pemeliharaan Printer</t>
           </r>
         </is>
       </c>
       <c r="O265" s="13" t="inlineStr"/>
       <c r="P265" s="13" t="inlineStr"/>
       <c r="Q265" s="14" t="n">
-        <v>1.562E7</v>
+        <v>2000000.0</v>
       </c>
       <c r="R265" s="14" t="inlineStr"/>
       <c r="S265" s="14" t="n">
@@ -15955,23 +15955,23 @@
       <c r="U265" s="14" t="inlineStr"/>
       <c r="V265" s="14" t="inlineStr"/>
       <c r="W265" s="14" t="n">
-        <v>3760846.0</v>
+        <v>1167558.0</v>
       </c>
       <c r="X265" s="14" t="n">
-        <v>1560138.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y265" s="14" t="inlineStr"/>
       <c r="Z265" s="14" t="n">
-        <v>5320984.0</v>
+        <v>1167558.0</v>
       </c>
       <c r="AA265" s="14" t="inlineStr"/>
       <c r="AB265" s="14" t="inlineStr"/>
       <c r="AC265" s="15" t="n">
-        <v>0.3406519846350832</v>
+        <v>0.583779</v>
       </c>
       <c r="AD265" s="15" t="inlineStr"/>
       <c r="AE265" s="14" t="n">
-        <v>1.0299016E7</v>
+        <v>832442.0</v>
       </c>
       <c r="AF265" s="14" t="inlineStr"/>
       <c r="AG265" s="14" t="inlineStr"/>
@@ -15995,14 +15995,14 @@
       <c r="N266" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000283. Pemeliharaan Kulkas</t>
+            <t xml:space="preserve">000192. Pemeliharaan Komputer/PC</t>
           </r>
         </is>
       </c>
       <c r="O266" s="13" t="inlineStr"/>
       <c r="P266" s="13" t="inlineStr"/>
       <c r="Q266" s="14" t="n">
-        <v>500000.0</v>
+        <v>1.562E7</v>
       </c>
       <c r="R266" s="14" t="inlineStr"/>
       <c r="S266" s="14" t="n">
@@ -16012,23 +16012,23 @@
       <c r="U266" s="14" t="inlineStr"/>
       <c r="V266" s="14" t="inlineStr"/>
       <c r="W266" s="14" t="n">
-        <v>500000.0</v>
+        <v>3760846.0</v>
       </c>
       <c r="X266" s="14" t="n">
-        <v>0.0</v>
+        <v>9601868.0</v>
       </c>
       <c r="Y266" s="14" t="inlineStr"/>
       <c r="Z266" s="14" t="n">
-        <v>500000.0</v>
+        <v>1.3362714E7</v>
       </c>
       <c r="AA266" s="14" t="inlineStr"/>
       <c r="AB266" s="14" t="inlineStr"/>
       <c r="AC266" s="15" t="n">
-        <v>1.0</v>
+        <v>0.855487451984635</v>
       </c>
       <c r="AD266" s="15" t="inlineStr"/>
       <c r="AE266" s="14" t="n">
-        <v>0.0</v>
+        <v>2257286.0</v>
       </c>
       <c r="AF266" s="14" t="inlineStr"/>
       <c r="AG266" s="14" t="inlineStr"/>
@@ -16052,14 +16052,14 @@
       <c r="N267" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000299. Pemeliharaan Instalasi Air</t>
+            <t xml:space="preserve">000283. Pemeliharaan Kulkas</t>
           </r>
         </is>
       </c>
       <c r="O267" s="13" t="inlineStr"/>
       <c r="P267" s="13" t="inlineStr"/>
       <c r="Q267" s="14" t="n">
-        <v>1.3E7</v>
+        <v>500000.0</v>
       </c>
       <c r="R267" s="14" t="inlineStr"/>
       <c r="S267" s="14" t="n">
@@ -16069,23 +16069,23 @@
       <c r="U267" s="14" t="inlineStr"/>
       <c r="V267" s="14" t="inlineStr"/>
       <c r="W267" s="14" t="n">
-        <v>7889000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="X267" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y267" s="14" t="inlineStr"/>
       <c r="Z267" s="14" t="n">
-        <v>7889000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="AA267" s="14" t="inlineStr"/>
       <c r="AB267" s="14" t="inlineStr"/>
       <c r="AC267" s="15" t="n">
-        <v>0.6068461538461538</v>
+        <v>1.0</v>
       </c>
       <c r="AD267" s="15" t="inlineStr"/>
       <c r="AE267" s="14" t="n">
-        <v>5111000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF267" s="14" t="inlineStr"/>
       <c r="AG267" s="14" t="inlineStr"/>
@@ -16109,14 +16109,14 @@
       <c r="N268" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000304. Pemeliharaan Alat Laboratorium</t>
+            <t xml:space="preserve">000299. Pemeliharaan Instalasi Air</t>
           </r>
         </is>
       </c>
       <c r="O268" s="13" t="inlineStr"/>
       <c r="P268" s="13" t="inlineStr"/>
       <c r="Q268" s="14" t="n">
-        <v>2500000.0</v>
+        <v>9400000.0</v>
       </c>
       <c r="R268" s="14" t="inlineStr"/>
       <c r="S268" s="14" t="n">
@@ -16126,23 +16126,23 @@
       <c r="U268" s="14" t="inlineStr"/>
       <c r="V268" s="14" t="inlineStr"/>
       <c r="W268" s="14" t="n">
-        <v>0.0</v>
+        <v>7889000.0</v>
       </c>
       <c r="X268" s="14" t="n">
-        <v>0.0</v>
+        <v>581410.0</v>
       </c>
       <c r="Y268" s="14" t="inlineStr"/>
       <c r="Z268" s="14" t="n">
-        <v>0.0</v>
+        <v>8470410.0</v>
       </c>
       <c r="AA268" s="14" t="inlineStr"/>
       <c r="AB268" s="14" t="inlineStr"/>
       <c r="AC268" s="15" t="n">
-        <v>0.0</v>
+        <v>0.9011074468085106</v>
       </c>
       <c r="AD268" s="15" t="inlineStr"/>
       <c r="AE268" s="14" t="n">
-        <v>2500000.0</v>
+        <v>929590.0</v>
       </c>
       <c r="AF268" s="14" t="inlineStr"/>
       <c r="AG268" s="14" t="inlineStr"/>
@@ -16186,20 +16186,20 @@
         <v>0.0</v>
       </c>
       <c r="X269" s="14" t="n">
-        <v>750000.0</v>
+        <v>1450000.0</v>
       </c>
       <c r="Y269" s="14" t="inlineStr"/>
       <c r="Z269" s="14" t="n">
-        <v>750000.0</v>
+        <v>1450000.0</v>
       </c>
       <c r="AA269" s="14" t="inlineStr"/>
       <c r="AB269" s="14" t="inlineStr"/>
       <c r="AC269" s="15" t="n">
-        <v>0.5</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="AD269" s="15" t="inlineStr"/>
       <c r="AE269" s="14" t="n">
-        <v>750000.0</v>
+        <v>50000.0</v>
       </c>
       <c r="AF269" s="14" t="inlineStr"/>
       <c r="AG269" s="14" t="inlineStr"/>
@@ -16230,7 +16230,7 @@
       <c r="O270" s="13" t="inlineStr"/>
       <c r="P270" s="13" t="inlineStr"/>
       <c r="Q270" s="14" t="n">
-        <v>5000000.0</v>
+        <v>4000000.0</v>
       </c>
       <c r="R270" s="14" t="inlineStr"/>
       <c r="S270" s="14" t="n">
@@ -16243,20 +16243,20 @@
         <v>0.0</v>
       </c>
       <c r="X270" s="14" t="n">
-        <v>0.0</v>
+        <v>3955000.0</v>
       </c>
       <c r="Y270" s="14" t="inlineStr"/>
       <c r="Z270" s="14" t="n">
-        <v>0.0</v>
+        <v>3955000.0</v>
       </c>
       <c r="AA270" s="14" t="inlineStr"/>
       <c r="AB270" s="14" t="inlineStr"/>
       <c r="AC270" s="15" t="n">
-        <v>0.0</v>
+        <v>0.98875</v>
       </c>
       <c r="AD270" s="15" t="inlineStr"/>
       <c r="AE270" s="14" t="n">
-        <v>5000000.0</v>
+        <v>45000.0</v>
       </c>
       <c r="AF270" s="14" t="inlineStr"/>
       <c r="AG270" s="14" t="inlineStr"/>
@@ -16271,29 +16271,23 @@
       <c r="E271" s="2" t="inlineStr"/>
       <c r="F271" s="2" t="inlineStr"/>
       <c r="G271" s="2" t="inlineStr"/>
-      <c r="H271" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">523132</t>
-          </r>
-        </is>
-      </c>
-      <c r="I271" s="13" t="inlineStr"/>
-      <c r="J271" s="13" t="inlineStr"/>
-      <c r="K271" s="13" t="inlineStr"/>
-      <c r="L271" s="13" t="inlineStr"/>
-      <c r="M271" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Pemeliharaan Irigasi</t>
-          </r>
-        </is>
-      </c>
-      <c r="N271" s="13" t="inlineStr"/>
+      <c r="H271" s="2" t="inlineStr"/>
+      <c r="I271" s="2" t="inlineStr"/>
+      <c r="J271" s="2" t="inlineStr"/>
+      <c r="K271" s="2" t="inlineStr"/>
+      <c r="L271" s="2" t="inlineStr"/>
+      <c r="M271" s="2" t="inlineStr"/>
+      <c r="N271" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000308. Pemeliharaan Genset Portable</t>
+          </r>
+        </is>
+      </c>
       <c r="O271" s="13" t="inlineStr"/>
       <c r="P271" s="13" t="inlineStr"/>
       <c r="Q271" s="14" t="n">
-        <v>1.5292E8</v>
+        <v>1000000.0</v>
       </c>
       <c r="R271" s="14" t="inlineStr"/>
       <c r="S271" s="14" t="n">
@@ -16303,23 +16297,23 @@
       <c r="U271" s="14" t="inlineStr"/>
       <c r="V271" s="14" t="inlineStr"/>
       <c r="W271" s="14" t="n">
-        <v>8.0551E7</v>
+        <v>0.0</v>
       </c>
       <c r="X271" s="14" t="n">
-        <v>0.0</v>
+        <v>488000.0</v>
       </c>
       <c r="Y271" s="14" t="inlineStr"/>
       <c r="Z271" s="14" t="n">
-        <v>8.0551E7</v>
+        <v>488000.0</v>
       </c>
       <c r="AA271" s="14" t="inlineStr"/>
       <c r="AB271" s="14" t="inlineStr"/>
       <c r="AC271" s="15" t="n">
-        <v>0.5267525503531258</v>
+        <v>0.488</v>
       </c>
       <c r="AD271" s="15" t="inlineStr"/>
       <c r="AE271" s="14" t="n">
-        <v>7.2369E7</v>
+        <v>512000.0</v>
       </c>
       <c r="AF271" s="14" t="inlineStr"/>
       <c r="AG271" s="14" t="inlineStr"/>
@@ -16334,23 +16328,29 @@
       <c r="E272" s="2" t="inlineStr"/>
       <c r="F272" s="2" t="inlineStr"/>
       <c r="G272" s="2" t="inlineStr"/>
-      <c r="H272" s="2" t="inlineStr"/>
-      <c r="I272" s="2" t="inlineStr"/>
-      <c r="J272" s="2" t="inlineStr"/>
-      <c r="K272" s="2" t="inlineStr"/>
-      <c r="L272" s="2" t="inlineStr"/>
-      <c r="M272" s="2" t="inlineStr"/>
-      <c r="N272" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000195. Pemeliharaan Talud Cijeruk</t>
-          </r>
-        </is>
-      </c>
+      <c r="H272" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">523132</t>
+          </r>
+        </is>
+      </c>
+      <c r="I272" s="13" t="inlineStr"/>
+      <c r="J272" s="13" t="inlineStr"/>
+      <c r="K272" s="13" t="inlineStr"/>
+      <c r="L272" s="13" t="inlineStr"/>
+      <c r="M272" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Pemeliharaan Irigasi</t>
+          </r>
+        </is>
+      </c>
+      <c r="N272" s="13" t="inlineStr"/>
       <c r="O272" s="13" t="inlineStr"/>
       <c r="P272" s="13" t="inlineStr"/>
       <c r="Q272" s="14" t="n">
-        <v>6.216E7</v>
+        <v>1.5136E8</v>
       </c>
       <c r="R272" s="14" t="inlineStr"/>
       <c r="S272" s="14" t="n">
@@ -16360,23 +16360,23 @@
       <c r="U272" s="14" t="inlineStr"/>
       <c r="V272" s="14" t="inlineStr"/>
       <c r="W272" s="14" t="n">
-        <v>3.909E7</v>
+        <v>8.0551E7</v>
       </c>
       <c r="X272" s="14" t="n">
-        <v>0.0</v>
+        <v>6.9975E7</v>
       </c>
       <c r="Y272" s="14" t="inlineStr"/>
       <c r="Z272" s="14" t="n">
-        <v>3.909E7</v>
+        <v>1.50526E8</v>
       </c>
       <c r="AA272" s="14" t="inlineStr"/>
       <c r="AB272" s="14" t="inlineStr"/>
       <c r="AC272" s="15" t="n">
-        <v>0.6288610038610039</v>
+        <v>0.9944899577167019</v>
       </c>
       <c r="AD272" s="15" t="inlineStr"/>
       <c r="AE272" s="14" t="n">
-        <v>2.307E7</v>
+        <v>834000.0</v>
       </c>
       <c r="AF272" s="14" t="inlineStr"/>
       <c r="AG272" s="14" t="inlineStr"/>
@@ -16400,14 +16400,14 @@
       <c r="N273" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000284. Pemeliharaan Talud Cibalagung</t>
+            <t xml:space="preserve">000195. Pemeliharaan Talud Cijeruk</t>
           </r>
         </is>
       </c>
       <c r="O273" s="13" t="inlineStr"/>
       <c r="P273" s="13" t="inlineStr"/>
       <c r="Q273" s="14" t="n">
-        <v>3.07E7</v>
+        <v>6.06E7</v>
       </c>
       <c r="R273" s="14" t="inlineStr"/>
       <c r="S273" s="14" t="n">
@@ -16417,23 +16417,23 @@
       <c r="U273" s="14" t="inlineStr"/>
       <c r="V273" s="14" t="inlineStr"/>
       <c r="W273" s="14" t="n">
-        <v>3.0685E7</v>
+        <v>3.909E7</v>
       </c>
       <c r="X273" s="14" t="n">
-        <v>0.0</v>
+        <v>2.1185E7</v>
       </c>
       <c r="Y273" s="14" t="inlineStr"/>
       <c r="Z273" s="14" t="n">
-        <v>3.0685E7</v>
+        <v>6.0275E7</v>
       </c>
       <c r="AA273" s="14" t="inlineStr"/>
       <c r="AB273" s="14" t="inlineStr"/>
       <c r="AC273" s="15" t="n">
-        <v>0.9995114006514658</v>
+        <v>0.9946369636963697</v>
       </c>
       <c r="AD273" s="15" t="inlineStr"/>
       <c r="AE273" s="14" t="n">
-        <v>15000.0</v>
+        <v>325000.0</v>
       </c>
       <c r="AF273" s="14" t="inlineStr"/>
       <c r="AG273" s="14" t="inlineStr"/>
@@ -16457,14 +16457,14 @@
       <c r="N274" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000285. Pemeliharaan Saluran Air Cijeruk</t>
+            <t xml:space="preserve">000284. Pemeliharaan Talud Cibalagung</t>
           </r>
         </is>
       </c>
       <c r="O274" s="13" t="inlineStr"/>
       <c r="P274" s="13" t="inlineStr"/>
       <c r="Q274" s="14" t="n">
-        <v>6.006E7</v>
+        <v>3.07E7</v>
       </c>
       <c r="R274" s="14" t="inlineStr"/>
       <c r="S274" s="14" t="n">
@@ -16474,23 +16474,23 @@
       <c r="U274" s="14" t="inlineStr"/>
       <c r="V274" s="14" t="inlineStr"/>
       <c r="W274" s="14" t="n">
-        <v>1.0776E7</v>
+        <v>3.0685E7</v>
       </c>
       <c r="X274" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y274" s="14" t="inlineStr"/>
       <c r="Z274" s="14" t="n">
-        <v>1.0776E7</v>
+        <v>3.0685E7</v>
       </c>
       <c r="AA274" s="14" t="inlineStr"/>
       <c r="AB274" s="14" t="inlineStr"/>
       <c r="AC274" s="15" t="n">
-        <v>0.17942057942057943</v>
+        <v>0.9995114006514658</v>
       </c>
       <c r="AD274" s="15" t="inlineStr"/>
       <c r="AE274" s="14" t="n">
-        <v>4.9284E7</v>
+        <v>15000.0</v>
       </c>
       <c r="AF274" s="14" t="inlineStr"/>
       <c r="AG274" s="14" t="inlineStr"/>
@@ -16503,31 +16503,25 @@
       <c r="C275" s="2" t="inlineStr"/>
       <c r="D275" s="2" t="inlineStr"/>
       <c r="E275" s="2" t="inlineStr"/>
-      <c r="F275" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">002.DD</t>
-          </r>
-        </is>
-      </c>
-      <c r="G275" s="13" t="inlineStr"/>
-      <c r="H275" s="13" t="inlineStr"/>
-      <c r="I275" s="13" t="inlineStr"/>
-      <c r="J275" s="13" t="inlineStr"/>
-      <c r="K275" s="13" t="inlineStr"/>
-      <c r="L275" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pembayaran Terkait Pelaksanaan Operasional Kantor</t>
-          </r>
-        </is>
-      </c>
-      <c r="M275" s="13" t="inlineStr"/>
-      <c r="N275" s="13" t="inlineStr"/>
+      <c r="F275" s="2" t="inlineStr"/>
+      <c r="G275" s="2" t="inlineStr"/>
+      <c r="H275" s="2" t="inlineStr"/>
+      <c r="I275" s="2" t="inlineStr"/>
+      <c r="J275" s="2" t="inlineStr"/>
+      <c r="K275" s="2" t="inlineStr"/>
+      <c r="L275" s="2" t="inlineStr"/>
+      <c r="M275" s="2" t="inlineStr"/>
+      <c r="N275" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000285. Pemeliharaan Saluran Air Cijeruk</t>
+          </r>
+        </is>
+      </c>
       <c r="O275" s="13" t="inlineStr"/>
       <c r="P275" s="13" t="inlineStr"/>
       <c r="Q275" s="14" t="n">
-        <v>1.3218E8</v>
+        <v>6.006E7</v>
       </c>
       <c r="R275" s="14" t="inlineStr"/>
       <c r="S275" s="14" t="n">
@@ -16537,23 +16531,23 @@
       <c r="U275" s="14" t="inlineStr"/>
       <c r="V275" s="14" t="inlineStr"/>
       <c r="W275" s="14" t="n">
-        <v>1.3074E8</v>
+        <v>1.0776E7</v>
       </c>
       <c r="X275" s="14" t="n">
-        <v>480000.0</v>
+        <v>4.879E7</v>
       </c>
       <c r="Y275" s="14" t="inlineStr"/>
       <c r="Z275" s="14" t="n">
-        <v>1.3122E8</v>
+        <v>5.9566E7</v>
       </c>
       <c r="AA275" s="14" t="inlineStr"/>
       <c r="AB275" s="14" t="inlineStr"/>
       <c r="AC275" s="15" t="n">
-        <v>0.9927371765773945</v>
+        <v>0.9917748917748918</v>
       </c>
       <c r="AD275" s="15" t="inlineStr"/>
       <c r="AE275" s="14" t="n">
-        <v>960000.0</v>
+        <v>494000.0</v>
       </c>
       <c r="AF275" s="14" t="inlineStr"/>
       <c r="AG275" s="14" t="inlineStr"/>
@@ -16566,31 +16560,31 @@
       <c r="C276" s="2" t="inlineStr"/>
       <c r="D276" s="2" t="inlineStr"/>
       <c r="E276" s="2" t="inlineStr"/>
-      <c r="F276" s="2" t="inlineStr"/>
-      <c r="G276" s="2" t="inlineStr"/>
-      <c r="H276" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521115</t>
-          </r>
-        </is>
-      </c>
+      <c r="F276" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">002.DD</t>
+          </r>
+        </is>
+      </c>
+      <c r="G276" s="13" t="inlineStr"/>
+      <c r="H276" s="13" t="inlineStr"/>
       <c r="I276" s="13" t="inlineStr"/>
       <c r="J276" s="13" t="inlineStr"/>
       <c r="K276" s="13" t="inlineStr"/>
-      <c r="L276" s="13" t="inlineStr"/>
-      <c r="M276" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Honor Operasional Satuan Kerja</t>
-          </r>
-        </is>
-      </c>
+      <c r="L276" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pembayaran Terkait Pelaksanaan Operasional Kantor</t>
+          </r>
+        </is>
+      </c>
+      <c r="M276" s="13" t="inlineStr"/>
       <c r="N276" s="13" t="inlineStr"/>
       <c r="O276" s="13" t="inlineStr"/>
       <c r="P276" s="13" t="inlineStr"/>
       <c r="Q276" s="14" t="n">
-        <v>1.2468E8</v>
+        <v>1.5218E8</v>
       </c>
       <c r="R276" s="14" t="inlineStr"/>
       <c r="S276" s="14" t="n">
@@ -16600,23 +16594,23 @@
       <c r="U276" s="14" t="inlineStr"/>
       <c r="V276" s="14" t="inlineStr"/>
       <c r="W276" s="14" t="n">
-        <v>1.2324E8</v>
+        <v>1.3074E8</v>
       </c>
       <c r="X276" s="14" t="n">
-        <v>480000.0</v>
+        <v>2.124E7</v>
       </c>
       <c r="Y276" s="14" t="inlineStr"/>
       <c r="Z276" s="14" t="n">
-        <v>1.2372E8</v>
+        <v>1.5198E8</v>
       </c>
       <c r="AA276" s="14" t="inlineStr"/>
       <c r="AB276" s="14" t="inlineStr"/>
       <c r="AC276" s="15" t="n">
-        <v>0.9923002887391723</v>
+        <v>0.9986857668550401</v>
       </c>
       <c r="AD276" s="15" t="inlineStr"/>
       <c r="AE276" s="14" t="n">
-        <v>960000.0</v>
+        <v>200000.0</v>
       </c>
       <c r="AF276" s="14" t="inlineStr"/>
       <c r="AG276" s="14" t="inlineStr"/>
@@ -16631,23 +16625,29 @@
       <c r="E277" s="2" t="inlineStr"/>
       <c r="F277" s="2" t="inlineStr"/>
       <c r="G277" s="2" t="inlineStr"/>
-      <c r="H277" s="2" t="inlineStr"/>
-      <c r="I277" s="2" t="inlineStr"/>
-      <c r="J277" s="2" t="inlineStr"/>
-      <c r="K277" s="2" t="inlineStr"/>
-      <c r="L277" s="2" t="inlineStr"/>
-      <c r="M277" s="2" t="inlineStr"/>
-      <c r="N277" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000197. Honorarium Pejabat Kuasa Pengguna Anggaran</t>
-          </r>
-        </is>
-      </c>
+      <c r="H277" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521115</t>
+          </r>
+        </is>
+      </c>
+      <c r="I277" s="13" t="inlineStr"/>
+      <c r="J277" s="13" t="inlineStr"/>
+      <c r="K277" s="13" t="inlineStr"/>
+      <c r="L277" s="13" t="inlineStr"/>
+      <c r="M277" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Honor Operasional Satuan Kerja</t>
+          </r>
+        </is>
+      </c>
+      <c r="N277" s="13" t="inlineStr"/>
       <c r="O277" s="13" t="inlineStr"/>
       <c r="P277" s="13" t="inlineStr"/>
       <c r="Q277" s="14" t="n">
-        <v>3.06E7</v>
+        <v>1.2468E8</v>
       </c>
       <c r="R277" s="14" t="inlineStr"/>
       <c r="S277" s="14" t="n">
@@ -16657,14 +16657,14 @@
       <c r="U277" s="14" t="inlineStr"/>
       <c r="V277" s="14" t="inlineStr"/>
       <c r="W277" s="14" t="n">
-        <v>3.06E7</v>
+        <v>1.2324E8</v>
       </c>
       <c r="X277" s="14" t="n">
-        <v>0.0</v>
+        <v>1440000.0</v>
       </c>
       <c r="Y277" s="14" t="inlineStr"/>
       <c r="Z277" s="14" t="n">
-        <v>3.06E7</v>
+        <v>1.2468E8</v>
       </c>
       <c r="AA277" s="14" t="inlineStr"/>
       <c r="AB277" s="14" t="inlineStr"/>
@@ -16697,14 +16697,14 @@
       <c r="N278" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000198. Honorarium Pejabat Pembuat Komitmen</t>
+            <t xml:space="preserve">000197. Honorarium Pejabat Kuasa Pengguna Anggaran</t>
           </r>
         </is>
       </c>
       <c r="O278" s="13" t="inlineStr"/>
       <c r="P278" s="13" t="inlineStr"/>
       <c r="Q278" s="14" t="n">
-        <v>2.976E7</v>
+        <v>3.06E7</v>
       </c>
       <c r="R278" s="14" t="inlineStr"/>
       <c r="S278" s="14" t="n">
@@ -16714,14 +16714,14 @@
       <c r="U278" s="14" t="inlineStr"/>
       <c r="V278" s="14" t="inlineStr"/>
       <c r="W278" s="14" t="n">
-        <v>2.976E7</v>
+        <v>3.06E7</v>
       </c>
       <c r="X278" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y278" s="14" t="inlineStr"/>
       <c r="Z278" s="14" t="n">
-        <v>2.976E7</v>
+        <v>3.06E7</v>
       </c>
       <c r="AA278" s="14" t="inlineStr"/>
       <c r="AB278" s="14" t="inlineStr"/>
@@ -16737,7 +16737,7 @@
       <c r="AH278" s="14" t="inlineStr"/>
       <c r="AI278" s="14" t="inlineStr"/>
     </row>
-    <row r="279" customHeight="1" ht="18">
+    <row r="279" customHeight="1" ht="15">
       <c r="A279" s="2" t="inlineStr"/>
       <c r="B279" s="2" t="inlineStr"/>
       <c r="C279" s="2" t="inlineStr"/>
@@ -16754,14 +16754,14 @@
       <c r="N279" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000199. Honorarium Pejabat  Penguji Tagihan   Penandatangan  Spm</t>
+            <t xml:space="preserve">000198. Honorarium Pejabat Pembuat Komitmen</t>
           </r>
         </is>
       </c>
       <c r="O279" s="13" t="inlineStr"/>
       <c r="P279" s="13" t="inlineStr"/>
       <c r="Q279" s="14" t="n">
-        <v>1.476E7</v>
+        <v>2.976E7</v>
       </c>
       <c r="R279" s="14" t="inlineStr"/>
       <c r="S279" s="14" t="n">
@@ -16771,14 +16771,14 @@
       <c r="U279" s="14" t="inlineStr"/>
       <c r="V279" s="14" t="inlineStr"/>
       <c r="W279" s="14" t="n">
-        <v>1.476E7</v>
+        <v>2.976E7</v>
       </c>
       <c r="X279" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y279" s="14" t="inlineStr"/>
       <c r="Z279" s="14" t="n">
-        <v>1.476E7</v>
+        <v>2.976E7</v>
       </c>
       <c r="AA279" s="14" t="inlineStr"/>
       <c r="AB279" s="14" t="inlineStr"/>
@@ -16794,7 +16794,7 @@
       <c r="AH279" s="14" t="inlineStr"/>
       <c r="AI279" s="14" t="inlineStr"/>
     </row>
-    <row r="280" customHeight="1" ht="15">
+    <row r="280" customHeight="1" ht="18">
       <c r="A280" s="2" t="inlineStr"/>
       <c r="B280" s="2" t="inlineStr"/>
       <c r="C280" s="2" t="inlineStr"/>
@@ -16811,14 +16811,14 @@
       <c r="N280" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000200. Honorarium Bendahara  Pengeluaran</t>
+            <t xml:space="preserve">000199. Honorarium Pejabat  Penguji Tagihan   Penandatangan  Spm</t>
           </r>
         </is>
       </c>
       <c r="O280" s="13" t="inlineStr"/>
       <c r="P280" s="13" t="inlineStr"/>
       <c r="Q280" s="14" t="n">
-        <v>1.284E7</v>
+        <v>1.476E7</v>
       </c>
       <c r="R280" s="14" t="inlineStr"/>
       <c r="S280" s="14" t="n">
@@ -16828,14 +16828,14 @@
       <c r="U280" s="14" t="inlineStr"/>
       <c r="V280" s="14" t="inlineStr"/>
       <c r="W280" s="14" t="n">
-        <v>1.284E7</v>
+        <v>1.476E7</v>
       </c>
       <c r="X280" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y280" s="14" t="inlineStr"/>
       <c r="Z280" s="14" t="n">
-        <v>1.284E7</v>
+        <v>1.476E7</v>
       </c>
       <c r="AA280" s="14" t="inlineStr"/>
       <c r="AB280" s="14" t="inlineStr"/>
@@ -16911,14 +16911,14 @@
       <c r="N282" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000201. Honorarium Staf  Pengelola</t>
+            <t xml:space="preserve">000200. Honorarium Bendahara  Pengeluaran</t>
           </r>
         </is>
       </c>
       <c r="O282" s="13" t="inlineStr"/>
       <c r="P282" s="13" t="inlineStr"/>
       <c r="Q282" s="14" t="n">
-        <v>2.88E7</v>
+        <v>1.284E7</v>
       </c>
       <c r="R282" s="14" t="inlineStr"/>
       <c r="S282" s="14" t="n">
@@ -16928,14 +16928,14 @@
       <c r="U282" s="14" t="inlineStr"/>
       <c r="V282" s="14" t="inlineStr"/>
       <c r="W282" s="14" t="n">
-        <v>2.88E7</v>
+        <v>1.284E7</v>
       </c>
       <c r="X282" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="Y282" s="14" t="inlineStr"/>
       <c r="Z282" s="14" t="n">
-        <v>2.88E7</v>
+        <v>1.284E7</v>
       </c>
       <c r="AA282" s="14" t="inlineStr"/>
       <c r="AB282" s="14" t="inlineStr"/>
@@ -16968,14 +16968,14 @@
       <c r="N283" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000202. Honorarium Anggota/Petugas (UAKPA/Barang)</t>
+            <t xml:space="preserve">000201. Honorarium Staf  Pengelola</t>
           </r>
         </is>
       </c>
       <c r="O283" s="13" t="inlineStr"/>
       <c r="P283" s="13" t="inlineStr"/>
       <c r="Q283" s="14" t="n">
-        <v>3600000.0</v>
+        <v>2.88E7</v>
       </c>
       <c r="R283" s="14" t="inlineStr"/>
       <c r="S283" s="14" t="n">
@@ -16985,30 +16985,30 @@
       <c r="U283" s="14" t="inlineStr"/>
       <c r="V283" s="14" t="inlineStr"/>
       <c r="W283" s="14" t="n">
-        <v>2700000.0</v>
+        <v>2.88E7</v>
       </c>
       <c r="X283" s="14" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y283" s="14" t="inlineStr"/>
       <c r="Z283" s="14" t="n">
-        <v>3000000.0</v>
+        <v>2.88E7</v>
       </c>
       <c r="AA283" s="14" t="inlineStr"/>
       <c r="AB283" s="14" t="inlineStr"/>
       <c r="AC283" s="15" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.0</v>
       </c>
       <c r="AD283" s="15" t="inlineStr"/>
       <c r="AE283" s="14" t="n">
-        <v>600000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF283" s="14" t="inlineStr"/>
       <c r="AG283" s="14" t="inlineStr"/>
       <c r="AH283" s="14" t="inlineStr"/>
       <c r="AI283" s="14" t="inlineStr"/>
     </row>
-    <row r="284" customHeight="1" ht="18">
+    <row r="284" customHeight="1" ht="15">
       <c r="A284" s="2" t="inlineStr"/>
       <c r="B284" s="2" t="inlineStr"/>
       <c r="C284" s="2" t="inlineStr"/>
@@ -17025,14 +17025,14 @@
       <c r="N284" s="13" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">000203. Honorarium Pengurus/Penyimpan Bmn Tingkat Kuasa Pengguna Barang</t>
+            <t xml:space="preserve">000202. Honorarium Anggota/Petugas (UAKPA/Barang)</t>
           </r>
         </is>
       </c>
       <c r="O284" s="13" t="inlineStr"/>
       <c r="P284" s="13" t="inlineStr"/>
       <c r="Q284" s="14" t="n">
-        <v>4320000.0</v>
+        <v>3600000.0</v>
       </c>
       <c r="R284" s="14" t="inlineStr"/>
       <c r="S284" s="14" t="n">
@@ -17042,30 +17042,30 @@
       <c r="U284" s="14" t="inlineStr"/>
       <c r="V284" s="14" t="inlineStr"/>
       <c r="W284" s="14" t="n">
-        <v>3780000.0</v>
+        <v>2700000.0</v>
       </c>
       <c r="X284" s="14" t="n">
-        <v>180000.0</v>
+        <v>900000.0</v>
       </c>
       <c r="Y284" s="14" t="inlineStr"/>
       <c r="Z284" s="14" t="n">
-        <v>3960000.0</v>
+        <v>3600000.0</v>
       </c>
       <c r="AA284" s="14" t="inlineStr"/>
       <c r="AB284" s="14" t="inlineStr"/>
       <c r="AC284" s="15" t="n">
-        <v>0.9166666666666666</v>
+        <v>1.0</v>
       </c>
       <c r="AD284" s="15" t="inlineStr"/>
       <c r="AE284" s="14" t="n">
-        <v>360000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AF284" s="14" t="inlineStr"/>
       <c r="AG284" s="14" t="inlineStr"/>
       <c r="AH284" s="14" t="inlineStr"/>
       <c r="AI284" s="14" t="inlineStr"/>
     </row>
-    <row r="285" customHeight="1" ht="15">
+    <row r="285" customHeight="1" ht="18">
       <c r="A285" s="2" t="inlineStr"/>
       <c r="B285" s="2" t="inlineStr"/>
       <c r="C285" s="2" t="inlineStr"/>
@@ -17073,29 +17073,23 @@
       <c r="E285" s="2" t="inlineStr"/>
       <c r="F285" s="2" t="inlineStr"/>
       <c r="G285" s="2" t="inlineStr"/>
-      <c r="H285" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">521119</t>
-          </r>
-        </is>
-      </c>
-      <c r="I285" s="13" t="inlineStr"/>
-      <c r="J285" s="13" t="inlineStr"/>
-      <c r="K285" s="13" t="inlineStr"/>
-      <c r="L285" s="13" t="inlineStr"/>
-      <c r="M285" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
-          </r>
-        </is>
-      </c>
-      <c r="N285" s="13" t="inlineStr"/>
+      <c r="H285" s="2" t="inlineStr"/>
+      <c r="I285" s="2" t="inlineStr"/>
+      <c r="J285" s="2" t="inlineStr"/>
+      <c r="K285" s="2" t="inlineStr"/>
+      <c r="L285" s="2" t="inlineStr"/>
+      <c r="M285" s="2" t="inlineStr"/>
+      <c r="N285" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000203. Honorarium Pengurus/Penyimpan Bmn Tingkat Kuasa Pengguna Barang</t>
+          </r>
+        </is>
+      </c>
       <c r="O285" s="13" t="inlineStr"/>
       <c r="P285" s="13" t="inlineStr"/>
       <c r="Q285" s="14" t="n">
-        <v>7500000.0</v>
+        <v>4320000.0</v>
       </c>
       <c r="R285" s="14" t="inlineStr"/>
       <c r="S285" s="14" t="n">
@@ -17105,14 +17099,14 @@
       <c r="U285" s="14" t="inlineStr"/>
       <c r="V285" s="14" t="inlineStr"/>
       <c r="W285" s="14" t="n">
-        <v>7500000.0</v>
+        <v>3780000.0</v>
       </c>
       <c r="X285" s="14" t="n">
-        <v>0.0</v>
+        <v>540000.0</v>
       </c>
       <c r="Y285" s="14" t="inlineStr"/>
       <c r="Z285" s="14" t="n">
-        <v>7500000.0</v>
+        <v>4320000.0</v>
       </c>
       <c r="AA285" s="14" t="inlineStr"/>
       <c r="AB285" s="14" t="inlineStr"/>
@@ -17136,23 +17130,29 @@
       <c r="E286" s="2" t="inlineStr"/>
       <c r="F286" s="2" t="inlineStr"/>
       <c r="G286" s="2" t="inlineStr"/>
-      <c r="H286" s="2" t="inlineStr"/>
-      <c r="I286" s="2" t="inlineStr"/>
-      <c r="J286" s="2" t="inlineStr"/>
-      <c r="K286" s="2" t="inlineStr"/>
-      <c r="L286" s="2" t="inlineStr"/>
-      <c r="M286" s="2" t="inlineStr"/>
-      <c r="N286" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000243. Pakaian Kerja PJLP</t>
-          </r>
-        </is>
-      </c>
+      <c r="H286" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">521119</t>
+          </r>
+        </is>
+      </c>
+      <c r="I286" s="13" t="inlineStr"/>
+      <c r="J286" s="13" t="inlineStr"/>
+      <c r="K286" s="13" t="inlineStr"/>
+      <c r="L286" s="13" t="inlineStr"/>
+      <c r="M286" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Barang Operasional Lainnya</t>
+          </r>
+        </is>
+      </c>
+      <c r="N286" s="13" t="inlineStr"/>
       <c r="O286" s="13" t="inlineStr"/>
       <c r="P286" s="13" t="inlineStr"/>
       <c r="Q286" s="14" t="n">
-        <v>7500000.0</v>
+        <v>2.75E7</v>
       </c>
       <c r="R286" s="14" t="inlineStr"/>
       <c r="S286" s="14" t="n">
@@ -17165,20 +17165,20 @@
         <v>7500000.0</v>
       </c>
       <c r="X286" s="14" t="n">
-        <v>0.0</v>
+        <v>1.98E7</v>
       </c>
       <c r="Y286" s="14" t="inlineStr"/>
       <c r="Z286" s="14" t="n">
-        <v>7500000.0</v>
+        <v>2.73E7</v>
       </c>
       <c r="AA286" s="14" t="inlineStr"/>
       <c r="AB286" s="14" t="inlineStr"/>
       <c r="AC286" s="15" t="n">
-        <v>1.0</v>
+        <v>0.9927272727272727</v>
       </c>
       <c r="AD286" s="15" t="inlineStr"/>
       <c r="AE286" s="14" t="n">
-        <v>0.0</v>
+        <v>200000.0</v>
       </c>
       <c r="AF286" s="14" t="inlineStr"/>
       <c r="AG286" s="14" t="inlineStr"/>
@@ -17188,317 +17188,305 @@
     <row r="287" customHeight="1" ht="15">
       <c r="A287" s="2" t="inlineStr"/>
       <c r="B287" s="2" t="inlineStr"/>
-      <c r="C287" s="16" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">EBD</t>
-          </r>
-        </is>
-      </c>
-      <c r="D287" s="16" t="inlineStr"/>
-      <c r="E287" s="16" t="inlineStr"/>
-      <c r="F287" s="16" t="inlineStr"/>
-      <c r="G287" s="16" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Manajemen Kinerja Internal</t>
-          </r>
-        </is>
-      </c>
-      <c r="H287" s="16" t="inlineStr"/>
-      <c r="I287" s="16" t="inlineStr"/>
-      <c r="J287" s="16" t="inlineStr"/>
-      <c r="K287" s="16" t="inlineStr"/>
-      <c r="L287" s="16" t="inlineStr"/>
-      <c r="M287" s="16" t="inlineStr"/>
-      <c r="N287" s="16" t="inlineStr"/>
-      <c r="O287" s="16" t="inlineStr"/>
-      <c r="P287" s="16" t="inlineStr"/>
-      <c r="Q287" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="R287" s="17" t="inlineStr"/>
-      <c r="S287" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T287" s="17" t="inlineStr"/>
-      <c r="U287" s="17" t="inlineStr"/>
-      <c r="V287" s="17" t="inlineStr"/>
-      <c r="W287" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="X287" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y287" s="17" t="inlineStr"/>
-      <c r="Z287" s="17" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="AA287" s="17" t="inlineStr"/>
-      <c r="AB287" s="17" t="inlineStr"/>
-      <c r="AC287" s="18" t="n">
+      <c r="C287" s="2" t="inlineStr"/>
+      <c r="D287" s="2" t="inlineStr"/>
+      <c r="E287" s="2" t="inlineStr"/>
+      <c r="F287" s="2" t="inlineStr"/>
+      <c r="G287" s="2" t="inlineStr"/>
+      <c r="H287" s="2" t="inlineStr"/>
+      <c r="I287" s="2" t="inlineStr"/>
+      <c r="J287" s="2" t="inlineStr"/>
+      <c r="K287" s="2" t="inlineStr"/>
+      <c r="L287" s="2" t="inlineStr"/>
+      <c r="M287" s="2" t="inlineStr"/>
+      <c r="N287" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000243. Pakaian Kerja PJLP</t>
+          </r>
+        </is>
+      </c>
+      <c r="O287" s="13" t="inlineStr"/>
+      <c r="P287" s="13" t="inlineStr"/>
+      <c r="Q287" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="R287" s="14" t="inlineStr"/>
+      <c r="S287" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T287" s="14" t="inlineStr"/>
+      <c r="U287" s="14" t="inlineStr"/>
+      <c r="V287" s="14" t="inlineStr"/>
+      <c r="W287" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="X287" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y287" s="14" t="inlineStr"/>
+      <c r="Z287" s="14" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="AA287" s="14" t="inlineStr"/>
+      <c r="AB287" s="14" t="inlineStr"/>
+      <c r="AC287" s="15" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD287" s="18" t="inlineStr"/>
-      <c r="AE287" s="17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF287" s="17" t="inlineStr"/>
-      <c r="AG287" s="17" t="inlineStr"/>
-      <c r="AH287" s="17" t="inlineStr"/>
-      <c r="AI287" s="17" t="inlineStr"/>
+      <c r="AD287" s="15" t="inlineStr"/>
+      <c r="AE287" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF287" s="14" t="inlineStr"/>
+      <c r="AG287" s="14" t="inlineStr"/>
+      <c r="AH287" s="14" t="inlineStr"/>
+      <c r="AI287" s="14" t="inlineStr"/>
     </row>
     <row r="288" customHeight="1" ht="15">
       <c r="A288" s="2" t="inlineStr"/>
       <c r="B288" s="2" t="inlineStr"/>
-      <c r="C288" s="28" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">EBD.955</t>
-          </r>
-        </is>
-      </c>
-      <c r="D288" s="28" t="inlineStr"/>
-      <c r="E288" s="28" t="inlineStr"/>
-      <c r="F288" s="28" t="inlineStr"/>
-      <c r="G288" s="28" t="inlineStr"/>
-      <c r="H288" s="28" t="inlineStr"/>
-      <c r="I288" s="28" t="inlineStr"/>
-      <c r="J288" s="28" t="inlineStr"/>
-      <c r="K288" s="20" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Manajemen Keuangan</t>
-          </r>
-        </is>
-      </c>
-      <c r="L288" s="20" t="inlineStr"/>
-      <c r="M288" s="20" t="inlineStr"/>
-      <c r="N288" s="20" t="inlineStr"/>
-      <c r="O288" s="20" t="inlineStr"/>
-      <c r="P288" s="20" t="inlineStr"/>
-      <c r="Q288" s="21" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="R288" s="21" t="inlineStr"/>
-      <c r="S288" s="21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T288" s="21" t="inlineStr"/>
-      <c r="U288" s="21" t="inlineStr"/>
-      <c r="V288" s="21" t="inlineStr"/>
-      <c r="W288" s="22" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="X288" s="22" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y288" s="22" t="inlineStr"/>
-      <c r="Z288" s="21" t="n">
-        <v>600000.0</v>
-      </c>
-      <c r="AA288" s="21" t="inlineStr"/>
-      <c r="AB288" s="21" t="inlineStr"/>
-      <c r="AC288" s="23" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AD288" s="23" t="inlineStr"/>
-      <c r="AE288" s="21" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF288" s="21" t="inlineStr"/>
-      <c r="AG288" s="21" t="inlineStr"/>
-      <c r="AH288" s="21" t="inlineStr"/>
-      <c r="AI288" s="21" t="inlineStr"/>
+      <c r="C288" s="2" t="inlineStr"/>
+      <c r="D288" s="2" t="inlineStr"/>
+      <c r="E288" s="2" t="inlineStr"/>
+      <c r="F288" s="2" t="inlineStr"/>
+      <c r="G288" s="2" t="inlineStr"/>
+      <c r="H288" s="2" t="inlineStr"/>
+      <c r="I288" s="2" t="inlineStr"/>
+      <c r="J288" s="2" t="inlineStr"/>
+      <c r="K288" s="2" t="inlineStr"/>
+      <c r="L288" s="2" t="inlineStr"/>
+      <c r="M288" s="2" t="inlineStr"/>
+      <c r="N288" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000309. Pakaian Lapangan</t>
+          </r>
+        </is>
+      </c>
+      <c r="O288" s="13" t="inlineStr"/>
+      <c r="P288" s="13" t="inlineStr"/>
+      <c r="Q288" s="14" t="n">
+        <v>2.0E7</v>
+      </c>
+      <c r="R288" s="14" t="inlineStr"/>
+      <c r="S288" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T288" s="14" t="inlineStr"/>
+      <c r="U288" s="14" t="inlineStr"/>
+      <c r="V288" s="14" t="inlineStr"/>
+      <c r="W288" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X288" s="14" t="n">
+        <v>1.98E7</v>
+      </c>
+      <c r="Y288" s="14" t="inlineStr"/>
+      <c r="Z288" s="14" t="n">
+        <v>1.98E7</v>
+      </c>
+      <c r="AA288" s="14" t="inlineStr"/>
+      <c r="AB288" s="14" t="inlineStr"/>
+      <c r="AC288" s="15" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AD288" s="15" t="inlineStr"/>
+      <c r="AE288" s="14" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="AF288" s="14" t="inlineStr"/>
+      <c r="AG288" s="14" t="inlineStr"/>
+      <c r="AH288" s="14" t="inlineStr"/>
+      <c r="AI288" s="14" t="inlineStr"/>
     </row>
     <row r="289" customHeight="1" ht="15">
       <c r="A289" s="2" t="inlineStr"/>
       <c r="B289" s="2" t="inlineStr"/>
-      <c r="C289" s="2" t="inlineStr"/>
-      <c r="D289" s="2" t="inlineStr"/>
-      <c r="E289" s="24" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">201</t>
-          </r>
-        </is>
-      </c>
-      <c r="F289" s="24" t="inlineStr"/>
-      <c r="G289" s="24" t="inlineStr"/>
-      <c r="H289" s="24" t="inlineStr"/>
-      <c r="I289" s="24" t="inlineStr"/>
-      <c r="J289" s="24" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pelayanan Keuangan Penyuluhan Kelautan dan Perikanan</t>
-          </r>
-        </is>
-      </c>
-      <c r="K289" s="24" t="inlineStr"/>
-      <c r="L289" s="24" t="inlineStr"/>
-      <c r="M289" s="24" t="inlineStr"/>
-      <c r="N289" s="24" t="inlineStr"/>
-      <c r="O289" s="24" t="inlineStr"/>
-      <c r="P289" s="24" t="inlineStr"/>
-      <c r="Q289" s="25" t="n">
+      <c r="C289" s="16" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">EBD</t>
+          </r>
+        </is>
+      </c>
+      <c r="D289" s="16" t="inlineStr"/>
+      <c r="E289" s="16" t="inlineStr"/>
+      <c r="F289" s="16" t="inlineStr"/>
+      <c r="G289" s="16" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Manajemen Kinerja Internal</t>
+          </r>
+        </is>
+      </c>
+      <c r="H289" s="16" t="inlineStr"/>
+      <c r="I289" s="16" t="inlineStr"/>
+      <c r="J289" s="16" t="inlineStr"/>
+      <c r="K289" s="16" t="inlineStr"/>
+      <c r="L289" s="16" t="inlineStr"/>
+      <c r="M289" s="16" t="inlineStr"/>
+      <c r="N289" s="16" t="inlineStr"/>
+      <c r="O289" s="16" t="inlineStr"/>
+      <c r="P289" s="16" t="inlineStr"/>
+      <c r="Q289" s="17" t="n">
         <v>600000.0</v>
       </c>
-      <c r="R289" s="25" t="inlineStr"/>
-      <c r="S289" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T289" s="25" t="inlineStr"/>
-      <c r="U289" s="25" t="inlineStr"/>
-      <c r="V289" s="25" t="inlineStr"/>
-      <c r="W289" s="25" t="n">
+      <c r="R289" s="17" t="inlineStr"/>
+      <c r="S289" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T289" s="17" t="inlineStr"/>
+      <c r="U289" s="17" t="inlineStr"/>
+      <c r="V289" s="17" t="inlineStr"/>
+      <c r="W289" s="17" t="n">
         <v>600000.0</v>
       </c>
-      <c r="X289" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y289" s="25" t="inlineStr"/>
-      <c r="Z289" s="25" t="n">
+      <c r="X289" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y289" s="17" t="inlineStr"/>
+      <c r="Z289" s="17" t="n">
         <v>600000.0</v>
       </c>
-      <c r="AA289" s="25" t="inlineStr"/>
-      <c r="AB289" s="25" t="inlineStr"/>
-      <c r="AC289" s="26" t="n">
+      <c r="AA289" s="17" t="inlineStr"/>
+      <c r="AB289" s="17" t="inlineStr"/>
+      <c r="AC289" s="18" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD289" s="26" t="inlineStr"/>
-      <c r="AE289" s="25" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF289" s="25" t="inlineStr"/>
-      <c r="AG289" s="25" t="inlineStr"/>
-      <c r="AH289" s="25" t="inlineStr"/>
-      <c r="AI289" s="25" t="inlineStr"/>
+      <c r="AD289" s="18" t="inlineStr"/>
+      <c r="AE289" s="17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF289" s="17" t="inlineStr"/>
+      <c r="AG289" s="17" t="inlineStr"/>
+      <c r="AH289" s="17" t="inlineStr"/>
+      <c r="AI289" s="17" t="inlineStr"/>
     </row>
     <row r="290" customHeight="1" ht="15">
       <c r="A290" s="2" t="inlineStr"/>
       <c r="B290" s="2" t="inlineStr"/>
-      <c r="C290" s="2" t="inlineStr"/>
-      <c r="D290" s="2" t="inlineStr"/>
-      <c r="E290" s="2" t="inlineStr"/>
-      <c r="F290" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">201.DA</t>
-          </r>
-        </is>
-      </c>
-      <c r="G290" s="13" t="inlineStr"/>
-      <c r="H290" s="13" t="inlineStr"/>
-      <c r="I290" s="13" t="inlineStr"/>
-      <c r="J290" s="13" t="inlineStr"/>
-      <c r="K290" s="13" t="inlineStr"/>
-      <c r="L290" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Layanan Keuangan</t>
-          </r>
-        </is>
-      </c>
-      <c r="M290" s="13" t="inlineStr"/>
-      <c r="N290" s="13" t="inlineStr"/>
-      <c r="O290" s="13" t="inlineStr"/>
-      <c r="P290" s="13" t="inlineStr"/>
-      <c r="Q290" s="14" t="n">
+      <c r="C290" s="28" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">EBD.955</t>
+          </r>
+        </is>
+      </c>
+      <c r="D290" s="28" t="inlineStr"/>
+      <c r="E290" s="28" t="inlineStr"/>
+      <c r="F290" s="28" t="inlineStr"/>
+      <c r="G290" s="28" t="inlineStr"/>
+      <c r="H290" s="28" t="inlineStr"/>
+      <c r="I290" s="28" t="inlineStr"/>
+      <c r="J290" s="28" t="inlineStr"/>
+      <c r="K290" s="20" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Manajemen Keuangan</t>
+          </r>
+        </is>
+      </c>
+      <c r="L290" s="20" t="inlineStr"/>
+      <c r="M290" s="20" t="inlineStr"/>
+      <c r="N290" s="20" t="inlineStr"/>
+      <c r="O290" s="20" t="inlineStr"/>
+      <c r="P290" s="20" t="inlineStr"/>
+      <c r="Q290" s="21" t="n">
         <v>600000.0</v>
       </c>
-      <c r="R290" s="14" t="inlineStr"/>
-      <c r="S290" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T290" s="14" t="inlineStr"/>
-      <c r="U290" s="14" t="inlineStr"/>
-      <c r="V290" s="14" t="inlineStr"/>
-      <c r="W290" s="14" t="n">
+      <c r="R290" s="21" t="inlineStr"/>
+      <c r="S290" s="21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T290" s="21" t="inlineStr"/>
+      <c r="U290" s="21" t="inlineStr"/>
+      <c r="V290" s="21" t="inlineStr"/>
+      <c r="W290" s="22" t="n">
         <v>600000.0</v>
       </c>
-      <c r="X290" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y290" s="14" t="inlineStr"/>
-      <c r="Z290" s="14" t="n">
+      <c r="X290" s="22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y290" s="22" t="inlineStr"/>
+      <c r="Z290" s="21" t="n">
         <v>600000.0</v>
       </c>
-      <c r="AA290" s="14" t="inlineStr"/>
-      <c r="AB290" s="14" t="inlineStr"/>
-      <c r="AC290" s="15" t="n">
+      <c r="AA290" s="21" t="inlineStr"/>
+      <c r="AB290" s="21" t="inlineStr"/>
+      <c r="AC290" s="23" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD290" s="15" t="inlineStr"/>
-      <c r="AE290" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF290" s="14" t="inlineStr"/>
-      <c r="AG290" s="14" t="inlineStr"/>
-      <c r="AH290" s="14" t="inlineStr"/>
-      <c r="AI290" s="14" t="inlineStr"/>
+      <c r="AD290" s="23" t="inlineStr"/>
+      <c r="AE290" s="21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF290" s="21" t="inlineStr"/>
+      <c r="AG290" s="21" t="inlineStr"/>
+      <c r="AH290" s="21" t="inlineStr"/>
+      <c r="AI290" s="21" t="inlineStr"/>
     </row>
     <row r="291" customHeight="1" ht="15">
       <c r="A291" s="2" t="inlineStr"/>
       <c r="B291" s="2" t="inlineStr"/>
       <c r="C291" s="2" t="inlineStr"/>
       <c r="D291" s="2" t="inlineStr"/>
-      <c r="E291" s="2" t="inlineStr"/>
-      <c r="F291" s="2" t="inlineStr"/>
-      <c r="G291" s="2" t="inlineStr"/>
-      <c r="H291" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">524111</t>
-          </r>
-        </is>
-      </c>
-      <c r="I291" s="13" t="inlineStr"/>
-      <c r="J291" s="13" t="inlineStr"/>
-      <c r="K291" s="13" t="inlineStr"/>
-      <c r="L291" s="13" t="inlineStr"/>
-      <c r="M291" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Belanja Perjalanan Dinas Biasa</t>
-          </r>
-        </is>
-      </c>
-      <c r="N291" s="13" t="inlineStr"/>
-      <c r="O291" s="13" t="inlineStr"/>
-      <c r="P291" s="13" t="inlineStr"/>
-      <c r="Q291" s="14" t="n">
+      <c r="E291" s="24" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">201</t>
+          </r>
+        </is>
+      </c>
+      <c r="F291" s="24" t="inlineStr"/>
+      <c r="G291" s="24" t="inlineStr"/>
+      <c r="H291" s="24" t="inlineStr"/>
+      <c r="I291" s="24" t="inlineStr"/>
+      <c r="J291" s="24" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pelayanan Keuangan Penyuluhan Kelautan dan Perikanan</t>
+          </r>
+        </is>
+      </c>
+      <c r="K291" s="24" t="inlineStr"/>
+      <c r="L291" s="24" t="inlineStr"/>
+      <c r="M291" s="24" t="inlineStr"/>
+      <c r="N291" s="24" t="inlineStr"/>
+      <c r="O291" s="24" t="inlineStr"/>
+      <c r="P291" s="24" t="inlineStr"/>
+      <c r="Q291" s="25" t="n">
         <v>600000.0</v>
       </c>
-      <c r="R291" s="14" t="inlineStr"/>
-      <c r="S291" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="T291" s="14" t="inlineStr"/>
-      <c r="U291" s="14" t="inlineStr"/>
-      <c r="V291" s="14" t="inlineStr"/>
-      <c r="W291" s="14" t="n">
+      <c r="R291" s="25" t="inlineStr"/>
+      <c r="S291" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T291" s="25" t="inlineStr"/>
+      <c r="U291" s="25" t="inlineStr"/>
+      <c r="V291" s="25" t="inlineStr"/>
+      <c r="W291" s="25" t="n">
         <v>600000.0</v>
       </c>
-      <c r="X291" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Y291" s="14" t="inlineStr"/>
-      <c r="Z291" s="14" t="n">
+      <c r="X291" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y291" s="25" t="inlineStr"/>
+      <c r="Z291" s="25" t="n">
         <v>600000.0</v>
       </c>
-      <c r="AA291" s="14" t="inlineStr"/>
-      <c r="AB291" s="14" t="inlineStr"/>
-      <c r="AC291" s="15" t="n">
+      <c r="AA291" s="25" t="inlineStr"/>
+      <c r="AB291" s="25" t="inlineStr"/>
+      <c r="AC291" s="26" t="n">
         <v>1.0</v>
       </c>
-      <c r="AD291" s="15" t="inlineStr"/>
-      <c r="AE291" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF291" s="14" t="inlineStr"/>
-      <c r="AG291" s="14" t="inlineStr"/>
-      <c r="AH291" s="14" t="inlineStr"/>
-      <c r="AI291" s="14" t="inlineStr"/>
+      <c r="AD291" s="26" t="inlineStr"/>
+      <c r="AE291" s="25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF291" s="25" t="inlineStr"/>
+      <c r="AG291" s="25" t="inlineStr"/>
+      <c r="AH291" s="25" t="inlineStr"/>
+      <c r="AI291" s="25" t="inlineStr"/>
     </row>
     <row r="292" customHeight="1" ht="15">
       <c r="A292" s="2" t="inlineStr"/>
@@ -17506,21 +17494,27 @@
       <c r="C292" s="2" t="inlineStr"/>
       <c r="D292" s="2" t="inlineStr"/>
       <c r="E292" s="2" t="inlineStr"/>
-      <c r="F292" s="2" t="inlineStr"/>
-      <c r="G292" s="2" t="inlineStr"/>
-      <c r="H292" s="2" t="inlineStr"/>
-      <c r="I292" s="2" t="inlineStr"/>
-      <c r="J292" s="2" t="inlineStr"/>
-      <c r="K292" s="2" t="inlineStr"/>
-      <c r="L292" s="2" t="inlineStr"/>
-      <c r="M292" s="2" t="inlineStr"/>
-      <c r="N292" s="13" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">000231. Uang Harian</t>
-          </r>
-        </is>
-      </c>
+      <c r="F292" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">201.DA</t>
+          </r>
+        </is>
+      </c>
+      <c r="G292" s="13" t="inlineStr"/>
+      <c r="H292" s="13" t="inlineStr"/>
+      <c r="I292" s="13" t="inlineStr"/>
+      <c r="J292" s="13" t="inlineStr"/>
+      <c r="K292" s="13" t="inlineStr"/>
+      <c r="L292" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Layanan Keuangan</t>
+          </r>
+        </is>
+      </c>
+      <c r="M292" s="13" t="inlineStr"/>
+      <c r="N292" s="13" t="inlineStr"/>
       <c r="O292" s="13" t="inlineStr"/>
       <c r="P292" s="13" t="inlineStr"/>
       <c r="Q292" s="14" t="n">
@@ -17557,48 +17551,168 @@
       <c r="AH292" s="14" t="inlineStr"/>
       <c r="AI292" s="14" t="inlineStr"/>
     </row>
-    <row r="293" customHeight="1" ht="12">
+    <row r="293" customHeight="1" ht="15">
       <c r="A293" s="2" t="inlineStr"/>
-      <c r="B293" s="27" t="inlineStr">
+      <c r="B293" s="2" t="inlineStr"/>
+      <c r="C293" s="2" t="inlineStr"/>
+      <c r="D293" s="2" t="inlineStr"/>
+      <c r="E293" s="2" t="inlineStr"/>
+      <c r="F293" s="2" t="inlineStr"/>
+      <c r="G293" s="2" t="inlineStr"/>
+      <c r="H293" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">524111</t>
+          </r>
+        </is>
+      </c>
+      <c r="I293" s="13" t="inlineStr"/>
+      <c r="J293" s="13" t="inlineStr"/>
+      <c r="K293" s="13" t="inlineStr"/>
+      <c r="L293" s="13" t="inlineStr"/>
+      <c r="M293" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Belanja Perjalanan Dinas Biasa</t>
+          </r>
+        </is>
+      </c>
+      <c r="N293" s="13" t="inlineStr"/>
+      <c r="O293" s="13" t="inlineStr"/>
+      <c r="P293" s="13" t="inlineStr"/>
+      <c r="Q293" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R293" s="14" t="inlineStr"/>
+      <c r="S293" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T293" s="14" t="inlineStr"/>
+      <c r="U293" s="14" t="inlineStr"/>
+      <c r="V293" s="14" t="inlineStr"/>
+      <c r="W293" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X293" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y293" s="14" t="inlineStr"/>
+      <c r="Z293" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA293" s="14" t="inlineStr"/>
+      <c r="AB293" s="14" t="inlineStr"/>
+      <c r="AC293" s="15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD293" s="15" t="inlineStr"/>
+      <c r="AE293" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF293" s="14" t="inlineStr"/>
+      <c r="AG293" s="14" t="inlineStr"/>
+      <c r="AH293" s="14" t="inlineStr"/>
+      <c r="AI293" s="14" t="inlineStr"/>
+    </row>
+    <row r="294" customHeight="1" ht="15">
+      <c r="A294" s="2" t="inlineStr"/>
+      <c r="B294" s="2" t="inlineStr"/>
+      <c r="C294" s="2" t="inlineStr"/>
+      <c r="D294" s="2" t="inlineStr"/>
+      <c r="E294" s="2" t="inlineStr"/>
+      <c r="F294" s="2" t="inlineStr"/>
+      <c r="G294" s="2" t="inlineStr"/>
+      <c r="H294" s="2" t="inlineStr"/>
+      <c r="I294" s="2" t="inlineStr"/>
+      <c r="J294" s="2" t="inlineStr"/>
+      <c r="K294" s="2" t="inlineStr"/>
+      <c r="L294" s="2" t="inlineStr"/>
+      <c r="M294" s="2" t="inlineStr"/>
+      <c r="N294" s="13" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">000231. Uang Harian</t>
+          </r>
+        </is>
+      </c>
+      <c r="O294" s="13" t="inlineStr"/>
+      <c r="P294" s="13" t="inlineStr"/>
+      <c r="Q294" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="R294" s="14" t="inlineStr"/>
+      <c r="S294" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T294" s="14" t="inlineStr"/>
+      <c r="U294" s="14" t="inlineStr"/>
+      <c r="V294" s="14" t="inlineStr"/>
+      <c r="W294" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="X294" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y294" s="14" t="inlineStr"/>
+      <c r="Z294" s="14" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="AA294" s="14" t="inlineStr"/>
+      <c r="AB294" s="14" t="inlineStr"/>
+      <c r="AC294" s="15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AD294" s="15" t="inlineStr"/>
+      <c r="AE294" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF294" s="14" t="inlineStr"/>
+      <c r="AG294" s="14" t="inlineStr"/>
+      <c r="AH294" s="14" t="inlineStr"/>
+      <c r="AI294" s="14" t="inlineStr"/>
+    </row>
+    <row r="295" customHeight="1" ht="12">
+      <c r="A295" s="2" t="inlineStr"/>
+      <c r="B295" s="27" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">*Lock Pagu adalah jumlah pagu yang sedang dalam proses usulan revisi DIPA atau POK. Lock pagu akan hilang setelah usulan revisi DIPA/POK selesai menjadi DIPA.</t>
           </r>
         </is>
       </c>
-      <c r="C293" s="27" t="inlineStr"/>
-      <c r="D293" s="27" t="inlineStr"/>
-      <c r="E293" s="27" t="inlineStr"/>
-      <c r="F293" s="27" t="inlineStr"/>
-      <c r="G293" s="27" t="inlineStr"/>
-      <c r="H293" s="27" t="inlineStr"/>
-      <c r="I293" s="27" t="inlineStr"/>
-      <c r="J293" s="27" t="inlineStr"/>
-      <c r="K293" s="27" t="inlineStr"/>
-      <c r="L293" s="27" t="inlineStr"/>
-      <c r="M293" s="27" t="inlineStr"/>
-      <c r="N293" s="27" t="inlineStr"/>
-      <c r="O293" s="27" t="inlineStr"/>
-      <c r="P293" s="27" t="inlineStr"/>
-      <c r="Q293" s="27" t="inlineStr"/>
-      <c r="R293" s="27" t="inlineStr"/>
-      <c r="S293" s="27" t="inlineStr"/>
-      <c r="T293" s="27" t="inlineStr"/>
-      <c r="U293" s="27" t="inlineStr"/>
-      <c r="V293" s="27" t="inlineStr"/>
-      <c r="W293" s="27" t="inlineStr"/>
-      <c r="X293" s="27" t="inlineStr"/>
-      <c r="Y293" s="27" t="inlineStr"/>
-      <c r="Z293" s="27" t="inlineStr"/>
-      <c r="AA293" s="27" t="inlineStr"/>
-      <c r="AB293" s="27" t="inlineStr"/>
-      <c r="AC293" s="27" t="inlineStr"/>
-      <c r="AD293" s="27" t="inlineStr"/>
-      <c r="AE293" s="27" t="inlineStr"/>
-      <c r="AF293" s="27" t="inlineStr"/>
-      <c r="AG293" s="2" t="inlineStr"/>
-      <c r="AH293" s="2" t="inlineStr"/>
-      <c r="AI293" s="2" t="inlineStr"/>
+      <c r="C295" s="27" t="inlineStr"/>
+      <c r="D295" s="27" t="inlineStr"/>
+      <c r="E295" s="27" t="inlineStr"/>
+      <c r="F295" s="27" t="inlineStr"/>
+      <c r="G295" s="27" t="inlineStr"/>
+      <c r="H295" s="27" t="inlineStr"/>
+      <c r="I295" s="27" t="inlineStr"/>
+      <c r="J295" s="27" t="inlineStr"/>
+      <c r="K295" s="27" t="inlineStr"/>
+      <c r="L295" s="27" t="inlineStr"/>
+      <c r="M295" s="27" t="inlineStr"/>
+      <c r="N295" s="27" t="inlineStr"/>
+      <c r="O295" s="27" t="inlineStr"/>
+      <c r="P295" s="27" t="inlineStr"/>
+      <c r="Q295" s="27" t="inlineStr"/>
+      <c r="R295" s="27" t="inlineStr"/>
+      <c r="S295" s="27" t="inlineStr"/>
+      <c r="T295" s="27" t="inlineStr"/>
+      <c r="U295" s="27" t="inlineStr"/>
+      <c r="V295" s="27" t="inlineStr"/>
+      <c r="W295" s="27" t="inlineStr"/>
+      <c r="X295" s="27" t="inlineStr"/>
+      <c r="Y295" s="27" t="inlineStr"/>
+      <c r="Z295" s="27" t="inlineStr"/>
+      <c r="AA295" s="27" t="inlineStr"/>
+      <c r="AB295" s="27" t="inlineStr"/>
+      <c r="AC295" s="27" t="inlineStr"/>
+      <c r="AD295" s="27" t="inlineStr"/>
+      <c r="AE295" s="27" t="inlineStr"/>
+      <c r="AF295" s="27" t="inlineStr"/>
+      <c r="AG295" s="2" t="inlineStr"/>
+      <c r="AH295" s="2" t="inlineStr"/>
+      <c r="AI295" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -19361,8 +19475,7 @@
     <mergeCell ref="Z252:AB252"/>
     <mergeCell ref="AC252:AD252"/>
     <mergeCell ref="AE252:AI252"/>
-    <mergeCell ref="H253:L253"/>
-    <mergeCell ref="M253:P253"/>
+    <mergeCell ref="N253:P253"/>
     <mergeCell ref="Q253:R253"/>
     <mergeCell ref="S253:V253"/>
     <mergeCell ref="X253:Y253"/>
@@ -19370,7 +19483,8 @@
     <mergeCell ref="AC253:AD253"/>
     <mergeCell ref="AE253:AI253"/>
     <mergeCell ref="B254:AF254"/>
-    <mergeCell ref="N255:P255"/>
+    <mergeCell ref="H255:L255"/>
+    <mergeCell ref="M255:P255"/>
     <mergeCell ref="Q255:R255"/>
     <mergeCell ref="S255:V255"/>
     <mergeCell ref="X255:Y255"/>
@@ -19482,15 +19596,15 @@
     <mergeCell ref="Z270:AB270"/>
     <mergeCell ref="AC270:AD270"/>
     <mergeCell ref="AE270:AI270"/>
-    <mergeCell ref="H271:L271"/>
-    <mergeCell ref="M271:P271"/>
+    <mergeCell ref="N271:P271"/>
     <mergeCell ref="Q271:R271"/>
     <mergeCell ref="S271:V271"/>
     <mergeCell ref="X271:Y271"/>
     <mergeCell ref="Z271:AB271"/>
     <mergeCell ref="AC271:AD271"/>
     <mergeCell ref="AE271:AI271"/>
-    <mergeCell ref="N272:P272"/>
+    <mergeCell ref="H272:L272"/>
+    <mergeCell ref="M272:P272"/>
     <mergeCell ref="Q272:R272"/>
     <mergeCell ref="S272:V272"/>
     <mergeCell ref="X272:Y272"/>
@@ -19511,23 +19625,23 @@
     <mergeCell ref="Z274:AB274"/>
     <mergeCell ref="AC274:AD274"/>
     <mergeCell ref="AE274:AI274"/>
-    <mergeCell ref="F275:K275"/>
-    <mergeCell ref="L275:P275"/>
+    <mergeCell ref="N275:P275"/>
     <mergeCell ref="Q275:R275"/>
     <mergeCell ref="S275:V275"/>
     <mergeCell ref="X275:Y275"/>
     <mergeCell ref="Z275:AB275"/>
     <mergeCell ref="AC275:AD275"/>
     <mergeCell ref="AE275:AI275"/>
-    <mergeCell ref="H276:L276"/>
-    <mergeCell ref="M276:P276"/>
+    <mergeCell ref="F276:K276"/>
+    <mergeCell ref="L276:P276"/>
     <mergeCell ref="Q276:R276"/>
     <mergeCell ref="S276:V276"/>
     <mergeCell ref="X276:Y276"/>
     <mergeCell ref="Z276:AB276"/>
     <mergeCell ref="AC276:AD276"/>
     <mergeCell ref="AE276:AI276"/>
-    <mergeCell ref="N277:P277"/>
+    <mergeCell ref="H277:L277"/>
+    <mergeCell ref="M277:P277"/>
     <mergeCell ref="Q277:R277"/>
     <mergeCell ref="S277:V277"/>
     <mergeCell ref="X277:Y277"/>
@@ -19577,69 +19691,83 @@
     <mergeCell ref="Z284:AB284"/>
     <mergeCell ref="AC284:AD284"/>
     <mergeCell ref="AE284:AI284"/>
-    <mergeCell ref="H285:L285"/>
-    <mergeCell ref="M285:P285"/>
+    <mergeCell ref="N285:P285"/>
     <mergeCell ref="Q285:R285"/>
     <mergeCell ref="S285:V285"/>
     <mergeCell ref="X285:Y285"/>
     <mergeCell ref="Z285:AB285"/>
     <mergeCell ref="AC285:AD285"/>
     <mergeCell ref="AE285:AI285"/>
-    <mergeCell ref="N286:P286"/>
+    <mergeCell ref="H286:L286"/>
+    <mergeCell ref="M286:P286"/>
     <mergeCell ref="Q286:R286"/>
     <mergeCell ref="S286:V286"/>
     <mergeCell ref="X286:Y286"/>
     <mergeCell ref="Z286:AB286"/>
     <mergeCell ref="AC286:AD286"/>
     <mergeCell ref="AE286:AI286"/>
-    <mergeCell ref="C287:F287"/>
-    <mergeCell ref="G287:P287"/>
+    <mergeCell ref="N287:P287"/>
     <mergeCell ref="Q287:R287"/>
     <mergeCell ref="S287:V287"/>
     <mergeCell ref="X287:Y287"/>
     <mergeCell ref="Z287:AB287"/>
     <mergeCell ref="AC287:AD287"/>
     <mergeCell ref="AE287:AI287"/>
-    <mergeCell ref="C288:J288"/>
-    <mergeCell ref="K288:P288"/>
+    <mergeCell ref="N288:P288"/>
     <mergeCell ref="Q288:R288"/>
     <mergeCell ref="S288:V288"/>
     <mergeCell ref="X288:Y288"/>
     <mergeCell ref="Z288:AB288"/>
     <mergeCell ref="AC288:AD288"/>
     <mergeCell ref="AE288:AI288"/>
-    <mergeCell ref="E289:I289"/>
-    <mergeCell ref="J289:P289"/>
+    <mergeCell ref="C289:F289"/>
+    <mergeCell ref="G289:P289"/>
     <mergeCell ref="Q289:R289"/>
     <mergeCell ref="S289:V289"/>
     <mergeCell ref="X289:Y289"/>
     <mergeCell ref="Z289:AB289"/>
     <mergeCell ref="AC289:AD289"/>
     <mergeCell ref="AE289:AI289"/>
-    <mergeCell ref="F290:K290"/>
-    <mergeCell ref="L290:P290"/>
+    <mergeCell ref="C290:J290"/>
+    <mergeCell ref="K290:P290"/>
     <mergeCell ref="Q290:R290"/>
     <mergeCell ref="S290:V290"/>
     <mergeCell ref="X290:Y290"/>
     <mergeCell ref="Z290:AB290"/>
     <mergeCell ref="AC290:AD290"/>
     <mergeCell ref="AE290:AI290"/>
-    <mergeCell ref="H291:L291"/>
-    <mergeCell ref="M291:P291"/>
+    <mergeCell ref="E291:I291"/>
+    <mergeCell ref="J291:P291"/>
     <mergeCell ref="Q291:R291"/>
     <mergeCell ref="S291:V291"/>
     <mergeCell ref="X291:Y291"/>
     <mergeCell ref="Z291:AB291"/>
     <mergeCell ref="AC291:AD291"/>
     <mergeCell ref="AE291:AI291"/>
-    <mergeCell ref="N292:P292"/>
+    <mergeCell ref="F292:K292"/>
+    <mergeCell ref="L292:P292"/>
     <mergeCell ref="Q292:R292"/>
     <mergeCell ref="S292:V292"/>
     <mergeCell ref="X292:Y292"/>
     <mergeCell ref="Z292:AB292"/>
     <mergeCell ref="AC292:AD292"/>
     <mergeCell ref="AE292:AI292"/>
-    <mergeCell ref="B293:AF293"/>
+    <mergeCell ref="H293:L293"/>
+    <mergeCell ref="M293:P293"/>
+    <mergeCell ref="Q293:R293"/>
+    <mergeCell ref="S293:V293"/>
+    <mergeCell ref="X293:Y293"/>
+    <mergeCell ref="Z293:AB293"/>
+    <mergeCell ref="AC293:AD293"/>
+    <mergeCell ref="AE293:AI293"/>
+    <mergeCell ref="N294:P294"/>
+    <mergeCell ref="Q294:R294"/>
+    <mergeCell ref="S294:V294"/>
+    <mergeCell ref="X294:Y294"/>
+    <mergeCell ref="Z294:AB294"/>
+    <mergeCell ref="AC294:AD294"/>
+    <mergeCell ref="AE294:AI294"/>
+    <mergeCell ref="B295:AF295"/>
   </mergeCells>
   <pageMargins left="0.0" right="0.0" top="0.0" bottom="0.00" header="0.0" footer="0.0"/>
   <pageSetup orientation="landscape" paperSize="9"/>

--- a/Database/Akrual.xlsx
+++ b/Database/Akrual.xlsx
@@ -982,19 +982,19 @@
         <v>9.0559784495E10</v>
       </c>
       <c r="X9" s="11" t="n">
-        <v>8.096493585E9</v>
+        <v>8.742642945E9</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>9.865627808E10</v>
+        <v>9.930242744E10</v>
       </c>
       <c r="Z9" s="10" t="inlineStr"/>
       <c r="AA9" s="10" t="inlineStr"/>
       <c r="AB9" s="10" t="inlineStr"/>
       <c r="AC9" s="12" t="n">
-        <v>0.986601869966088</v>
+        <v>0.9930636195806077</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>1.33975992E9</v>
+        <v>6.9361056E8</v>
       </c>
       <c r="AE9" s="10" t="inlineStr"/>
       <c r="AF9" s="10" t="inlineStr"/>
@@ -1714,20 +1714,20 @@
         <v>8.6526416455E10</v>
       </c>
       <c r="X21" s="14" t="n">
-        <v>8.096493585E9</v>
+        <v>8.742642945E9</v>
       </c>
       <c r="Y21" s="14" t="inlineStr"/>
       <c r="Z21" s="14" t="n">
-        <v>9.462291004E10</v>
+        <v>9.52690594E10</v>
       </c>
       <c r="AA21" s="14" t="inlineStr"/>
       <c r="AB21" s="14" t="inlineStr"/>
       <c r="AC21" s="15" t="n">
-        <v>0.9860390669960531</v>
+        <v>0.9927724100289949</v>
       </c>
       <c r="AD21" s="15" t="inlineStr"/>
       <c r="AE21" s="14" t="n">
-        <v>1.33972796E9</v>
+        <v>6.935786E8</v>
       </c>
       <c r="AF21" s="14" t="inlineStr"/>
       <c r="AG21" s="14" t="inlineStr"/>
@@ -1777,20 +1777,20 @@
         <v>8.6526416455E10</v>
       </c>
       <c r="X22" s="14" t="n">
-        <v>8.096493585E9</v>
+        <v>8.742642945E9</v>
       </c>
       <c r="Y22" s="14" t="inlineStr"/>
       <c r="Z22" s="14" t="n">
-        <v>9.462291004E10</v>
+        <v>9.52690594E10</v>
       </c>
       <c r="AA22" s="14" t="inlineStr"/>
       <c r="AB22" s="14" t="inlineStr"/>
       <c r="AC22" s="15" t="n">
-        <v>0.9860390669960531</v>
+        <v>0.9927724100289949</v>
       </c>
       <c r="AD22" s="15" t="inlineStr"/>
       <c r="AE22" s="14" t="n">
-        <v>1.33972796E9</v>
+        <v>6.935786E8</v>
       </c>
       <c r="AF22" s="14" t="inlineStr"/>
       <c r="AG22" s="14" t="inlineStr"/>
@@ -1840,20 +1840,20 @@
         <v>8.6525816455E10</v>
       </c>
       <c r="X23" s="17" t="n">
-        <v>8.096493585E9</v>
+        <v>8.742642945E9</v>
       </c>
       <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="17" t="n">
-        <v>9.462231004E10</v>
+        <v>9.52684594E10</v>
       </c>
       <c r="AA23" s="17" t="inlineStr"/>
       <c r="AB23" s="17" t="inlineStr"/>
       <c r="AC23" s="18" t="n">
-        <v>0.9860389797057041</v>
+        <v>0.9927723648386876</v>
       </c>
       <c r="AD23" s="18" t="inlineStr"/>
       <c r="AE23" s="17" t="n">
-        <v>1.33972796E9</v>
+        <v>6.935786E8</v>
       </c>
       <c r="AF23" s="17" t="inlineStr"/>
       <c r="AG23" s="17" t="inlineStr"/>
@@ -3233,20 +3233,20 @@
         <v>8.6508305403E10</v>
       </c>
       <c r="X46" s="22" t="n">
-        <v>8.095693585E9</v>
+        <v>8.741842945E9</v>
       </c>
       <c r="Y46" s="22" t="inlineStr"/>
       <c r="Z46" s="21" t="n">
-        <v>9.4603998988E10</v>
+        <v>9.5250148348E10</v>
       </c>
       <c r="AA46" s="21" t="inlineStr"/>
       <c r="AB46" s="21" t="inlineStr"/>
       <c r="AC46" s="23" t="n">
-        <v>0.9860385654024658</v>
+        <v>0.9927732509843188</v>
       </c>
       <c r="AD46" s="23" t="inlineStr"/>
       <c r="AE46" s="21" t="n">
-        <v>1.339509012E9</v>
+        <v>6.93359652E8</v>
       </c>
       <c r="AF46" s="21" t="inlineStr"/>
       <c r="AG46" s="21" t="inlineStr"/>
@@ -3296,20 +3296,20 @@
         <v>8.0279551347E10</v>
       </c>
       <c r="X47" s="25" t="n">
-        <v>7.495823038E9</v>
+        <v>8.034845038E9</v>
       </c>
       <c r="Y47" s="25" t="inlineStr"/>
       <c r="Z47" s="25" t="n">
-        <v>8.7775374385E10</v>
+        <v>8.8314396385E10</v>
       </c>
       <c r="AA47" s="25" t="inlineStr"/>
       <c r="AB47" s="25" t="inlineStr"/>
       <c r="AC47" s="26" t="n">
-        <v>0.9862764765507153</v>
+        <v>0.9923331265242205</v>
       </c>
       <c r="AD47" s="26" t="inlineStr"/>
       <c r="AE47" s="25" t="n">
-        <v>1.221348615E9</v>
+        <v>6.82326615E8</v>
       </c>
       <c r="AF47" s="25" t="inlineStr"/>
       <c r="AG47" s="25" t="inlineStr"/>
@@ -3359,20 +3359,20 @@
         <v>5.831238104E9</v>
       </c>
       <c r="X48" s="14" t="n">
-        <v>2.8323E7</v>
+        <v>5.3354E7</v>
       </c>
       <c r="Y48" s="14" t="inlineStr"/>
       <c r="Z48" s="14" t="n">
-        <v>5.859561104E9</v>
+        <v>5.884592104E9</v>
       </c>
       <c r="AA48" s="14" t="inlineStr"/>
       <c r="AB48" s="14" t="inlineStr"/>
       <c r="AC48" s="15" t="n">
-        <v>0.9897271972407177</v>
+        <v>0.9939551353122603</v>
       </c>
       <c r="AD48" s="15" t="inlineStr"/>
       <c r="AE48" s="14" t="n">
-        <v>6.0818896E7</v>
+        <v>3.5787896E7</v>
       </c>
       <c r="AF48" s="14" t="inlineStr"/>
       <c r="AG48" s="14" t="inlineStr"/>
@@ -5337,20 +5337,20 @@
         <v>2.77741E8</v>
       </c>
       <c r="X82" s="14" t="n">
-        <v>2.8323E7</v>
+        <v>5.3354E7</v>
       </c>
       <c r="Y82" s="14" t="inlineStr"/>
       <c r="Z82" s="14" t="n">
-        <v>3.06064E8</v>
+        <v>3.31095E8</v>
       </c>
       <c r="AA82" s="14" t="inlineStr"/>
       <c r="AB82" s="14" t="inlineStr"/>
       <c r="AC82" s="15" t="n">
-        <v>0.9049900057954559</v>
+        <v>0.9790032998616187</v>
       </c>
       <c r="AD82" s="15" t="inlineStr"/>
       <c r="AE82" s="14" t="n">
-        <v>3.2132E7</v>
+        <v>7101000.0</v>
       </c>
       <c r="AF82" s="14" t="inlineStr"/>
       <c r="AG82" s="14" t="inlineStr"/>
@@ -5394,20 +5394,20 @@
         <v>1.554E7</v>
       </c>
       <c r="X83" s="14" t="n">
-        <v>1400000.0</v>
+        <v>2870000.0</v>
       </c>
       <c r="Y83" s="14" t="inlineStr"/>
       <c r="Z83" s="14" t="n">
-        <v>1.694E7</v>
+        <v>1.841E7</v>
       </c>
       <c r="AA83" s="14" t="inlineStr"/>
       <c r="AB83" s="14" t="inlineStr"/>
       <c r="AC83" s="15" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9962121212121212</v>
       </c>
       <c r="AD83" s="15" t="inlineStr"/>
       <c r="AE83" s="14" t="n">
-        <v>1540000.0</v>
+        <v>70000.0</v>
       </c>
       <c r="AF83" s="14" t="inlineStr"/>
       <c r="AG83" s="14" t="inlineStr"/>
@@ -5451,20 +5451,20 @@
         <v>2.28253E8</v>
       </c>
       <c r="X84" s="14" t="n">
-        <v>2.3643E7</v>
+        <v>4.5769E7</v>
       </c>
       <c r="Y84" s="14" t="inlineStr"/>
       <c r="Z84" s="14" t="n">
-        <v>2.51896E8</v>
+        <v>2.74022E8</v>
       </c>
       <c r="AA84" s="14" t="inlineStr"/>
       <c r="AB84" s="14" t="inlineStr"/>
       <c r="AC84" s="15" t="n">
-        <v>0.9048378522062732</v>
+        <v>0.9843168527379054</v>
       </c>
       <c r="AD84" s="15" t="inlineStr"/>
       <c r="AE84" s="14" t="n">
-        <v>2.6492E7</v>
+        <v>4366000.0</v>
       </c>
       <c r="AF84" s="14" t="inlineStr"/>
       <c r="AG84" s="14" t="inlineStr"/>
@@ -5508,20 +5508,20 @@
         <v>3.3948E7</v>
       </c>
       <c r="X85" s="14" t="n">
-        <v>3280000.0</v>
+        <v>4715000.0</v>
       </c>
       <c r="Y85" s="14" t="inlineStr"/>
       <c r="Z85" s="14" t="n">
-        <v>3.7228E7</v>
+        <v>3.8663E7</v>
       </c>
       <c r="AA85" s="14" t="inlineStr"/>
       <c r="AB85" s="14" t="inlineStr"/>
       <c r="AC85" s="15" t="n">
-        <v>0.9007936507936508</v>
+        <v>0.935515873015873</v>
       </c>
       <c r="AD85" s="15" t="inlineStr"/>
       <c r="AE85" s="14" t="n">
-        <v>4100000.0</v>
+        <v>2665000.0</v>
       </c>
       <c r="AF85" s="14" t="inlineStr"/>
       <c r="AG85" s="14" t="inlineStr"/>
@@ -6082,20 +6082,20 @@
         <v>5.93914035E8</v>
       </c>
       <c r="X95" s="14" t="n">
-        <v>3.10703762E8</v>
+        <v>3.39619762E8</v>
       </c>
       <c r="Y95" s="14" t="inlineStr"/>
       <c r="Z95" s="14" t="n">
-        <v>9.04617797E8</v>
+        <v>9.33533797E8</v>
       </c>
       <c r="AA95" s="14" t="inlineStr"/>
       <c r="AB95" s="14" t="inlineStr"/>
       <c r="AC95" s="15" t="n">
-        <v>0.9302087704848075</v>
+        <v>0.9599427829003722</v>
       </c>
       <c r="AD95" s="15" t="inlineStr"/>
       <c r="AE95" s="14" t="n">
-        <v>6.7871203E7</v>
+        <v>3.8955203E7</v>
       </c>
       <c r="AF95" s="14" t="inlineStr"/>
       <c r="AG95" s="14" t="inlineStr"/>
@@ -6745,20 +6745,20 @@
         <v>3.0833E7</v>
       </c>
       <c r="X106" s="14" t="n">
-        <v>2.694E7</v>
+        <v>5.5856E7</v>
       </c>
       <c r="Y106" s="14" t="inlineStr"/>
       <c r="Z106" s="14" t="n">
-        <v>5.7773E7</v>
+        <v>8.6689E7</v>
       </c>
       <c r="AA106" s="14" t="inlineStr"/>
       <c r="AB106" s="14" t="inlineStr"/>
       <c r="AC106" s="15" t="n">
-        <v>0.6554908835108978</v>
+        <v>0.9835710314623825</v>
       </c>
       <c r="AD106" s="15" t="inlineStr"/>
       <c r="AE106" s="14" t="n">
-        <v>3.0364E7</v>
+        <v>1448000.0</v>
       </c>
       <c r="AF106" s="14" t="inlineStr"/>
       <c r="AG106" s="14" t="inlineStr"/>
@@ -6802,20 +6802,20 @@
         <v>8855000.0</v>
       </c>
       <c r="X107" s="14" t="n">
-        <v>7700000.0</v>
+        <v>1.5785E7</v>
       </c>
       <c r="Y107" s="14" t="inlineStr"/>
       <c r="Z107" s="14" t="n">
-        <v>1.6555E7</v>
+        <v>2.464E7</v>
       </c>
       <c r="AA107" s="14" t="inlineStr"/>
       <c r="AB107" s="14" t="inlineStr"/>
       <c r="AC107" s="15" t="n">
-        <v>0.6569444444444444</v>
+        <v>0.9777777777777777</v>
       </c>
       <c r="AD107" s="15" t="inlineStr"/>
       <c r="AE107" s="14" t="n">
-        <v>8645000.0</v>
+        <v>560000.0</v>
       </c>
       <c r="AF107" s="14" t="inlineStr"/>
       <c r="AG107" s="14" t="inlineStr"/>
@@ -6859,20 +6859,20 @@
         <v>2.1978E7</v>
       </c>
       <c r="X108" s="14" t="n">
-        <v>1.924E7</v>
+        <v>4.0071E7</v>
       </c>
       <c r="Y108" s="14" t="inlineStr"/>
       <c r="Z108" s="14" t="n">
-        <v>4.1218E7</v>
+        <v>6.2049E7</v>
       </c>
       <c r="AA108" s="14" t="inlineStr"/>
       <c r="AB108" s="14" t="inlineStr"/>
       <c r="AC108" s="15" t="n">
-        <v>0.6549088771310994</v>
+        <v>0.9858906525573192</v>
       </c>
       <c r="AD108" s="15" t="inlineStr"/>
       <c r="AE108" s="14" t="n">
-        <v>2.1719E7</v>
+        <v>888000.0</v>
       </c>
       <c r="AF108" s="14" t="inlineStr"/>
       <c r="AG108" s="14" t="inlineStr"/>
@@ -7162,20 +7162,20 @@
         <v>5.0689888E10</v>
       </c>
       <c r="X113" s="14" t="n">
-        <v>3.759233212E9</v>
+        <v>3.988527212E9</v>
       </c>
       <c r="Y113" s="14" t="inlineStr"/>
       <c r="Z113" s="14" t="n">
-        <v>5.4449121212E10</v>
+        <v>5.4678415212E10</v>
       </c>
       <c r="AA113" s="14" t="inlineStr"/>
       <c r="AB113" s="14" t="inlineStr"/>
       <c r="AC113" s="15" t="n">
-        <v>0.987214096723776</v>
+        <v>0.9913714139413089</v>
       </c>
       <c r="AD113" s="15" t="inlineStr"/>
       <c r="AE113" s="14" t="n">
-        <v>7.05197788E8</v>
+        <v>4.75903788E8</v>
       </c>
       <c r="AF113" s="14" t="inlineStr"/>
       <c r="AG113" s="14" t="inlineStr"/>
@@ -8906,20 +8906,20 @@
         <v>2.213268E9</v>
       </c>
       <c r="X143" s="14" t="n">
-        <v>2.19192E8</v>
+        <v>4.48486E8</v>
       </c>
       <c r="Y143" s="14" t="inlineStr"/>
       <c r="Z143" s="14" t="n">
-        <v>2.43246E9</v>
+        <v>2.661754E9</v>
       </c>
       <c r="AA143" s="14" t="inlineStr"/>
       <c r="AB143" s="14" t="inlineStr"/>
       <c r="AC143" s="15" t="n">
-        <v>0.904383945461684</v>
+        <v>0.9896350132657553</v>
       </c>
       <c r="AD143" s="15" t="inlineStr"/>
       <c r="AE143" s="14" t="n">
-        <v>2.57172E8</v>
+        <v>2.7878E7</v>
       </c>
       <c r="AF143" s="14" t="inlineStr"/>
       <c r="AG143" s="14" t="inlineStr"/>
@@ -8963,20 +8963,20 @@
         <v>1.9894E8</v>
       </c>
       <c r="X144" s="14" t="n">
-        <v>3.0567E7</v>
+        <v>5.1952E7</v>
       </c>
       <c r="Y144" s="14" t="inlineStr"/>
       <c r="Z144" s="14" t="n">
-        <v>2.29507E8</v>
+        <v>2.50892E8</v>
       </c>
       <c r="AA144" s="14" t="inlineStr"/>
       <c r="AB144" s="14" t="inlineStr"/>
       <c r="AC144" s="15" t="n">
-        <v>0.9107420634920635</v>
+        <v>0.9956031746031746</v>
       </c>
       <c r="AD144" s="15" t="inlineStr"/>
       <c r="AE144" s="14" t="n">
-        <v>2.2493E7</v>
+        <v>1108000.0</v>
       </c>
       <c r="AF144" s="14" t="inlineStr"/>
       <c r="AG144" s="14" t="inlineStr"/>
@@ -9063,20 +9063,20 @@
         <v>1.581491E9</v>
       </c>
       <c r="X146" s="14" t="n">
-        <v>1.60099E8</v>
+        <v>3.29263E8</v>
       </c>
       <c r="Y146" s="14" t="inlineStr"/>
       <c r="Z146" s="14" t="n">
-        <v>1.74159E9</v>
+        <v>1.910754E9</v>
       </c>
       <c r="AA146" s="14" t="inlineStr"/>
       <c r="AB146" s="14" t="inlineStr"/>
       <c r="AC146" s="15" t="n">
-        <v>0.9079861111111112</v>
+        <v>0.9961805555555555</v>
       </c>
       <c r="AD146" s="15" t="inlineStr"/>
       <c r="AE146" s="14" t="n">
-        <v>1.7649E8</v>
+        <v>7326000.0</v>
       </c>
       <c r="AF146" s="14" t="inlineStr"/>
       <c r="AG146" s="14" t="inlineStr"/>
@@ -9120,20 +9120,20 @@
         <v>4.32837E8</v>
       </c>
       <c r="X147" s="14" t="n">
-        <v>2.8526E7</v>
+        <v>6.7271E7</v>
       </c>
       <c r="Y147" s="14" t="inlineStr"/>
       <c r="Z147" s="14" t="n">
-        <v>4.61363E8</v>
+        <v>5.00108E8</v>
       </c>
       <c r="AA147" s="14" t="inlineStr"/>
       <c r="AB147" s="14" t="inlineStr"/>
       <c r="AC147" s="15" t="n">
-        <v>0.8880015859817689</v>
+        <v>0.9625754496181326</v>
       </c>
       <c r="AD147" s="15" t="inlineStr"/>
       <c r="AE147" s="14" t="n">
-        <v>5.8189E7</v>
+        <v>1.9444E7</v>
       </c>
       <c r="AF147" s="14" t="inlineStr"/>
       <c r="AG147" s="14" t="inlineStr"/>
@@ -9651,20 +9651,20 @@
         <v>2.3164511208E10</v>
       </c>
       <c r="X156" s="14" t="n">
-        <v>3.397563064E9</v>
+        <v>3.653344064E9</v>
       </c>
       <c r="Y156" s="14" t="inlineStr"/>
       <c r="Z156" s="14" t="n">
-        <v>2.6562074272E10</v>
+        <v>2.6817855272E10</v>
       </c>
       <c r="AA156" s="14" t="inlineStr"/>
       <c r="AB156" s="14" t="inlineStr"/>
       <c r="AC156" s="15" t="n">
-        <v>0.9856227304849602</v>
+        <v>0.9951138404428871</v>
       </c>
       <c r="AD156" s="15" t="inlineStr"/>
       <c r="AE156" s="14" t="n">
-        <v>3.87460728E8</v>
+        <v>1.31679728E8</v>
       </c>
       <c r="AF156" s="14" t="inlineStr"/>
       <c r="AG156" s="14" t="inlineStr"/>
@@ -11161,20 +11161,20 @@
         <v>1.310426E9</v>
       </c>
       <c r="X182" s="14" t="n">
-        <v>2.45185E8</v>
+        <v>5.00966E8</v>
       </c>
       <c r="Y182" s="14" t="inlineStr"/>
       <c r="Z182" s="14" t="n">
-        <v>1.555611E9</v>
+        <v>1.811392E9</v>
       </c>
       <c r="AA182" s="14" t="inlineStr"/>
       <c r="AB182" s="14" t="inlineStr"/>
       <c r="AC182" s="15" t="n">
-        <v>0.8509534593672049</v>
+        <v>0.9908712966609776</v>
       </c>
       <c r="AD182" s="15" t="inlineStr"/>
       <c r="AE182" s="14" t="n">
-        <v>2.72469E8</v>
+        <v>1.6688E7</v>
       </c>
       <c r="AF182" s="14" t="inlineStr"/>
       <c r="AG182" s="14" t="inlineStr"/>
@@ -11218,20 +11218,20 @@
         <v>1.2502E8</v>
       </c>
       <c r="X183" s="14" t="n">
-        <v>2.226E7</v>
+        <v>4.557E7</v>
       </c>
       <c r="Y183" s="14" t="inlineStr"/>
       <c r="Z183" s="14" t="n">
-        <v>1.4728E8</v>
+        <v>1.7059E8</v>
       </c>
       <c r="AA183" s="14" t="inlineStr"/>
       <c r="AB183" s="14" t="inlineStr"/>
       <c r="AC183" s="15" t="n">
-        <v>0.834920634920635</v>
+        <v>0.9670634920634921</v>
       </c>
       <c r="AD183" s="15" t="inlineStr"/>
       <c r="AE183" s="14" t="n">
-        <v>2.912E7</v>
+        <v>5810000.0</v>
       </c>
       <c r="AF183" s="14" t="inlineStr"/>
       <c r="AG183" s="14" t="inlineStr"/>
@@ -11275,20 +11275,20 @@
         <v>1.185406E9</v>
       </c>
       <c r="X184" s="14" t="n">
-        <v>2.22925E8</v>
+        <v>4.55396E8</v>
       </c>
       <c r="Y184" s="14" t="inlineStr"/>
       <c r="Z184" s="14" t="n">
-        <v>1.408331E9</v>
+        <v>1.640802E9</v>
       </c>
       <c r="AA184" s="14" t="inlineStr"/>
       <c r="AB184" s="14" t="inlineStr"/>
       <c r="AC184" s="15" t="n">
-        <v>0.852665770609319</v>
+        <v>0.9934139784946237</v>
       </c>
       <c r="AD184" s="15" t="inlineStr"/>
       <c r="AE184" s="14" t="n">
-        <v>2.43349E8</v>
+        <v>1.0878E7</v>
       </c>
       <c r="AF184" s="14" t="inlineStr"/>
       <c r="AG184" s="14" t="inlineStr"/>
@@ -11572,20 +11572,20 @@
         <v>6.228754056E9</v>
       </c>
       <c r="X189" s="25" t="n">
-        <v>5.99870547E8</v>
+        <v>7.06997907E8</v>
       </c>
       <c r="Y189" s="25" t="inlineStr"/>
       <c r="Z189" s="25" t="n">
-        <v>6.828624603E9</v>
+        <v>6.935751963E9</v>
       </c>
       <c r="AA189" s="25" t="inlineStr"/>
       <c r="AB189" s="25" t="inlineStr"/>
       <c r="AC189" s="26" t="n">
-        <v>0.9829906356681544</v>
+        <v>0.9984117779663543</v>
       </c>
       <c r="AD189" s="26" t="inlineStr"/>
       <c r="AE189" s="25" t="n">
-        <v>1.18160397E8</v>
+        <v>1.1033037E7</v>
       </c>
       <c r="AF189" s="25" t="inlineStr"/>
       <c r="AG189" s="25" t="inlineStr"/>
@@ -11635,20 +11635,20 @@
         <v>4.783558496E9</v>
       </c>
       <c r="X190" s="14" t="n">
-        <v>1.9710595E8</v>
+        <v>2.21112562E8</v>
       </c>
       <c r="Y190" s="14" t="inlineStr"/>
       <c r="Z190" s="14" t="n">
-        <v>4.980664446E9</v>
+        <v>5.004671058E9</v>
       </c>
       <c r="AA190" s="14" t="inlineStr"/>
       <c r="AB190" s="14" t="inlineStr"/>
       <c r="AC190" s="15" t="n">
-        <v>0.9943994520751426</v>
+        <v>0.9991924193745463</v>
       </c>
       <c r="AD190" s="15" t="inlineStr"/>
       <c r="AE190" s="14" t="n">
-        <v>2.8051554E7</v>
+        <v>4044942.0</v>
       </c>
       <c r="AF190" s="14" t="inlineStr"/>
       <c r="AG190" s="14" t="inlineStr"/>
@@ -11698,20 +11698,20 @@
         <v>1.777909494E9</v>
       </c>
       <c r="X191" s="14" t="n">
-        <v>1.07421314E8</v>
+        <v>1.14587926E8</v>
       </c>
       <c r="Y191" s="14" t="inlineStr"/>
       <c r="Z191" s="14" t="n">
-        <v>1.885330808E9</v>
+        <v>1.89249742E9</v>
       </c>
       <c r="AA191" s="14" t="inlineStr"/>
       <c r="AB191" s="14" t="inlineStr"/>
       <c r="AC191" s="15" t="n">
-        <v>0.9960081124758108</v>
+        <v>0.9997941873973459</v>
       </c>
       <c r="AD191" s="15" t="inlineStr"/>
       <c r="AE191" s="14" t="n">
-        <v>7556192.0</v>
+        <v>389580.0</v>
       </c>
       <c r="AF191" s="14" t="inlineStr"/>
       <c r="AG191" s="14" t="inlineStr"/>
@@ -11869,20 +11869,20 @@
         <v>5.5184254E7</v>
       </c>
       <c r="X194" s="14" t="n">
-        <v>3.3419714E7</v>
+        <v>4.0586326E7</v>
       </c>
       <c r="Y194" s="14" t="inlineStr"/>
       <c r="Z194" s="14" t="n">
-        <v>8.8603968E7</v>
+        <v>9.577058E7</v>
       </c>
       <c r="AA194" s="14" t="inlineStr"/>
       <c r="AB194" s="14" t="inlineStr"/>
       <c r="AC194" s="15" t="n">
-        <v>0.922958</v>
+        <v>0.9976102083333334</v>
       </c>
       <c r="AD194" s="15" t="inlineStr"/>
       <c r="AE194" s="14" t="n">
-        <v>7396032.0</v>
+        <v>229420.0</v>
       </c>
       <c r="AF194" s="14" t="inlineStr"/>
       <c r="AG194" s="14" t="inlineStr"/>
@@ -12317,20 +12317,20 @@
         <v>9417000.0</v>
       </c>
       <c r="X202" s="14" t="n">
-        <v>3215000.0</v>
+        <v>4155500.0</v>
       </c>
       <c r="Y202" s="14" t="inlineStr"/>
       <c r="Z202" s="14" t="n">
-        <v>1.2632E7</v>
+        <v>1.35725E7</v>
       </c>
       <c r="AA202" s="14" t="inlineStr"/>
       <c r="AB202" s="14" t="inlineStr"/>
       <c r="AC202" s="15" t="n">
-        <v>0.8489247311827957</v>
+        <v>0.912130376344086</v>
       </c>
       <c r="AD202" s="15" t="inlineStr"/>
       <c r="AE202" s="14" t="n">
-        <v>2248000.0</v>
+        <v>1307500.0</v>
       </c>
       <c r="AF202" s="14" t="inlineStr"/>
       <c r="AG202" s="14" t="inlineStr"/>
@@ -12374,20 +12374,20 @@
         <v>5781000.0</v>
       </c>
       <c r="X203" s="14" t="n">
-        <v>2407000.0</v>
+        <v>3347500.0</v>
       </c>
       <c r="Y203" s="14" t="inlineStr"/>
       <c r="Z203" s="14" t="n">
-        <v>8188000.0</v>
+        <v>9128500.0</v>
       </c>
       <c r="AA203" s="14" t="inlineStr"/>
       <c r="AB203" s="14" t="inlineStr"/>
       <c r="AC203" s="15" t="n">
-        <v>0.7888246628131022</v>
+        <v>0.879431599229287</v>
       </c>
       <c r="AD203" s="15" t="inlineStr"/>
       <c r="AE203" s="14" t="n">
-        <v>2192000.0</v>
+        <v>1251500.0</v>
       </c>
       <c r="AF203" s="14" t="inlineStr"/>
       <c r="AG203" s="14" t="inlineStr"/>
@@ -12494,20 +12494,20 @@
         <v>5.526601E7</v>
       </c>
       <c r="X205" s="14" t="n">
-        <v>1.23661E7</v>
+        <v>2.15411E7</v>
       </c>
       <c r="Y205" s="14" t="inlineStr"/>
       <c r="Z205" s="14" t="n">
-        <v>6.763211E7</v>
+        <v>7.680711E7</v>
       </c>
       <c r="AA205" s="14" t="inlineStr"/>
       <c r="AB205" s="14" t="inlineStr"/>
       <c r="AC205" s="15" t="n">
-        <v>0.8606674641452768</v>
+        <v>0.9774259681093395</v>
       </c>
       <c r="AD205" s="15" t="inlineStr"/>
       <c r="AE205" s="14" t="n">
-        <v>1.094889E7</v>
+        <v>1773890.0</v>
       </c>
       <c r="AF205" s="14" t="inlineStr"/>
       <c r="AG205" s="14" t="inlineStr"/>
@@ -12551,20 +12551,20 @@
         <v>5.526601E7</v>
       </c>
       <c r="X206" s="14" t="n">
-        <v>9616100.0</v>
+        <v>1.57661E7</v>
       </c>
       <c r="Y206" s="14" t="inlineStr"/>
       <c r="Z206" s="14" t="n">
-        <v>6.488211E7</v>
+        <v>7.103211E7</v>
       </c>
       <c r="AA206" s="14" t="inlineStr"/>
       <c r="AB206" s="14" t="inlineStr"/>
       <c r="AC206" s="15" t="n">
-        <v>0.8949133115405304</v>
+        <v>0.9797397277278934</v>
       </c>
       <c r="AD206" s="15" t="inlineStr"/>
       <c r="AE206" s="14" t="n">
-        <v>7618890.0</v>
+        <v>1468890.0</v>
       </c>
       <c r="AF206" s="14" t="inlineStr"/>
       <c r="AG206" s="14" t="inlineStr"/>
@@ -12608,20 +12608,20 @@
         <v>0.0</v>
       </c>
       <c r="X207" s="14" t="n">
-        <v>2750000.0</v>
+        <v>5775000.0</v>
       </c>
       <c r="Y207" s="14" t="inlineStr"/>
       <c r="Z207" s="14" t="n">
-        <v>2750000.0</v>
+        <v>5775000.0</v>
       </c>
       <c r="AA207" s="14" t="inlineStr"/>
       <c r="AB207" s="14" t="inlineStr"/>
       <c r="AC207" s="15" t="n">
-        <v>0.45230263157894735</v>
+        <v>0.9498355263157895</v>
       </c>
       <c r="AD207" s="15" t="inlineStr"/>
       <c r="AE207" s="14" t="n">
-        <v>3330000.0</v>
+        <v>305000.0</v>
       </c>
       <c r="AF207" s="14" t="inlineStr"/>
       <c r="AG207" s="14" t="inlineStr"/>
@@ -12671,20 +12671,20 @@
         <v>4274800.0</v>
       </c>
       <c r="X208" s="14" t="n">
-        <v>0.0</v>
+        <v>6724500.0</v>
       </c>
       <c r="Y208" s="14" t="inlineStr"/>
       <c r="Z208" s="14" t="n">
-        <v>4274800.0</v>
+        <v>1.09993E7</v>
       </c>
       <c r="AA208" s="14" t="inlineStr"/>
       <c r="AB208" s="14" t="inlineStr"/>
       <c r="AC208" s="15" t="n">
-        <v>0.3886181818181818</v>
+        <v>0.9999363636363636</v>
       </c>
       <c r="AD208" s="15" t="inlineStr"/>
       <c r="AE208" s="14" t="n">
-        <v>6725200.0</v>
+        <v>700.0</v>
       </c>
       <c r="AF208" s="14" t="inlineStr"/>
       <c r="AG208" s="14" t="inlineStr"/>
@@ -12728,20 +12728,20 @@
         <v>3964800.0</v>
       </c>
       <c r="X209" s="14" t="n">
-        <v>0.0</v>
+        <v>5035000.0</v>
       </c>
       <c r="Y209" s="14" t="inlineStr"/>
       <c r="Z209" s="14" t="n">
-        <v>3964800.0</v>
+        <v>8999800.0</v>
       </c>
       <c r="AA209" s="14" t="inlineStr"/>
       <c r="AB209" s="14" t="inlineStr"/>
       <c r="AC209" s="15" t="n">
-        <v>0.44053333333333333</v>
+        <v>0.9999777777777777</v>
       </c>
       <c r="AD209" s="15" t="inlineStr"/>
       <c r="AE209" s="14" t="n">
-        <v>5035200.0</v>
+        <v>200.0</v>
       </c>
       <c r="AF209" s="14" t="inlineStr"/>
       <c r="AG209" s="14" t="inlineStr"/>
@@ -12785,20 +12785,20 @@
         <v>310000.0</v>
       </c>
       <c r="X210" s="14" t="n">
-        <v>0.0</v>
+        <v>1689500.0</v>
       </c>
       <c r="Y210" s="14" t="inlineStr"/>
       <c r="Z210" s="14" t="n">
-        <v>310000.0</v>
+        <v>1999500.0</v>
       </c>
       <c r="AA210" s="14" t="inlineStr"/>
       <c r="AB210" s="14" t="inlineStr"/>
       <c r="AC210" s="15" t="n">
-        <v>0.155</v>
+        <v>0.99975</v>
       </c>
       <c r="AD210" s="15" t="inlineStr"/>
       <c r="AE210" s="14" t="n">
-        <v>1690000.0</v>
+        <v>500.0</v>
       </c>
       <c r="AF210" s="14" t="inlineStr"/>
       <c r="AG210" s="14" t="inlineStr"/>
@@ -13953,20 +13953,20 @@
         <v>6.74613153E8</v>
       </c>
       <c r="X230" s="14" t="n">
-        <v>3.2949829E8</v>
+        <v>4.12619038E8</v>
       </c>
       <c r="Y230" s="14" t="inlineStr"/>
       <c r="Z230" s="14" t="n">
-        <v>1.004111443E9</v>
+        <v>1.087232191E9</v>
       </c>
       <c r="AA230" s="14" t="inlineStr"/>
       <c r="AB230" s="14" t="inlineStr"/>
       <c r="AC230" s="15" t="n">
-        <v>0.9185192286758417</v>
+        <v>0.9945546188431053</v>
       </c>
       <c r="AD230" s="15" t="inlineStr"/>
       <c r="AE230" s="14" t="n">
-        <v>8.9073557E7</v>
+        <v>5952809.0</v>
       </c>
       <c r="AF230" s="14" t="inlineStr"/>
       <c r="AG230" s="14" t="inlineStr"/>
@@ -14313,20 +14313,20 @@
         <v>1.34221533E8</v>
       </c>
       <c r="X236" s="14" t="n">
-        <v>1.508445E8</v>
+        <v>2.1079542E8</v>
       </c>
       <c r="Y236" s="14" t="inlineStr"/>
       <c r="Z236" s="14" t="n">
-        <v>2.85066033E8</v>
+        <v>3.45016953E8</v>
       </c>
       <c r="AA236" s="14" t="inlineStr"/>
       <c r="AB236" s="14" t="inlineStr"/>
       <c r="AC236" s="15" t="n">
-        <v>0.8215159452449567</v>
+        <v>0.994285167146974</v>
       </c>
       <c r="AD236" s="15" t="inlineStr"/>
       <c r="AE236" s="14" t="n">
-        <v>6.1933967E7</v>
+        <v>1983047.0</v>
       </c>
       <c r="AF236" s="14" t="inlineStr"/>
       <c r="AG236" s="14" t="inlineStr"/>
@@ -14427,20 +14427,20 @@
         <v>2.1347299E7</v>
       </c>
       <c r="X238" s="14" t="n">
-        <v>1.47355E7</v>
+        <v>1.57755E7</v>
       </c>
       <c r="Y238" s="14" t="inlineStr"/>
       <c r="Z238" s="14" t="n">
-        <v>3.6082799E7</v>
+        <v>3.7122799E7</v>
       </c>
       <c r="AA238" s="14" t="inlineStr"/>
       <c r="AB238" s="14" t="inlineStr"/>
       <c r="AC238" s="15" t="n">
-        <v>0.9673672654155496</v>
+        <v>0.9952493029490617</v>
       </c>
       <c r="AD238" s="15" t="inlineStr"/>
       <c r="AE238" s="14" t="n">
-        <v>1217201.0</v>
+        <v>177201.0</v>
       </c>
       <c r="AF238" s="14" t="inlineStr"/>
       <c r="AG238" s="14" t="inlineStr"/>
@@ -14484,20 +14484,20 @@
         <v>2.5327E7</v>
       </c>
       <c r="X239" s="14" t="n">
-        <v>375000.0</v>
+        <v>595920.0</v>
       </c>
       <c r="Y239" s="14" t="inlineStr"/>
       <c r="Z239" s="14" t="n">
-        <v>2.5702E7</v>
+        <v>2.592292E7</v>
       </c>
       <c r="AA239" s="14" t="inlineStr"/>
       <c r="AB239" s="14" t="inlineStr"/>
       <c r="AC239" s="15" t="n">
-        <v>0.9904431599229288</v>
+        <v>0.9989564547206166</v>
       </c>
       <c r="AD239" s="15" t="inlineStr"/>
       <c r="AE239" s="14" t="n">
-        <v>248000.0</v>
+        <v>27080.0</v>
       </c>
       <c r="AF239" s="14" t="inlineStr"/>
       <c r="AG239" s="14" t="inlineStr"/>
@@ -14598,20 +14598,20 @@
         <v>4421000.0</v>
       </c>
       <c r="X241" s="14" t="n">
-        <v>7.4724E7</v>
+        <v>1.18724E8</v>
       </c>
       <c r="Y241" s="14" t="inlineStr"/>
       <c r="Z241" s="14" t="n">
-        <v>7.9145E7</v>
+        <v>1.23145E8</v>
       </c>
       <c r="AA241" s="14" t="inlineStr"/>
       <c r="AB241" s="14" t="inlineStr"/>
       <c r="AC241" s="15" t="n">
-        <v>0.640331715210356</v>
+        <v>0.9963187702265373</v>
       </c>
       <c r="AD241" s="15" t="inlineStr"/>
       <c r="AE241" s="14" t="n">
-        <v>4.4455E7</v>
+        <v>455000.0</v>
       </c>
       <c r="AF241" s="14" t="inlineStr"/>
       <c r="AG241" s="14" t="inlineStr"/>
@@ -14712,20 +14712,20 @@
         <v>1.2143622E7</v>
       </c>
       <c r="X243" s="14" t="n">
-        <v>0.0</v>
+        <v>4395000.0</v>
       </c>
       <c r="Y243" s="14" t="inlineStr"/>
       <c r="Z243" s="14" t="n">
-        <v>1.2143622E7</v>
+        <v>1.6538622E7</v>
       </c>
       <c r="AA243" s="14" t="inlineStr"/>
       <c r="AB243" s="14" t="inlineStr"/>
       <c r="AC243" s="15" t="n">
-        <v>0.7315434939759036</v>
+        <v>0.996302530120482</v>
       </c>
       <c r="AD243" s="15" t="inlineStr"/>
       <c r="AE243" s="14" t="n">
-        <v>4456378.0</v>
+        <v>61378.0</v>
       </c>
       <c r="AF243" s="14" t="inlineStr"/>
       <c r="AG243" s="14" t="inlineStr"/>
@@ -14826,20 +14826,20 @@
         <v>1576500.0</v>
       </c>
       <c r="X245" s="14" t="n">
-        <v>1800000.0</v>
+        <v>2400000.0</v>
       </c>
       <c r="Y245" s="14" t="inlineStr"/>
       <c r="Z245" s="14" t="n">
-        <v>3376500.0</v>
+        <v>3976500.0</v>
       </c>
       <c r="AA245" s="14" t="inlineStr"/>
       <c r="AB245" s="14" t="inlineStr"/>
       <c r="AC245" s="15" t="n">
-        <v>0.8136144578313254</v>
+        <v>0.9581927710843373</v>
       </c>
       <c r="AD245" s="15" t="inlineStr"/>
       <c r="AE245" s="14" t="n">
-        <v>773500.0</v>
+        <v>173500.0</v>
       </c>
       <c r="AF245" s="14" t="inlineStr"/>
       <c r="AG245" s="14" t="inlineStr"/>
@@ -15168,20 +15168,20 @@
         <v>0.0</v>
       </c>
       <c r="X251" s="14" t="n">
-        <v>0.0</v>
+        <v>5695000.0</v>
       </c>
       <c r="Y251" s="14" t="inlineStr"/>
       <c r="Z251" s="14" t="n">
-        <v>0.0</v>
+        <v>5695000.0</v>
       </c>
       <c r="AA251" s="14" t="inlineStr"/>
       <c r="AB251" s="14" t="inlineStr"/>
       <c r="AC251" s="15" t="n">
-        <v>0.0</v>
+        <v>0.9991228070175439</v>
       </c>
       <c r="AD251" s="15" t="inlineStr"/>
       <c r="AE251" s="14" t="n">
-        <v>5700000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="AF251" s="14" t="inlineStr"/>
       <c r="AG251" s="14" t="inlineStr"/>
@@ -15225,20 +15225,20 @@
         <v>5413000.0</v>
       </c>
       <c r="X252" s="14" t="n">
-        <v>0.0</v>
+        <v>4000000.0</v>
       </c>
       <c r="Y252" s="14" t="inlineStr"/>
       <c r="Z252" s="14" t="n">
-        <v>5413000.0</v>
+        <v>9413000.0</v>
       </c>
       <c r="AA252" s="14" t="inlineStr"/>
       <c r="AB252" s="14" t="inlineStr"/>
       <c r="AC252" s="15" t="n">
-        <v>0.5697894736842105</v>
+        <v>0.9908421052631579</v>
       </c>
       <c r="AD252" s="15" t="inlineStr"/>
       <c r="AE252" s="14" t="n">
-        <v>4087000.0</v>
+        <v>87000.0</v>
       </c>
       <c r="AF252" s="14" t="inlineStr"/>
       <c r="AG252" s="14" t="inlineStr"/>
@@ -15388,20 +15388,20 @@
         <v>2.11521335E8</v>
       </c>
       <c r="X255" s="14" t="n">
-        <v>8.661379E7</v>
+        <v>1.09783618E8</v>
       </c>
       <c r="Y255" s="14" t="inlineStr"/>
       <c r="Z255" s="14" t="n">
-        <v>2.98135125E8</v>
+        <v>3.21304953E8</v>
       </c>
       <c r="AA255" s="14" t="inlineStr"/>
       <c r="AB255" s="14" t="inlineStr"/>
       <c r="AC255" s="15" t="n">
-        <v>0.918993033614352</v>
+        <v>0.9904133686790069</v>
       </c>
       <c r="AD255" s="15" t="inlineStr"/>
       <c r="AE255" s="14" t="n">
-        <v>2.6279875E7</v>
+        <v>3110047.0</v>
       </c>
       <c r="AF255" s="14" t="inlineStr"/>
       <c r="AG255" s="14" t="inlineStr"/>
@@ -15445,20 +15445,20 @@
         <v>1.396E7</v>
       </c>
       <c r="X256" s="14" t="n">
-        <v>5220000.0</v>
+        <v>8440000.0</v>
       </c>
       <c r="Y256" s="14" t="inlineStr"/>
       <c r="Z256" s="14" t="n">
-        <v>1.918E7</v>
+        <v>2.24E7</v>
       </c>
       <c r="AA256" s="14" t="inlineStr"/>
       <c r="AB256" s="14" t="inlineStr"/>
       <c r="AC256" s="15" t="n">
-        <v>0.8498006202924235</v>
+        <v>0.9924678777137793</v>
       </c>
       <c r="AD256" s="15" t="inlineStr"/>
       <c r="AE256" s="14" t="n">
-        <v>3390000.0</v>
+        <v>170000.0</v>
       </c>
       <c r="AF256" s="14" t="inlineStr"/>
       <c r="AG256" s="14" t="inlineStr"/>
@@ -15559,20 +15559,20 @@
         <v>2.9845218E7</v>
       </c>
       <c r="X258" s="14" t="n">
-        <v>1.279805E7</v>
+        <v>1.510805E7</v>
       </c>
       <c r="Y258" s="14" t="inlineStr"/>
       <c r="Z258" s="14" t="n">
-        <v>4.2643268E7</v>
+        <v>4.4953268E7</v>
       </c>
       <c r="AA258" s="14" t="inlineStr"/>
       <c r="AB258" s="14" t="inlineStr"/>
       <c r="AC258" s="15" t="n">
-        <v>0.9476281777777777</v>
+        <v>0.9989615111111111</v>
       </c>
       <c r="AD258" s="15" t="inlineStr"/>
       <c r="AE258" s="14" t="n">
-        <v>2356732.0</v>
+        <v>46732.0</v>
       </c>
       <c r="AF258" s="14" t="inlineStr"/>
       <c r="AG258" s="14" t="inlineStr"/>
@@ -15616,20 +15616,20 @@
         <v>1.22043496E8</v>
       </c>
       <c r="X259" s="14" t="n">
-        <v>4.7543521E7</v>
+        <v>5.1816623E7</v>
       </c>
       <c r="Y259" s="14" t="inlineStr"/>
       <c r="Z259" s="14" t="n">
-        <v>1.69587017E8</v>
+        <v>1.73860119E8</v>
       </c>
       <c r="AA259" s="14" t="inlineStr"/>
       <c r="AB259" s="14" t="inlineStr"/>
       <c r="AC259" s="15" t="n">
-        <v>0.9731559234499182</v>
+        <v>0.9976766361575761</v>
       </c>
       <c r="AD259" s="15" t="inlineStr"/>
       <c r="AE259" s="14" t="n">
-        <v>4677983.0</v>
+        <v>404881.0</v>
       </c>
       <c r="AF259" s="14" t="inlineStr"/>
       <c r="AG259" s="14" t="inlineStr"/>
@@ -15673,20 +15673,20 @@
         <v>4147992.0</v>
       </c>
       <c r="X260" s="14" t="n">
-        <v>90000.0</v>
+        <v>225000.0</v>
       </c>
       <c r="Y260" s="14" t="inlineStr"/>
       <c r="Z260" s="14" t="n">
-        <v>4237992.0</v>
+        <v>4372992.0</v>
       </c>
       <c r="AA260" s="14" t="inlineStr"/>
       <c r="AB260" s="14" t="inlineStr"/>
       <c r="AC260" s="15" t="n">
-        <v>0.941776</v>
+        <v>0.971776</v>
       </c>
       <c r="AD260" s="15" t="inlineStr"/>
       <c r="AE260" s="14" t="n">
-        <v>262008.0</v>
+        <v>127008.0</v>
       </c>
       <c r="AF260" s="14" t="inlineStr"/>
       <c r="AG260" s="14" t="inlineStr"/>
@@ -15787,20 +15787,20 @@
         <v>1000052.0</v>
       </c>
       <c r="X262" s="14" t="n">
-        <v>0.0</v>
+        <v>7986000.0</v>
       </c>
       <c r="Y262" s="14" t="inlineStr"/>
       <c r="Z262" s="14" t="n">
-        <v>1000052.0</v>
+        <v>8986052.0</v>
       </c>
       <c r="AA262" s="14" t="inlineStr"/>
       <c r="AB262" s="14" t="inlineStr"/>
       <c r="AC262" s="15" t="n">
-        <v>0.11099356270810211</v>
+        <v>0.997342064372919</v>
       </c>
       <c r="AD262" s="15" t="inlineStr"/>
       <c r="AE262" s="14" t="n">
-        <v>8009948.0</v>
+        <v>23948.0</v>
       </c>
       <c r="AF262" s="14" t="inlineStr"/>
       <c r="AG262" s="14" t="inlineStr"/>
@@ -15844,20 +15844,20 @@
         <v>1978406.0</v>
       </c>
       <c r="X263" s="14" t="n">
-        <v>0.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="Y263" s="14" t="inlineStr"/>
       <c r="Z263" s="14" t="n">
-        <v>1978406.0</v>
+        <v>2978406.0</v>
       </c>
       <c r="AA263" s="14" t="inlineStr"/>
       <c r="AB263" s="14" t="inlineStr"/>
       <c r="AC263" s="15" t="n">
-        <v>0.6486577049180328</v>
+        <v>0.9765265573770492</v>
       </c>
       <c r="AD263" s="15" t="inlineStr"/>
       <c r="AE263" s="14" t="n">
-        <v>1071594.0</v>
+        <v>71594.0</v>
       </c>
       <c r="AF263" s="14" t="inlineStr"/>
       <c r="AG263" s="14" t="inlineStr"/>
@@ -15901,20 +15901,20 @@
         <v>8450284.0</v>
       </c>
       <c r="X264" s="14" t="n">
-        <v>2385941.0</v>
+        <v>3365941.0</v>
       </c>
       <c r="Y264" s="14" t="inlineStr"/>
       <c r="Z264" s="14" t="n">
-        <v>1.0836225E7</v>
+        <v>1.1816225E7</v>
       </c>
       <c r="AA264" s="14" t="inlineStr"/>
       <c r="AB264" s="14" t="inlineStr"/>
       <c r="AC264" s="15" t="n">
-        <v>0.90301875</v>
+        <v>0.9846854166666666</v>
       </c>
       <c r="AD264" s="15" t="inlineStr"/>
       <c r="AE264" s="14" t="n">
-        <v>1163775.0</v>
+        <v>183775.0</v>
       </c>
       <c r="AF264" s="14" t="inlineStr"/>
       <c r="AG264" s="14" t="inlineStr"/>
@@ -15958,20 +15958,20 @@
         <v>1167558.0</v>
       </c>
       <c r="X265" s="14" t="n">
-        <v>0.0</v>
+        <v>500000.0</v>
       </c>
       <c r="Y265" s="14" t="inlineStr"/>
       <c r="Z265" s="14" t="n">
-        <v>1167558.0</v>
+        <v>1667558.0</v>
       </c>
       <c r="AA265" s="14" t="inlineStr"/>
       <c r="AB265" s="14" t="inlineStr"/>
       <c r="AC265" s="15" t="n">
-        <v>0.583779</v>
+        <v>0.833779</v>
       </c>
       <c r="AD265" s="15" t="inlineStr"/>
       <c r="AE265" s="14" t="n">
-        <v>832442.0</v>
+        <v>332442.0</v>
       </c>
       <c r="AF265" s="14" t="inlineStr"/>
       <c r="AG265" s="14" t="inlineStr"/>
@@ -16015,20 +16015,20 @@
         <v>3760846.0</v>
       </c>
       <c r="X266" s="14" t="n">
-        <v>9601868.0</v>
+        <v>1.1772594E7</v>
       </c>
       <c r="Y266" s="14" t="inlineStr"/>
       <c r="Z266" s="14" t="n">
-        <v>1.3362714E7</v>
+        <v>1.553344E7</v>
       </c>
       <c r="AA266" s="14" t="inlineStr"/>
       <c r="AB266" s="14" t="inlineStr"/>
       <c r="AC266" s="15" t="n">
-        <v>0.855487451984635</v>
+        <v>0.9944583866837388</v>
       </c>
       <c r="AD266" s="15" t="inlineStr"/>
       <c r="AE266" s="14" t="n">
-        <v>2257286.0</v>
+        <v>86560.0</v>
       </c>
       <c r="AF266" s="14" t="inlineStr"/>
       <c r="AG266" s="14" t="inlineStr"/>
@@ -16129,20 +16129,20 @@
         <v>7889000.0</v>
       </c>
       <c r="X268" s="14" t="n">
-        <v>581410.0</v>
+        <v>666410.0</v>
       </c>
       <c r="Y268" s="14" t="inlineStr"/>
       <c r="Z268" s="14" t="n">
-        <v>8470410.0</v>
+        <v>8555410.0</v>
       </c>
       <c r="AA268" s="14" t="inlineStr"/>
       <c r="AB268" s="14" t="inlineStr"/>
       <c r="AC268" s="15" t="n">
-        <v>0.9011074468085106</v>
+        <v>0.91015</v>
       </c>
       <c r="AD268" s="15" t="inlineStr"/>
       <c r="AE268" s="14" t="n">
-        <v>929590.0</v>
+        <v>844590.0</v>
       </c>
       <c r="AF268" s="14" t="inlineStr"/>
       <c r="AG268" s="14" t="inlineStr"/>
@@ -16300,20 +16300,20 @@
         <v>0.0</v>
       </c>
       <c r="X271" s="14" t="n">
-        <v>488000.0</v>
+        <v>998000.0</v>
       </c>
       <c r="Y271" s="14" t="inlineStr"/>
       <c r="Z271" s="14" t="n">
-        <v>488000.0</v>
+        <v>998000.0</v>
       </c>
       <c r="AA271" s="14" t="inlineStr"/>
       <c r="AB271" s="14" t="inlineStr"/>
       <c r="AC271" s="15" t="n">
-        <v>0.488</v>
+        <v>0.998</v>
       </c>
       <c r="AD271" s="15" t="inlineStr"/>
       <c r="AE271" s="14" t="n">
-        <v>512000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="AF271" s="14" t="inlineStr"/>
       <c r="AG271" s="14" t="inlineStr"/>
